--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2463BBAB-D7D3-4559-9E45-D05724FC9F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2DCD291-834A-47F7-9D2A-584E4EC37E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7737" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7737" uniqueCount="126">
   <si>
     <t>Date</t>
   </si>
@@ -398,12 +398,6 @@
   </si>
   <si>
     <t>Fallou SOLY1</t>
-  </si>
-  <si>
-    <t>Fallou SOLY2</t>
-  </si>
-  <si>
-    <t>Fallou SOLY3</t>
   </si>
 </sst>
 </file>
@@ -3299,7 +3293,7 @@
         <v>19</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1" t="s">
@@ -3341,7 +3335,7 @@
         <v>19</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>127</v>
+        <v>79</v>
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1" t="s">

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="J27" s="1" t="n">
-        <v>0.11111111</v>
+        <v>0.22222222</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>3111.111</v>
+        <v>6222.222</v>
       </c>
       <c r="L27" s="1"/>
       <c r="M27" s="1" t="n">
@@ -4465,7 +4465,7 @@
         <v>0.041666668</v>
       </c>
       <c r="K80" s="1" t="n">
-        <v>1083.3334</v>
+        <v>791.6667</v>
       </c>
       <c r="L80" s="1" t="n">
         <v>2000.0</v>
@@ -4581,7 +4581,7 @@
         <v>0.29166666</v>
       </c>
       <c r="K82" s="1" t="n">
-        <v>7583.3335</v>
+        <v>5541.6665</v>
       </c>
       <c r="L82" s="1" t="n">
         <v>2000.0</v>
@@ -4929,7 +4929,7 @@
         <v>0.5</v>
       </c>
       <c r="K88" s="1" t="n">
-        <v>13000.0</v>
+        <v>9500.0</v>
       </c>
       <c r="L88" s="1" t="n">
         <v>2000.0</v>
@@ -5045,7 +5045,7 @@
         <v>0.041666668</v>
       </c>
       <c r="K90" s="1" t="n">
-        <v>1083.3334</v>
+        <v>791.6667</v>
       </c>
       <c r="L90" s="1" t="n">
         <v>2000.0</v>
@@ -5103,7 +5103,7 @@
         <v>0.041666668</v>
       </c>
       <c r="K91" s="1" t="n">
-        <v>1083.3334</v>
+        <v>791.6667</v>
       </c>
       <c r="L91" s="1" t="n">
         <v>2000.0</v>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -5650,10 +5650,10 @@
         </is>
       </c>
       <c r="J102" s="1" t="n">
-        <v>39.625</v>
+        <v>26.625</v>
       </c>
       <c r="K102" s="1" t="n">
-        <v>594375.0</v>
+        <v>399375.0</v>
       </c>
       <c r="L102" s="1"/>
       <c r="M102" s="1"/>
@@ -5698,10 +5698,10 @@
         </is>
       </c>
       <c r="J103" s="1" t="n">
-        <v>12.777778</v>
+        <v>12.888889</v>
       </c>
       <c r="K103" s="1" t="n">
-        <v>332222.22</v>
+        <v>335111.12</v>
       </c>
       <c r="L103" s="1"/>
       <c r="M103" s="1"/>
@@ -5749,7 +5749,7 @@
         <v>9.083333</v>
       </c>
       <c r="K104" s="1" t="n">
-        <v>236166.67</v>
+        <v>172583.33</v>
       </c>
       <c r="L104" s="1"/>
       <c r="M104" s="1"/>
@@ -5842,10 +5842,10 @@
         </is>
       </c>
       <c r="J106" s="1" t="n">
-        <v>21.0</v>
+        <v>21.11111</v>
       </c>
       <c r="K106" s="1" t="n">
-        <v>588000.0</v>
+        <v>591111.1</v>
       </c>
       <c r="L106" s="1"/>
       <c r="M106" s="1"/>
@@ -5986,10 +5986,10 @@
         </is>
       </c>
       <c r="J109" s="1" t="n">
-        <v>7.1666665</v>
+        <v>7.25</v>
       </c>
       <c r="K109" s="1" t="n">
-        <v>240083.33</v>
+        <v>242875.0</v>
       </c>
       <c r="L109" s="1"/>
       <c r="M109" s="1"/>
@@ -6034,10 +6034,10 @@
         </is>
       </c>
       <c r="J110" s="1" t="n">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
       <c r="K110" s="1" t="n">
-        <v>336000.0</v>
+        <v>315000.0</v>
       </c>
       <c r="L110" s="1"/>
       <c r="M110" s="1"/>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -6370,10 +6370,10 @@
         </is>
       </c>
       <c r="J117" s="1" t="n">
-        <v>6.0</v>
+        <v>6.4</v>
       </c>
       <c r="K117" s="1" t="n">
-        <v>27000.0</v>
+        <v>28800.0</v>
       </c>
       <c r="L117" s="1"/>
       <c r="M117" s="1"/>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -35312,10 +35312,10 @@
         </is>
       </c>
       <c r="J650" s="1" t="n">
-        <v>59.8</v>
+        <v>35.2</v>
       </c>
       <c r="K650" s="1" t="n">
-        <v>717600.0</v>
+        <v>422400.0</v>
       </c>
       <c r="L650" s="1"/>
       <c r="M650" s="1"/>
@@ -35987,7 +35987,7 @@
         <v>10.0</v>
       </c>
       <c r="K664" s="1" t="n">
-        <v>260000.0</v>
+        <v>190000.0</v>
       </c>
       <c r="L664" s="1"/>
       <c r="M664" s="1"/>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="J29" s="1" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>12000.0</v>
+        <v>24000.0</v>
       </c>
       <c r="L29" s="1" t="n">
         <v>1000.0</v>
@@ -35312,10 +35312,10 @@
         </is>
       </c>
       <c r="J650" s="1" t="n">
-        <v>35.2</v>
+        <v>34.2</v>
       </c>
       <c r="K650" s="1" t="n">
-        <v>422400.0</v>
+        <v>410400.0</v>
       </c>
       <c r="L650" s="1"/>
       <c r="M650" s="1"/>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -4997,7 +4997,9 @@
       <c r="A93" s="2" t="n">
         <v>46186.0</v>
       </c>
-      <c r="B93" s="1"/>
+      <c r="B93" s="1" t="n">
+        <v>0.0</v>
+      </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
           <t>TATA 2</t>
@@ -5022,10 +5024,10 @@
         </is>
       </c>
       <c r="J93" s="1" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="K93" s="1" t="n">
-        <v>168000.0</v>
+        <v>180000.0</v>
       </c>
       <c r="L93" s="1"/>
       <c r="M93" s="1"/>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95642DBC-81DD-4EB7-B7F3-65C7915C7B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA914DE-593B-4DBC-80F5-2B8F74FDCE50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8" yWindow="8" windowWidth="19185" windowHeight="10784" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15" yWindow="15" windowWidth="19185" windowHeight="10785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1994,7 +1994,7 @@
         <v>35</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1" t="s">
@@ -2036,7 +2036,7 @@
         <v>35</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1" t="s">
@@ -6170,7 +6170,7 @@
         <v>1</v>
       </c>
       <c r="K132" s="1">
-        <v>54000</v>
+        <v>55000</v>
       </c>
       <c r="L132" s="1"/>
       <c r="M132" s="1"/>
@@ -6214,7 +6214,7 @@
         <v>2</v>
       </c>
       <c r="K133" s="1">
-        <v>108000</v>
+        <v>110000</v>
       </c>
       <c r="L133" s="1"/>
       <c r="M133" s="1"/>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA914DE-593B-4DBC-80F5-2B8F74FDCE50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8298A639-3224-470F-9B62-35571CE0DD00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15" yWindow="15" windowWidth="19185" windowHeight="10785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -4574,7 +4587,9 @@
       <c r="K94" s="1">
         <v>600</v>
       </c>
-      <c r="L94" s="1"/>
+      <c r="L94" s="1">
+        <v>30000</v>
+      </c>
       <c r="M94" s="1">
         <v>3500</v>
       </c>
@@ -7123,7 +7138,7 @@
         <v>3666.6667000000002</v>
       </c>
       <c r="L156" s="1">
-        <v>3000</v>
+        <v>23000</v>
       </c>
       <c r="M156" s="1"/>
       <c r="N156" s="1"/>
@@ -8767,7 +8782,7 @@
         <v>0</v>
       </c>
       <c r="L197" s="1">
-        <v>3000</v>
+        <v>33000</v>
       </c>
       <c r="M197" s="1"/>
       <c r="N197" s="1"/>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F8B028-B05F-4D99-A777-4D6B1A3ED82A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC78EA0-AF2F-489A-85B7-1299A5694803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15" yWindow="15" windowWidth="19185" windowHeight="10785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17167,7 +17167,9 @@
       <c r="K405" s="1">
         <v>600</v>
       </c>
-      <c r="L405" s="1"/>
+      <c r="L405" s="1">
+        <v>30000</v>
+      </c>
       <c r="M405" s="1">
         <v>3500</v>
       </c>
@@ -19716,7 +19718,7 @@
         <v>3666.6667000000002</v>
       </c>
       <c r="L467" s="1">
-        <v>3000</v>
+        <v>23000</v>
       </c>
       <c r="M467" s="1"/>
       <c r="N467" s="1"/>
@@ -21360,7 +21362,7 @@
         <v>0</v>
       </c>
       <c r="L508" s="1">
-        <v>3000</v>
+        <v>33000</v>
       </c>
       <c r="M508" s="1"/>
       <c r="N508" s="1"/>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -8,14 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D4BFFA8-77A3-4CE7-AD67-8609ADB3BCE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460C97C8-D2F0-4A61-9288-9FC4AC2BC063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15" yWindow="15" windowWidth="19185" windowHeight="10785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$755</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -59900,6 +59916,7 @@
       <c r="P2346" s="1"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:P755" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460C97C8-D2F0-4A61-9288-9FC4AC2BC063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16546959-7765-4219-9465-424B71C5B0D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15" yWindow="15" windowWidth="19185" windowHeight="10785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$755</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$754</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4669" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4661" uniqueCount="114">
   <si>
     <t>Date</t>
   </si>
@@ -363,12 +363,6 @@
   </si>
   <si>
     <t>CASTOR</t>
-  </si>
-  <si>
-    <t>Autre</t>
-  </si>
-  <si>
-    <t>Mamadou BA</t>
   </si>
   <si>
     <t>YENE</t>
@@ -764,7 +758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P2346"/>
+  <dimension ref="A1:P2345"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.3984375" customWidth="1"/>
@@ -5514,7 +5508,7 @@
         <v>3875</v>
       </c>
       <c r="L119" s="1">
-        <v>1000</v>
+        <v>51000</v>
       </c>
       <c r="M119" s="1"/>
       <c r="N119" s="1"/>
@@ -7154,7 +7148,7 @@
         <v>23000</v>
       </c>
       <c r="L158" s="1">
-        <v>3200</v>
+        <v>53200</v>
       </c>
       <c r="M158" s="1">
         <v>3000</v>
@@ -17643,25 +17637,23 @@
         <v>108</v>
       </c>
       <c r="G418" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="H418" s="1" t="s">
-        <v>110</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="H418" s="1"/>
       <c r="I418" s="1" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="J418" s="1">
-        <v>10</v>
+        <v>0.91666669999999995</v>
       </c>
       <c r="K418" s="1">
-        <v>195000</v>
+        <v>30708.333999999999</v>
       </c>
       <c r="L418" s="1"/>
       <c r="M418" s="1"/>
       <c r="N418" s="1"/>
       <c r="O418" s="1">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="P418" s="1" t="s">
         <v>20</v>
@@ -17691,19 +17683,19 @@
       </c>
       <c r="H419" s="1"/>
       <c r="I419" s="1" t="s">
-        <v>97</v>
+        <v>40</v>
       </c>
       <c r="J419" s="1">
-        <v>0.91666669999999995</v>
+        <v>4.1666667999999997E-2</v>
       </c>
       <c r="K419" s="1">
-        <v>30708.333999999999</v>
+        <v>1104.1666</v>
       </c>
       <c r="L419" s="1"/>
       <c r="M419" s="1"/>
       <c r="N419" s="1"/>
       <c r="O419" s="1">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="P419" s="1" t="s">
         <v>20</v>
@@ -17729,23 +17721,23 @@
         <v>108</v>
       </c>
       <c r="G420" s="1" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="H420" s="1"/>
       <c r="I420" s="1" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="J420" s="1">
-        <v>4.1666667999999997E-2</v>
+        <v>1.1111112000000001</v>
       </c>
       <c r="K420" s="1">
-        <v>1104.1666</v>
+        <v>28888.888999999999</v>
       </c>
       <c r="L420" s="1"/>
       <c r="M420" s="1"/>
       <c r="N420" s="1"/>
       <c r="O420" s="1">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="P420" s="1" t="s">
         <v>20</v>
@@ -17759,10 +17751,10 @@
         <v>0</v>
       </c>
       <c r="C421" s="1" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="D421" s="1" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="E421" s="1" t="s">
         <v>41</v>
@@ -17771,23 +17763,23 @@
         <v>108</v>
       </c>
       <c r="G421" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H421" s="1"/>
       <c r="I421" s="1" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="J421" s="1">
-        <v>1.1111112000000001</v>
+        <v>0.625</v>
       </c>
       <c r="K421" s="1">
-        <v>28888.888999999999</v>
+        <v>9375</v>
       </c>
       <c r="L421" s="1"/>
       <c r="M421" s="1"/>
       <c r="N421" s="1"/>
       <c r="O421" s="1">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="P421" s="1" t="s">
         <v>20</v>
@@ -17817,19 +17809,19 @@
       </c>
       <c r="H422" s="1"/>
       <c r="I422" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J422" s="1">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="K422" s="1">
-        <v>9375</v>
+        <v>9000</v>
       </c>
       <c r="L422" s="1"/>
       <c r="M422" s="1"/>
       <c r="N422" s="1"/>
       <c r="O422" s="1">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="P422" s="1" t="s">
         <v>20</v>
@@ -17855,23 +17847,23 @@
         <v>108</v>
       </c>
       <c r="G423" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H423" s="1"/>
       <c r="I423" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J423" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K423" s="1">
-        <v>9000</v>
+        <v>7500</v>
       </c>
       <c r="L423" s="1"/>
       <c r="M423" s="1"/>
       <c r="N423" s="1"/>
       <c r="O423" s="1">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="P423" s="1" t="s">
         <v>20</v>
@@ -17901,19 +17893,19 @@
       </c>
       <c r="H424" s="1"/>
       <c r="I424" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J424" s="1">
-        <v>0.5</v>
+        <v>0.58333330000000005</v>
       </c>
       <c r="K424" s="1">
-        <v>7500</v>
+        <v>5250</v>
       </c>
       <c r="L424" s="1"/>
       <c r="M424" s="1"/>
       <c r="N424" s="1"/>
       <c r="O424" s="1">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="P424" s="1" t="s">
         <v>20</v>
@@ -17939,23 +17931,23 @@
         <v>108</v>
       </c>
       <c r="G425" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H425" s="1"/>
       <c r="I425" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J425" s="1">
-        <v>0.58333330000000005</v>
+        <v>0.5</v>
       </c>
       <c r="K425" s="1">
-        <v>5250</v>
+        <v>5500</v>
       </c>
       <c r="L425" s="1"/>
       <c r="M425" s="1"/>
       <c r="N425" s="1"/>
       <c r="O425" s="1">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="P425" s="1" t="s">
         <v>20</v>
@@ -17981,23 +17973,23 @@
         <v>108</v>
       </c>
       <c r="G426" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H426" s="1"/>
       <c r="I426" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J426" s="1">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="K426" s="1">
-        <v>5500</v>
+        <v>13750</v>
       </c>
       <c r="L426" s="1"/>
       <c r="M426" s="1"/>
       <c r="N426" s="1"/>
       <c r="O426" s="1">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="P426" s="1" t="s">
         <v>20</v>
@@ -18023,23 +18015,23 @@
         <v>108</v>
       </c>
       <c r="G427" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H427" s="1"/>
       <c r="I427" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J427" s="1">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="K427" s="1">
-        <v>13750</v>
+        <v>5500</v>
       </c>
       <c r="L427" s="1"/>
       <c r="M427" s="1"/>
       <c r="N427" s="1"/>
       <c r="O427" s="1">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="P427" s="1" t="s">
         <v>20</v>
@@ -18065,7 +18057,7 @@
         <v>108</v>
       </c>
       <c r="G428" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H428" s="1"/>
       <c r="I428" s="1" t="s">
@@ -18081,7 +18073,7 @@
       <c r="M428" s="1"/>
       <c r="N428" s="1"/>
       <c r="O428" s="1">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="P428" s="1" t="s">
         <v>20</v>
@@ -18107,23 +18099,23 @@
         <v>108</v>
       </c>
       <c r="G429" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H429" s="1"/>
       <c r="I429" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J429" s="1">
-        <v>0.5</v>
+        <v>8.3333335999999994E-2</v>
       </c>
       <c r="K429" s="1">
-        <v>5500</v>
+        <v>916.66669999999999</v>
       </c>
       <c r="L429" s="1"/>
       <c r="M429" s="1"/>
       <c r="N429" s="1"/>
       <c r="O429" s="1">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="P429" s="1" t="s">
         <v>20</v>
@@ -18149,23 +18141,23 @@
         <v>108</v>
       </c>
       <c r="G430" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H430" s="1"/>
       <c r="I430" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J430" s="1">
-        <v>8.3333335999999994E-2</v>
+        <v>0.5</v>
       </c>
       <c r="K430" s="1">
-        <v>916.66669999999999</v>
+        <v>5500</v>
       </c>
       <c r="L430" s="1"/>
       <c r="M430" s="1"/>
       <c r="N430" s="1"/>
       <c r="O430" s="1">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="P430" s="1" t="s">
         <v>20</v>
@@ -18191,23 +18183,23 @@
         <v>108</v>
       </c>
       <c r="G431" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H431" s="1"/>
       <c r="I431" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J431" s="1">
-        <v>0.5</v>
+        <v>0.16666666999999999</v>
       </c>
       <c r="K431" s="1">
-        <v>5500</v>
+        <v>1833.3334</v>
       </c>
       <c r="L431" s="1"/>
       <c r="M431" s="1"/>
       <c r="N431" s="1"/>
       <c r="O431" s="1">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="P431" s="1" t="s">
         <v>20</v>
@@ -18233,23 +18225,23 @@
         <v>108</v>
       </c>
       <c r="G432" s="1" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="H432" s="1"/>
       <c r="I432" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="J432" s="1">
-        <v>0.16666666999999999</v>
+        <v>0.25</v>
       </c>
       <c r="K432" s="1">
-        <v>1833.3334</v>
+        <v>3750</v>
       </c>
       <c r="L432" s="1"/>
       <c r="M432" s="1"/>
       <c r="N432" s="1"/>
       <c r="O432" s="1">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="P432" s="1" t="s">
         <v>20</v>
@@ -18279,10 +18271,10 @@
       </c>
       <c r="H433" s="1"/>
       <c r="I433" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J433" s="1">
-        <v>0.25</v>
+        <v>0.41666666000000002</v>
       </c>
       <c r="K433" s="1">
         <v>3750</v>
@@ -18291,7 +18283,7 @@
       <c r="M433" s="1"/>
       <c r="N433" s="1"/>
       <c r="O433" s="1">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="P433" s="1" t="s">
         <v>20</v>
@@ -18317,23 +18309,23 @@
         <v>108</v>
       </c>
       <c r="G434" s="1" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="H434" s="1"/>
       <c r="I434" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J434" s="1">
-        <v>0.41666666000000002</v>
+        <v>0.5</v>
       </c>
       <c r="K434" s="1">
-        <v>3750</v>
+        <v>7500</v>
       </c>
       <c r="L434" s="1"/>
       <c r="M434" s="1"/>
       <c r="N434" s="1"/>
       <c r="O434" s="1">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="P434" s="1" t="s">
         <v>20</v>
@@ -18363,19 +18355,19 @@
       </c>
       <c r="H435" s="1"/>
       <c r="I435" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J435" s="1">
-        <v>0.5</v>
+        <v>0.58333330000000005</v>
       </c>
       <c r="K435" s="1">
-        <v>7500</v>
+        <v>5250</v>
       </c>
       <c r="L435" s="1"/>
       <c r="M435" s="1"/>
       <c r="N435" s="1"/>
       <c r="O435" s="1">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="P435" s="1" t="s">
         <v>20</v>
@@ -18401,23 +18393,23 @@
         <v>108</v>
       </c>
       <c r="G436" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H436" s="1"/>
       <c r="I436" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J436" s="1">
-        <v>0.58333330000000005</v>
+        <v>1.25</v>
       </c>
       <c r="K436" s="1">
-        <v>5250</v>
+        <v>13750</v>
       </c>
       <c r="L436" s="1"/>
       <c r="M436" s="1"/>
       <c r="N436" s="1"/>
       <c r="O436" s="1">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="P436" s="1" t="s">
         <v>20</v>
@@ -18443,23 +18435,23 @@
         <v>108</v>
       </c>
       <c r="G437" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H437" s="1"/>
       <c r="I437" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J437" s="1">
-        <v>1.25</v>
+        <v>0.58333330000000005</v>
       </c>
       <c r="K437" s="1">
-        <v>13750</v>
+        <v>6416.6665000000003</v>
       </c>
       <c r="L437" s="1"/>
       <c r="M437" s="1"/>
       <c r="N437" s="1"/>
       <c r="O437" s="1">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="P437" s="1" t="s">
         <v>20</v>
@@ -18485,23 +18477,23 @@
         <v>108</v>
       </c>
       <c r="G438" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H438" s="1"/>
       <c r="I438" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J438" s="1">
-        <v>0.58333330000000005</v>
+        <v>0.66666669999999995</v>
       </c>
       <c r="K438" s="1">
-        <v>6416.6665000000003</v>
+        <v>7333.3334999999997</v>
       </c>
       <c r="L438" s="1"/>
       <c r="M438" s="1"/>
       <c r="N438" s="1"/>
       <c r="O438" s="1">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="P438" s="1" t="s">
         <v>20</v>
@@ -18527,23 +18519,23 @@
         <v>108</v>
       </c>
       <c r="G439" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H439" s="1"/>
       <c r="I439" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J439" s="1">
-        <v>0.66666669999999995</v>
+        <v>0.41666666000000002</v>
       </c>
       <c r="K439" s="1">
-        <v>7333.3334999999997</v>
+        <v>4583.3334999999997</v>
       </c>
       <c r="L439" s="1"/>
       <c r="M439" s="1"/>
       <c r="N439" s="1"/>
       <c r="O439" s="1">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="P439" s="1" t="s">
         <v>20</v>
@@ -18563,29 +18555,25 @@
         <v>76</v>
       </c>
       <c r="E440" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F440" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G440" s="1" t="s">
-        <v>93</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="F440" s="1"/>
+      <c r="G440" s="1"/>
       <c r="H440" s="1"/>
       <c r="I440" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J440" s="1">
-        <v>0.41666666000000002</v>
+        <v>60.5</v>
       </c>
       <c r="K440" s="1">
-        <v>4583.3334999999997</v>
+        <v>665500</v>
       </c>
       <c r="L440" s="1"/>
       <c r="M440" s="1"/>
       <c r="N440" s="1"/>
       <c r="O440" s="1">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="P440" s="1" t="s">
         <v>20</v>
@@ -18611,19 +18599,19 @@
       <c r="G441" s="1"/>
       <c r="H441" s="1"/>
       <c r="I441" s="1" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J441" s="1">
-        <v>60.5</v>
+        <v>0.16666666999999999</v>
       </c>
       <c r="K441" s="1">
-        <v>665500</v>
+        <v>1500</v>
       </c>
       <c r="L441" s="1"/>
       <c r="M441" s="1"/>
       <c r="N441" s="1"/>
       <c r="O441" s="1">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="P441" s="1" t="s">
         <v>20</v>
@@ -18649,19 +18637,19 @@
       <c r="G442" s="1"/>
       <c r="H442" s="1"/>
       <c r="I442" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J442" s="1">
-        <v>0.16666666999999999</v>
+        <v>0.5</v>
       </c>
       <c r="K442" s="1">
-        <v>1500</v>
+        <v>7500</v>
       </c>
       <c r="L442" s="1"/>
       <c r="M442" s="1"/>
       <c r="N442" s="1"/>
       <c r="O442" s="1">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="P442" s="1" t="s">
         <v>20</v>
@@ -18687,19 +18675,19 @@
       <c r="G443" s="1"/>
       <c r="H443" s="1"/>
       <c r="I443" s="1" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="J443" s="1">
-        <v>0.5</v>
+        <v>5.1666664999999998</v>
       </c>
       <c r="K443" s="1">
-        <v>7500</v>
+        <v>46500</v>
       </c>
       <c r="L443" s="1"/>
       <c r="M443" s="1"/>
       <c r="N443" s="1"/>
       <c r="O443" s="1">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="P443" s="1" t="s">
         <v>20</v>
@@ -18725,19 +18713,19 @@
       <c r="G444" s="1"/>
       <c r="H444" s="1"/>
       <c r="I444" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J444" s="1">
-        <v>5.1666664999999998</v>
+        <v>24.75</v>
       </c>
       <c r="K444" s="1">
-        <v>46500</v>
+        <v>371250</v>
       </c>
       <c r="L444" s="1"/>
       <c r="M444" s="1"/>
       <c r="N444" s="1"/>
       <c r="O444" s="1">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="P444" s="1" t="s">
         <v>20</v>
@@ -18745,16 +18733,16 @@
     </row>
     <row r="445" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A445" s="2">
-        <v>46190</v>
+        <v>46189</v>
       </c>
       <c r="B445" s="1">
         <v>0</v>
       </c>
       <c r="C445" s="1" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="D445" s="1" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="E445" s="1" t="s">
         <v>18</v>
@@ -18763,19 +18751,19 @@
       <c r="G445" s="1"/>
       <c r="H445" s="1"/>
       <c r="I445" s="1" t="s">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="J445" s="1">
-        <v>24.75</v>
+        <v>32.5</v>
       </c>
       <c r="K445" s="1">
-        <v>371250</v>
+        <v>341250</v>
       </c>
       <c r="L445" s="1"/>
       <c r="M445" s="1"/>
       <c r="N445" s="1"/>
       <c r="O445" s="1">
-        <v>2015</v>
+        <v>1793</v>
       </c>
       <c r="P445" s="1" t="s">
         <v>20</v>
@@ -18801,19 +18789,19 @@
       <c r="G446" s="1"/>
       <c r="H446" s="1"/>
       <c r="I446" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J446" s="1">
-        <v>32.5</v>
+        <v>11</v>
       </c>
       <c r="K446" s="1">
-        <v>341250</v>
+        <v>66000</v>
       </c>
       <c r="L446" s="1"/>
       <c r="M446" s="1"/>
       <c r="N446" s="1"/>
       <c r="O446" s="1">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="P446" s="1" t="s">
         <v>20</v>
@@ -18839,19 +18827,19 @@
       <c r="G447" s="1"/>
       <c r="H447" s="1"/>
       <c r="I447" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J447" s="1">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K447" s="1">
-        <v>66000</v>
+        <v>32500</v>
       </c>
       <c r="L447" s="1"/>
       <c r="M447" s="1"/>
       <c r="N447" s="1"/>
       <c r="O447" s="1">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="P447" s="1" t="s">
         <v>20</v>
@@ -18877,19 +18865,19 @@
       <c r="G448" s="1"/>
       <c r="H448" s="1"/>
       <c r="I448" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J448" s="1">
-        <v>5</v>
+        <v>19.5</v>
       </c>
       <c r="K448" s="1">
-        <v>32500</v>
+        <v>234000</v>
       </c>
       <c r="L448" s="1"/>
       <c r="M448" s="1"/>
       <c r="N448" s="1"/>
       <c r="O448" s="1">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="P448" s="1" t="s">
         <v>20</v>
@@ -18915,19 +18903,19 @@
       <c r="G449" s="1"/>
       <c r="H449" s="1"/>
       <c r="I449" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J449" s="1">
-        <v>19.5</v>
+        <v>13.166667</v>
       </c>
       <c r="K449" s="1">
-        <v>234000</v>
+        <v>230416.67</v>
       </c>
       <c r="L449" s="1"/>
       <c r="M449" s="1"/>
       <c r="N449" s="1"/>
       <c r="O449" s="1">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="P449" s="1" t="s">
         <v>20</v>
@@ -18953,19 +18941,19 @@
       <c r="G450" s="1"/>
       <c r="H450" s="1"/>
       <c r="I450" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J450" s="1">
-        <v>13.166667</v>
+        <v>10.375</v>
       </c>
       <c r="K450" s="1">
-        <v>230416.67</v>
+        <v>347562.5</v>
       </c>
       <c r="L450" s="1"/>
       <c r="M450" s="1"/>
       <c r="N450" s="1"/>
       <c r="O450" s="1">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="P450" s="1" t="s">
         <v>20</v>
@@ -18991,19 +18979,19 @@
       <c r="G451" s="1"/>
       <c r="H451" s="1"/>
       <c r="I451" s="1" t="s">
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="J451" s="1">
-        <v>10.375</v>
+        <v>1</v>
       </c>
       <c r="K451" s="1">
-        <v>347562.5</v>
+        <v>33500</v>
       </c>
       <c r="L451" s="1"/>
       <c r="M451" s="1"/>
       <c r="N451" s="1"/>
       <c r="O451" s="1">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="P451" s="1" t="s">
         <v>20</v>
@@ -19029,19 +19017,19 @@
       <c r="G452" s="1"/>
       <c r="H452" s="1"/>
       <c r="I452" s="1" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="J452" s="1">
-        <v>1</v>
+        <v>13.222222</v>
       </c>
       <c r="K452" s="1">
-        <v>33500</v>
+        <v>370222.22</v>
       </c>
       <c r="L452" s="1"/>
       <c r="M452" s="1"/>
       <c r="N452" s="1"/>
       <c r="O452" s="1">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="P452" s="1" t="s">
         <v>20</v>
@@ -19067,19 +19055,19 @@
       <c r="G453" s="1"/>
       <c r="H453" s="1"/>
       <c r="I453" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J453" s="1">
-        <v>13.222222</v>
+        <v>3.3333333000000001</v>
       </c>
       <c r="K453" s="1">
-        <v>370222.22</v>
+        <v>86666.664000000004</v>
       </c>
       <c r="L453" s="1"/>
       <c r="M453" s="1"/>
       <c r="N453" s="1"/>
       <c r="O453" s="1">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="P453" s="1" t="s">
         <v>20</v>
@@ -19105,19 +19093,19 @@
       <c r="G454" s="1"/>
       <c r="H454" s="1"/>
       <c r="I454" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="J454" s="1">
-        <v>3.3333333000000001</v>
+        <v>10</v>
       </c>
       <c r="K454" s="1">
-        <v>86666.664000000004</v>
+        <v>190000</v>
       </c>
       <c r="L454" s="1"/>
       <c r="M454" s="1"/>
       <c r="N454" s="1"/>
       <c r="O454" s="1">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="P454" s="1" t="s">
         <v>20</v>
@@ -19143,19 +19131,19 @@
       <c r="G455" s="1"/>
       <c r="H455" s="1"/>
       <c r="I455" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J455" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K455" s="1">
-        <v>190000</v>
+        <v>390000</v>
       </c>
       <c r="L455" s="1"/>
       <c r="M455" s="1"/>
       <c r="N455" s="1"/>
       <c r="O455" s="1">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="P455" s="1" t="s">
         <v>20</v>
@@ -19181,19 +19169,19 @@
       <c r="G456" s="1"/>
       <c r="H456" s="1"/>
       <c r="I456" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J456" s="1">
-        <v>20</v>
+        <v>7.9166664999999998</v>
       </c>
       <c r="K456" s="1">
-        <v>390000</v>
+        <v>98958.335999999996</v>
       </c>
       <c r="L456" s="1"/>
       <c r="M456" s="1"/>
       <c r="N456" s="1"/>
       <c r="O456" s="1">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="P456" s="1" t="s">
         <v>20</v>
@@ -19219,19 +19207,19 @@
       <c r="G457" s="1"/>
       <c r="H457" s="1"/>
       <c r="I457" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J457" s="1">
-        <v>7.9166664999999998</v>
+        <v>3.5</v>
       </c>
       <c r="K457" s="1">
-        <v>98958.335999999996</v>
+        <v>43750</v>
       </c>
       <c r="L457" s="1"/>
       <c r="M457" s="1"/>
       <c r="N457" s="1"/>
       <c r="O457" s="1">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="P457" s="1" t="s">
         <v>20</v>
@@ -19257,19 +19245,19 @@
       <c r="G458" s="1"/>
       <c r="H458" s="1"/>
       <c r="I458" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J458" s="1">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="K458" s="1">
-        <v>43750</v>
+        <v>155000</v>
       </c>
       <c r="L458" s="1"/>
       <c r="M458" s="1"/>
       <c r="N458" s="1"/>
       <c r="O458" s="1">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="P458" s="1" t="s">
         <v>20</v>
@@ -19295,19 +19283,19 @@
       <c r="G459" s="1"/>
       <c r="H459" s="1"/>
       <c r="I459" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J459" s="1">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="K459" s="1">
-        <v>155000</v>
+        <v>85250</v>
       </c>
       <c r="L459" s="1"/>
       <c r="M459" s="1"/>
       <c r="N459" s="1"/>
       <c r="O459" s="1">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="P459" s="1" t="s">
         <v>20</v>
@@ -19333,19 +19321,19 @@
       <c r="G460" s="1"/>
       <c r="H460" s="1"/>
       <c r="I460" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J460" s="1">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="K460" s="1">
-        <v>85250</v>
+        <v>75000</v>
       </c>
       <c r="L460" s="1"/>
       <c r="M460" s="1"/>
       <c r="N460" s="1"/>
       <c r="O460" s="1">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="P460" s="1" t="s">
         <v>20</v>
@@ -19371,19 +19359,19 @@
       <c r="G461" s="1"/>
       <c r="H461" s="1"/>
       <c r="I461" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J461" s="1">
-        <v>7.5</v>
+        <v>5.8333335000000002</v>
       </c>
       <c r="K461" s="1">
-        <v>75000</v>
+        <v>70000</v>
       </c>
       <c r="L461" s="1"/>
       <c r="M461" s="1"/>
       <c r="N461" s="1"/>
       <c r="O461" s="1">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="P461" s="1" t="s">
         <v>20</v>
@@ -19409,19 +19397,19 @@
       <c r="G462" s="1"/>
       <c r="H462" s="1"/>
       <c r="I462" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J462" s="1">
-        <v>5.8333335000000002</v>
+        <v>5</v>
       </c>
       <c r="K462" s="1">
-        <v>70000</v>
+        <v>55000</v>
       </c>
       <c r="L462" s="1"/>
       <c r="M462" s="1"/>
       <c r="N462" s="1"/>
       <c r="O462" s="1">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="P462" s="1" t="s">
         <v>20</v>
@@ -19447,19 +19435,19 @@
       <c r="G463" s="1"/>
       <c r="H463" s="1"/>
       <c r="I463" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J463" s="1">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="K463" s="1">
-        <v>55000</v>
+        <v>251750</v>
       </c>
       <c r="L463" s="1"/>
       <c r="M463" s="1"/>
       <c r="N463" s="1"/>
       <c r="O463" s="1">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="P463" s="1" t="s">
         <v>20</v>
@@ -19485,19 +19473,19 @@
       <c r="G464" s="1"/>
       <c r="H464" s="1"/>
       <c r="I464" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J464" s="1">
-        <v>9.5</v>
+        <v>4.8333335000000002</v>
       </c>
       <c r="K464" s="1">
-        <v>251750</v>
+        <v>87000</v>
       </c>
       <c r="L464" s="1"/>
       <c r="M464" s="1"/>
       <c r="N464" s="1"/>
       <c r="O464" s="1">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="P464" s="1" t="s">
         <v>20</v>
@@ -19523,19 +19511,19 @@
       <c r="G465" s="1"/>
       <c r="H465" s="1"/>
       <c r="I465" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J465" s="1">
-        <v>4.8333335000000002</v>
+        <v>13</v>
       </c>
       <c r="K465" s="1">
-        <v>87000</v>
+        <v>58500</v>
       </c>
       <c r="L465" s="1"/>
       <c r="M465" s="1"/>
       <c r="N465" s="1"/>
       <c r="O465" s="1">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="P465" s="1" t="s">
         <v>20</v>
@@ -19561,19 +19549,19 @@
       <c r="G466" s="1"/>
       <c r="H466" s="1"/>
       <c r="I466" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J466" s="1">
-        <v>13</v>
+        <v>18.458334000000001</v>
       </c>
       <c r="K466" s="1">
-        <v>58500</v>
+        <v>212270.83</v>
       </c>
       <c r="L466" s="1"/>
       <c r="M466" s="1"/>
       <c r="N466" s="1"/>
       <c r="O466" s="1">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="P466" s="1" t="s">
         <v>20</v>
@@ -19593,25 +19581,31 @@
         <v>17</v>
       </c>
       <c r="E467" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F467" s="1"/>
-      <c r="G467" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="F467" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G467" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="H467" s="1"/>
       <c r="I467" s="1" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="J467" s="1">
-        <v>18.458334000000001</v>
+        <v>1.5</v>
       </c>
       <c r="K467" s="1">
-        <v>212270.83</v>
+        <v>15750</v>
       </c>
       <c r="L467" s="1"/>
-      <c r="M467" s="1"/>
+      <c r="M467" s="1">
+        <v>5000</v>
+      </c>
       <c r="N467" s="1"/>
       <c r="O467" s="1">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="P467" s="1" t="s">
         <v>20</v>
@@ -19634,28 +19628,26 @@
         <v>41</v>
       </c>
       <c r="F468" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G468" s="1" t="s">
         <v>51</v>
       </c>
       <c r="H468" s="1"/>
       <c r="I468" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J468" s="1">
-        <v>1.5</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="K468" s="1">
-        <v>15750</v>
+        <v>13200</v>
       </c>
       <c r="L468" s="1"/>
-      <c r="M468" s="1">
-        <v>5000</v>
-      </c>
+      <c r="M468" s="1"/>
       <c r="N468" s="1"/>
       <c r="O468" s="1">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="P468" s="1" t="s">
         <v>20</v>
@@ -19678,26 +19670,26 @@
         <v>41</v>
       </c>
       <c r="F469" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G469" s="1" t="s">
         <v>51</v>
       </c>
       <c r="H469" s="1"/>
       <c r="I469" s="1" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="J469" s="1">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="K469" s="1">
-        <v>13200</v>
+        <v>4500</v>
       </c>
       <c r="L469" s="1"/>
       <c r="M469" s="1"/>
       <c r="N469" s="1"/>
       <c r="O469" s="1">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="P469" s="1" t="s">
         <v>20</v>
@@ -19720,26 +19712,26 @@
         <v>41</v>
       </c>
       <c r="F470" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G470" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H470" s="1"/>
       <c r="I470" s="1" t="s">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="J470" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K470" s="1">
-        <v>4500</v>
+        <v>16750</v>
       </c>
       <c r="L470" s="1"/>
       <c r="M470" s="1"/>
       <c r="N470" s="1"/>
       <c r="O470" s="1">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="P470" s="1" t="s">
         <v>20</v>
@@ -19762,26 +19754,26 @@
         <v>41</v>
       </c>
       <c r="F471" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G471" s="1" t="s">
         <v>50</v>
       </c>
       <c r="H471" s="1"/>
       <c r="I471" s="1" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="J471" s="1">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="K471" s="1">
-        <v>16750</v>
+        <v>56000</v>
       </c>
       <c r="L471" s="1"/>
       <c r="M471" s="1"/>
       <c r="N471" s="1"/>
       <c r="O471" s="1">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="P471" s="1" t="s">
         <v>20</v>
@@ -19804,26 +19796,26 @@
         <v>41</v>
       </c>
       <c r="F472" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G472" s="1" t="s">
         <v>50</v>
       </c>
       <c r="H472" s="1"/>
       <c r="I472" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J472" s="1">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="K472" s="1">
-        <v>56000</v>
+        <v>16750</v>
       </c>
       <c r="L472" s="1"/>
       <c r="M472" s="1"/>
       <c r="N472" s="1"/>
       <c r="O472" s="1">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="P472" s="1" t="s">
         <v>20</v>
@@ -19846,26 +19838,26 @@
         <v>41</v>
       </c>
       <c r="F473" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G473" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H473" s="1"/>
       <c r="I473" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J473" s="1">
-        <v>0.5</v>
+        <v>0.22222222</v>
       </c>
       <c r="K473" s="1">
-        <v>16750</v>
+        <v>6222.2219999999998</v>
       </c>
       <c r="L473" s="1"/>
       <c r="M473" s="1"/>
       <c r="N473" s="1"/>
       <c r="O473" s="1">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="P473" s="1" t="s">
         <v>20</v>
@@ -19888,26 +19880,26 @@
         <v>41</v>
       </c>
       <c r="F474" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G474" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H474" s="1"/>
       <c r="I474" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J474" s="1">
-        <v>0.22222222</v>
+        <v>0.5</v>
       </c>
       <c r="K474" s="1">
-        <v>6222.2219999999998</v>
+        <v>5000</v>
       </c>
       <c r="L474" s="1"/>
       <c r="M474" s="1"/>
       <c r="N474" s="1"/>
       <c r="O474" s="1">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="P474" s="1" t="s">
         <v>20</v>
@@ -19930,26 +19922,26 @@
         <v>41</v>
       </c>
       <c r="F475" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G475" s="1" t="s">
         <v>53</v>
       </c>
       <c r="H475" s="1"/>
       <c r="I475" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J475" s="1">
-        <v>0.5</v>
+        <v>0.33333333999999998</v>
       </c>
       <c r="K475" s="1">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="L475" s="1"/>
       <c r="M475" s="1"/>
       <c r="N475" s="1"/>
       <c r="O475" s="1">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="P475" s="1" t="s">
         <v>20</v>
@@ -19972,26 +19964,26 @@
         <v>41</v>
       </c>
       <c r="F476" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G476" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H476" s="1"/>
       <c r="I476" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J476" s="1">
-        <v>0.33333333999999998</v>
+        <v>1</v>
       </c>
       <c r="K476" s="1">
-        <v>4000</v>
+        <v>15500</v>
       </c>
       <c r="L476" s="1"/>
       <c r="M476" s="1"/>
       <c r="N476" s="1"/>
       <c r="O476" s="1">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="P476" s="1" t="s">
         <v>20</v>
@@ -20014,26 +20006,26 @@
         <v>41</v>
       </c>
       <c r="F477" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G477" s="1" t="s">
         <v>52</v>
       </c>
       <c r="H477" s="1"/>
       <c r="I477" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J477" s="1">
-        <v>1</v>
+        <v>0.16666666999999999</v>
       </c>
       <c r="K477" s="1">
-        <v>15500</v>
+        <v>1666.6666</v>
       </c>
       <c r="L477" s="1"/>
       <c r="M477" s="1"/>
       <c r="N477" s="1"/>
       <c r="O477" s="1">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="P477" s="1" t="s">
         <v>20</v>
@@ -20056,26 +20048,26 @@
         <v>41</v>
       </c>
       <c r="F478" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G478" s="1" t="s">
         <v>52</v>
       </c>
       <c r="H478" s="1"/>
       <c r="I478" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J478" s="1">
         <v>0.16666666999999999</v>
       </c>
       <c r="K478" s="1">
-        <v>1666.6666</v>
+        <v>2000</v>
       </c>
       <c r="L478" s="1"/>
       <c r="M478" s="1"/>
       <c r="N478" s="1"/>
       <c r="O478" s="1">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="P478" s="1" t="s">
         <v>20</v>
@@ -20098,26 +20090,26 @@
         <v>41</v>
       </c>
       <c r="F479" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G479" s="1" t="s">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="H479" s="1"/>
       <c r="I479" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J479" s="1">
-        <v>0.16666666999999999</v>
+        <v>2.5</v>
       </c>
       <c r="K479" s="1">
-        <v>2000</v>
+        <v>48750</v>
       </c>
       <c r="L479" s="1"/>
       <c r="M479" s="1"/>
       <c r="N479" s="1"/>
       <c r="O479" s="1">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="P479" s="1" t="s">
         <v>20</v>
@@ -20140,26 +20132,26 @@
         <v>41</v>
       </c>
       <c r="F480" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G480" s="1" t="s">
-        <v>99</v>
+        <v>48</v>
       </c>
       <c r="H480" s="1"/>
       <c r="I480" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="J480" s="1">
-        <v>2.5</v>
+        <v>1.3333333999999999</v>
       </c>
       <c r="K480" s="1">
-        <v>48750</v>
+        <v>34666.667999999998</v>
       </c>
       <c r="L480" s="1"/>
       <c r="M480" s="1"/>
       <c r="N480" s="1"/>
       <c r="O480" s="1">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="P480" s="1" t="s">
         <v>20</v>
@@ -20182,26 +20174,26 @@
         <v>41</v>
       </c>
       <c r="F481" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G481" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H481" s="1"/>
       <c r="I481" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J481" s="1">
-        <v>1.3333333999999999</v>
+        <v>2</v>
       </c>
       <c r="K481" s="1">
-        <v>34666.667999999998</v>
+        <v>21000</v>
       </c>
       <c r="L481" s="1"/>
       <c r="M481" s="1"/>
       <c r="N481" s="1"/>
       <c r="O481" s="1">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="P481" s="1" t="s">
         <v>20</v>
@@ -20224,26 +20216,26 @@
         <v>41</v>
       </c>
       <c r="F482" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G482" s="1" t="s">
         <v>46</v>
       </c>
       <c r="H482" s="1"/>
       <c r="I482" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J482" s="1">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="K482" s="1">
-        <v>21000</v>
+        <v>6000</v>
       </c>
       <c r="L482" s="1"/>
       <c r="M482" s="1"/>
       <c r="N482" s="1"/>
       <c r="O482" s="1">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="P482" s="1" t="s">
         <v>20</v>
@@ -20266,26 +20258,26 @@
         <v>41</v>
       </c>
       <c r="F483" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G483" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H483" s="1"/>
       <c r="I483" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J483" s="1">
         <v>0.5</v>
       </c>
       <c r="K483" s="1">
-        <v>6000</v>
+        <v>6250</v>
       </c>
       <c r="L483" s="1"/>
       <c r="M483" s="1"/>
       <c r="N483" s="1"/>
       <c r="O483" s="1">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="P483" s="1" t="s">
         <v>20</v>
@@ -20308,10 +20300,10 @@
         <v>41</v>
       </c>
       <c r="F484" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G484" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H484" s="1"/>
       <c r="I484" s="1" t="s">
@@ -20327,7 +20319,7 @@
       <c r="M484" s="1"/>
       <c r="N484" s="1"/>
       <c r="O484" s="1">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="P484" s="1" t="s">
         <v>20</v>
@@ -20350,26 +20342,26 @@
         <v>41</v>
       </c>
       <c r="F485" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G485" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H485" s="1"/>
       <c r="I485" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="J485" s="1">
-        <v>0.5</v>
+        <v>0.54166669999999995</v>
       </c>
       <c r="K485" s="1">
-        <v>6250</v>
+        <v>6229.1665000000003</v>
       </c>
       <c r="L485" s="1"/>
       <c r="M485" s="1"/>
       <c r="N485" s="1"/>
       <c r="O485" s="1">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="P485" s="1" t="s">
         <v>20</v>
@@ -20392,26 +20384,26 @@
         <v>41</v>
       </c>
       <c r="F486" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G486" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H486" s="1"/>
       <c r="I486" s="1" t="s">
         <v>38</v>
       </c>
       <c r="J486" s="1">
-        <v>0.54166669999999995</v>
+        <v>1</v>
       </c>
       <c r="K486" s="1">
-        <v>6229.1665000000003</v>
+        <v>11500</v>
       </c>
       <c r="L486" s="1"/>
       <c r="M486" s="1"/>
       <c r="N486" s="1"/>
       <c r="O486" s="1">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="P486" s="1" t="s">
         <v>20</v>
@@ -20434,26 +20426,26 @@
         <v>41</v>
       </c>
       <c r="F487" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G487" s="1" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="H487" s="1"/>
       <c r="I487" s="1" t="s">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="J487" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K487" s="1">
-        <v>11500</v>
+        <v>0</v>
       </c>
       <c r="L487" s="1"/>
       <c r="M487" s="1"/>
       <c r="N487" s="1"/>
       <c r="O487" s="1">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="P487" s="1" t="s">
         <v>20</v>
@@ -20467,10 +20459,10 @@
         <v>0</v>
       </c>
       <c r="C488" s="1" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="D488" s="1" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="E488" s="1" t="s">
         <v>41</v>
@@ -20479,23 +20471,23 @@
         <v>111</v>
       </c>
       <c r="G488" s="1" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="H488" s="1"/>
       <c r="I488" s="1" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="J488" s="1">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="K488" s="1">
-        <v>0</v>
+        <v>8250</v>
       </c>
       <c r="L488" s="1"/>
       <c r="M488" s="1"/>
       <c r="N488" s="1"/>
       <c r="O488" s="1">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="P488" s="1" t="s">
         <v>20</v>
@@ -20518,26 +20510,26 @@
         <v>41</v>
       </c>
       <c r="F489" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G489" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H489" s="1"/>
       <c r="I489" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J489" s="1">
-        <v>0.75</v>
+        <v>1.3333333999999999</v>
       </c>
       <c r="K489" s="1">
-        <v>8250</v>
+        <v>14666.666999999999</v>
       </c>
       <c r="L489" s="1"/>
       <c r="M489" s="1"/>
       <c r="N489" s="1"/>
       <c r="O489" s="1">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="P489" s="1" t="s">
         <v>20</v>
@@ -20560,26 +20552,26 @@
         <v>41</v>
       </c>
       <c r="F490" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G490" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H490" s="1"/>
       <c r="I490" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J490" s="1">
-        <v>1.3333333999999999</v>
+        <v>0.66666669999999995</v>
       </c>
       <c r="K490" s="1">
-        <v>14666.666999999999</v>
+        <v>7333.3334999999997</v>
       </c>
       <c r="L490" s="1"/>
       <c r="M490" s="1"/>
       <c r="N490" s="1"/>
       <c r="O490" s="1">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="P490" s="1" t="s">
         <v>20</v>
@@ -20602,26 +20594,26 @@
         <v>41</v>
       </c>
       <c r="F491" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G491" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H491" s="1"/>
       <c r="I491" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J491" s="1">
-        <v>0.66666669999999995</v>
+        <v>0.75</v>
       </c>
       <c r="K491" s="1">
-        <v>7333.3334999999997</v>
+        <v>8250</v>
       </c>
       <c r="L491" s="1"/>
       <c r="M491" s="1"/>
       <c r="N491" s="1"/>
       <c r="O491" s="1">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="P491" s="1" t="s">
         <v>20</v>
@@ -20644,26 +20636,26 @@
         <v>41</v>
       </c>
       <c r="F492" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G492" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H492" s="1"/>
       <c r="I492" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J492" s="1">
-        <v>0.75</v>
+        <v>0.83333330000000005</v>
       </c>
       <c r="K492" s="1">
-        <v>8250</v>
+        <v>9166.6669999999995</v>
       </c>
       <c r="L492" s="1"/>
       <c r="M492" s="1"/>
       <c r="N492" s="1"/>
       <c r="O492" s="1">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="P492" s="1" t="s">
         <v>20</v>
@@ -20686,26 +20678,26 @@
         <v>41</v>
       </c>
       <c r="F493" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G493" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H493" s="1"/>
       <c r="I493" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J493" s="1">
-        <v>0.83333330000000005</v>
+        <v>0.66666669999999995</v>
       </c>
       <c r="K493" s="1">
-        <v>9166.6669999999995</v>
+        <v>7333.3334999999997</v>
       </c>
       <c r="L493" s="1"/>
       <c r="M493" s="1"/>
       <c r="N493" s="1"/>
       <c r="O493" s="1">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="P493" s="1" t="s">
         <v>20</v>
@@ -20728,26 +20720,26 @@
         <v>41</v>
       </c>
       <c r="F494" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G494" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H494" s="1"/>
       <c r="I494" s="1" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J494" s="1">
-        <v>0.66666669999999995</v>
+        <v>8.3333335999999994E-2</v>
       </c>
       <c r="K494" s="1">
-        <v>7333.3334999999997</v>
+        <v>750</v>
       </c>
       <c r="L494" s="1"/>
       <c r="M494" s="1"/>
       <c r="N494" s="1"/>
       <c r="O494" s="1">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="P494" s="1" t="s">
         <v>20</v>
@@ -20770,26 +20762,26 @@
         <v>41</v>
       </c>
       <c r="F495" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G495" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H495" s="1"/>
       <c r="I495" s="1" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J495" s="1">
-        <v>8.3333335999999994E-2</v>
+        <v>0.75</v>
       </c>
       <c r="K495" s="1">
-        <v>750</v>
+        <v>8250</v>
       </c>
       <c r="L495" s="1"/>
       <c r="M495" s="1"/>
       <c r="N495" s="1"/>
       <c r="O495" s="1">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="P495" s="1" t="s">
         <v>20</v>
@@ -20812,10 +20804,10 @@
         <v>41</v>
       </c>
       <c r="F496" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G496" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H496" s="1"/>
       <c r="I496" s="1" t="s">
@@ -20831,7 +20823,7 @@
       <c r="M496" s="1"/>
       <c r="N496" s="1"/>
       <c r="O496" s="1">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="P496" s="1" t="s">
         <v>20</v>
@@ -20854,26 +20846,26 @@
         <v>41</v>
       </c>
       <c r="F497" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G497" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H497" s="1"/>
       <c r="I497" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J497" s="1">
-        <v>0.75</v>
+        <v>0.33333333999999998</v>
       </c>
       <c r="K497" s="1">
-        <v>8250</v>
+        <v>3666.6667000000002</v>
       </c>
       <c r="L497" s="1"/>
       <c r="M497" s="1"/>
       <c r="N497" s="1"/>
       <c r="O497" s="1">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="P497" s="1" t="s">
         <v>20</v>
@@ -20896,26 +20888,26 @@
         <v>41</v>
       </c>
       <c r="F498" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G498" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H498" s="1"/>
       <c r="I498" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J498" s="1">
-        <v>0.33333333999999998</v>
+        <v>0.75</v>
       </c>
       <c r="K498" s="1">
-        <v>3666.6667000000002</v>
+        <v>8250</v>
       </c>
       <c r="L498" s="1"/>
       <c r="M498" s="1"/>
       <c r="N498" s="1"/>
       <c r="O498" s="1">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="P498" s="1" t="s">
         <v>20</v>
@@ -20938,26 +20930,26 @@
         <v>41</v>
       </c>
       <c r="F499" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G499" s="1" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="H499" s="1"/>
       <c r="I499" s="1" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="J499" s="1">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="K499" s="1">
-        <v>8250</v>
+        <v>22500</v>
       </c>
       <c r="L499" s="1"/>
       <c r="M499" s="1"/>
       <c r="N499" s="1"/>
       <c r="O499" s="1">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="P499" s="1" t="s">
         <v>20</v>
@@ -20980,26 +20972,26 @@
         <v>41</v>
       </c>
       <c r="F500" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G500" s="1" t="s">
         <v>77</v>
       </c>
       <c r="H500" s="1"/>
       <c r="I500" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J500" s="1">
-        <v>1.5</v>
+        <v>1.0833333999999999</v>
       </c>
       <c r="K500" s="1">
-        <v>22500</v>
+        <v>9750</v>
       </c>
       <c r="L500" s="1"/>
       <c r="M500" s="1"/>
       <c r="N500" s="1"/>
       <c r="O500" s="1">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="P500" s="1" t="s">
         <v>20</v>
@@ -21022,26 +21014,26 @@
         <v>41</v>
       </c>
       <c r="F501" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G501" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H501" s="1"/>
       <c r="I501" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J501" s="1">
-        <v>1.0833333999999999</v>
+        <v>0.75</v>
       </c>
       <c r="K501" s="1">
-        <v>9750</v>
+        <v>11250</v>
       </c>
       <c r="L501" s="1"/>
       <c r="M501" s="1"/>
       <c r="N501" s="1"/>
       <c r="O501" s="1">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="P501" s="1" t="s">
         <v>20</v>
@@ -21064,26 +21056,26 @@
         <v>41</v>
       </c>
       <c r="F502" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G502" s="1" t="s">
         <v>79</v>
       </c>
       <c r="H502" s="1"/>
       <c r="I502" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J502" s="1">
-        <v>0.75</v>
+        <v>0.58333330000000005</v>
       </c>
       <c r="K502" s="1">
-        <v>11250</v>
+        <v>5250</v>
       </c>
       <c r="L502" s="1"/>
       <c r="M502" s="1"/>
       <c r="N502" s="1"/>
       <c r="O502" s="1">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="P502" s="1" t="s">
         <v>20</v>
@@ -21106,26 +21098,26 @@
         <v>41</v>
       </c>
       <c r="F503" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G503" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H503" s="1"/>
       <c r="I503" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J503" s="1">
-        <v>0.58333330000000005</v>
+        <v>1.25</v>
       </c>
       <c r="K503" s="1">
-        <v>5250</v>
+        <v>18750</v>
       </c>
       <c r="L503" s="1"/>
       <c r="M503" s="1"/>
       <c r="N503" s="1"/>
       <c r="O503" s="1">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="P503" s="1" t="s">
         <v>20</v>
@@ -21148,26 +21140,26 @@
         <v>41</v>
       </c>
       <c r="F504" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G504" s="1" t="s">
         <v>89</v>
       </c>
       <c r="H504" s="1"/>
       <c r="I504" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J504" s="1">
-        <v>1.25</v>
+        <v>1.1666666000000001</v>
       </c>
       <c r="K504" s="1">
-        <v>18750</v>
+        <v>10500</v>
       </c>
       <c r="L504" s="1"/>
       <c r="M504" s="1"/>
       <c r="N504" s="1"/>
       <c r="O504" s="1">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="P504" s="1" t="s">
         <v>20</v>
@@ -21190,26 +21182,26 @@
         <v>41</v>
       </c>
       <c r="F505" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G505" s="1" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="H505" s="1"/>
       <c r="I505" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J505" s="1">
-        <v>1.1666666000000001</v>
+        <v>0.5</v>
       </c>
       <c r="K505" s="1">
-        <v>10500</v>
+        <v>7500</v>
       </c>
       <c r="L505" s="1"/>
       <c r="M505" s="1"/>
       <c r="N505" s="1"/>
       <c r="O505" s="1">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="P505" s="1" t="s">
         <v>20</v>
@@ -21232,26 +21224,26 @@
         <v>41</v>
       </c>
       <c r="F506" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G506" s="1" t="s">
         <v>102</v>
       </c>
       <c r="H506" s="1"/>
       <c r="I506" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J506" s="1">
-        <v>0.5</v>
+        <v>0.58333330000000005</v>
       </c>
       <c r="K506" s="1">
-        <v>7500</v>
+        <v>5250</v>
       </c>
       <c r="L506" s="1"/>
       <c r="M506" s="1"/>
       <c r="N506" s="1"/>
       <c r="O506" s="1">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="P506" s="1" t="s">
         <v>20</v>
@@ -21265,35 +21257,37 @@
         <v>0</v>
       </c>
       <c r="C507" s="1" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="D507" s="1" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="E507" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F507" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G507" s="1" t="s">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="H507" s="1"/>
       <c r="I507" s="1" t="s">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="J507" s="1">
-        <v>0.58333330000000005</v>
+        <v>1.5</v>
       </c>
       <c r="K507" s="1">
-        <v>5250</v>
-      </c>
-      <c r="L507" s="1"/>
+        <v>17250</v>
+      </c>
+      <c r="L507" s="1">
+        <v>6000</v>
+      </c>
       <c r="M507" s="1"/>
       <c r="N507" s="1"/>
       <c r="O507" s="1">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="P507" s="1" t="s">
         <v>20</v>
@@ -21316,28 +21310,26 @@
         <v>41</v>
       </c>
       <c r="F508" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G508" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H508" s="1"/>
       <c r="I508" s="1" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="J508" s="1">
-        <v>1.5</v>
+        <v>0.11111111</v>
       </c>
       <c r="K508" s="1">
-        <v>17250</v>
-      </c>
-      <c r="L508" s="1">
-        <v>6000</v>
-      </c>
+        <v>3111.1109999999999</v>
+      </c>
+      <c r="L508" s="1"/>
       <c r="M508" s="1"/>
       <c r="N508" s="1"/>
       <c r="O508" s="1">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="P508" s="1" t="s">
         <v>20</v>
@@ -21360,26 +21352,26 @@
         <v>41</v>
       </c>
       <c r="F509" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G509" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H509" s="1"/>
       <c r="I509" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="J509" s="1">
-        <v>0.11111111</v>
+        <v>0</v>
       </c>
       <c r="K509" s="1">
-        <v>3111.1109999999999</v>
+        <v>0</v>
       </c>
       <c r="L509" s="1"/>
       <c r="M509" s="1"/>
       <c r="N509" s="1"/>
       <c r="O509" s="1">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="P509" s="1" t="s">
         <v>20</v>
@@ -21402,26 +21394,26 @@
         <v>41</v>
       </c>
       <c r="F510" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G510" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H510" s="1"/>
       <c r="I510" s="1" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J510" s="1">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="K510" s="1">
-        <v>0</v>
+        <v>56400</v>
       </c>
       <c r="L510" s="1"/>
       <c r="M510" s="1"/>
       <c r="N510" s="1"/>
       <c r="O510" s="1">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="P510" s="1" t="s">
         <v>20</v>
@@ -21444,26 +21436,26 @@
         <v>41</v>
       </c>
       <c r="F511" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G511" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H511" s="1"/>
       <c r="I511" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J511" s="1">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="K511" s="1">
-        <v>56400</v>
+        <v>24000</v>
       </c>
       <c r="L511" s="1"/>
       <c r="M511" s="1"/>
       <c r="N511" s="1"/>
       <c r="O511" s="1">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="P511" s="1" t="s">
         <v>20</v>
@@ -21486,26 +21478,26 @@
         <v>41</v>
       </c>
       <c r="F512" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G512" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H512" s="1"/>
       <c r="I512" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J512" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K512" s="1">
-        <v>24000</v>
+        <v>10500</v>
       </c>
       <c r="L512" s="1"/>
       <c r="M512" s="1"/>
       <c r="N512" s="1"/>
       <c r="O512" s="1">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="P512" s="1" t="s">
         <v>20</v>
@@ -21528,26 +21520,26 @@
         <v>41</v>
       </c>
       <c r="F513" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G513" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H513" s="1"/>
       <c r="I513" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="J513" s="1">
-        <v>1</v>
+        <v>0.20833333000000001</v>
       </c>
       <c r="K513" s="1">
-        <v>10500</v>
+        <v>5520.8334999999997</v>
       </c>
       <c r="L513" s="1"/>
       <c r="M513" s="1"/>
       <c r="N513" s="1"/>
       <c r="O513" s="1">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="P513" s="1" t="s">
         <v>20</v>
@@ -21570,26 +21562,26 @@
         <v>41</v>
       </c>
       <c r="F514" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G514" s="1" t="s">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="H514" s="1"/>
       <c r="I514" s="1" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="J514" s="1">
-        <v>0.20833333000000001</v>
+        <v>0.44444444999999999</v>
       </c>
       <c r="K514" s="1">
-        <v>5520.8334999999997</v>
+        <v>12444.444</v>
       </c>
       <c r="L514" s="1"/>
       <c r="M514" s="1"/>
       <c r="N514" s="1"/>
       <c r="O514" s="1">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="P514" s="1" t="s">
         <v>20</v>
@@ -21612,26 +21604,26 @@
         <v>41</v>
       </c>
       <c r="F515" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G515" s="1" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="H515" s="1"/>
       <c r="I515" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="J515" s="1">
-        <v>0.44444444999999999</v>
+        <v>1.5</v>
       </c>
       <c r="K515" s="1">
-        <v>12444.444</v>
+        <v>17250</v>
       </c>
       <c r="L515" s="1"/>
       <c r="M515" s="1"/>
       <c r="N515" s="1"/>
       <c r="O515" s="1">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="P515" s="1" t="s">
         <v>20</v>
@@ -21654,26 +21646,26 @@
         <v>41</v>
       </c>
       <c r="F516" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G516" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H516" s="1"/>
       <c r="I516" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="J516" s="1">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="K516" s="1">
-        <v>17250</v>
+        <v>0</v>
       </c>
       <c r="L516" s="1"/>
       <c r="M516" s="1"/>
       <c r="N516" s="1"/>
       <c r="O516" s="1">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="P516" s="1" t="s">
         <v>20</v>
@@ -21696,26 +21688,26 @@
         <v>41</v>
       </c>
       <c r="F517" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G517" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H517" s="1"/>
       <c r="I517" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J517" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K517" s="1">
-        <v>0</v>
+        <v>6250</v>
       </c>
       <c r="L517" s="1"/>
       <c r="M517" s="1"/>
       <c r="N517" s="1"/>
       <c r="O517" s="1">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="P517" s="1" t="s">
         <v>20</v>
@@ -21738,26 +21730,26 @@
         <v>41</v>
       </c>
       <c r="F518" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G518" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H518" s="1"/>
       <c r="I518" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J518" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K518" s="1">
-        <v>6250</v>
+        <v>0</v>
       </c>
       <c r="L518" s="1"/>
       <c r="M518" s="1"/>
       <c r="N518" s="1"/>
       <c r="O518" s="1">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="P518" s="1" t="s">
         <v>20</v>
@@ -21780,14 +21772,14 @@
         <v>41</v>
       </c>
       <c r="F519" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G519" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H519" s="1"/>
       <c r="I519" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J519" s="1">
         <v>0</v>
@@ -21799,7 +21791,7 @@
       <c r="M519" s="1"/>
       <c r="N519" s="1"/>
       <c r="O519" s="1">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="P519" s="1" t="s">
         <v>20</v>
@@ -21822,26 +21814,26 @@
         <v>41</v>
       </c>
       <c r="F520" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G520" s="1" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="H520" s="1"/>
       <c r="I520" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J520" s="1">
-        <v>0</v>
+        <v>2.1111111999999999</v>
       </c>
       <c r="K520" s="1">
-        <v>0</v>
+        <v>54888.89</v>
       </c>
       <c r="L520" s="1"/>
       <c r="M520" s="1"/>
       <c r="N520" s="1"/>
       <c r="O520" s="1">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="P520" s="1" t="s">
         <v>20</v>
@@ -21864,26 +21856,26 @@
         <v>41</v>
       </c>
       <c r="F521" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G521" s="1" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="H521" s="1"/>
       <c r="I521" s="1" t="s">
         <v>27</v>
       </c>
       <c r="J521" s="1">
-        <v>2.1111111999999999</v>
+        <v>2</v>
       </c>
       <c r="K521" s="1">
-        <v>54888.89</v>
+        <v>52000</v>
       </c>
       <c r="L521" s="1"/>
       <c r="M521" s="1"/>
       <c r="N521" s="1"/>
       <c r="O521" s="1">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="P521" s="1" t="s">
         <v>20</v>
@@ -21906,26 +21898,26 @@
         <v>41</v>
       </c>
       <c r="F522" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G522" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H522" s="1"/>
       <c r="I522" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J522" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K522" s="1">
-        <v>52000</v>
+        <v>31500</v>
       </c>
       <c r="L522" s="1"/>
       <c r="M522" s="1"/>
       <c r="N522" s="1"/>
       <c r="O522" s="1">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="P522" s="1" t="s">
         <v>20</v>
@@ -21948,26 +21940,26 @@
         <v>41</v>
       </c>
       <c r="F523" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G523" s="1" t="s">
         <v>68</v>
       </c>
       <c r="H523" s="1"/>
       <c r="I523" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J523" s="1">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="K523" s="1">
-        <v>31500</v>
+        <v>4200</v>
       </c>
       <c r="L523" s="1"/>
       <c r="M523" s="1"/>
       <c r="N523" s="1"/>
       <c r="O523" s="1">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="P523" s="1" t="s">
         <v>20</v>
@@ -21990,26 +21982,26 @@
         <v>41</v>
       </c>
       <c r="F524" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G524" s="1" t="s">
         <v>68</v>
       </c>
       <c r="H524" s="1"/>
       <c r="I524" s="1" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="J524" s="1">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="K524" s="1">
-        <v>4200</v>
+        <v>26500</v>
       </c>
       <c r="L524" s="1"/>
       <c r="M524" s="1"/>
       <c r="N524" s="1"/>
       <c r="O524" s="1">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="P524" s="1" t="s">
         <v>20</v>
@@ -22032,26 +22024,26 @@
         <v>41</v>
       </c>
       <c r="F525" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G525" s="1" t="s">
         <v>68</v>
       </c>
       <c r="H525" s="1"/>
       <c r="I525" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="J525" s="1">
         <v>1</v>
       </c>
       <c r="K525" s="1">
-        <v>26500</v>
+        <v>12000</v>
       </c>
       <c r="L525" s="1"/>
       <c r="M525" s="1"/>
       <c r="N525" s="1"/>
       <c r="O525" s="1">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="P525" s="1" t="s">
         <v>20</v>
@@ -22074,26 +22066,26 @@
         <v>41</v>
       </c>
       <c r="F526" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G526" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H526" s="1"/>
       <c r="I526" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J526" s="1">
-        <v>1</v>
+        <v>0.55555560000000004</v>
       </c>
       <c r="K526" s="1">
-        <v>12000</v>
+        <v>14444.444</v>
       </c>
       <c r="L526" s="1"/>
       <c r="M526" s="1"/>
       <c r="N526" s="1"/>
       <c r="O526" s="1">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="P526" s="1" t="s">
         <v>20</v>
@@ -22116,26 +22108,26 @@
         <v>41</v>
       </c>
       <c r="F527" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G527" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H527" s="1"/>
       <c r="I527" s="1" t="s">
         <v>27</v>
       </c>
       <c r="J527" s="1">
-        <v>0.55555560000000004</v>
+        <v>0.66666669999999995</v>
       </c>
       <c r="K527" s="1">
-        <v>14444.444</v>
+        <v>17333.333999999999</v>
       </c>
       <c r="L527" s="1"/>
       <c r="M527" s="1"/>
       <c r="N527" s="1"/>
       <c r="O527" s="1">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="P527" s="1" t="s">
         <v>20</v>
@@ -22158,26 +22150,26 @@
         <v>41</v>
       </c>
       <c r="F528" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G528" s="1" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="H528" s="1"/>
       <c r="I528" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="J528" s="1">
-        <v>0.66666669999999995</v>
+        <v>1</v>
       </c>
       <c r="K528" s="1">
-        <v>17333.333999999999</v>
+        <v>4500</v>
       </c>
       <c r="L528" s="1"/>
       <c r="M528" s="1"/>
       <c r="N528" s="1"/>
       <c r="O528" s="1">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="P528" s="1" t="s">
         <v>20</v>
@@ -22200,26 +22192,26 @@
         <v>41</v>
       </c>
       <c r="F529" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G529" s="1" t="s">
         <v>59</v>
       </c>
       <c r="H529" s="1"/>
       <c r="I529" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J529" s="1">
-        <v>1</v>
+        <v>0.45833333999999998</v>
       </c>
       <c r="K529" s="1">
-        <v>4500</v>
+        <v>5270.8334999999997</v>
       </c>
       <c r="L529" s="1"/>
       <c r="M529" s="1"/>
       <c r="N529" s="1"/>
       <c r="O529" s="1">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="P529" s="1" t="s">
         <v>20</v>
@@ -22242,26 +22234,26 @@
         <v>41</v>
       </c>
       <c r="F530" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G530" s="1" t="s">
         <v>59</v>
       </c>
       <c r="H530" s="1"/>
       <c r="I530" s="1" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J530" s="1">
-        <v>0.45833333999999998</v>
+        <v>0.1</v>
       </c>
       <c r="K530" s="1">
-        <v>5270.8334999999997</v>
+        <v>1200</v>
       </c>
       <c r="L530" s="1"/>
       <c r="M530" s="1"/>
       <c r="N530" s="1"/>
       <c r="O530" s="1">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="P530" s="1" t="s">
         <v>20</v>
@@ -22284,26 +22276,26 @@
         <v>41</v>
       </c>
       <c r="F531" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G531" s="1" t="s">
         <v>59</v>
       </c>
       <c r="H531" s="1"/>
       <c r="I531" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J531" s="1">
-        <v>0.1</v>
+        <v>0.11111111</v>
       </c>
       <c r="K531" s="1">
-        <v>1200</v>
+        <v>3111.1109999999999</v>
       </c>
       <c r="L531" s="1"/>
       <c r="M531" s="1"/>
       <c r="N531" s="1"/>
       <c r="O531" s="1">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="P531" s="1" t="s">
         <v>20</v>
@@ -22323,29 +22315,25 @@
         <v>57</v>
       </c>
       <c r="E532" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F532" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="G532" s="1" t="s">
-        <v>59</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="F532" s="1"/>
+      <c r="G532" s="1"/>
       <c r="H532" s="1"/>
       <c r="I532" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J532" s="1">
-        <v>0.11111111</v>
+        <v>1.6666666000000001</v>
       </c>
       <c r="K532" s="1">
-        <v>3111.1109999999999</v>
+        <v>43333.332000000002</v>
       </c>
       <c r="L532" s="1"/>
       <c r="M532" s="1"/>
       <c r="N532" s="1"/>
       <c r="O532" s="1">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="P532" s="1" t="s">
         <v>20</v>
@@ -22371,19 +22359,19 @@
       <c r="G533" s="1"/>
       <c r="H533" s="1"/>
       <c r="I533" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="J533" s="1">
-        <v>1.6666666000000001</v>
+        <v>9.0416670000000003</v>
       </c>
       <c r="K533" s="1">
-        <v>43333.332000000002</v>
+        <v>171791.67</v>
       </c>
       <c r="L533" s="1"/>
       <c r="M533" s="1"/>
       <c r="N533" s="1"/>
       <c r="O533" s="1">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="P533" s="1" t="s">
         <v>20</v>
@@ -22409,19 +22397,19 @@
       <c r="G534" s="1"/>
       <c r="H534" s="1"/>
       <c r="I534" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J534" s="1">
-        <v>9.0416670000000003</v>
+        <v>18</v>
       </c>
       <c r="K534" s="1">
-        <v>171791.67</v>
+        <v>351000</v>
       </c>
       <c r="L534" s="1"/>
       <c r="M534" s="1"/>
       <c r="N534" s="1"/>
       <c r="O534" s="1">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="P534" s="1" t="s">
         <v>20</v>
@@ -22447,19 +22435,19 @@
       <c r="G535" s="1"/>
       <c r="H535" s="1"/>
       <c r="I535" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="J535" s="1">
-        <v>18</v>
+        <v>14.666667</v>
       </c>
       <c r="K535" s="1">
-        <v>351000</v>
+        <v>410666.66</v>
       </c>
       <c r="L535" s="1"/>
       <c r="M535" s="1"/>
       <c r="N535" s="1"/>
       <c r="O535" s="1">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="P535" s="1" t="s">
         <v>20</v>
@@ -22485,19 +22473,19 @@
       <c r="G536" s="1"/>
       <c r="H536" s="1"/>
       <c r="I536" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J536" s="1">
-        <v>14.666667</v>
+        <v>4.5</v>
       </c>
       <c r="K536" s="1">
-        <v>410666.66</v>
+        <v>78750</v>
       </c>
       <c r="L536" s="1"/>
       <c r="M536" s="1"/>
       <c r="N536" s="1"/>
       <c r="O536" s="1">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="P536" s="1" t="s">
         <v>20</v>
@@ -22523,19 +22511,19 @@
       <c r="G537" s="1"/>
       <c r="H537" s="1"/>
       <c r="I537" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J537" s="1">
-        <v>4.5</v>
+        <v>14.541667</v>
       </c>
       <c r="K537" s="1">
-        <v>78750</v>
+        <v>487145.84</v>
       </c>
       <c r="L537" s="1"/>
       <c r="M537" s="1"/>
       <c r="N537" s="1"/>
       <c r="O537" s="1">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="P537" s="1" t="s">
         <v>20</v>
@@ -22561,19 +22549,19 @@
       <c r="G538" s="1"/>
       <c r="H538" s="1"/>
       <c r="I538" s="1" t="s">
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="J538" s="1">
-        <v>14.541667</v>
+        <v>6.5833335000000002</v>
       </c>
       <c r="K538" s="1">
-        <v>487145.84</v>
+        <v>220541.67</v>
       </c>
       <c r="L538" s="1"/>
       <c r="M538" s="1"/>
       <c r="N538" s="1"/>
       <c r="O538" s="1">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="P538" s="1" t="s">
         <v>20</v>
@@ -22599,19 +22587,19 @@
       <c r="G539" s="1"/>
       <c r="H539" s="1"/>
       <c r="I539" s="1" t="s">
-        <v>97</v>
+        <v>19</v>
       </c>
       <c r="J539" s="1">
-        <v>6.5833335000000002</v>
+        <v>11</v>
       </c>
       <c r="K539" s="1">
-        <v>220541.67</v>
+        <v>115500</v>
       </c>
       <c r="L539" s="1"/>
       <c r="M539" s="1"/>
       <c r="N539" s="1"/>
       <c r="O539" s="1">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="P539" s="1" t="s">
         <v>20</v>
@@ -22637,19 +22625,19 @@
       <c r="G540" s="1"/>
       <c r="H540" s="1"/>
       <c r="I540" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J540" s="1">
-        <v>11</v>
+        <v>51.8</v>
       </c>
       <c r="K540" s="1">
-        <v>115500</v>
+        <v>621600</v>
       </c>
       <c r="L540" s="1"/>
       <c r="M540" s="1"/>
       <c r="N540" s="1"/>
       <c r="O540" s="1">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="P540" s="1" t="s">
         <v>20</v>
@@ -22675,19 +22663,19 @@
       <c r="G541" s="1"/>
       <c r="H541" s="1"/>
       <c r="I541" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J541" s="1">
-        <v>51.8</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="K541" s="1">
-        <v>621600</v>
+        <v>58200</v>
       </c>
       <c r="L541" s="1"/>
       <c r="M541" s="1"/>
       <c r="N541" s="1"/>
       <c r="O541" s="1">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="P541" s="1" t="s">
         <v>20</v>
@@ -22713,19 +22701,19 @@
       <c r="G542" s="1"/>
       <c r="H542" s="1"/>
       <c r="I542" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J542" s="1">
-        <v>9.6999999999999993</v>
+        <v>4</v>
       </c>
       <c r="K542" s="1">
-        <v>58200</v>
+        <v>50000</v>
       </c>
       <c r="L542" s="1"/>
       <c r="M542" s="1"/>
       <c r="N542" s="1"/>
       <c r="O542" s="1">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="P542" s="1" t="s">
         <v>20</v>
@@ -22751,19 +22739,19 @@
       <c r="G543" s="1"/>
       <c r="H543" s="1"/>
       <c r="I543" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J543" s="1">
-        <v>4</v>
+        <v>9.5</v>
       </c>
       <c r="K543" s="1">
-        <v>50000</v>
+        <v>147250</v>
       </c>
       <c r="L543" s="1"/>
       <c r="M543" s="1"/>
       <c r="N543" s="1"/>
       <c r="O543" s="1">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="P543" s="1" t="s">
         <v>20</v>
@@ -22789,19 +22777,19 @@
       <c r="G544" s="1"/>
       <c r="H544" s="1"/>
       <c r="I544" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J544" s="1">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="K544" s="1">
-        <v>147250</v>
+        <v>131750</v>
       </c>
       <c r="L544" s="1"/>
       <c r="M544" s="1"/>
       <c r="N544" s="1"/>
       <c r="O544" s="1">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="P544" s="1" t="s">
         <v>20</v>
@@ -22827,19 +22815,19 @@
       <c r="G545" s="1"/>
       <c r="H545" s="1"/>
       <c r="I545" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J545" s="1">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="K545" s="1">
-        <v>131750</v>
+        <v>180000</v>
       </c>
       <c r="L545" s="1"/>
       <c r="M545" s="1"/>
       <c r="N545" s="1"/>
       <c r="O545" s="1">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="P545" s="1" t="s">
         <v>20</v>
@@ -22865,19 +22853,19 @@
       <c r="G546" s="1"/>
       <c r="H546" s="1"/>
       <c r="I546" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J546" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K546" s="1">
-        <v>180000</v>
+        <v>31500</v>
       </c>
       <c r="L546" s="1"/>
       <c r="M546" s="1"/>
       <c r="N546" s="1"/>
       <c r="O546" s="1">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="P546" s="1" t="s">
         <v>20</v>
@@ -22903,19 +22891,19 @@
       <c r="G547" s="1"/>
       <c r="H547" s="1"/>
       <c r="I547" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J547" s="1">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K547" s="1">
-        <v>31500</v>
+        <v>218500</v>
       </c>
       <c r="L547" s="1"/>
       <c r="M547" s="1"/>
       <c r="N547" s="1"/>
       <c r="O547" s="1">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="P547" s="1" t="s">
         <v>20</v>
@@ -22941,19 +22929,19 @@
       <c r="G548" s="1"/>
       <c r="H548" s="1"/>
       <c r="I548" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J548" s="1">
-        <v>19</v>
+        <v>7.125</v>
       </c>
       <c r="K548" s="1">
-        <v>218500</v>
+        <v>188812.5</v>
       </c>
       <c r="L548" s="1"/>
       <c r="M548" s="1"/>
       <c r="N548" s="1"/>
       <c r="O548" s="1">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="P548" s="1" t="s">
         <v>20</v>
@@ -22967,10 +22955,10 @@
         <v>0</v>
       </c>
       <c r="C549" s="1" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="D549" s="1" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="E549" s="1" t="s">
         <v>18</v>
@@ -22979,19 +22967,19 @@
       <c r="G549" s="1"/>
       <c r="H549" s="1"/>
       <c r="I549" s="1" t="s">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J549" s="1">
-        <v>7.125</v>
+        <v>66.916663999999997</v>
       </c>
       <c r="K549" s="1">
-        <v>188812.5</v>
+        <v>736083.3</v>
       </c>
       <c r="L549" s="1"/>
       <c r="M549" s="1"/>
       <c r="N549" s="1"/>
       <c r="O549" s="1">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="P549" s="1" t="s">
         <v>20</v>
@@ -23017,19 +23005,19 @@
       <c r="G550" s="1"/>
       <c r="H550" s="1"/>
       <c r="I550" s="1" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J550" s="1">
-        <v>66.916663999999997</v>
+        <v>0.16666666999999999</v>
       </c>
       <c r="K550" s="1">
-        <v>736083.3</v>
+        <v>1500</v>
       </c>
       <c r="L550" s="1"/>
       <c r="M550" s="1"/>
       <c r="N550" s="1"/>
       <c r="O550" s="1">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="P550" s="1" t="s">
         <v>20</v>
@@ -23055,19 +23043,19 @@
       <c r="G551" s="1"/>
       <c r="H551" s="1"/>
       <c r="I551" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J551" s="1">
-        <v>0.16666666999999999</v>
+        <v>0.5</v>
       </c>
       <c r="K551" s="1">
-        <v>1500</v>
+        <v>7500</v>
       </c>
       <c r="L551" s="1"/>
       <c r="M551" s="1"/>
       <c r="N551" s="1"/>
       <c r="O551" s="1">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="P551" s="1" t="s">
         <v>20</v>
@@ -23093,19 +23081,19 @@
       <c r="G552" s="1"/>
       <c r="H552" s="1"/>
       <c r="I552" s="1" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="J552" s="1">
-        <v>0.5</v>
+        <v>7.75</v>
       </c>
       <c r="K552" s="1">
-        <v>7500</v>
+        <v>69750</v>
       </c>
       <c r="L552" s="1"/>
       <c r="M552" s="1"/>
       <c r="N552" s="1"/>
       <c r="O552" s="1">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="P552" s="1" t="s">
         <v>20</v>
@@ -23131,19 +23119,19 @@
       <c r="G553" s="1"/>
       <c r="H553" s="1"/>
       <c r="I553" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J553" s="1">
-        <v>7.75</v>
+        <v>26.625</v>
       </c>
       <c r="K553" s="1">
-        <v>69750</v>
+        <v>399375</v>
       </c>
       <c r="L553" s="1"/>
       <c r="M553" s="1"/>
       <c r="N553" s="1"/>
       <c r="O553" s="1">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="P553" s="1" t="s">
         <v>20</v>
@@ -23151,37 +23139,37 @@
     </row>
     <row r="554" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A554" s="2">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="B554" s="1">
         <v>0</v>
       </c>
       <c r="C554" s="1" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="D554" s="1" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="E554" s="1" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F554" s="1"/>
       <c r="G554" s="1"/>
       <c r="H554" s="1"/>
       <c r="I554" s="1" t="s">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="J554" s="1">
-        <v>26.625</v>
+        <v>49</v>
       </c>
       <c r="K554" s="1">
-        <v>399375</v>
+        <v>514500</v>
       </c>
       <c r="L554" s="1"/>
       <c r="M554" s="1"/>
       <c r="N554" s="1"/>
       <c r="O554" s="1">
-        <v>1901</v>
+        <v>1592</v>
       </c>
       <c r="P554" s="1" t="s">
         <v>20</v>
@@ -23207,19 +23195,19 @@
       <c r="G555" s="1"/>
       <c r="H555" s="1"/>
       <c r="I555" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J555" s="1">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="K555" s="1">
-        <v>514500</v>
+        <v>66000</v>
       </c>
       <c r="L555" s="1"/>
       <c r="M555" s="1"/>
       <c r="N555" s="1"/>
       <c r="O555" s="1">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="P555" s="1" t="s">
         <v>20</v>
@@ -23245,19 +23233,19 @@
       <c r="G556" s="1"/>
       <c r="H556" s="1"/>
       <c r="I556" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J556" s="1">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K556" s="1">
-        <v>66000</v>
+        <v>30000</v>
       </c>
       <c r="L556" s="1"/>
       <c r="M556" s="1"/>
       <c r="N556" s="1"/>
       <c r="O556" s="1">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="P556" s="1" t="s">
         <v>20</v>
@@ -23283,19 +23271,19 @@
       <c r="G557" s="1"/>
       <c r="H557" s="1"/>
       <c r="I557" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J557" s="1">
-        <v>5</v>
+        <v>22.1</v>
       </c>
       <c r="K557" s="1">
-        <v>30000</v>
+        <v>265200</v>
       </c>
       <c r="L557" s="1"/>
       <c r="M557" s="1"/>
       <c r="N557" s="1"/>
       <c r="O557" s="1">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="P557" s="1" t="s">
         <v>20</v>
@@ -23321,19 +23309,19 @@
       <c r="G558" s="1"/>
       <c r="H558" s="1"/>
       <c r="I558" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J558" s="1">
-        <v>22.1</v>
+        <v>15.166667</v>
       </c>
       <c r="K558" s="1">
-        <v>265200</v>
+        <v>265416.65999999997</v>
       </c>
       <c r="L558" s="1"/>
       <c r="M558" s="1"/>
       <c r="N558" s="1"/>
       <c r="O558" s="1">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="P558" s="1" t="s">
         <v>20</v>
@@ -23359,19 +23347,19 @@
       <c r="G559" s="1"/>
       <c r="H559" s="1"/>
       <c r="I559" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J559" s="1">
-        <v>15.166667</v>
+        <v>13.875</v>
       </c>
       <c r="K559" s="1">
-        <v>265416.65999999997</v>
+        <v>464812.5</v>
       </c>
       <c r="L559" s="1"/>
       <c r="M559" s="1"/>
       <c r="N559" s="1"/>
       <c r="O559" s="1">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="P559" s="1" t="s">
         <v>20</v>
@@ -23397,19 +23385,19 @@
       <c r="G560" s="1"/>
       <c r="H560" s="1"/>
       <c r="I560" s="1" t="s">
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="J560" s="1">
-        <v>13.875</v>
+        <v>4.5</v>
       </c>
       <c r="K560" s="1">
-        <v>464812.5</v>
+        <v>150750</v>
       </c>
       <c r="L560" s="1"/>
       <c r="M560" s="1"/>
       <c r="N560" s="1"/>
       <c r="O560" s="1">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="P560" s="1" t="s">
         <v>20</v>
@@ -23435,19 +23423,19 @@
       <c r="G561" s="1"/>
       <c r="H561" s="1"/>
       <c r="I561" s="1" t="s">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="J561" s="1">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="K561" s="1">
-        <v>150750</v>
+        <v>190000</v>
       </c>
       <c r="L561" s="1"/>
       <c r="M561" s="1"/>
       <c r="N561" s="1"/>
       <c r="O561" s="1">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="P561" s="1" t="s">
         <v>20</v>
@@ -23473,19 +23461,19 @@
       <c r="G562" s="1"/>
       <c r="H562" s="1"/>
       <c r="I562" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J562" s="1">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="K562" s="1">
-        <v>190000</v>
+        <v>507000</v>
       </c>
       <c r="L562" s="1"/>
       <c r="M562" s="1"/>
       <c r="N562" s="1"/>
       <c r="O562" s="1">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="P562" s="1" t="s">
         <v>20</v>
@@ -23511,19 +23499,19 @@
       <c r="G563" s="1"/>
       <c r="H563" s="1"/>
       <c r="I563" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="J563" s="1">
-        <v>26</v>
+        <v>17.555554999999998</v>
       </c>
       <c r="K563" s="1">
-        <v>507000</v>
+        <v>491555.56</v>
       </c>
       <c r="L563" s="1"/>
       <c r="M563" s="1"/>
       <c r="N563" s="1"/>
       <c r="O563" s="1">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="P563" s="1" t="s">
         <v>20</v>
@@ -23549,19 +23537,19 @@
       <c r="G564" s="1"/>
       <c r="H564" s="1"/>
       <c r="I564" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J564" s="1">
-        <v>17.555554999999998</v>
+        <v>8.8888890000000007</v>
       </c>
       <c r="K564" s="1">
-        <v>491555.56</v>
+        <v>231111.11</v>
       </c>
       <c r="L564" s="1"/>
       <c r="M564" s="1"/>
       <c r="N564" s="1"/>
       <c r="O564" s="1">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="P564" s="1" t="s">
         <v>20</v>
@@ -23587,19 +23575,19 @@
       <c r="G565" s="1"/>
       <c r="H565" s="1"/>
       <c r="I565" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J565" s="1">
-        <v>8.8888890000000007</v>
+        <v>8.9166670000000003</v>
       </c>
       <c r="K565" s="1">
-        <v>231111.11</v>
+        <v>111458.336</v>
       </c>
       <c r="L565" s="1"/>
       <c r="M565" s="1"/>
       <c r="N565" s="1"/>
       <c r="O565" s="1">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="P565" s="1" t="s">
         <v>20</v>
@@ -23625,19 +23613,19 @@
       <c r="G566" s="1"/>
       <c r="H566" s="1"/>
       <c r="I566" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J566" s="1">
-        <v>8.9166670000000003</v>
+        <v>3.5</v>
       </c>
       <c r="K566" s="1">
-        <v>111458.336</v>
+        <v>43750</v>
       </c>
       <c r="L566" s="1"/>
       <c r="M566" s="1"/>
       <c r="N566" s="1"/>
       <c r="O566" s="1">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="P566" s="1" t="s">
         <v>20</v>
@@ -23663,19 +23651,19 @@
       <c r="G567" s="1"/>
       <c r="H567" s="1"/>
       <c r="I567" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J567" s="1">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="K567" s="1">
-        <v>43750</v>
+        <v>170500</v>
       </c>
       <c r="L567" s="1"/>
       <c r="M567" s="1"/>
       <c r="N567" s="1"/>
       <c r="O567" s="1">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="P567" s="1" t="s">
         <v>20</v>
@@ -23701,19 +23689,19 @@
       <c r="G568" s="1"/>
       <c r="H568" s="1"/>
       <c r="I568" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J568" s="1">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="K568" s="1">
-        <v>170500</v>
+        <v>85250</v>
       </c>
       <c r="L568" s="1"/>
       <c r="M568" s="1"/>
       <c r="N568" s="1"/>
       <c r="O568" s="1">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="P568" s="1" t="s">
         <v>20</v>
@@ -23739,19 +23727,19 @@
       <c r="G569" s="1"/>
       <c r="H569" s="1"/>
       <c r="I569" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J569" s="1">
-        <v>5.5</v>
+        <v>10.166667</v>
       </c>
       <c r="K569" s="1">
-        <v>85250</v>
+        <v>101666.664</v>
       </c>
       <c r="L569" s="1"/>
       <c r="M569" s="1"/>
       <c r="N569" s="1"/>
       <c r="O569" s="1">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="P569" s="1" t="s">
         <v>20</v>
@@ -23777,19 +23765,19 @@
       <c r="G570" s="1"/>
       <c r="H570" s="1"/>
       <c r="I570" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J570" s="1">
-        <v>10.166667</v>
+        <v>7</v>
       </c>
       <c r="K570" s="1">
-        <v>101666.664</v>
+        <v>84000</v>
       </c>
       <c r="L570" s="1"/>
       <c r="M570" s="1"/>
       <c r="N570" s="1"/>
       <c r="O570" s="1">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="P570" s="1" t="s">
         <v>20</v>
@@ -23815,19 +23803,19 @@
       <c r="G571" s="1"/>
       <c r="H571" s="1"/>
       <c r="I571" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J571" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K571" s="1">
-        <v>84000</v>
+        <v>55000</v>
       </c>
       <c r="L571" s="1"/>
       <c r="M571" s="1"/>
       <c r="N571" s="1"/>
       <c r="O571" s="1">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="P571" s="1" t="s">
         <v>20</v>
@@ -23853,19 +23841,19 @@
       <c r="G572" s="1"/>
       <c r="H572" s="1"/>
       <c r="I572" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J572" s="1">
-        <v>5</v>
+        <v>4.8333335000000002</v>
       </c>
       <c r="K572" s="1">
-        <v>55000</v>
+        <v>87000</v>
       </c>
       <c r="L572" s="1"/>
       <c r="M572" s="1"/>
       <c r="N572" s="1"/>
       <c r="O572" s="1">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="P572" s="1" t="s">
         <v>20</v>
@@ -23891,19 +23879,19 @@
       <c r="G573" s="1"/>
       <c r="H573" s="1"/>
       <c r="I573" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J573" s="1">
-        <v>4.8333335000000002</v>
+        <v>12</v>
       </c>
       <c r="K573" s="1">
-        <v>87000</v>
+        <v>318000</v>
       </c>
       <c r="L573" s="1"/>
       <c r="M573" s="1"/>
       <c r="N573" s="1"/>
       <c r="O573" s="1">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="P573" s="1" t="s">
         <v>20</v>
@@ -23929,19 +23917,19 @@
       <c r="G574" s="1"/>
       <c r="H574" s="1"/>
       <c r="I574" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J574" s="1">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K574" s="1">
-        <v>318000</v>
+        <v>67500</v>
       </c>
       <c r="L574" s="1"/>
       <c r="M574" s="1"/>
       <c r="N574" s="1"/>
       <c r="O574" s="1">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="P574" s="1" t="s">
         <v>20</v>
@@ -23967,19 +23955,19 @@
       <c r="G575" s="1"/>
       <c r="H575" s="1"/>
       <c r="I575" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J575" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K575" s="1">
-        <v>67500</v>
+        <v>230000</v>
       </c>
       <c r="L575" s="1"/>
       <c r="M575" s="1"/>
       <c r="N575" s="1"/>
       <c r="O575" s="1">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="P575" s="1" t="s">
         <v>20</v>
@@ -23999,25 +23987,25 @@
         <v>17</v>
       </c>
       <c r="E576" s="1" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F576" s="1"/>
       <c r="G576" s="1"/>
       <c r="H576" s="1"/>
       <c r="I576" s="1" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="J576" s="1">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="K576" s="1">
-        <v>230000</v>
+        <v>378000</v>
       </c>
       <c r="L576" s="1"/>
       <c r="M576" s="1"/>
       <c r="N576" s="1"/>
       <c r="O576" s="1">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="P576" s="1" t="s">
         <v>20</v>
@@ -24043,19 +24031,19 @@
       <c r="G577" s="1"/>
       <c r="H577" s="1"/>
       <c r="I577" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J577" s="1">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="K577" s="1">
-        <v>378000</v>
+        <v>66000</v>
       </c>
       <c r="L577" s="1"/>
       <c r="M577" s="1"/>
       <c r="N577" s="1"/>
       <c r="O577" s="1">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="P577" s="1" t="s">
         <v>20</v>
@@ -24081,19 +24069,19 @@
       <c r="G578" s="1"/>
       <c r="H578" s="1"/>
       <c r="I578" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J578" s="1">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K578" s="1">
-        <v>66000</v>
+        <v>32500</v>
       </c>
       <c r="L578" s="1"/>
       <c r="M578" s="1"/>
       <c r="N578" s="1"/>
       <c r="O578" s="1">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="P578" s="1" t="s">
         <v>20</v>
@@ -24119,19 +24107,19 @@
       <c r="G579" s="1"/>
       <c r="H579" s="1"/>
       <c r="I579" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J579" s="1">
-        <v>5</v>
+        <v>21.1</v>
       </c>
       <c r="K579" s="1">
-        <v>32500</v>
+        <v>253200</v>
       </c>
       <c r="L579" s="1"/>
       <c r="M579" s="1"/>
       <c r="N579" s="1"/>
       <c r="O579" s="1">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="P579" s="1" t="s">
         <v>20</v>
@@ -24157,19 +24145,19 @@
       <c r="G580" s="1"/>
       <c r="H580" s="1"/>
       <c r="I580" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J580" s="1">
-        <v>21.1</v>
+        <v>13.166667</v>
       </c>
       <c r="K580" s="1">
-        <v>253200</v>
+        <v>230416.67</v>
       </c>
       <c r="L580" s="1"/>
       <c r="M580" s="1"/>
       <c r="N580" s="1"/>
       <c r="O580" s="1">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="P580" s="1" t="s">
         <v>20</v>
@@ -24195,19 +24183,19 @@
       <c r="G581" s="1"/>
       <c r="H581" s="1"/>
       <c r="I581" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J581" s="1">
-        <v>13.166667</v>
+        <v>10.875</v>
       </c>
       <c r="K581" s="1">
-        <v>230416.67</v>
+        <v>364312.5</v>
       </c>
       <c r="L581" s="1"/>
       <c r="M581" s="1"/>
       <c r="N581" s="1"/>
       <c r="O581" s="1">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="P581" s="1" t="s">
         <v>20</v>
@@ -24233,19 +24221,19 @@
       <c r="G582" s="1"/>
       <c r="H582" s="1"/>
       <c r="I582" s="1" t="s">
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="J582" s="1">
-        <v>10.875</v>
+        <v>1.5</v>
       </c>
       <c r="K582" s="1">
-        <v>364312.5</v>
+        <v>50250</v>
       </c>
       <c r="L582" s="1"/>
       <c r="M582" s="1"/>
       <c r="N582" s="1"/>
       <c r="O582" s="1">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="P582" s="1" t="s">
         <v>20</v>
@@ -24271,19 +24259,19 @@
       <c r="G583" s="1"/>
       <c r="H583" s="1"/>
       <c r="I583" s="1" t="s">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="J583" s="1">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="K583" s="1">
-        <v>50250</v>
+        <v>190000</v>
       </c>
       <c r="L583" s="1"/>
       <c r="M583" s="1"/>
       <c r="N583" s="1"/>
       <c r="O583" s="1">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="P583" s="1" t="s">
         <v>20</v>
@@ -24309,19 +24297,19 @@
       <c r="G584" s="1"/>
       <c r="H584" s="1"/>
       <c r="I584" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J584" s="1">
-        <v>10</v>
+        <v>22.5</v>
       </c>
       <c r="K584" s="1">
-        <v>190000</v>
+        <v>438750</v>
       </c>
       <c r="L584" s="1"/>
       <c r="M584" s="1"/>
       <c r="N584" s="1"/>
       <c r="O584" s="1">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="P584" s="1" t="s">
         <v>20</v>
@@ -24347,19 +24335,19 @@
       <c r="G585" s="1"/>
       <c r="H585" s="1"/>
       <c r="I585" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="J585" s="1">
-        <v>22.5</v>
+        <v>15.444445</v>
       </c>
       <c r="K585" s="1">
-        <v>438750</v>
+        <v>432444.44</v>
       </c>
       <c r="L585" s="1"/>
       <c r="M585" s="1"/>
       <c r="N585" s="1"/>
       <c r="O585" s="1">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="P585" s="1" t="s">
         <v>20</v>
@@ -24385,19 +24373,19 @@
       <c r="G586" s="1"/>
       <c r="H586" s="1"/>
       <c r="I586" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J586" s="1">
-        <v>15.444445</v>
+        <v>4.6666664999999998</v>
       </c>
       <c r="K586" s="1">
-        <v>432444.44</v>
+        <v>121333.336</v>
       </c>
       <c r="L586" s="1"/>
       <c r="M586" s="1"/>
       <c r="N586" s="1"/>
       <c r="O586" s="1">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="P586" s="1" t="s">
         <v>20</v>
@@ -24423,19 +24411,19 @@
       <c r="G587" s="1"/>
       <c r="H587" s="1"/>
       <c r="I587" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J587" s="1">
-        <v>4.6666664999999998</v>
+        <v>8.9166670000000003</v>
       </c>
       <c r="K587" s="1">
-        <v>121333.336</v>
+        <v>111458.336</v>
       </c>
       <c r="L587" s="1"/>
       <c r="M587" s="1"/>
       <c r="N587" s="1"/>
       <c r="O587" s="1">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="P587" s="1" t="s">
         <v>20</v>
@@ -24461,19 +24449,19 @@
       <c r="G588" s="1"/>
       <c r="H588" s="1"/>
       <c r="I588" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J588" s="1">
-        <v>8.9166670000000003</v>
+        <v>3.5</v>
       </c>
       <c r="K588" s="1">
-        <v>111458.336</v>
+        <v>43750</v>
       </c>
       <c r="L588" s="1"/>
       <c r="M588" s="1"/>
       <c r="N588" s="1"/>
       <c r="O588" s="1">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="P588" s="1" t="s">
         <v>20</v>
@@ -24499,19 +24487,19 @@
       <c r="G589" s="1"/>
       <c r="H589" s="1"/>
       <c r="I589" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J589" s="1">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="K589" s="1">
-        <v>43750</v>
+        <v>170500</v>
       </c>
       <c r="L589" s="1"/>
       <c r="M589" s="1"/>
       <c r="N589" s="1"/>
       <c r="O589" s="1">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="P589" s="1" t="s">
         <v>20</v>
@@ -24537,19 +24525,19 @@
       <c r="G590" s="1"/>
       <c r="H590" s="1"/>
       <c r="I590" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J590" s="1">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="K590" s="1">
-        <v>170500</v>
+        <v>85250</v>
       </c>
       <c r="L590" s="1"/>
       <c r="M590" s="1"/>
       <c r="N590" s="1"/>
       <c r="O590" s="1">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="P590" s="1" t="s">
         <v>20</v>
@@ -24575,19 +24563,19 @@
       <c r="G591" s="1"/>
       <c r="H591" s="1"/>
       <c r="I591" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J591" s="1">
-        <v>5.5</v>
+        <v>8.1666670000000003</v>
       </c>
       <c r="K591" s="1">
-        <v>85250</v>
+        <v>81666.664000000004</v>
       </c>
       <c r="L591" s="1"/>
       <c r="M591" s="1"/>
       <c r="N591" s="1"/>
       <c r="O591" s="1">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="P591" s="1" t="s">
         <v>20</v>
@@ -24613,19 +24601,19 @@
       <c r="G592" s="1"/>
       <c r="H592" s="1"/>
       <c r="I592" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J592" s="1">
-        <v>8.1666670000000003</v>
+        <v>6.3333335000000002</v>
       </c>
       <c r="K592" s="1">
-        <v>81666.664000000004</v>
+        <v>76000</v>
       </c>
       <c r="L592" s="1"/>
       <c r="M592" s="1"/>
       <c r="N592" s="1"/>
       <c r="O592" s="1">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="P592" s="1" t="s">
         <v>20</v>
@@ -24651,19 +24639,19 @@
       <c r="G593" s="1"/>
       <c r="H593" s="1"/>
       <c r="I593" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J593" s="1">
-        <v>6.3333335000000002</v>
+        <v>5</v>
       </c>
       <c r="K593" s="1">
-        <v>76000</v>
+        <v>55000</v>
       </c>
       <c r="L593" s="1"/>
       <c r="M593" s="1"/>
       <c r="N593" s="1"/>
       <c r="O593" s="1">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="P593" s="1" t="s">
         <v>20</v>
@@ -24689,19 +24677,19 @@
       <c r="G594" s="1"/>
       <c r="H594" s="1"/>
       <c r="I594" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J594" s="1">
-        <v>5</v>
+        <v>4.8333335000000002</v>
       </c>
       <c r="K594" s="1">
-        <v>55000</v>
+        <v>87000</v>
       </c>
       <c r="L594" s="1"/>
       <c r="M594" s="1"/>
       <c r="N594" s="1"/>
       <c r="O594" s="1">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="P594" s="1" t="s">
         <v>20</v>
@@ -24727,19 +24715,19 @@
       <c r="G595" s="1"/>
       <c r="H595" s="1"/>
       <c r="I595" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J595" s="1">
-        <v>4.8333335000000002</v>
+        <v>9.5</v>
       </c>
       <c r="K595" s="1">
-        <v>87000</v>
+        <v>251750</v>
       </c>
       <c r="L595" s="1"/>
       <c r="M595" s="1"/>
       <c r="N595" s="1"/>
       <c r="O595" s="1">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="P595" s="1" t="s">
         <v>20</v>
@@ -24765,19 +24753,19 @@
       <c r="G596" s="1"/>
       <c r="H596" s="1"/>
       <c r="I596" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J596" s="1">
-        <v>9.5</v>
+        <v>14</v>
       </c>
       <c r="K596" s="1">
-        <v>251750</v>
+        <v>63000</v>
       </c>
       <c r="L596" s="1"/>
       <c r="M596" s="1"/>
       <c r="N596" s="1"/>
       <c r="O596" s="1">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="P596" s="1" t="s">
         <v>20</v>
@@ -24803,19 +24791,19 @@
       <c r="G597" s="1"/>
       <c r="H597" s="1"/>
       <c r="I597" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J597" s="1">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K597" s="1">
-        <v>63000</v>
+        <v>230000</v>
       </c>
       <c r="L597" s="1"/>
       <c r="M597" s="1"/>
       <c r="N597" s="1"/>
       <c r="O597" s="1">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="P597" s="1" t="s">
         <v>20</v>
@@ -24835,25 +24823,33 @@
         <v>17</v>
       </c>
       <c r="E598" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F598" s="1"/>
-      <c r="G598" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="F598" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G598" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="H598" s="1"/>
       <c r="I598" s="1" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="J598" s="1">
-        <v>20</v>
+        <v>0.5</v>
       </c>
       <c r="K598" s="1">
-        <v>230000</v>
-      </c>
-      <c r="L598" s="1"/>
-      <c r="M598" s="1"/>
+        <v>8750</v>
+      </c>
+      <c r="L598" s="1">
+        <v>3000</v>
+      </c>
+      <c r="M598" s="1">
+        <v>15000</v>
+      </c>
       <c r="N598" s="1"/>
       <c r="O598" s="1">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="P598" s="1" t="s">
         <v>20</v>
@@ -24876,30 +24872,26 @@
         <v>41</v>
       </c>
       <c r="F599" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G599" s="1" t="s">
         <v>50</v>
       </c>
       <c r="H599" s="1"/>
       <c r="I599" s="1" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="J599" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K599" s="1">
-        <v>8750</v>
-      </c>
-      <c r="L599" s="1">
-        <v>3000</v>
-      </c>
-      <c r="M599" s="1">
-        <v>15000</v>
-      </c>
+        <v>19500</v>
+      </c>
+      <c r="L599" s="1"/>
+      <c r="M599" s="1"/>
       <c r="N599" s="1"/>
       <c r="O599" s="1">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="P599" s="1" t="s">
         <v>20</v>
@@ -24922,26 +24914,26 @@
         <v>41</v>
       </c>
       <c r="F600" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G600" s="1" t="s">
         <v>50</v>
       </c>
       <c r="H600" s="1"/>
       <c r="I600" s="1" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="J600" s="1">
         <v>1</v>
       </c>
       <c r="K600" s="1">
-        <v>19500</v>
+        <v>33500</v>
       </c>
       <c r="L600" s="1"/>
       <c r="M600" s="1"/>
       <c r="N600" s="1"/>
       <c r="O600" s="1">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="P600" s="1" t="s">
         <v>20</v>
@@ -24964,14 +24956,14 @@
         <v>41</v>
       </c>
       <c r="F601" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G601" s="1" t="s">
         <v>50</v>
       </c>
       <c r="H601" s="1"/>
       <c r="I601" s="1" t="s">
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="J601" s="1">
         <v>1</v>
@@ -24983,7 +24975,7 @@
       <c r="M601" s="1"/>
       <c r="N601" s="1"/>
       <c r="O601" s="1">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="P601" s="1" t="s">
         <v>20</v>
@@ -25006,26 +24998,26 @@
         <v>41</v>
       </c>
       <c r="F602" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G602" s="1" t="s">
         <v>50</v>
       </c>
       <c r="H602" s="1"/>
       <c r="I602" s="1" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="J602" s="1">
-        <v>1</v>
+        <v>0.22222222</v>
       </c>
       <c r="K602" s="1">
-        <v>33500</v>
+        <v>6222.2219999999998</v>
       </c>
       <c r="L602" s="1"/>
       <c r="M602" s="1"/>
       <c r="N602" s="1"/>
       <c r="O602" s="1">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="P602" s="1" t="s">
         <v>20</v>
@@ -25048,26 +25040,26 @@
         <v>41</v>
       </c>
       <c r="F603" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G603" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H603" s="1"/>
       <c r="I603" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J603" s="1">
-        <v>0.22222222</v>
+        <v>0.5</v>
       </c>
       <c r="K603" s="1">
-        <v>6222.2219999999998</v>
+        <v>8750</v>
       </c>
       <c r="L603" s="1"/>
       <c r="M603" s="1"/>
       <c r="N603" s="1"/>
       <c r="O603" s="1">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="P603" s="1" t="s">
         <v>20</v>
@@ -25090,26 +25082,26 @@
         <v>41</v>
       </c>
       <c r="F604" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G604" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H604" s="1"/>
       <c r="I604" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J604" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K604" s="1">
-        <v>8750</v>
+        <v>26000</v>
       </c>
       <c r="L604" s="1"/>
       <c r="M604" s="1"/>
       <c r="N604" s="1"/>
       <c r="O604" s="1">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="P604" s="1" t="s">
         <v>20</v>
@@ -25132,26 +25124,26 @@
         <v>41</v>
       </c>
       <c r="F605" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G605" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H605" s="1"/>
       <c r="I605" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J605" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K605" s="1">
-        <v>26000</v>
+        <v>21000</v>
       </c>
       <c r="L605" s="1"/>
       <c r="M605" s="1"/>
       <c r="N605" s="1"/>
       <c r="O605" s="1">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="P605" s="1" t="s">
         <v>20</v>
@@ -25174,26 +25166,26 @@
         <v>41</v>
       </c>
       <c r="F606" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G606" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H606" s="1"/>
       <c r="I606" s="1" t="s">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="J606" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K606" s="1">
-        <v>21000</v>
+        <v>33500</v>
       </c>
       <c r="L606" s="1"/>
       <c r="M606" s="1"/>
       <c r="N606" s="1"/>
       <c r="O606" s="1">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="P606" s="1" t="s">
         <v>20</v>
@@ -25216,26 +25208,26 @@
         <v>41</v>
       </c>
       <c r="F607" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G607" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="H607" s="1"/>
       <c r="I607" s="1" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="J607" s="1">
         <v>1</v>
       </c>
       <c r="K607" s="1">
-        <v>33500</v>
+        <v>28000</v>
       </c>
       <c r="L607" s="1"/>
       <c r="M607" s="1"/>
       <c r="N607" s="1"/>
       <c r="O607" s="1">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="P607" s="1" t="s">
         <v>20</v>
@@ -25258,26 +25250,26 @@
         <v>41</v>
       </c>
       <c r="F608" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G608" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H608" s="1"/>
       <c r="I608" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J608" s="1">
         <v>1</v>
       </c>
       <c r="K608" s="1">
-        <v>28000</v>
+        <v>10500</v>
       </c>
       <c r="L608" s="1"/>
       <c r="M608" s="1"/>
       <c r="N608" s="1"/>
       <c r="O608" s="1">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="P608" s="1" t="s">
         <v>20</v>
@@ -25300,26 +25292,26 @@
         <v>41</v>
       </c>
       <c r="F609" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G609" s="1" t="s">
         <v>53</v>
       </c>
       <c r="H609" s="1"/>
       <c r="I609" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J609" s="1">
-        <v>1</v>
+        <v>0.44444444999999999</v>
       </c>
       <c r="K609" s="1">
-        <v>10500</v>
+        <v>12444.444</v>
       </c>
       <c r="L609" s="1"/>
       <c r="M609" s="1"/>
       <c r="N609" s="1"/>
       <c r="O609" s="1">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="P609" s="1" t="s">
         <v>20</v>
@@ -25342,26 +25334,26 @@
         <v>41</v>
       </c>
       <c r="F610" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G610" s="1" t="s">
         <v>53</v>
       </c>
       <c r="H610" s="1"/>
       <c r="I610" s="1" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="J610" s="1">
-        <v>0.44444444999999999</v>
+        <v>1</v>
       </c>
       <c r="K610" s="1">
-        <v>12444.444</v>
+        <v>26500</v>
       </c>
       <c r="L610" s="1"/>
       <c r="M610" s="1"/>
       <c r="N610" s="1"/>
       <c r="O610" s="1">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="P610" s="1" t="s">
         <v>20</v>
@@ -25384,26 +25376,26 @@
         <v>41</v>
       </c>
       <c r="F611" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G611" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H611" s="1"/>
       <c r="I611" s="1" t="s">
         <v>40</v>
       </c>
       <c r="J611" s="1">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="K611" s="1">
-        <v>26500</v>
+        <v>39750</v>
       </c>
       <c r="L611" s="1"/>
       <c r="M611" s="1"/>
       <c r="N611" s="1"/>
       <c r="O611" s="1">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="P611" s="1" t="s">
         <v>20</v>
@@ -25426,26 +25418,26 @@
         <v>41</v>
       </c>
       <c r="F612" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G612" s="1" t="s">
         <v>52</v>
       </c>
       <c r="H612" s="1"/>
       <c r="I612" s="1" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="J612" s="1">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K612" s="1">
-        <v>39750</v>
+        <v>10500</v>
       </c>
       <c r="L612" s="1"/>
       <c r="M612" s="1"/>
       <c r="N612" s="1"/>
       <c r="O612" s="1">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="P612" s="1" t="s">
         <v>20</v>
@@ -25468,26 +25460,26 @@
         <v>41</v>
       </c>
       <c r="F613" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G613" s="1" t="s">
         <v>52</v>
       </c>
       <c r="H613" s="1"/>
       <c r="I613" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J613" s="1">
-        <v>1</v>
+        <v>0.44444444999999999</v>
       </c>
       <c r="K613" s="1">
-        <v>10500</v>
+        <v>11555.556</v>
       </c>
       <c r="L613" s="1"/>
       <c r="M613" s="1"/>
       <c r="N613" s="1"/>
       <c r="O613" s="1">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="P613" s="1" t="s">
         <v>20</v>
@@ -25510,26 +25502,26 @@
         <v>41</v>
       </c>
       <c r="F614" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G614" s="1" t="s">
         <v>52</v>
       </c>
       <c r="H614" s="1"/>
       <c r="I614" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J614" s="1">
-        <v>0.44444444999999999</v>
+        <v>0.22222222</v>
       </c>
       <c r="K614" s="1">
-        <v>11555.556</v>
+        <v>6222.2219999999998</v>
       </c>
       <c r="L614" s="1"/>
       <c r="M614" s="1"/>
       <c r="N614" s="1"/>
       <c r="O614" s="1">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="P614" s="1" t="s">
         <v>20</v>
@@ -25552,26 +25544,26 @@
         <v>41</v>
       </c>
       <c r="F615" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G615" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H615" s="1"/>
       <c r="I615" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J615" s="1">
-        <v>0.22222222</v>
+        <v>1.5</v>
       </c>
       <c r="K615" s="1">
-        <v>6222.2219999999998</v>
+        <v>15750</v>
       </c>
       <c r="L615" s="1"/>
       <c r="M615" s="1"/>
       <c r="N615" s="1"/>
       <c r="O615" s="1">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="P615" s="1" t="s">
         <v>20</v>
@@ -25594,26 +25586,26 @@
         <v>41</v>
       </c>
       <c r="F616" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G616" s="1" t="s">
         <v>47</v>
       </c>
       <c r="H616" s="1"/>
       <c r="I616" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J616" s="1">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K616" s="1">
-        <v>15750</v>
+        <v>26000</v>
       </c>
       <c r="L616" s="1"/>
       <c r="M616" s="1"/>
       <c r="N616" s="1"/>
       <c r="O616" s="1">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="P616" s="1" t="s">
         <v>20</v>
@@ -25636,26 +25628,26 @@
         <v>41</v>
       </c>
       <c r="F617" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G617" s="1" t="s">
         <v>47</v>
       </c>
       <c r="H617" s="1"/>
       <c r="I617" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J617" s="1">
-        <v>1</v>
+        <v>0.22222222</v>
       </c>
       <c r="K617" s="1">
-        <v>26000</v>
+        <v>6222.2219999999998</v>
       </c>
       <c r="L617" s="1"/>
       <c r="M617" s="1"/>
       <c r="N617" s="1"/>
       <c r="O617" s="1">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="P617" s="1" t="s">
         <v>20</v>
@@ -25678,26 +25670,26 @@
         <v>41</v>
       </c>
       <c r="F618" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G618" s="1" t="s">
         <v>47</v>
       </c>
       <c r="H618" s="1"/>
       <c r="I618" s="1" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="J618" s="1">
-        <v>0.22222222</v>
+        <v>1</v>
       </c>
       <c r="K618" s="1">
-        <v>6222.2219999999998</v>
+        <v>4500</v>
       </c>
       <c r="L618" s="1"/>
       <c r="M618" s="1"/>
       <c r="N618" s="1"/>
       <c r="O618" s="1">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="P618" s="1" t="s">
         <v>20</v>
@@ -25720,26 +25712,26 @@
         <v>41</v>
       </c>
       <c r="F619" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G619" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H619" s="1"/>
       <c r="I619" s="1" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="J619" s="1">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="K619" s="1">
-        <v>4500</v>
+        <v>36750</v>
       </c>
       <c r="L619" s="1"/>
       <c r="M619" s="1"/>
       <c r="N619" s="1"/>
       <c r="O619" s="1">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="P619" s="1" t="s">
         <v>20</v>
@@ -25762,26 +25754,26 @@
         <v>41</v>
       </c>
       <c r="F620" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G620" s="1" t="s">
         <v>51</v>
       </c>
       <c r="H620" s="1"/>
       <c r="I620" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="J620" s="1">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="K620" s="1">
-        <v>36750</v>
+        <v>6000</v>
       </c>
       <c r="L620" s="1"/>
       <c r="M620" s="1"/>
       <c r="N620" s="1"/>
       <c r="O620" s="1">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="P620" s="1" t="s">
         <v>20</v>
@@ -25804,26 +25796,26 @@
         <v>41</v>
       </c>
       <c r="F621" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G621" s="1" t="s">
         <v>51</v>
       </c>
       <c r="H621" s="1"/>
       <c r="I621" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="J621" s="1">
-        <v>0.5</v>
+        <v>0.11111111</v>
       </c>
       <c r="K621" s="1">
-        <v>6000</v>
+        <v>2888.8890000000001</v>
       </c>
       <c r="L621" s="1"/>
       <c r="M621" s="1"/>
       <c r="N621" s="1"/>
       <c r="O621" s="1">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="P621" s="1" t="s">
         <v>20</v>
@@ -25846,26 +25838,26 @@
         <v>41</v>
       </c>
       <c r="F622" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G622" s="1" t="s">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="H622" s="1"/>
       <c r="I622" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J622" s="1">
-        <v>0.11111111</v>
+        <v>2</v>
       </c>
       <c r="K622" s="1">
-        <v>2888.8890000000001</v>
+        <v>21000</v>
       </c>
       <c r="L622" s="1"/>
       <c r="M622" s="1"/>
       <c r="N622" s="1"/>
       <c r="O622" s="1">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="P622" s="1" t="s">
         <v>20</v>
@@ -25888,26 +25880,26 @@
         <v>41</v>
       </c>
       <c r="F623" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G623" s="1" t="s">
         <v>99</v>
       </c>
       <c r="H623" s="1"/>
       <c r="I623" s="1" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="J623" s="1">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="K623" s="1">
-        <v>21000</v>
+        <v>9750</v>
       </c>
       <c r="L623" s="1"/>
       <c r="M623" s="1"/>
       <c r="N623" s="1"/>
       <c r="O623" s="1">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="P623" s="1" t="s">
         <v>20</v>
@@ -25930,26 +25922,26 @@
         <v>41</v>
       </c>
       <c r="F624" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G624" s="1" t="s">
         <v>99</v>
       </c>
       <c r="H624" s="1"/>
       <c r="I624" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="J624" s="1">
-        <v>0.5</v>
+        <v>0.44444444999999999</v>
       </c>
       <c r="K624" s="1">
-        <v>9750</v>
+        <v>11555.556</v>
       </c>
       <c r="L624" s="1"/>
       <c r="M624" s="1"/>
       <c r="N624" s="1"/>
       <c r="O624" s="1">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="P624" s="1" t="s">
         <v>20</v>
@@ -25972,26 +25964,26 @@
         <v>41</v>
       </c>
       <c r="F625" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G625" s="1" t="s">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="H625" s="1"/>
       <c r="I625" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J625" s="1">
-        <v>0.44444444999999999</v>
+        <v>1</v>
       </c>
       <c r="K625" s="1">
-        <v>11555.556</v>
+        <v>10500</v>
       </c>
       <c r="L625" s="1"/>
       <c r="M625" s="1"/>
       <c r="N625" s="1"/>
       <c r="O625" s="1">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="P625" s="1" t="s">
         <v>20</v>
@@ -26014,26 +26006,26 @@
         <v>41</v>
       </c>
       <c r="F626" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G626" s="1" t="s">
         <v>45</v>
       </c>
       <c r="H626" s="1"/>
       <c r="I626" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J626" s="1">
         <v>1</v>
       </c>
       <c r="K626" s="1">
-        <v>10500</v>
+        <v>26000</v>
       </c>
       <c r="L626" s="1"/>
       <c r="M626" s="1"/>
       <c r="N626" s="1"/>
       <c r="O626" s="1">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="P626" s="1" t="s">
         <v>20</v>
@@ -26056,26 +26048,26 @@
         <v>41</v>
       </c>
       <c r="F627" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G627" s="1" t="s">
         <v>45</v>
       </c>
       <c r="H627" s="1"/>
       <c r="I627" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J627" s="1">
         <v>1</v>
       </c>
       <c r="K627" s="1">
-        <v>26000</v>
+        <v>17500</v>
       </c>
       <c r="L627" s="1"/>
       <c r="M627" s="1"/>
       <c r="N627" s="1"/>
       <c r="O627" s="1">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="P627" s="1" t="s">
         <v>20</v>
@@ -26098,26 +26090,26 @@
         <v>41</v>
       </c>
       <c r="F628" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G628" s="1" t="s">
         <v>45</v>
       </c>
       <c r="H628" s="1"/>
       <c r="I628" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J628" s="1">
         <v>1</v>
       </c>
       <c r="K628" s="1">
-        <v>17500</v>
+        <v>10000</v>
       </c>
       <c r="L628" s="1"/>
       <c r="M628" s="1"/>
       <c r="N628" s="1"/>
       <c r="O628" s="1">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="P628" s="1" t="s">
         <v>20</v>
@@ -26140,10 +26132,10 @@
         <v>41</v>
       </c>
       <c r="F629" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G629" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H629" s="1"/>
       <c r="I629" s="1" t="s">
@@ -26159,7 +26151,7 @@
       <c r="M629" s="1"/>
       <c r="N629" s="1"/>
       <c r="O629" s="1">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="P629" s="1" t="s">
         <v>20</v>
@@ -26182,26 +26174,26 @@
         <v>41</v>
       </c>
       <c r="F630" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G630" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H630" s="1"/>
       <c r="I630" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J630" s="1">
-        <v>1</v>
+        <v>0.16666666999999999</v>
       </c>
       <c r="K630" s="1">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="L630" s="1"/>
       <c r="M630" s="1"/>
       <c r="N630" s="1"/>
       <c r="O630" s="1">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="P630" s="1" t="s">
         <v>20</v>
@@ -26224,26 +26216,26 @@
         <v>41</v>
       </c>
       <c r="F631" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G631" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H631" s="1"/>
       <c r="I631" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J631" s="1">
-        <v>0.16666666999999999</v>
+        <v>1</v>
       </c>
       <c r="K631" s="1">
-        <v>2000</v>
+        <v>12000</v>
       </c>
       <c r="L631" s="1"/>
       <c r="M631" s="1"/>
       <c r="N631" s="1"/>
       <c r="O631" s="1">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="P631" s="1" t="s">
         <v>20</v>
@@ -26266,26 +26258,26 @@
         <v>41</v>
       </c>
       <c r="F632" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G632" s="1" t="s">
         <v>46</v>
       </c>
       <c r="H632" s="1"/>
       <c r="I632" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J632" s="1">
         <v>1</v>
       </c>
       <c r="K632" s="1">
-        <v>12000</v>
+        <v>10500</v>
       </c>
       <c r="L632" s="1"/>
       <c r="M632" s="1"/>
       <c r="N632" s="1"/>
       <c r="O632" s="1">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="P632" s="1" t="s">
         <v>20</v>
@@ -26308,26 +26300,26 @@
         <v>41</v>
       </c>
       <c r="F633" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G633" s="1" t="s">
         <v>46</v>
       </c>
       <c r="H633" s="1"/>
       <c r="I633" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J633" s="1">
-        <v>1</v>
+        <v>0.22222222</v>
       </c>
       <c r="K633" s="1">
-        <v>10500</v>
+        <v>5777.7780000000002</v>
       </c>
       <c r="L633" s="1"/>
       <c r="M633" s="1"/>
       <c r="N633" s="1"/>
       <c r="O633" s="1">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="P633" s="1" t="s">
         <v>20</v>
@@ -26350,26 +26342,26 @@
         <v>41</v>
       </c>
       <c r="F634" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G634" s="1" t="s">
         <v>46</v>
       </c>
       <c r="H634" s="1"/>
       <c r="I634" s="1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="J634" s="1">
-        <v>0.22222222</v>
+        <v>0.5</v>
       </c>
       <c r="K634" s="1">
-        <v>5777.7780000000002</v>
+        <v>9750</v>
       </c>
       <c r="L634" s="1"/>
       <c r="M634" s="1"/>
       <c r="N634" s="1"/>
       <c r="O634" s="1">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="P634" s="1" t="s">
         <v>20</v>
@@ -26392,26 +26384,26 @@
         <v>41</v>
       </c>
       <c r="F635" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G635" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H635" s="1"/>
       <c r="I635" s="1" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="J635" s="1">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="K635" s="1">
-        <v>9750</v>
+        <v>67000</v>
       </c>
       <c r="L635" s="1"/>
       <c r="M635" s="1"/>
       <c r="N635" s="1"/>
       <c r="O635" s="1">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="P635" s="1" t="s">
         <v>20</v>
@@ -26434,26 +26426,26 @@
         <v>41</v>
       </c>
       <c r="F636" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G636" s="1" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="H636" s="1"/>
       <c r="I636" s="1" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J636" s="1">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K636" s="1">
-        <v>67000</v>
+        <v>29250</v>
       </c>
       <c r="L636" s="1"/>
       <c r="M636" s="1"/>
       <c r="N636" s="1"/>
       <c r="O636" s="1">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="P636" s="1" t="s">
         <v>20</v>
@@ -26476,26 +26468,26 @@
         <v>41</v>
       </c>
       <c r="F637" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G637" s="1" t="s">
         <v>100</v>
       </c>
       <c r="H637" s="1"/>
       <c r="I637" s="1" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="J637" s="1">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K637" s="1">
-        <v>29250</v>
+        <v>33500</v>
       </c>
       <c r="L637" s="1"/>
       <c r="M637" s="1"/>
       <c r="N637" s="1"/>
       <c r="O637" s="1">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="P637" s="1" t="s">
         <v>20</v>
@@ -26509,35 +26501,31 @@
         <v>0</v>
       </c>
       <c r="C638" s="1" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="D638" s="1" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="E638" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F638" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G638" s="1" t="s">
-        <v>100</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="F638" s="1"/>
+      <c r="G638" s="1"/>
       <c r="H638" s="1"/>
       <c r="I638" s="1" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="J638" s="1">
-        <v>1</v>
+        <v>80.25</v>
       </c>
       <c r="K638" s="1">
-        <v>33500</v>
+        <v>882750</v>
       </c>
       <c r="L638" s="1"/>
       <c r="M638" s="1"/>
       <c r="N638" s="1"/>
       <c r="O638" s="1">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="P638" s="1" t="s">
         <v>20</v>
@@ -26563,19 +26551,19 @@
       <c r="G639" s="1"/>
       <c r="H639" s="1"/>
       <c r="I639" s="1" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J639" s="1">
-        <v>80.25</v>
+        <v>3.6666666999999999</v>
       </c>
       <c r="K639" s="1">
-        <v>882750</v>
+        <v>33000</v>
       </c>
       <c r="L639" s="1"/>
       <c r="M639" s="1"/>
       <c r="N639" s="1"/>
       <c r="O639" s="1">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="P639" s="1" t="s">
         <v>20</v>
@@ -26601,19 +26589,19 @@
       <c r="G640" s="1"/>
       <c r="H640" s="1"/>
       <c r="I640" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J640" s="1">
-        <v>3.6666666999999999</v>
+        <v>4.5</v>
       </c>
       <c r="K640" s="1">
-        <v>33000</v>
+        <v>67500</v>
       </c>
       <c r="L640" s="1"/>
       <c r="M640" s="1"/>
       <c r="N640" s="1"/>
       <c r="O640" s="1">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="P640" s="1" t="s">
         <v>20</v>
@@ -26639,19 +26627,19 @@
       <c r="G641" s="1"/>
       <c r="H641" s="1"/>
       <c r="I641" s="1" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="J641" s="1">
-        <v>4.5</v>
+        <v>7.75</v>
       </c>
       <c r="K641" s="1">
-        <v>67500</v>
+        <v>69750</v>
       </c>
       <c r="L641" s="1"/>
       <c r="M641" s="1"/>
       <c r="N641" s="1"/>
       <c r="O641" s="1">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="P641" s="1" t="s">
         <v>20</v>
@@ -26677,19 +26665,19 @@
       <c r="G642" s="1"/>
       <c r="H642" s="1"/>
       <c r="I642" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J642" s="1">
-        <v>7.75</v>
+        <v>26.625</v>
       </c>
       <c r="K642" s="1">
-        <v>69750</v>
+        <v>399375</v>
       </c>
       <c r="L642" s="1"/>
       <c r="M642" s="1"/>
       <c r="N642" s="1"/>
       <c r="O642" s="1">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="P642" s="1" t="s">
         <v>20</v>
@@ -26709,25 +26697,31 @@
         <v>76</v>
       </c>
       <c r="E643" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F643" s="1"/>
-      <c r="G643" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="F643" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G643" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="H643" s="1"/>
       <c r="I643" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J643" s="1">
-        <v>26.625</v>
+        <v>0.41666666000000002</v>
       </c>
       <c r="K643" s="1">
-        <v>399375</v>
-      </c>
-      <c r="L643" s="1"/>
+        <v>4583.3334999999997</v>
+      </c>
+      <c r="L643" s="1">
+        <v>1000</v>
+      </c>
       <c r="M643" s="1"/>
       <c r="N643" s="1"/>
       <c r="O643" s="1">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="P643" s="1" t="s">
         <v>20</v>
@@ -26750,28 +26744,26 @@
         <v>41</v>
       </c>
       <c r="F644" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G644" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H644" s="1"/>
       <c r="I644" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J644" s="1">
-        <v>0.41666666000000002</v>
+        <v>0.33333333999999998</v>
       </c>
       <c r="K644" s="1">
-        <v>4583.3334999999997</v>
-      </c>
-      <c r="L644" s="1">
-        <v>1000</v>
-      </c>
+        <v>3666.6667000000002</v>
+      </c>
+      <c r="L644" s="1"/>
       <c r="M644" s="1"/>
       <c r="N644" s="1"/>
       <c r="O644" s="1">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="P644" s="1" t="s">
         <v>20</v>
@@ -26794,26 +26786,26 @@
         <v>41</v>
       </c>
       <c r="F645" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G645" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H645" s="1"/>
       <c r="I645" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J645" s="1">
-        <v>0.33333333999999998</v>
+        <v>0.41666666000000002</v>
       </c>
       <c r="K645" s="1">
-        <v>3666.6667000000002</v>
+        <v>4583.3334999999997</v>
       </c>
       <c r="L645" s="1"/>
       <c r="M645" s="1"/>
       <c r="N645" s="1"/>
       <c r="O645" s="1">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="P645" s="1" t="s">
         <v>20</v>
@@ -26836,26 +26828,26 @@
         <v>41</v>
       </c>
       <c r="F646" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G646" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H646" s="1"/>
       <c r="I646" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J646" s="1">
-        <v>0.41666666000000002</v>
+        <v>0.5</v>
       </c>
       <c r="K646" s="1">
-        <v>4583.3334999999997</v>
+        <v>5500</v>
       </c>
       <c r="L646" s="1"/>
       <c r="M646" s="1"/>
       <c r="N646" s="1"/>
       <c r="O646" s="1">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="P646" s="1" t="s">
         <v>20</v>
@@ -26878,26 +26870,26 @@
         <v>41</v>
       </c>
       <c r="F647" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G647" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H647" s="1"/>
       <c r="I647" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J647" s="1">
-        <v>0.5</v>
+        <v>0.41666666000000002</v>
       </c>
       <c r="K647" s="1">
-        <v>5500</v>
+        <v>4583.3334999999997</v>
       </c>
       <c r="L647" s="1"/>
       <c r="M647" s="1"/>
       <c r="N647" s="1"/>
       <c r="O647" s="1">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="P647" s="1" t="s">
         <v>20</v>
@@ -26920,26 +26912,26 @@
         <v>41</v>
       </c>
       <c r="F648" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G648" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H648" s="1"/>
       <c r="I648" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J648" s="1">
-        <v>0.41666666000000002</v>
+        <v>0.16666666999999999</v>
       </c>
       <c r="K648" s="1">
-        <v>4583.3334999999997</v>
+        <v>1833.3334</v>
       </c>
       <c r="L648" s="1"/>
       <c r="M648" s="1"/>
       <c r="N648" s="1"/>
       <c r="O648" s="1">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="P648" s="1" t="s">
         <v>20</v>
@@ -26962,26 +26954,26 @@
         <v>41</v>
       </c>
       <c r="F649" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G649" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H649" s="1"/>
       <c r="I649" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J649" s="1">
-        <v>0.16666666999999999</v>
+        <v>0.41666666000000002</v>
       </c>
       <c r="K649" s="1">
-        <v>1833.3334</v>
+        <v>4583.3334999999997</v>
       </c>
       <c r="L649" s="1"/>
       <c r="M649" s="1"/>
       <c r="N649" s="1"/>
       <c r="O649" s="1">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="P649" s="1" t="s">
         <v>20</v>
@@ -27004,26 +26996,26 @@
         <v>41</v>
       </c>
       <c r="F650" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G650" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H650" s="1"/>
       <c r="I650" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J650" s="1">
-        <v>0.41666666000000002</v>
+        <v>0.33333333999999998</v>
       </c>
       <c r="K650" s="1">
-        <v>4583.3334999999997</v>
+        <v>3666.6667000000002</v>
       </c>
       <c r="L650" s="1"/>
       <c r="M650" s="1"/>
       <c r="N650" s="1"/>
       <c r="O650" s="1">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="P650" s="1" t="s">
         <v>20</v>
@@ -27046,26 +27038,26 @@
         <v>41</v>
       </c>
       <c r="F651" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G651" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H651" s="1"/>
       <c r="I651" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J651" s="1">
-        <v>0.33333333999999998</v>
+        <v>8.3333335999999994E-2</v>
       </c>
       <c r="K651" s="1">
-        <v>3666.6667000000002</v>
+        <v>916.66669999999999</v>
       </c>
       <c r="L651" s="1"/>
       <c r="M651" s="1"/>
       <c r="N651" s="1"/>
       <c r="O651" s="1">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="P651" s="1" t="s">
         <v>20</v>
@@ -27088,10 +27080,10 @@
         <v>41</v>
       </c>
       <c r="F652" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G652" s="1" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="H652" s="1"/>
       <c r="I652" s="1" t="s">
@@ -27107,7 +27099,7 @@
       <c r="M652" s="1"/>
       <c r="N652" s="1"/>
       <c r="O652" s="1">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="P652" s="1" t="s">
         <v>20</v>
@@ -27130,26 +27122,26 @@
         <v>41</v>
       </c>
       <c r="F653" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G653" s="1" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="H653" s="1"/>
       <c r="I653" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J653" s="1">
-        <v>8.3333335999999994E-2</v>
+        <v>0.16666666999999999</v>
       </c>
       <c r="K653" s="1">
-        <v>916.66669999999999</v>
+        <v>1833.3334</v>
       </c>
       <c r="L653" s="1"/>
       <c r="M653" s="1"/>
       <c r="N653" s="1"/>
       <c r="O653" s="1">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="P653" s="1" t="s">
         <v>20</v>
@@ -27172,26 +27164,26 @@
         <v>41</v>
       </c>
       <c r="F654" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G654" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H654" s="1"/>
       <c r="I654" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J654" s="1">
-        <v>0.16666666999999999</v>
+        <v>0.41666666000000002</v>
       </c>
       <c r="K654" s="1">
-        <v>1833.3334</v>
+        <v>4583.3334999999997</v>
       </c>
       <c r="L654" s="1"/>
       <c r="M654" s="1"/>
       <c r="N654" s="1"/>
       <c r="O654" s="1">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="P654" s="1" t="s">
         <v>20</v>
@@ -27214,26 +27206,26 @@
         <v>41</v>
       </c>
       <c r="F655" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G655" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H655" s="1"/>
       <c r="I655" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J655" s="1">
-        <v>0.41666666000000002</v>
+        <v>0.75</v>
       </c>
       <c r="K655" s="1">
-        <v>4583.3334999999997</v>
+        <v>8250</v>
       </c>
       <c r="L655" s="1"/>
       <c r="M655" s="1"/>
       <c r="N655" s="1"/>
       <c r="O655" s="1">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="P655" s="1" t="s">
         <v>20</v>
@@ -27256,26 +27248,26 @@
         <v>41</v>
       </c>
       <c r="F656" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G656" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H656" s="1"/>
       <c r="I656" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J656" s="1">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="K656" s="1">
-        <v>8250</v>
+        <v>5500</v>
       </c>
       <c r="L656" s="1"/>
       <c r="M656" s="1"/>
       <c r="N656" s="1"/>
       <c r="O656" s="1">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="P656" s="1" t="s">
         <v>20</v>
@@ -27298,26 +27290,26 @@
         <v>41</v>
       </c>
       <c r="F657" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G657" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H657" s="1"/>
       <c r="I657" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J657" s="1">
-        <v>0.5</v>
+        <v>0.33333333999999998</v>
       </c>
       <c r="K657" s="1">
-        <v>5500</v>
+        <v>3666.6667000000002</v>
       </c>
       <c r="L657" s="1"/>
       <c r="M657" s="1"/>
       <c r="N657" s="1"/>
       <c r="O657" s="1">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="P657" s="1" t="s">
         <v>20</v>
@@ -27340,26 +27332,26 @@
         <v>41</v>
       </c>
       <c r="F658" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G658" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H658" s="1"/>
       <c r="I658" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J658" s="1">
-        <v>0.33333333999999998</v>
+        <v>0.41666666000000002</v>
       </c>
       <c r="K658" s="1">
-        <v>3666.6667000000002</v>
+        <v>4583.3334999999997</v>
       </c>
       <c r="L658" s="1"/>
       <c r="M658" s="1"/>
       <c r="N658" s="1"/>
       <c r="O658" s="1">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="P658" s="1" t="s">
         <v>20</v>
@@ -27379,29 +27371,25 @@
         <v>76</v>
       </c>
       <c r="E659" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F659" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="G659" s="1" t="s">
-        <v>94</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="F659" s="1"/>
+      <c r="G659" s="1"/>
       <c r="H659" s="1"/>
       <c r="I659" s="1" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J659" s="1">
-        <v>0.41666666000000002</v>
+        <v>3.6666666999999999</v>
       </c>
       <c r="K659" s="1">
-        <v>4583.3334999999997</v>
+        <v>33000</v>
       </c>
       <c r="L659" s="1"/>
       <c r="M659" s="1"/>
       <c r="N659" s="1"/>
       <c r="O659" s="1">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="P659" s="1" t="s">
         <v>20</v>
@@ -27427,19 +27415,19 @@
       <c r="G660" s="1"/>
       <c r="H660" s="1"/>
       <c r="I660" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J660" s="1">
-        <v>3.6666666999999999</v>
+        <v>4.5</v>
       </c>
       <c r="K660" s="1">
-        <v>33000</v>
+        <v>67500</v>
       </c>
       <c r="L660" s="1"/>
       <c r="M660" s="1"/>
       <c r="N660" s="1"/>
       <c r="O660" s="1">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="P660" s="1" t="s">
         <v>20</v>
@@ -27465,19 +27453,19 @@
       <c r="G661" s="1"/>
       <c r="H661" s="1"/>
       <c r="I661" s="1" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="J661" s="1">
-        <v>4.5</v>
+        <v>7.75</v>
       </c>
       <c r="K661" s="1">
-        <v>67500</v>
+        <v>69750</v>
       </c>
       <c r="L661" s="1"/>
       <c r="M661" s="1"/>
       <c r="N661" s="1"/>
       <c r="O661" s="1">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="P661" s="1" t="s">
         <v>20</v>
@@ -27503,19 +27491,19 @@
       <c r="G662" s="1"/>
       <c r="H662" s="1"/>
       <c r="I662" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J662" s="1">
-        <v>7.75</v>
+        <v>26.875</v>
       </c>
       <c r="K662" s="1">
-        <v>69750</v>
+        <v>403125</v>
       </c>
       <c r="L662" s="1"/>
       <c r="M662" s="1"/>
       <c r="N662" s="1"/>
       <c r="O662" s="1">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="P662" s="1" t="s">
         <v>20</v>
@@ -27541,19 +27529,19 @@
       <c r="G663" s="1"/>
       <c r="H663" s="1"/>
       <c r="I663" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J663" s="1">
-        <v>26.875</v>
+        <v>74.5</v>
       </c>
       <c r="K663" s="1">
-        <v>403125</v>
+        <v>819500</v>
       </c>
       <c r="L663" s="1"/>
       <c r="M663" s="1"/>
       <c r="N663" s="1"/>
       <c r="O663" s="1">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="P663" s="1" t="s">
         <v>20</v>
@@ -27567,31 +27555,37 @@
         <v>0</v>
       </c>
       <c r="C664" s="1" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="D664" s="1" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="E664" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F664" s="1"/>
-      <c r="G664" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="F664" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G664" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="H664" s="1"/>
       <c r="I664" s="1" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="J664" s="1">
-        <v>74.5</v>
+        <v>1</v>
       </c>
       <c r="K664" s="1">
-        <v>819500</v>
-      </c>
-      <c r="L664" s="1"/>
+        <v>26500</v>
+      </c>
+      <c r="L664" s="1">
+        <v>5500</v>
+      </c>
       <c r="M664" s="1"/>
       <c r="N664" s="1"/>
       <c r="O664" s="1">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="P664" s="1" t="s">
         <v>20</v>
@@ -27614,28 +27608,26 @@
         <v>41</v>
       </c>
       <c r="F665" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G665" s="1" t="s">
         <v>58</v>
       </c>
       <c r="H665" s="1"/>
       <c r="I665" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J665" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K665" s="1">
-        <v>26500</v>
-      </c>
-      <c r="L665" s="1">
-        <v>5500</v>
-      </c>
+        <v>9000</v>
+      </c>
+      <c r="L665" s="1"/>
       <c r="M665" s="1"/>
       <c r="N665" s="1"/>
       <c r="O665" s="1">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="P665" s="1" t="s">
         <v>20</v>
@@ -27658,26 +27650,26 @@
         <v>41</v>
       </c>
       <c r="F666" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G666" s="1" t="s">
         <v>58</v>
       </c>
       <c r="H666" s="1"/>
       <c r="I666" s="1" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="J666" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K666" s="1">
-        <v>9000</v>
+        <v>10500</v>
       </c>
       <c r="L666" s="1"/>
       <c r="M666" s="1"/>
       <c r="N666" s="1"/>
       <c r="O666" s="1">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="P666" s="1" t="s">
         <v>20</v>
@@ -27700,26 +27692,26 @@
         <v>41</v>
       </c>
       <c r="F667" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G667" s="1" t="s">
         <v>58</v>
       </c>
       <c r="H667" s="1"/>
       <c r="I667" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J667" s="1">
-        <v>1</v>
+        <v>0.11111111</v>
       </c>
       <c r="K667" s="1">
-        <v>10500</v>
+        <v>3111.1109999999999</v>
       </c>
       <c r="L667" s="1"/>
       <c r="M667" s="1"/>
       <c r="N667" s="1"/>
       <c r="O667" s="1">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="P667" s="1" t="s">
         <v>20</v>
@@ -27742,26 +27734,26 @@
         <v>41</v>
       </c>
       <c r="F668" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G668" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H668" s="1"/>
       <c r="I668" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J668" s="1">
-        <v>0.11111111</v>
+        <v>0.5</v>
       </c>
       <c r="K668" s="1">
-        <v>3111.1109999999999</v>
+        <v>16750</v>
       </c>
       <c r="L668" s="1"/>
       <c r="M668" s="1"/>
       <c r="N668" s="1"/>
       <c r="O668" s="1">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="P668" s="1" t="s">
         <v>20</v>
@@ -27784,26 +27776,26 @@
         <v>41</v>
       </c>
       <c r="F669" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G669" s="1" t="s">
         <v>59</v>
       </c>
       <c r="H669" s="1"/>
       <c r="I669" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J669" s="1">
-        <v>0.5</v>
+        <v>0.11111111</v>
       </c>
       <c r="K669" s="1">
-        <v>16750</v>
+        <v>3111.1109999999999</v>
       </c>
       <c r="L669" s="1"/>
       <c r="M669" s="1"/>
       <c r="N669" s="1"/>
       <c r="O669" s="1">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="P669" s="1" t="s">
         <v>20</v>
@@ -27826,26 +27818,26 @@
         <v>41</v>
       </c>
       <c r="F670" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G670" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H670" s="1"/>
       <c r="I670" s="1" t="s">
         <v>26</v>
       </c>
       <c r="J670" s="1">
-        <v>0.11111111</v>
+        <v>0.66666669999999995</v>
       </c>
       <c r="K670" s="1">
-        <v>3111.1109999999999</v>
+        <v>18666.666000000001</v>
       </c>
       <c r="L670" s="1"/>
       <c r="M670" s="1"/>
       <c r="N670" s="1"/>
       <c r="O670" s="1">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="P670" s="1" t="s">
         <v>20</v>
@@ -27868,26 +27860,26 @@
         <v>41</v>
       </c>
       <c r="F671" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G671" s="1" t="s">
         <v>60</v>
       </c>
       <c r="H671" s="1"/>
       <c r="I671" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J671" s="1">
-        <v>0.66666669999999995</v>
+        <v>0.55555560000000004</v>
       </c>
       <c r="K671" s="1">
-        <v>18666.666000000001</v>
+        <v>14444.444</v>
       </c>
       <c r="L671" s="1"/>
       <c r="M671" s="1"/>
       <c r="N671" s="1"/>
       <c r="O671" s="1">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="P671" s="1" t="s">
         <v>20</v>
@@ -27910,26 +27902,26 @@
         <v>41</v>
       </c>
       <c r="F672" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G672" s="1" t="s">
         <v>60</v>
       </c>
       <c r="H672" s="1"/>
       <c r="I672" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J672" s="1">
-        <v>0.55555560000000004</v>
+        <v>4.1666667999999997E-2</v>
       </c>
       <c r="K672" s="1">
-        <v>14444.444</v>
+        <v>1395.8334</v>
       </c>
       <c r="L672" s="1"/>
       <c r="M672" s="1"/>
       <c r="N672" s="1"/>
       <c r="O672" s="1">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="P672" s="1" t="s">
         <v>20</v>
@@ -27952,26 +27944,26 @@
         <v>41</v>
       </c>
       <c r="F673" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G673" s="1" t="s">
         <v>60</v>
       </c>
       <c r="H673" s="1"/>
       <c r="I673" s="1" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="J673" s="1">
-        <v>4.1666667999999997E-2</v>
+        <v>1</v>
       </c>
       <c r="K673" s="1">
-        <v>1395.8334</v>
+        <v>26500</v>
       </c>
       <c r="L673" s="1"/>
       <c r="M673" s="1"/>
       <c r="N673" s="1"/>
       <c r="O673" s="1">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="P673" s="1" t="s">
         <v>20</v>
@@ -27994,26 +27986,26 @@
         <v>41</v>
       </c>
       <c r="F674" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G674" s="1" t="s">
         <v>60</v>
       </c>
       <c r="H674" s="1"/>
       <c r="I674" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J674" s="1">
         <v>1</v>
       </c>
       <c r="K674" s="1">
-        <v>26500</v>
+        <v>4500</v>
       </c>
       <c r="L674" s="1"/>
       <c r="M674" s="1"/>
       <c r="N674" s="1"/>
       <c r="O674" s="1">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="P674" s="1" t="s">
         <v>20</v>
@@ -28036,26 +28028,26 @@
         <v>41</v>
       </c>
       <c r="F675" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G675" s="1" t="s">
         <v>60</v>
       </c>
       <c r="H675" s="1"/>
       <c r="I675" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="J675" s="1">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="K675" s="1">
-        <v>4500</v>
+        <v>29250</v>
       </c>
       <c r="L675" s="1"/>
       <c r="M675" s="1"/>
       <c r="N675" s="1"/>
       <c r="O675" s="1">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="P675" s="1" t="s">
         <v>20</v>
@@ -28078,26 +28070,26 @@
         <v>41</v>
       </c>
       <c r="F676" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G676" s="1" t="s">
         <v>60</v>
       </c>
       <c r="H676" s="1"/>
       <c r="I676" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J676" s="1">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="K676" s="1">
-        <v>29250</v>
+        <v>7750</v>
       </c>
       <c r="L676" s="1"/>
       <c r="M676" s="1"/>
       <c r="N676" s="1"/>
       <c r="O676" s="1">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="P676" s="1" t="s">
         <v>20</v>
@@ -28120,26 +28112,26 @@
         <v>41</v>
       </c>
       <c r="F677" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G677" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H677" s="1"/>
       <c r="I677" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J677" s="1">
-        <v>0.5</v>
+        <v>1.1111112000000001</v>
       </c>
       <c r="K677" s="1">
-        <v>7750</v>
+        <v>31111.111000000001</v>
       </c>
       <c r="L677" s="1"/>
       <c r="M677" s="1"/>
       <c r="N677" s="1"/>
       <c r="O677" s="1">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="P677" s="1" t="s">
         <v>20</v>
@@ -28162,26 +28154,26 @@
         <v>41</v>
       </c>
       <c r="F678" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G678" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H678" s="1"/>
       <c r="I678" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J678" s="1">
-        <v>1.1111112000000001</v>
+        <v>1</v>
       </c>
       <c r="K678" s="1">
-        <v>31111.111000000001</v>
+        <v>10500</v>
       </c>
       <c r="L678" s="1"/>
       <c r="M678" s="1"/>
       <c r="N678" s="1"/>
       <c r="O678" s="1">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="P678" s="1" t="s">
         <v>20</v>
@@ -28204,26 +28196,26 @@
         <v>41</v>
       </c>
       <c r="F679" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G679" s="1" t="s">
         <v>61</v>
       </c>
       <c r="H679" s="1"/>
       <c r="I679" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J679" s="1">
-        <v>1</v>
+        <v>0.11111111</v>
       </c>
       <c r="K679" s="1">
-        <v>10500</v>
+        <v>2888.8890000000001</v>
       </c>
       <c r="L679" s="1"/>
       <c r="M679" s="1"/>
       <c r="N679" s="1"/>
       <c r="O679" s="1">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="P679" s="1" t="s">
         <v>20</v>
@@ -28246,26 +28238,26 @@
         <v>41</v>
       </c>
       <c r="F680" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G680" s="1" t="s">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="H680" s="1"/>
       <c r="I680" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="J680" s="1">
-        <v>0.11111111</v>
+        <v>1</v>
       </c>
       <c r="K680" s="1">
-        <v>2888.8890000000001</v>
+        <v>4500</v>
       </c>
       <c r="L680" s="1"/>
       <c r="M680" s="1"/>
       <c r="N680" s="1"/>
       <c r="O680" s="1">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="P680" s="1" t="s">
         <v>20</v>
@@ -28288,26 +28280,26 @@
         <v>41</v>
       </c>
       <c r="F681" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G681" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H681" s="1"/>
       <c r="I681" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J681" s="1">
-        <v>1</v>
+        <v>0.70833330000000005</v>
       </c>
       <c r="K681" s="1">
-        <v>4500</v>
+        <v>18770.833999999999</v>
       </c>
       <c r="L681" s="1"/>
       <c r="M681" s="1"/>
       <c r="N681" s="1"/>
       <c r="O681" s="1">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="P681" s="1" t="s">
         <v>20</v>
@@ -28330,26 +28322,26 @@
         <v>41</v>
       </c>
       <c r="F682" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G682" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H682" s="1"/>
       <c r="I682" s="1" t="s">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="J682" s="1">
-        <v>0.70833330000000005</v>
+        <v>0.5</v>
       </c>
       <c r="K682" s="1">
-        <v>18770.833999999999</v>
+        <v>16750</v>
       </c>
       <c r="L682" s="1"/>
       <c r="M682" s="1"/>
       <c r="N682" s="1"/>
       <c r="O682" s="1">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="P682" s="1" t="s">
         <v>20</v>
@@ -28372,26 +28364,26 @@
         <v>41</v>
       </c>
       <c r="F683" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G683" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H683" s="1"/>
       <c r="I683" s="1" t="s">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="J683" s="1">
-        <v>0.5</v>
+        <v>0.33333333999999998</v>
       </c>
       <c r="K683" s="1">
-        <v>16750</v>
+        <v>8666.6669999999995</v>
       </c>
       <c r="L683" s="1"/>
       <c r="M683" s="1"/>
       <c r="N683" s="1"/>
       <c r="O683" s="1">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="P683" s="1" t="s">
         <v>20</v>
@@ -28414,26 +28406,26 @@
         <v>41</v>
       </c>
       <c r="F684" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G684" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H684" s="1"/>
       <c r="I684" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J684" s="1">
-        <v>0.33333333999999998</v>
+        <v>0.1</v>
       </c>
       <c r="K684" s="1">
-        <v>8666.6669999999995</v>
+        <v>1200</v>
       </c>
       <c r="L684" s="1"/>
       <c r="M684" s="1"/>
       <c r="N684" s="1"/>
       <c r="O684" s="1">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="P684" s="1" t="s">
         <v>20</v>
@@ -28456,26 +28448,26 @@
         <v>41</v>
       </c>
       <c r="F685" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G685" s="1" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="H685" s="1"/>
       <c r="I685" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J685" s="1">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="K685" s="1">
-        <v>1200</v>
+        <v>15750</v>
       </c>
       <c r="L685" s="1"/>
       <c r="M685" s="1"/>
       <c r="N685" s="1"/>
       <c r="O685" s="1">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="P685" s="1" t="s">
         <v>20</v>
@@ -28498,26 +28490,26 @@
         <v>41</v>
       </c>
       <c r="F686" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G686" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H686" s="1"/>
       <c r="I686" s="1" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="J686" s="1">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K686" s="1">
-        <v>15750</v>
+        <v>19500</v>
       </c>
       <c r="L686" s="1"/>
       <c r="M686" s="1"/>
       <c r="N686" s="1"/>
       <c r="O686" s="1">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="P686" s="1" t="s">
         <v>20</v>
@@ -28540,26 +28532,26 @@
         <v>41</v>
       </c>
       <c r="F687" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G687" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H687" s="1"/>
       <c r="I687" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="J687" s="1">
         <v>1</v>
       </c>
       <c r="K687" s="1">
-        <v>19500</v>
+        <v>17500</v>
       </c>
       <c r="L687" s="1"/>
       <c r="M687" s="1"/>
       <c r="N687" s="1"/>
       <c r="O687" s="1">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="P687" s="1" t="s">
         <v>20</v>
@@ -28582,26 +28574,26 @@
         <v>41</v>
       </c>
       <c r="F688" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G688" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H688" s="1"/>
       <c r="I688" s="1" t="s">
-        <v>24</v>
+        <v>97</v>
       </c>
       <c r="J688" s="1">
-        <v>1</v>
+        <v>8.3333335999999994E-2</v>
       </c>
       <c r="K688" s="1">
-        <v>17500</v>
+        <v>2791.6667000000002</v>
       </c>
       <c r="L688" s="1"/>
       <c r="M688" s="1"/>
       <c r="N688" s="1"/>
       <c r="O688" s="1">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="P688" s="1" t="s">
         <v>20</v>
@@ -28624,26 +28616,26 @@
         <v>41</v>
       </c>
       <c r="F689" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G689" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H689" s="1"/>
       <c r="I689" s="1" t="s">
-        <v>97</v>
+        <v>19</v>
       </c>
       <c r="J689" s="1">
-        <v>8.3333335999999994E-2</v>
+        <v>1</v>
       </c>
       <c r="K689" s="1">
-        <v>2791.6667000000002</v>
+        <v>10500</v>
       </c>
       <c r="L689" s="1"/>
       <c r="M689" s="1"/>
       <c r="N689" s="1"/>
       <c r="O689" s="1">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="P689" s="1" t="s">
         <v>20</v>
@@ -28666,26 +28658,26 @@
         <v>41</v>
       </c>
       <c r="F690" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G690" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H690" s="1"/>
       <c r="I690" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J690" s="1">
-        <v>1</v>
+        <v>0.11111111</v>
       </c>
       <c r="K690" s="1">
-        <v>10500</v>
+        <v>2888.8890000000001</v>
       </c>
       <c r="L690" s="1"/>
       <c r="M690" s="1"/>
       <c r="N690" s="1"/>
       <c r="O690" s="1">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="P690" s="1" t="s">
         <v>20</v>
@@ -28708,26 +28700,26 @@
         <v>41</v>
       </c>
       <c r="F691" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G691" s="1" t="s">
         <v>63</v>
       </c>
       <c r="H691" s="1"/>
       <c r="I691" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J691" s="1">
         <v>0.11111111</v>
       </c>
       <c r="K691" s="1">
-        <v>2888.8890000000001</v>
+        <v>3111.1109999999999</v>
       </c>
       <c r="L691" s="1"/>
       <c r="M691" s="1"/>
       <c r="N691" s="1"/>
       <c r="O691" s="1">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="P691" s="1" t="s">
         <v>20</v>
@@ -28750,26 +28742,26 @@
         <v>41</v>
       </c>
       <c r="F692" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G692" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H692" s="1"/>
       <c r="I692" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J692" s="1">
-        <v>0.11111111</v>
+        <v>1</v>
       </c>
       <c r="K692" s="1">
-        <v>3111.1109999999999</v>
+        <v>17500</v>
       </c>
       <c r="L692" s="1"/>
       <c r="M692" s="1"/>
       <c r="N692" s="1"/>
       <c r="O692" s="1">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="P692" s="1" t="s">
         <v>20</v>
@@ -28792,26 +28784,26 @@
         <v>41</v>
       </c>
       <c r="F693" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G693" s="1" t="s">
         <v>64</v>
       </c>
       <c r="H693" s="1"/>
       <c r="I693" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J693" s="1">
         <v>1</v>
       </c>
       <c r="K693" s="1">
-        <v>17500</v>
+        <v>10500</v>
       </c>
       <c r="L693" s="1"/>
       <c r="M693" s="1"/>
       <c r="N693" s="1"/>
       <c r="O693" s="1">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="P693" s="1" t="s">
         <v>20</v>
@@ -28834,26 +28826,26 @@
         <v>41</v>
       </c>
       <c r="F694" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G694" s="1" t="s">
         <v>64</v>
       </c>
       <c r="H694" s="1"/>
       <c r="I694" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="J694" s="1">
-        <v>1</v>
+        <v>0.54166669999999995</v>
       </c>
       <c r="K694" s="1">
-        <v>10500</v>
+        <v>14354.166999999999</v>
       </c>
       <c r="L694" s="1"/>
       <c r="M694" s="1"/>
       <c r="N694" s="1"/>
       <c r="O694" s="1">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="P694" s="1" t="s">
         <v>20</v>
@@ -28876,26 +28868,26 @@
         <v>41</v>
       </c>
       <c r="F695" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G695" s="1" t="s">
         <v>64</v>
       </c>
       <c r="H695" s="1"/>
       <c r="I695" s="1" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="J695" s="1">
-        <v>0.54166669999999995</v>
+        <v>0.11111111</v>
       </c>
       <c r="K695" s="1">
-        <v>14354.166999999999</v>
+        <v>2888.8890000000001</v>
       </c>
       <c r="L695" s="1"/>
       <c r="M695" s="1"/>
       <c r="N695" s="1"/>
       <c r="O695" s="1">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="P695" s="1" t="s">
         <v>20</v>
@@ -28918,26 +28910,26 @@
         <v>41</v>
       </c>
       <c r="F696" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G696" s="1" t="s">
         <v>64</v>
       </c>
       <c r="H696" s="1"/>
       <c r="I696" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J696" s="1">
         <v>0.11111111</v>
       </c>
       <c r="K696" s="1">
-        <v>2888.8890000000001</v>
+        <v>3111.1109999999999</v>
       </c>
       <c r="L696" s="1"/>
       <c r="M696" s="1"/>
       <c r="N696" s="1"/>
       <c r="O696" s="1">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="P696" s="1" t="s">
         <v>20</v>
@@ -28960,26 +28952,26 @@
         <v>41</v>
       </c>
       <c r="F697" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G697" s="1" t="s">
         <v>64</v>
       </c>
       <c r="H697" s="1"/>
       <c r="I697" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J697" s="1">
-        <v>0.11111111</v>
+        <v>0.1</v>
       </c>
       <c r="K697" s="1">
-        <v>3111.1109999999999</v>
+        <v>1200</v>
       </c>
       <c r="L697" s="1"/>
       <c r="M697" s="1"/>
       <c r="N697" s="1"/>
       <c r="O697" s="1">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="P697" s="1" t="s">
         <v>20</v>
@@ -29002,26 +28994,26 @@
         <v>41</v>
       </c>
       <c r="F698" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G698" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H698" s="1"/>
       <c r="I698" s="1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J698" s="1">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="K698" s="1">
-        <v>1200</v>
+        <v>9750</v>
       </c>
       <c r="L698" s="1"/>
       <c r="M698" s="1"/>
       <c r="N698" s="1"/>
       <c r="O698" s="1">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="P698" s="1" t="s">
         <v>20</v>
@@ -29044,26 +29036,26 @@
         <v>41</v>
       </c>
       <c r="F699" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G699" s="1" t="s">
         <v>66</v>
       </c>
       <c r="H699" s="1"/>
       <c r="I699" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="J699" s="1">
-        <v>0.5</v>
+        <v>0.11111111</v>
       </c>
       <c r="K699" s="1">
-        <v>9750</v>
+        <v>2888.8890000000001</v>
       </c>
       <c r="L699" s="1"/>
       <c r="M699" s="1"/>
       <c r="N699" s="1"/>
       <c r="O699" s="1">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="P699" s="1" t="s">
         <v>20</v>
@@ -29086,26 +29078,26 @@
         <v>41</v>
       </c>
       <c r="F700" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G700" s="1" t="s">
         <v>66</v>
       </c>
       <c r="H700" s="1"/>
       <c r="I700" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J700" s="1">
         <v>0.11111111</v>
       </c>
       <c r="K700" s="1">
-        <v>2888.8890000000001</v>
+        <v>3111.1109999999999</v>
       </c>
       <c r="L700" s="1"/>
       <c r="M700" s="1"/>
       <c r="N700" s="1"/>
       <c r="O700" s="1">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="P700" s="1" t="s">
         <v>20</v>
@@ -29128,26 +29120,26 @@
         <v>41</v>
       </c>
       <c r="F701" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G701" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H701" s="1"/>
       <c r="I701" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J701" s="1">
-        <v>0.11111111</v>
+        <v>0.66666669999999995</v>
       </c>
       <c r="K701" s="1">
-        <v>3111.1109999999999</v>
+        <v>17333.333999999999</v>
       </c>
       <c r="L701" s="1"/>
       <c r="M701" s="1"/>
       <c r="N701" s="1"/>
       <c r="O701" s="1">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="P701" s="1" t="s">
         <v>20</v>
@@ -29170,26 +29162,26 @@
         <v>41</v>
       </c>
       <c r="F702" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G702" s="1" t="s">
         <v>65</v>
       </c>
       <c r="H702" s="1"/>
       <c r="I702" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J702" s="1">
-        <v>0.66666669999999995</v>
+        <v>0.11111111</v>
       </c>
       <c r="K702" s="1">
-        <v>17333.333999999999</v>
+        <v>3111.1109999999999</v>
       </c>
       <c r="L702" s="1"/>
       <c r="M702" s="1"/>
       <c r="N702" s="1"/>
       <c r="O702" s="1">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="P702" s="1" t="s">
         <v>20</v>
@@ -29212,26 +29204,26 @@
         <v>41</v>
       </c>
       <c r="F703" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G703" s="1" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="H703" s="1"/>
       <c r="I703" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J703" s="1">
-        <v>0.11111111</v>
+        <v>1</v>
       </c>
       <c r="K703" s="1">
-        <v>3111.1109999999999</v>
+        <v>10500</v>
       </c>
       <c r="L703" s="1"/>
       <c r="M703" s="1"/>
       <c r="N703" s="1"/>
       <c r="O703" s="1">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="P703" s="1" t="s">
         <v>20</v>
@@ -29254,26 +29246,26 @@
         <v>41</v>
       </c>
       <c r="F704" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G704" s="1" t="s">
         <v>104</v>
       </c>
       <c r="H704" s="1"/>
       <c r="I704" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J704" s="1">
-        <v>1</v>
+        <v>0.55555560000000004</v>
       </c>
       <c r="K704" s="1">
-        <v>10500</v>
+        <v>15555.556</v>
       </c>
       <c r="L704" s="1"/>
       <c r="M704" s="1"/>
       <c r="N704" s="1"/>
       <c r="O704" s="1">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="P704" s="1" t="s">
         <v>20</v>
@@ -29296,26 +29288,26 @@
         <v>41</v>
       </c>
       <c r="F705" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G705" s="1" t="s">
         <v>104</v>
       </c>
       <c r="H705" s="1"/>
       <c r="I705" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J705" s="1">
-        <v>0.55555560000000004</v>
+        <v>0.11111111</v>
       </c>
       <c r="K705" s="1">
-        <v>15555.556</v>
+        <v>2888.8890000000001</v>
       </c>
       <c r="L705" s="1"/>
       <c r="M705" s="1"/>
       <c r="N705" s="1"/>
       <c r="O705" s="1">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="P705" s="1" t="s">
         <v>20</v>
@@ -29338,26 +29330,26 @@
         <v>41</v>
       </c>
       <c r="F706" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G706" s="1" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="H706" s="1"/>
       <c r="I706" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J706" s="1">
-        <v>0.11111111</v>
+        <v>1</v>
       </c>
       <c r="K706" s="1">
-        <v>2888.8890000000001</v>
+        <v>17500</v>
       </c>
       <c r="L706" s="1"/>
       <c r="M706" s="1"/>
       <c r="N706" s="1"/>
       <c r="O706" s="1">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="P706" s="1" t="s">
         <v>20</v>
@@ -29380,26 +29372,26 @@
         <v>41</v>
       </c>
       <c r="F707" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G707" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H707" s="1"/>
       <c r="I707" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J707" s="1">
-        <v>1</v>
+        <v>0.33333333999999998</v>
       </c>
       <c r="K707" s="1">
-        <v>17500</v>
+        <v>9333.3330000000005</v>
       </c>
       <c r="L707" s="1"/>
       <c r="M707" s="1"/>
       <c r="N707" s="1"/>
       <c r="O707" s="1">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="P707" s="1" t="s">
         <v>20</v>
@@ -29422,26 +29414,26 @@
         <v>41</v>
       </c>
       <c r="F708" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G708" s="1" t="s">
         <v>68</v>
       </c>
       <c r="H708" s="1"/>
       <c r="I708" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J708" s="1">
-        <v>0.33333333999999998</v>
+        <v>0.22222222</v>
       </c>
       <c r="K708" s="1">
-        <v>9333.3330000000005</v>
+        <v>5777.7780000000002</v>
       </c>
       <c r="L708" s="1"/>
       <c r="M708" s="1"/>
       <c r="N708" s="1"/>
       <c r="O708" s="1">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="P708" s="1" t="s">
         <v>20</v>
@@ -29464,26 +29456,26 @@
         <v>41</v>
       </c>
       <c r="F709" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G709" s="1" t="s">
         <v>68</v>
       </c>
       <c r="H709" s="1"/>
       <c r="I709" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="J709" s="1">
-        <v>0.22222222</v>
+        <v>1</v>
       </c>
       <c r="K709" s="1">
-        <v>5777.7780000000002</v>
+        <v>4500</v>
       </c>
       <c r="L709" s="1"/>
       <c r="M709" s="1"/>
       <c r="N709" s="1"/>
       <c r="O709" s="1">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="P709" s="1" t="s">
         <v>20</v>
@@ -29506,10 +29498,10 @@
         <v>41</v>
       </c>
       <c r="F710" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G710" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H710" s="1"/>
       <c r="I710" s="1" t="s">
@@ -29525,7 +29517,7 @@
       <c r="M710" s="1"/>
       <c r="N710" s="1"/>
       <c r="O710" s="1">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="P710" s="1" t="s">
         <v>20</v>
@@ -29548,26 +29540,26 @@
         <v>41</v>
       </c>
       <c r="F711" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G711" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H711" s="1"/>
       <c r="I711" s="1" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="J711" s="1">
-        <v>1</v>
+        <v>0.22222222</v>
       </c>
       <c r="K711" s="1">
-        <v>4500</v>
+        <v>6222.2219999999998</v>
       </c>
       <c r="L711" s="1"/>
       <c r="M711" s="1"/>
       <c r="N711" s="1"/>
       <c r="O711" s="1">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="P711" s="1" t="s">
         <v>20</v>
@@ -29590,26 +29582,26 @@
         <v>41</v>
       </c>
       <c r="F712" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G712" s="1" t="s">
         <v>70</v>
       </c>
       <c r="H712" s="1"/>
       <c r="I712" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J712" s="1">
-        <v>0.22222222</v>
+        <v>0.33333333999999998</v>
       </c>
       <c r="K712" s="1">
-        <v>6222.2219999999998</v>
+        <v>8666.6669999999995</v>
       </c>
       <c r="L712" s="1"/>
       <c r="M712" s="1"/>
       <c r="N712" s="1"/>
       <c r="O712" s="1">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="P712" s="1" t="s">
         <v>20</v>
@@ -29632,26 +29624,26 @@
         <v>41</v>
       </c>
       <c r="F713" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G713" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H713" s="1"/>
       <c r="I713" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J713" s="1">
-        <v>0.33333333999999998</v>
+        <v>1</v>
       </c>
       <c r="K713" s="1">
-        <v>8666.6669999999995</v>
+        <v>17500</v>
       </c>
       <c r="L713" s="1"/>
       <c r="M713" s="1"/>
       <c r="N713" s="1"/>
       <c r="O713" s="1">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="P713" s="1" t="s">
         <v>20</v>
@@ -29674,26 +29666,26 @@
         <v>41</v>
       </c>
       <c r="F714" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G714" s="1" t="s">
         <v>71</v>
       </c>
       <c r="H714" s="1"/>
       <c r="I714" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J714" s="1">
         <v>1</v>
       </c>
       <c r="K714" s="1">
-        <v>17500</v>
+        <v>10500</v>
       </c>
       <c r="L714" s="1"/>
       <c r="M714" s="1"/>
       <c r="N714" s="1"/>
       <c r="O714" s="1">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="P714" s="1" t="s">
         <v>20</v>
@@ -29716,26 +29708,26 @@
         <v>41</v>
       </c>
       <c r="F715" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G715" s="1" t="s">
         <v>71</v>
       </c>
       <c r="H715" s="1"/>
       <c r="I715" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J715" s="1">
-        <v>1</v>
+        <v>0.22222222</v>
       </c>
       <c r="K715" s="1">
-        <v>10500</v>
+        <v>5777.7780000000002</v>
       </c>
       <c r="L715" s="1"/>
       <c r="M715" s="1"/>
       <c r="N715" s="1"/>
       <c r="O715" s="1">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="P715" s="1" t="s">
         <v>20</v>
@@ -29758,26 +29750,26 @@
         <v>41</v>
       </c>
       <c r="F716" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G716" s="1" t="s">
         <v>71</v>
       </c>
       <c r="H716" s="1"/>
       <c r="I716" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J716" s="1">
-        <v>0.22222222</v>
+        <v>0.11111111</v>
       </c>
       <c r="K716" s="1">
-        <v>5777.7780000000002</v>
+        <v>3111.1109999999999</v>
       </c>
       <c r="L716" s="1"/>
       <c r="M716" s="1"/>
       <c r="N716" s="1"/>
       <c r="O716" s="1">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="P716" s="1" t="s">
         <v>20</v>
@@ -29800,26 +29792,26 @@
         <v>41</v>
       </c>
       <c r="F717" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G717" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H717" s="1"/>
       <c r="I717" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="J717" s="1">
-        <v>0.11111111</v>
+        <v>0.5</v>
       </c>
       <c r="K717" s="1">
-        <v>3111.1109999999999</v>
+        <v>9750</v>
       </c>
       <c r="L717" s="1"/>
       <c r="M717" s="1"/>
       <c r="N717" s="1"/>
       <c r="O717" s="1">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="P717" s="1" t="s">
         <v>20</v>
@@ -29842,26 +29834,26 @@
         <v>41</v>
       </c>
       <c r="F718" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G718" s="1" t="s">
         <v>72</v>
       </c>
       <c r="H718" s="1"/>
       <c r="I718" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="J718" s="1">
-        <v>0.5</v>
+        <v>0.11111111</v>
       </c>
       <c r="K718" s="1">
-        <v>9750</v>
+        <v>2888.8890000000001</v>
       </c>
       <c r="L718" s="1"/>
       <c r="M718" s="1"/>
       <c r="N718" s="1"/>
       <c r="O718" s="1">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="P718" s="1" t="s">
         <v>20</v>
@@ -29881,29 +29873,25 @@
         <v>57</v>
       </c>
       <c r="E719" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F719" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="G719" s="1" t="s">
-        <v>72</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="F719" s="1"/>
+      <c r="G719" s="1"/>
       <c r="H719" s="1"/>
       <c r="I719" s="1" t="s">
         <v>27</v>
       </c>
       <c r="J719" s="1">
-        <v>0.11111111</v>
+        <v>7</v>
       </c>
       <c r="K719" s="1">
-        <v>2888.8890000000001</v>
+        <v>182000</v>
       </c>
       <c r="L719" s="1"/>
       <c r="M719" s="1"/>
       <c r="N719" s="1"/>
       <c r="O719" s="1">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="P719" s="1" t="s">
         <v>20</v>
@@ -29929,19 +29917,19 @@
       <c r="G720" s="1"/>
       <c r="H720" s="1"/>
       <c r="I720" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="J720" s="1">
-        <v>7</v>
+        <v>9.0416670000000003</v>
       </c>
       <c r="K720" s="1">
-        <v>182000</v>
+        <v>171791.67</v>
       </c>
       <c r="L720" s="1"/>
       <c r="M720" s="1"/>
       <c r="N720" s="1"/>
       <c r="O720" s="1">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="P720" s="1" t="s">
         <v>20</v>
@@ -29967,19 +29955,19 @@
       <c r="G721" s="1"/>
       <c r="H721" s="1"/>
       <c r="I721" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J721" s="1">
-        <v>9.0416670000000003</v>
+        <v>18</v>
       </c>
       <c r="K721" s="1">
-        <v>171791.67</v>
+        <v>351000</v>
       </c>
       <c r="L721" s="1"/>
       <c r="M721" s="1"/>
       <c r="N721" s="1"/>
       <c r="O721" s="1">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="P721" s="1" t="s">
         <v>20</v>
@@ -30005,19 +29993,19 @@
       <c r="G722" s="1"/>
       <c r="H722" s="1"/>
       <c r="I722" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="J722" s="1">
-        <v>18</v>
+        <v>15.333333</v>
       </c>
       <c r="K722" s="1">
-        <v>351000</v>
+        <v>429333.34</v>
       </c>
       <c r="L722" s="1"/>
       <c r="M722" s="1"/>
       <c r="N722" s="1"/>
       <c r="O722" s="1">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="P722" s="1" t="s">
         <v>20</v>
@@ -30043,19 +30031,19 @@
       <c r="G723" s="1"/>
       <c r="H723" s="1"/>
       <c r="I723" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J723" s="1">
-        <v>15.333333</v>
+        <v>4.5</v>
       </c>
       <c r="K723" s="1">
-        <v>429333.34</v>
+        <v>78750</v>
       </c>
       <c r="L723" s="1"/>
       <c r="M723" s="1"/>
       <c r="N723" s="1"/>
       <c r="O723" s="1">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="P723" s="1" t="s">
         <v>20</v>
@@ -30081,19 +30069,19 @@
       <c r="G724" s="1"/>
       <c r="H724" s="1"/>
       <c r="I724" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J724" s="1">
-        <v>4.5</v>
+        <v>14.541667</v>
       </c>
       <c r="K724" s="1">
-        <v>78750</v>
+        <v>487145.84</v>
       </c>
       <c r="L724" s="1"/>
       <c r="M724" s="1"/>
       <c r="N724" s="1"/>
       <c r="O724" s="1">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="P724" s="1" t="s">
         <v>20</v>
@@ -30119,19 +30107,19 @@
       <c r="G725" s="1"/>
       <c r="H725" s="1"/>
       <c r="I725" s="1" t="s">
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="J725" s="1">
-        <v>14.541667</v>
+        <v>6.5833335000000002</v>
       </c>
       <c r="K725" s="1">
-        <v>487145.84</v>
+        <v>220541.67</v>
       </c>
       <c r="L725" s="1"/>
       <c r="M725" s="1"/>
       <c r="N725" s="1"/>
       <c r="O725" s="1">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="P725" s="1" t="s">
         <v>20</v>
@@ -30157,19 +30145,19 @@
       <c r="G726" s="1"/>
       <c r="H726" s="1"/>
       <c r="I726" s="1" t="s">
-        <v>97</v>
+        <v>19</v>
       </c>
       <c r="J726" s="1">
-        <v>6.5833335000000002</v>
+        <v>15</v>
       </c>
       <c r="K726" s="1">
-        <v>220541.67</v>
+        <v>157500</v>
       </c>
       <c r="L726" s="1"/>
       <c r="M726" s="1"/>
       <c r="N726" s="1"/>
       <c r="O726" s="1">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="P726" s="1" t="s">
         <v>20</v>
@@ -30195,19 +30183,19 @@
       <c r="G727" s="1"/>
       <c r="H727" s="1"/>
       <c r="I727" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="J727" s="1">
-        <v>15</v>
+        <v>8.3333329999999997</v>
       </c>
       <c r="K727" s="1">
-        <v>157500</v>
+        <v>220833.33</v>
       </c>
       <c r="L727" s="1"/>
       <c r="M727" s="1"/>
       <c r="N727" s="1"/>
       <c r="O727" s="1">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="P727" s="1" t="s">
         <v>20</v>
@@ -30233,19 +30221,19 @@
       <c r="G728" s="1"/>
       <c r="H728" s="1"/>
       <c r="I728" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="J728" s="1">
-        <v>8.3333329999999997</v>
+        <v>57.6</v>
       </c>
       <c r="K728" s="1">
-        <v>220833.33</v>
+        <v>691200</v>
       </c>
       <c r="L728" s="1"/>
       <c r="M728" s="1"/>
       <c r="N728" s="1"/>
       <c r="O728" s="1">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="P728" s="1" t="s">
         <v>20</v>
@@ -30271,19 +30259,19 @@
       <c r="G729" s="1"/>
       <c r="H729" s="1"/>
       <c r="I729" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J729" s="1">
-        <v>57.6</v>
+        <v>14.4</v>
       </c>
       <c r="K729" s="1">
-        <v>691200</v>
+        <v>86400</v>
       </c>
       <c r="L729" s="1"/>
       <c r="M729" s="1"/>
       <c r="N729" s="1"/>
       <c r="O729" s="1">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="P729" s="1" t="s">
         <v>20</v>
@@ -30309,19 +30297,19 @@
       <c r="G730" s="1"/>
       <c r="H730" s="1"/>
       <c r="I730" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J730" s="1">
-        <v>14.4</v>
+        <v>4.5</v>
       </c>
       <c r="K730" s="1">
-        <v>86400</v>
+        <v>56250</v>
       </c>
       <c r="L730" s="1"/>
       <c r="M730" s="1"/>
       <c r="N730" s="1"/>
       <c r="O730" s="1">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="P730" s="1" t="s">
         <v>20</v>
@@ -30347,19 +30335,19 @@
       <c r="G731" s="1"/>
       <c r="H731" s="1"/>
       <c r="I731" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J731" s="1">
-        <v>4.5</v>
+        <v>9.5</v>
       </c>
       <c r="K731" s="1">
-        <v>56250</v>
+        <v>147250</v>
       </c>
       <c r="L731" s="1"/>
       <c r="M731" s="1"/>
       <c r="N731" s="1"/>
       <c r="O731" s="1">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="P731" s="1" t="s">
         <v>20</v>
@@ -30385,19 +30373,19 @@
       <c r="G732" s="1"/>
       <c r="H732" s="1"/>
       <c r="I732" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J732" s="1">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="K732" s="1">
-        <v>147250</v>
+        <v>131750</v>
       </c>
       <c r="L732" s="1"/>
       <c r="M732" s="1"/>
       <c r="N732" s="1"/>
       <c r="O732" s="1">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="P732" s="1" t="s">
         <v>20</v>
@@ -30423,19 +30411,19 @@
       <c r="G733" s="1"/>
       <c r="H733" s="1"/>
       <c r="I733" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="J733" s="1">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="K733" s="1">
-        <v>131750</v>
+        <v>36000</v>
       </c>
       <c r="L733" s="1"/>
       <c r="M733" s="1"/>
       <c r="N733" s="1"/>
       <c r="O733" s="1">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="P733" s="1" t="s">
         <v>20</v>
@@ -30461,19 +30449,19 @@
       <c r="G734" s="1"/>
       <c r="H734" s="1"/>
       <c r="I734" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J734" s="1">
-        <v>8</v>
+        <v>22.458334000000001</v>
       </c>
       <c r="K734" s="1">
-        <v>36000</v>
+        <v>258270.83</v>
       </c>
       <c r="L734" s="1"/>
       <c r="M734" s="1"/>
       <c r="N734" s="1"/>
       <c r="O734" s="1">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="P734" s="1" t="s">
         <v>20</v>
@@ -30499,19 +30487,19 @@
       <c r="G735" s="1"/>
       <c r="H735" s="1"/>
       <c r="I735" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J735" s="1">
-        <v>22.458334000000001</v>
+        <v>10</v>
       </c>
       <c r="K735" s="1">
-        <v>258270.83</v>
+        <v>180000</v>
       </c>
       <c r="L735" s="1"/>
       <c r="M735" s="1"/>
       <c r="N735" s="1"/>
       <c r="O735" s="1">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="P735" s="1" t="s">
         <v>20</v>
@@ -30531,25 +30519,25 @@
         <v>57</v>
       </c>
       <c r="E736" s="1" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F736" s="1"/>
       <c r="G736" s="1"/>
       <c r="H736" s="1"/>
       <c r="I736" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="J736" s="1">
         <v>10</v>
       </c>
       <c r="K736" s="1">
-        <v>180000</v>
+        <v>260000</v>
       </c>
       <c r="L736" s="1"/>
       <c r="M736" s="1"/>
       <c r="N736" s="1"/>
       <c r="O736" s="1">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="P736" s="1" t="s">
         <v>20</v>
@@ -30575,19 +30563,19 @@
       <c r="G737" s="1"/>
       <c r="H737" s="1"/>
       <c r="I737" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="J737" s="1">
-        <v>10</v>
+        <v>9.0416670000000003</v>
       </c>
       <c r="K737" s="1">
-        <v>260000</v>
+        <v>171791.67</v>
       </c>
       <c r="L737" s="1"/>
       <c r="M737" s="1"/>
       <c r="N737" s="1"/>
       <c r="O737" s="1">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="P737" s="1" t="s">
         <v>20</v>
@@ -30613,19 +30601,19 @@
       <c r="G738" s="1"/>
       <c r="H738" s="1"/>
       <c r="I738" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J738" s="1">
-        <v>9.0416670000000003</v>
+        <v>21.5</v>
       </c>
       <c r="K738" s="1">
-        <v>171791.67</v>
+        <v>419250</v>
       </c>
       <c r="L738" s="1"/>
       <c r="M738" s="1"/>
       <c r="N738" s="1"/>
       <c r="O738" s="1">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="P738" s="1" t="s">
         <v>20</v>
@@ -30651,19 +30639,19 @@
       <c r="G739" s="1"/>
       <c r="H739" s="1"/>
       <c r="I739" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="J739" s="1">
-        <v>21.5</v>
+        <v>19</v>
       </c>
       <c r="K739" s="1">
-        <v>419250</v>
+        <v>532000</v>
       </c>
       <c r="L739" s="1"/>
       <c r="M739" s="1"/>
       <c r="N739" s="1"/>
       <c r="O739" s="1">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="P739" s="1" t="s">
         <v>20</v>
@@ -30689,19 +30677,19 @@
       <c r="G740" s="1"/>
       <c r="H740" s="1"/>
       <c r="I740" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J740" s="1">
-        <v>19</v>
+        <v>8.5</v>
       </c>
       <c r="K740" s="1">
-        <v>532000</v>
+        <v>148750</v>
       </c>
       <c r="L740" s="1"/>
       <c r="M740" s="1"/>
       <c r="N740" s="1"/>
       <c r="O740" s="1">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="P740" s="1" t="s">
         <v>20</v>
@@ -30727,19 +30715,19 @@
       <c r="G741" s="1"/>
       <c r="H741" s="1"/>
       <c r="I741" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J741" s="1">
-        <v>8.5</v>
+        <v>15.083333</v>
       </c>
       <c r="K741" s="1">
-        <v>148750</v>
+        <v>505291.66</v>
       </c>
       <c r="L741" s="1"/>
       <c r="M741" s="1"/>
       <c r="N741" s="1"/>
       <c r="O741" s="1">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="P741" s="1" t="s">
         <v>20</v>
@@ -30765,19 +30753,19 @@
       <c r="G742" s="1"/>
       <c r="H742" s="1"/>
       <c r="I742" s="1" t="s">
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="J742" s="1">
-        <v>15.083333</v>
+        <v>7.1666664999999998</v>
       </c>
       <c r="K742" s="1">
-        <v>505291.66</v>
+        <v>240083.33</v>
       </c>
       <c r="L742" s="1"/>
       <c r="M742" s="1"/>
       <c r="N742" s="1"/>
       <c r="O742" s="1">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="P742" s="1" t="s">
         <v>20</v>
@@ -30803,19 +30791,19 @@
       <c r="G743" s="1"/>
       <c r="H743" s="1"/>
       <c r="I743" s="1" t="s">
-        <v>97</v>
+        <v>19</v>
       </c>
       <c r="J743" s="1">
-        <v>7.1666664999999998</v>
+        <v>22.5</v>
       </c>
       <c r="K743" s="1">
-        <v>240083.33</v>
+        <v>236250</v>
       </c>
       <c r="L743" s="1"/>
       <c r="M743" s="1"/>
       <c r="N743" s="1"/>
       <c r="O743" s="1">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="P743" s="1" t="s">
         <v>20</v>
@@ -30841,19 +30829,19 @@
       <c r="G744" s="1"/>
       <c r="H744" s="1"/>
       <c r="I744" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="J744" s="1">
-        <v>22.5</v>
+        <v>11.583333</v>
       </c>
       <c r="K744" s="1">
-        <v>236250</v>
+        <v>306958.34000000003</v>
       </c>
       <c r="L744" s="1"/>
       <c r="M744" s="1"/>
       <c r="N744" s="1"/>
       <c r="O744" s="1">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="P744" s="1" t="s">
         <v>20</v>
@@ -30879,19 +30867,19 @@
       <c r="G745" s="1"/>
       <c r="H745" s="1"/>
       <c r="I745" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="J745" s="1">
-        <v>11.583333</v>
+        <v>39.9</v>
       </c>
       <c r="K745" s="1">
-        <v>306958.34000000003</v>
+        <v>478800</v>
       </c>
       <c r="L745" s="1"/>
       <c r="M745" s="1"/>
       <c r="N745" s="1"/>
       <c r="O745" s="1">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="P745" s="1" t="s">
         <v>20</v>
@@ -30917,19 +30905,19 @@
       <c r="G746" s="1"/>
       <c r="H746" s="1"/>
       <c r="I746" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J746" s="1">
-        <v>39.9</v>
+        <v>10.4</v>
       </c>
       <c r="K746" s="1">
-        <v>478800</v>
+        <v>62400</v>
       </c>
       <c r="L746" s="1"/>
       <c r="M746" s="1"/>
       <c r="N746" s="1"/>
       <c r="O746" s="1">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="P746" s="1" t="s">
         <v>20</v>
@@ -30955,19 +30943,19 @@
       <c r="G747" s="1"/>
       <c r="H747" s="1"/>
       <c r="I747" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J747" s="1">
-        <v>10.4</v>
+        <v>4.5</v>
       </c>
       <c r="K747" s="1">
-        <v>62400</v>
+        <v>56250</v>
       </c>
       <c r="L747" s="1"/>
       <c r="M747" s="1"/>
       <c r="N747" s="1"/>
       <c r="O747" s="1">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="P747" s="1" t="s">
         <v>20</v>
@@ -30993,19 +30981,19 @@
       <c r="G748" s="1"/>
       <c r="H748" s="1"/>
       <c r="I748" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J748" s="1">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="K748" s="1">
-        <v>56250</v>
+        <v>155000</v>
       </c>
       <c r="L748" s="1"/>
       <c r="M748" s="1"/>
       <c r="N748" s="1"/>
       <c r="O748" s="1">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="P748" s="1" t="s">
         <v>20</v>
@@ -31031,19 +31019,19 @@
       <c r="G749" s="1"/>
       <c r="H749" s="1"/>
       <c r="I749" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J749" s="1">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="K749" s="1">
-        <v>155000</v>
+        <v>131750</v>
       </c>
       <c r="L749" s="1"/>
       <c r="M749" s="1"/>
       <c r="N749" s="1"/>
       <c r="O749" s="1">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="P749" s="1" t="s">
         <v>20</v>
@@ -31069,19 +31057,19 @@
       <c r="G750" s="1"/>
       <c r="H750" s="1"/>
       <c r="I750" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J750" s="1">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="K750" s="1">
-        <v>131750</v>
+        <v>180000</v>
       </c>
       <c r="L750" s="1"/>
       <c r="M750" s="1"/>
       <c r="N750" s="1"/>
       <c r="O750" s="1">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="P750" s="1" t="s">
         <v>20</v>
@@ -31107,19 +31095,19 @@
       <c r="G751" s="1"/>
       <c r="H751" s="1"/>
       <c r="I751" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J751" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K751" s="1">
-        <v>180000</v>
+        <v>63000</v>
       </c>
       <c r="L751" s="1"/>
       <c r="M751" s="1"/>
       <c r="N751" s="1"/>
       <c r="O751" s="1">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="P751" s="1" t="s">
         <v>20</v>
@@ -31145,19 +31133,19 @@
       <c r="G752" s="1"/>
       <c r="H752" s="1"/>
       <c r="I752" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J752" s="1">
-        <v>14</v>
+        <v>22.458334000000001</v>
       </c>
       <c r="K752" s="1">
-        <v>63000</v>
+        <v>258270.83</v>
       </c>
       <c r="L752" s="1"/>
       <c r="M752" s="1"/>
       <c r="N752" s="1"/>
       <c r="O752" s="1">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="P752" s="1" t="s">
         <v>20</v>
@@ -31183,19 +31171,19 @@
       <c r="G753" s="1"/>
       <c r="H753" s="1"/>
       <c r="I753" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="J753" s="1">
-        <v>22.458334000000001</v>
+        <v>12.833333</v>
       </c>
       <c r="K753" s="1">
-        <v>258270.83</v>
+        <v>128333.336</v>
       </c>
       <c r="L753" s="1"/>
       <c r="M753" s="1"/>
       <c r="N753" s="1"/>
       <c r="O753" s="1">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="P753" s="1" t="s">
         <v>20</v>
@@ -31221,61 +31209,41 @@
       <c r="G754" s="1"/>
       <c r="H754" s="1"/>
       <c r="I754" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J754" s="1">
-        <v>12.833333</v>
+        <v>5.1666664999999998</v>
       </c>
       <c r="K754" s="1">
-        <v>128333.336</v>
+        <v>62000</v>
       </c>
       <c r="L754" s="1"/>
       <c r="M754" s="1"/>
       <c r="N754" s="1"/>
       <c r="O754" s="1">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="P754" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="755" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A755" s="2">
-        <v>46188</v>
-      </c>
-      <c r="B755" s="1">
-        <v>0</v>
-      </c>
-      <c r="C755" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D755" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E755" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="A755" s="2"/>
+      <c r="B755" s="1"/>
+      <c r="C755" s="1"/>
+      <c r="D755" s="1"/>
+      <c r="E755" s="1"/>
       <c r="F755" s="1"/>
       <c r="G755" s="1"/>
       <c r="H755" s="1"/>
-      <c r="I755" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J755" s="1">
-        <v>5.1666664999999998</v>
-      </c>
-      <c r="K755" s="1">
-        <v>62000</v>
-      </c>
+      <c r="I755" s="1"/>
+      <c r="J755" s="1"/>
+      <c r="K755" s="1"/>
       <c r="L755" s="1"/>
       <c r="M755" s="1"/>
       <c r="N755" s="1"/>
-      <c r="O755" s="1">
-        <v>1792</v>
-      </c>
-      <c r="P755" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="O755" s="1"/>
+      <c r="P755" s="1"/>
     </row>
     <row r="756" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A756" s="2"/>
@@ -59897,26 +59865,8 @@
       <c r="O2345" s="1"/>
       <c r="P2345" s="1"/>
     </row>
-    <row r="2346" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A2346" s="2"/>
-      <c r="B2346" s="1"/>
-      <c r="C2346" s="1"/>
-      <c r="D2346" s="1"/>
-      <c r="E2346" s="1"/>
-      <c r="F2346" s="1"/>
-      <c r="G2346" s="1"/>
-      <c r="H2346" s="1"/>
-      <c r="I2346" s="1"/>
-      <c r="J2346" s="1"/>
-      <c r="K2346" s="1"/>
-      <c r="L2346" s="1"/>
-      <c r="M2346" s="1"/>
-      <c r="N2346" s="1"/>
-      <c r="O2346" s="1"/>
-      <c r="P2346" s="1"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P755" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:P754" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -70,7 +70,7 @@
     <col min="2" max="2" width="26.43359375" customWidth="true"/>
     <col min="3" max="3" width="8.57421875" customWidth="true"/>
     <col min="4" max="4" width="15.296875" customWidth="true"/>
-    <col min="5" max="5" width="12.61328125" customWidth="true"/>
+    <col min="5" max="5" width="16.5234375" customWidth="true"/>
     <col min="6" max="6" width="8.6953125" customWidth="true"/>
     <col min="7" max="7" width="26.671875" customWidth="true"/>
     <col min="8" max="8" width="9.55078125" customWidth="true"/>
@@ -2034,6 +2034,556 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1" t="inlineStr">
+        <is>
+          <t>Cafe au Lait 3-en-1</t>
+        </is>
+      </c>
+      <c r="J32" s="1" t="n">
+        <v>99.0</v>
+      </c>
+      <c r="K32" s="1" t="n">
+        <v>445500.0</v>
+      </c>
+      <c r="L32" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M32" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="P32" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q32" s="1"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F33" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1" t="inlineStr">
+        <is>
+          <t>Chocolat 3-en-1 30x120 pcs</t>
+        </is>
+      </c>
+      <c r="J33" s="1" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="K33" s="1" t="n">
+        <v>1100000.0</v>
+      </c>
+      <c r="L33" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M33" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="P33" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q33" s="1"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1" t="inlineStr">
+        <is>
+          <t>Cowmilk 200gx10</t>
+        </is>
+      </c>
+      <c r="J34" s="1" t="n">
+        <v>134.0</v>
+      </c>
+      <c r="K34" s="1" t="n">
+        <v>804000.0</v>
+      </c>
+      <c r="L34" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M34" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="P34" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q34" s="1"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F35" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1" t="inlineStr">
+        <is>
+          <t>Cowmilk 5kg</t>
+        </is>
+      </c>
+      <c r="J35" s="1" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="K35" s="1" t="n">
+        <v>176000.0</v>
+      </c>
+      <c r="L35" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M35" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="P35" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q35" s="1"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F36" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1" t="inlineStr">
+        <is>
+          <t>Jus Lido</t>
+        </is>
+      </c>
+      <c r="J36" s="1" t="n">
+        <v>200.0</v>
+      </c>
+      <c r="K36" s="1" t="n">
+        <v>2200000.0</v>
+      </c>
+      <c r="L36" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M36" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="P36" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q36" s="1"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F37" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1" t="inlineStr">
+        <is>
+          <t>Kamlac Junior BLE cereal 230g x 12 sachet</t>
+        </is>
+      </c>
+      <c r="J37" s="1" t="n">
+        <v>24.416666</v>
+      </c>
+      <c r="K37" s="1" t="n">
+        <v>219750.0</v>
+      </c>
+      <c r="L37" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M37" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="P37" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q37" s="1"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F38" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1" t="inlineStr">
+        <is>
+          <t>Kamlac Junior BLE cereal 50g x 10 x 8 sachet</t>
+        </is>
+      </c>
+      <c r="J38" s="1" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="K38" s="1" t="n">
+        <v>375000.0</v>
+      </c>
+      <c r="L38" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M38" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1" t="n">
+        <v>37.0</v>
+      </c>
+      <c r="P38" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q38" s="1"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E39" s="1" t="inlineStr">
+        <is>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F39" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1" t="inlineStr">
+        <is>
+          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
+        </is>
+      </c>
+      <c r="J39" s="1" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="K39" s="1" t="n">
+        <v>225000.0</v>
+      </c>
+      <c r="L39" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M39" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1" t="n">
+        <v>38.0</v>
+      </c>
+      <c r="P39" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q39" s="1"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E40" s="1" t="inlineStr">
+        <is>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F40" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1" t="inlineStr">
+        <is>
+          <t>Kamlac Junior mais cereal 50g x 10 x 8 sachet</t>
+        </is>
+      </c>
+      <c r="J40" s="1" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="K40" s="1" t="n">
+        <v>375000.0</v>
+      </c>
+      <c r="L40" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M40" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="P40" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q40" s="1"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="inlineStr">
+        <is>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F41" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1" t="inlineStr">
+        <is>
+          <t>Kamlac Thé 7g</t>
+        </is>
+      </c>
+      <c r="J41" s="1" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="K41" s="1" t="n">
+        <v>1150000.0</v>
+      </c>
+      <c r="L41" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M41" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="P41" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q41" s="1"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -2038,7 +2038,9 @@
       <c r="A32" s="2" t="n">
         <v>46221.0</v>
       </c>
-      <c r="B32" s="1"/>
+      <c r="B32" s="1" t="n">
+        <v>0.0</v>
+      </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
           <t>TATA 1</t>
@@ -2093,7 +2095,9 @@
       <c r="A33" s="2" t="n">
         <v>46221.0</v>
       </c>
-      <c r="B33" s="1"/>
+      <c r="B33" s="1" t="n">
+        <v>0.0</v>
+      </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
           <t>TATA 1</t>
@@ -2148,7 +2152,9 @@
       <c r="A34" s="2" t="n">
         <v>46221.0</v>
       </c>
-      <c r="B34" s="1"/>
+      <c r="B34" s="1" t="n">
+        <v>0.0</v>
+      </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
           <t>TATA 1</t>
@@ -2203,7 +2209,9 @@
       <c r="A35" s="2" t="n">
         <v>46221.0</v>
       </c>
-      <c r="B35" s="1"/>
+      <c r="B35" s="1" t="n">
+        <v>0.0</v>
+      </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
           <t>TATA 1</t>
@@ -2258,7 +2266,9 @@
       <c r="A36" s="2" t="n">
         <v>46221.0</v>
       </c>
-      <c r="B36" s="1"/>
+      <c r="B36" s="1" t="n">
+        <v>0.0</v>
+      </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
           <t>TATA 1</t>
@@ -2313,7 +2323,9 @@
       <c r="A37" s="2" t="n">
         <v>46221.0</v>
       </c>
-      <c r="B37" s="1"/>
+      <c r="B37" s="1" t="n">
+        <v>0.0</v>
+      </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
           <t>TATA 1</t>
@@ -2368,7 +2380,9 @@
       <c r="A38" s="2" t="n">
         <v>46221.0</v>
       </c>
-      <c r="B38" s="1"/>
+      <c r="B38" s="1" t="n">
+        <v>0.0</v>
+      </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
           <t>TATA 1</t>
@@ -2423,7 +2437,9 @@
       <c r="A39" s="2" t="n">
         <v>46221.0</v>
       </c>
-      <c r="B39" s="1"/>
+      <c r="B39" s="1" t="n">
+        <v>0.0</v>
+      </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
           <t>TATA 1</t>
@@ -2478,7 +2494,9 @@
       <c r="A40" s="2" t="n">
         <v>46221.0</v>
       </c>
-      <c r="B40" s="1"/>
+      <c r="B40" s="1" t="n">
+        <v>0.0</v>
+      </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
           <t>TATA 1</t>
@@ -2533,7 +2551,9 @@
       <c r="A41" s="2" t="n">
         <v>46221.0</v>
       </c>
-      <c r="B41" s="1"/>
+      <c r="B41" s="1" t="n">
+        <v>0.0</v>
+      </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
           <t>TATA 1</t>
@@ -2583,6 +2603,63 @@
         </is>
       </c>
       <c r="Q41" s="1"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E42" s="1" t="inlineStr">
+        <is>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F42" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1" t="inlineStr">
+        <is>
+          <t>Kamlac évaporé 48x160g</t>
+        </is>
+      </c>
+      <c r="J42" s="1" t="n">
+        <v>599.0</v>
+      </c>
+      <c r="K42" s="1" t="n">
+        <v>6289500.0</v>
+      </c>
+      <c r="L42" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M42" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="P42" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q42" s="1"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -174,7 +174,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46221.0</v>
+        <v>46222.0</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>0.0</v>
@@ -191,7 +191,7 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>Stock Lundi</t>
+          <t>Vente</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
@@ -199,39 +199,47 @@
           <t>TOUBA</t>
         </is>
       </c>
-      <c r="G2" s="1"/>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>Saliou KONE</t>
+        </is>
+      </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>Kamlac évaporé 48x160g</t>
+          <t>Cowmilk 5kg</t>
         </is>
       </c>
       <c r="J2" s="1" t="n">
-        <v>600.0</v>
+        <v>2.0</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>6300000.0</v>
+        <v>22000.0</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>0.0</v>
+        <v>5000.0</v>
       </c>
       <c r="M2" s="1" t="n">
         <v>0.0</v>
       </c>
       <c r="N2" s="1"/>
       <c r="O2" s="1" t="n">
-        <v>1.0</v>
+        <v>42.0</v>
       </c>
       <c r="P2" s="1" t="inlineStr">
         <is>
           <t>S29</t>
         </is>
       </c>
-      <c r="Q2" s="1"/>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46221.0</v>
+        <v>46222.0</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>0.0</v>
@@ -248,7 +256,7 @@
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>Stock Lundi</t>
+          <t>Vente</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
@@ -256,18 +264,22 @@
           <t>TOUBA</t>
         </is>
       </c>
-      <c r="G3" s="1"/>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>Saliou KONE</t>
+        </is>
+      </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>Jus Lido</t>
+          <t>Cowmilk 200gx10</t>
         </is>
       </c>
       <c r="J3" s="1" t="n">
-        <v>200.0</v>
+        <v>1.0</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>2200000.0</v>
+        <v>6000.0</v>
       </c>
       <c r="L3" s="1" t="n">
         <v>0.0</v>
@@ -277,18 +289,22 @@
       </c>
       <c r="N3" s="1"/>
       <c r="O3" s="1" t="n">
-        <v>2.0</v>
+        <v>43.0</v>
       </c>
       <c r="P3" s="1" t="inlineStr">
         <is>
           <t>S29</t>
         </is>
       </c>
-      <c r="Q3" s="1"/>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46221.0</v>
+        <v>46222.0</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>0.0</v>
@@ -305,7 +321,7 @@
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>Stock Lundi</t>
+          <t>Vente</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
@@ -313,7 +329,11 @@
           <t>TOUBA</t>
         </is>
       </c>
-      <c r="G4" s="1"/>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>Saliou KONE</t>
+        </is>
+      </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1" t="inlineStr">
         <is>
@@ -321,10 +341,10 @@
         </is>
       </c>
       <c r="J4" s="1" t="n">
-        <v>100.0</v>
+        <v>1.0</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>450000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="L4" s="1" t="n">
         <v>0.0</v>
@@ -334,18 +354,22 @@
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1" t="n">
-        <v>3.0</v>
+        <v>44.0</v>
       </c>
       <c r="P4" s="1" t="inlineStr">
         <is>
           <t>S29</t>
         </is>
       </c>
-      <c r="Q4" s="1"/>
+      <c r="Q4" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46221.0</v>
+        <v>46222.0</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>0.0</v>
@@ -362,7 +386,7 @@
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>Stock Lundi</t>
+          <t>Vente</t>
         </is>
       </c>
       <c r="F5" s="1" t="inlineStr">
@@ -370,18 +394,22 @@
           <t>TOUBA</t>
         </is>
       </c>
-      <c r="G5" s="1"/>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>Adama DABO</t>
+        </is>
+      </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>Chocolat 3-en-1 30x120 pcs</t>
+          <t>Cowmilk 5kg</t>
         </is>
       </c>
       <c r="J5" s="1" t="n">
-        <v>100.0</v>
+        <v>2.0</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>1100000.0</v>
+        <v>22000.0</v>
       </c>
       <c r="L5" s="1" t="n">
         <v>0.0</v>
@@ -391,18 +419,22 @@
       </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1" t="n">
-        <v>4.0</v>
+        <v>45.0</v>
       </c>
       <c r="P5" s="1" t="inlineStr">
         <is>
           <t>S29</t>
         </is>
       </c>
-      <c r="Q5" s="1"/>
+      <c r="Q5" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46221.0</v>
+        <v>46222.0</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>0.0</v>
@@ -419,7 +451,7 @@
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>Stock Lundi</t>
+          <t>Vente</t>
         </is>
       </c>
       <c r="F6" s="1" t="inlineStr">
@@ -427,18 +459,22 @@
           <t>TOUBA</t>
         </is>
       </c>
-      <c r="G6" s="1"/>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>Adama DABO</t>
+        </is>
+      </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Thé 7g</t>
+          <t>Cowmilk 200gx10</t>
         </is>
       </c>
       <c r="J6" s="1" t="n">
-        <v>100.0</v>
+        <v>2.0</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>1150000.0</v>
+        <v>12000.0</v>
       </c>
       <c r="L6" s="1" t="n">
         <v>0.0</v>
@@ -448,18 +484,22 @@
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1" t="n">
-        <v>5.0</v>
+        <v>46.0</v>
       </c>
       <c r="P6" s="1" t="inlineStr">
         <is>
           <t>S29</t>
         </is>
       </c>
-      <c r="Q6" s="1"/>
+      <c r="Q6" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46221.0</v>
+        <v>46222.0</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>0.0</v>
@@ -476,7 +516,7 @@
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>Stock Lundi</t>
+          <t>Vente</t>
         </is>
       </c>
       <c r="F7" s="1" t="inlineStr">
@@ -484,18 +524,22 @@
           <t>TOUBA</t>
         </is>
       </c>
-      <c r="G7" s="1"/>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>Adama DABO</t>
+        </is>
+      </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1" t="inlineStr">
         <is>
-          <t>Cowmilk 5kg</t>
+          <t>Kamlac évaporé 48x160g</t>
         </is>
       </c>
       <c r="J7" s="1" t="n">
-        <v>100.0</v>
+        <v>3.0</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>1100000.0</v>
+        <v>31500.0</v>
       </c>
       <c r="L7" s="1" t="n">
         <v>0.0</v>
@@ -505,18 +549,22 @@
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1" t="n">
-        <v>6.0</v>
+        <v>47.0</v>
       </c>
       <c r="P7" s="1" t="inlineStr">
         <is>
           <t>S29</t>
         </is>
       </c>
-      <c r="Q7" s="1"/>
+      <c r="Q7" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46221.0</v>
+        <v>46222.0</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>0.0</v>
@@ -533,7 +581,7 @@
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>Stock Lundi</t>
+          <t>Vente</t>
         </is>
       </c>
       <c r="F8" s="1" t="inlineStr">
@@ -541,18 +589,22 @@
           <t>TOUBA</t>
         </is>
       </c>
-      <c r="G8" s="1"/>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>Adama DABO</t>
+        </is>
+      </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="inlineStr">
         <is>
-          <t>Cowmilk 200gx10</t>
+          <t>Kamlac Junior BLE cereal 230g x 12 sachet</t>
         </is>
       </c>
       <c r="J8" s="1" t="n">
-        <v>140.0</v>
+        <v>1.0</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>840000.0</v>
+        <v>9000.0</v>
       </c>
       <c r="L8" s="1" t="n">
         <v>0.0</v>
@@ -562,18 +614,22 @@
       </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1" t="n">
-        <v>7.0</v>
+        <v>48.0</v>
       </c>
       <c r="P8" s="1" t="inlineStr">
         <is>
           <t>S29</t>
         </is>
       </c>
-      <c r="Q8" s="1"/>
+      <c r="Q8" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46221.0</v>
+        <v>46222.0</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>0.0</v>
@@ -590,7 +646,7 @@
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>Stock Lundi</t>
+          <t>Vente</t>
         </is>
       </c>
       <c r="F9" s="1" t="inlineStr">
@@ -598,18 +654,22 @@
           <t>TOUBA</t>
         </is>
       </c>
-      <c r="G9" s="1"/>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>Adama DABO</t>
+        </is>
+      </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior BLE cereal 50g x 10 x 8 sachet</t>
+          <t>Kamlac Thé 7g</t>
         </is>
       </c>
       <c r="J9" s="1" t="n">
-        <v>25.0</v>
+        <v>0.25</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>375000.0</v>
+        <v>2875.0</v>
       </c>
       <c r="L9" s="1" t="n">
         <v>0.0</v>
@@ -619,18 +679,22 @@
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1" t="n">
-        <v>8.0</v>
+        <v>49.0</v>
       </c>
       <c r="P9" s="1" t="inlineStr">
         <is>
           <t>S29</t>
         </is>
       </c>
-      <c r="Q9" s="1"/>
+      <c r="Q9" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46221.0</v>
+        <v>46222.0</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>0.0</v>
@@ -647,7 +711,7 @@
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>Stock Lundi</t>
+          <t>Vente</t>
         </is>
       </c>
       <c r="F10" s="1" t="inlineStr">
@@ -655,18 +719,22 @@
           <t>TOUBA</t>
         </is>
       </c>
-      <c r="G10" s="1"/>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>Saly THIOUNE (T2)</t>
+        </is>
+      </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior mais cereal 50g x 10 x 8 sachet</t>
+          <t>Kamlac évaporé 48x160g</t>
         </is>
       </c>
       <c r="J10" s="1" t="n">
-        <v>25.0</v>
+        <v>2.0</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>375000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="L10" s="1" t="n">
         <v>0.0</v>
@@ -676,18 +744,22 @@
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1" t="n">
-        <v>9.0</v>
+        <v>50.0</v>
       </c>
       <c r="P10" s="1" t="inlineStr">
         <is>
           <t>S29</t>
         </is>
       </c>
-      <c r="Q10" s="1"/>
+      <c r="Q10" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46221.0</v>
+        <v>46222.0</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>0.0</v>
@@ -704,7 +776,7 @@
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>Stock Lundi</t>
+          <t>Vente</t>
         </is>
       </c>
       <c r="F11" s="1" t="inlineStr">
@@ -712,18 +784,22 @@
           <t>TOUBA</t>
         </is>
       </c>
-      <c r="G11" s="1"/>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>Sokhna (T2)</t>
+        </is>
+      </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
+          <t>Kamlac évaporé 48x160g</t>
         </is>
       </c>
       <c r="J11" s="1" t="n">
-        <v>25.0</v>
+        <v>1.0</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>225000.0</v>
+        <v>10500.0</v>
       </c>
       <c r="L11" s="1" t="n">
         <v>0.0</v>
@@ -733,18 +809,22 @@
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1" t="n">
-        <v>10.0</v>
+        <v>51.0</v>
       </c>
       <c r="P11" s="1" t="inlineStr">
         <is>
           <t>S29</t>
         </is>
       </c>
-      <c r="Q11" s="1"/>
+      <c r="Q11" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46221.0</v>
+        <v>46222.0</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>0.0</v>
@@ -761,7 +841,7 @@
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>Stock Lundi</t>
+          <t>Vente</t>
         </is>
       </c>
       <c r="F12" s="1" t="inlineStr">
@@ -769,18 +849,22 @@
           <t>TOUBA</t>
         </is>
       </c>
-      <c r="G12" s="1"/>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>Sokhna (T2)</t>
+        </is>
+      </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior BLE cereal 230g x 12 sachet</t>
+          <t>Cowmilk 200gx10</t>
         </is>
       </c>
       <c r="J12" s="1" t="n">
-        <v>25.0</v>
+        <v>0.5</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>225000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="L12" s="1" t="n">
         <v>0.0</v>
@@ -790,18 +874,22 @@
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1" t="n">
-        <v>11.0</v>
+        <v>52.0</v>
       </c>
       <c r="P12" s="1" t="inlineStr">
         <is>
           <t>S29</t>
         </is>
       </c>
-      <c r="Q12" s="1"/>
+      <c r="Q12" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46221.0</v>
+        <v>46222.0</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>0.0</v>
@@ -828,7 +916,7 @@
       </c>
       <c r="G13" s="1" t="inlineStr">
         <is>
-          <t>Jackline DIEDHIOU (T3)</t>
+          <t>Sokhna (T2)</t>
         </is>
       </c>
       <c r="H13" s="1"/>
@@ -838,20 +926,20 @@
         </is>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.5833333</v>
+        <v>1.0</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>5250.0</v>
+        <v>9000.0</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>10000.0</v>
+        <v>0.0</v>
       </c>
       <c r="M13" s="1" t="n">
         <v>0.0</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1" t="n">
-        <v>12.0</v>
+        <v>53.0</v>
       </c>
       <c r="P13" s="1" t="inlineStr">
         <is>
@@ -866,7 +954,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46221.0</v>
+        <v>46222.0</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>0.0</v>
@@ -893,20 +981,20 @@
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>Jackline DIEDHIOU (T3)</t>
+          <t>Ndeye Fatou GUEYE (T3)</t>
         </is>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1" t="inlineStr">
         <is>
-          <t>Cowmilk 5kg</t>
+          <t>Cowmilk 200gx10</t>
         </is>
       </c>
       <c r="J14" s="1" t="n">
-        <v>6.0</v>
+        <v>0.5</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>66000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="L14" s="1" t="n">
         <v>0.0</v>
@@ -916,7 +1004,7 @@
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1" t="n">
-        <v>13.0</v>
+        <v>54.0</v>
       </c>
       <c r="P14" s="1" t="inlineStr">
         <is>
@@ -931,7 +1019,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46221.0</v>
+        <v>46222.0</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>0.0</v>
@@ -958,20 +1046,20 @@
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
-          <t>Ndeye Fatou GUEYE (T3)</t>
+          <t>Jackline DIEDHIOU (T3)</t>
         </is>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1" t="inlineStr">
         <is>
-          <t>Cowmilk 5kg</t>
+          <t>Cowmilk 200gx10</t>
         </is>
       </c>
       <c r="J15" s="1" t="n">
-        <v>6.0</v>
+        <v>0.5</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>66000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="L15" s="1" t="n">
         <v>0.0</v>
@@ -981,7 +1069,7 @@
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1" t="n">
-        <v>14.0</v>
+        <v>55.0</v>
       </c>
       <c r="P15" s="1" t="inlineStr">
         <is>
@@ -996,7 +1084,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46221.0</v>
+        <v>46222.0</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>0.0</v>
@@ -1023,7 +1111,7 @@
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
-          <t>Saliou KONE</t>
+          <t>Fama DIOUF</t>
         </is>
       </c>
       <c r="H16" s="1"/>
@@ -1033,10 +1121,10 @@
         </is>
       </c>
       <c r="J16" s="1" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>66000.0</v>
+        <v>55000.0</v>
       </c>
       <c r="L16" s="1" t="n">
         <v>0.0</v>
@@ -1046,7 +1134,7 @@
       </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1" t="n">
-        <v>15.0</v>
+        <v>56.0</v>
       </c>
       <c r="P16" s="1" t="inlineStr">
         <is>
@@ -1061,7 +1149,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46221.0</v>
+        <v>46222.0</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>0.0</v>
@@ -1088,20 +1176,20 @@
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
-          <t>Saliou KONE</t>
+          <t>Mariama KANE</t>
         </is>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1" t="inlineStr">
         <is>
-          <t>Kamlac évaporé 48x160g</t>
+          <t>Cowmilk 5kg</t>
         </is>
       </c>
       <c r="J17" s="1" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>10500.0</v>
+        <v>55000.0</v>
       </c>
       <c r="L17" s="1" t="n">
         <v>0.0</v>
@@ -1111,7 +1199,7 @@
       </c>
       <c r="N17" s="1"/>
       <c r="O17" s="1" t="n">
-        <v>16.0</v>
+        <v>57.0</v>
       </c>
       <c r="P17" s="1" t="inlineStr">
         <is>
@@ -1126,7 +1214,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46221.0</v>
+        <v>46222.0</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>0.0</v>
@@ -1153,20 +1241,20 @@
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>Saliou KONE</t>
+          <t>Fallou SOLY (T2)</t>
         </is>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1" t="inlineStr">
         <is>
-          <t>Cowmilk 200gx10</t>
+          <t>Kamlac Thé 7g</t>
         </is>
       </c>
       <c r="J18" s="1" t="n">
-        <v>2.0</v>
+        <v>0.25</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>12000.0</v>
+        <v>2875.0</v>
       </c>
       <c r="L18" s="1" t="n">
         <v>0.0</v>
@@ -1176,7 +1264,7 @@
       </c>
       <c r="N18" s="1"/>
       <c r="O18" s="1" t="n">
-        <v>17.0</v>
+        <v>58.0</v>
       </c>
       <c r="P18" s="1" t="inlineStr">
         <is>
@@ -1191,7 +1279,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46221.0</v>
+        <v>46222.0</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>0.0</v>
@@ -1218,20 +1306,20 @@
       </c>
       <c r="G19" s="1" t="inlineStr">
         <is>
-          <t>Adama DABO</t>
+          <t>Mariama BA</t>
         </is>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1" t="inlineStr">
         <is>
-          <t>Cowmilk 5kg</t>
+          <t>Kamlac Thé 7g</t>
         </is>
       </c>
       <c r="J19" s="1" t="n">
-        <v>7.0</v>
+        <v>0.25</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>77000.0</v>
+        <v>2875.0</v>
       </c>
       <c r="L19" s="1" t="n">
         <v>0.0</v>
@@ -1241,7 +1329,7 @@
       </c>
       <c r="N19" s="1"/>
       <c r="O19" s="1" t="n">
-        <v>18.0</v>
+        <v>59.0</v>
       </c>
       <c r="P19" s="1" t="inlineStr">
         <is>
@@ -1256,7 +1344,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46221.0</v>
+        <v>46222.0</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>0.0</v>
@@ -1283,20 +1371,20 @@
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>Adama DABO</t>
+          <t>Coumba Touré (T2)</t>
         </is>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1" t="inlineStr">
         <is>
-          <t>Cowmilk 200gx10</t>
+          <t>Cowmilk 5kg</t>
         </is>
       </c>
       <c r="J20" s="1" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>12000.0</v>
+        <v>11000.0</v>
       </c>
       <c r="L20" s="1" t="n">
         <v>0.0</v>
@@ -1306,7 +1394,7 @@
       </c>
       <c r="N20" s="1"/>
       <c r="O20" s="1" t="n">
-        <v>19.0</v>
+        <v>60.0</v>
       </c>
       <c r="P20" s="1" t="inlineStr">
         <is>
@@ -1321,7 +1409,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46221.0</v>
+        <v>46222.0</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>0.0</v>
@@ -1348,20 +1436,20 @@
       </c>
       <c r="G21" s="1" t="inlineStr">
         <is>
-          <t>Saly THIOUNE (T2)</t>
+          <t>Coumba Touré (T2)</t>
         </is>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1" t="inlineStr">
         <is>
-          <t>Cowmilk 5kg</t>
+          <t>Kamlac évaporé 48x160g</t>
         </is>
       </c>
       <c r="J21" s="1" t="n">
         <v>1.0</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>11000.0</v>
+        <v>10500.0</v>
       </c>
       <c r="L21" s="1" t="n">
         <v>0.0</v>
@@ -1371,7 +1459,7 @@
       </c>
       <c r="N21" s="1"/>
       <c r="O21" s="1" t="n">
-        <v>20.0</v>
+        <v>61.0</v>
       </c>
       <c r="P21" s="1" t="inlineStr">
         <is>
@@ -1386,7 +1474,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46221.0</v>
+        <v>46222.0</v>
       </c>
       <c r="B22" s="1" t="n">
         <v>0.0</v>
@@ -1413,21 +1501,19 @@
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
-          <t>Sokhna (T2)</t>
+          <t>Coumba Touré (T2)</t>
         </is>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1" t="inlineStr">
         <is>
-          <t>Cowmilk 5kg</t>
+          <t>Kamlac Thé 7g</t>
         </is>
       </c>
       <c r="J22" s="1" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="K22" s="1" t="n">
-        <v>22000.0</v>
-      </c>
+        <v>0.45833334</v>
+      </c>
+      <c r="K22" s="1"/>
       <c r="L22" s="1" t="n">
         <v>0.0</v>
       </c>
@@ -1436,7 +1522,7 @@
       </c>
       <c r="N22" s="1"/>
       <c r="O22" s="1" t="n">
-        <v>21.0</v>
+        <v>62.0</v>
       </c>
       <c r="P22" s="1" t="inlineStr">
         <is>
@@ -1451,7 +1537,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46221.0</v>
+        <v>46222.0</v>
       </c>
       <c r="B23" s="1" t="n">
         <v>0.0</v>
@@ -1478,20 +1564,20 @@
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
-          <t>Sokhna (T2)</t>
+          <t>Nogueye THIAME (T2)</t>
         </is>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1" t="inlineStr">
         <is>
-          <t>Cowmilk 200gx10</t>
+          <t>Cowmilk 5kg</t>
         </is>
       </c>
       <c r="J23" s="1" t="n">
         <v>1.0</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>6000.0</v>
+        <v>11000.0</v>
       </c>
       <c r="L23" s="1" t="n">
         <v>0.0</v>
@@ -1501,7 +1587,7 @@
       </c>
       <c r="N23" s="1"/>
       <c r="O23" s="1" t="n">
-        <v>22.0</v>
+        <v>63.0</v>
       </c>
       <c r="P23" s="1" t="inlineStr">
         <is>
@@ -1516,7 +1602,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46221.0</v>
+        <v>46222.0</v>
       </c>
       <c r="B24" s="1" t="n">
         <v>0.0</v>
@@ -1549,14 +1635,14 @@
       <c r="H24" s="1"/>
       <c r="I24" s="1" t="inlineStr">
         <is>
-          <t>Cowmilk 5kg</t>
+          <t>Cafe au Lait 3-en-1</t>
         </is>
       </c>
       <c r="J24" s="1" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>110000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="L24" s="1" t="n">
         <v>0.0</v>
@@ -1566,7 +1652,7 @@
       </c>
       <c r="N24" s="1"/>
       <c r="O24" s="1" t="n">
-        <v>23.0</v>
+        <v>64.0</v>
       </c>
       <c r="P24" s="1" t="inlineStr">
         <is>
@@ -1598,7 +1684,7 @@
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
+          <t>Stock Lundi</t>
         </is>
       </c>
       <c r="F25" s="1" t="inlineStr">
@@ -1606,22 +1692,18 @@
           <t>TOUBA</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>Coumba Touré (T2)</t>
-        </is>
-      </c>
+      <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1" t="inlineStr">
         <is>
-          <t>Cowmilk 5kg</t>
+          <t>Kamlac évaporé 48x160g</t>
         </is>
       </c>
       <c r="J25" s="1" t="n">
-        <v>11.0</v>
+        <v>600.0</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>121000.0</v>
+        <v>6300000.0</v>
       </c>
       <c r="L25" s="1" t="n">
         <v>0.0</v>
@@ -1631,18 +1713,14 @@
       </c>
       <c r="N25" s="1"/>
       <c r="O25" s="1" t="n">
-        <v>24.0</v>
+        <v>1.0</v>
       </c>
       <c r="P25" s="1" t="inlineStr">
         <is>
           <t>S29</t>
         </is>
       </c>
-      <c r="Q25" s="1" t="inlineStr">
-        <is>
-          <t>Equipe</t>
-        </is>
-      </c>
+      <c r="Q25" s="1"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1663,7 +1741,7 @@
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
+          <t>Stock Lundi</t>
         </is>
       </c>
       <c r="F26" s="1" t="inlineStr">
@@ -1671,22 +1749,18 @@
           <t>TOUBA</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>Fama DIOUF</t>
-        </is>
-      </c>
+      <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1" t="inlineStr">
         <is>
-          <t>Cowmilk 5kg</t>
+          <t>Jus Lido</t>
         </is>
       </c>
       <c r="J26" s="1" t="n">
-        <v>5.0</v>
+        <v>200.0</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>55000.0</v>
+        <v>2200000.0</v>
       </c>
       <c r="L26" s="1" t="n">
         <v>0.0</v>
@@ -1696,18 +1770,14 @@
       </c>
       <c r="N26" s="1"/>
       <c r="O26" s="1" t="n">
-        <v>25.0</v>
+        <v>2.0</v>
       </c>
       <c r="P26" s="1" t="inlineStr">
         <is>
           <t>S29</t>
         </is>
       </c>
-      <c r="Q26" s="1" t="inlineStr">
-        <is>
-          <t>Equipe</t>
-        </is>
-      </c>
+      <c r="Q26" s="1"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1728,7 +1798,7 @@
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
+          <t>Stock Lundi</t>
         </is>
       </c>
       <c r="F27" s="1" t="inlineStr">
@@ -1736,22 +1806,18 @@
           <t>TOUBA</t>
         </is>
       </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>Mariama KANE</t>
-        </is>
-      </c>
+      <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1" t="inlineStr">
         <is>
-          <t>Cowmilk 5kg</t>
+          <t>Cafe au Lait 3-en-1</t>
         </is>
       </c>
       <c r="J27" s="1" t="n">
-        <v>5.0</v>
+        <v>100.0</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>55000.0</v>
+        <v>450000.0</v>
       </c>
       <c r="L27" s="1" t="n">
         <v>0.0</v>
@@ -1761,18 +1827,14 @@
       </c>
       <c r="N27" s="1"/>
       <c r="O27" s="1" t="n">
-        <v>26.0</v>
+        <v>3.0</v>
       </c>
       <c r="P27" s="1" t="inlineStr">
         <is>
           <t>S29</t>
         </is>
       </c>
-      <c r="Q27" s="1" t="inlineStr">
-        <is>
-          <t>Equipe</t>
-        </is>
-      </c>
+      <c r="Q27" s="1"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1793,7 +1855,7 @@
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
+          <t>Stock Lundi</t>
         </is>
       </c>
       <c r="F28" s="1" t="inlineStr">
@@ -1801,22 +1863,18 @@
           <t>TOUBA</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>Mariama KANE</t>
-        </is>
-      </c>
+      <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1" t="inlineStr">
         <is>
-          <t>Cowmilk 200gx10</t>
+          <t>Chocolat 3-en-1 30x120 pcs</t>
         </is>
       </c>
       <c r="J28" s="1" t="n">
-        <v>1.0</v>
+        <v>100.0</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>6000.0</v>
+        <v>1100000.0</v>
       </c>
       <c r="L28" s="1" t="n">
         <v>0.0</v>
@@ -1826,18 +1884,14 @@
       </c>
       <c r="N28" s="1"/>
       <c r="O28" s="1" t="n">
-        <v>27.0</v>
+        <v>4.0</v>
       </c>
       <c r="P28" s="1" t="inlineStr">
         <is>
           <t>S29</t>
         </is>
       </c>
-      <c r="Q28" s="1" t="inlineStr">
-        <is>
-          <t>Equipe</t>
-        </is>
-      </c>
+      <c r="Q28" s="1"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -1858,7 +1912,7 @@
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
+          <t>Stock Lundi</t>
         </is>
       </c>
       <c r="F29" s="1" t="inlineStr">
@@ -1866,22 +1920,18 @@
           <t>TOUBA</t>
         </is>
       </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>Fallou SOLY (T2)</t>
-        </is>
-      </c>
+      <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1" t="inlineStr">
         <is>
-          <t>Cowmilk 5kg</t>
+          <t>Kamlac Thé 7g</t>
         </is>
       </c>
       <c r="J29" s="1" t="n">
-        <v>15.0</v>
+        <v>100.0</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>165000.0</v>
+        <v>1150000.0</v>
       </c>
       <c r="L29" s="1" t="n">
         <v>0.0</v>
@@ -1891,18 +1941,14 @@
       </c>
       <c r="N29" s="1"/>
       <c r="O29" s="1" t="n">
-        <v>28.0</v>
+        <v>5.0</v>
       </c>
       <c r="P29" s="1" t="inlineStr">
         <is>
           <t>S29</t>
         </is>
       </c>
-      <c r="Q29" s="1" t="inlineStr">
-        <is>
-          <t>Equipe</t>
-        </is>
-      </c>
+      <c r="Q29" s="1"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1923,7 +1969,7 @@
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
+          <t>Stock Lundi</t>
         </is>
       </c>
       <c r="F30" s="1" t="inlineStr">
@@ -1931,22 +1977,18 @@
           <t>TOUBA</t>
         </is>
       </c>
-      <c r="G30" s="1" t="inlineStr">
-        <is>
-          <t>Fallou SOLY (T2)</t>
-        </is>
-      </c>
+      <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1" t="inlineStr">
         <is>
-          <t>Cafe au Lait 3-en-1</t>
+          <t>Cowmilk 5kg</t>
         </is>
       </c>
       <c r="J30" s="1" t="n">
-        <v>1.0</v>
+        <v>100.0</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>4500.0</v>
+        <v>1100000.0</v>
       </c>
       <c r="L30" s="1" t="n">
         <v>0.0</v>
@@ -1956,18 +1998,14 @@
       </c>
       <c r="N30" s="1"/>
       <c r="O30" s="1" t="n">
-        <v>29.0</v>
+        <v>6.0</v>
       </c>
       <c r="P30" s="1" t="inlineStr">
         <is>
           <t>S29</t>
         </is>
       </c>
-      <c r="Q30" s="1" t="inlineStr">
-        <is>
-          <t>Equipe</t>
-        </is>
-      </c>
+      <c r="Q30" s="1"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -1988,7 +2026,7 @@
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
+          <t>Stock Lundi</t>
         </is>
       </c>
       <c r="F31" s="1" t="inlineStr">
@@ -1996,22 +2034,18 @@
           <t>TOUBA</t>
         </is>
       </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>Mariama BA</t>
-        </is>
-      </c>
+      <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1" t="inlineStr">
         <is>
-          <t>Cowmilk 5kg</t>
+          <t>Cowmilk 200gx10</t>
         </is>
       </c>
       <c r="J31" s="1" t="n">
-        <v>10.0</v>
+        <v>140.0</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>110000.0</v>
+        <v>840000.0</v>
       </c>
       <c r="L31" s="1" t="n">
         <v>0.0</v>
@@ -2021,18 +2055,14 @@
       </c>
       <c r="N31" s="1"/>
       <c r="O31" s="1" t="n">
-        <v>30.0</v>
+        <v>7.0</v>
       </c>
       <c r="P31" s="1" t="inlineStr">
         <is>
           <t>S29</t>
         </is>
       </c>
-      <c r="Q31" s="1" t="inlineStr">
-        <is>
-          <t>Equipe</t>
-        </is>
-      </c>
+      <c r="Q31" s="1"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -2053,7 +2083,7 @@
       </c>
       <c r="E32" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
+          <t>Stock Lundi</t>
         </is>
       </c>
       <c r="F32" s="1" t="inlineStr">
@@ -2065,14 +2095,14 @@
       <c r="H32" s="1"/>
       <c r="I32" s="1" t="inlineStr">
         <is>
-          <t>Cafe au Lait 3-en-1</t>
+          <t>Kamlac Junior BLE cereal 50g x 10 x 8 sachet</t>
         </is>
       </c>
       <c r="J32" s="1" t="n">
-        <v>99.0</v>
+        <v>25.0</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>445500.0</v>
+        <v>375000.0</v>
       </c>
       <c r="L32" s="1" t="n">
         <v>0.0</v>
@@ -2082,7 +2112,7 @@
       </c>
       <c r="N32" s="1"/>
       <c r="O32" s="1" t="n">
-        <v>31.0</v>
+        <v>8.0</v>
       </c>
       <c r="P32" s="1" t="inlineStr">
         <is>
@@ -2110,7 +2140,7 @@
       </c>
       <c r="E33" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
+          <t>Stock Lundi</t>
         </is>
       </c>
       <c r="F33" s="1" t="inlineStr">
@@ -2122,14 +2152,14 @@
       <c r="H33" s="1"/>
       <c r="I33" s="1" t="inlineStr">
         <is>
-          <t>Chocolat 3-en-1 30x120 pcs</t>
+          <t>Kamlac Junior mais cereal 50g x 10 x 8 sachet</t>
         </is>
       </c>
       <c r="J33" s="1" t="n">
-        <v>100.0</v>
+        <v>25.0</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>1100000.0</v>
+        <v>375000.0</v>
       </c>
       <c r="L33" s="1" t="n">
         <v>0.0</v>
@@ -2139,7 +2169,7 @@
       </c>
       <c r="N33" s="1"/>
       <c r="O33" s="1" t="n">
-        <v>32.0</v>
+        <v>9.0</v>
       </c>
       <c r="P33" s="1" t="inlineStr">
         <is>
@@ -2167,7 +2197,7 @@
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
+          <t>Stock Lundi</t>
         </is>
       </c>
       <c r="F34" s="1" t="inlineStr">
@@ -2179,14 +2209,14 @@
       <c r="H34" s="1"/>
       <c r="I34" s="1" t="inlineStr">
         <is>
-          <t>Cowmilk 200gx10</t>
+          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
         </is>
       </c>
       <c r="J34" s="1" t="n">
-        <v>134.0</v>
+        <v>25.0</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>804000.0</v>
+        <v>225000.0</v>
       </c>
       <c r="L34" s="1" t="n">
         <v>0.0</v>
@@ -2196,7 +2226,7 @@
       </c>
       <c r="N34" s="1"/>
       <c r="O34" s="1" t="n">
-        <v>33.0</v>
+        <v>10.0</v>
       </c>
       <c r="P34" s="1" t="inlineStr">
         <is>
@@ -2224,7 +2254,7 @@
       </c>
       <c r="E35" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
+          <t>Stock Lundi</t>
         </is>
       </c>
       <c r="F35" s="1" t="inlineStr">
@@ -2236,14 +2266,14 @@
       <c r="H35" s="1"/>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>Cowmilk 5kg</t>
+          <t>Kamlac Junior BLE cereal 230g x 12 sachet</t>
         </is>
       </c>
       <c r="J35" s="1" t="n">
-        <v>16.0</v>
+        <v>25.0</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>176000.0</v>
+        <v>225000.0</v>
       </c>
       <c r="L35" s="1" t="n">
         <v>0.0</v>
@@ -2253,7 +2283,7 @@
       </c>
       <c r="N35" s="1"/>
       <c r="O35" s="1" t="n">
-        <v>34.0</v>
+        <v>11.0</v>
       </c>
       <c r="P35" s="1" t="inlineStr">
         <is>
@@ -2281,7 +2311,7 @@
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
+          <t>Vente</t>
         </is>
       </c>
       <c r="F36" s="1" t="inlineStr">
@@ -2289,35 +2319,43 @@
           <t>TOUBA</t>
         </is>
       </c>
-      <c r="G36" s="1"/>
+      <c r="G36" s="1" t="inlineStr">
+        <is>
+          <t>Jackline DIEDHIOU (T3)</t>
+        </is>
+      </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1" t="inlineStr">
         <is>
-          <t>Jus Lido</t>
+          <t>Kamlac Junior BLE cereal 230g x 12 sachet</t>
         </is>
       </c>
       <c r="J36" s="1" t="n">
-        <v>200.0</v>
+        <v>0.5833333</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>2200000.0</v>
+        <v>5250.0</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>0.0</v>
+        <v>10000.0</v>
       </c>
       <c r="M36" s="1" t="n">
         <v>0.0</v>
       </c>
       <c r="N36" s="1"/>
       <c r="O36" s="1" t="n">
-        <v>35.0</v>
+        <v>12.0</v>
       </c>
       <c r="P36" s="1" t="inlineStr">
         <is>
           <t>S29</t>
         </is>
       </c>
-      <c r="Q36" s="1"/>
+      <c r="Q36" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -2338,7 +2376,7 @@
       </c>
       <c r="E37" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
+          <t>Vente</t>
         </is>
       </c>
       <c r="F37" s="1" t="inlineStr">
@@ -2346,18 +2384,22 @@
           <t>TOUBA</t>
         </is>
       </c>
-      <c r="G37" s="1"/>
+      <c r="G37" s="1" t="inlineStr">
+        <is>
+          <t>Jackline DIEDHIOU (T3)</t>
+        </is>
+      </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior BLE cereal 230g x 12 sachet</t>
+          <t>Cowmilk 5kg</t>
         </is>
       </c>
       <c r="J37" s="1" t="n">
-        <v>24.416666</v>
+        <v>6.0</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>219750.0</v>
+        <v>66000.0</v>
       </c>
       <c r="L37" s="1" t="n">
         <v>0.0</v>
@@ -2367,14 +2409,18 @@
       </c>
       <c r="N37" s="1"/>
       <c r="O37" s="1" t="n">
-        <v>36.0</v>
+        <v>13.0</v>
       </c>
       <c r="P37" s="1" t="inlineStr">
         <is>
           <t>S29</t>
         </is>
       </c>
-      <c r="Q37" s="1"/>
+      <c r="Q37" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -2395,7 +2441,7 @@
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
+          <t>Vente</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
@@ -2403,18 +2449,22 @@
           <t>TOUBA</t>
         </is>
       </c>
-      <c r="G38" s="1"/>
+      <c r="G38" s="1" t="inlineStr">
+        <is>
+          <t>Ndeye Fatou GUEYE (T3)</t>
+        </is>
+      </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior BLE cereal 50g x 10 x 8 sachet</t>
+          <t>Cowmilk 5kg</t>
         </is>
       </c>
       <c r="J38" s="1" t="n">
-        <v>25.0</v>
+        <v>6.0</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>375000.0</v>
+        <v>66000.0</v>
       </c>
       <c r="L38" s="1" t="n">
         <v>0.0</v>
@@ -2424,14 +2474,18 @@
       </c>
       <c r="N38" s="1"/>
       <c r="O38" s="1" t="n">
-        <v>37.0</v>
+        <v>14.0</v>
       </c>
       <c r="P38" s="1" t="inlineStr">
         <is>
           <t>S29</t>
         </is>
       </c>
-      <c r="Q38" s="1"/>
+      <c r="Q38" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -2452,7 +2506,7 @@
       </c>
       <c r="E39" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
+          <t>Vente</t>
         </is>
       </c>
       <c r="F39" s="1" t="inlineStr">
@@ -2460,18 +2514,22 @@
           <t>TOUBA</t>
         </is>
       </c>
-      <c r="G39" s="1"/>
+      <c r="G39" s="1" t="inlineStr">
+        <is>
+          <t>Saliou KONE</t>
+        </is>
+      </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
+          <t>Cowmilk 5kg</t>
         </is>
       </c>
       <c r="J39" s="1" t="n">
-        <v>25.0</v>
+        <v>6.0</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>225000.0</v>
+        <v>66000.0</v>
       </c>
       <c r="L39" s="1" t="n">
         <v>0.0</v>
@@ -2481,14 +2539,18 @@
       </c>
       <c r="N39" s="1"/>
       <c r="O39" s="1" t="n">
-        <v>38.0</v>
+        <v>15.0</v>
       </c>
       <c r="P39" s="1" t="inlineStr">
         <is>
           <t>S29</t>
         </is>
       </c>
-      <c r="Q39" s="1"/>
+      <c r="Q39" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -2509,7 +2571,7 @@
       </c>
       <c r="E40" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
+          <t>Vente</t>
         </is>
       </c>
       <c r="F40" s="1" t="inlineStr">
@@ -2517,18 +2579,22 @@
           <t>TOUBA</t>
         </is>
       </c>
-      <c r="G40" s="1"/>
+      <c r="G40" s="1" t="inlineStr">
+        <is>
+          <t>Saliou KONE</t>
+        </is>
+      </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior mais cereal 50g x 10 x 8 sachet</t>
+          <t>Kamlac évaporé 48x160g</t>
         </is>
       </c>
       <c r="J40" s="1" t="n">
-        <v>25.0</v>
+        <v>1.0</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>375000.0</v>
+        <v>10500.0</v>
       </c>
       <c r="L40" s="1" t="n">
         <v>0.0</v>
@@ -2538,14 +2604,18 @@
       </c>
       <c r="N40" s="1"/>
       <c r="O40" s="1" t="n">
-        <v>39.0</v>
+        <v>16.0</v>
       </c>
       <c r="P40" s="1" t="inlineStr">
         <is>
           <t>S29</t>
         </is>
       </c>
-      <c r="Q40" s="1"/>
+      <c r="Q40" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -2566,7 +2636,7 @@
       </c>
       <c r="E41" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
+          <t>Vente</t>
         </is>
       </c>
       <c r="F41" s="1" t="inlineStr">
@@ -2574,18 +2644,22 @@
           <t>TOUBA</t>
         </is>
       </c>
-      <c r="G41" s="1"/>
+      <c r="G41" s="1" t="inlineStr">
+        <is>
+          <t>Saliou KONE</t>
+        </is>
+      </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Thé 7g</t>
+          <t>Cowmilk 200gx10</t>
         </is>
       </c>
       <c r="J41" s="1" t="n">
-        <v>100.0</v>
+        <v>2.0</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>1150000.0</v>
+        <v>12000.0</v>
       </c>
       <c r="L41" s="1" t="n">
         <v>0.0</v>
@@ -2595,14 +2669,18 @@
       </c>
       <c r="N41" s="1"/>
       <c r="O41" s="1" t="n">
-        <v>40.0</v>
+        <v>17.0</v>
       </c>
       <c r="P41" s="1" t="inlineStr">
         <is>
           <t>S29</t>
         </is>
       </c>
-      <c r="Q41" s="1"/>
+      <c r="Q41" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -2623,7 +2701,7 @@
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
+          <t>Vente</t>
         </is>
       </c>
       <c r="F42" s="1" t="inlineStr">
@@ -2631,18 +2709,22 @@
           <t>TOUBA</t>
         </is>
       </c>
-      <c r="G42" s="1"/>
+      <c r="G42" s="1" t="inlineStr">
+        <is>
+          <t>Adama DABO</t>
+        </is>
+      </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>Kamlac évaporé 48x160g</t>
+          <t>Cowmilk 5kg</t>
         </is>
       </c>
       <c r="J42" s="1" t="n">
-        <v>599.0</v>
+        <v>7.0</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>6289500.0</v>
+        <v>77000.0</v>
       </c>
       <c r="L42" s="1" t="n">
         <v>0.0</v>
@@ -2652,14 +2734,1425 @@
       </c>
       <c r="N42" s="1"/>
       <c r="O42" s="1" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="P42" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q42" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F43" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G43" s="1" t="inlineStr">
+        <is>
+          <t>Adama DABO</t>
+        </is>
+      </c>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1" t="inlineStr">
+        <is>
+          <t>Cowmilk 200gx10</t>
+        </is>
+      </c>
+      <c r="J43" s="1" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K43" s="1" t="n">
+        <v>12000.0</v>
+      </c>
+      <c r="L43" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M43" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="P43" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q43" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="inlineStr">
+        <is>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F44" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G44" s="1" t="inlineStr">
+        <is>
+          <t>Saly THIOUNE (T2)</t>
+        </is>
+      </c>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1" t="inlineStr">
+        <is>
+          <t>Cowmilk 5kg</t>
+        </is>
+      </c>
+      <c r="J44" s="1" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K44" s="1" t="n">
+        <v>11000.0</v>
+      </c>
+      <c r="L44" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M44" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="P44" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q44" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E45" s="1" t="inlineStr">
+        <is>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F45" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G45" s="1" t="inlineStr">
+        <is>
+          <t>Sokhna (T2)</t>
+        </is>
+      </c>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1" t="inlineStr">
+        <is>
+          <t>Cowmilk 5kg</t>
+        </is>
+      </c>
+      <c r="J45" s="1" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K45" s="1" t="n">
+        <v>22000.0</v>
+      </c>
+      <c r="L45" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M45" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="P45" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q45" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E46" s="1" t="inlineStr">
+        <is>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F46" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G46" s="1" t="inlineStr">
+        <is>
+          <t>Sokhna (T2)</t>
+        </is>
+      </c>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1" t="inlineStr">
+        <is>
+          <t>Cowmilk 200gx10</t>
+        </is>
+      </c>
+      <c r="J46" s="1" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K46" s="1" t="n">
+        <v>6000.0</v>
+      </c>
+      <c r="L46" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M46" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N46" s="1"/>
+      <c r="O46" s="1" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="P46" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q46" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F47" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G47" s="1" t="inlineStr">
+        <is>
+          <t>Nogueye THIAME (T2)</t>
+        </is>
+      </c>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1" t="inlineStr">
+        <is>
+          <t>Cowmilk 5kg</t>
+        </is>
+      </c>
+      <c r="J47" s="1" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="K47" s="1" t="n">
+        <v>110000.0</v>
+      </c>
+      <c r="L47" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M47" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N47" s="1"/>
+      <c r="O47" s="1" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="P47" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q47" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B48" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E48" s="1" t="inlineStr">
+        <is>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F48" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G48" s="1" t="inlineStr">
+        <is>
+          <t>Coumba Touré (T2)</t>
+        </is>
+      </c>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1" t="inlineStr">
+        <is>
+          <t>Cowmilk 5kg</t>
+        </is>
+      </c>
+      <c r="J48" s="1" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="K48" s="1" t="n">
+        <v>121000.0</v>
+      </c>
+      <c r="L48" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M48" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="P48" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q48" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B49" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E49" s="1" t="inlineStr">
+        <is>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F49" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G49" s="1" t="inlineStr">
+        <is>
+          <t>Fama DIOUF</t>
+        </is>
+      </c>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1" t="inlineStr">
+        <is>
+          <t>Cowmilk 5kg</t>
+        </is>
+      </c>
+      <c r="J49" s="1" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="K49" s="1" t="n">
+        <v>55000.0</v>
+      </c>
+      <c r="L49" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M49" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N49" s="1"/>
+      <c r="O49" s="1" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="P49" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q49" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B50" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E50" s="1" t="inlineStr">
+        <is>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F50" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G50" s="1" t="inlineStr">
+        <is>
+          <t>Mariama KANE</t>
+        </is>
+      </c>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1" t="inlineStr">
+        <is>
+          <t>Cowmilk 5kg</t>
+        </is>
+      </c>
+      <c r="J50" s="1" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="K50" s="1" t="n">
+        <v>55000.0</v>
+      </c>
+      <c r="L50" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M50" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="P50" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q50" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B51" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E51" s="1" t="inlineStr">
+        <is>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F51" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G51" s="1" t="inlineStr">
+        <is>
+          <t>Mariama KANE</t>
+        </is>
+      </c>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1" t="inlineStr">
+        <is>
+          <t>Cowmilk 200gx10</t>
+        </is>
+      </c>
+      <c r="J51" s="1" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K51" s="1" t="n">
+        <v>6000.0</v>
+      </c>
+      <c r="L51" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M51" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="P51" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q51" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B52" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E52" s="1" t="inlineStr">
+        <is>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F52" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G52" s="1" t="inlineStr">
+        <is>
+          <t>Fallou SOLY (T2)</t>
+        </is>
+      </c>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1" t="inlineStr">
+        <is>
+          <t>Cowmilk 5kg</t>
+        </is>
+      </c>
+      <c r="J52" s="1" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="K52" s="1" t="n">
+        <v>165000.0</v>
+      </c>
+      <c r="L52" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M52" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N52" s="1"/>
+      <c r="O52" s="1" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="P52" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q52" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B53" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E53" s="1" t="inlineStr">
+        <is>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F53" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G53" s="1" t="inlineStr">
+        <is>
+          <t>Fallou SOLY (T2)</t>
+        </is>
+      </c>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1" t="inlineStr">
+        <is>
+          <t>Cafe au Lait 3-en-1</t>
+        </is>
+      </c>
+      <c r="J53" s="1" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K53" s="1" t="n">
+        <v>4500.0</v>
+      </c>
+      <c r="L53" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M53" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N53" s="1"/>
+      <c r="O53" s="1" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="P53" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q53" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B54" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E54" s="1" t="inlineStr">
+        <is>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F54" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G54" s="1" t="inlineStr">
+        <is>
+          <t>Mariama BA</t>
+        </is>
+      </c>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1" t="inlineStr">
+        <is>
+          <t>Cowmilk 5kg</t>
+        </is>
+      </c>
+      <c r="J54" s="1" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="K54" s="1" t="n">
+        <v>110000.0</v>
+      </c>
+      <c r="L54" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M54" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N54" s="1"/>
+      <c r="O54" s="1" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="P54" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q54" s="1" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B55" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C55" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D55" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E55" s="1" t="inlineStr">
+        <is>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F55" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1" t="inlineStr">
+        <is>
+          <t>Cafe au Lait 3-en-1</t>
+        </is>
+      </c>
+      <c r="J55" s="1" t="n">
+        <v>99.0</v>
+      </c>
+      <c r="K55" s="1" t="n">
+        <v>445500.0</v>
+      </c>
+      <c r="L55" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M55" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N55" s="1"/>
+      <c r="O55" s="1" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="P55" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q55" s="1"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E56" s="1" t="inlineStr">
+        <is>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F56" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1" t="inlineStr">
+        <is>
+          <t>Chocolat 3-en-1 30x120 pcs</t>
+        </is>
+      </c>
+      <c r="J56" s="1" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="K56" s="1" t="n">
+        <v>1100000.0</v>
+      </c>
+      <c r="L56" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M56" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N56" s="1"/>
+      <c r="O56" s="1" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="P56" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q56" s="1"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E57" s="1" t="inlineStr">
+        <is>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F57" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1" t="inlineStr">
+        <is>
+          <t>Cowmilk 200gx10</t>
+        </is>
+      </c>
+      <c r="J57" s="1" t="n">
+        <v>134.0</v>
+      </c>
+      <c r="K57" s="1" t="n">
+        <v>804000.0</v>
+      </c>
+      <c r="L57" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M57" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N57" s="1"/>
+      <c r="O57" s="1" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="P57" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q57" s="1"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D58" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E58" s="1" t="inlineStr">
+        <is>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F58" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1" t="inlineStr">
+        <is>
+          <t>Cowmilk 5kg</t>
+        </is>
+      </c>
+      <c r="J58" s="1" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="K58" s="1" t="n">
+        <v>176000.0</v>
+      </c>
+      <c r="L58" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M58" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N58" s="1"/>
+      <c r="O58" s="1" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="P58" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q58" s="1"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B59" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D59" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E59" s="1" t="inlineStr">
+        <is>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F59" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1" t="inlineStr">
+        <is>
+          <t>Jus Lido</t>
+        </is>
+      </c>
+      <c r="J59" s="1" t="n">
+        <v>200.0</v>
+      </c>
+      <c r="K59" s="1" t="n">
+        <v>2200000.0</v>
+      </c>
+      <c r="L59" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M59" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N59" s="1"/>
+      <c r="O59" s="1" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="P59" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q59" s="1"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D60" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E60" s="1" t="inlineStr">
+        <is>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F60" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1" t="inlineStr">
+        <is>
+          <t>Kamlac Junior BLE cereal 230g x 12 sachet</t>
+        </is>
+      </c>
+      <c r="J60" s="1" t="n">
+        <v>24.416666</v>
+      </c>
+      <c r="K60" s="1" t="n">
+        <v>219750.0</v>
+      </c>
+      <c r="L60" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M60" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N60" s="1"/>
+      <c r="O60" s="1" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="P60" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q60" s="1"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D61" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E61" s="1" t="inlineStr">
+        <is>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F61" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1" t="inlineStr">
+        <is>
+          <t>Kamlac Junior BLE cereal 50g x 10 x 8 sachet</t>
+        </is>
+      </c>
+      <c r="J61" s="1" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="K61" s="1" t="n">
+        <v>375000.0</v>
+      </c>
+      <c r="L61" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M61" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N61" s="1"/>
+      <c r="O61" s="1" t="n">
+        <v>37.0</v>
+      </c>
+      <c r="P61" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q61" s="1"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D62" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E62" s="1" t="inlineStr">
+        <is>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F62" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1" t="inlineStr">
+        <is>
+          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
+        </is>
+      </c>
+      <c r="J62" s="1" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="K62" s="1" t="n">
+        <v>225000.0</v>
+      </c>
+      <c r="L62" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M62" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N62" s="1"/>
+      <c r="O62" s="1" t="n">
+        <v>38.0</v>
+      </c>
+      <c r="P62" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q62" s="1"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D63" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E63" s="1" t="inlineStr">
+        <is>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F63" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1" t="inlineStr">
+        <is>
+          <t>Kamlac Junior mais cereal 50g x 10 x 8 sachet</t>
+        </is>
+      </c>
+      <c r="J63" s="1" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="K63" s="1" t="n">
+        <v>375000.0</v>
+      </c>
+      <c r="L63" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M63" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N63" s="1"/>
+      <c r="O63" s="1" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="P63" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q63" s="1"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D64" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E64" s="1" t="inlineStr">
+        <is>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F64" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1" t="inlineStr">
+        <is>
+          <t>Kamlac Thé 7g</t>
+        </is>
+      </c>
+      <c r="J64" s="1" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="K64" s="1" t="n">
+        <v>1150000.0</v>
+      </c>
+      <c r="L64" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M64" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N64" s="1"/>
+      <c r="O64" s="1" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="P64" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q64" s="1"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>46221.0</v>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>TATA 1</t>
+        </is>
+      </c>
+      <c r="D65" s="1" t="inlineStr">
+        <is>
+          <t>DJIBRIL DIOP</t>
+        </is>
+      </c>
+      <c r="E65" s="1" t="inlineStr">
+        <is>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F65" s="1" t="inlineStr">
+        <is>
+          <t>TOUBA</t>
+        </is>
+      </c>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1" t="inlineStr">
+        <is>
+          <t>Kamlac évaporé 48x160g</t>
+        </is>
+      </c>
+      <c r="J65" s="1" t="n">
+        <v>599.0</v>
+      </c>
+      <c r="K65" s="1" t="n">
+        <v>6289500.0</v>
+      </c>
+      <c r="L65" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M65" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N65" s="1"/>
+      <c r="O65" s="1" t="n">
         <v>41.0</v>
       </c>
-      <c r="P42" s="1" t="inlineStr">
-        <is>
-          <t>S29</t>
-        </is>
-      </c>
-      <c r="Q42" s="1"/>
+      <c r="P65" s="1" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="Q65" s="1"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -76,7 +76,7 @@
     <col min="8" max="8" width="9.55078125" customWidth="true"/>
     <col min="9" max="9" width="46.60546875" customWidth="true"/>
     <col min="10" max="10" width="19.4609375" customWidth="true"/>
-    <col min="11" max="11" width="9.6796875" customWidth="true"/>
+    <col min="11" max="11" width="11.515625" customWidth="true"/>
     <col min="12" max="12" width="10.53125" customWidth="true"/>
     <col min="13" max="13" width="15.3046875" customWidth="true"/>
     <col min="14" max="14" width="14.3203125" customWidth="true"/>
@@ -1501,19 +1501,21 @@
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
-          <t>Coumba Touré (T2)</t>
+          <t>Nogueye THIAME (T2)</t>
         </is>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Thé 7g</t>
+          <t>Cowmilk 5kg</t>
         </is>
       </c>
       <c r="J22" s="1" t="n">
-        <v>0.45833334</v>
-      </c>
-      <c r="K22" s="1"/>
+        <v>1.0</v>
+      </c>
+      <c r="K22" s="1" t="n">
+        <v>11000.0</v>
+      </c>
       <c r="L22" s="1" t="n">
         <v>0.0</v>
       </c>
@@ -1570,14 +1572,14 @@
       <c r="H23" s="1"/>
       <c r="I23" s="1" t="inlineStr">
         <is>
-          <t>Cowmilk 5kg</t>
+          <t>Cafe au Lait 3-en-1</t>
         </is>
       </c>
       <c r="J23" s="1" t="n">
         <v>1.0</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>11000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="L23" s="1" t="n">
         <v>0.0</v>
@@ -1635,14 +1637,14 @@
       <c r="H24" s="1"/>
       <c r="I24" s="1" t="inlineStr">
         <is>
-          <t>Cafe au Lait 3-en-1</t>
+          <t>Kamlac Thé 7g</t>
         </is>
       </c>
       <c r="J24" s="1" t="n">
-        <v>1.0</v>
+        <v>0.45833334</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>4500.0</v>
+        <v>5270.8335</v>
       </c>
       <c r="L24" s="1" t="n">
         <v>0.0</v>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B750145-9190-450F-BF98-50BD980FA9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD2109A-E271-47A1-808A-244AACFF70CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="47">
   <si>
     <t>Date</t>
   </si>
@@ -142,25 +142,25 @@
     <t>Jackline DIEDHIOU (T3)</t>
   </si>
   <si>
-    <t>Cowmilk 5kg</t>
+    <t>Stock Descente</t>
   </si>
   <si>
     <t>Cafe au Lait 3-en-1</t>
   </si>
   <si>
-    <t>Stock Lundi</t>
+    <t>Chocolat 3-en-1 30x120 pcs</t>
   </si>
   <si>
-    <t>Chocolat 3-en-1 30x120 pcs</t>
+    <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
   </si>
   <si>
     <t>Kamlac Junior mais cereal 50g x 10 x 8 sachet</t>
   </si>
   <si>
-    <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
+    <t>Cowmilk 5kg</t>
   </si>
   <si>
-    <t>Stock Descente</t>
+    <t>Stock Lundi</t>
   </si>
 </sst>
 </file>
@@ -547,25 +547,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q92"/>
+  <dimension ref="A1:Q101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.3984375" customWidth="1"/>
-    <col min="2" max="2" width="26.3984375" customWidth="1"/>
+    <col min="2" max="2" width="2.33203125" customWidth="1"/>
     <col min="3" max="3" width="8.59765625" customWidth="1"/>
     <col min="4" max="4" width="15.265625" customWidth="1"/>
     <col min="5" max="5" width="16.53125" customWidth="1"/>
     <col min="6" max="6" width="8.6640625" customWidth="1"/>
     <col min="7" max="7" width="26.6640625" customWidth="1"/>
-    <col min="8" max="8" width="9.53125" customWidth="1"/>
     <col min="9" max="9" width="46.59765625" customWidth="1"/>
-    <col min="10" max="10" width="19.46484375" customWidth="1"/>
+    <col min="10" max="10" width="13.9296875" customWidth="1"/>
     <col min="11" max="11" width="11.53125" customWidth="1"/>
-    <col min="12" max="12" width="10.53125" customWidth="1"/>
-    <col min="13" max="13" width="15.33203125" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" customWidth="1"/>
-    <col min="15" max="15" width="11.53125" customWidth="1"/>
-    <col min="16" max="16" width="18.46484375" customWidth="1"/>
+    <col min="12" max="12" width="7.19921875" customWidth="1"/>
+    <col min="13" max="13" width="2.33203125" customWidth="1"/>
+    <col min="15" max="15" width="4.796875" customWidth="1"/>
+    <col min="16" max="16" width="5" customWidth="1"/>
     <col min="17" max="17" width="8" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1947,11 +1945,9 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A29" s="2">
-        <v>46222</v>
-      </c>
-      <c r="B29" s="1">
-        <v>0</v>
-      </c>
+        <v>46223</v>
+      </c>
+      <c r="B29" s="1"/>
       <c r="C29" s="1" t="s">
         <v>17</v>
       </c>
@@ -1959,48 +1955,42 @@
         <v>18</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J29" s="1">
-        <v>2</v>
+        <v>97</v>
       </c>
       <c r="K29" s="1">
-        <v>22000</v>
+        <v>436500</v>
       </c>
       <c r="L29" s="1">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="M29" s="1">
         <v>0</v>
       </c>
       <c r="N29" s="1"/>
       <c r="O29" s="1">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="P29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q29" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q29" s="1"/>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A30" s="2">
-        <v>46222</v>
-      </c>
-      <c r="B30" s="1">
-        <v>0</v>
-      </c>
+        <v>46223</v>
+      </c>
+      <c r="B30" s="1"/>
       <c r="C30" s="1" t="s">
         <v>17</v>
       </c>
@@ -2008,23 +1998,21 @@
         <v>18</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="J30" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="K30" s="1">
-        <v>6000</v>
+        <v>1100000</v>
       </c>
       <c r="L30" s="1">
         <v>0</v>
@@ -2034,22 +2022,18 @@
       </c>
       <c r="N30" s="1"/>
       <c r="O30" s="1">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="P30" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q30" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q30" s="1"/>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A31" s="2">
-        <v>46222</v>
-      </c>
-      <c r="B31" s="1">
-        <v>0</v>
-      </c>
+        <v>46223</v>
+      </c>
+      <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
         <v>17</v>
       </c>
@@ -2057,23 +2041,21 @@
         <v>18</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="J31" s="1">
-        <v>1</v>
+        <v>116.5</v>
       </c>
       <c r="K31" s="1">
-        <v>4500</v>
+        <v>699000</v>
       </c>
       <c r="L31" s="1">
         <v>0</v>
@@ -2083,22 +2065,18 @@
       </c>
       <c r="N31" s="1"/>
       <c r="O31" s="1">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="P31" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q31" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q31" s="1"/>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A32" s="2">
-        <v>46222</v>
-      </c>
-      <c r="B32" s="1">
-        <v>0</v>
-      </c>
+        <v>46223</v>
+      </c>
+      <c r="B32" s="1"/>
       <c r="C32" s="1" t="s">
         <v>17</v>
       </c>
@@ -2106,23 +2084,21 @@
         <v>18</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J32" s="1">
-        <v>2</v>
+        <v>198.75</v>
       </c>
       <c r="K32" s="1">
-        <v>22000</v>
+        <v>2186250</v>
       </c>
       <c r="L32" s="1">
         <v>0</v>
@@ -2132,22 +2108,18 @@
       </c>
       <c r="N32" s="1"/>
       <c r="O32" s="1">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q32" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q32" s="1"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A33" s="2">
-        <v>46222</v>
-      </c>
-      <c r="B33" s="1">
-        <v>0</v>
-      </c>
+        <v>46223</v>
+      </c>
+      <c r="B33" s="1"/>
       <c r="C33" s="1" t="s">
         <v>17</v>
       </c>
@@ -2155,23 +2127,21 @@
         <v>18</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J33" s="1">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="K33" s="1">
-        <v>12000</v>
+        <v>345000</v>
       </c>
       <c r="L33" s="1">
         <v>0</v>
@@ -2181,22 +2151,18 @@
       </c>
       <c r="N33" s="1"/>
       <c r="O33" s="1">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q33" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q33" s="1"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A34" s="2">
-        <v>46222</v>
-      </c>
-      <c r="B34" s="1">
-        <v>0</v>
-      </c>
+        <v>46223</v>
+      </c>
+      <c r="B34" s="1"/>
       <c r="C34" s="1" t="s">
         <v>17</v>
       </c>
@@ -2204,23 +2170,21 @@
         <v>18</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G34" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J34" s="1">
-        <v>3</v>
+        <v>21.916665999999999</v>
       </c>
       <c r="K34" s="1">
-        <v>31500</v>
+        <v>197250</v>
       </c>
       <c r="L34" s="1">
         <v>0</v>
@@ -2230,22 +2194,18 @@
       </c>
       <c r="N34" s="1"/>
       <c r="O34" s="1">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q34" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q34" s="1"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A35" s="2">
-        <v>46222</v>
-      </c>
-      <c r="B35" s="1">
-        <v>0</v>
-      </c>
+        <v>46223</v>
+      </c>
+      <c r="B35" s="1"/>
       <c r="C35" s="1" t="s">
         <v>17</v>
       </c>
@@ -2253,23 +2213,21 @@
         <v>18</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J35" s="1">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="K35" s="1">
-        <v>9000</v>
+        <v>225000</v>
       </c>
       <c r="L35" s="1">
         <v>0</v>
@@ -2279,22 +2237,18 @@
       </c>
       <c r="N35" s="1"/>
       <c r="O35" s="1">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="P35" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q35" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q35" s="1"/>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A36" s="2">
-        <v>46222</v>
-      </c>
-      <c r="B36" s="1">
-        <v>0</v>
-      </c>
+        <v>46223</v>
+      </c>
+      <c r="B36" s="1"/>
       <c r="C36" s="1" t="s">
         <v>17</v>
       </c>
@@ -2302,23 +2256,21 @@
         <v>18</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G36" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="J36" s="1">
-        <v>0.25</v>
+        <v>25</v>
       </c>
       <c r="K36" s="1">
-        <v>2875</v>
+        <v>375000</v>
       </c>
       <c r="L36" s="1">
         <v>0</v>
@@ -2328,22 +2280,18 @@
       </c>
       <c r="N36" s="1"/>
       <c r="O36" s="1">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="P36" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q36" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q36" s="1"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A37" s="2">
-        <v>46222</v>
-      </c>
-      <c r="B37" s="1">
-        <v>0</v>
-      </c>
+        <v>46223</v>
+      </c>
+      <c r="B37" s="1"/>
       <c r="C37" s="1" t="s">
         <v>17</v>
       </c>
@@ -2351,23 +2299,21 @@
         <v>18</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G37" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J37" s="1">
-        <v>2</v>
+        <v>96.041663999999997</v>
       </c>
       <c r="K37" s="1">
-        <v>21000</v>
+        <v>1104479.1000000001</v>
       </c>
       <c r="L37" s="1">
         <v>0</v>
@@ -2377,14 +2323,12 @@
       </c>
       <c r="N37" s="1"/>
       <c r="O37" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P37" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q37" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q37" s="1"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A38" s="2">
@@ -2406,27 +2350,27 @@
         <v>20</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="J38" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K38" s="1">
-        <v>10500</v>
+        <v>22000</v>
       </c>
       <c r="L38" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="M38" s="1">
         <v>0</v>
       </c>
       <c r="N38" s="1"/>
       <c r="O38" s="1">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="P38" s="1" t="s">
         <v>23</v>
@@ -2455,17 +2399,17 @@
         <v>20</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J39" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K39" s="1">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="L39" s="1">
         <v>0</v>
@@ -2475,7 +2419,7 @@
       </c>
       <c r="N39" s="1"/>
       <c r="O39" s="1">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="P39" s="1" t="s">
         <v>23</v>
@@ -2504,17 +2448,17 @@
         <v>20</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J40" s="1">
         <v>1</v>
       </c>
       <c r="K40" s="1">
-        <v>9000</v>
+        <v>4500</v>
       </c>
       <c r="L40" s="1">
         <v>0</v>
@@ -2524,7 +2468,7 @@
       </c>
       <c r="N40" s="1"/>
       <c r="O40" s="1">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="P40" s="1" t="s">
         <v>23</v>
@@ -2553,17 +2497,17 @@
         <v>20</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="J41" s="1">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="K41" s="1">
-        <v>3000</v>
+        <v>22000</v>
       </c>
       <c r="L41" s="1">
         <v>0</v>
@@ -2573,7 +2517,7 @@
       </c>
       <c r="N41" s="1"/>
       <c r="O41" s="1">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="P41" s="1" t="s">
         <v>23</v>
@@ -2602,17 +2546,17 @@
         <v>20</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J42" s="1">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="K42" s="1">
-        <v>3000</v>
+        <v>12000</v>
       </c>
       <c r="L42" s="1">
         <v>0</v>
@@ -2622,7 +2566,7 @@
       </c>
       <c r="N42" s="1"/>
       <c r="O42" s="1">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="P42" s="1" t="s">
         <v>23</v>
@@ -2651,17 +2595,17 @@
         <v>20</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="J43" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K43" s="1">
-        <v>55000</v>
+        <v>31500</v>
       </c>
       <c r="L43" s="1">
         <v>0</v>
@@ -2671,7 +2615,7 @@
       </c>
       <c r="N43" s="1"/>
       <c r="O43" s="1">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>23</v>
@@ -2700,17 +2644,17 @@
         <v>20</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J44" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K44" s="1">
-        <v>55000</v>
+        <v>9000</v>
       </c>
       <c r="L44" s="1">
         <v>0</v>
@@ -2720,7 +2664,7 @@
       </c>
       <c r="N44" s="1"/>
       <c r="O44" s="1">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="P44" s="1" t="s">
         <v>23</v>
@@ -2749,7 +2693,7 @@
         <v>20</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1" t="s">
@@ -2769,7 +2713,7 @@
       </c>
       <c r="N45" s="1"/>
       <c r="O45" s="1">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="P45" s="1" t="s">
         <v>23</v>
@@ -2798,17 +2742,17 @@
         <v>20</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J46" s="1">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="K46" s="1">
-        <v>2875</v>
+        <v>21000</v>
       </c>
       <c r="L46" s="1">
         <v>0</v>
@@ -2818,7 +2762,7 @@
       </c>
       <c r="N46" s="1"/>
       <c r="O46" s="1">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="P46" s="1" t="s">
         <v>23</v>
@@ -2847,17 +2791,17 @@
         <v>20</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="J47" s="1">
         <v>1</v>
       </c>
       <c r="K47" s="1">
-        <v>11000</v>
+        <v>10500</v>
       </c>
       <c r="L47" s="1">
         <v>0</v>
@@ -2867,7 +2811,7 @@
       </c>
       <c r="N47" s="1"/>
       <c r="O47" s="1">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="P47" s="1" t="s">
         <v>23</v>
@@ -2896,17 +2840,17 @@
         <v>20</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J48" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K48" s="1">
-        <v>10500</v>
+        <v>3000</v>
       </c>
       <c r="L48" s="1">
         <v>0</v>
@@ -2916,7 +2860,7 @@
       </c>
       <c r="N48" s="1"/>
       <c r="O48" s="1">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="P48" s="1" t="s">
         <v>23</v>
@@ -2945,17 +2889,17 @@
         <v>20</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J49" s="1">
         <v>1</v>
       </c>
       <c r="K49" s="1">
-        <v>11000</v>
+        <v>9000</v>
       </c>
       <c r="L49" s="1">
         <v>0</v>
@@ -2965,7 +2909,7 @@
       </c>
       <c r="N49" s="1"/>
       <c r="O49" s="1">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="P49" s="1" t="s">
         <v>23</v>
@@ -2994,17 +2938,17 @@
         <v>20</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="J50" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K50" s="1">
-        <v>4500</v>
+        <v>3000</v>
       </c>
       <c r="L50" s="1">
         <v>0</v>
@@ -3014,7 +2958,7 @@
       </c>
       <c r="N50" s="1"/>
       <c r="O50" s="1">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="P50" s="1" t="s">
         <v>23</v>
@@ -3043,17 +2987,17 @@
         <v>20</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J51" s="1">
-        <v>0.45833333999999998</v>
+        <v>0.5</v>
       </c>
       <c r="K51" s="1">
-        <v>5270.8334999999997</v>
+        <v>3000</v>
       </c>
       <c r="L51" s="1">
         <v>0</v>
@@ -3063,7 +3007,7 @@
       </c>
       <c r="N51" s="1"/>
       <c r="O51" s="1">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="P51" s="1" t="s">
         <v>23</v>
@@ -3074,7 +3018,7 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A52" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B52" s="1">
         <v>0</v>
@@ -3086,21 +3030,23 @@
         <v>18</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G52" s="1"/>
+      <c r="G52" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="J52" s="1">
-        <v>600</v>
+        <v>5</v>
       </c>
       <c r="K52" s="1">
-        <v>6300000</v>
+        <v>55000</v>
       </c>
       <c r="L52" s="1">
         <v>0</v>
@@ -3110,16 +3056,18 @@
       </c>
       <c r="N52" s="1"/>
       <c r="O52" s="1">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="P52" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q52" s="1"/>
+      <c r="Q52" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A53" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B53" s="1">
         <v>0</v>
@@ -3131,21 +3079,23 @@
         <v>18</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G53" s="1"/>
+      <c r="G53" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J53" s="1">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="K53" s="1">
-        <v>2200000</v>
+        <v>55000</v>
       </c>
       <c r="L53" s="1">
         <v>0</v>
@@ -3155,16 +3105,18 @@
       </c>
       <c r="N53" s="1"/>
       <c r="O53" s="1">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="P53" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q53" s="1"/>
+      <c r="Q53" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A54" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B54" s="1">
         <v>0</v>
@@ -3176,21 +3128,23 @@
         <v>18</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G54" s="1"/>
+      <c r="G54" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="J54" s="1">
-        <v>100</v>
+        <v>0.25</v>
       </c>
       <c r="K54" s="1">
-        <v>450000</v>
+        <v>2875</v>
       </c>
       <c r="L54" s="1">
         <v>0</v>
@@ -3200,16 +3154,18 @@
       </c>
       <c r="N54" s="1"/>
       <c r="O54" s="1">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="P54" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q54" s="1"/>
+      <c r="Q54" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A55" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B55" s="1">
         <v>0</v>
@@ -3221,21 +3177,23 @@
         <v>18</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G55" s="1"/>
+      <c r="G55" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="J55" s="1">
-        <v>100</v>
+        <v>0.25</v>
       </c>
       <c r="K55" s="1">
-        <v>1100000</v>
+        <v>2875</v>
       </c>
       <c r="L55" s="1">
         <v>0</v>
@@ -3245,16 +3203,18 @@
       </c>
       <c r="N55" s="1"/>
       <c r="O55" s="1">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="P55" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q55" s="1"/>
+      <c r="Q55" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A56" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B56" s="1">
         <v>0</v>
@@ -3266,21 +3226,23 @@
         <v>18</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G56" s="1"/>
+      <c r="G56" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="J56" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K56" s="1">
-        <v>1150000</v>
+        <v>11000</v>
       </c>
       <c r="L56" s="1">
         <v>0</v>
@@ -3290,16 +3252,18 @@
       </c>
       <c r="N56" s="1"/>
       <c r="O56" s="1">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="P56" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q56" s="1"/>
+      <c r="Q56" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A57" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B57" s="1">
         <v>0</v>
@@ -3311,21 +3275,23 @@
         <v>18</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G57" s="1"/>
+      <c r="G57" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="J57" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K57" s="1">
-        <v>1100000</v>
+        <v>10500</v>
       </c>
       <c r="L57" s="1">
         <v>0</v>
@@ -3335,16 +3301,18 @@
       </c>
       <c r="N57" s="1"/>
       <c r="O57" s="1">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="P57" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q57" s="1"/>
+      <c r="Q57" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A58" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B58" s="1">
         <v>0</v>
@@ -3356,21 +3324,23 @@
         <v>18</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G58" s="1"/>
+      <c r="G58" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="J58" s="1">
-        <v>140</v>
+        <v>1</v>
       </c>
       <c r="K58" s="1">
-        <v>840000</v>
+        <v>11000</v>
       </c>
       <c r="L58" s="1">
         <v>0</v>
@@ -3380,16 +3350,18 @@
       </c>
       <c r="N58" s="1"/>
       <c r="O58" s="1">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="P58" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q58" s="1"/>
+      <c r="Q58" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A59" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B59" s="1">
         <v>0</v>
@@ -3401,21 +3373,23 @@
         <v>18</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G59" s="1"/>
+      <c r="G59" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="J59" s="1">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K59" s="1">
-        <v>375000</v>
+        <v>4500</v>
       </c>
       <c r="L59" s="1">
         <v>0</v>
@@ -3425,16 +3399,18 @@
       </c>
       <c r="N59" s="1"/>
       <c r="O59" s="1">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="P59" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q59" s="1"/>
+      <c r="Q59" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A60" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B60" s="1">
         <v>0</v>
@@ -3446,21 +3422,23 @@
         <v>18</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G60" s="1"/>
+      <c r="G60" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="J60" s="1">
-        <v>25</v>
+        <v>0.45833333999999998</v>
       </c>
       <c r="K60" s="1">
-        <v>375000</v>
+        <v>5270.8334999999997</v>
       </c>
       <c r="L60" s="1">
         <v>0</v>
@@ -3470,12 +3448,14 @@
       </c>
       <c r="N60" s="1"/>
       <c r="O60" s="1">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="P60" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q60" s="1"/>
+      <c r="Q60" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A61" s="2">
@@ -3491,7 +3471,7 @@
         <v>18</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>20</v>
@@ -3499,13 +3479,13 @@
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="J61" s="1">
-        <v>25</v>
+        <v>600</v>
       </c>
       <c r="K61" s="1">
-        <v>225000</v>
+        <v>6300000</v>
       </c>
       <c r="L61" s="1">
         <v>0</v>
@@ -3515,7 +3495,7 @@
       </c>
       <c r="N61" s="1"/>
       <c r="O61" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P61" s="1" t="s">
         <v>23</v>
@@ -3536,7 +3516,7 @@
         <v>18</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>20</v>
@@ -3544,13 +3524,13 @@
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J62" s="1">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="K62" s="1">
-        <v>225000</v>
+        <v>2200000</v>
       </c>
       <c r="L62" s="1">
         <v>0</v>
@@ -3560,7 +3540,7 @@
       </c>
       <c r="N62" s="1"/>
       <c r="O62" s="1">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="P62" s="1" t="s">
         <v>23</v>
@@ -3581,40 +3561,36 @@
         <v>18</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G63" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="G63" s="1"/>
       <c r="H63" s="1"/>
       <c r="I63" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J63" s="1">
-        <v>0.58333330000000005</v>
+        <v>100</v>
       </c>
       <c r="K63" s="1">
-        <v>5250</v>
+        <v>450000</v>
       </c>
       <c r="L63" s="1">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="M63" s="1">
         <v>0</v>
       </c>
       <c r="N63" s="1"/>
       <c r="O63" s="1">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="P63" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q63" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q63" s="1"/>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A64" s="2">
@@ -3630,23 +3606,21 @@
         <v>18</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G64" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="G64" s="1"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J64" s="1">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="K64" s="1">
-        <v>66000</v>
+        <v>1100000</v>
       </c>
       <c r="L64" s="1">
         <v>0</v>
@@ -3656,14 +3630,12 @@
       </c>
       <c r="N64" s="1"/>
       <c r="O64" s="1">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="P64" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q64" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q64" s="1"/>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A65" s="2">
@@ -3679,23 +3651,21 @@
         <v>18</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G65" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="G65" s="1"/>
       <c r="H65" s="1"/>
       <c r="I65" s="1" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="J65" s="1">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="K65" s="1">
-        <v>66000</v>
+        <v>1150000</v>
       </c>
       <c r="L65" s="1">
         <v>0</v>
@@ -3705,14 +3675,12 @@
       </c>
       <c r="N65" s="1"/>
       <c r="O65" s="1">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="P65" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q65" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q65" s="1"/>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A66" s="2">
@@ -3728,23 +3696,21 @@
         <v>18</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G66" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J66" s="1">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="K66" s="1">
-        <v>66000</v>
+        <v>1100000</v>
       </c>
       <c r="L66" s="1">
         <v>0</v>
@@ -3754,14 +3720,12 @@
       </c>
       <c r="N66" s="1"/>
       <c r="O66" s="1">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="P66" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q66" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q66" s="1"/>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A67" s="2">
@@ -3777,23 +3741,21 @@
         <v>18</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G67" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="G67" s="1"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J67" s="1">
-        <v>1</v>
+        <v>140</v>
       </c>
       <c r="K67" s="1">
-        <v>10500</v>
+        <v>840000</v>
       </c>
       <c r="L67" s="1">
         <v>0</v>
@@ -3803,14 +3765,12 @@
       </c>
       <c r="N67" s="1"/>
       <c r="O67" s="1">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="P67" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q67" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q67" s="1"/>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A68" s="2">
@@ -3826,23 +3786,21 @@
         <v>18</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G68" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="G68" s="1"/>
       <c r="H68" s="1"/>
       <c r="I68" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J68" s="1">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="K68" s="1">
-        <v>12000</v>
+        <v>375000</v>
       </c>
       <c r="L68" s="1">
         <v>0</v>
@@ -3852,14 +3810,12 @@
       </c>
       <c r="N68" s="1"/>
       <c r="O68" s="1">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="P68" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q68" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q68" s="1"/>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A69" s="2">
@@ -3875,23 +3831,21 @@
         <v>18</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G69" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="G69" s="1"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J69" s="1">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="K69" s="1">
-        <v>77000</v>
+        <v>375000</v>
       </c>
       <c r="L69" s="1">
         <v>0</v>
@@ -3901,14 +3855,12 @@
       </c>
       <c r="N69" s="1"/>
       <c r="O69" s="1">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="P69" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q69" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q69" s="1"/>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A70" s="2">
@@ -3924,23 +3876,21 @@
         <v>18</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G70" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="G70" s="1"/>
       <c r="H70" s="1"/>
       <c r="I70" s="1" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="J70" s="1">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="K70" s="1">
-        <v>12000</v>
+        <v>225000</v>
       </c>
       <c r="L70" s="1">
         <v>0</v>
@@ -3950,14 +3900,12 @@
       </c>
       <c r="N70" s="1"/>
       <c r="O70" s="1">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="P70" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q70" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q70" s="1"/>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A71" s="2">
@@ -3973,23 +3921,21 @@
         <v>18</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G71" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="G71" s="1"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J71" s="1">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="K71" s="1">
-        <v>11000</v>
+        <v>225000</v>
       </c>
       <c r="L71" s="1">
         <v>0</v>
@@ -3999,14 +3945,12 @@
       </c>
       <c r="N71" s="1"/>
       <c r="O71" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="P71" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q71" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q71" s="1"/>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A72" s="2">
@@ -4028,27 +3972,27 @@
         <v>20</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H72" s="1"/>
       <c r="I72" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J72" s="1">
-        <v>2</v>
+        <v>0.58333330000000005</v>
       </c>
       <c r="K72" s="1">
-        <v>22000</v>
+        <v>5250</v>
       </c>
       <c r="L72" s="1">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="M72" s="1">
         <v>0</v>
       </c>
       <c r="N72" s="1"/>
       <c r="O72" s="1">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="P72" s="1" t="s">
         <v>23</v>
@@ -4077,17 +4021,17 @@
         <v>20</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="J73" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K73" s="1">
-        <v>6000</v>
+        <v>66000</v>
       </c>
       <c r="L73" s="1">
         <v>0</v>
@@ -4097,7 +4041,7 @@
       </c>
       <c r="N73" s="1"/>
       <c r="O73" s="1">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="P73" s="1" t="s">
         <v>23</v>
@@ -4126,17 +4070,17 @@
         <v>20</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J74" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K74" s="1">
-        <v>110000</v>
+        <v>66000</v>
       </c>
       <c r="L74" s="1">
         <v>0</v>
@@ -4146,7 +4090,7 @@
       </c>
       <c r="N74" s="1"/>
       <c r="O74" s="1">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="P74" s="1" t="s">
         <v>23</v>
@@ -4175,17 +4119,17 @@
         <v>20</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J75" s="1">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K75" s="1">
-        <v>121000</v>
+        <v>66000</v>
       </c>
       <c r="L75" s="1">
         <v>0</v>
@@ -4195,7 +4139,7 @@
       </c>
       <c r="N75" s="1"/>
       <c r="O75" s="1">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="P75" s="1" t="s">
         <v>23</v>
@@ -4224,17 +4168,17 @@
         <v>20</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="J76" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K76" s="1">
-        <v>55000</v>
+        <v>10500</v>
       </c>
       <c r="L76" s="1">
         <v>0</v>
@@ -4244,7 +4188,7 @@
       </c>
       <c r="N76" s="1"/>
       <c r="O76" s="1">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="P76" s="1" t="s">
         <v>23</v>
@@ -4273,17 +4217,17 @@
         <v>20</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="J77" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K77" s="1">
-        <v>55000</v>
+        <v>12000</v>
       </c>
       <c r="L77" s="1">
         <v>0</v>
@@ -4293,7 +4237,7 @@
       </c>
       <c r="N77" s="1"/>
       <c r="O77" s="1">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="P77" s="1" t="s">
         <v>23</v>
@@ -4322,17 +4266,17 @@
         <v>20</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H78" s="1"/>
       <c r="I78" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="J78" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K78" s="1">
-        <v>6000</v>
+        <v>77000</v>
       </c>
       <c r="L78" s="1">
         <v>0</v>
@@ -4342,7 +4286,7 @@
       </c>
       <c r="N78" s="1"/>
       <c r="O78" s="1">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="P78" s="1" t="s">
         <v>23</v>
@@ -4371,17 +4315,17 @@
         <v>20</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="J79" s="1">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="K79" s="1">
-        <v>165000</v>
+        <v>12000</v>
       </c>
       <c r="L79" s="1">
         <v>0</v>
@@ -4391,7 +4335,7 @@
       </c>
       <c r="N79" s="1"/>
       <c r="O79" s="1">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="P79" s="1" t="s">
         <v>23</v>
@@ -4420,17 +4364,17 @@
         <v>20</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H80" s="1"/>
       <c r="I80" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J80" s="1">
         <v>1</v>
       </c>
       <c r="K80" s="1">
-        <v>4500</v>
+        <v>11000</v>
       </c>
       <c r="L80" s="1">
         <v>0</v>
@@ -4440,7 +4384,7 @@
       </c>
       <c r="N80" s="1"/>
       <c r="O80" s="1">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="P80" s="1" t="s">
         <v>23</v>
@@ -4469,17 +4413,17 @@
         <v>20</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H81" s="1"/>
       <c r="I81" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J81" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K81" s="1">
-        <v>110000</v>
+        <v>22000</v>
       </c>
       <c r="L81" s="1">
         <v>0</v>
@@ -4489,7 +4433,7 @@
       </c>
       <c r="N81" s="1"/>
       <c r="O81" s="1">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="P81" s="1" t="s">
         <v>23</v>
@@ -4512,21 +4456,23 @@
         <v>18</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G82" s="1"/>
+      <c r="G82" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="H82" s="1"/>
       <c r="I82" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="J82" s="1">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="K82" s="1">
-        <v>445500</v>
+        <v>6000</v>
       </c>
       <c r="L82" s="1">
         <v>0</v>
@@ -4536,12 +4482,14 @@
       </c>
       <c r="N82" s="1"/>
       <c r="O82" s="1">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="P82" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q82" s="1"/>
+      <c r="Q82" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A83" s="2">
@@ -4557,21 +4505,23 @@
         <v>18</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G83" s="1"/>
+      <c r="G83" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="H83" s="1"/>
       <c r="I83" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J83" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K83" s="1">
-        <v>1100000</v>
+        <v>110000</v>
       </c>
       <c r="L83" s="1">
         <v>0</v>
@@ -4581,12 +4531,14 @@
       </c>
       <c r="N83" s="1"/>
       <c r="O83" s="1">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="P83" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q83" s="1"/>
+      <c r="Q83" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A84" s="2">
@@ -4602,21 +4554,23 @@
         <v>18</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G84" s="1"/>
+      <c r="G84" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="H84" s="1"/>
       <c r="I84" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="J84" s="1">
-        <v>134</v>
+        <v>11</v>
       </c>
       <c r="K84" s="1">
-        <v>804000</v>
+        <v>121000</v>
       </c>
       <c r="L84" s="1">
         <v>0</v>
@@ -4626,12 +4580,14 @@
       </c>
       <c r="N84" s="1"/>
       <c r="O84" s="1">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="P84" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q84" s="1"/>
+      <c r="Q84" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A85" s="2">
@@ -4647,21 +4603,23 @@
         <v>18</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G85" s="1"/>
+      <c r="G85" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="H85" s="1"/>
       <c r="I85" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J85" s="1">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="K85" s="1">
-        <v>176000</v>
+        <v>55000</v>
       </c>
       <c r="L85" s="1">
         <v>0</v>
@@ -4671,12 +4629,14 @@
       </c>
       <c r="N85" s="1"/>
       <c r="O85" s="1">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="P85" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q85" s="1"/>
+      <c r="Q85" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A86" s="2">
@@ -4692,21 +4652,23 @@
         <v>18</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G86" s="1"/>
+      <c r="G86" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="H86" s="1"/>
       <c r="I86" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J86" s="1">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="K86" s="1">
-        <v>2200000</v>
+        <v>55000</v>
       </c>
       <c r="L86" s="1">
         <v>0</v>
@@ -4716,12 +4678,14 @@
       </c>
       <c r="N86" s="1"/>
       <c r="O86" s="1">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="P86" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q86" s="1"/>
+      <c r="Q86" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A87" s="2">
@@ -4737,21 +4701,23 @@
         <v>18</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G87" s="1"/>
+      <c r="G87" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="H87" s="1"/>
       <c r="I87" s="1" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="J87" s="1">
-        <v>24.416665999999999</v>
+        <v>1</v>
       </c>
       <c r="K87" s="1">
-        <v>219750</v>
+        <v>6000</v>
       </c>
       <c r="L87" s="1">
         <v>0</v>
@@ -4761,12 +4727,14 @@
       </c>
       <c r="N87" s="1"/>
       <c r="O87" s="1">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="P87" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q87" s="1"/>
+      <c r="Q87" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A88" s="2">
@@ -4782,21 +4750,23 @@
         <v>18</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G88" s="1"/>
+      <c r="G88" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="H88" s="1"/>
       <c r="I88" s="1" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="J88" s="1">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K88" s="1">
-        <v>375000</v>
+        <v>165000</v>
       </c>
       <c r="L88" s="1">
         <v>0</v>
@@ -4806,12 +4776,14 @@
       </c>
       <c r="N88" s="1"/>
       <c r="O88" s="1">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="P88" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q88" s="1"/>
+      <c r="Q88" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A89" s="2">
@@ -4827,21 +4799,23 @@
         <v>18</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G89" s="1"/>
+      <c r="G89" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="J89" s="1">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K89" s="1">
-        <v>225000</v>
+        <v>4500</v>
       </c>
       <c r="L89" s="1">
         <v>0</v>
@@ -4851,12 +4825,14 @@
       </c>
       <c r="N89" s="1"/>
       <c r="O89" s="1">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="P89" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q89" s="1"/>
+      <c r="Q89" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A90" s="2">
@@ -4872,21 +4848,23 @@
         <v>18</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G90" s="1"/>
+      <c r="G90" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="H90" s="1"/>
       <c r="I90" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J90" s="1">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="K90" s="1">
-        <v>375000</v>
+        <v>110000</v>
       </c>
       <c r="L90" s="1">
         <v>0</v>
@@ -4896,12 +4874,14 @@
       </c>
       <c r="N90" s="1"/>
       <c r="O90" s="1">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="P90" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q90" s="1"/>
+      <c r="Q90" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A91" s="2">
@@ -4917,7 +4897,7 @@
         <v>18</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>20</v>
@@ -4925,13 +4905,13 @@
       <c r="G91" s="1"/>
       <c r="H91" s="1"/>
       <c r="I91" s="1" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="J91" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K91" s="1">
-        <v>1150000</v>
+        <v>445500</v>
       </c>
       <c r="L91" s="1">
         <v>0</v>
@@ -4941,7 +4921,7 @@
       </c>
       <c r="N91" s="1"/>
       <c r="O91" s="1">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="P91" s="1" t="s">
         <v>23</v>
@@ -4962,7 +4942,7 @@
         <v>18</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>20</v>
@@ -4970,13 +4950,13 @@
       <c r="G92" s="1"/>
       <c r="H92" s="1"/>
       <c r="I92" s="1" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="J92" s="1">
-        <v>599</v>
+        <v>100</v>
       </c>
       <c r="K92" s="1">
-        <v>6289500</v>
+        <v>1100000</v>
       </c>
       <c r="L92" s="1">
         <v>0</v>
@@ -4986,12 +4966,417 @@
       </c>
       <c r="N92" s="1"/>
       <c r="O92" s="1">
+        <v>32</v>
+      </c>
+      <c r="P92" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q92" s="1"/>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A93" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B93" s="1">
+        <v>0</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J93" s="1">
+        <v>134</v>
+      </c>
+      <c r="K93" s="1">
+        <v>804000</v>
+      </c>
+      <c r="L93" s="1">
+        <v>0</v>
+      </c>
+      <c r="M93" s="1">
+        <v>0</v>
+      </c>
+      <c r="N93" s="1"/>
+      <c r="O93" s="1">
+        <v>33</v>
+      </c>
+      <c r="P93" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q93" s="1"/>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A94" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B94" s="1">
+        <v>0</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G94" s="1"/>
+      <c r="H94" s="1"/>
+      <c r="I94" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J94" s="1">
+        <v>16</v>
+      </c>
+      <c r="K94" s="1">
+        <v>176000</v>
+      </c>
+      <c r="L94" s="1">
+        <v>0</v>
+      </c>
+      <c r="M94" s="1">
+        <v>0</v>
+      </c>
+      <c r="N94" s="1"/>
+      <c r="O94" s="1">
+        <v>34</v>
+      </c>
+      <c r="P94" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q94" s="1"/>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A95" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B95" s="1">
+        <v>0</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1"/>
+      <c r="I95" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J95" s="1">
+        <v>200</v>
+      </c>
+      <c r="K95" s="1">
+        <v>2200000</v>
+      </c>
+      <c r="L95" s="1">
+        <v>0</v>
+      </c>
+      <c r="M95" s="1">
+        <v>0</v>
+      </c>
+      <c r="N95" s="1"/>
+      <c r="O95" s="1">
+        <v>35</v>
+      </c>
+      <c r="P95" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q95" s="1"/>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A96" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B96" s="1">
+        <v>0</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G96" s="1"/>
+      <c r="H96" s="1"/>
+      <c r="I96" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J96" s="1">
+        <v>24.416665999999999</v>
+      </c>
+      <c r="K96" s="1">
+        <v>219750</v>
+      </c>
+      <c r="L96" s="1">
+        <v>0</v>
+      </c>
+      <c r="M96" s="1">
+        <v>0</v>
+      </c>
+      <c r="N96" s="1"/>
+      <c r="O96" s="1">
+        <v>36</v>
+      </c>
+      <c r="P96" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q96" s="1"/>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A97" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B97" s="1">
+        <v>0</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G97" s="1"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J97" s="1">
+        <v>25</v>
+      </c>
+      <c r="K97" s="1">
+        <v>375000</v>
+      </c>
+      <c r="L97" s="1">
+        <v>0</v>
+      </c>
+      <c r="M97" s="1">
+        <v>0</v>
+      </c>
+      <c r="N97" s="1"/>
+      <c r="O97" s="1">
+        <v>37</v>
+      </c>
+      <c r="P97" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q97" s="1"/>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A98" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B98" s="1">
+        <v>0</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G98" s="1"/>
+      <c r="H98" s="1"/>
+      <c r="I98" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J98" s="1">
+        <v>25</v>
+      </c>
+      <c r="K98" s="1">
+        <v>225000</v>
+      </c>
+      <c r="L98" s="1">
+        <v>0</v>
+      </c>
+      <c r="M98" s="1">
+        <v>0</v>
+      </c>
+      <c r="N98" s="1"/>
+      <c r="O98" s="1">
+        <v>38</v>
+      </c>
+      <c r="P98" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q98" s="1"/>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A99" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B99" s="1">
+        <v>0</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G99" s="1"/>
+      <c r="H99" s="1"/>
+      <c r="I99" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J99" s="1">
+        <v>25</v>
+      </c>
+      <c r="K99" s="1">
+        <v>375000</v>
+      </c>
+      <c r="L99" s="1">
+        <v>0</v>
+      </c>
+      <c r="M99" s="1">
+        <v>0</v>
+      </c>
+      <c r="N99" s="1"/>
+      <c r="O99" s="1">
+        <v>39</v>
+      </c>
+      <c r="P99" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q99" s="1"/>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A100" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B100" s="1">
+        <v>0</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J100" s="1">
+        <v>100</v>
+      </c>
+      <c r="K100" s="1">
+        <v>1150000</v>
+      </c>
+      <c r="L100" s="1">
+        <v>0</v>
+      </c>
+      <c r="M100" s="1">
+        <v>0</v>
+      </c>
+      <c r="N100" s="1"/>
+      <c r="O100" s="1">
+        <v>40</v>
+      </c>
+      <c r="P100" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q100" s="1"/>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A101" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B101" s="1">
+        <v>0</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G101" s="1"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J101" s="1">
+        <v>599</v>
+      </c>
+      <c r="K101" s="1">
+        <v>6289500</v>
+      </c>
+      <c r="L101" s="1">
+        <v>0</v>
+      </c>
+      <c r="M101" s="1">
+        <v>0</v>
+      </c>
+      <c r="N101" s="1"/>
+      <c r="O101" s="1">
         <v>41</v>
       </c>
-      <c r="P92" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q92" s="1"/>
+      <c r="P101" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q101" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD2109A-E271-47A1-808A-244AACFF70CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7D609EC-8164-48CF-8B01-9E47BC057E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="47">
   <si>
     <t>Date</t>
   </si>
@@ -79,28 +79,52 @@
     <t>DJIBRIL DIOP</t>
   </si>
   <si>
-    <t>Vente</t>
+    <t>Stock Descente</t>
   </si>
   <si>
     <t>TOUBA</t>
   </si>
   <si>
-    <t>Saliou KONE</t>
+    <t>Cafe au Lait 3-en-1</t>
+  </si>
+  <si>
+    <t>S30</t>
+  </si>
+  <si>
+    <t>Chocolat 3-en-1 30x120 pcs</t>
+  </si>
+  <si>
+    <t>Cowmilk 200gx10</t>
+  </si>
+  <si>
+    <t>Jus Lido</t>
+  </si>
+  <si>
+    <t>Kamlac Junior BLE cereal 50g x 10 x 8 sachet</t>
+  </si>
+  <si>
+    <t>Kamlac Junior BLE cereal 230g x 12 sachet</t>
+  </si>
+  <si>
+    <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
+  </si>
+  <si>
+    <t>Kamlac Junior mais cereal 50g x 10 x 8 sachet</t>
+  </si>
+  <si>
+    <t>Kamlac Thé 7g</t>
   </si>
   <si>
     <t>Kamlac évaporé 48x160g</t>
   </si>
   <si>
-    <t>S30</t>
+    <t>Vente</t>
   </si>
   <si>
-    <t>Cowmilk 200gx10</t>
+    <t>Saliou KONE</t>
   </si>
   <si>
     <t>Adama DABO</t>
-  </si>
-  <si>
-    <t>Kamlac Thé 7g</t>
   </si>
   <si>
     <t>Fallou SOLY (T2)</t>
@@ -124,37 +148,13 @@
     <t>Coumba Touré (T2)</t>
   </si>
   <si>
-    <t>Kamlac Junior BLE cereal 50g x 10 x 8 sachet</t>
-  </si>
-  <si>
-    <t>Jus Lido</t>
-  </si>
-  <si>
     <t>Nogueye THIAME (T2)</t>
   </si>
   <si>
     <t>Ndeye Fatou GUEYE (T3)</t>
   </si>
   <si>
-    <t>Kamlac Junior BLE cereal 230g x 12 sachet</t>
-  </si>
-  <si>
     <t>Jackline DIEDHIOU (T3)</t>
-  </si>
-  <si>
-    <t>Stock Descente</t>
-  </si>
-  <si>
-    <t>Cafe au Lait 3-en-1</t>
-  </si>
-  <si>
-    <t>Chocolat 3-en-1 30x120 pcs</t>
-  </si>
-  <si>
-    <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
-  </si>
-  <si>
-    <t>Kamlac Junior mais cereal 50g x 10 x 8 sachet</t>
   </si>
   <si>
     <t>Cowmilk 5kg</t>
@@ -547,7 +547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q101"/>
+  <dimension ref="A1:Q102"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.3984375" customWidth="1"/>
@@ -639,35 +639,31 @@
       <c r="F2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J2" s="1">
-        <v>3</v>
+        <v>97</v>
       </c>
       <c r="K2" s="1">
-        <v>27000</v>
+        <v>436500</v>
       </c>
       <c r="L2" s="1">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="M2" s="1">
         <v>0</v>
       </c>
       <c r="N2" s="1"/>
       <c r="O2" s="1">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="Q2" s="1"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
@@ -688,18 +684,16 @@
       <c r="F3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J3" s="1">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="K3" s="1">
-        <v>12000</v>
+        <v>1100000</v>
       </c>
       <c r="L3" s="1">
         <v>0</v>
@@ -709,14 +703,12 @@
       </c>
       <c r="N3" s="1"/>
       <c r="O3" s="1">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="Q3" s="1"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
@@ -737,18 +729,16 @@
       <c r="F4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J4" s="1">
-        <v>2</v>
+        <v>116.5</v>
       </c>
       <c r="K4" s="1">
-        <v>18000</v>
+        <v>699000</v>
       </c>
       <c r="L4" s="1">
         <v>0</v>
@@ -758,14 +748,12 @@
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="Q4" s="1"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
@@ -786,18 +774,16 @@
       <c r="F5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J5" s="1">
-        <v>1.625</v>
+        <v>198.75</v>
       </c>
       <c r="K5" s="1">
-        <v>18687.5</v>
+        <v>2186250</v>
       </c>
       <c r="L5" s="1">
         <v>0</v>
@@ -807,14 +793,12 @@
       </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="Q5" s="1"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
@@ -835,18 +819,16 @@
       <c r="F6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J6" s="1">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="K6" s="1">
-        <v>12000</v>
+        <v>345000</v>
       </c>
       <c r="L6" s="1">
         <v>0</v>
@@ -856,14 +838,12 @@
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="Q6" s="1"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
@@ -884,18 +864,16 @@
       <c r="F7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J7" s="1">
-        <v>1</v>
+        <v>21.916665999999999</v>
       </c>
       <c r="K7" s="1">
-        <v>6000</v>
+        <v>197250</v>
       </c>
       <c r="L7" s="1">
         <v>0</v>
@@ -905,14 +883,12 @@
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="Q7" s="1"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
@@ -933,18 +909,16 @@
       <c r="F8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J8" s="1">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="K8" s="1">
-        <v>9000</v>
+        <v>225000</v>
       </c>
       <c r="L8" s="1">
         <v>0</v>
@@ -954,14 +928,12 @@
       </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="Q8" s="1"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
@@ -982,18 +954,16 @@
       <c r="F9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J9" s="1">
-        <v>4.1666667999999997E-2</v>
+        <v>25</v>
       </c>
       <c r="K9" s="1">
-        <v>479.16665999999998</v>
+        <v>375000</v>
       </c>
       <c r="L9" s="1">
         <v>0</v>
@@ -1003,14 +973,12 @@
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="Q9" s="1"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
@@ -1031,18 +999,16 @@
       <c r="F10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J10" s="1">
-        <v>1</v>
+        <v>96.041663999999997</v>
       </c>
       <c r="K10" s="1">
-        <v>9000</v>
+        <v>1104479.1000000001</v>
       </c>
       <c r="L10" s="1">
         <v>0</v>
@@ -1052,14 +1018,12 @@
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="Q10" s="1"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A11" s="2">
@@ -1080,18 +1044,16 @@
       <c r="F11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J11" s="1">
-        <v>2</v>
+        <v>568</v>
       </c>
       <c r="K11" s="1">
-        <v>18000</v>
+        <v>5112000</v>
       </c>
       <c r="L11" s="1">
         <v>0</v>
@@ -1101,14 +1063,12 @@
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A12" s="2">
@@ -1124,36 +1084,36 @@
         <v>18</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J12" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K12" s="1">
-        <v>9000</v>
+        <v>27000</v>
       </c>
       <c r="L12" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="M12" s="1">
         <v>0</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q12" s="1" t="s">
         <v>16</v>
@@ -1173,23 +1133,23 @@
         <v>18</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J13" s="1">
         <v>2</v>
       </c>
       <c r="K13" s="1">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="L13" s="1">
         <v>0</v>
@@ -1199,10 +1159,10 @@
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q13" s="1" t="s">
         <v>16</v>
@@ -1222,23 +1182,23 @@
         <v>18</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J14" s="1">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="K14" s="1">
-        <v>4500</v>
+        <v>18000</v>
       </c>
       <c r="L14" s="1">
         <v>0</v>
@@ -1248,10 +1208,10 @@
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q14" s="1" t="s">
         <v>16</v>
@@ -1271,23 +1231,23 @@
         <v>18</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J15" s="1">
-        <v>0.5</v>
+        <v>1.625</v>
       </c>
       <c r="K15" s="1">
-        <v>4500</v>
+        <v>18687.5</v>
       </c>
       <c r="L15" s="1">
         <v>0</v>
@@ -1297,10 +1257,10 @@
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q15" s="1" t="s">
         <v>16</v>
@@ -1320,23 +1280,23 @@
         <v>18</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J16" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" s="1">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="L16" s="1">
         <v>0</v>
@@ -1346,10 +1306,10 @@
       </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q16" s="1" t="s">
         <v>16</v>
@@ -1369,23 +1329,23 @@
         <v>18</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J17" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K17" s="1">
-        <v>27000</v>
+        <v>6000</v>
       </c>
       <c r="L17" s="1">
         <v>0</v>
@@ -1395,10 +1355,10 @@
       </c>
       <c r="N17" s="1"/>
       <c r="O17" s="1">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q17" s="1" t="s">
         <v>16</v>
@@ -1418,23 +1378,23 @@
         <v>18</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J18" s="1">
         <v>1</v>
       </c>
       <c r="K18" s="1">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="L18" s="1">
         <v>0</v>
@@ -1444,10 +1404,10 @@
       </c>
       <c r="N18" s="1"/>
       <c r="O18" s="1">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q18" s="1" t="s">
         <v>16</v>
@@ -1467,23 +1427,23 @@
         <v>18</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J19" s="1">
-        <v>0.16666666999999999</v>
+        <v>4.1666667999999997E-2</v>
       </c>
       <c r="K19" s="1">
-        <v>1833.3334</v>
+        <v>479.16665999999998</v>
       </c>
       <c r="L19" s="1">
         <v>0</v>
@@ -1493,10 +1453,10 @@
       </c>
       <c r="N19" s="1"/>
       <c r="O19" s="1">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q19" s="1" t="s">
         <v>16</v>
@@ -1516,7 +1476,7 @@
         <v>18</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>20</v>
@@ -1526,7 +1486,7 @@
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J20" s="1">
         <v>1</v>
@@ -1542,10 +1502,10 @@
       </c>
       <c r="N20" s="1"/>
       <c r="O20" s="1">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q20" s="1" t="s">
         <v>16</v>
@@ -1565,23 +1525,23 @@
         <v>18</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J21" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K21" s="1">
-        <v>36000</v>
+        <v>18000</v>
       </c>
       <c r="L21" s="1">
         <v>0</v>
@@ -1591,10 +1551,10 @@
       </c>
       <c r="N21" s="1"/>
       <c r="O21" s="1">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q21" s="1" t="s">
         <v>16</v>
@@ -1614,7 +1574,7 @@
         <v>18</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>20</v>
@@ -1624,13 +1584,13 @@
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J22" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K22" s="1">
-        <v>18000</v>
+        <v>9000</v>
       </c>
       <c r="L22" s="1">
         <v>0</v>
@@ -1640,10 +1600,10 @@
       </c>
       <c r="N22" s="1"/>
       <c r="O22" s="1">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q22" s="1" t="s">
         <v>16</v>
@@ -1663,23 +1623,23 @@
         <v>18</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J23" s="1">
-        <v>1.0833333999999999</v>
+        <v>2</v>
       </c>
       <c r="K23" s="1">
-        <v>12458.333000000001</v>
+        <v>18000</v>
       </c>
       <c r="L23" s="1">
         <v>0</v>
@@ -1689,10 +1649,10 @@
       </c>
       <c r="N23" s="1"/>
       <c r="O23" s="1">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q23" s="1" t="s">
         <v>16</v>
@@ -1712,17 +1672,17 @@
         <v>18</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="J24" s="1">
         <v>0.5</v>
@@ -1738,10 +1698,10 @@
       </c>
       <c r="N24" s="1"/>
       <c r="O24" s="1">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q24" s="1" t="s">
         <v>16</v>
@@ -1761,23 +1721,23 @@
         <v>18</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J25" s="1">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="K25" s="1">
-        <v>27000</v>
+        <v>4500</v>
       </c>
       <c r="L25" s="1">
         <v>0</v>
@@ -1787,10 +1747,10 @@
       </c>
       <c r="N25" s="1"/>
       <c r="O25" s="1">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q25" s="1" t="s">
         <v>16</v>
@@ -1810,23 +1770,23 @@
         <v>18</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="J26" s="1">
-        <v>1.0833333999999999</v>
+        <v>1</v>
       </c>
       <c r="K26" s="1">
-        <v>11916.666999999999</v>
+        <v>15000</v>
       </c>
       <c r="L26" s="1">
         <v>0</v>
@@ -1836,10 +1796,10 @@
       </c>
       <c r="N26" s="1"/>
       <c r="O26" s="1">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q26" s="1" t="s">
         <v>16</v>
@@ -1859,23 +1819,23 @@
         <v>18</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J27" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K27" s="1">
-        <v>24000</v>
+        <v>27000</v>
       </c>
       <c r="L27" s="1">
         <v>0</v>
@@ -1885,10 +1845,10 @@
       </c>
       <c r="N27" s="1"/>
       <c r="O27" s="1">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q27" s="1" t="s">
         <v>16</v>
@@ -1908,23 +1868,23 @@
         <v>18</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J28" s="1">
         <v>1</v>
       </c>
       <c r="K28" s="1">
-        <v>15000</v>
+        <v>6000</v>
       </c>
       <c r="L28" s="1">
         <v>0</v>
@@ -1934,10 +1894,10 @@
       </c>
       <c r="N28" s="1"/>
       <c r="O28" s="1">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q28" s="1" t="s">
         <v>16</v>
@@ -1947,7 +1907,9 @@
       <c r="A29" s="2">
         <v>46223</v>
       </c>
-      <c r="B29" s="1"/>
+      <c r="B29" s="1">
+        <v>0</v>
+      </c>
       <c r="C29" s="1" t="s">
         <v>17</v>
       </c>
@@ -1955,21 +1917,23 @@
         <v>18</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="1"/>
+      <c r="G29" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="J29" s="1">
-        <v>97</v>
+        <v>0.16666666999999999</v>
       </c>
       <c r="K29" s="1">
-        <v>436500</v>
+        <v>1833.3334</v>
       </c>
       <c r="L29" s="1">
         <v>0</v>
@@ -1979,18 +1943,22 @@
       </c>
       <c r="N29" s="1"/>
       <c r="O29" s="1">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q29" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="Q29" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A30" s="2">
         <v>46223</v>
       </c>
-      <c r="B30" s="1"/>
+      <c r="B30" s="1">
+        <v>0</v>
+      </c>
       <c r="C30" s="1" t="s">
         <v>17</v>
       </c>
@@ -1998,21 +1966,23 @@
         <v>18</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="1"/>
+      <c r="G30" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="J30" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K30" s="1">
-        <v>1100000</v>
+        <v>9000</v>
       </c>
       <c r="L30" s="1">
         <v>0</v>
@@ -2022,18 +1992,22 @@
       </c>
       <c r="N30" s="1"/>
       <c r="O30" s="1">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q30" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="Q30" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A31" s="2">
         <v>46223</v>
       </c>
-      <c r="B31" s="1"/>
+      <c r="B31" s="1">
+        <v>0</v>
+      </c>
       <c r="C31" s="1" t="s">
         <v>17</v>
       </c>
@@ -2041,21 +2015,23 @@
         <v>18</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="1"/>
+      <c r="G31" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J31" s="1">
-        <v>116.5</v>
+        <v>4</v>
       </c>
       <c r="K31" s="1">
-        <v>699000</v>
+        <v>36000</v>
       </c>
       <c r="L31" s="1">
         <v>0</v>
@@ -2065,18 +2041,22 @@
       </c>
       <c r="N31" s="1"/>
       <c r="O31" s="1">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q31" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A32" s="2">
         <v>46223</v>
       </c>
-      <c r="B32" s="1"/>
+      <c r="B32" s="1">
+        <v>0</v>
+      </c>
       <c r="C32" s="1" t="s">
         <v>17</v>
       </c>
@@ -2084,21 +2064,23 @@
         <v>18</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G32" s="1"/>
+      <c r="G32" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="J32" s="1">
-        <v>198.75</v>
+        <v>3</v>
       </c>
       <c r="K32" s="1">
-        <v>2186250</v>
+        <v>18000</v>
       </c>
       <c r="L32" s="1">
         <v>0</v>
@@ -2108,18 +2090,22 @@
       </c>
       <c r="N32" s="1"/>
       <c r="O32" s="1">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q32" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A33" s="2">
         <v>46223</v>
       </c>
-      <c r="B33" s="1"/>
+      <c r="B33" s="1">
+        <v>0</v>
+      </c>
       <c r="C33" s="1" t="s">
         <v>17</v>
       </c>
@@ -2127,21 +2113,23 @@
         <v>18</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="1"/>
+      <c r="G33" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J33" s="1">
-        <v>23</v>
+        <v>1.0833333999999999</v>
       </c>
       <c r="K33" s="1">
-        <v>345000</v>
+        <v>12458.333000000001</v>
       </c>
       <c r="L33" s="1">
         <v>0</v>
@@ -2151,18 +2139,22 @@
       </c>
       <c r="N33" s="1"/>
       <c r="O33" s="1">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q33" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A34" s="2">
         <v>46223</v>
       </c>
-      <c r="B34" s="1"/>
+      <c r="B34" s="1">
+        <v>0</v>
+      </c>
       <c r="C34" s="1" t="s">
         <v>17</v>
       </c>
@@ -2170,21 +2162,23 @@
         <v>18</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G34" s="1"/>
+      <c r="G34" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="J34" s="1">
-        <v>21.916665999999999</v>
+        <v>0.5</v>
       </c>
       <c r="K34" s="1">
-        <v>197250</v>
+        <v>4500</v>
       </c>
       <c r="L34" s="1">
         <v>0</v>
@@ -2194,18 +2188,22 @@
       </c>
       <c r="N34" s="1"/>
       <c r="O34" s="1">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q34" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A35" s="2">
         <v>46223</v>
       </c>
-      <c r="B35" s="1"/>
+      <c r="B35" s="1">
+        <v>0</v>
+      </c>
       <c r="C35" s="1" t="s">
         <v>17</v>
       </c>
@@ -2213,21 +2211,23 @@
         <v>18</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G35" s="1"/>
+      <c r="G35" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="J35" s="1">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="K35" s="1">
-        <v>225000</v>
+        <v>27000</v>
       </c>
       <c r="L35" s="1">
         <v>0</v>
@@ -2237,18 +2237,22 @@
       </c>
       <c r="N35" s="1"/>
       <c r="O35" s="1">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q35" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="Q35" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A36" s="2">
         <v>46223</v>
       </c>
-      <c r="B36" s="1"/>
+      <c r="B36" s="1">
+        <v>0</v>
+      </c>
       <c r="C36" s="1" t="s">
         <v>17</v>
       </c>
@@ -2256,21 +2260,23 @@
         <v>18</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G36" s="1"/>
+      <c r="G36" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="J36" s="1">
-        <v>25</v>
+        <v>1.0833333999999999</v>
       </c>
       <c r="K36" s="1">
-        <v>375000</v>
+        <v>11916.666999999999</v>
       </c>
       <c r="L36" s="1">
         <v>0</v>
@@ -2280,18 +2286,22 @@
       </c>
       <c r="N36" s="1"/>
       <c r="O36" s="1">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q36" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A37" s="2">
         <v>46223</v>
       </c>
-      <c r="B37" s="1"/>
+      <c r="B37" s="1">
+        <v>0</v>
+      </c>
       <c r="C37" s="1" t="s">
         <v>17</v>
       </c>
@@ -2299,21 +2309,23 @@
         <v>18</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G37" s="1"/>
+      <c r="G37" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J37" s="1">
-        <v>96.041663999999997</v>
+        <v>4</v>
       </c>
       <c r="K37" s="1">
-        <v>1104479.1000000001</v>
+        <v>24000</v>
       </c>
       <c r="L37" s="1">
         <v>0</v>
@@ -2323,16 +2335,18 @@
       </c>
       <c r="N37" s="1"/>
       <c r="O37" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q37" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A38" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B38" s="1">
         <v>0</v>
@@ -2344,36 +2358,36 @@
         <v>18</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="J38" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K38" s="1">
-        <v>22000</v>
+        <v>15000</v>
       </c>
       <c r="L38" s="1">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="M38" s="1">
         <v>0</v>
       </c>
       <c r="N38" s="1"/>
       <c r="O38" s="1">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q38" s="1" t="s">
         <v>16</v>
@@ -2393,36 +2407,36 @@
         <v>18</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="J39" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K39" s="1">
-        <v>6000</v>
+        <v>22000</v>
       </c>
       <c r="L39" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="M39" s="1">
         <v>0</v>
       </c>
       <c r="N39" s="1"/>
       <c r="O39" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q39" s="1" t="s">
         <v>16</v>
@@ -2442,23 +2456,23 @@
         <v>18</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="J40" s="1">
         <v>1</v>
       </c>
       <c r="K40" s="1">
-        <v>4500</v>
+        <v>6000</v>
       </c>
       <c r="L40" s="1">
         <v>0</v>
@@ -2468,10 +2482,10 @@
       </c>
       <c r="N40" s="1"/>
       <c r="O40" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q40" s="1" t="s">
         <v>16</v>
@@ -2491,23 +2505,23 @@
         <v>18</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="J41" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K41" s="1">
-        <v>22000</v>
+        <v>4500</v>
       </c>
       <c r="L41" s="1">
         <v>0</v>
@@ -2517,10 +2531,10 @@
       </c>
       <c r="N41" s="1"/>
       <c r="O41" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q41" s="1" t="s">
         <v>16</v>
@@ -2540,23 +2554,23 @@
         <v>18</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="J42" s="1">
         <v>2</v>
       </c>
       <c r="K42" s="1">
-        <v>12000</v>
+        <v>22000</v>
       </c>
       <c r="L42" s="1">
         <v>0</v>
@@ -2566,10 +2580,10 @@
       </c>
       <c r="N42" s="1"/>
       <c r="O42" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q42" s="1" t="s">
         <v>16</v>
@@ -2589,23 +2603,23 @@
         <v>18</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J43" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K43" s="1">
-        <v>31500</v>
+        <v>12000</v>
       </c>
       <c r="L43" s="1">
         <v>0</v>
@@ -2615,10 +2629,10 @@
       </c>
       <c r="N43" s="1"/>
       <c r="O43" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q43" s="1" t="s">
         <v>16</v>
@@ -2638,23 +2652,23 @@
         <v>18</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="J44" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K44" s="1">
-        <v>9000</v>
+        <v>31500</v>
       </c>
       <c r="L44" s="1">
         <v>0</v>
@@ -2664,10 +2678,10 @@
       </c>
       <c r="N44" s="1"/>
       <c r="O44" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q44" s="1" t="s">
         <v>16</v>
@@ -2687,23 +2701,23 @@
         <v>18</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J45" s="1">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="K45" s="1">
-        <v>2875</v>
+        <v>9000</v>
       </c>
       <c r="L45" s="1">
         <v>0</v>
@@ -2713,10 +2727,10 @@
       </c>
       <c r="N45" s="1"/>
       <c r="O45" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q45" s="1" t="s">
         <v>16</v>
@@ -2736,23 +2750,23 @@
         <v>18</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J46" s="1">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="K46" s="1">
-        <v>21000</v>
+        <v>2875</v>
       </c>
       <c r="L46" s="1">
         <v>0</v>
@@ -2762,10 +2776,10 @@
       </c>
       <c r="N46" s="1"/>
       <c r="O46" s="1">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q46" s="1" t="s">
         <v>16</v>
@@ -2785,23 +2799,23 @@
         <v>18</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J47" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K47" s="1">
-        <v>10500</v>
+        <v>21000</v>
       </c>
       <c r="L47" s="1">
         <v>0</v>
@@ -2811,10 +2825,10 @@
       </c>
       <c r="N47" s="1"/>
       <c r="O47" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q47" s="1" t="s">
         <v>16</v>
@@ -2834,23 +2848,23 @@
         <v>18</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J48" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K48" s="1">
-        <v>3000</v>
+        <v>10500</v>
       </c>
       <c r="L48" s="1">
         <v>0</v>
@@ -2860,10 +2874,10 @@
       </c>
       <c r="N48" s="1"/>
       <c r="O48" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q48" s="1" t="s">
         <v>16</v>
@@ -2883,23 +2897,23 @@
         <v>18</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="J49" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K49" s="1">
-        <v>9000</v>
+        <v>3000</v>
       </c>
       <c r="L49" s="1">
         <v>0</v>
@@ -2909,10 +2923,10 @@
       </c>
       <c r="N49" s="1"/>
       <c r="O49" s="1">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q49" s="1" t="s">
         <v>16</v>
@@ -2932,23 +2946,23 @@
         <v>18</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J50" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K50" s="1">
-        <v>3000</v>
+        <v>9000</v>
       </c>
       <c r="L50" s="1">
         <v>0</v>
@@ -2958,10 +2972,10 @@
       </c>
       <c r="N50" s="1"/>
       <c r="O50" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q50" s="1" t="s">
         <v>16</v>
@@ -2981,13 +2995,13 @@
         <v>18</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1" t="s">
@@ -3007,10 +3021,10 @@
       </c>
       <c r="N51" s="1"/>
       <c r="O51" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q51" s="1" t="s">
         <v>16</v>
@@ -3030,23 +3044,23 @@
         <v>18</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="J52" s="1">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="K52" s="1">
-        <v>55000</v>
+        <v>3000</v>
       </c>
       <c r="L52" s="1">
         <v>0</v>
@@ -3056,10 +3070,10 @@
       </c>
       <c r="N52" s="1"/>
       <c r="O52" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q52" s="1" t="s">
         <v>16</v>
@@ -3079,13 +3093,13 @@
         <v>18</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1" t="s">
@@ -3105,10 +3119,10 @@
       </c>
       <c r="N53" s="1"/>
       <c r="O53" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q53" s="1" t="s">
         <v>16</v>
@@ -3128,23 +3142,23 @@
         <v>18</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="J54" s="1">
-        <v>0.25</v>
+        <v>5</v>
       </c>
       <c r="K54" s="1">
-        <v>2875</v>
+        <v>55000</v>
       </c>
       <c r="L54" s="1">
         <v>0</v>
@@ -3154,10 +3168,10 @@
       </c>
       <c r="N54" s="1"/>
       <c r="O54" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q54" s="1" t="s">
         <v>16</v>
@@ -3177,17 +3191,17 @@
         <v>18</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J55" s="1">
         <v>0.25</v>
@@ -3203,10 +3217,10 @@
       </c>
       <c r="N55" s="1"/>
       <c r="O55" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q55" s="1" t="s">
         <v>16</v>
@@ -3226,23 +3240,23 @@
         <v>18</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="J56" s="1">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K56" s="1">
-        <v>11000</v>
+        <v>2875</v>
       </c>
       <c r="L56" s="1">
         <v>0</v>
@@ -3252,10 +3266,10 @@
       </c>
       <c r="N56" s="1"/>
       <c r="O56" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q56" s="1" t="s">
         <v>16</v>
@@ -3275,23 +3289,23 @@
         <v>18</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="J57" s="1">
         <v>1</v>
       </c>
       <c r="K57" s="1">
-        <v>10500</v>
+        <v>11000</v>
       </c>
       <c r="L57" s="1">
         <v>0</v>
@@ -3301,10 +3315,10 @@
       </c>
       <c r="N57" s="1"/>
       <c r="O57" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q57" s="1" t="s">
         <v>16</v>
@@ -3324,23 +3338,23 @@
         <v>18</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="J58" s="1">
         <v>1</v>
       </c>
       <c r="K58" s="1">
-        <v>11000</v>
+        <v>10500</v>
       </c>
       <c r="L58" s="1">
         <v>0</v>
@@ -3350,10 +3364,10 @@
       </c>
       <c r="N58" s="1"/>
       <c r="O58" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q58" s="1" t="s">
         <v>16</v>
@@ -3373,23 +3387,23 @@
         <v>18</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J59" s="1">
         <v>1</v>
       </c>
       <c r="K59" s="1">
-        <v>4500</v>
+        <v>11000</v>
       </c>
       <c r="L59" s="1">
         <v>0</v>
@@ -3399,10 +3413,10 @@
       </c>
       <c r="N59" s="1"/>
       <c r="O59" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q59" s="1" t="s">
         <v>16</v>
@@ -3422,23 +3436,23 @@
         <v>18</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J60" s="1">
-        <v>0.45833333999999998</v>
+        <v>1</v>
       </c>
       <c r="K60" s="1">
-        <v>5270.8334999999997</v>
+        <v>4500</v>
       </c>
       <c r="L60" s="1">
         <v>0</v>
@@ -3448,10 +3462,10 @@
       </c>
       <c r="N60" s="1"/>
       <c r="O60" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q60" s="1" t="s">
         <v>16</v>
@@ -3459,7 +3473,7 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A61" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B61" s="1">
         <v>0</v>
@@ -3471,21 +3485,23 @@
         <v>18</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G61" s="1"/>
+      <c r="G61" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J61" s="1">
-        <v>600</v>
+        <v>0.45833333999999998</v>
       </c>
       <c r="K61" s="1">
-        <v>6300000</v>
+        <v>5270.8334999999997</v>
       </c>
       <c r="L61" s="1">
         <v>0</v>
@@ -3495,12 +3511,14 @@
       </c>
       <c r="N61" s="1"/>
       <c r="O61" s="1">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q61" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="Q61" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A62" s="2">
@@ -3524,13 +3542,13 @@
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J62" s="1">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="K62" s="1">
-        <v>2200000</v>
+        <v>6300000</v>
       </c>
       <c r="L62" s="1">
         <v>0</v>
@@ -3540,10 +3558,10 @@
       </c>
       <c r="N62" s="1"/>
       <c r="O62" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P62" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q62" s="1"/>
     </row>
@@ -3569,13 +3587,13 @@
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
       <c r="I63" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="J63" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K63" s="1">
-        <v>450000</v>
+        <v>2200000</v>
       </c>
       <c r="L63" s="1">
         <v>0</v>
@@ -3585,10 +3603,10 @@
       </c>
       <c r="N63" s="1"/>
       <c r="O63" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P63" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q63" s="1"/>
     </row>
@@ -3614,13 +3632,13 @@
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="J64" s="1">
         <v>100</v>
       </c>
       <c r="K64" s="1">
-        <v>1100000</v>
+        <v>450000</v>
       </c>
       <c r="L64" s="1">
         <v>0</v>
@@ -3630,10 +3648,10 @@
       </c>
       <c r="N64" s="1"/>
       <c r="O64" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P64" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q64" s="1"/>
     </row>
@@ -3659,13 +3677,13 @@
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
       <c r="I65" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J65" s="1">
         <v>100</v>
       </c>
       <c r="K65" s="1">
-        <v>1150000</v>
+        <v>1100000</v>
       </c>
       <c r="L65" s="1">
         <v>0</v>
@@ -3675,10 +3693,10 @@
       </c>
       <c r="N65" s="1"/>
       <c r="O65" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P65" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q65" s="1"/>
     </row>
@@ -3704,13 +3722,13 @@
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="J66" s="1">
         <v>100</v>
       </c>
       <c r="K66" s="1">
-        <v>1100000</v>
+        <v>1150000</v>
       </c>
       <c r="L66" s="1">
         <v>0</v>
@@ -3720,10 +3738,10 @@
       </c>
       <c r="N66" s="1"/>
       <c r="O66" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P66" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q66" s="1"/>
     </row>
@@ -3749,13 +3767,13 @@
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="J67" s="1">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="K67" s="1">
-        <v>840000</v>
+        <v>1100000</v>
       </c>
       <c r="L67" s="1">
         <v>0</v>
@@ -3765,10 +3783,10 @@
       </c>
       <c r="N67" s="1"/>
       <c r="O67" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P67" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q67" s="1"/>
     </row>
@@ -3794,13 +3812,13 @@
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
       <c r="I68" s="1" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J68" s="1">
-        <v>25</v>
+        <v>140</v>
       </c>
       <c r="K68" s="1">
-        <v>375000</v>
+        <v>840000</v>
       </c>
       <c r="L68" s="1">
         <v>0</v>
@@ -3810,10 +3828,10 @@
       </c>
       <c r="N68" s="1"/>
       <c r="O68" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P68" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q68" s="1"/>
     </row>
@@ -3839,7 +3857,7 @@
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="J69" s="1">
         <v>25</v>
@@ -3855,10 +3873,10 @@
       </c>
       <c r="N69" s="1"/>
       <c r="O69" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P69" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q69" s="1"/>
     </row>
@@ -3884,13 +3902,13 @@
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
       <c r="I70" s="1" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="J70" s="1">
         <v>25</v>
       </c>
       <c r="K70" s="1">
-        <v>225000</v>
+        <v>375000</v>
       </c>
       <c r="L70" s="1">
         <v>0</v>
@@ -3900,10 +3918,10 @@
       </c>
       <c r="N70" s="1"/>
       <c r="O70" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P70" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q70" s="1"/>
     </row>
@@ -3929,7 +3947,7 @@
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="J71" s="1">
         <v>25</v>
@@ -3945,10 +3963,10 @@
       </c>
       <c r="N71" s="1"/>
       <c r="O71" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P71" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q71" s="1"/>
     </row>
@@ -3966,40 +3984,36 @@
         <v>18</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G72" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="G72" s="1"/>
       <c r="H72" s="1"/>
       <c r="I72" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="J72" s="1">
-        <v>0.58333330000000005</v>
+        <v>25</v>
       </c>
       <c r="K72" s="1">
-        <v>5250</v>
+        <v>225000</v>
       </c>
       <c r="L72" s="1">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="M72" s="1">
         <v>0</v>
       </c>
       <c r="N72" s="1"/>
       <c r="O72" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P72" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q72" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="Q72" s="1"/>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A73" s="2">
@@ -4015,36 +4029,36 @@
         <v>18</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="J73" s="1">
-        <v>6</v>
+        <v>0.58333330000000005</v>
       </c>
       <c r="K73" s="1">
-        <v>66000</v>
+        <v>5250</v>
       </c>
       <c r="L73" s="1">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="M73" s="1">
         <v>0</v>
       </c>
       <c r="N73" s="1"/>
       <c r="O73" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P73" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q73" s="1" t="s">
         <v>16</v>
@@ -4064,13 +4078,13 @@
         <v>18</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1" t="s">
@@ -4090,10 +4104,10 @@
       </c>
       <c r="N74" s="1"/>
       <c r="O74" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P74" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q74" s="1" t="s">
         <v>16</v>
@@ -4113,13 +4127,13 @@
         <v>18</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1" t="s">
@@ -4139,10 +4153,10 @@
       </c>
       <c r="N75" s="1"/>
       <c r="O75" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P75" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q75" s="1" t="s">
         <v>16</v>
@@ -4162,23 +4176,23 @@
         <v>18</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="J76" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K76" s="1">
-        <v>10500</v>
+        <v>66000</v>
       </c>
       <c r="L76" s="1">
         <v>0</v>
@@ -4188,10 +4202,10 @@
       </c>
       <c r="N76" s="1"/>
       <c r="O76" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P76" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q76" s="1" t="s">
         <v>16</v>
@@ -4211,23 +4225,23 @@
         <v>18</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J77" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K77" s="1">
-        <v>12000</v>
+        <v>10500</v>
       </c>
       <c r="L77" s="1">
         <v>0</v>
@@ -4237,10 +4251,10 @@
       </c>
       <c r="N77" s="1"/>
       <c r="O77" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P77" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q77" s="1" t="s">
         <v>16</v>
@@ -4260,23 +4274,23 @@
         <v>18</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H78" s="1"/>
       <c r="I78" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="J78" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K78" s="1">
-        <v>77000</v>
+        <v>12000</v>
       </c>
       <c r="L78" s="1">
         <v>0</v>
@@ -4286,10 +4300,10 @@
       </c>
       <c r="N78" s="1"/>
       <c r="O78" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P78" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q78" s="1" t="s">
         <v>16</v>
@@ -4309,23 +4323,23 @@
         <v>18</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="J79" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K79" s="1">
-        <v>12000</v>
+        <v>77000</v>
       </c>
       <c r="L79" s="1">
         <v>0</v>
@@ -4335,10 +4349,10 @@
       </c>
       <c r="N79" s="1"/>
       <c r="O79" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P79" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q79" s="1" t="s">
         <v>16</v>
@@ -4358,23 +4372,23 @@
         <v>18</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H80" s="1"/>
       <c r="I80" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="J80" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K80" s="1">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="L80" s="1">
         <v>0</v>
@@ -4384,10 +4398,10 @@
       </c>
       <c r="N80" s="1"/>
       <c r="O80" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P80" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q80" s="1" t="s">
         <v>16</v>
@@ -4407,23 +4421,23 @@
         <v>18</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H81" s="1"/>
       <c r="I81" s="1" t="s">
         <v>45</v>
       </c>
       <c r="J81" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K81" s="1">
-        <v>22000</v>
+        <v>11000</v>
       </c>
       <c r="L81" s="1">
         <v>0</v>
@@ -4433,10 +4447,10 @@
       </c>
       <c r="N81" s="1"/>
       <c r="O81" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P81" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q81" s="1" t="s">
         <v>16</v>
@@ -4456,23 +4470,23 @@
         <v>18</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H82" s="1"/>
       <c r="I82" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="J82" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K82" s="1">
-        <v>6000</v>
+        <v>22000</v>
       </c>
       <c r="L82" s="1">
         <v>0</v>
@@ -4482,10 +4496,10 @@
       </c>
       <c r="N82" s="1"/>
       <c r="O82" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P82" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q82" s="1" t="s">
         <v>16</v>
@@ -4505,23 +4519,23 @@
         <v>18</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H83" s="1"/>
       <c r="I83" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="J83" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K83" s="1">
-        <v>110000</v>
+        <v>6000</v>
       </c>
       <c r="L83" s="1">
         <v>0</v>
@@ -4531,10 +4545,10 @@
       </c>
       <c r="N83" s="1"/>
       <c r="O83" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P83" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q83" s="1" t="s">
         <v>16</v>
@@ -4554,23 +4568,23 @@
         <v>18</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H84" s="1"/>
       <c r="I84" s="1" t="s">
         <v>45</v>
       </c>
       <c r="J84" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K84" s="1">
-        <v>121000</v>
+        <v>110000</v>
       </c>
       <c r="L84" s="1">
         <v>0</v>
@@ -4580,10 +4594,10 @@
       </c>
       <c r="N84" s="1"/>
       <c r="O84" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P84" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q84" s="1" t="s">
         <v>16</v>
@@ -4603,23 +4617,23 @@
         <v>18</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="H85" s="1"/>
       <c r="I85" s="1" t="s">
         <v>45</v>
       </c>
       <c r="J85" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K85" s="1">
-        <v>55000</v>
+        <v>121000</v>
       </c>
       <c r="L85" s="1">
         <v>0</v>
@@ -4629,10 +4643,10 @@
       </c>
       <c r="N85" s="1"/>
       <c r="O85" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P85" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q85" s="1" t="s">
         <v>16</v>
@@ -4652,13 +4666,13 @@
         <v>18</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H86" s="1"/>
       <c r="I86" s="1" t="s">
@@ -4678,10 +4692,10 @@
       </c>
       <c r="N86" s="1"/>
       <c r="O86" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P86" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q86" s="1" t="s">
         <v>16</v>
@@ -4701,23 +4715,23 @@
         <v>18</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H87" s="1"/>
       <c r="I87" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="J87" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K87" s="1">
-        <v>6000</v>
+        <v>55000</v>
       </c>
       <c r="L87" s="1">
         <v>0</v>
@@ -4727,10 +4741,10 @@
       </c>
       <c r="N87" s="1"/>
       <c r="O87" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P87" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q87" s="1" t="s">
         <v>16</v>
@@ -4750,23 +4764,23 @@
         <v>18</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="H88" s="1"/>
       <c r="I88" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="J88" s="1">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K88" s="1">
-        <v>165000</v>
+        <v>6000</v>
       </c>
       <c r="L88" s="1">
         <v>0</v>
@@ -4776,10 +4790,10 @@
       </c>
       <c r="N88" s="1"/>
       <c r="O88" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P88" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q88" s="1" t="s">
         <v>16</v>
@@ -4799,23 +4813,23 @@
         <v>18</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J89" s="1">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K89" s="1">
-        <v>4500</v>
+        <v>165000</v>
       </c>
       <c r="L89" s="1">
         <v>0</v>
@@ -4825,10 +4839,10 @@
       </c>
       <c r="N89" s="1"/>
       <c r="O89" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P89" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q89" s="1" t="s">
         <v>16</v>
@@ -4848,23 +4862,23 @@
         <v>18</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H90" s="1"/>
       <c r="I90" s="1" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="J90" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K90" s="1">
-        <v>110000</v>
+        <v>4500</v>
       </c>
       <c r="L90" s="1">
         <v>0</v>
@@ -4874,10 +4888,10 @@
       </c>
       <c r="N90" s="1"/>
       <c r="O90" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P90" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q90" s="1" t="s">
         <v>16</v>
@@ -4897,21 +4911,23 @@
         <v>18</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G91" s="1"/>
+      <c r="G91" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="H91" s="1"/>
       <c r="I91" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J91" s="1">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="K91" s="1">
-        <v>445500</v>
+        <v>110000</v>
       </c>
       <c r="L91" s="1">
         <v>0</v>
@@ -4921,12 +4937,14 @@
       </c>
       <c r="N91" s="1"/>
       <c r="O91" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P91" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q91" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="Q91" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A92" s="2">
@@ -4942,7 +4960,7 @@
         <v>18</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>20</v>
@@ -4950,13 +4968,13 @@
       <c r="G92" s="1"/>
       <c r="H92" s="1"/>
       <c r="I92" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="J92" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K92" s="1">
-        <v>1100000</v>
+        <v>445500</v>
       </c>
       <c r="L92" s="1">
         <v>0</v>
@@ -4966,10 +4984,10 @@
       </c>
       <c r="N92" s="1"/>
       <c r="O92" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P92" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q92" s="1"/>
     </row>
@@ -4987,7 +5005,7 @@
         <v>18</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>20</v>
@@ -4995,13 +5013,13 @@
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
       <c r="I93" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J93" s="1">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="K93" s="1">
-        <v>804000</v>
+        <v>1100000</v>
       </c>
       <c r="L93" s="1">
         <v>0</v>
@@ -5011,10 +5029,10 @@
       </c>
       <c r="N93" s="1"/>
       <c r="O93" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P93" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q93" s="1"/>
     </row>
@@ -5032,7 +5050,7 @@
         <v>18</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>20</v>
@@ -5040,13 +5058,13 @@
       <c r="G94" s="1"/>
       <c r="H94" s="1"/>
       <c r="I94" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="J94" s="1">
-        <v>16</v>
+        <v>134</v>
       </c>
       <c r="K94" s="1">
-        <v>176000</v>
+        <v>804000</v>
       </c>
       <c r="L94" s="1">
         <v>0</v>
@@ -5056,10 +5074,10 @@
       </c>
       <c r="N94" s="1"/>
       <c r="O94" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P94" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q94" s="1"/>
     </row>
@@ -5077,7 +5095,7 @@
         <v>18</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>20</v>
@@ -5085,13 +5103,13 @@
       <c r="G95" s="1"/>
       <c r="H95" s="1"/>
       <c r="I95" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J95" s="1">
-        <v>200</v>
+        <v>16</v>
       </c>
       <c r="K95" s="1">
-        <v>2200000</v>
+        <v>176000</v>
       </c>
       <c r="L95" s="1">
         <v>0</v>
@@ -5101,10 +5119,10 @@
       </c>
       <c r="N95" s="1"/>
       <c r="O95" s="1">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P95" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q95" s="1"/>
     </row>
@@ -5122,7 +5140,7 @@
         <v>18</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>20</v>
@@ -5130,13 +5148,13 @@
       <c r="G96" s="1"/>
       <c r="H96" s="1"/>
       <c r="I96" s="1" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="J96" s="1">
-        <v>24.416665999999999</v>
+        <v>200</v>
       </c>
       <c r="K96" s="1">
-        <v>219750</v>
+        <v>2200000</v>
       </c>
       <c r="L96" s="1">
         <v>0</v>
@@ -5146,10 +5164,10 @@
       </c>
       <c r="N96" s="1"/>
       <c r="O96" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P96" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q96" s="1"/>
     </row>
@@ -5167,7 +5185,7 @@
         <v>18</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>20</v>
@@ -5175,13 +5193,13 @@
       <c r="G97" s="1"/>
       <c r="H97" s="1"/>
       <c r="I97" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="J97" s="1">
-        <v>25</v>
+        <v>24.416665999999999</v>
       </c>
       <c r="K97" s="1">
-        <v>375000</v>
+        <v>219750</v>
       </c>
       <c r="L97" s="1">
         <v>0</v>
@@ -5191,10 +5209,10 @@
       </c>
       <c r="N97" s="1"/>
       <c r="O97" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P97" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q97" s="1"/>
     </row>
@@ -5212,7 +5230,7 @@
         <v>18</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>20</v>
@@ -5220,13 +5238,13 @@
       <c r="G98" s="1"/>
       <c r="H98" s="1"/>
       <c r="I98" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="J98" s="1">
         <v>25</v>
       </c>
       <c r="K98" s="1">
-        <v>225000</v>
+        <v>375000</v>
       </c>
       <c r="L98" s="1">
         <v>0</v>
@@ -5236,10 +5254,10 @@
       </c>
       <c r="N98" s="1"/>
       <c r="O98" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P98" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q98" s="1"/>
     </row>
@@ -5257,7 +5275,7 @@
         <v>18</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>20</v>
@@ -5265,13 +5283,13 @@
       <c r="G99" s="1"/>
       <c r="H99" s="1"/>
       <c r="I99" s="1" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="J99" s="1">
         <v>25</v>
       </c>
       <c r="K99" s="1">
-        <v>375000</v>
+        <v>225000</v>
       </c>
       <c r="L99" s="1">
         <v>0</v>
@@ -5281,10 +5299,10 @@
       </c>
       <c r="N99" s="1"/>
       <c r="O99" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P99" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q99" s="1"/>
     </row>
@@ -5302,7 +5320,7 @@
         <v>18</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>20</v>
@@ -5310,13 +5328,13 @@
       <c r="G100" s="1"/>
       <c r="H100" s="1"/>
       <c r="I100" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J100" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="K100" s="1">
-        <v>1150000</v>
+        <v>375000</v>
       </c>
       <c r="L100" s="1">
         <v>0</v>
@@ -5326,10 +5344,10 @@
       </c>
       <c r="N100" s="1"/>
       <c r="O100" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P100" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q100" s="1"/>
     </row>
@@ -5347,7 +5365,7 @@
         <v>18</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>20</v>
@@ -5355,13 +5373,13 @@
       <c r="G101" s="1"/>
       <c r="H101" s="1"/>
       <c r="I101" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J101" s="1">
-        <v>599</v>
+        <v>100</v>
       </c>
       <c r="K101" s="1">
-        <v>6289500</v>
+        <v>1150000</v>
       </c>
       <c r="L101" s="1">
         <v>0</v>
@@ -5371,12 +5389,57 @@
       </c>
       <c r="N101" s="1"/>
       <c r="O101" s="1">
+        <v>40</v>
+      </c>
+      <c r="P101" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q101" s="1"/>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A102" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B102" s="1">
+        <v>0</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G102" s="1"/>
+      <c r="H102" s="1"/>
+      <c r="I102" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J102" s="1">
+        <v>599</v>
+      </c>
+      <c r="K102" s="1">
+        <v>6289500</v>
+      </c>
+      <c r="L102" s="1">
+        <v>0</v>
+      </c>
+      <c r="M102" s="1">
+        <v>0</v>
+      </c>
+      <c r="N102" s="1"/>
+      <c r="O102" s="1">
         <v>41</v>
       </c>
-      <c r="P101" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q101" s="1"/>
+      <c r="P102" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q102" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{414B7B26-5509-47EA-95E1-BBE3BF3F7193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C060F6EC-E054-4160-B669-4885555410F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1219" uniqueCount="49">
   <si>
     <t>Date</t>
   </si>
@@ -79,70 +79,52 @@
     <t>DJIBRIL DIOP</t>
   </si>
   <si>
-    <t>Stock Descente</t>
+    <t>Vente</t>
   </si>
   <si>
     <t>TOUBA</t>
   </si>
   <si>
-    <t>Cafe au Lait 3-en-1</t>
+    <t>Coumba Touré (T2)</t>
+  </si>
+  <si>
+    <t>Kamlac évaporé 48x160g</t>
   </si>
   <si>
     <t>S30</t>
   </si>
   <si>
+    <t>Nogueye THIAME (T2)</t>
+  </si>
+  <si>
+    <t>Kamlac Thé 7g</t>
+  </si>
+  <si>
+    <t>Fama DIOUF</t>
+  </si>
+  <si>
     <t>Chocolat 3-en-1 30x120 pcs</t>
+  </si>
+  <si>
+    <t>Mariama KANE</t>
   </si>
   <si>
     <t>Cowmilk 200gx10</t>
   </si>
   <si>
+    <t>Adama DABO</t>
+  </si>
+  <si>
     <t>Jus Lido</t>
   </si>
   <si>
-    <t>Kamlac Junior BLE cereal 50g x 10 x 8 sachet</t>
-  </si>
-  <si>
-    <t>Kamlac Junior BLE cereal 230g x 12 sachet</t>
-  </si>
-  <si>
-    <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
-  </si>
-  <si>
-    <t>Kamlac Junior mais cereal 50g x 10 x 8 sachet</t>
-  </si>
-  <si>
-    <t>Kamlac Thé 7g</t>
-  </si>
-  <si>
-    <t>Kamlac évaporé 48x160g</t>
-  </si>
-  <si>
-    <t>Vente</t>
-  </si>
-  <si>
-    <t>Coumba Touré (T2)</t>
-  </si>
-  <si>
-    <t>Nogueye THIAME (T2)</t>
+    <t>Saliou KONE</t>
   </si>
   <si>
     <t>Fallou SOLY (T2)</t>
   </si>
   <si>
     <t>Mariama BA</t>
-  </si>
-  <si>
-    <t>Fama DIOUF</t>
-  </si>
-  <si>
-    <t>Mariama KANE</t>
-  </si>
-  <si>
-    <t>Saliou KONE</t>
-  </si>
-  <si>
-    <t>Adama DABO</t>
   </si>
   <si>
     <t>Saly THIOUNE (T2)</t>
@@ -154,7 +136,25 @@
     <t>Jackline DIEDHIOU (T3)</t>
   </si>
   <si>
+    <t>Kamlac Junior BLE cereal 230g x 12 sachet</t>
+  </si>
+  <si>
     <t>Ndeye Fatou GUEYE (T3)</t>
+  </si>
+  <si>
+    <t>Stock Descente</t>
+  </si>
+  <si>
+    <t>Cafe au Lait 3-en-1</t>
+  </si>
+  <si>
+    <t>Kamlac Junior BLE cereal 50g x 10 x 8 sachet</t>
+  </si>
+  <si>
+    <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
+  </si>
+  <si>
+    <t>Kamlac Junior mais cereal 50g x 10 x 8 sachet</t>
   </si>
   <si>
     <t>Autre</t>
@@ -553,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q131"/>
+  <dimension ref="A1:Q159"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.3984375" customWidth="1"/>
@@ -629,7 +629,7 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
@@ -646,35 +646,39 @@
       <c r="F2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="1"/>
+      <c r="G2" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J2" s="1">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="K2" s="1">
-        <v>427500</v>
+        <v>27000</v>
       </c>
       <c r="L2" s="1">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="M2" s="1">
         <v>0</v>
       </c>
       <c r="N2" s="1"/>
       <c r="O2" s="1">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q2" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B3" s="1">
         <v>0</v>
@@ -691,16 +695,18 @@
       <c r="F3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="1"/>
+      <c r="G3" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J3" s="1">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="K3" s="1">
-        <v>1100000</v>
+        <v>27000</v>
       </c>
       <c r="L3" s="1">
         <v>0</v>
@@ -710,16 +716,18 @@
       </c>
       <c r="N3" s="1"/>
       <c r="O3" s="1">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q3" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B4" s="1">
         <v>0</v>
@@ -736,16 +744,18 @@
       <c r="F4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="1"/>
+      <c r="G4" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J4" s="1">
-        <v>107.5</v>
+        <v>4.1666667999999997E-2</v>
       </c>
       <c r="K4" s="1">
-        <v>645000</v>
+        <v>479.16665999999998</v>
       </c>
       <c r="L4" s="1">
         <v>0</v>
@@ -755,16 +765,18 @@
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q4" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B5" s="1">
         <v>0</v>
@@ -781,16 +793,18 @@
       <c r="F5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="1"/>
+      <c r="G5" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J5" s="1">
-        <v>194.16667000000001</v>
+        <v>1</v>
       </c>
       <c r="K5" s="1">
-        <v>2135833.2000000002</v>
+        <v>9000</v>
       </c>
       <c r="L5" s="1">
         <v>0</v>
@@ -800,16 +814,18 @@
       </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q5" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B6" s="1">
         <v>0</v>
@@ -826,16 +842,18 @@
       <c r="F6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="1"/>
+      <c r="G6" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J6" s="1">
-        <v>23</v>
+        <v>0.5</v>
       </c>
       <c r="K6" s="1">
-        <v>345000</v>
+        <v>5750</v>
       </c>
       <c r="L6" s="1">
         <v>0</v>
@@ -845,16 +863,18 @@
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q6" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B7" s="1">
         <v>0</v>
@@ -871,16 +891,18 @@
       <c r="F7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1" t="s">
         <v>27</v>
       </c>
       <c r="J7" s="1">
-        <v>21.916665999999999</v>
+        <v>0.2</v>
       </c>
       <c r="K7" s="1">
-        <v>197250</v>
+        <v>2200</v>
       </c>
       <c r="L7" s="1">
         <v>0</v>
@@ -890,16 +912,18 @@
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q7" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B8" s="1">
         <v>0</v>
@@ -916,16 +940,18 @@
       <c r="F8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="1"/>
+      <c r="G8" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J8" s="1">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="K8" s="1">
-        <v>225000</v>
+        <v>12000</v>
       </c>
       <c r="L8" s="1">
         <v>0</v>
@@ -935,16 +961,18 @@
       </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q8" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B9" s="1">
         <v>0</v>
@@ -961,16 +989,18 @@
       <c r="F9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="1"/>
+      <c r="G9" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J9" s="1">
-        <v>25</v>
+        <v>8.3333335999999994E-2</v>
       </c>
       <c r="K9" s="1">
-        <v>375000</v>
+        <v>958.33330000000001</v>
       </c>
       <c r="L9" s="1">
         <v>0</v>
@@ -980,16 +1010,18 @@
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q9" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B10" s="1">
         <v>0</v>
@@ -1006,16 +1038,18 @@
       <c r="F10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="1"/>
+      <c r="G10" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J10" s="1">
-        <v>92.375</v>
+        <v>1.5</v>
       </c>
       <c r="K10" s="1">
-        <v>1062312.5</v>
+        <v>13500</v>
       </c>
       <c r="L10" s="1">
         <v>0</v>
@@ -1025,16 +1059,18 @@
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q10" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A11" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B11" s="1">
         <v>0</v>
@@ -1051,16 +1087,18 @@
       <c r="F11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G11" s="1"/>
+      <c r="G11" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1" t="s">
         <v>31</v>
       </c>
       <c r="J11" s="1">
-        <v>409</v>
+        <v>0.5</v>
       </c>
       <c r="K11" s="1">
-        <v>3681000</v>
+        <v>5500</v>
       </c>
       <c r="L11" s="1">
         <v>0</v>
@@ -1070,16 +1108,18 @@
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q11" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A12" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B12" s="1">
         <v>0</v>
@@ -1091,36 +1131,36 @@
         <v>18</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J12" s="1">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="K12" s="1">
-        <v>297000</v>
+        <v>6000</v>
       </c>
       <c r="L12" s="1">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="M12" s="1">
         <v>0</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q12" s="1" t="s">
         <v>16</v>
@@ -1128,7 +1168,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A13" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B13" s="1">
         <v>0</v>
@@ -1140,23 +1180,23 @@
         <v>18</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J13" s="1">
-        <v>3</v>
+        <v>8.3333335999999994E-2</v>
       </c>
       <c r="K13" s="1">
-        <v>27000</v>
+        <v>958.33330000000001</v>
       </c>
       <c r="L13" s="1">
         <v>0</v>
@@ -1166,10 +1206,10 @@
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q13" s="1" t="s">
         <v>16</v>
@@ -1177,7 +1217,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A14" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B14" s="1">
         <v>0</v>
@@ -1189,23 +1229,23 @@
         <v>18</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J14" s="1">
         <v>1</v>
       </c>
       <c r="K14" s="1">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="L14" s="1">
         <v>0</v>
@@ -1215,10 +1255,10 @@
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q14" s="1" t="s">
         <v>16</v>
@@ -1226,7 +1266,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A15" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B15" s="1">
         <v>0</v>
@@ -1238,23 +1278,23 @@
         <v>18</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1" t="s">
         <v>31</v>
       </c>
       <c r="J15" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K15" s="1">
-        <v>54000</v>
+        <v>11000</v>
       </c>
       <c r="L15" s="1">
         <v>0</v>
@@ -1264,10 +1304,10 @@
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q15" s="1" t="s">
         <v>16</v>
@@ -1275,7 +1315,7 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A16" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B16" s="1">
         <v>0</v>
@@ -1287,23 +1327,23 @@
         <v>18</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J16" s="1">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="K16" s="1">
-        <v>18000</v>
+        <v>1100</v>
       </c>
       <c r="L16" s="1">
         <v>0</v>
@@ -1313,10 +1353,10 @@
       </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q16" s="1" t="s">
         <v>16</v>
@@ -1324,7 +1364,7 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A17" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B17" s="1">
         <v>0</v>
@@ -1336,23 +1376,23 @@
         <v>18</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J17" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K17" s="1">
-        <v>54000</v>
+        <v>45000</v>
       </c>
       <c r="L17" s="1">
         <v>0</v>
@@ -1362,10 +1402,10 @@
       </c>
       <c r="N17" s="1"/>
       <c r="O17" s="1">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q17" s="1" t="s">
         <v>16</v>
@@ -1373,7 +1413,7 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A18" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B18" s="1">
         <v>0</v>
@@ -1385,23 +1425,23 @@
         <v>18</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J18" s="1">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="K18" s="1">
-        <v>12000</v>
+        <v>2875</v>
       </c>
       <c r="L18" s="1">
         <v>0</v>
@@ -1411,10 +1451,10 @@
       </c>
       <c r="N18" s="1"/>
       <c r="O18" s="1">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q18" s="1" t="s">
         <v>16</v>
@@ -1422,7 +1462,7 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A19" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B19" s="1">
         <v>0</v>
@@ -1434,23 +1474,23 @@
         <v>18</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J19" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K19" s="1">
-        <v>4500</v>
+        <v>54000</v>
       </c>
       <c r="L19" s="1">
         <v>0</v>
@@ -1460,10 +1500,10 @@
       </c>
       <c r="N19" s="1"/>
       <c r="O19" s="1">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q19" s="1" t="s">
         <v>16</v>
@@ -1471,7 +1511,7 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A20" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B20" s="1">
         <v>0</v>
@@ -1483,23 +1523,23 @@
         <v>18</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1" t="s">
         <v>31</v>
       </c>
       <c r="J20" s="1">
-        <v>2</v>
+        <v>8.3333335999999994E-2</v>
       </c>
       <c r="K20" s="1">
-        <v>18000</v>
+        <v>916.66669999999999</v>
       </c>
       <c r="L20" s="1">
         <v>0</v>
@@ -1509,10 +1549,10 @@
       </c>
       <c r="N20" s="1"/>
       <c r="O20" s="1">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q20" s="1" t="s">
         <v>16</v>
@@ -1520,7 +1560,7 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A21" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B21" s="1">
         <v>0</v>
@@ -1532,23 +1572,23 @@
         <v>18</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J21" s="1">
-        <v>4.1666667999999997E-2</v>
+        <v>2</v>
       </c>
       <c r="K21" s="1">
-        <v>479.16665999999998</v>
+        <v>18000</v>
       </c>
       <c r="L21" s="1">
         <v>0</v>
@@ -1558,10 +1598,10 @@
       </c>
       <c r="N21" s="1"/>
       <c r="O21" s="1">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q21" s="1" t="s">
         <v>16</v>
@@ -1569,7 +1609,7 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A22" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B22" s="1">
         <v>0</v>
@@ -1581,23 +1621,23 @@
         <v>18</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J22" s="1">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="K22" s="1">
-        <v>18000</v>
+        <v>1100</v>
       </c>
       <c r="L22" s="1">
         <v>0</v>
@@ -1607,10 +1647,10 @@
       </c>
       <c r="N22" s="1"/>
       <c r="O22" s="1">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q22" s="1" t="s">
         <v>16</v>
@@ -1618,7 +1658,7 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A23" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B23" s="1">
         <v>0</v>
@@ -1630,23 +1670,23 @@
         <v>18</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J23" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K23" s="1">
-        <v>72000</v>
+        <v>18000</v>
       </c>
       <c r="L23" s="1">
         <v>0</v>
@@ -1656,10 +1696,10 @@
       </c>
       <c r="N23" s="1"/>
       <c r="O23" s="1">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q23" s="1" t="s">
         <v>16</v>
@@ -1667,7 +1707,7 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A24" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B24" s="1">
         <v>0</v>
@@ -1679,23 +1719,23 @@
         <v>18</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J24" s="1">
-        <v>0.54166669999999995</v>
+        <v>5.5</v>
       </c>
       <c r="K24" s="1">
-        <v>6229.1665000000003</v>
+        <v>49500</v>
       </c>
       <c r="L24" s="1">
         <v>0</v>
@@ -1705,10 +1745,10 @@
       </c>
       <c r="N24" s="1"/>
       <c r="O24" s="1">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q24" s="1" t="s">
         <v>16</v>
@@ -1716,7 +1756,7 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A25" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B25" s="1">
         <v>0</v>
@@ -1728,23 +1768,23 @@
         <v>18</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="J25" s="1">
         <v>2</v>
       </c>
       <c r="K25" s="1">
-        <v>22000</v>
+        <v>18000</v>
       </c>
       <c r="L25" s="1">
         <v>0</v>
@@ -1754,10 +1794,10 @@
       </c>
       <c r="N25" s="1"/>
       <c r="O25" s="1">
-        <v>115</v>
+        <v>154</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q25" s="1" t="s">
         <v>16</v>
@@ -1765,7 +1805,7 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A26" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B26" s="1">
         <v>0</v>
@@ -1777,23 +1817,23 @@
         <v>18</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1" t="s">
         <v>31</v>
       </c>
       <c r="J26" s="1">
-        <v>6</v>
+        <v>8.3333335999999994E-2</v>
       </c>
       <c r="K26" s="1">
-        <v>54000</v>
+        <v>916.66669999999999</v>
       </c>
       <c r="L26" s="1">
         <v>0</v>
@@ -1803,10 +1843,10 @@
       </c>
       <c r="N26" s="1"/>
       <c r="O26" s="1">
-        <v>116</v>
+        <v>155</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q26" s="1" t="s">
         <v>16</v>
@@ -1814,7 +1854,7 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A27" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B27" s="1">
         <v>0</v>
@@ -1826,23 +1866,23 @@
         <v>18</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J27" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K27" s="1">
-        <v>23000</v>
+        <v>54000</v>
       </c>
       <c r="L27" s="1">
         <v>0</v>
@@ -1852,10 +1892,10 @@
       </c>
       <c r="N27" s="1"/>
       <c r="O27" s="1">
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q27" s="1" t="s">
         <v>16</v>
@@ -1863,7 +1903,7 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A28" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B28" s="1">
         <v>0</v>
@@ -1875,23 +1915,23 @@
         <v>18</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J28" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K28" s="1">
-        <v>5500</v>
+        <v>6000</v>
       </c>
       <c r="L28" s="1">
         <v>0</v>
@@ -1901,10 +1941,10 @@
       </c>
       <c r="N28" s="1"/>
       <c r="O28" s="1">
-        <v>118</v>
+        <v>157</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q28" s="1" t="s">
         <v>16</v>
@@ -1912,7 +1952,7 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A29" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B29" s="1">
         <v>0</v>
@@ -1924,23 +1964,23 @@
         <v>18</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J29" s="1">
-        <v>1</v>
+        <v>4.1666667999999997E-2</v>
       </c>
       <c r="K29" s="1">
-        <v>6000</v>
+        <v>479.16665999999998</v>
       </c>
       <c r="L29" s="1">
         <v>0</v>
@@ -1950,10 +1990,10 @@
       </c>
       <c r="N29" s="1"/>
       <c r="O29" s="1">
-        <v>119</v>
+        <v>158</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q29" s="1" t="s">
         <v>16</v>
@@ -1973,23 +2013,21 @@
         <v>18</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="J30" s="1">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c r="K30" s="1">
-        <v>36000</v>
+        <v>427500</v>
       </c>
       <c r="L30" s="1">
         <v>0</v>
@@ -1999,14 +2037,12 @@
       </c>
       <c r="N30" s="1"/>
       <c r="O30" s="1">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q30" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="Q30" s="1"/>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A31" s="2">
@@ -2022,23 +2058,21 @@
         <v>18</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J31" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="K31" s="1">
-        <v>6000</v>
+        <v>1100000</v>
       </c>
       <c r="L31" s="1">
         <v>0</v>
@@ -2048,14 +2082,12 @@
       </c>
       <c r="N31" s="1"/>
       <c r="O31" s="1">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q31" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="Q31" s="1"/>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A32" s="2">
@@ -2071,23 +2103,21 @@
         <v>18</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J32" s="1">
-        <v>5</v>
+        <v>107.5</v>
       </c>
       <c r="K32" s="1">
-        <v>45000</v>
+        <v>645000</v>
       </c>
       <c r="L32" s="1">
         <v>0</v>
@@ -2097,14 +2127,12 @@
       </c>
       <c r="N32" s="1"/>
       <c r="O32" s="1">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q32" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="Q32" s="1"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A33" s="2">
@@ -2120,23 +2148,21 @@
         <v>18</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J33" s="1">
-        <v>1</v>
+        <v>194.16667000000001</v>
       </c>
       <c r="K33" s="1">
-        <v>11000</v>
+        <v>2135833.2000000002</v>
       </c>
       <c r="L33" s="1">
         <v>0</v>
@@ -2146,14 +2172,12 @@
       </c>
       <c r="N33" s="1"/>
       <c r="O33" s="1">
-        <v>123</v>
+        <v>95</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q33" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="Q33" s="1"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A34" s="2">
@@ -2169,23 +2193,21 @@
         <v>18</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G34" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="J34" s="1">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="K34" s="1">
-        <v>4500</v>
+        <v>345000</v>
       </c>
       <c r="L34" s="1">
         <v>0</v>
@@ -2195,14 +2217,12 @@
       </c>
       <c r="N34" s="1"/>
       <c r="O34" s="1">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q34" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="Q34" s="1"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A35" s="2">
@@ -2218,23 +2238,21 @@
         <v>18</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J35" s="1">
-        <v>19</v>
+        <v>21.916665999999999</v>
       </c>
       <c r="K35" s="1">
-        <v>171000</v>
+        <v>197250</v>
       </c>
       <c r="L35" s="1">
         <v>0</v>
@@ -2244,14 +2262,12 @@
       </c>
       <c r="N35" s="1"/>
       <c r="O35" s="1">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q35" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="Q35" s="1"/>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A36" s="2">
@@ -2267,23 +2283,21 @@
         <v>18</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G36" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J36" s="1">
         <v>25</v>
       </c>
-      <c r="J36" s="1">
-        <v>1.0833333999999999</v>
-      </c>
       <c r="K36" s="1">
-        <v>11916.666999999999</v>
+        <v>225000</v>
       </c>
       <c r="L36" s="1">
         <v>0</v>
@@ -2293,14 +2307,12 @@
       </c>
       <c r="N36" s="1"/>
       <c r="O36" s="1">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q36" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="Q36" s="1"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A37" s="2">
@@ -2316,23 +2328,21 @@
         <v>18</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G37" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="J37" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K37" s="1">
-        <v>135000</v>
+        <v>375000</v>
       </c>
       <c r="L37" s="1">
         <v>0</v>
@@ -2342,14 +2352,12 @@
       </c>
       <c r="N37" s="1"/>
       <c r="O37" s="1">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q37" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="Q37" s="1"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A38" s="2">
@@ -2365,23 +2373,21 @@
         <v>18</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J38" s="1">
-        <v>1.0833333999999999</v>
+        <v>92.375</v>
       </c>
       <c r="K38" s="1">
-        <v>12458.333000000001</v>
+        <v>1062312.5</v>
       </c>
       <c r="L38" s="1">
         <v>0</v>
@@ -2391,14 +2397,12 @@
       </c>
       <c r="N38" s="1"/>
       <c r="O38" s="1">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q38" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="Q38" s="1"/>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A39" s="2">
@@ -2414,25 +2418,21 @@
         <v>18</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G39" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
       <c r="I39" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J39" s="1">
-        <v>50</v>
+        <v>409</v>
       </c>
       <c r="K39" s="1">
-        <v>450000</v>
+        <v>3681000</v>
       </c>
       <c r="L39" s="1">
         <v>0</v>
@@ -2442,14 +2442,12 @@
       </c>
       <c r="N39" s="1"/>
       <c r="O39" s="1">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q39" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="Q39" s="1"/>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A40" s="2">
@@ -2465,38 +2463,36 @@
         <v>18</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>46</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="H40" s="1"/>
       <c r="I40" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J40" s="1">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="K40" s="1">
-        <v>6000</v>
+        <v>297000</v>
       </c>
       <c r="L40" s="1">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="M40" s="1">
         <v>0</v>
       </c>
       <c r="N40" s="1"/>
       <c r="O40" s="1">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q40" s="1" t="s">
         <v>16</v>
@@ -2504,7 +2500,7 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A41" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B41" s="1">
         <v>0</v>
@@ -2516,17 +2512,17 @@
         <v>18</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J41" s="1">
         <v>3</v>
@@ -2535,17 +2531,17 @@
         <v>27000</v>
       </c>
       <c r="L41" s="1">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="M41" s="1">
         <v>0</v>
       </c>
       <c r="N41" s="1"/>
       <c r="O41" s="1">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q41" s="1" t="s">
         <v>16</v>
@@ -2553,7 +2549,7 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A42" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B42" s="1">
         <v>0</v>
@@ -2565,23 +2561,23 @@
         <v>18</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J42" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K42" s="1">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="L42" s="1">
         <v>0</v>
@@ -2591,10 +2587,10 @@
       </c>
       <c r="N42" s="1"/>
       <c r="O42" s="1">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q42" s="1" t="s">
         <v>16</v>
@@ -2602,7 +2598,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A43" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B43" s="1">
         <v>0</v>
@@ -2614,23 +2610,23 @@
         <v>18</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J43" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K43" s="1">
-        <v>18000</v>
+        <v>54000</v>
       </c>
       <c r="L43" s="1">
         <v>0</v>
@@ -2640,10 +2636,10 @@
       </c>
       <c r="N43" s="1"/>
       <c r="O43" s="1">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q43" s="1" t="s">
         <v>16</v>
@@ -2651,7 +2647,7 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A44" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B44" s="1">
         <v>0</v>
@@ -2663,23 +2659,23 @@
         <v>18</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J44" s="1">
-        <v>1.625</v>
+        <v>3</v>
       </c>
       <c r="K44" s="1">
-        <v>18687.5</v>
+        <v>18000</v>
       </c>
       <c r="L44" s="1">
         <v>0</v>
@@ -2689,10 +2685,10 @@
       </c>
       <c r="N44" s="1"/>
       <c r="O44" s="1">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q44" s="1" t="s">
         <v>16</v>
@@ -2700,7 +2696,7 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A45" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B45" s="1">
         <v>0</v>
@@ -2712,23 +2708,23 @@
         <v>18</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J45" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K45" s="1">
-        <v>12000</v>
+        <v>54000</v>
       </c>
       <c r="L45" s="1">
         <v>0</v>
@@ -2738,10 +2734,10 @@
       </c>
       <c r="N45" s="1"/>
       <c r="O45" s="1">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q45" s="1" t="s">
         <v>16</v>
@@ -2749,7 +2745,7 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A46" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B46" s="1">
         <v>0</v>
@@ -2761,23 +2757,23 @@
         <v>18</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J46" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K46" s="1">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="L46" s="1">
         <v>0</v>
@@ -2787,10 +2783,10 @@
       </c>
       <c r="N46" s="1"/>
       <c r="O46" s="1">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q46" s="1" t="s">
         <v>16</v>
@@ -2798,7 +2794,7 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A47" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B47" s="1">
         <v>0</v>
@@ -2810,23 +2806,23 @@
         <v>18</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="J47" s="1">
         <v>1</v>
       </c>
       <c r="K47" s="1">
-        <v>9000</v>
+        <v>4500</v>
       </c>
       <c r="L47" s="1">
         <v>0</v>
@@ -2836,10 +2832,10 @@
       </c>
       <c r="N47" s="1"/>
       <c r="O47" s="1">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q47" s="1" t="s">
         <v>16</v>
@@ -2847,7 +2843,7 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A48" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B48" s="1">
         <v>0</v>
@@ -2859,23 +2855,23 @@
         <v>18</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J48" s="1">
-        <v>4.1666667999999997E-2</v>
+        <v>2</v>
       </c>
       <c r="K48" s="1">
-        <v>479.16665999999998</v>
+        <v>18000</v>
       </c>
       <c r="L48" s="1">
         <v>0</v>
@@ -2885,10 +2881,10 @@
       </c>
       <c r="N48" s="1"/>
       <c r="O48" s="1">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q48" s="1" t="s">
         <v>16</v>
@@ -2896,7 +2892,7 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A49" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B49" s="1">
         <v>0</v>
@@ -2908,23 +2904,23 @@
         <v>18</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J49" s="1">
-        <v>1</v>
+        <v>4.1666667999999997E-2</v>
       </c>
       <c r="K49" s="1">
-        <v>9000</v>
+        <v>479.16665999999998</v>
       </c>
       <c r="L49" s="1">
         <v>0</v>
@@ -2934,10 +2930,10 @@
       </c>
       <c r="N49" s="1"/>
       <c r="O49" s="1">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q49" s="1" t="s">
         <v>16</v>
@@ -2945,7 +2941,7 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A50" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B50" s="1">
         <v>0</v>
@@ -2957,17 +2953,17 @@
         <v>18</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J50" s="1">
         <v>2</v>
@@ -2983,10 +2979,10 @@
       </c>
       <c r="N50" s="1"/>
       <c r="O50" s="1">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q50" s="1" t="s">
         <v>16</v>
@@ -2994,7 +2990,7 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A51" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B51" s="1">
         <v>0</v>
@@ -3006,23 +3002,23 @@
         <v>18</v>
       </c>
       <c r="E51" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G51" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J51" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K51" s="1">
-        <v>9000</v>
+        <v>72000</v>
       </c>
       <c r="L51" s="1">
         <v>0</v>
@@ -3032,10 +3028,10 @@
       </c>
       <c r="N51" s="1"/>
       <c r="O51" s="1">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q51" s="1" t="s">
         <v>16</v>
@@ -3043,7 +3039,7 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A52" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B52" s="1">
         <v>0</v>
@@ -3055,23 +3051,23 @@
         <v>18</v>
       </c>
       <c r="E52" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G52" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J52" s="1">
-        <v>2</v>
+        <v>0.54166669999999995</v>
       </c>
       <c r="K52" s="1">
-        <v>18000</v>
+        <v>6229.1665000000003</v>
       </c>
       <c r="L52" s="1">
         <v>0</v>
@@ -3081,10 +3077,10 @@
       </c>
       <c r="N52" s="1"/>
       <c r="O52" s="1">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q52" s="1" t="s">
         <v>16</v>
@@ -3092,7 +3088,7 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A53" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B53" s="1">
         <v>0</v>
@@ -3104,23 +3100,23 @@
         <v>18</v>
       </c>
       <c r="E53" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G53" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1" t="s">
         <v>31</v>
       </c>
       <c r="J53" s="1">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="K53" s="1">
-        <v>4500</v>
+        <v>22000</v>
       </c>
       <c r="L53" s="1">
         <v>0</v>
@@ -3130,10 +3126,10 @@
       </c>
       <c r="N53" s="1"/>
       <c r="O53" s="1">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q53" s="1" t="s">
         <v>16</v>
@@ -3141,7 +3137,7 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A54" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B54" s="1">
         <v>0</v>
@@ -3153,23 +3149,23 @@
         <v>18</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J54" s="1">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="K54" s="1">
-        <v>4500</v>
+        <v>54000</v>
       </c>
       <c r="L54" s="1">
         <v>0</v>
@@ -3179,10 +3175,10 @@
       </c>
       <c r="N54" s="1"/>
       <c r="O54" s="1">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q54" s="1" t="s">
         <v>16</v>
@@ -3190,7 +3186,7 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A55" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B55" s="1">
         <v>0</v>
@@ -3202,23 +3198,23 @@
         <v>18</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J55" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K55" s="1">
-        <v>15000</v>
+        <v>23000</v>
       </c>
       <c r="L55" s="1">
         <v>0</v>
@@ -3228,10 +3224,10 @@
       </c>
       <c r="N55" s="1"/>
       <c r="O55" s="1">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q55" s="1" t="s">
         <v>16</v>
@@ -3239,7 +3235,7 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A56" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B56" s="1">
         <v>0</v>
@@ -3251,23 +3247,23 @@
         <v>18</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1" t="s">
         <v>31</v>
       </c>
       <c r="J56" s="1">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="K56" s="1">
-        <v>27000</v>
+        <v>5500</v>
       </c>
       <c r="L56" s="1">
         <v>0</v>
@@ -3277,10 +3273,10 @@
       </c>
       <c r="N56" s="1"/>
       <c r="O56" s="1">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q56" s="1" t="s">
         <v>16</v>
@@ -3288,7 +3284,7 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A57" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B57" s="1">
         <v>0</v>
@@ -3300,17 +3296,17 @@
         <v>18</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J57" s="1">
         <v>1</v>
@@ -3326,10 +3322,10 @@
       </c>
       <c r="N57" s="1"/>
       <c r="O57" s="1">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q57" s="1" t="s">
         <v>16</v>
@@ -3337,7 +3333,7 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A58" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B58" s="1">
         <v>0</v>
@@ -3349,23 +3345,23 @@
         <v>18</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J58" s="1">
-        <v>0.16666666999999999</v>
+        <v>4</v>
       </c>
       <c r="K58" s="1">
-        <v>1833.3334</v>
+        <v>36000</v>
       </c>
       <c r="L58" s="1">
         <v>0</v>
@@ -3375,10 +3371,10 @@
       </c>
       <c r="N58" s="1"/>
       <c r="O58" s="1">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q58" s="1" t="s">
         <v>16</v>
@@ -3386,7 +3382,7 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A59" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B59" s="1">
         <v>0</v>
@@ -3398,23 +3394,23 @@
         <v>18</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J59" s="1">
         <v>1</v>
       </c>
       <c r="K59" s="1">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="L59" s="1">
         <v>0</v>
@@ -3424,10 +3420,10 @@
       </c>
       <c r="N59" s="1"/>
       <c r="O59" s="1">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q59" s="1" t="s">
         <v>16</v>
@@ -3435,7 +3431,7 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A60" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B60" s="1">
         <v>0</v>
@@ -3447,23 +3443,23 @@
         <v>18</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J60" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K60" s="1">
-        <v>36000</v>
+        <v>45000</v>
       </c>
       <c r="L60" s="1">
         <v>0</v>
@@ -3473,10 +3469,10 @@
       </c>
       <c r="N60" s="1"/>
       <c r="O60" s="1">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q60" s="1" t="s">
         <v>16</v>
@@ -3484,7 +3480,7 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A61" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B61" s="1">
         <v>0</v>
@@ -3496,23 +3492,23 @@
         <v>18</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J61" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K61" s="1">
-        <v>18000</v>
+        <v>11000</v>
       </c>
       <c r="L61" s="1">
         <v>0</v>
@@ -3522,10 +3518,10 @@
       </c>
       <c r="N61" s="1"/>
       <c r="O61" s="1">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q61" s="1" t="s">
         <v>16</v>
@@ -3533,7 +3529,7 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A62" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B62" s="1">
         <v>0</v>
@@ -3545,23 +3541,23 @@
         <v>18</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="J62" s="1">
-        <v>1.0833333999999999</v>
+        <v>1</v>
       </c>
       <c r="K62" s="1">
-        <v>12458.333000000001</v>
+        <v>4500</v>
       </c>
       <c r="L62" s="1">
         <v>0</v>
@@ -3571,10 +3567,10 @@
       </c>
       <c r="N62" s="1"/>
       <c r="O62" s="1">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="P62" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q62" s="1" t="s">
         <v>16</v>
@@ -3582,7 +3578,7 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A63" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B63" s="1">
         <v>0</v>
@@ -3594,23 +3590,23 @@
         <v>18</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J63" s="1">
-        <v>0.5</v>
+        <v>19</v>
       </c>
       <c r="K63" s="1">
-        <v>4500</v>
+        <v>171000</v>
       </c>
       <c r="L63" s="1">
         <v>0</v>
@@ -3620,10 +3616,10 @@
       </c>
       <c r="N63" s="1"/>
       <c r="O63" s="1">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="P63" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q63" s="1" t="s">
         <v>16</v>
@@ -3631,7 +3627,7 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A64" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B64" s="1">
         <v>0</v>
@@ -3643,23 +3639,23 @@
         <v>18</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1" t="s">
         <v>31</v>
       </c>
       <c r="J64" s="1">
-        <v>3</v>
+        <v>1.0833333999999999</v>
       </c>
       <c r="K64" s="1">
-        <v>27000</v>
+        <v>11916.666999999999</v>
       </c>
       <c r="L64" s="1">
         <v>0</v>
@@ -3669,10 +3665,10 @@
       </c>
       <c r="N64" s="1"/>
       <c r="O64" s="1">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="P64" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q64" s="1" t="s">
         <v>16</v>
@@ -3680,7 +3676,7 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A65" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B65" s="1">
         <v>0</v>
@@ -3692,23 +3688,23 @@
         <v>18</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J65" s="1">
-        <v>1.0833333999999999</v>
+        <v>15</v>
       </c>
       <c r="K65" s="1">
-        <v>11916.666999999999</v>
+        <v>135000</v>
       </c>
       <c r="L65" s="1">
         <v>0</v>
@@ -3718,10 +3714,10 @@
       </c>
       <c r="N65" s="1"/>
       <c r="O65" s="1">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="P65" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q65" s="1" t="s">
         <v>16</v>
@@ -3729,7 +3725,7 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A66" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B66" s="1">
         <v>0</v>
@@ -3741,23 +3737,23 @@
         <v>18</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J66" s="1">
-        <v>4</v>
+        <v>1.0833333999999999</v>
       </c>
       <c r="K66" s="1">
-        <v>24000</v>
+        <v>12458.333000000001</v>
       </c>
       <c r="L66" s="1">
         <v>0</v>
@@ -3767,10 +3763,10 @@
       </c>
       <c r="N66" s="1"/>
       <c r="O66" s="1">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="P66" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q66" s="1" t="s">
         <v>16</v>
@@ -3778,7 +3774,7 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A67" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B67" s="1">
         <v>0</v>
@@ -3790,23 +3786,25 @@
         <v>18</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H67" s="1"/>
+        <v>45</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="I67" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J67" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="K67" s="1">
-        <v>15000</v>
+        <v>450000</v>
       </c>
       <c r="L67" s="1">
         <v>0</v>
@@ -3816,10 +3814,10 @@
       </c>
       <c r="N67" s="1"/>
       <c r="O67" s="1">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="P67" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q67" s="1" t="s">
         <v>16</v>
@@ -3827,7 +3825,7 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A68" s="2">
-        <v>46222</v>
+        <v>46224</v>
       </c>
       <c r="B68" s="1">
         <v>0</v>
@@ -3839,36 +3837,38 @@
         <v>18</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H68" s="1"/>
+        <v>45</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="I68" s="1" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="J68" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K68" s="1">
-        <v>22000</v>
+        <v>6000</v>
       </c>
       <c r="L68" s="1">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="M68" s="1">
         <v>0</v>
       </c>
       <c r="N68" s="1"/>
       <c r="O68" s="1">
-        <v>42</v>
+        <v>130</v>
       </c>
       <c r="P68" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q68" s="1" t="s">
         <v>16</v>
@@ -3876,7 +3876,7 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A69" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B69" s="1">
         <v>0</v>
@@ -3888,36 +3888,36 @@
         <v>18</v>
       </c>
       <c r="E69" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G69" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="H69" s="1"/>
       <c r="I69" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J69" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K69" s="1">
-        <v>6000</v>
+        <v>27000</v>
       </c>
       <c r="L69" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="M69" s="1">
         <v>0</v>
       </c>
       <c r="N69" s="1"/>
       <c r="O69" s="1">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="P69" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q69" s="1" t="s">
         <v>16</v>
@@ -3925,7 +3925,7 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A70" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B70" s="1">
         <v>0</v>
@@ -3937,23 +3937,23 @@
         <v>18</v>
       </c>
       <c r="E70" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G70" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J70" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K70" s="1">
-        <v>4500</v>
+        <v>12000</v>
       </c>
       <c r="L70" s="1">
         <v>0</v>
@@ -3963,10 +3963,10 @@
       </c>
       <c r="N70" s="1"/>
       <c r="O70" s="1">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="P70" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q70" s="1" t="s">
         <v>16</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A71" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B71" s="1">
         <v>0</v>
@@ -3986,23 +3986,23 @@
         <v>18</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H71" s="1"/>
       <c r="I71" s="1" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="J71" s="1">
         <v>2</v>
       </c>
       <c r="K71" s="1">
-        <v>22000</v>
+        <v>18000</v>
       </c>
       <c r="L71" s="1">
         <v>0</v>
@@ -4012,10 +4012,10 @@
       </c>
       <c r="N71" s="1"/>
       <c r="O71" s="1">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="P71" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q71" s="1" t="s">
         <v>16</v>
@@ -4023,7 +4023,7 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A72" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B72" s="1">
         <v>0</v>
@@ -4035,23 +4035,23 @@
         <v>18</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H72" s="1"/>
       <c r="I72" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J72" s="1">
-        <v>2</v>
+        <v>1.625</v>
       </c>
       <c r="K72" s="1">
-        <v>12000</v>
+        <v>18687.5</v>
       </c>
       <c r="L72" s="1">
         <v>0</v>
@@ -4061,10 +4061,10 @@
       </c>
       <c r="N72" s="1"/>
       <c r="O72" s="1">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="P72" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q72" s="1" t="s">
         <v>16</v>
@@ -4072,7 +4072,7 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A73" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B73" s="1">
         <v>0</v>
@@ -4084,23 +4084,23 @@
         <v>18</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J73" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K73" s="1">
-        <v>31500</v>
+        <v>12000</v>
       </c>
       <c r="L73" s="1">
         <v>0</v>
@@ -4110,10 +4110,10 @@
       </c>
       <c r="N73" s="1"/>
       <c r="O73" s="1">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="P73" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q73" s="1" t="s">
         <v>16</v>
@@ -4121,7 +4121,7 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A74" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B74" s="1">
         <v>0</v>
@@ -4133,23 +4133,23 @@
         <v>18</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J74" s="1">
         <v>1</v>
       </c>
       <c r="K74" s="1">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="L74" s="1">
         <v>0</v>
@@ -4159,10 +4159,10 @@
       </c>
       <c r="N74" s="1"/>
       <c r="O74" s="1">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="P74" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q74" s="1" t="s">
         <v>16</v>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A75" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B75" s="1">
         <v>0</v>
@@ -4182,23 +4182,23 @@
         <v>18</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J75" s="1">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="K75" s="1">
-        <v>2875</v>
+        <v>9000</v>
       </c>
       <c r="L75" s="1">
         <v>0</v>
@@ -4208,10 +4208,10 @@
       </c>
       <c r="N75" s="1"/>
       <c r="O75" s="1">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="P75" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q75" s="1" t="s">
         <v>16</v>
@@ -4219,7 +4219,7 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A76" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B76" s="1">
         <v>0</v>
@@ -4231,23 +4231,23 @@
         <v>18</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J76" s="1">
-        <v>2</v>
+        <v>4.1666667999999997E-2</v>
       </c>
       <c r="K76" s="1">
-        <v>21000</v>
+        <v>479.16665999999998</v>
       </c>
       <c r="L76" s="1">
         <v>0</v>
@@ -4257,10 +4257,10 @@
       </c>
       <c r="N76" s="1"/>
       <c r="O76" s="1">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="P76" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q76" s="1" t="s">
         <v>16</v>
@@ -4268,7 +4268,7 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A77" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B77" s="1">
         <v>0</v>
@@ -4280,23 +4280,23 @@
         <v>18</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J77" s="1">
         <v>1</v>
       </c>
       <c r="K77" s="1">
-        <v>10500</v>
+        <v>9000</v>
       </c>
       <c r="L77" s="1">
         <v>0</v>
@@ -4306,10 +4306,10 @@
       </c>
       <c r="N77" s="1"/>
       <c r="O77" s="1">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="P77" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q77" s="1" t="s">
         <v>16</v>
@@ -4317,7 +4317,7 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A78" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B78" s="1">
         <v>0</v>
@@ -4329,23 +4329,23 @@
         <v>18</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H78" s="1"/>
       <c r="I78" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J78" s="1">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="K78" s="1">
-        <v>3000</v>
+        <v>18000</v>
       </c>
       <c r="L78" s="1">
         <v>0</v>
@@ -4355,10 +4355,10 @@
       </c>
       <c r="N78" s="1"/>
       <c r="O78" s="1">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="P78" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q78" s="1" t="s">
         <v>16</v>
@@ -4366,7 +4366,7 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A79" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B79" s="1">
         <v>0</v>
@@ -4378,17 +4378,17 @@
         <v>18</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J79" s="1">
         <v>1</v>
@@ -4404,10 +4404,10 @@
       </c>
       <c r="N79" s="1"/>
       <c r="O79" s="1">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="P79" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q79" s="1" t="s">
         <v>16</v>
@@ -4415,7 +4415,7 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A80" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B80" s="1">
         <v>0</v>
@@ -4427,23 +4427,23 @@
         <v>18</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="H80" s="1"/>
       <c r="I80" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J80" s="1">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="K80" s="1">
-        <v>3000</v>
+        <v>18000</v>
       </c>
       <c r="L80" s="1">
         <v>0</v>
@@ -4453,10 +4453,10 @@
       </c>
       <c r="N80" s="1"/>
       <c r="O80" s="1">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="P80" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q80" s="1" t="s">
         <v>16</v>
@@ -4464,7 +4464,7 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A81" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B81" s="1">
         <v>0</v>
@@ -4476,23 +4476,23 @@
         <v>18</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="H81" s="1"/>
       <c r="I81" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J81" s="1">
         <v>0.5</v>
       </c>
       <c r="K81" s="1">
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="L81" s="1">
         <v>0</v>
@@ -4502,10 +4502,10 @@
       </c>
       <c r="N81" s="1"/>
       <c r="O81" s="1">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="P81" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q81" s="1" t="s">
         <v>16</v>
@@ -4513,7 +4513,7 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A82" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B82" s="1">
         <v>0</v>
@@ -4525,23 +4525,23 @@
         <v>18</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H82" s="1"/>
       <c r="I82" s="1" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="J82" s="1">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="K82" s="1">
-        <v>55000</v>
+        <v>4500</v>
       </c>
       <c r="L82" s="1">
         <v>0</v>
@@ -4551,10 +4551,10 @@
       </c>
       <c r="N82" s="1"/>
       <c r="O82" s="1">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="P82" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q82" s="1" t="s">
         <v>16</v>
@@ -4562,7 +4562,7 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A83" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B83" s="1">
         <v>0</v>
@@ -4574,23 +4574,23 @@
         <v>18</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="H83" s="1"/>
       <c r="I83" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="J83" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K83" s="1">
-        <v>55000</v>
+        <v>15000</v>
       </c>
       <c r="L83" s="1">
         <v>0</v>
@@ -4600,10 +4600,10 @@
       </c>
       <c r="N83" s="1"/>
       <c r="O83" s="1">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="P83" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q83" s="1" t="s">
         <v>16</v>
@@ -4611,7 +4611,7 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A84" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B84" s="1">
         <v>0</v>
@@ -4623,23 +4623,23 @@
         <v>18</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H84" s="1"/>
       <c r="I84" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J84" s="1">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="K84" s="1">
-        <v>2875</v>
+        <v>27000</v>
       </c>
       <c r="L84" s="1">
         <v>0</v>
@@ -4649,10 +4649,10 @@
       </c>
       <c r="N84" s="1"/>
       <c r="O84" s="1">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="P84" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q84" s="1" t="s">
         <v>16</v>
@@ -4660,7 +4660,7 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A85" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B85" s="1">
         <v>0</v>
@@ -4672,23 +4672,23 @@
         <v>18</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="H85" s="1"/>
       <c r="I85" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J85" s="1">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="K85" s="1">
-        <v>2875</v>
+        <v>6000</v>
       </c>
       <c r="L85" s="1">
         <v>0</v>
@@ -4698,10 +4698,10 @@
       </c>
       <c r="N85" s="1"/>
       <c r="O85" s="1">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="P85" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q85" s="1" t="s">
         <v>16</v>
@@ -4709,7 +4709,7 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A86" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B86" s="1">
         <v>0</v>
@@ -4721,23 +4721,23 @@
         <v>18</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H86" s="1"/>
       <c r="I86" s="1" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="J86" s="1">
-        <v>1</v>
+        <v>0.16666666999999999</v>
       </c>
       <c r="K86" s="1">
-        <v>11000</v>
+        <v>1833.3334</v>
       </c>
       <c r="L86" s="1">
         <v>0</v>
@@ -4747,10 +4747,10 @@
       </c>
       <c r="N86" s="1"/>
       <c r="O86" s="1">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="P86" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q86" s="1" t="s">
         <v>16</v>
@@ -4758,7 +4758,7 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A87" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B87" s="1">
         <v>0</v>
@@ -4770,23 +4770,23 @@
         <v>18</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="H87" s="1"/>
       <c r="I87" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J87" s="1">
         <v>1</v>
       </c>
       <c r="K87" s="1">
-        <v>10500</v>
+        <v>9000</v>
       </c>
       <c r="L87" s="1">
         <v>0</v>
@@ -4796,10 +4796,10 @@
       </c>
       <c r="N87" s="1"/>
       <c r="O87" s="1">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="P87" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q87" s="1" t="s">
         <v>16</v>
@@ -4807,7 +4807,7 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A88" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B88" s="1">
         <v>0</v>
@@ -4819,23 +4819,23 @@
         <v>18</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H88" s="1"/>
       <c r="I88" s="1" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="J88" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K88" s="1">
-        <v>11000</v>
+        <v>36000</v>
       </c>
       <c r="L88" s="1">
         <v>0</v>
@@ -4845,10 +4845,10 @@
       </c>
       <c r="N88" s="1"/>
       <c r="O88" s="1">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="P88" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q88" s="1" t="s">
         <v>16</v>
@@ -4856,7 +4856,7 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A89" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B89" s="1">
         <v>0</v>
@@ -4868,23 +4868,23 @@
         <v>18</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J89" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K89" s="1">
-        <v>4500</v>
+        <v>18000</v>
       </c>
       <c r="L89" s="1">
         <v>0</v>
@@ -4894,10 +4894,10 @@
       </c>
       <c r="N89" s="1"/>
       <c r="O89" s="1">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="P89" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q89" s="1" t="s">
         <v>16</v>
@@ -4905,7 +4905,7 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A90" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B90" s="1">
         <v>0</v>
@@ -4917,23 +4917,23 @@
         <v>18</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H90" s="1"/>
       <c r="I90" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J90" s="1">
-        <v>0.45833333999999998</v>
+        <v>1.0833333999999999</v>
       </c>
       <c r="K90" s="1">
-        <v>5270.8334999999997</v>
+        <v>12458.333000000001</v>
       </c>
       <c r="L90" s="1">
         <v>0</v>
@@ -4943,10 +4943,10 @@
       </c>
       <c r="N90" s="1"/>
       <c r="O90" s="1">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="P90" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q90" s="1" t="s">
         <v>16</v>
@@ -4954,7 +4954,7 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A91" s="2">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="B91" s="1">
         <v>0</v>
@@ -4966,21 +4966,23 @@
         <v>18</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G91" s="1"/>
+      <c r="G91" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="H91" s="1"/>
       <c r="I91" s="1" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J91" s="1">
-        <v>600</v>
+        <v>0.5</v>
       </c>
       <c r="K91" s="1">
-        <v>6300000</v>
+        <v>4500</v>
       </c>
       <c r="L91" s="1">
         <v>0</v>
@@ -4990,16 +4992,18 @@
       </c>
       <c r="N91" s="1"/>
       <c r="O91" s="1">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="P91" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q91" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="Q91" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A92" s="2">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="B92" s="1">
         <v>0</v>
@@ -5011,21 +5015,23 @@
         <v>18</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G92" s="1"/>
+      <c r="G92" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J92" s="1">
-        <v>200</v>
+        <v>3</v>
       </c>
       <c r="K92" s="1">
-        <v>2200000</v>
+        <v>27000</v>
       </c>
       <c r="L92" s="1">
         <v>0</v>
@@ -5035,16 +5041,18 @@
       </c>
       <c r="N92" s="1"/>
       <c r="O92" s="1">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="P92" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q92" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="Q92" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A93" s="2">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="B93" s="1">
         <v>0</v>
@@ -5056,21 +5064,23 @@
         <v>18</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G93" s="1"/>
+      <c r="G93" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="H93" s="1"/>
       <c r="I93" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J93" s="1">
-        <v>100</v>
+        <v>1.0833333999999999</v>
       </c>
       <c r="K93" s="1">
-        <v>450000</v>
+        <v>11916.666999999999</v>
       </c>
       <c r="L93" s="1">
         <v>0</v>
@@ -5080,16 +5090,18 @@
       </c>
       <c r="N93" s="1"/>
       <c r="O93" s="1">
-        <v>3</v>
+        <v>89</v>
       </c>
       <c r="P93" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q93" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="Q93" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A94" s="2">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="B94" s="1">
         <v>0</v>
@@ -5101,21 +5113,23 @@
         <v>18</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G94" s="1"/>
+      <c r="G94" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J94" s="1">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="K94" s="1">
-        <v>1100000</v>
+        <v>24000</v>
       </c>
       <c r="L94" s="1">
         <v>0</v>
@@ -5125,16 +5139,18 @@
       </c>
       <c r="N94" s="1"/>
       <c r="O94" s="1">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="P94" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q94" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="Q94" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A95" s="2">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="B95" s="1">
         <v>0</v>
@@ -5146,21 +5162,23 @@
         <v>18</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G95" s="1"/>
+      <c r="G95" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="J95" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K95" s="1">
-        <v>1150000</v>
+        <v>15000</v>
       </c>
       <c r="L95" s="1">
         <v>0</v>
@@ -5170,16 +5188,18 @@
       </c>
       <c r="N95" s="1"/>
       <c r="O95" s="1">
-        <v>5</v>
+        <v>91</v>
       </c>
       <c r="P95" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q95" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="Q95" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A96" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B96" s="1">
         <v>0</v>
@@ -5191,40 +5211,44 @@
         <v>18</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G96" s="1"/>
+      <c r="G96" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="H96" s="1"/>
       <c r="I96" s="1" t="s">
         <v>47</v>
       </c>
       <c r="J96" s="1">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="K96" s="1">
-        <v>1100000</v>
+        <v>22000</v>
       </c>
       <c r="L96" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="M96" s="1">
         <v>0</v>
       </c>
       <c r="N96" s="1"/>
       <c r="O96" s="1">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="P96" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q96" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="Q96" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A97" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B97" s="1">
         <v>0</v>
@@ -5236,21 +5260,23 @@
         <v>18</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G97" s="1"/>
+      <c r="G97" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="H97" s="1"/>
       <c r="I97" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J97" s="1">
-        <v>140</v>
+        <v>1</v>
       </c>
       <c r="K97" s="1">
-        <v>840000</v>
+        <v>6000</v>
       </c>
       <c r="L97" s="1">
         <v>0</v>
@@ -5260,16 +5286,18 @@
       </c>
       <c r="N97" s="1"/>
       <c r="O97" s="1">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="P97" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q97" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="Q97" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A98" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B98" s="1">
         <v>0</v>
@@ -5281,21 +5309,23 @@
         <v>18</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G98" s="1"/>
+      <c r="G98" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="H98" s="1"/>
       <c r="I98" s="1" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="J98" s="1">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K98" s="1">
-        <v>375000</v>
+        <v>4500</v>
       </c>
       <c r="L98" s="1">
         <v>0</v>
@@ -5305,16 +5335,18 @@
       </c>
       <c r="N98" s="1"/>
       <c r="O98" s="1">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="P98" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q98" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="Q98" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A99" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B99" s="1">
         <v>0</v>
@@ -5326,21 +5358,23 @@
         <v>18</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G99" s="1"/>
+      <c r="G99" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="H99" s="1"/>
       <c r="I99" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="J99" s="1">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="K99" s="1">
-        <v>375000</v>
+        <v>22000</v>
       </c>
       <c r="L99" s="1">
         <v>0</v>
@@ -5350,16 +5384,18 @@
       </c>
       <c r="N99" s="1"/>
       <c r="O99" s="1">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="P99" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q99" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="Q99" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A100" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B100" s="1">
         <v>0</v>
@@ -5371,21 +5407,23 @@
         <v>18</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G100" s="1"/>
+      <c r="G100" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="H100" s="1"/>
       <c r="I100" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J100" s="1">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="K100" s="1">
-        <v>225000</v>
+        <v>12000</v>
       </c>
       <c r="L100" s="1">
         <v>0</v>
@@ -5395,16 +5433,18 @@
       </c>
       <c r="N100" s="1"/>
       <c r="O100" s="1">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="P100" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q100" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="Q100" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A101" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B101" s="1">
         <v>0</v>
@@ -5416,21 +5456,23 @@
         <v>18</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G101" s="1"/>
+      <c r="G101" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="H101" s="1"/>
       <c r="I101" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J101" s="1">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="K101" s="1">
-        <v>225000</v>
+        <v>31500</v>
       </c>
       <c r="L101" s="1">
         <v>0</v>
@@ -5440,16 +5482,18 @@
       </c>
       <c r="N101" s="1"/>
       <c r="O101" s="1">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="P101" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q101" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="Q101" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A102" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B102" s="1">
         <v>0</v>
@@ -5461,36 +5505,36 @@
         <v>18</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="H102" s="1"/>
       <c r="I102" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="J102" s="1">
-        <v>0.58333330000000005</v>
+        <v>1</v>
       </c>
       <c r="K102" s="1">
-        <v>5250</v>
+        <v>9000</v>
       </c>
       <c r="L102" s="1">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="M102" s="1">
         <v>0</v>
       </c>
       <c r="N102" s="1"/>
       <c r="O102" s="1">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="P102" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q102" s="1" t="s">
         <v>16</v>
@@ -5498,7 +5542,7 @@
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A103" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B103" s="1">
         <v>0</v>
@@ -5510,23 +5554,23 @@
         <v>18</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="H103" s="1"/>
       <c r="I103" s="1" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="J103" s="1">
-        <v>6</v>
+        <v>0.25</v>
       </c>
       <c r="K103" s="1">
-        <v>66000</v>
+        <v>2875</v>
       </c>
       <c r="L103" s="1">
         <v>0</v>
@@ -5536,10 +5580,10 @@
       </c>
       <c r="N103" s="1"/>
       <c r="O103" s="1">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="P103" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q103" s="1" t="s">
         <v>16</v>
@@ -5547,7 +5591,7 @@
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A104" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B104" s="1">
         <v>0</v>
@@ -5559,23 +5603,23 @@
         <v>18</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="H104" s="1"/>
       <c r="I104" s="1" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="J104" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K104" s="1">
-        <v>66000</v>
+        <v>21000</v>
       </c>
       <c r="L104" s="1">
         <v>0</v>
@@ -5585,10 +5629,10 @@
       </c>
       <c r="N104" s="1"/>
       <c r="O104" s="1">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="P104" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q104" s="1" t="s">
         <v>16</v>
@@ -5596,7 +5640,7 @@
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A105" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B105" s="1">
         <v>0</v>
@@ -5608,23 +5652,23 @@
         <v>18</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H105" s="1"/>
       <c r="I105" s="1" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="J105" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K105" s="1">
-        <v>66000</v>
+        <v>10500</v>
       </c>
       <c r="L105" s="1">
         <v>0</v>
@@ -5634,10 +5678,10 @@
       </c>
       <c r="N105" s="1"/>
       <c r="O105" s="1">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="P105" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q105" s="1" t="s">
         <v>16</v>
@@ -5645,7 +5689,7 @@
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A106" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B106" s="1">
         <v>0</v>
@@ -5657,23 +5701,23 @@
         <v>18</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H106" s="1"/>
       <c r="I106" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J106" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K106" s="1">
-        <v>10500</v>
+        <v>3000</v>
       </c>
       <c r="L106" s="1">
         <v>0</v>
@@ -5683,10 +5727,10 @@
       </c>
       <c r="N106" s="1"/>
       <c r="O106" s="1">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="P106" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q106" s="1" t="s">
         <v>16</v>
@@ -5694,7 +5738,7 @@
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A107" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B107" s="1">
         <v>0</v>
@@ -5706,23 +5750,23 @@
         <v>18</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H107" s="1"/>
       <c r="I107" s="1" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="J107" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K107" s="1">
-        <v>12000</v>
+        <v>9000</v>
       </c>
       <c r="L107" s="1">
         <v>0</v>
@@ -5732,10 +5776,10 @@
       </c>
       <c r="N107" s="1"/>
       <c r="O107" s="1">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="P107" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q107" s="1" t="s">
         <v>16</v>
@@ -5743,7 +5787,7 @@
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A108" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B108" s="1">
         <v>0</v>
@@ -5755,23 +5799,23 @@
         <v>18</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H108" s="1"/>
       <c r="I108" s="1" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="J108" s="1">
-        <v>7</v>
+        <v>0.5</v>
       </c>
       <c r="K108" s="1">
-        <v>77000</v>
+        <v>3000</v>
       </c>
       <c r="L108" s="1">
         <v>0</v>
@@ -5781,10 +5825,10 @@
       </c>
       <c r="N108" s="1"/>
       <c r="O108" s="1">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="P108" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q108" s="1" t="s">
         <v>16</v>
@@ -5792,7 +5836,7 @@
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A109" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B109" s="1">
         <v>0</v>
@@ -5804,23 +5848,23 @@
         <v>18</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H109" s="1"/>
       <c r="I109" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J109" s="1">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="K109" s="1">
-        <v>12000</v>
+        <v>3000</v>
       </c>
       <c r="L109" s="1">
         <v>0</v>
@@ -5830,10 +5874,10 @@
       </c>
       <c r="N109" s="1"/>
       <c r="O109" s="1">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="P109" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q109" s="1" t="s">
         <v>16</v>
@@ -5841,7 +5885,7 @@
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A110" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B110" s="1">
         <v>0</v>
@@ -5853,23 +5897,23 @@
         <v>18</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="H110" s="1"/>
       <c r="I110" s="1" t="s">
         <v>47</v>
       </c>
       <c r="J110" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K110" s="1">
-        <v>11000</v>
+        <v>55000</v>
       </c>
       <c r="L110" s="1">
         <v>0</v>
@@ -5879,10 +5923,10 @@
       </c>
       <c r="N110" s="1"/>
       <c r="O110" s="1">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="P110" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q110" s="1" t="s">
         <v>16</v>
@@ -5890,7 +5934,7 @@
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A111" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B111" s="1">
         <v>0</v>
@@ -5902,23 +5946,23 @@
         <v>18</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="H111" s="1"/>
       <c r="I111" s="1" t="s">
         <v>47</v>
       </c>
       <c r="J111" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K111" s="1">
-        <v>22000</v>
+        <v>55000</v>
       </c>
       <c r="L111" s="1">
         <v>0</v>
@@ -5928,10 +5972,10 @@
       </c>
       <c r="N111" s="1"/>
       <c r="O111" s="1">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="P111" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q111" s="1" t="s">
         <v>16</v>
@@ -5939,7 +5983,7 @@
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A112" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B112" s="1">
         <v>0</v>
@@ -5951,23 +5995,23 @@
         <v>18</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H112" s="1"/>
       <c r="I112" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J112" s="1">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K112" s="1">
-        <v>6000</v>
+        <v>2875</v>
       </c>
       <c r="L112" s="1">
         <v>0</v>
@@ -5977,10 +6021,10 @@
       </c>
       <c r="N112" s="1"/>
       <c r="O112" s="1">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="P112" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q112" s="1" t="s">
         <v>16</v>
@@ -5988,7 +6032,7 @@
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A113" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B113" s="1">
         <v>0</v>
@@ -6000,7 +6044,7 @@
         <v>18</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>20</v>
@@ -6010,13 +6054,13 @@
       </c>
       <c r="H113" s="1"/>
       <c r="I113" s="1" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="J113" s="1">
-        <v>10</v>
+        <v>0.25</v>
       </c>
       <c r="K113" s="1">
-        <v>110000</v>
+        <v>2875</v>
       </c>
       <c r="L113" s="1">
         <v>0</v>
@@ -6026,10 +6070,10 @@
       </c>
       <c r="N113" s="1"/>
       <c r="O113" s="1">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="P113" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q113" s="1" t="s">
         <v>16</v>
@@ -6037,7 +6081,7 @@
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A114" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B114" s="1">
         <v>0</v>
@@ -6049,23 +6093,23 @@
         <v>18</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H114" s="1"/>
       <c r="I114" s="1" t="s">
         <v>47</v>
       </c>
       <c r="J114" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K114" s="1">
-        <v>121000</v>
+        <v>11000</v>
       </c>
       <c r="L114" s="1">
         <v>0</v>
@@ -6075,10 +6119,10 @@
       </c>
       <c r="N114" s="1"/>
       <c r="O114" s="1">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="P114" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q114" s="1" t="s">
         <v>16</v>
@@ -6086,7 +6130,7 @@
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A115" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B115" s="1">
         <v>0</v>
@@ -6098,23 +6142,23 @@
         <v>18</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="H115" s="1"/>
       <c r="I115" s="1" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="J115" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K115" s="1">
-        <v>55000</v>
+        <v>10500</v>
       </c>
       <c r="L115" s="1">
         <v>0</v>
@@ -6124,10 +6168,10 @@
       </c>
       <c r="N115" s="1"/>
       <c r="O115" s="1">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="P115" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q115" s="1" t="s">
         <v>16</v>
@@ -6135,7 +6179,7 @@
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A116" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B116" s="1">
         <v>0</v>
@@ -6147,23 +6191,23 @@
         <v>18</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="H116" s="1"/>
       <c r="I116" s="1" t="s">
         <v>47</v>
       </c>
       <c r="J116" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K116" s="1">
-        <v>55000</v>
+        <v>11000</v>
       </c>
       <c r="L116" s="1">
         <v>0</v>
@@ -6173,10 +6217,10 @@
       </c>
       <c r="N116" s="1"/>
       <c r="O116" s="1">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="P116" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q116" s="1" t="s">
         <v>16</v>
@@ -6184,7 +6228,7 @@
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A117" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B117" s="1">
         <v>0</v>
@@ -6196,23 +6240,23 @@
         <v>18</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="H117" s="1"/>
       <c r="I117" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="J117" s="1">
         <v>1</v>
       </c>
       <c r="K117" s="1">
-        <v>6000</v>
+        <v>4500</v>
       </c>
       <c r="L117" s="1">
         <v>0</v>
@@ -6222,10 +6266,10 @@
       </c>
       <c r="N117" s="1"/>
       <c r="O117" s="1">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="P117" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q117" s="1" t="s">
         <v>16</v>
@@ -6233,7 +6277,7 @@
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A118" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B118" s="1">
         <v>0</v>
@@ -6245,23 +6289,23 @@
         <v>18</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="H118" s="1"/>
       <c r="I118" s="1" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="J118" s="1">
-        <v>15</v>
+        <v>0.45833333999999998</v>
       </c>
       <c r="K118" s="1">
-        <v>165000</v>
+        <v>5270.8334999999997</v>
       </c>
       <c r="L118" s="1">
         <v>0</v>
@@ -6271,10 +6315,10 @@
       </c>
       <c r="N118" s="1"/>
       <c r="O118" s="1">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="P118" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q118" s="1" t="s">
         <v>16</v>
@@ -6294,23 +6338,21 @@
         <v>18</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G119" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="G119" s="1"/>
       <c r="H119" s="1"/>
       <c r="I119" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J119" s="1">
-        <v>1</v>
+        <v>600</v>
       </c>
       <c r="K119" s="1">
-        <v>4500</v>
+        <v>6300000</v>
       </c>
       <c r="L119" s="1">
         <v>0</v>
@@ -6320,14 +6362,12 @@
       </c>
       <c r="N119" s="1"/>
       <c r="O119" s="1">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="P119" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q119" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="Q119" s="1"/>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A120" s="2">
@@ -6343,23 +6383,21 @@
         <v>18</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G120" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="G120" s="1"/>
       <c r="H120" s="1"/>
       <c r="I120" s="1" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="J120" s="1">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="K120" s="1">
-        <v>110000</v>
+        <v>2200000</v>
       </c>
       <c r="L120" s="1">
         <v>0</v>
@@ -6369,14 +6407,12 @@
       </c>
       <c r="N120" s="1"/>
       <c r="O120" s="1">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="P120" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q120" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="Q120" s="1"/>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A121" s="2">
@@ -6392,7 +6428,7 @@
         <v>18</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>20</v>
@@ -6400,13 +6436,13 @@
       <c r="G121" s="1"/>
       <c r="H121" s="1"/>
       <c r="I121" s="1" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="J121" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K121" s="1">
-        <v>445500</v>
+        <v>450000</v>
       </c>
       <c r="L121" s="1">
         <v>0</v>
@@ -6416,10 +6452,10 @@
       </c>
       <c r="N121" s="1"/>
       <c r="O121" s="1">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="P121" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q121" s="1"/>
     </row>
@@ -6437,7 +6473,7 @@
         <v>18</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>20</v>
@@ -6445,7 +6481,7 @@
       <c r="G122" s="1"/>
       <c r="H122" s="1"/>
       <c r="I122" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J122" s="1">
         <v>100</v>
@@ -6461,10 +6497,10 @@
       </c>
       <c r="N122" s="1"/>
       <c r="O122" s="1">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="P122" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q122" s="1"/>
     </row>
@@ -6482,7 +6518,7 @@
         <v>18</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>20</v>
@@ -6490,13 +6526,13 @@
       <c r="G123" s="1"/>
       <c r="H123" s="1"/>
       <c r="I123" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J123" s="1">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="K123" s="1">
-        <v>804000</v>
+        <v>1150000</v>
       </c>
       <c r="L123" s="1">
         <v>0</v>
@@ -6506,10 +6542,10 @@
       </c>
       <c r="N123" s="1"/>
       <c r="O123" s="1">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="P123" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q123" s="1"/>
     </row>
@@ -6527,7 +6563,7 @@
         <v>18</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>20</v>
@@ -6538,10 +6574,10 @@
         <v>47</v>
       </c>
       <c r="J124" s="1">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="K124" s="1">
-        <v>176000</v>
+        <v>1100000</v>
       </c>
       <c r="L124" s="1">
         <v>0</v>
@@ -6551,10 +6587,10 @@
       </c>
       <c r="N124" s="1"/>
       <c r="O124" s="1">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="P124" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q124" s="1"/>
     </row>
@@ -6572,7 +6608,7 @@
         <v>18</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>20</v>
@@ -6580,13 +6616,13 @@
       <c r="G125" s="1"/>
       <c r="H125" s="1"/>
       <c r="I125" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J125" s="1">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="K125" s="1">
-        <v>2200000</v>
+        <v>840000</v>
       </c>
       <c r="L125" s="1">
         <v>0</v>
@@ -6596,10 +6632,10 @@
       </c>
       <c r="N125" s="1"/>
       <c r="O125" s="1">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="P125" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q125" s="1"/>
     </row>
@@ -6617,7 +6653,7 @@
         <v>18</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>20</v>
@@ -6625,13 +6661,13 @@
       <c r="G126" s="1"/>
       <c r="H126" s="1"/>
       <c r="I126" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="J126" s="1">
-        <v>24.416665999999999</v>
+        <v>25</v>
       </c>
       <c r="K126" s="1">
-        <v>219750</v>
+        <v>375000</v>
       </c>
       <c r="L126" s="1">
         <v>0</v>
@@ -6641,10 +6677,10 @@
       </c>
       <c r="N126" s="1"/>
       <c r="O126" s="1">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="P126" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q126" s="1"/>
     </row>
@@ -6662,7 +6698,7 @@
         <v>18</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>20</v>
@@ -6670,7 +6706,7 @@
       <c r="G127" s="1"/>
       <c r="H127" s="1"/>
       <c r="I127" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="J127" s="1">
         <v>25</v>
@@ -6686,10 +6722,10 @@
       </c>
       <c r="N127" s="1"/>
       <c r="O127" s="1">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="P127" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q127" s="1"/>
     </row>
@@ -6707,7 +6743,7 @@
         <v>18</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>20</v>
@@ -6715,7 +6751,7 @@
       <c r="G128" s="1"/>
       <c r="H128" s="1"/>
       <c r="I128" s="1" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="J128" s="1">
         <v>25</v>
@@ -6731,10 +6767,10 @@
       </c>
       <c r="N128" s="1"/>
       <c r="O128" s="1">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="P128" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q128" s="1"/>
     </row>
@@ -6752,7 +6788,7 @@
         <v>18</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>20</v>
@@ -6760,13 +6796,13 @@
       <c r="G129" s="1"/>
       <c r="H129" s="1"/>
       <c r="I129" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="J129" s="1">
         <v>25</v>
       </c>
       <c r="K129" s="1">
-        <v>375000</v>
+        <v>225000</v>
       </c>
       <c r="L129" s="1">
         <v>0</v>
@@ -6776,10 +6812,10 @@
       </c>
       <c r="N129" s="1"/>
       <c r="O129" s="1">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="P129" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q129" s="1"/>
     </row>
@@ -6802,31 +6838,35 @@
       <c r="F130" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G130" s="1"/>
+      <c r="G130" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="H130" s="1"/>
       <c r="I130" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="J130" s="1">
-        <v>100</v>
+        <v>0.58333330000000005</v>
       </c>
       <c r="K130" s="1">
-        <v>1150000</v>
+        <v>5250</v>
       </c>
       <c r="L130" s="1">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="M130" s="1">
         <v>0</v>
       </c>
       <c r="N130" s="1"/>
       <c r="O130" s="1">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="P130" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q130" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="Q130" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A131" s="2">
@@ -6847,16 +6887,18 @@
       <c r="F131" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G131" s="1"/>
+      <c r="G131" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="H131" s="1"/>
       <c r="I131" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="J131" s="1">
-        <v>599</v>
+        <v>6</v>
       </c>
       <c r="K131" s="1">
-        <v>6289500</v>
+        <v>66000</v>
       </c>
       <c r="L131" s="1">
         <v>0</v>
@@ -6866,12 +6908,1342 @@
       </c>
       <c r="N131" s="1"/>
       <c r="O131" s="1">
+        <v>13</v>
+      </c>
+      <c r="P131" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q131" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A132" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B132" s="1">
+        <v>0</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H132" s="1"/>
+      <c r="I132" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J132" s="1">
+        <v>6</v>
+      </c>
+      <c r="K132" s="1">
+        <v>66000</v>
+      </c>
+      <c r="L132" s="1">
+        <v>0</v>
+      </c>
+      <c r="M132" s="1">
+        <v>0</v>
+      </c>
+      <c r="N132" s="1"/>
+      <c r="O132" s="1">
+        <v>14</v>
+      </c>
+      <c r="P132" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q132" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A133" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B133" s="1">
+        <v>0</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H133" s="1"/>
+      <c r="I133" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J133" s="1">
+        <v>6</v>
+      </c>
+      <c r="K133" s="1">
+        <v>66000</v>
+      </c>
+      <c r="L133" s="1">
+        <v>0</v>
+      </c>
+      <c r="M133" s="1">
+        <v>0</v>
+      </c>
+      <c r="N133" s="1"/>
+      <c r="O133" s="1">
+        <v>15</v>
+      </c>
+      <c r="P133" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q133" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A134" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B134" s="1">
+        <v>0</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H134" s="1"/>
+      <c r="I134" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J134" s="1">
+        <v>1</v>
+      </c>
+      <c r="K134" s="1">
+        <v>10500</v>
+      </c>
+      <c r="L134" s="1">
+        <v>0</v>
+      </c>
+      <c r="M134" s="1">
+        <v>0</v>
+      </c>
+      <c r="N134" s="1"/>
+      <c r="O134" s="1">
+        <v>16</v>
+      </c>
+      <c r="P134" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q134" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A135" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B135" s="1">
+        <v>0</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H135" s="1"/>
+      <c r="I135" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J135" s="1">
+        <v>2</v>
+      </c>
+      <c r="K135" s="1">
+        <v>12000</v>
+      </c>
+      <c r="L135" s="1">
+        <v>0</v>
+      </c>
+      <c r="M135" s="1">
+        <v>0</v>
+      </c>
+      <c r="N135" s="1"/>
+      <c r="O135" s="1">
+        <v>17</v>
+      </c>
+      <c r="P135" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q135" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A136" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B136" s="1">
+        <v>0</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H136" s="1"/>
+      <c r="I136" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J136" s="1">
+        <v>7</v>
+      </c>
+      <c r="K136" s="1">
+        <v>77000</v>
+      </c>
+      <c r="L136" s="1">
+        <v>0</v>
+      </c>
+      <c r="M136" s="1">
+        <v>0</v>
+      </c>
+      <c r="N136" s="1"/>
+      <c r="O136" s="1">
+        <v>18</v>
+      </c>
+      <c r="P136" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q136" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A137" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B137" s="1">
+        <v>0</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H137" s="1"/>
+      <c r="I137" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J137" s="1">
+        <v>2</v>
+      </c>
+      <c r="K137" s="1">
+        <v>12000</v>
+      </c>
+      <c r="L137" s="1">
+        <v>0</v>
+      </c>
+      <c r="M137" s="1">
+        <v>0</v>
+      </c>
+      <c r="N137" s="1"/>
+      <c r="O137" s="1">
+        <v>19</v>
+      </c>
+      <c r="P137" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q137" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A138" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B138" s="1">
+        <v>0</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H138" s="1"/>
+      <c r="I138" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J138" s="1">
+        <v>1</v>
+      </c>
+      <c r="K138" s="1">
+        <v>11000</v>
+      </c>
+      <c r="L138" s="1">
+        <v>0</v>
+      </c>
+      <c r="M138" s="1">
+        <v>0</v>
+      </c>
+      <c r="N138" s="1"/>
+      <c r="O138" s="1">
+        <v>20</v>
+      </c>
+      <c r="P138" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q138" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A139" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B139" s="1">
+        <v>0</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H139" s="1"/>
+      <c r="I139" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J139" s="1">
+        <v>2</v>
+      </c>
+      <c r="K139" s="1">
+        <v>22000</v>
+      </c>
+      <c r="L139" s="1">
+        <v>0</v>
+      </c>
+      <c r="M139" s="1">
+        <v>0</v>
+      </c>
+      <c r="N139" s="1"/>
+      <c r="O139" s="1">
+        <v>21</v>
+      </c>
+      <c r="P139" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q139" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A140" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B140" s="1">
+        <v>0</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H140" s="1"/>
+      <c r="I140" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J140" s="1">
+        <v>1</v>
+      </c>
+      <c r="K140" s="1">
+        <v>6000</v>
+      </c>
+      <c r="L140" s="1">
+        <v>0</v>
+      </c>
+      <c r="M140" s="1">
+        <v>0</v>
+      </c>
+      <c r="N140" s="1"/>
+      <c r="O140" s="1">
+        <v>22</v>
+      </c>
+      <c r="P140" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q140" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A141" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B141" s="1">
+        <v>0</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H141" s="1"/>
+      <c r="I141" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J141" s="1">
+        <v>10</v>
+      </c>
+      <c r="K141" s="1">
+        <v>110000</v>
+      </c>
+      <c r="L141" s="1">
+        <v>0</v>
+      </c>
+      <c r="M141" s="1">
+        <v>0</v>
+      </c>
+      <c r="N141" s="1"/>
+      <c r="O141" s="1">
+        <v>23</v>
+      </c>
+      <c r="P141" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q141" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A142" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B142" s="1">
+        <v>0</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H142" s="1"/>
+      <c r="I142" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J142" s="1">
+        <v>11</v>
+      </c>
+      <c r="K142" s="1">
+        <v>121000</v>
+      </c>
+      <c r="L142" s="1">
+        <v>0</v>
+      </c>
+      <c r="M142" s="1">
+        <v>0</v>
+      </c>
+      <c r="N142" s="1"/>
+      <c r="O142" s="1">
+        <v>24</v>
+      </c>
+      <c r="P142" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q142" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A143" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B143" s="1">
+        <v>0</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H143" s="1"/>
+      <c r="I143" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J143" s="1">
+        <v>5</v>
+      </c>
+      <c r="K143" s="1">
+        <v>55000</v>
+      </c>
+      <c r="L143" s="1">
+        <v>0</v>
+      </c>
+      <c r="M143" s="1">
+        <v>0</v>
+      </c>
+      <c r="N143" s="1"/>
+      <c r="O143" s="1">
+        <v>25</v>
+      </c>
+      <c r="P143" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q143" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A144" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B144" s="1">
+        <v>0</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H144" s="1"/>
+      <c r="I144" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J144" s="1">
+        <v>5</v>
+      </c>
+      <c r="K144" s="1">
+        <v>55000</v>
+      </c>
+      <c r="L144" s="1">
+        <v>0</v>
+      </c>
+      <c r="M144" s="1">
+        <v>0</v>
+      </c>
+      <c r="N144" s="1"/>
+      <c r="O144" s="1">
+        <v>26</v>
+      </c>
+      <c r="P144" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q144" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A145" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B145" s="1">
+        <v>0</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H145" s="1"/>
+      <c r="I145" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J145" s="1">
+        <v>1</v>
+      </c>
+      <c r="K145" s="1">
+        <v>6000</v>
+      </c>
+      <c r="L145" s="1">
+        <v>0</v>
+      </c>
+      <c r="M145" s="1">
+        <v>0</v>
+      </c>
+      <c r="N145" s="1"/>
+      <c r="O145" s="1">
+        <v>27</v>
+      </c>
+      <c r="P145" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q145" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A146" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B146" s="1">
+        <v>0</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H146" s="1"/>
+      <c r="I146" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J146" s="1">
+        <v>15</v>
+      </c>
+      <c r="K146" s="1">
+        <v>165000</v>
+      </c>
+      <c r="L146" s="1">
+        <v>0</v>
+      </c>
+      <c r="M146" s="1">
+        <v>0</v>
+      </c>
+      <c r="N146" s="1"/>
+      <c r="O146" s="1">
+        <v>28</v>
+      </c>
+      <c r="P146" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q146" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A147" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B147" s="1">
+        <v>0</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H147" s="1"/>
+      <c r="I147" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P131" s="1" t="s">
+      <c r="J147" s="1">
+        <v>1</v>
+      </c>
+      <c r="K147" s="1">
+        <v>4500</v>
+      </c>
+      <c r="L147" s="1">
+        <v>0</v>
+      </c>
+      <c r="M147" s="1">
+        <v>0</v>
+      </c>
+      <c r="N147" s="1"/>
+      <c r="O147" s="1">
+        <v>29</v>
+      </c>
+      <c r="P147" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q147" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A148" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B148" s="1">
+        <v>0</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H148" s="1"/>
+      <c r="I148" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J148" s="1">
+        <v>10</v>
+      </c>
+      <c r="K148" s="1">
+        <v>110000</v>
+      </c>
+      <c r="L148" s="1">
+        <v>0</v>
+      </c>
+      <c r="M148" s="1">
+        <v>0</v>
+      </c>
+      <c r="N148" s="1"/>
+      <c r="O148" s="1">
+        <v>30</v>
+      </c>
+      <c r="P148" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q148" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="149" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A149" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B149" s="1">
+        <v>0</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G149" s="1"/>
+      <c r="H149" s="1"/>
+      <c r="I149" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J149" s="1">
+        <v>99</v>
+      </c>
+      <c r="K149" s="1">
+        <v>445500</v>
+      </c>
+      <c r="L149" s="1">
+        <v>0</v>
+      </c>
+      <c r="M149" s="1">
+        <v>0</v>
+      </c>
+      <c r="N149" s="1"/>
+      <c r="O149" s="1">
+        <v>31</v>
+      </c>
+      <c r="P149" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q149" s="1"/>
+    </row>
+    <row r="150" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A150" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B150" s="1">
+        <v>0</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G150" s="1"/>
+      <c r="H150" s="1"/>
+      <c r="I150" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J150" s="1">
+        <v>100</v>
+      </c>
+      <c r="K150" s="1">
+        <v>1100000</v>
+      </c>
+      <c r="L150" s="1">
+        <v>0</v>
+      </c>
+      <c r="M150" s="1">
+        <v>0</v>
+      </c>
+      <c r="N150" s="1"/>
+      <c r="O150" s="1">
+        <v>32</v>
+      </c>
+      <c r="P150" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q150" s="1"/>
+    </row>
+    <row r="151" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A151" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B151" s="1">
+        <v>0</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G151" s="1"/>
+      <c r="H151" s="1"/>
+      <c r="I151" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J151" s="1">
+        <v>134</v>
+      </c>
+      <c r="K151" s="1">
+        <v>804000</v>
+      </c>
+      <c r="L151" s="1">
+        <v>0</v>
+      </c>
+      <c r="M151" s="1">
+        <v>0</v>
+      </c>
+      <c r="N151" s="1"/>
+      <c r="O151" s="1">
+        <v>33</v>
+      </c>
+      <c r="P151" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q151" s="1"/>
+    </row>
+    <row r="152" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A152" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B152" s="1">
+        <v>0</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G152" s="1"/>
+      <c r="H152" s="1"/>
+      <c r="I152" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J152" s="1">
+        <v>16</v>
+      </c>
+      <c r="K152" s="1">
+        <v>176000</v>
+      </c>
+      <c r="L152" s="1">
+        <v>0</v>
+      </c>
+      <c r="M152" s="1">
+        <v>0</v>
+      </c>
+      <c r="N152" s="1"/>
+      <c r="O152" s="1">
+        <v>34</v>
+      </c>
+      <c r="P152" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q152" s="1"/>
+    </row>
+    <row r="153" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A153" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B153" s="1">
+        <v>0</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G153" s="1"/>
+      <c r="H153" s="1"/>
+      <c r="I153" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J153" s="1">
+        <v>200</v>
+      </c>
+      <c r="K153" s="1">
+        <v>2200000</v>
+      </c>
+      <c r="L153" s="1">
+        <v>0</v>
+      </c>
+      <c r="M153" s="1">
+        <v>0</v>
+      </c>
+      <c r="N153" s="1"/>
+      <c r="O153" s="1">
+        <v>35</v>
+      </c>
+      <c r="P153" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q153" s="1"/>
+    </row>
+    <row r="154" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A154" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B154" s="1">
+        <v>0</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G154" s="1"/>
+      <c r="H154" s="1"/>
+      <c r="I154" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J154" s="1">
+        <v>24.416665999999999</v>
+      </c>
+      <c r="K154" s="1">
+        <v>219750</v>
+      </c>
+      <c r="L154" s="1">
+        <v>0</v>
+      </c>
+      <c r="M154" s="1">
+        <v>0</v>
+      </c>
+      <c r="N154" s="1"/>
+      <c r="O154" s="1">
+        <v>36</v>
+      </c>
+      <c r="P154" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q154" s="1"/>
+    </row>
+    <row r="155" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A155" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B155" s="1">
+        <v>0</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G155" s="1"/>
+      <c r="H155" s="1"/>
+      <c r="I155" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J155" s="1">
+        <v>25</v>
+      </c>
+      <c r="K155" s="1">
+        <v>375000</v>
+      </c>
+      <c r="L155" s="1">
+        <v>0</v>
+      </c>
+      <c r="M155" s="1">
+        <v>0</v>
+      </c>
+      <c r="N155" s="1"/>
+      <c r="O155" s="1">
+        <v>37</v>
+      </c>
+      <c r="P155" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q155" s="1"/>
+    </row>
+    <row r="156" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A156" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B156" s="1">
+        <v>0</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G156" s="1"/>
+      <c r="H156" s="1"/>
+      <c r="I156" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J156" s="1">
+        <v>25</v>
+      </c>
+      <c r="K156" s="1">
+        <v>225000</v>
+      </c>
+      <c r="L156" s="1">
+        <v>0</v>
+      </c>
+      <c r="M156" s="1">
+        <v>0</v>
+      </c>
+      <c r="N156" s="1"/>
+      <c r="O156" s="1">
+        <v>38</v>
+      </c>
+      <c r="P156" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q156" s="1"/>
+    </row>
+    <row r="157" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A157" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B157" s="1">
+        <v>0</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G157" s="1"/>
+      <c r="H157" s="1"/>
+      <c r="I157" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J157" s="1">
+        <v>25</v>
+      </c>
+      <c r="K157" s="1">
+        <v>375000</v>
+      </c>
+      <c r="L157" s="1">
+        <v>0</v>
+      </c>
+      <c r="M157" s="1">
+        <v>0</v>
+      </c>
+      <c r="N157" s="1"/>
+      <c r="O157" s="1">
+        <v>39</v>
+      </c>
+      <c r="P157" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q157" s="1"/>
+    </row>
+    <row r="158" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A158" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B158" s="1">
+        <v>0</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G158" s="1"/>
+      <c r="H158" s="1"/>
+      <c r="I158" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J158" s="1">
+        <v>100</v>
+      </c>
+      <c r="K158" s="1">
+        <v>1150000</v>
+      </c>
+      <c r="L158" s="1">
+        <v>0</v>
+      </c>
+      <c r="M158" s="1">
+        <v>0</v>
+      </c>
+      <c r="N158" s="1"/>
+      <c r="O158" s="1">
+        <v>40</v>
+      </c>
+      <c r="P158" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q158" s="1"/>
+    </row>
+    <row r="159" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A159" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B159" s="1">
+        <v>0</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G159" s="1"/>
+      <c r="H159" s="1"/>
+      <c r="I159" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="Q131" s="1"/>
+      <c r="J159" s="1">
+        <v>599</v>
+      </c>
+      <c r="K159" s="1">
+        <v>6289500</v>
+      </c>
+      <c r="L159" s="1">
+        <v>0</v>
+      </c>
+      <c r="M159" s="1">
+        <v>0</v>
+      </c>
+      <c r="N159" s="1"/>
+      <c r="O159" s="1">
+        <v>41</v>
+      </c>
+      <c r="P159" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q159" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C060F6EC-E054-4160-B669-4885555410F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAFDDB29-4D9F-4042-A695-513D185323A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1219" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="49">
   <si>
     <t>Date</t>
   </si>
@@ -553,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q159"/>
+  <dimension ref="A1:Q169"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.3984375" customWidth="1"/>
@@ -2001,11 +2001,9 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A30" s="2">
-        <v>46224</v>
-      </c>
-      <c r="B30" s="1">
-        <v>0</v>
-      </c>
+        <v>46225</v>
+      </c>
+      <c r="B30" s="1"/>
       <c r="C30" s="1" t="s">
         <v>17</v>
       </c>
@@ -2021,13 +2019,13 @@
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="J30" s="1">
-        <v>95</v>
+        <v>99.6</v>
       </c>
       <c r="K30" s="1">
-        <v>427500</v>
+        <v>1095600</v>
       </c>
       <c r="L30" s="1">
         <v>0</v>
@@ -2037,7 +2035,7 @@
       </c>
       <c r="N30" s="1"/>
       <c r="O30" s="1">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="P30" s="1" t="s">
         <v>23</v>
@@ -2046,11 +2044,9 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A31" s="2">
-        <v>46224</v>
-      </c>
-      <c r="B31" s="1">
-        <v>0</v>
-      </c>
+        <v>46225</v>
+      </c>
+      <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
         <v>17</v>
       </c>
@@ -2066,13 +2062,13 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J31" s="1">
-        <v>100</v>
+        <v>103.5</v>
       </c>
       <c r="K31" s="1">
-        <v>1100000</v>
+        <v>621000</v>
       </c>
       <c r="L31" s="1">
         <v>0</v>
@@ -2082,7 +2078,7 @@
       </c>
       <c r="N31" s="1"/>
       <c r="O31" s="1">
-        <v>93</v>
+        <v>160</v>
       </c>
       <c r="P31" s="1" t="s">
         <v>23</v>
@@ -2091,11 +2087,9 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A32" s="2">
-        <v>46224</v>
-      </c>
-      <c r="B32" s="1">
-        <v>0</v>
-      </c>
+        <v>46225</v>
+      </c>
+      <c r="B32" s="1"/>
       <c r="C32" s="1" t="s">
         <v>17</v>
       </c>
@@ -2111,13 +2105,13 @@
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J32" s="1">
-        <v>107.5</v>
+        <v>192.5</v>
       </c>
       <c r="K32" s="1">
-        <v>645000</v>
+        <v>2117500</v>
       </c>
       <c r="L32" s="1">
         <v>0</v>
@@ -2127,7 +2121,7 @@
       </c>
       <c r="N32" s="1"/>
       <c r="O32" s="1">
-        <v>94</v>
+        <v>161</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>23</v>
@@ -2136,11 +2130,9 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A33" s="2">
-        <v>46224</v>
-      </c>
-      <c r="B33" s="1">
-        <v>0</v>
-      </c>
+        <v>46225</v>
+      </c>
+      <c r="B33" s="1"/>
       <c r="C33" s="1" t="s">
         <v>17</v>
       </c>
@@ -2156,13 +2148,13 @@
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J33" s="1">
-        <v>194.16667000000001</v>
+        <v>19.916665999999999</v>
       </c>
       <c r="K33" s="1">
-        <v>2135833.2000000002</v>
+        <v>179250</v>
       </c>
       <c r="L33" s="1">
         <v>0</v>
@@ -2172,7 +2164,7 @@
       </c>
       <c r="N33" s="1"/>
       <c r="O33" s="1">
-        <v>95</v>
+        <v>162</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>23</v>
@@ -2181,11 +2173,9 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A34" s="2">
-        <v>46224</v>
-      </c>
-      <c r="B34" s="1">
-        <v>0</v>
-      </c>
+        <v>46225</v>
+      </c>
+      <c r="B34" s="1"/>
       <c r="C34" s="1" t="s">
         <v>17</v>
       </c>
@@ -2201,13 +2191,13 @@
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J34" s="1">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="K34" s="1">
-        <v>345000</v>
+        <v>427500</v>
       </c>
       <c r="L34" s="1">
         <v>0</v>
@@ -2217,7 +2207,7 @@
       </c>
       <c r="N34" s="1"/>
       <c r="O34" s="1">
-        <v>96</v>
+        <v>163</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>23</v>
@@ -2226,11 +2216,9 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A35" s="2">
-        <v>46224</v>
-      </c>
-      <c r="B35" s="1">
-        <v>0</v>
-      </c>
+        <v>46225</v>
+      </c>
+      <c r="B35" s="1"/>
       <c r="C35" s="1" t="s">
         <v>17</v>
       </c>
@@ -2246,13 +2234,13 @@
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J35" s="1">
-        <v>21.916665999999999</v>
+        <v>23</v>
       </c>
       <c r="K35" s="1">
-        <v>197250</v>
+        <v>345000</v>
       </c>
       <c r="L35" s="1">
         <v>0</v>
@@ -2262,7 +2250,7 @@
       </c>
       <c r="N35" s="1"/>
       <c r="O35" s="1">
-        <v>97</v>
+        <v>164</v>
       </c>
       <c r="P35" s="1" t="s">
         <v>23</v>
@@ -2271,11 +2259,9 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A36" s="2">
-        <v>46224</v>
-      </c>
-      <c r="B36" s="1">
-        <v>0</v>
-      </c>
+        <v>46225</v>
+      </c>
+      <c r="B36" s="1"/>
       <c r="C36" s="1" t="s">
         <v>17</v>
       </c>
@@ -2307,7 +2293,7 @@
       </c>
       <c r="N36" s="1"/>
       <c r="O36" s="1">
-        <v>98</v>
+        <v>165</v>
       </c>
       <c r="P36" s="1" t="s">
         <v>23</v>
@@ -2316,11 +2302,9 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A37" s="2">
-        <v>46224</v>
-      </c>
-      <c r="B37" s="1">
-        <v>0</v>
-      </c>
+        <v>46225</v>
+      </c>
+      <c r="B37" s="1"/>
       <c r="C37" s="1" t="s">
         <v>17</v>
       </c>
@@ -2352,7 +2336,7 @@
       </c>
       <c r="N37" s="1"/>
       <c r="O37" s="1">
-        <v>99</v>
+        <v>166</v>
       </c>
       <c r="P37" s="1" t="s">
         <v>23</v>
@@ -2361,11 +2345,9 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A38" s="2">
-        <v>46224</v>
-      </c>
-      <c r="B38" s="1">
-        <v>0</v>
-      </c>
+        <v>46225</v>
+      </c>
+      <c r="B38" s="1"/>
       <c r="C38" s="1" t="s">
         <v>17</v>
       </c>
@@ -2384,10 +2366,10 @@
         <v>25</v>
       </c>
       <c r="J38" s="1">
-        <v>92.375</v>
+        <v>91.375</v>
       </c>
       <c r="K38" s="1">
-        <v>1062312.5</v>
+        <v>1050812.5</v>
       </c>
       <c r="L38" s="1">
         <v>0</v>
@@ -2397,7 +2379,7 @@
       </c>
       <c r="N38" s="1"/>
       <c r="O38" s="1">
-        <v>100</v>
+        <v>167</v>
       </c>
       <c r="P38" s="1" t="s">
         <v>23</v>
@@ -2406,11 +2388,9 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A39" s="2">
-        <v>46224</v>
-      </c>
-      <c r="B39" s="1">
-        <v>0</v>
-      </c>
+        <v>46225</v>
+      </c>
+      <c r="B39" s="1"/>
       <c r="C39" s="1" t="s">
         <v>17</v>
       </c>
@@ -2429,10 +2409,10 @@
         <v>22</v>
       </c>
       <c r="J39" s="1">
-        <v>409</v>
+        <v>373</v>
       </c>
       <c r="K39" s="1">
-        <v>3681000</v>
+        <v>3357000</v>
       </c>
       <c r="L39" s="1">
         <v>0</v>
@@ -2442,7 +2422,7 @@
       </c>
       <c r="N39" s="1"/>
       <c r="O39" s="1">
-        <v>101</v>
+        <v>168</v>
       </c>
       <c r="P39" s="1" t="s">
         <v>23</v>
@@ -2463,40 +2443,36 @@
         <v>18</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G40" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="J40" s="1">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="K40" s="1">
-        <v>297000</v>
+        <v>427500</v>
       </c>
       <c r="L40" s="1">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="M40" s="1">
         <v>0</v>
       </c>
       <c r="N40" s="1"/>
       <c r="O40" s="1">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="P40" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q40" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q40" s="1"/>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A41" s="2">
@@ -2512,23 +2488,21 @@
         <v>18</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G41" s="1" t="s">
-        <v>24</v>
-      </c>
+      <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J41" s="1">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="K41" s="1">
-        <v>27000</v>
+        <v>1100000</v>
       </c>
       <c r="L41" s="1">
         <v>0</v>
@@ -2538,14 +2512,12 @@
       </c>
       <c r="N41" s="1"/>
       <c r="O41" s="1">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="P41" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q41" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q41" s="1"/>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A42" s="2">
@@ -2561,23 +2533,21 @@
         <v>18</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>24</v>
-      </c>
+      <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1" t="s">
         <v>29</v>
       </c>
       <c r="J42" s="1">
-        <v>1</v>
+        <v>107.5</v>
       </c>
       <c r="K42" s="1">
-        <v>6000</v>
+        <v>645000</v>
       </c>
       <c r="L42" s="1">
         <v>0</v>
@@ -2587,14 +2557,12 @@
       </c>
       <c r="N42" s="1"/>
       <c r="O42" s="1">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="P42" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q42" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q42" s="1"/>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A43" s="2">
@@ -2610,23 +2578,21 @@
         <v>18</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G43" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J43" s="1">
-        <v>6</v>
+        <v>194.16667000000001</v>
       </c>
       <c r="K43" s="1">
-        <v>54000</v>
+        <v>2135833.2000000002</v>
       </c>
       <c r="L43" s="1">
         <v>0</v>
@@ -2636,14 +2602,12 @@
       </c>
       <c r="N43" s="1"/>
       <c r="O43" s="1">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q43" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q43" s="1"/>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A44" s="2">
@@ -2659,23 +2623,21 @@
         <v>18</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G44" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="J44" s="1">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="K44" s="1">
-        <v>18000</v>
+        <v>345000</v>
       </c>
       <c r="L44" s="1">
         <v>0</v>
@@ -2685,14 +2647,12 @@
       </c>
       <c r="N44" s="1"/>
       <c r="O44" s="1">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="P44" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q44" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q44" s="1"/>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A45" s="2">
@@ -2708,23 +2668,21 @@
         <v>18</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G45" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J45" s="1">
-        <v>6</v>
+        <v>21.916665999999999</v>
       </c>
       <c r="K45" s="1">
-        <v>54000</v>
+        <v>197250</v>
       </c>
       <c r="L45" s="1">
         <v>0</v>
@@ -2734,14 +2692,12 @@
       </c>
       <c r="N45" s="1"/>
       <c r="O45" s="1">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="P45" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q45" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q45" s="1"/>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A46" s="2">
@@ -2757,23 +2713,21 @@
         <v>18</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G46" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="J46" s="1">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="K46" s="1">
-        <v>12000</v>
+        <v>225000</v>
       </c>
       <c r="L46" s="1">
         <v>0</v>
@@ -2783,14 +2737,12 @@
       </c>
       <c r="N46" s="1"/>
       <c r="O46" s="1">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="P46" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q46" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q46" s="1"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A47" s="2">
@@ -2806,23 +2758,21 @@
         <v>18</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G47" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J47" s="1">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="K47" s="1">
-        <v>4500</v>
+        <v>375000</v>
       </c>
       <c r="L47" s="1">
         <v>0</v>
@@ -2832,14 +2782,12 @@
       </c>
       <c r="N47" s="1"/>
       <c r="O47" s="1">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="P47" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q47" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q47" s="1"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A48" s="2">
@@ -2855,23 +2803,21 @@
         <v>18</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G48" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="G48" s="1"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J48" s="1">
-        <v>2</v>
+        <v>92.375</v>
       </c>
       <c r="K48" s="1">
-        <v>18000</v>
+        <v>1062312.5</v>
       </c>
       <c r="L48" s="1">
         <v>0</v>
@@ -2881,14 +2827,12 @@
       </c>
       <c r="N48" s="1"/>
       <c r="O48" s="1">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P48" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q48" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q48" s="1"/>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A49" s="2">
@@ -2904,23 +2848,21 @@
         <v>18</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G49" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="G49" s="1"/>
       <c r="H49" s="1"/>
       <c r="I49" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J49" s="1">
-        <v>4.1666667999999997E-2</v>
+        <v>409</v>
       </c>
       <c r="K49" s="1">
-        <v>479.16665999999998</v>
+        <v>3681000</v>
       </c>
       <c r="L49" s="1">
         <v>0</v>
@@ -2930,14 +2872,12 @@
       </c>
       <c r="N49" s="1"/>
       <c r="O49" s="1">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="P49" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q49" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q49" s="1"/>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A50" s="2">
@@ -2959,27 +2899,27 @@
         <v>20</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1" t="s">
         <v>22</v>
       </c>
       <c r="J50" s="1">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="K50" s="1">
-        <v>18000</v>
+        <v>297000</v>
       </c>
       <c r="L50" s="1">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="M50" s="1">
         <v>0</v>
       </c>
       <c r="N50" s="1"/>
       <c r="O50" s="1">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="P50" s="1" t="s">
         <v>23</v>
@@ -3008,17 +2948,17 @@
         <v>20</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1" t="s">
         <v>22</v>
       </c>
       <c r="J51" s="1">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K51" s="1">
-        <v>72000</v>
+        <v>27000</v>
       </c>
       <c r="L51" s="1">
         <v>0</v>
@@ -3028,7 +2968,7 @@
       </c>
       <c r="N51" s="1"/>
       <c r="O51" s="1">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="P51" s="1" t="s">
         <v>23</v>
@@ -3057,17 +2997,17 @@
         <v>20</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J52" s="1">
-        <v>0.54166669999999995</v>
+        <v>1</v>
       </c>
       <c r="K52" s="1">
-        <v>6229.1665000000003</v>
+        <v>6000</v>
       </c>
       <c r="L52" s="1">
         <v>0</v>
@@ -3077,7 +3017,7 @@
       </c>
       <c r="N52" s="1"/>
       <c r="O52" s="1">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="P52" s="1" t="s">
         <v>23</v>
@@ -3106,17 +3046,17 @@
         <v>20</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J53" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K53" s="1">
-        <v>22000</v>
+        <v>54000</v>
       </c>
       <c r="L53" s="1">
         <v>0</v>
@@ -3126,7 +3066,7 @@
       </c>
       <c r="N53" s="1"/>
       <c r="O53" s="1">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="P53" s="1" t="s">
         <v>23</v>
@@ -3155,17 +3095,17 @@
         <v>20</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J54" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K54" s="1">
-        <v>54000</v>
+        <v>18000</v>
       </c>
       <c r="L54" s="1">
         <v>0</v>
@@ -3175,7 +3115,7 @@
       </c>
       <c r="N54" s="1"/>
       <c r="O54" s="1">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="P54" s="1" t="s">
         <v>23</v>
@@ -3204,17 +3144,17 @@
         <v>20</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J55" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K55" s="1">
-        <v>23000</v>
+        <v>54000</v>
       </c>
       <c r="L55" s="1">
         <v>0</v>
@@ -3224,7 +3164,7 @@
       </c>
       <c r="N55" s="1"/>
       <c r="O55" s="1">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="P55" s="1" t="s">
         <v>23</v>
@@ -3253,17 +3193,17 @@
         <v>20</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J56" s="1">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="K56" s="1">
-        <v>5500</v>
+        <v>12000</v>
       </c>
       <c r="L56" s="1">
         <v>0</v>
@@ -3273,7 +3213,7 @@
       </c>
       <c r="N56" s="1"/>
       <c r="O56" s="1">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="P56" s="1" t="s">
         <v>23</v>
@@ -3302,17 +3242,17 @@
         <v>20</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="J57" s="1">
         <v>1</v>
       </c>
       <c r="K57" s="1">
-        <v>6000</v>
+        <v>4500</v>
       </c>
       <c r="L57" s="1">
         <v>0</v>
@@ -3322,7 +3262,7 @@
       </c>
       <c r="N57" s="1"/>
       <c r="O57" s="1">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="P57" s="1" t="s">
         <v>23</v>
@@ -3351,17 +3291,17 @@
         <v>20</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1" t="s">
         <v>22</v>
       </c>
       <c r="J58" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K58" s="1">
-        <v>36000</v>
+        <v>18000</v>
       </c>
       <c r="L58" s="1">
         <v>0</v>
@@ -3371,7 +3311,7 @@
       </c>
       <c r="N58" s="1"/>
       <c r="O58" s="1">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="P58" s="1" t="s">
         <v>23</v>
@@ -3400,17 +3340,17 @@
         <v>20</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J59" s="1">
-        <v>1</v>
+        <v>4.1666667999999997E-2</v>
       </c>
       <c r="K59" s="1">
-        <v>6000</v>
+        <v>479.16665999999998</v>
       </c>
       <c r="L59" s="1">
         <v>0</v>
@@ -3420,7 +3360,7 @@
       </c>
       <c r="N59" s="1"/>
       <c r="O59" s="1">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="P59" s="1" t="s">
         <v>23</v>
@@ -3449,17 +3389,17 @@
         <v>20</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1" t="s">
         <v>22</v>
       </c>
       <c r="J60" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K60" s="1">
-        <v>45000</v>
+        <v>18000</v>
       </c>
       <c r="L60" s="1">
         <v>0</v>
@@ -3469,7 +3409,7 @@
       </c>
       <c r="N60" s="1"/>
       <c r="O60" s="1">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="P60" s="1" t="s">
         <v>23</v>
@@ -3498,17 +3438,17 @@
         <v>20</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J61" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K61" s="1">
-        <v>11000</v>
+        <v>72000</v>
       </c>
       <c r="L61" s="1">
         <v>0</v>
@@ -3518,7 +3458,7 @@
       </c>
       <c r="N61" s="1"/>
       <c r="O61" s="1">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="P61" s="1" t="s">
         <v>23</v>
@@ -3547,17 +3487,17 @@
         <v>20</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="J62" s="1">
-        <v>1</v>
+        <v>0.54166669999999995</v>
       </c>
       <c r="K62" s="1">
-        <v>4500</v>
+        <v>6229.1665000000003</v>
       </c>
       <c r="L62" s="1">
         <v>0</v>
@@ -3567,7 +3507,7 @@
       </c>
       <c r="N62" s="1"/>
       <c r="O62" s="1">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="P62" s="1" t="s">
         <v>23</v>
@@ -3596,17 +3536,17 @@
         <v>20</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J63" s="1">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="K63" s="1">
-        <v>171000</v>
+        <v>22000</v>
       </c>
       <c r="L63" s="1">
         <v>0</v>
@@ -3616,7 +3556,7 @@
       </c>
       <c r="N63" s="1"/>
       <c r="O63" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="P63" s="1" t="s">
         <v>23</v>
@@ -3645,17 +3585,17 @@
         <v>20</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J64" s="1">
-        <v>1.0833333999999999</v>
+        <v>6</v>
       </c>
       <c r="K64" s="1">
-        <v>11916.666999999999</v>
+        <v>54000</v>
       </c>
       <c r="L64" s="1">
         <v>0</v>
@@ -3665,7 +3605,7 @@
       </c>
       <c r="N64" s="1"/>
       <c r="O64" s="1">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="P64" s="1" t="s">
         <v>23</v>
@@ -3694,17 +3634,17 @@
         <v>20</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J65" s="1">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="K65" s="1">
-        <v>135000</v>
+        <v>23000</v>
       </c>
       <c r="L65" s="1">
         <v>0</v>
@@ -3714,7 +3654,7 @@
       </c>
       <c r="N65" s="1"/>
       <c r="O65" s="1">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="P65" s="1" t="s">
         <v>23</v>
@@ -3743,17 +3683,17 @@
         <v>20</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J66" s="1">
-        <v>1.0833333999999999</v>
+        <v>0.5</v>
       </c>
       <c r="K66" s="1">
-        <v>12458.333000000001</v>
+        <v>5500</v>
       </c>
       <c r="L66" s="1">
         <v>0</v>
@@ -3763,7 +3703,7 @@
       </c>
       <c r="N66" s="1"/>
       <c r="O66" s="1">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="P66" s="1" t="s">
         <v>23</v>
@@ -3792,19 +3732,17 @@
         <v>20</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>46</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="H67" s="1"/>
       <c r="I67" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J67" s="1">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="K67" s="1">
-        <v>450000</v>
+        <v>6000</v>
       </c>
       <c r="L67" s="1">
         <v>0</v>
@@ -3814,7 +3752,7 @@
       </c>
       <c r="N67" s="1"/>
       <c r="O67" s="1">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="P67" s="1" t="s">
         <v>23</v>
@@ -3843,19 +3781,17 @@
         <v>20</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>46</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="H68" s="1"/>
       <c r="I68" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J68" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K68" s="1">
-        <v>6000</v>
+        <v>36000</v>
       </c>
       <c r="L68" s="1">
         <v>0</v>
@@ -3865,7 +3801,7 @@
       </c>
       <c r="N68" s="1"/>
       <c r="O68" s="1">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="P68" s="1" t="s">
         <v>23</v>
@@ -3876,7 +3812,7 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A69" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B69" s="1">
         <v>0</v>
@@ -3894,27 +3830,27 @@
         <v>20</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H69" s="1"/>
       <c r="I69" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J69" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K69" s="1">
-        <v>27000</v>
+        <v>6000</v>
       </c>
       <c r="L69" s="1">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="M69" s="1">
         <v>0</v>
       </c>
       <c r="N69" s="1"/>
       <c r="O69" s="1">
-        <v>65</v>
+        <v>121</v>
       </c>
       <c r="P69" s="1" t="s">
         <v>23</v>
@@ -3925,7 +3861,7 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A70" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B70" s="1">
         <v>0</v>
@@ -3943,17 +3879,17 @@
         <v>20</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J70" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K70" s="1">
-        <v>12000</v>
+        <v>45000</v>
       </c>
       <c r="L70" s="1">
         <v>0</v>
@@ -3963,7 +3899,7 @@
       </c>
       <c r="N70" s="1"/>
       <c r="O70" s="1">
-        <v>66</v>
+        <v>122</v>
       </c>
       <c r="P70" s="1" t="s">
         <v>23</v>
@@ -3974,7 +3910,7 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A71" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B71" s="1">
         <v>0</v>
@@ -3992,17 +3928,17 @@
         <v>20</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H71" s="1"/>
       <c r="I71" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J71" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K71" s="1">
-        <v>18000</v>
+        <v>11000</v>
       </c>
       <c r="L71" s="1">
         <v>0</v>
@@ -4012,7 +3948,7 @@
       </c>
       <c r="N71" s="1"/>
       <c r="O71" s="1">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="P71" s="1" t="s">
         <v>23</v>
@@ -4023,7 +3959,7 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A72" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B72" s="1">
         <v>0</v>
@@ -4041,17 +3977,17 @@
         <v>20</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H72" s="1"/>
       <c r="I72" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="J72" s="1">
-        <v>1.625</v>
+        <v>1</v>
       </c>
       <c r="K72" s="1">
-        <v>18687.5</v>
+        <v>4500</v>
       </c>
       <c r="L72" s="1">
         <v>0</v>
@@ -4061,7 +3997,7 @@
       </c>
       <c r="N72" s="1"/>
       <c r="O72" s="1">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="P72" s="1" t="s">
         <v>23</v>
@@ -4072,7 +4008,7 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A73" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B73" s="1">
         <v>0</v>
@@ -4090,17 +4026,17 @@
         <v>20</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J73" s="1">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K73" s="1">
-        <v>12000</v>
+        <v>171000</v>
       </c>
       <c r="L73" s="1">
         <v>0</v>
@@ -4110,7 +4046,7 @@
       </c>
       <c r="N73" s="1"/>
       <c r="O73" s="1">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="P73" s="1" t="s">
         <v>23</v>
@@ -4121,7 +4057,7 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A74" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B74" s="1">
         <v>0</v>
@@ -4139,17 +4075,17 @@
         <v>20</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J74" s="1">
-        <v>1</v>
+        <v>1.0833333999999999</v>
       </c>
       <c r="K74" s="1">
-        <v>6000</v>
+        <v>11916.666999999999</v>
       </c>
       <c r="L74" s="1">
         <v>0</v>
@@ -4159,7 +4095,7 @@
       </c>
       <c r="N74" s="1"/>
       <c r="O74" s="1">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="P74" s="1" t="s">
         <v>23</v>
@@ -4170,7 +4106,7 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A75" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B75" s="1">
         <v>0</v>
@@ -4188,17 +4124,17 @@
         <v>20</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1" t="s">
         <v>22</v>
       </c>
       <c r="J75" s="1">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K75" s="1">
-        <v>9000</v>
+        <v>135000</v>
       </c>
       <c r="L75" s="1">
         <v>0</v>
@@ -4208,7 +4144,7 @@
       </c>
       <c r="N75" s="1"/>
       <c r="O75" s="1">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="P75" s="1" t="s">
         <v>23</v>
@@ -4219,7 +4155,7 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A76" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B76" s="1">
         <v>0</v>
@@ -4237,17 +4173,17 @@
         <v>20</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J76" s="1">
-        <v>4.1666667999999997E-2</v>
+        <v>1.0833333999999999</v>
       </c>
       <c r="K76" s="1">
-        <v>479.16665999999998</v>
+        <v>12458.333000000001</v>
       </c>
       <c r="L76" s="1">
         <v>0</v>
@@ -4257,7 +4193,7 @@
       </c>
       <c r="N76" s="1"/>
       <c r="O76" s="1">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="P76" s="1" t="s">
         <v>23</v>
@@ -4268,7 +4204,7 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A77" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B77" s="1">
         <v>0</v>
@@ -4286,17 +4222,19 @@
         <v>20</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H77" s="1"/>
+        <v>45</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="I77" s="1" t="s">
         <v>22</v>
       </c>
       <c r="J77" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="K77" s="1">
-        <v>9000</v>
+        <v>450000</v>
       </c>
       <c r="L77" s="1">
         <v>0</v>
@@ -4306,7 +4244,7 @@
       </c>
       <c r="N77" s="1"/>
       <c r="O77" s="1">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="P77" s="1" t="s">
         <v>23</v>
@@ -4317,7 +4255,7 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A78" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B78" s="1">
         <v>0</v>
@@ -4335,17 +4273,19 @@
         <v>20</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H78" s="1"/>
+        <v>45</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="I78" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J78" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K78" s="1">
-        <v>18000</v>
+        <v>6000</v>
       </c>
       <c r="L78" s="1">
         <v>0</v>
@@ -4355,7 +4295,7 @@
       </c>
       <c r="N78" s="1"/>
       <c r="O78" s="1">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="P78" s="1" t="s">
         <v>23</v>
@@ -4384,27 +4324,27 @@
         <v>20</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1" t="s">
         <v>22</v>
       </c>
       <c r="J79" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K79" s="1">
-        <v>9000</v>
+        <v>27000</v>
       </c>
       <c r="L79" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="M79" s="1">
         <v>0</v>
       </c>
       <c r="N79" s="1"/>
       <c r="O79" s="1">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="P79" s="1" t="s">
         <v>23</v>
@@ -4433,17 +4373,17 @@
         <v>20</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H80" s="1"/>
       <c r="I80" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J80" s="1">
         <v>2</v>
       </c>
       <c r="K80" s="1">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="L80" s="1">
         <v>0</v>
@@ -4453,7 +4393,7 @@
       </c>
       <c r="N80" s="1"/>
       <c r="O80" s="1">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="P80" s="1" t="s">
         <v>23</v>
@@ -4482,17 +4422,17 @@
         <v>20</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H81" s="1"/>
       <c r="I81" s="1" t="s">
         <v>22</v>
       </c>
       <c r="J81" s="1">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="K81" s="1">
-        <v>4500</v>
+        <v>18000</v>
       </c>
       <c r="L81" s="1">
         <v>0</v>
@@ -4502,7 +4442,7 @@
       </c>
       <c r="N81" s="1"/>
       <c r="O81" s="1">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="P81" s="1" t="s">
         <v>23</v>
@@ -4531,17 +4471,17 @@
         <v>20</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="H82" s="1"/>
       <c r="I82" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J82" s="1">
-        <v>0.5</v>
+        <v>1.625</v>
       </c>
       <c r="K82" s="1">
-        <v>4500</v>
+        <v>18687.5</v>
       </c>
       <c r="L82" s="1">
         <v>0</v>
@@ -4551,7 +4491,7 @@
       </c>
       <c r="N82" s="1"/>
       <c r="O82" s="1">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="P82" s="1" t="s">
         <v>23</v>
@@ -4580,17 +4520,17 @@
         <v>20</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H83" s="1"/>
       <c r="I83" s="1" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="J83" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K83" s="1">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="L83" s="1">
         <v>0</v>
@@ -4600,7 +4540,7 @@
       </c>
       <c r="N83" s="1"/>
       <c r="O83" s="1">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="P83" s="1" t="s">
         <v>23</v>
@@ -4629,17 +4569,17 @@
         <v>20</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H84" s="1"/>
       <c r="I84" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J84" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K84" s="1">
-        <v>27000</v>
+        <v>6000</v>
       </c>
       <c r="L84" s="1">
         <v>0</v>
@@ -4649,7 +4589,7 @@
       </c>
       <c r="N84" s="1"/>
       <c r="O84" s="1">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="P84" s="1" t="s">
         <v>23</v>
@@ -4678,17 +4618,17 @@
         <v>20</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H85" s="1"/>
       <c r="I85" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J85" s="1">
         <v>1</v>
       </c>
       <c r="K85" s="1">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="L85" s="1">
         <v>0</v>
@@ -4698,7 +4638,7 @@
       </c>
       <c r="N85" s="1"/>
       <c r="O85" s="1">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="P85" s="1" t="s">
         <v>23</v>
@@ -4727,17 +4667,17 @@
         <v>20</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H86" s="1"/>
       <c r="I86" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J86" s="1">
-        <v>0.16666666999999999</v>
+        <v>4.1666667999999997E-2</v>
       </c>
       <c r="K86" s="1">
-        <v>1833.3334</v>
+        <v>479.16665999999998</v>
       </c>
       <c r="L86" s="1">
         <v>0</v>
@@ -4747,7 +4687,7 @@
       </c>
       <c r="N86" s="1"/>
       <c r="O86" s="1">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="P86" s="1" t="s">
         <v>23</v>
@@ -4776,7 +4716,7 @@
         <v>20</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="H87" s="1"/>
       <c r="I87" s="1" t="s">
@@ -4796,7 +4736,7 @@
       </c>
       <c r="N87" s="1"/>
       <c r="O87" s="1">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="P87" s="1" t="s">
         <v>23</v>
@@ -4825,17 +4765,17 @@
         <v>20</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H88" s="1"/>
       <c r="I88" s="1" t="s">
         <v>22</v>
       </c>
       <c r="J88" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K88" s="1">
-        <v>36000</v>
+        <v>18000</v>
       </c>
       <c r="L88" s="1">
         <v>0</v>
@@ -4845,7 +4785,7 @@
       </c>
       <c r="N88" s="1"/>
       <c r="O88" s="1">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="P88" s="1" t="s">
         <v>23</v>
@@ -4874,17 +4814,17 @@
         <v>20</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J89" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K89" s="1">
-        <v>18000</v>
+        <v>9000</v>
       </c>
       <c r="L89" s="1">
         <v>0</v>
@@ -4894,7 +4834,7 @@
       </c>
       <c r="N89" s="1"/>
       <c r="O89" s="1">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="P89" s="1" t="s">
         <v>23</v>
@@ -4923,17 +4863,17 @@
         <v>20</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="H90" s="1"/>
       <c r="I90" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J90" s="1">
-        <v>1.0833333999999999</v>
+        <v>2</v>
       </c>
       <c r="K90" s="1">
-        <v>12458.333000000001</v>
+        <v>18000</v>
       </c>
       <c r="L90" s="1">
         <v>0</v>
@@ -4943,7 +4883,7 @@
       </c>
       <c r="N90" s="1"/>
       <c r="O90" s="1">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="P90" s="1" t="s">
         <v>23</v>
@@ -4972,11 +4912,11 @@
         <v>20</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H91" s="1"/>
       <c r="I91" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="J91" s="1">
         <v>0.5</v>
@@ -4992,7 +4932,7 @@
       </c>
       <c r="N91" s="1"/>
       <c r="O91" s="1">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="P91" s="1" t="s">
         <v>23</v>
@@ -5021,17 +4961,17 @@
         <v>20</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1" t="s">
         <v>22</v>
       </c>
       <c r="J92" s="1">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="K92" s="1">
-        <v>27000</v>
+        <v>4500</v>
       </c>
       <c r="L92" s="1">
         <v>0</v>
@@ -5041,7 +4981,7 @@
       </c>
       <c r="N92" s="1"/>
       <c r="O92" s="1">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="P92" s="1" t="s">
         <v>23</v>
@@ -5070,17 +5010,17 @@
         <v>20</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="H93" s="1"/>
       <c r="I93" s="1" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="J93" s="1">
-        <v>1.0833333999999999</v>
+        <v>1</v>
       </c>
       <c r="K93" s="1">
-        <v>11916.666999999999</v>
+        <v>15000</v>
       </c>
       <c r="L93" s="1">
         <v>0</v>
@@ -5090,7 +5030,7 @@
       </c>
       <c r="N93" s="1"/>
       <c r="O93" s="1">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="P93" s="1" t="s">
         <v>23</v>
@@ -5119,17 +5059,17 @@
         <v>20</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J94" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K94" s="1">
-        <v>24000</v>
+        <v>27000</v>
       </c>
       <c r="L94" s="1">
         <v>0</v>
@@ -5139,7 +5079,7 @@
       </c>
       <c r="N94" s="1"/>
       <c r="O94" s="1">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="P94" s="1" t="s">
         <v>23</v>
@@ -5168,17 +5108,17 @@
         <v>20</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="J95" s="1">
         <v>1</v>
       </c>
       <c r="K95" s="1">
-        <v>15000</v>
+        <v>6000</v>
       </c>
       <c r="L95" s="1">
         <v>0</v>
@@ -5188,7 +5128,7 @@
       </c>
       <c r="N95" s="1"/>
       <c r="O95" s="1">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="P95" s="1" t="s">
         <v>23</v>
@@ -5199,7 +5139,7 @@
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A96" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B96" s="1">
         <v>0</v>
@@ -5217,27 +5157,27 @@
         <v>20</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H96" s="1"/>
       <c r="I96" s="1" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="J96" s="1">
-        <v>2</v>
+        <v>0.16666666999999999</v>
       </c>
       <c r="K96" s="1">
-        <v>22000</v>
+        <v>1833.3334</v>
       </c>
       <c r="L96" s="1">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="M96" s="1">
         <v>0</v>
       </c>
       <c r="N96" s="1"/>
       <c r="O96" s="1">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="P96" s="1" t="s">
         <v>23</v>
@@ -5248,7 +5188,7 @@
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A97" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B97" s="1">
         <v>0</v>
@@ -5266,17 +5206,17 @@
         <v>20</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H97" s="1"/>
       <c r="I97" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J97" s="1">
         <v>1</v>
       </c>
       <c r="K97" s="1">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="L97" s="1">
         <v>0</v>
@@ -5286,7 +5226,7 @@
       </c>
       <c r="N97" s="1"/>
       <c r="O97" s="1">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="P97" s="1" t="s">
         <v>23</v>
@@ -5297,7 +5237,7 @@
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A98" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B98" s="1">
         <v>0</v>
@@ -5315,17 +5255,17 @@
         <v>20</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H98" s="1"/>
       <c r="I98" s="1" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="J98" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K98" s="1">
-        <v>4500</v>
+        <v>36000</v>
       </c>
       <c r="L98" s="1">
         <v>0</v>
@@ -5335,7 +5275,7 @@
       </c>
       <c r="N98" s="1"/>
       <c r="O98" s="1">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="P98" s="1" t="s">
         <v>23</v>
@@ -5346,7 +5286,7 @@
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A99" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B99" s="1">
         <v>0</v>
@@ -5364,17 +5304,17 @@
         <v>20</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H99" s="1"/>
       <c r="I99" s="1" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="J99" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K99" s="1">
-        <v>22000</v>
+        <v>18000</v>
       </c>
       <c r="L99" s="1">
         <v>0</v>
@@ -5384,7 +5324,7 @@
       </c>
       <c r="N99" s="1"/>
       <c r="O99" s="1">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="P99" s="1" t="s">
         <v>23</v>
@@ -5395,7 +5335,7 @@
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A100" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B100" s="1">
         <v>0</v>
@@ -5413,17 +5353,17 @@
         <v>20</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H100" s="1"/>
       <c r="I100" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J100" s="1">
-        <v>2</v>
+        <v>1.0833333999999999</v>
       </c>
       <c r="K100" s="1">
-        <v>12000</v>
+        <v>12458.333000000001</v>
       </c>
       <c r="L100" s="1">
         <v>0</v>
@@ -5433,7 +5373,7 @@
       </c>
       <c r="N100" s="1"/>
       <c r="O100" s="1">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="P100" s="1" t="s">
         <v>23</v>
@@ -5444,7 +5384,7 @@
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A101" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B101" s="1">
         <v>0</v>
@@ -5462,17 +5402,17 @@
         <v>20</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H101" s="1"/>
       <c r="I101" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J101" s="1">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="K101" s="1">
-        <v>31500</v>
+        <v>4500</v>
       </c>
       <c r="L101" s="1">
         <v>0</v>
@@ -5482,7 +5422,7 @@
       </c>
       <c r="N101" s="1"/>
       <c r="O101" s="1">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="P101" s="1" t="s">
         <v>23</v>
@@ -5493,7 +5433,7 @@
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A102" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B102" s="1">
         <v>0</v>
@@ -5511,17 +5451,17 @@
         <v>20</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H102" s="1"/>
       <c r="I102" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="J102" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K102" s="1">
-        <v>9000</v>
+        <v>27000</v>
       </c>
       <c r="L102" s="1">
         <v>0</v>
@@ -5531,7 +5471,7 @@
       </c>
       <c r="N102" s="1"/>
       <c r="O102" s="1">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="P102" s="1" t="s">
         <v>23</v>
@@ -5542,7 +5482,7 @@
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A103" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B103" s="1">
         <v>0</v>
@@ -5560,17 +5500,17 @@
         <v>20</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H103" s="1"/>
       <c r="I103" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J103" s="1">
-        <v>0.25</v>
+        <v>1.0833333999999999</v>
       </c>
       <c r="K103" s="1">
-        <v>2875</v>
+        <v>11916.666999999999</v>
       </c>
       <c r="L103" s="1">
         <v>0</v>
@@ -5580,7 +5520,7 @@
       </c>
       <c r="N103" s="1"/>
       <c r="O103" s="1">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="P103" s="1" t="s">
         <v>23</v>
@@ -5591,7 +5531,7 @@
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A104" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B104" s="1">
         <v>0</v>
@@ -5609,17 +5549,17 @@
         <v>20</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H104" s="1"/>
       <c r="I104" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J104" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K104" s="1">
-        <v>21000</v>
+        <v>24000</v>
       </c>
       <c r="L104" s="1">
         <v>0</v>
@@ -5629,7 +5569,7 @@
       </c>
       <c r="N104" s="1"/>
       <c r="O104" s="1">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="P104" s="1" t="s">
         <v>23</v>
@@ -5640,7 +5580,7 @@
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A105" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B105" s="1">
         <v>0</v>
@@ -5658,17 +5598,17 @@
         <v>20</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H105" s="1"/>
       <c r="I105" s="1" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="J105" s="1">
         <v>1</v>
       </c>
       <c r="K105" s="1">
-        <v>10500</v>
+        <v>15000</v>
       </c>
       <c r="L105" s="1">
         <v>0</v>
@@ -5678,7 +5618,7 @@
       </c>
       <c r="N105" s="1"/>
       <c r="O105" s="1">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="P105" s="1" t="s">
         <v>23</v>
@@ -5707,27 +5647,27 @@
         <v>20</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H106" s="1"/>
       <c r="I106" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="J106" s="1">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="K106" s="1">
-        <v>3000</v>
+        <v>22000</v>
       </c>
       <c r="L106" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="M106" s="1">
         <v>0</v>
       </c>
       <c r="N106" s="1"/>
       <c r="O106" s="1">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="P106" s="1" t="s">
         <v>23</v>
@@ -5756,17 +5696,17 @@
         <v>20</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H107" s="1"/>
       <c r="I107" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J107" s="1">
         <v>1</v>
       </c>
       <c r="K107" s="1">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="L107" s="1">
         <v>0</v>
@@ -5776,7 +5716,7 @@
       </c>
       <c r="N107" s="1"/>
       <c r="O107" s="1">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="P107" s="1" t="s">
         <v>23</v>
@@ -5805,17 +5745,17 @@
         <v>20</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H108" s="1"/>
       <c r="I108" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="J108" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K108" s="1">
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="L108" s="1">
         <v>0</v>
@@ -5825,7 +5765,7 @@
       </c>
       <c r="N108" s="1"/>
       <c r="O108" s="1">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="P108" s="1" t="s">
         <v>23</v>
@@ -5854,17 +5794,17 @@
         <v>20</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H109" s="1"/>
       <c r="I109" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="J109" s="1">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="K109" s="1">
-        <v>3000</v>
+        <v>22000</v>
       </c>
       <c r="L109" s="1">
         <v>0</v>
@@ -5874,7 +5814,7 @@
       </c>
       <c r="N109" s="1"/>
       <c r="O109" s="1">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="P109" s="1" t="s">
         <v>23</v>
@@ -5903,17 +5843,17 @@
         <v>20</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H110" s="1"/>
       <c r="I110" s="1" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="J110" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K110" s="1">
-        <v>55000</v>
+        <v>12000</v>
       </c>
       <c r="L110" s="1">
         <v>0</v>
@@ -5923,7 +5863,7 @@
       </c>
       <c r="N110" s="1"/>
       <c r="O110" s="1">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="P110" s="1" t="s">
         <v>23</v>
@@ -5952,17 +5892,17 @@
         <v>20</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H111" s="1"/>
       <c r="I111" s="1" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="J111" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K111" s="1">
-        <v>55000</v>
+        <v>31500</v>
       </c>
       <c r="L111" s="1">
         <v>0</v>
@@ -5972,7 +5912,7 @@
       </c>
       <c r="N111" s="1"/>
       <c r="O111" s="1">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="P111" s="1" t="s">
         <v>23</v>
@@ -6001,17 +5941,17 @@
         <v>20</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H112" s="1"/>
       <c r="I112" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="J112" s="1">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="K112" s="1">
-        <v>2875</v>
+        <v>9000</v>
       </c>
       <c r="L112" s="1">
         <v>0</v>
@@ -6021,7 +5961,7 @@
       </c>
       <c r="N112" s="1"/>
       <c r="O112" s="1">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="P112" s="1" t="s">
         <v>23</v>
@@ -6050,7 +5990,7 @@
         <v>20</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H113" s="1"/>
       <c r="I113" s="1" t="s">
@@ -6070,7 +6010,7 @@
       </c>
       <c r="N113" s="1"/>
       <c r="O113" s="1">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="P113" s="1" t="s">
         <v>23</v>
@@ -6099,17 +6039,17 @@
         <v>20</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="H114" s="1"/>
       <c r="I114" s="1" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="J114" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K114" s="1">
-        <v>11000</v>
+        <v>21000</v>
       </c>
       <c r="L114" s="1">
         <v>0</v>
@@ -6119,7 +6059,7 @@
       </c>
       <c r="N114" s="1"/>
       <c r="O114" s="1">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P114" s="1" t="s">
         <v>23</v>
@@ -6148,7 +6088,7 @@
         <v>20</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H115" s="1"/>
       <c r="I115" s="1" t="s">
@@ -6168,7 +6108,7 @@
       </c>
       <c r="N115" s="1"/>
       <c r="O115" s="1">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="P115" s="1" t="s">
         <v>23</v>
@@ -6197,17 +6137,17 @@
         <v>20</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="H116" s="1"/>
       <c r="I116" s="1" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="J116" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K116" s="1">
-        <v>11000</v>
+        <v>3000</v>
       </c>
       <c r="L116" s="1">
         <v>0</v>
@@ -6217,7 +6157,7 @@
       </c>
       <c r="N116" s="1"/>
       <c r="O116" s="1">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="P116" s="1" t="s">
         <v>23</v>
@@ -6246,17 +6186,17 @@
         <v>20</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="H117" s="1"/>
       <c r="I117" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J117" s="1">
         <v>1</v>
       </c>
       <c r="K117" s="1">
-        <v>4500</v>
+        <v>9000</v>
       </c>
       <c r="L117" s="1">
         <v>0</v>
@@ -6266,7 +6206,7 @@
       </c>
       <c r="N117" s="1"/>
       <c r="O117" s="1">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="P117" s="1" t="s">
         <v>23</v>
@@ -6295,17 +6235,17 @@
         <v>20</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H118" s="1"/>
       <c r="I118" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J118" s="1">
-        <v>0.45833333999999998</v>
+        <v>0.5</v>
       </c>
       <c r="K118" s="1">
-        <v>5270.8334999999997</v>
+        <v>3000</v>
       </c>
       <c r="L118" s="1">
         <v>0</v>
@@ -6315,7 +6255,7 @@
       </c>
       <c r="N118" s="1"/>
       <c r="O118" s="1">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="P118" s="1" t="s">
         <v>23</v>
@@ -6326,7 +6266,7 @@
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A119" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B119" s="1">
         <v>0</v>
@@ -6338,21 +6278,23 @@
         <v>18</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G119" s="1"/>
+      <c r="G119" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="H119" s="1"/>
       <c r="I119" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J119" s="1">
-        <v>600</v>
+        <v>0.5</v>
       </c>
       <c r="K119" s="1">
-        <v>6300000</v>
+        <v>3000</v>
       </c>
       <c r="L119" s="1">
         <v>0</v>
@@ -6362,16 +6304,18 @@
       </c>
       <c r="N119" s="1"/>
       <c r="O119" s="1">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="P119" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q119" s="1"/>
+      <c r="Q119" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A120" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B120" s="1">
         <v>0</v>
@@ -6383,21 +6327,23 @@
         <v>18</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G120" s="1"/>
+      <c r="G120" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="H120" s="1"/>
       <c r="I120" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="J120" s="1">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="K120" s="1">
-        <v>2200000</v>
+        <v>55000</v>
       </c>
       <c r="L120" s="1">
         <v>0</v>
@@ -6407,16 +6353,18 @@
       </c>
       <c r="N120" s="1"/>
       <c r="O120" s="1">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="P120" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q120" s="1"/>
+      <c r="Q120" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A121" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B121" s="1">
         <v>0</v>
@@ -6428,21 +6376,23 @@
         <v>18</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G121" s="1"/>
+      <c r="G121" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="H121" s="1"/>
       <c r="I121" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J121" s="1">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="K121" s="1">
-        <v>450000</v>
+        <v>55000</v>
       </c>
       <c r="L121" s="1">
         <v>0</v>
@@ -6452,16 +6402,18 @@
       </c>
       <c r="N121" s="1"/>
       <c r="O121" s="1">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="P121" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q121" s="1"/>
+      <c r="Q121" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A122" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B122" s="1">
         <v>0</v>
@@ -6473,21 +6425,23 @@
         <v>18</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G122" s="1"/>
+      <c r="G122" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="H122" s="1"/>
       <c r="I122" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J122" s="1">
-        <v>100</v>
+        <v>0.25</v>
       </c>
       <c r="K122" s="1">
-        <v>1100000</v>
+        <v>2875</v>
       </c>
       <c r="L122" s="1">
         <v>0</v>
@@ -6497,16 +6451,18 @@
       </c>
       <c r="N122" s="1"/>
       <c r="O122" s="1">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="P122" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q122" s="1"/>
+      <c r="Q122" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A123" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B123" s="1">
         <v>0</v>
@@ -6518,21 +6474,23 @@
         <v>18</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G123" s="1"/>
+      <c r="G123" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="H123" s="1"/>
       <c r="I123" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J123" s="1">
-        <v>100</v>
+        <v>0.25</v>
       </c>
       <c r="K123" s="1">
-        <v>1150000</v>
+        <v>2875</v>
       </c>
       <c r="L123" s="1">
         <v>0</v>
@@ -6542,16 +6500,18 @@
       </c>
       <c r="N123" s="1"/>
       <c r="O123" s="1">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="P123" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q123" s="1"/>
+      <c r="Q123" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A124" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B124" s="1">
         <v>0</v>
@@ -6563,21 +6523,23 @@
         <v>18</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G124" s="1"/>
+      <c r="G124" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="H124" s="1"/>
       <c r="I124" s="1" t="s">
         <v>47</v>
       </c>
       <c r="J124" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K124" s="1">
-        <v>1100000</v>
+        <v>11000</v>
       </c>
       <c r="L124" s="1">
         <v>0</v>
@@ -6587,16 +6549,18 @@
       </c>
       <c r="N124" s="1"/>
       <c r="O124" s="1">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="P124" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q124" s="1"/>
+      <c r="Q124" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A125" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B125" s="1">
         <v>0</v>
@@ -6608,21 +6572,23 @@
         <v>18</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G125" s="1"/>
+      <c r="G125" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="H125" s="1"/>
       <c r="I125" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J125" s="1">
-        <v>140</v>
+        <v>1</v>
       </c>
       <c r="K125" s="1">
-        <v>840000</v>
+        <v>10500</v>
       </c>
       <c r="L125" s="1">
         <v>0</v>
@@ -6632,16 +6598,18 @@
       </c>
       <c r="N125" s="1"/>
       <c r="O125" s="1">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="P125" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q125" s="1"/>
+      <c r="Q125" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A126" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B126" s="1">
         <v>0</v>
@@ -6653,21 +6621,23 @@
         <v>18</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G126" s="1"/>
+      <c r="G126" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="H126" s="1"/>
       <c r="I126" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="J126" s="1">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K126" s="1">
-        <v>375000</v>
+        <v>11000</v>
       </c>
       <c r="L126" s="1">
         <v>0</v>
@@ -6677,16 +6647,18 @@
       </c>
       <c r="N126" s="1"/>
       <c r="O126" s="1">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="P126" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q126" s="1"/>
+      <c r="Q126" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A127" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B127" s="1">
         <v>0</v>
@@ -6698,21 +6670,23 @@
         <v>18</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G127" s="1"/>
+      <c r="G127" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="H127" s="1"/>
       <c r="I127" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J127" s="1">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K127" s="1">
-        <v>375000</v>
+        <v>4500</v>
       </c>
       <c r="L127" s="1">
         <v>0</v>
@@ -6722,16 +6696,18 @@
       </c>
       <c r="N127" s="1"/>
       <c r="O127" s="1">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="P127" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q127" s="1"/>
+      <c r="Q127" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A128" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B128" s="1">
         <v>0</v>
@@ -6743,21 +6719,23 @@
         <v>18</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G128" s="1"/>
+      <c r="G128" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="H128" s="1"/>
       <c r="I128" s="1" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="J128" s="1">
-        <v>25</v>
+        <v>0.45833333999999998</v>
       </c>
       <c r="K128" s="1">
-        <v>225000</v>
+        <v>5270.8334999999997</v>
       </c>
       <c r="L128" s="1">
         <v>0</v>
@@ -6767,12 +6745,14 @@
       </c>
       <c r="N128" s="1"/>
       <c r="O128" s="1">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="P128" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q128" s="1"/>
+      <c r="Q128" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A129" s="2">
@@ -6796,13 +6776,13 @@
       <c r="G129" s="1"/>
       <c r="H129" s="1"/>
       <c r="I129" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="J129" s="1">
-        <v>25</v>
+        <v>600</v>
       </c>
       <c r="K129" s="1">
-        <v>225000</v>
+        <v>6300000</v>
       </c>
       <c r="L129" s="1">
         <v>0</v>
@@ -6812,7 +6792,7 @@
       </c>
       <c r="N129" s="1"/>
       <c r="O129" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="P129" s="1" t="s">
         <v>23</v>
@@ -6833,40 +6813,36 @@
         <v>18</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G130" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="G130" s="1"/>
       <c r="H130" s="1"/>
       <c r="I130" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="J130" s="1">
-        <v>0.58333330000000005</v>
+        <v>200</v>
       </c>
       <c r="K130" s="1">
-        <v>5250</v>
+        <v>2200000</v>
       </c>
       <c r="L130" s="1">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="M130" s="1">
         <v>0</v>
       </c>
       <c r="N130" s="1"/>
       <c r="O130" s="1">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="P130" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q130" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q130" s="1"/>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A131" s="2">
@@ -6882,23 +6858,21 @@
         <v>18</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G131" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="G131" s="1"/>
       <c r="H131" s="1"/>
       <c r="I131" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J131" s="1">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="K131" s="1">
-        <v>66000</v>
+        <v>450000</v>
       </c>
       <c r="L131" s="1">
         <v>0</v>
@@ -6908,14 +6882,12 @@
       </c>
       <c r="N131" s="1"/>
       <c r="O131" s="1">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="P131" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q131" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q131" s="1"/>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A132" s="2">
@@ -6931,23 +6903,21 @@
         <v>18</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G132" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="G132" s="1"/>
       <c r="H132" s="1"/>
       <c r="I132" s="1" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="J132" s="1">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="K132" s="1">
-        <v>66000</v>
+        <v>1100000</v>
       </c>
       <c r="L132" s="1">
         <v>0</v>
@@ -6957,14 +6927,12 @@
       </c>
       <c r="N132" s="1"/>
       <c r="O132" s="1">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P132" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q132" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q132" s="1"/>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A133" s="2">
@@ -6980,23 +6948,21 @@
         <v>18</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G133" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="G133" s="1"/>
       <c r="H133" s="1"/>
       <c r="I133" s="1" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="J133" s="1">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="K133" s="1">
-        <v>66000</v>
+        <v>1150000</v>
       </c>
       <c r="L133" s="1">
         <v>0</v>
@@ -7006,14 +6972,12 @@
       </c>
       <c r="N133" s="1"/>
       <c r="O133" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="P133" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q133" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q133" s="1"/>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A134" s="2">
@@ -7029,23 +6993,21 @@
         <v>18</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G134" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="G134" s="1"/>
       <c r="H134" s="1"/>
       <c r="I134" s="1" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="J134" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="K134" s="1">
-        <v>10500</v>
+        <v>1100000</v>
       </c>
       <c r="L134" s="1">
         <v>0</v>
@@ -7055,14 +7017,12 @@
       </c>
       <c r="N134" s="1"/>
       <c r="O134" s="1">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="P134" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q134" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q134" s="1"/>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A135" s="2">
@@ -7078,23 +7038,21 @@
         <v>18</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G135" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="G135" s="1"/>
       <c r="H135" s="1"/>
       <c r="I135" s="1" t="s">
         <v>29</v>
       </c>
       <c r="J135" s="1">
-        <v>2</v>
+        <v>140</v>
       </c>
       <c r="K135" s="1">
-        <v>12000</v>
+        <v>840000</v>
       </c>
       <c r="L135" s="1">
         <v>0</v>
@@ -7104,14 +7062,12 @@
       </c>
       <c r="N135" s="1"/>
       <c r="O135" s="1">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="P135" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q135" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q135" s="1"/>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A136" s="2">
@@ -7127,23 +7083,21 @@
         <v>18</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G136" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="G136" s="1"/>
       <c r="H136" s="1"/>
       <c r="I136" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="J136" s="1">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="K136" s="1">
-        <v>77000</v>
+        <v>375000</v>
       </c>
       <c r="L136" s="1">
         <v>0</v>
@@ -7153,14 +7107,12 @@
       </c>
       <c r="N136" s="1"/>
       <c r="O136" s="1">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="P136" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q136" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q136" s="1"/>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A137" s="2">
@@ -7176,23 +7128,21 @@
         <v>18</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G137" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="G137" s="1"/>
       <c r="H137" s="1"/>
       <c r="I137" s="1" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J137" s="1">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="K137" s="1">
-        <v>12000</v>
+        <v>375000</v>
       </c>
       <c r="L137" s="1">
         <v>0</v>
@@ -7202,14 +7152,12 @@
       </c>
       <c r="N137" s="1"/>
       <c r="O137" s="1">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="P137" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q137" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q137" s="1"/>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A138" s="2">
@@ -7225,23 +7173,21 @@
         <v>18</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G138" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="G138" s="1"/>
       <c r="H138" s="1"/>
       <c r="I138" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="J138" s="1">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="K138" s="1">
-        <v>11000</v>
+        <v>225000</v>
       </c>
       <c r="L138" s="1">
         <v>0</v>
@@ -7251,14 +7197,12 @@
       </c>
       <c r="N138" s="1"/>
       <c r="O138" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="P138" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q138" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q138" s="1"/>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A139" s="2">
@@ -7274,23 +7218,21 @@
         <v>18</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G139" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="G139" s="1"/>
       <c r="H139" s="1"/>
       <c r="I139" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="J139" s="1">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="K139" s="1">
-        <v>22000</v>
+        <v>225000</v>
       </c>
       <c r="L139" s="1">
         <v>0</v>
@@ -7300,14 +7242,12 @@
       </c>
       <c r="N139" s="1"/>
       <c r="O139" s="1">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="P139" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q139" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q139" s="1"/>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A140" s="2">
@@ -7329,27 +7269,27 @@
         <v>20</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H140" s="1"/>
       <c r="I140" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="J140" s="1">
-        <v>1</v>
+        <v>0.58333330000000005</v>
       </c>
       <c r="K140" s="1">
-        <v>6000</v>
+        <v>5250</v>
       </c>
       <c r="L140" s="1">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="M140" s="1">
         <v>0</v>
       </c>
       <c r="N140" s="1"/>
       <c r="O140" s="1">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="P140" s="1" t="s">
         <v>23</v>
@@ -7378,17 +7318,17 @@
         <v>20</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="H141" s="1"/>
       <c r="I141" s="1" t="s">
         <v>47</v>
       </c>
       <c r="J141" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K141" s="1">
-        <v>110000</v>
+        <v>66000</v>
       </c>
       <c r="L141" s="1">
         <v>0</v>
@@ -7398,7 +7338,7 @@
       </c>
       <c r="N141" s="1"/>
       <c r="O141" s="1">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="P141" s="1" t="s">
         <v>23</v>
@@ -7427,17 +7367,17 @@
         <v>20</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H142" s="1"/>
       <c r="I142" s="1" t="s">
         <v>47</v>
       </c>
       <c r="J142" s="1">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K142" s="1">
-        <v>121000</v>
+        <v>66000</v>
       </c>
       <c r="L142" s="1">
         <v>0</v>
@@ -7447,7 +7387,7 @@
       </c>
       <c r="N142" s="1"/>
       <c r="O142" s="1">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="P142" s="1" t="s">
         <v>23</v>
@@ -7476,17 +7416,17 @@
         <v>20</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H143" s="1"/>
       <c r="I143" s="1" t="s">
         <v>47</v>
       </c>
       <c r="J143" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K143" s="1">
-        <v>55000</v>
+        <v>66000</v>
       </c>
       <c r="L143" s="1">
         <v>0</v>
@@ -7496,7 +7436,7 @@
       </c>
       <c r="N143" s="1"/>
       <c r="O143" s="1">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="P143" s="1" t="s">
         <v>23</v>
@@ -7525,17 +7465,17 @@
         <v>20</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H144" s="1"/>
       <c r="I144" s="1" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="J144" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K144" s="1">
-        <v>55000</v>
+        <v>10500</v>
       </c>
       <c r="L144" s="1">
         <v>0</v>
@@ -7545,7 +7485,7 @@
       </c>
       <c r="N144" s="1"/>
       <c r="O144" s="1">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="P144" s="1" t="s">
         <v>23</v>
@@ -7574,17 +7514,17 @@
         <v>20</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H145" s="1"/>
       <c r="I145" s="1" t="s">
         <v>29</v>
       </c>
       <c r="J145" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K145" s="1">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="L145" s="1">
         <v>0</v>
@@ -7594,7 +7534,7 @@
       </c>
       <c r="N145" s="1"/>
       <c r="O145" s="1">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="P145" s="1" t="s">
         <v>23</v>
@@ -7623,17 +7563,17 @@
         <v>20</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H146" s="1"/>
       <c r="I146" s="1" t="s">
         <v>47</v>
       </c>
       <c r="J146" s="1">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K146" s="1">
-        <v>165000</v>
+        <v>77000</v>
       </c>
       <c r="L146" s="1">
         <v>0</v>
@@ -7643,7 +7583,7 @@
       </c>
       <c r="N146" s="1"/>
       <c r="O146" s="1">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="P146" s="1" t="s">
         <v>23</v>
@@ -7672,17 +7612,17 @@
         <v>20</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H147" s="1"/>
       <c r="I147" s="1" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="J147" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K147" s="1">
-        <v>4500</v>
+        <v>12000</v>
       </c>
       <c r="L147" s="1">
         <v>0</v>
@@ -7692,7 +7632,7 @@
       </c>
       <c r="N147" s="1"/>
       <c r="O147" s="1">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="P147" s="1" t="s">
         <v>23</v>
@@ -7721,17 +7661,17 @@
         <v>20</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H148" s="1"/>
       <c r="I148" s="1" t="s">
         <v>47</v>
       </c>
       <c r="J148" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K148" s="1">
-        <v>110000</v>
+        <v>11000</v>
       </c>
       <c r="L148" s="1">
         <v>0</v>
@@ -7741,7 +7681,7 @@
       </c>
       <c r="N148" s="1"/>
       <c r="O148" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P148" s="1" t="s">
         <v>23</v>
@@ -7764,21 +7704,23 @@
         <v>18</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G149" s="1"/>
+      <c r="G149" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="H149" s="1"/>
       <c r="I149" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J149" s="1">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="K149" s="1">
-        <v>445500</v>
+        <v>22000</v>
       </c>
       <c r="L149" s="1">
         <v>0</v>
@@ -7788,12 +7730,14 @@
       </c>
       <c r="N149" s="1"/>
       <c r="O149" s="1">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="P149" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q149" s="1"/>
+      <c r="Q149" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A150" s="2">
@@ -7809,21 +7753,23 @@
         <v>18</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G150" s="1"/>
+      <c r="G150" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="H150" s="1"/>
       <c r="I150" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J150" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K150" s="1">
-        <v>1100000</v>
+        <v>6000</v>
       </c>
       <c r="L150" s="1">
         <v>0</v>
@@ -7833,12 +7779,14 @@
       </c>
       <c r="N150" s="1"/>
       <c r="O150" s="1">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="P150" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q150" s="1"/>
+      <c r="Q150" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A151" s="2">
@@ -7854,21 +7802,23 @@
         <v>18</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G151" s="1"/>
+      <c r="G151" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="H151" s="1"/>
       <c r="I151" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="J151" s="1">
-        <v>134</v>
+        <v>10</v>
       </c>
       <c r="K151" s="1">
-        <v>804000</v>
+        <v>110000</v>
       </c>
       <c r="L151" s="1">
         <v>0</v>
@@ -7878,12 +7828,14 @@
       </c>
       <c r="N151" s="1"/>
       <c r="O151" s="1">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="P151" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q151" s="1"/>
+      <c r="Q151" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A152" s="2">
@@ -7899,21 +7851,23 @@
         <v>18</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G152" s="1"/>
+      <c r="G152" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="H152" s="1"/>
       <c r="I152" s="1" t="s">
         <v>47</v>
       </c>
       <c r="J152" s="1">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K152" s="1">
-        <v>176000</v>
+        <v>121000</v>
       </c>
       <c r="L152" s="1">
         <v>0</v>
@@ -7923,12 +7877,14 @@
       </c>
       <c r="N152" s="1"/>
       <c r="O152" s="1">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="P152" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q152" s="1"/>
+      <c r="Q152" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A153" s="2">
@@ -7944,21 +7900,23 @@
         <v>18</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G153" s="1"/>
+      <c r="G153" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="H153" s="1"/>
       <c r="I153" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="J153" s="1">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="K153" s="1">
-        <v>2200000</v>
+        <v>55000</v>
       </c>
       <c r="L153" s="1">
         <v>0</v>
@@ -7968,12 +7926,14 @@
       </c>
       <c r="N153" s="1"/>
       <c r="O153" s="1">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="P153" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q153" s="1"/>
+      <c r="Q153" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A154" s="2">
@@ -7989,21 +7949,23 @@
         <v>18</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G154" s="1"/>
+      <c r="G154" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="H154" s="1"/>
       <c r="I154" s="1" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="J154" s="1">
-        <v>24.416665999999999</v>
+        <v>5</v>
       </c>
       <c r="K154" s="1">
-        <v>219750</v>
+        <v>55000</v>
       </c>
       <c r="L154" s="1">
         <v>0</v>
@@ -8013,12 +7975,14 @@
       </c>
       <c r="N154" s="1"/>
       <c r="O154" s="1">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="P154" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q154" s="1"/>
+      <c r="Q154" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A155" s="2">
@@ -8034,21 +7998,23 @@
         <v>18</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G155" s="1"/>
+      <c r="G155" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="H155" s="1"/>
       <c r="I155" s="1" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="J155" s="1">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K155" s="1">
-        <v>375000</v>
+        <v>6000</v>
       </c>
       <c r="L155" s="1">
         <v>0</v>
@@ -8058,12 +8024,14 @@
       </c>
       <c r="N155" s="1"/>
       <c r="O155" s="1">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="P155" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q155" s="1"/>
+      <c r="Q155" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A156" s="2">
@@ -8079,21 +8047,23 @@
         <v>18</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G156" s="1"/>
+      <c r="G156" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="H156" s="1"/>
       <c r="I156" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J156" s="1">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K156" s="1">
-        <v>225000</v>
+        <v>165000</v>
       </c>
       <c r="L156" s="1">
         <v>0</v>
@@ -8103,12 +8073,14 @@
       </c>
       <c r="N156" s="1"/>
       <c r="O156" s="1">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P156" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q156" s="1"/>
+      <c r="Q156" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A157" s="2">
@@ -8124,21 +8096,23 @@
         <v>18</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G157" s="1"/>
+      <c r="G157" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="H157" s="1"/>
       <c r="I157" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J157" s="1">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K157" s="1">
-        <v>375000</v>
+        <v>4500</v>
       </c>
       <c r="L157" s="1">
         <v>0</v>
@@ -8148,12 +8122,14 @@
       </c>
       <c r="N157" s="1"/>
       <c r="O157" s="1">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="P157" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q157" s="1"/>
+      <c r="Q157" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A158" s="2">
@@ -8169,21 +8145,23 @@
         <v>18</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G158" s="1"/>
+      <c r="G158" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="H158" s="1"/>
       <c r="I158" s="1" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="J158" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K158" s="1">
-        <v>1150000</v>
+        <v>110000</v>
       </c>
       <c r="L158" s="1">
         <v>0</v>
@@ -8193,12 +8171,14 @@
       </c>
       <c r="N158" s="1"/>
       <c r="O158" s="1">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="P158" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q158" s="1"/>
+      <c r="Q158" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A159" s="2">
@@ -8222,13 +8202,13 @@
       <c r="G159" s="1"/>
       <c r="H159" s="1"/>
       <c r="I159" s="1" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="J159" s="1">
-        <v>599</v>
+        <v>99</v>
       </c>
       <c r="K159" s="1">
-        <v>6289500</v>
+        <v>445500</v>
       </c>
       <c r="L159" s="1">
         <v>0</v>
@@ -8238,12 +8218,462 @@
       </c>
       <c r="N159" s="1"/>
       <c r="O159" s="1">
+        <v>31</v>
+      </c>
+      <c r="P159" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q159" s="1"/>
+    </row>
+    <row r="160" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A160" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B160" s="1">
+        <v>0</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G160" s="1"/>
+      <c r="H160" s="1"/>
+      <c r="I160" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J160" s="1">
+        <v>100</v>
+      </c>
+      <c r="K160" s="1">
+        <v>1100000</v>
+      </c>
+      <c r="L160" s="1">
+        <v>0</v>
+      </c>
+      <c r="M160" s="1">
+        <v>0</v>
+      </c>
+      <c r="N160" s="1"/>
+      <c r="O160" s="1">
+        <v>32</v>
+      </c>
+      <c r="P160" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q160" s="1"/>
+    </row>
+    <row r="161" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A161" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B161" s="1">
+        <v>0</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G161" s="1"/>
+      <c r="H161" s="1"/>
+      <c r="I161" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J161" s="1">
+        <v>134</v>
+      </c>
+      <c r="K161" s="1">
+        <v>804000</v>
+      </c>
+      <c r="L161" s="1">
+        <v>0</v>
+      </c>
+      <c r="M161" s="1">
+        <v>0</v>
+      </c>
+      <c r="N161" s="1"/>
+      <c r="O161" s="1">
+        <v>33</v>
+      </c>
+      <c r="P161" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q161" s="1"/>
+    </row>
+    <row r="162" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A162" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B162" s="1">
+        <v>0</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G162" s="1"/>
+      <c r="H162" s="1"/>
+      <c r="I162" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J162" s="1">
+        <v>16</v>
+      </c>
+      <c r="K162" s="1">
+        <v>176000</v>
+      </c>
+      <c r="L162" s="1">
+        <v>0</v>
+      </c>
+      <c r="M162" s="1">
+        <v>0</v>
+      </c>
+      <c r="N162" s="1"/>
+      <c r="O162" s="1">
+        <v>34</v>
+      </c>
+      <c r="P162" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q162" s="1"/>
+    </row>
+    <row r="163" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A163" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B163" s="1">
+        <v>0</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G163" s="1"/>
+      <c r="H163" s="1"/>
+      <c r="I163" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J163" s="1">
+        <v>200</v>
+      </c>
+      <c r="K163" s="1">
+        <v>2200000</v>
+      </c>
+      <c r="L163" s="1">
+        <v>0</v>
+      </c>
+      <c r="M163" s="1">
+        <v>0</v>
+      </c>
+      <c r="N163" s="1"/>
+      <c r="O163" s="1">
+        <v>35</v>
+      </c>
+      <c r="P163" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q163" s="1"/>
+    </row>
+    <row r="164" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A164" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B164" s="1">
+        <v>0</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G164" s="1"/>
+      <c r="H164" s="1"/>
+      <c r="I164" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J164" s="1">
+        <v>24.416665999999999</v>
+      </c>
+      <c r="K164" s="1">
+        <v>219750</v>
+      </c>
+      <c r="L164" s="1">
+        <v>0</v>
+      </c>
+      <c r="M164" s="1">
+        <v>0</v>
+      </c>
+      <c r="N164" s="1"/>
+      <c r="O164" s="1">
+        <v>36</v>
+      </c>
+      <c r="P164" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q164" s="1"/>
+    </row>
+    <row r="165" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A165" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B165" s="1">
+        <v>0</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G165" s="1"/>
+      <c r="H165" s="1"/>
+      <c r="I165" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J165" s="1">
+        <v>25</v>
+      </c>
+      <c r="K165" s="1">
+        <v>375000</v>
+      </c>
+      <c r="L165" s="1">
+        <v>0</v>
+      </c>
+      <c r="M165" s="1">
+        <v>0</v>
+      </c>
+      <c r="N165" s="1"/>
+      <c r="O165" s="1">
+        <v>37</v>
+      </c>
+      <c r="P165" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q165" s="1"/>
+    </row>
+    <row r="166" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A166" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B166" s="1">
+        <v>0</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G166" s="1"/>
+      <c r="H166" s="1"/>
+      <c r="I166" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J166" s="1">
+        <v>25</v>
+      </c>
+      <c r="K166" s="1">
+        <v>225000</v>
+      </c>
+      <c r="L166" s="1">
+        <v>0</v>
+      </c>
+      <c r="M166" s="1">
+        <v>0</v>
+      </c>
+      <c r="N166" s="1"/>
+      <c r="O166" s="1">
+        <v>38</v>
+      </c>
+      <c r="P166" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q166" s="1"/>
+    </row>
+    <row r="167" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A167" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B167" s="1">
+        <v>0</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G167" s="1"/>
+      <c r="H167" s="1"/>
+      <c r="I167" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J167" s="1">
+        <v>25</v>
+      </c>
+      <c r="K167" s="1">
+        <v>375000</v>
+      </c>
+      <c r="L167" s="1">
+        <v>0</v>
+      </c>
+      <c r="M167" s="1">
+        <v>0</v>
+      </c>
+      <c r="N167" s="1"/>
+      <c r="O167" s="1">
+        <v>39</v>
+      </c>
+      <c r="P167" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q167" s="1"/>
+    </row>
+    <row r="168" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A168" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B168" s="1">
+        <v>0</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G168" s="1"/>
+      <c r="H168" s="1"/>
+      <c r="I168" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J168" s="1">
+        <v>100</v>
+      </c>
+      <c r="K168" s="1">
+        <v>1150000</v>
+      </c>
+      <c r="L168" s="1">
+        <v>0</v>
+      </c>
+      <c r="M168" s="1">
+        <v>0</v>
+      </c>
+      <c r="N168" s="1"/>
+      <c r="O168" s="1">
+        <v>40</v>
+      </c>
+      <c r="P168" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q168" s="1"/>
+    </row>
+    <row r="169" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A169" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B169" s="1">
+        <v>0</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G169" s="1"/>
+      <c r="H169" s="1"/>
+      <c r="I169" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J169" s="1">
+        <v>599</v>
+      </c>
+      <c r="K169" s="1">
+        <v>6289500</v>
+      </c>
+      <c r="L169" s="1">
+        <v>0</v>
+      </c>
+      <c r="M169" s="1">
+        <v>0</v>
+      </c>
+      <c r="N169" s="1"/>
+      <c r="O169" s="1">
         <v>41</v>
       </c>
-      <c r="P159" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q159" s="1"/>
+      <c r="P169" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q169" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABC1AF5-717E-43B9-A0D7-268EE81DFABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B17AE2-89B6-455D-BF3E-166A0F3AF154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1564" uniqueCount="49">
   <si>
     <t>Date</t>
   </si>
@@ -553,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q197"/>
+  <dimension ref="A1:Q207"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.3984375" customWidth="1"/>
@@ -2003,11 +2003,9 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A30" s="2">
-        <v>46225</v>
-      </c>
-      <c r="B30" s="1">
-        <v>0</v>
-      </c>
+        <v>46226</v>
+      </c>
+      <c r="B30" s="1"/>
       <c r="C30" s="1" t="s">
         <v>17</v>
       </c>
@@ -2015,48 +2013,42 @@
         <v>18</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="J30" s="1">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="K30" s="1">
-        <v>27000</v>
+        <v>423000</v>
       </c>
       <c r="L30" s="1">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="M30" s="1">
         <v>0</v>
       </c>
       <c r="N30" s="1"/>
       <c r="O30" s="1">
-        <v>131</v>
+        <v>197</v>
       </c>
       <c r="P30" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q30" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q30" s="1"/>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A31" s="2">
-        <v>46225</v>
-      </c>
-      <c r="B31" s="1">
-        <v>0</v>
-      </c>
+        <v>46226</v>
+      </c>
+      <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
         <v>17</v>
       </c>
@@ -2064,23 +2056,21 @@
         <v>18</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J31" s="1">
-        <v>3</v>
+        <v>99.4</v>
       </c>
       <c r="K31" s="1">
-        <v>27000</v>
+        <v>1093400</v>
       </c>
       <c r="L31" s="1">
         <v>0</v>
@@ -2090,22 +2080,18 @@
       </c>
       <c r="N31" s="1"/>
       <c r="O31" s="1">
-        <v>132</v>
+        <v>198</v>
       </c>
       <c r="P31" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q31" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q31" s="1"/>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A32" s="2">
-        <v>46225</v>
-      </c>
-      <c r="B32" s="1">
-        <v>0</v>
-      </c>
+        <v>46226</v>
+      </c>
+      <c r="B32" s="1"/>
       <c r="C32" s="1" t="s">
         <v>17</v>
       </c>
@@ -2113,23 +2099,21 @@
         <v>18</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J32" s="1">
-        <v>4.1666667999999997E-2</v>
+        <v>99.5</v>
       </c>
       <c r="K32" s="1">
-        <v>479.16665999999998</v>
+        <v>597000</v>
       </c>
       <c r="L32" s="1">
         <v>0</v>
@@ -2139,22 +2123,18 @@
       </c>
       <c r="N32" s="1"/>
       <c r="O32" s="1">
-        <v>133</v>
+        <v>199</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q32" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q32" s="1"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A33" s="2">
-        <v>46225</v>
-      </c>
-      <c r="B33" s="1">
-        <v>0</v>
-      </c>
+        <v>46226</v>
+      </c>
+      <c r="B33" s="1"/>
       <c r="C33" s="1" t="s">
         <v>17</v>
       </c>
@@ -2162,23 +2142,21 @@
         <v>18</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J33" s="1">
-        <v>1</v>
+        <v>191.33332999999999</v>
       </c>
       <c r="K33" s="1">
-        <v>9000</v>
+        <v>2104666.7999999998</v>
       </c>
       <c r="L33" s="1">
         <v>0</v>
@@ -2188,22 +2166,18 @@
       </c>
       <c r="N33" s="1"/>
       <c r="O33" s="1">
-        <v>134</v>
+        <v>200</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q33" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q33" s="1"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A34" s="2">
-        <v>46225</v>
-      </c>
-      <c r="B34" s="1">
-        <v>0</v>
-      </c>
+        <v>46226</v>
+      </c>
+      <c r="B34" s="1"/>
       <c r="C34" s="1" t="s">
         <v>17</v>
       </c>
@@ -2211,23 +2185,21 @@
         <v>18</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G34" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J34" s="1">
-        <v>0.5</v>
+        <v>18.666665999999999</v>
       </c>
       <c r="K34" s="1">
-        <v>5750</v>
+        <v>168000</v>
       </c>
       <c r="L34" s="1">
         <v>0</v>
@@ -2237,22 +2209,18 @@
       </c>
       <c r="N34" s="1"/>
       <c r="O34" s="1">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q34" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q34" s="1"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A35" s="2">
-        <v>46225</v>
-      </c>
-      <c r="B35" s="1">
-        <v>0</v>
-      </c>
+        <v>46226</v>
+      </c>
+      <c r="B35" s="1"/>
       <c r="C35" s="1" t="s">
         <v>17</v>
       </c>
@@ -2260,23 +2228,21 @@
         <v>18</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="J35" s="1">
-        <v>0.2</v>
+        <v>23</v>
       </c>
       <c r="K35" s="1">
-        <v>2200</v>
+        <v>345000</v>
       </c>
       <c r="L35" s="1">
         <v>0</v>
@@ -2286,22 +2252,18 @@
       </c>
       <c r="N35" s="1"/>
       <c r="O35" s="1">
-        <v>136</v>
+        <v>202</v>
       </c>
       <c r="P35" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q35" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q35" s="1"/>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A36" s="2">
-        <v>46225</v>
-      </c>
-      <c r="B36" s="1">
-        <v>0</v>
-      </c>
+        <v>46226</v>
+      </c>
+      <c r="B36" s="1"/>
       <c r="C36" s="1" t="s">
         <v>17</v>
       </c>
@@ -2309,23 +2271,21 @@
         <v>18</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G36" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="J36" s="1">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="K36" s="1">
-        <v>12000</v>
+        <v>225000</v>
       </c>
       <c r="L36" s="1">
         <v>0</v>
@@ -2335,22 +2295,18 @@
       </c>
       <c r="N36" s="1"/>
       <c r="O36" s="1">
-        <v>137</v>
+        <v>203</v>
       </c>
       <c r="P36" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q36" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q36" s="1"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A37" s="2">
-        <v>46225</v>
-      </c>
-      <c r="B37" s="1">
-        <v>0</v>
-      </c>
+        <v>46226</v>
+      </c>
+      <c r="B37" s="1"/>
       <c r="C37" s="1" t="s">
         <v>17</v>
       </c>
@@ -2358,23 +2314,21 @@
         <v>18</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G37" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="J37" s="1">
-        <v>8.3333335999999994E-2</v>
+        <v>25</v>
       </c>
       <c r="K37" s="1">
-        <v>958.33330000000001</v>
+        <v>375000</v>
       </c>
       <c r="L37" s="1">
         <v>0</v>
@@ -2384,22 +2338,18 @@
       </c>
       <c r="N37" s="1"/>
       <c r="O37" s="1">
-        <v>138</v>
+        <v>204</v>
       </c>
       <c r="P37" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q37" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q37" s="1"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A38" s="2">
-        <v>46225</v>
-      </c>
-      <c r="B38" s="1">
-        <v>0</v>
-      </c>
+        <v>46226</v>
+      </c>
+      <c r="B38" s="1"/>
       <c r="C38" s="1" t="s">
         <v>17</v>
       </c>
@@ -2407,23 +2357,21 @@
         <v>18</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J38" s="1">
-        <v>1.5</v>
+        <v>88.041663999999997</v>
       </c>
       <c r="K38" s="1">
-        <v>13500</v>
+        <v>1012479.2</v>
       </c>
       <c r="L38" s="1">
         <v>0</v>
@@ -2433,22 +2381,18 @@
       </c>
       <c r="N38" s="1"/>
       <c r="O38" s="1">
-        <v>139</v>
+        <v>205</v>
       </c>
       <c r="P38" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q38" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q38" s="1"/>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A39" s="2">
-        <v>46225</v>
-      </c>
-      <c r="B39" s="1">
-        <v>0</v>
-      </c>
+        <v>46226</v>
+      </c>
+      <c r="B39" s="1"/>
       <c r="C39" s="1" t="s">
         <v>17</v>
       </c>
@@ -2456,23 +2400,21 @@
         <v>18</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G39" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J39" s="1">
-        <v>0.5</v>
+        <v>262</v>
       </c>
       <c r="K39" s="1">
-        <v>5500</v>
+        <v>2358000</v>
       </c>
       <c r="L39" s="1">
         <v>0</v>
@@ -2482,14 +2424,12 @@
       </c>
       <c r="N39" s="1"/>
       <c r="O39" s="1">
-        <v>140</v>
+        <v>206</v>
       </c>
       <c r="P39" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q39" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q39" s="1"/>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A40" s="2">
@@ -2511,27 +2451,27 @@
         <v>20</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J40" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K40" s="1">
-        <v>6000</v>
+        <v>27000</v>
       </c>
       <c r="L40" s="1">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="M40" s="1">
         <v>0</v>
       </c>
       <c r="N40" s="1"/>
       <c r="O40" s="1">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="P40" s="1" t="s">
         <v>23</v>
@@ -2560,17 +2500,17 @@
         <v>20</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J41" s="1">
-        <v>8.3333335999999994E-2</v>
+        <v>3</v>
       </c>
       <c r="K41" s="1">
-        <v>958.33330000000001</v>
+        <v>27000</v>
       </c>
       <c r="L41" s="1">
         <v>0</v>
@@ -2580,7 +2520,7 @@
       </c>
       <c r="N41" s="1"/>
       <c r="O41" s="1">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="P41" s="1" t="s">
         <v>23</v>
@@ -2609,17 +2549,17 @@
         <v>20</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J42" s="1">
-        <v>1</v>
+        <v>4.1666667999999997E-2</v>
       </c>
       <c r="K42" s="1">
-        <v>9000</v>
+        <v>479.16665999999998</v>
       </c>
       <c r="L42" s="1">
         <v>0</v>
@@ -2629,7 +2569,7 @@
       </c>
       <c r="N42" s="1"/>
       <c r="O42" s="1">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="P42" s="1" t="s">
         <v>23</v>
@@ -2658,17 +2598,17 @@
         <v>20</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J43" s="1">
         <v>1</v>
       </c>
       <c r="K43" s="1">
-        <v>11000</v>
+        <v>9000</v>
       </c>
       <c r="L43" s="1">
         <v>0</v>
@@ -2678,7 +2618,7 @@
       </c>
       <c r="N43" s="1"/>
       <c r="O43" s="1">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>23</v>
@@ -2707,17 +2647,17 @@
         <v>20</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J44" s="1">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="K44" s="1">
-        <v>1100</v>
+        <v>5750</v>
       </c>
       <c r="L44" s="1">
         <v>0</v>
@@ -2727,7 +2667,7 @@
       </c>
       <c r="N44" s="1"/>
       <c r="O44" s="1">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="P44" s="1" t="s">
         <v>23</v>
@@ -2756,17 +2696,17 @@
         <v>20</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J45" s="1">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="K45" s="1">
-        <v>45000</v>
+        <v>2200</v>
       </c>
       <c r="L45" s="1">
         <v>0</v>
@@ -2776,7 +2716,7 @@
       </c>
       <c r="N45" s="1"/>
       <c r="O45" s="1">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="P45" s="1" t="s">
         <v>23</v>
@@ -2805,17 +2745,17 @@
         <v>20</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J46" s="1">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="K46" s="1">
-        <v>2875</v>
+        <v>12000</v>
       </c>
       <c r="L46" s="1">
         <v>0</v>
@@ -2825,7 +2765,7 @@
       </c>
       <c r="N46" s="1"/>
       <c r="O46" s="1">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="P46" s="1" t="s">
         <v>23</v>
@@ -2854,17 +2794,17 @@
         <v>20</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J47" s="1">
-        <v>6</v>
+        <v>8.3333335999999994E-2</v>
       </c>
       <c r="K47" s="1">
-        <v>54000</v>
+        <v>958.33330000000001</v>
       </c>
       <c r="L47" s="1">
         <v>0</v>
@@ -2874,7 +2814,7 @@
       </c>
       <c r="N47" s="1"/>
       <c r="O47" s="1">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="P47" s="1" t="s">
         <v>23</v>
@@ -2903,17 +2843,17 @@
         <v>20</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J48" s="1">
-        <v>8.3333335999999994E-2</v>
+        <v>1.5</v>
       </c>
       <c r="K48" s="1">
-        <v>916.66669999999999</v>
+        <v>13500</v>
       </c>
       <c r="L48" s="1">
         <v>0</v>
@@ -2923,7 +2863,7 @@
       </c>
       <c r="N48" s="1"/>
       <c r="O48" s="1">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="P48" s="1" t="s">
         <v>23</v>
@@ -2952,17 +2892,17 @@
         <v>20</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J49" s="1">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="K49" s="1">
-        <v>18000</v>
+        <v>5500</v>
       </c>
       <c r="L49" s="1">
         <v>0</v>
@@ -2972,7 +2912,7 @@
       </c>
       <c r="N49" s="1"/>
       <c r="O49" s="1">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="P49" s="1" t="s">
         <v>23</v>
@@ -3001,17 +2941,17 @@
         <v>20</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J50" s="1">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="K50" s="1">
-        <v>1100</v>
+        <v>6000</v>
       </c>
       <c r="L50" s="1">
         <v>0</v>
@@ -3021,7 +2961,7 @@
       </c>
       <c r="N50" s="1"/>
       <c r="O50" s="1">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="P50" s="1" t="s">
         <v>23</v>
@@ -3050,17 +2990,17 @@
         <v>20</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J51" s="1">
-        <v>2</v>
+        <v>8.3333335999999994E-2</v>
       </c>
       <c r="K51" s="1">
-        <v>18000</v>
+        <v>958.33330000000001</v>
       </c>
       <c r="L51" s="1">
         <v>0</v>
@@ -3070,7 +3010,7 @@
       </c>
       <c r="N51" s="1"/>
       <c r="O51" s="1">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="P51" s="1" t="s">
         <v>23</v>
@@ -3099,17 +3039,17 @@
         <v>20</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J52" s="1">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="K52" s="1">
-        <v>49500</v>
+        <v>9000</v>
       </c>
       <c r="L52" s="1">
         <v>0</v>
@@ -3119,7 +3059,7 @@
       </c>
       <c r="N52" s="1"/>
       <c r="O52" s="1">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="P52" s="1" t="s">
         <v>23</v>
@@ -3148,17 +3088,17 @@
         <v>20</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J53" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K53" s="1">
-        <v>18000</v>
+        <v>11000</v>
       </c>
       <c r="L53" s="1">
         <v>0</v>
@@ -3168,7 +3108,7 @@
       </c>
       <c r="N53" s="1"/>
       <c r="O53" s="1">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="P53" s="1" t="s">
         <v>23</v>
@@ -3197,17 +3137,17 @@
         <v>20</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J54" s="1">
-        <v>8.3333335999999994E-2</v>
+        <v>0.1</v>
       </c>
       <c r="K54" s="1">
-        <v>916.66669999999999</v>
+        <v>1100</v>
       </c>
       <c r="L54" s="1">
         <v>0</v>
@@ -3217,7 +3157,7 @@
       </c>
       <c r="N54" s="1"/>
       <c r="O54" s="1">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="P54" s="1" t="s">
         <v>23</v>
@@ -3246,17 +3186,17 @@
         <v>20</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J55" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K55" s="1">
-        <v>54000</v>
+        <v>45000</v>
       </c>
       <c r="L55" s="1">
         <v>0</v>
@@ -3266,7 +3206,7 @@
       </c>
       <c r="N55" s="1"/>
       <c r="O55" s="1">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="P55" s="1" t="s">
         <v>23</v>
@@ -3295,17 +3235,17 @@
         <v>20</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J56" s="1">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K56" s="1">
-        <v>6000</v>
+        <v>2875</v>
       </c>
       <c r="L56" s="1">
         <v>0</v>
@@ -3315,7 +3255,7 @@
       </c>
       <c r="N56" s="1"/>
       <c r="O56" s="1">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="P56" s="1" t="s">
         <v>23</v>
@@ -3344,17 +3284,17 @@
         <v>20</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J57" s="1">
-        <v>4.1666667999999997E-2</v>
+        <v>6</v>
       </c>
       <c r="K57" s="1">
-        <v>479.16665999999998</v>
+        <v>54000</v>
       </c>
       <c r="L57" s="1">
         <v>0</v>
@@ -3364,7 +3304,7 @@
       </c>
       <c r="N57" s="1"/>
       <c r="O57" s="1">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="P57" s="1" t="s">
         <v>23</v>
@@ -3377,7 +3317,9 @@
       <c r="A58" s="2">
         <v>46225</v>
       </c>
-      <c r="B58" s="1"/>
+      <c r="B58" s="1">
+        <v>0</v>
+      </c>
       <c r="C58" s="1" t="s">
         <v>17</v>
       </c>
@@ -3385,21 +3327,23 @@
         <v>18</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G58" s="1"/>
+      <c r="G58" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J58" s="1">
-        <v>99.6</v>
+        <v>8.3333335999999994E-2</v>
       </c>
       <c r="K58" s="1">
-        <v>1095600</v>
+        <v>916.66669999999999</v>
       </c>
       <c r="L58" s="1">
         <v>0</v>
@@ -3409,18 +3353,22 @@
       </c>
       <c r="N58" s="1"/>
       <c r="O58" s="1">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="P58" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q58" s="1"/>
+      <c r="Q58" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A59" s="2">
         <v>46225</v>
       </c>
-      <c r="B59" s="1"/>
+      <c r="B59" s="1">
+        <v>0</v>
+      </c>
       <c r="C59" s="1" t="s">
         <v>17</v>
       </c>
@@ -3428,21 +3376,23 @@
         <v>18</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G59" s="1"/>
+      <c r="G59" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J59" s="1">
-        <v>103.5</v>
+        <v>2</v>
       </c>
       <c r="K59" s="1">
-        <v>621000</v>
+        <v>18000</v>
       </c>
       <c r="L59" s="1">
         <v>0</v>
@@ -3452,18 +3402,22 @@
       </c>
       <c r="N59" s="1"/>
       <c r="O59" s="1">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="P59" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q59" s="1"/>
+      <c r="Q59" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A60" s="2">
         <v>46225</v>
       </c>
-      <c r="B60" s="1"/>
+      <c r="B60" s="1">
+        <v>0</v>
+      </c>
       <c r="C60" s="1" t="s">
         <v>17</v>
       </c>
@@ -3471,21 +3425,23 @@
         <v>18</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G60" s="1"/>
+      <c r="G60" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J60" s="1">
-        <v>192.5</v>
+        <v>0.1</v>
       </c>
       <c r="K60" s="1">
-        <v>2117500</v>
+        <v>1100</v>
       </c>
       <c r="L60" s="1">
         <v>0</v>
@@ -3495,18 +3451,22 @@
       </c>
       <c r="N60" s="1"/>
       <c r="O60" s="1">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="P60" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q60" s="1"/>
+      <c r="Q60" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A61" s="2">
         <v>46225</v>
       </c>
-      <c r="B61" s="1"/>
+      <c r="B61" s="1">
+        <v>0</v>
+      </c>
       <c r="C61" s="1" t="s">
         <v>17</v>
       </c>
@@ -3514,21 +3474,23 @@
         <v>18</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G61" s="1"/>
+      <c r="G61" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J61" s="1">
-        <v>19.916665999999999</v>
+        <v>2</v>
       </c>
       <c r="K61" s="1">
-        <v>179250</v>
+        <v>18000</v>
       </c>
       <c r="L61" s="1">
         <v>0</v>
@@ -3538,18 +3500,22 @@
       </c>
       <c r="N61" s="1"/>
       <c r="O61" s="1">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="P61" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q61" s="1"/>
+      <c r="Q61" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A62" s="2">
         <v>46225</v>
       </c>
-      <c r="B62" s="1"/>
+      <c r="B62" s="1">
+        <v>0</v>
+      </c>
       <c r="C62" s="1" t="s">
         <v>17</v>
       </c>
@@ -3557,21 +3523,23 @@
         <v>18</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G62" s="1"/>
+      <c r="G62" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="J62" s="1">
-        <v>95</v>
+        <v>5.5</v>
       </c>
       <c r="K62" s="1">
-        <v>427500</v>
+        <v>49500</v>
       </c>
       <c r="L62" s="1">
         <v>0</v>
@@ -3581,18 +3549,22 @@
       </c>
       <c r="N62" s="1"/>
       <c r="O62" s="1">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="P62" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q62" s="1"/>
+      <c r="Q62" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A63" s="2">
         <v>46225</v>
       </c>
-      <c r="B63" s="1"/>
+      <c r="B63" s="1">
+        <v>0</v>
+      </c>
       <c r="C63" s="1" t="s">
         <v>17</v>
       </c>
@@ -3600,21 +3572,23 @@
         <v>18</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G63" s="1"/>
+      <c r="G63" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="J63" s="1">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="K63" s="1">
-        <v>345000</v>
+        <v>18000</v>
       </c>
       <c r="L63" s="1">
         <v>0</v>
@@ -3624,18 +3598,22 @@
       </c>
       <c r="N63" s="1"/>
       <c r="O63" s="1">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="P63" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q63" s="1"/>
+      <c r="Q63" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A64" s="2">
         <v>46225</v>
       </c>
-      <c r="B64" s="1"/>
+      <c r="B64" s="1">
+        <v>0</v>
+      </c>
       <c r="C64" s="1" t="s">
         <v>17</v>
       </c>
@@ -3643,21 +3621,23 @@
         <v>18</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G64" s="1"/>
+      <c r="G64" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="J64" s="1">
-        <v>25</v>
+        <v>8.3333335999999994E-2</v>
       </c>
       <c r="K64" s="1">
-        <v>225000</v>
+        <v>916.66669999999999</v>
       </c>
       <c r="L64" s="1">
         <v>0</v>
@@ -3667,18 +3647,22 @@
       </c>
       <c r="N64" s="1"/>
       <c r="O64" s="1">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="P64" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q64" s="1"/>
+      <c r="Q64" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A65" s="2">
         <v>46225</v>
       </c>
-      <c r="B65" s="1"/>
+      <c r="B65" s="1">
+        <v>0</v>
+      </c>
       <c r="C65" s="1" t="s">
         <v>17</v>
       </c>
@@ -3686,21 +3670,23 @@
         <v>18</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G65" s="1"/>
+      <c r="G65" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="J65" s="1">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="K65" s="1">
-        <v>375000</v>
+        <v>54000</v>
       </c>
       <c r="L65" s="1">
         <v>0</v>
@@ -3710,18 +3696,22 @@
       </c>
       <c r="N65" s="1"/>
       <c r="O65" s="1">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="P65" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q65" s="1"/>
+      <c r="Q65" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A66" s="2">
         <v>46225</v>
       </c>
-      <c r="B66" s="1"/>
+      <c r="B66" s="1">
+        <v>0</v>
+      </c>
       <c r="C66" s="1" t="s">
         <v>17</v>
       </c>
@@ -3729,21 +3719,23 @@
         <v>18</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G66" s="1"/>
+      <c r="G66" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J66" s="1">
-        <v>91.375</v>
+        <v>1</v>
       </c>
       <c r="K66" s="1">
-        <v>1050812.5</v>
+        <v>6000</v>
       </c>
       <c r="L66" s="1">
         <v>0</v>
@@ -3753,18 +3745,22 @@
       </c>
       <c r="N66" s="1"/>
       <c r="O66" s="1">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="P66" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q66" s="1"/>
+      <c r="Q66" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A67" s="2">
         <v>46225</v>
       </c>
-      <c r="B67" s="1"/>
+      <c r="B67" s="1">
+        <v>0</v>
+      </c>
       <c r="C67" s="1" t="s">
         <v>17</v>
       </c>
@@ -3772,21 +3768,23 @@
         <v>18</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G67" s="1"/>
+      <c r="G67" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J67" s="1">
-        <v>373</v>
+        <v>4.1666667999999997E-2</v>
       </c>
       <c r="K67" s="1">
-        <v>3357000</v>
+        <v>479.16665999999998</v>
       </c>
       <c r="L67" s="1">
         <v>0</v>
@@ -3796,20 +3794,20 @@
       </c>
       <c r="N67" s="1"/>
       <c r="O67" s="1">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="P67" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q67" s="1"/>
+      <c r="Q67" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A68" s="2">
-        <v>46224</v>
-      </c>
-      <c r="B68" s="1">
-        <v>0</v>
-      </c>
+        <v>46225</v>
+      </c>
+      <c r="B68" s="1"/>
       <c r="C68" s="1" t="s">
         <v>17</v>
       </c>
@@ -3825,13 +3823,13 @@
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
       <c r="I68" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="J68" s="1">
-        <v>95</v>
+        <v>99.6</v>
       </c>
       <c r="K68" s="1">
-        <v>427500</v>
+        <v>1095600</v>
       </c>
       <c r="L68" s="1">
         <v>0</v>
@@ -3841,7 +3839,7 @@
       </c>
       <c r="N68" s="1"/>
       <c r="O68" s="1">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="P68" s="1" t="s">
         <v>23</v>
@@ -3850,11 +3848,9 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A69" s="2">
-        <v>46224</v>
-      </c>
-      <c r="B69" s="1">
-        <v>0</v>
-      </c>
+        <v>46225</v>
+      </c>
+      <c r="B69" s="1"/>
       <c r="C69" s="1" t="s">
         <v>17</v>
       </c>
@@ -3870,13 +3866,13 @@
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J69" s="1">
-        <v>100</v>
+        <v>103.5</v>
       </c>
       <c r="K69" s="1">
-        <v>1100000</v>
+        <v>621000</v>
       </c>
       <c r="L69" s="1">
         <v>0</v>
@@ -3886,7 +3882,7 @@
       </c>
       <c r="N69" s="1"/>
       <c r="O69" s="1">
-        <v>93</v>
+        <v>160</v>
       </c>
       <c r="P69" s="1" t="s">
         <v>23</v>
@@ -3895,11 +3891,9 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A70" s="2">
-        <v>46224</v>
-      </c>
-      <c r="B70" s="1">
-        <v>0</v>
-      </c>
+        <v>46225</v>
+      </c>
+      <c r="B70" s="1"/>
       <c r="C70" s="1" t="s">
         <v>17</v>
       </c>
@@ -3915,13 +3909,13 @@
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
       <c r="I70" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J70" s="1">
-        <v>107.5</v>
+        <v>192.5</v>
       </c>
       <c r="K70" s="1">
-        <v>645000</v>
+        <v>2117500</v>
       </c>
       <c r="L70" s="1">
         <v>0</v>
@@ -3931,7 +3925,7 @@
       </c>
       <c r="N70" s="1"/>
       <c r="O70" s="1">
-        <v>94</v>
+        <v>161</v>
       </c>
       <c r="P70" s="1" t="s">
         <v>23</v>
@@ -3940,11 +3934,9 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A71" s="2">
-        <v>46224</v>
-      </c>
-      <c r="B71" s="1">
-        <v>0</v>
-      </c>
+        <v>46225</v>
+      </c>
+      <c r="B71" s="1"/>
       <c r="C71" s="1" t="s">
         <v>17</v>
       </c>
@@ -3960,13 +3952,13 @@
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J71" s="1">
-        <v>194.16667000000001</v>
+        <v>19.916665999999999</v>
       </c>
       <c r="K71" s="1">
-        <v>2135833.2000000002</v>
+        <v>179250</v>
       </c>
       <c r="L71" s="1">
         <v>0</v>
@@ -3976,7 +3968,7 @@
       </c>
       <c r="N71" s="1"/>
       <c r="O71" s="1">
-        <v>95</v>
+        <v>162</v>
       </c>
       <c r="P71" s="1" t="s">
         <v>23</v>
@@ -3985,11 +3977,9 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A72" s="2">
-        <v>46224</v>
-      </c>
-      <c r="B72" s="1">
-        <v>0</v>
-      </c>
+        <v>46225</v>
+      </c>
+      <c r="B72" s="1"/>
       <c r="C72" s="1" t="s">
         <v>17</v>
       </c>
@@ -4005,13 +3995,13 @@
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
       <c r="I72" s="1" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="J72" s="1">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="K72" s="1">
-        <v>345000</v>
+        <v>427500</v>
       </c>
       <c r="L72" s="1">
         <v>0</v>
@@ -4021,7 +4011,7 @@
       </c>
       <c r="N72" s="1"/>
       <c r="O72" s="1">
-        <v>96</v>
+        <v>163</v>
       </c>
       <c r="P72" s="1" t="s">
         <v>23</v>
@@ -4030,11 +4020,9 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A73" s="2">
-        <v>46224</v>
-      </c>
-      <c r="B73" s="1">
-        <v>0</v>
-      </c>
+        <v>46225</v>
+      </c>
+      <c r="B73" s="1"/>
       <c r="C73" s="1" t="s">
         <v>17</v>
       </c>
@@ -4050,13 +4038,13 @@
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
       <c r="I73" s="1" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="J73" s="1">
-        <v>21.916665999999999</v>
+        <v>23</v>
       </c>
       <c r="K73" s="1">
-        <v>197250</v>
+        <v>345000</v>
       </c>
       <c r="L73" s="1">
         <v>0</v>
@@ -4066,7 +4054,7 @@
       </c>
       <c r="N73" s="1"/>
       <c r="O73" s="1">
-        <v>97</v>
+        <v>164</v>
       </c>
       <c r="P73" s="1" t="s">
         <v>23</v>
@@ -4075,11 +4063,9 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A74" s="2">
-        <v>46224</v>
-      </c>
-      <c r="B74" s="1">
-        <v>0</v>
-      </c>
+        <v>46225</v>
+      </c>
+      <c r="B74" s="1"/>
       <c r="C74" s="1" t="s">
         <v>17</v>
       </c>
@@ -4111,7 +4097,7 @@
       </c>
       <c r="N74" s="1"/>
       <c r="O74" s="1">
-        <v>98</v>
+        <v>165</v>
       </c>
       <c r="P74" s="1" t="s">
         <v>23</v>
@@ -4120,11 +4106,9 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A75" s="2">
-        <v>46224</v>
-      </c>
-      <c r="B75" s="1">
-        <v>0</v>
-      </c>
+        <v>46225</v>
+      </c>
+      <c r="B75" s="1"/>
       <c r="C75" s="1" t="s">
         <v>17</v>
       </c>
@@ -4156,7 +4140,7 @@
       </c>
       <c r="N75" s="1"/>
       <c r="O75" s="1">
-        <v>99</v>
+        <v>166</v>
       </c>
       <c r="P75" s="1" t="s">
         <v>23</v>
@@ -4165,11 +4149,9 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A76" s="2">
-        <v>46224</v>
-      </c>
-      <c r="B76" s="1">
-        <v>0</v>
-      </c>
+        <v>46225</v>
+      </c>
+      <c r="B76" s="1"/>
       <c r="C76" s="1" t="s">
         <v>17</v>
       </c>
@@ -4188,10 +4170,10 @@
         <v>22</v>
       </c>
       <c r="J76" s="1">
-        <v>92.375</v>
+        <v>91.375</v>
       </c>
       <c r="K76" s="1">
-        <v>1062312.5</v>
+        <v>1050812.5</v>
       </c>
       <c r="L76" s="1">
         <v>0</v>
@@ -4201,7 +4183,7 @@
       </c>
       <c r="N76" s="1"/>
       <c r="O76" s="1">
-        <v>100</v>
+        <v>167</v>
       </c>
       <c r="P76" s="1" t="s">
         <v>23</v>
@@ -4210,11 +4192,9 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A77" s="2">
-        <v>46224</v>
-      </c>
-      <c r="B77" s="1">
-        <v>0</v>
-      </c>
+        <v>46225</v>
+      </c>
+      <c r="B77" s="1"/>
       <c r="C77" s="1" t="s">
         <v>17</v>
       </c>
@@ -4233,10 +4213,10 @@
         <v>25</v>
       </c>
       <c r="J77" s="1">
-        <v>409</v>
+        <v>373</v>
       </c>
       <c r="K77" s="1">
-        <v>3681000</v>
+        <v>3357000</v>
       </c>
       <c r="L77" s="1">
         <v>0</v>
@@ -4246,7 +4226,7 @@
       </c>
       <c r="N77" s="1"/>
       <c r="O77" s="1">
-        <v>101</v>
+        <v>168</v>
       </c>
       <c r="P77" s="1" t="s">
         <v>23</v>
@@ -4267,40 +4247,36 @@
         <v>18</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G78" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="G78" s="1"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="J78" s="1">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="K78" s="1">
-        <v>297000</v>
+        <v>427500</v>
       </c>
       <c r="L78" s="1">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="M78" s="1">
         <v>0</v>
       </c>
       <c r="N78" s="1"/>
       <c r="O78" s="1">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="P78" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q78" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q78" s="1"/>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A79" s="2">
@@ -4316,23 +4292,21 @@
         <v>18</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G79" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="G79" s="1"/>
       <c r="H79" s="1"/>
       <c r="I79" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J79" s="1">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="K79" s="1">
-        <v>27000</v>
+        <v>1100000</v>
       </c>
       <c r="L79" s="1">
         <v>0</v>
@@ -4342,14 +4316,12 @@
       </c>
       <c r="N79" s="1"/>
       <c r="O79" s="1">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="P79" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q79" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q79" s="1"/>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A80" s="2">
@@ -4365,23 +4337,21 @@
         <v>18</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G80" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="G80" s="1"/>
       <c r="H80" s="1"/>
       <c r="I80" s="1" t="s">
         <v>31</v>
       </c>
       <c r="J80" s="1">
-        <v>1</v>
+        <v>107.5</v>
       </c>
       <c r="K80" s="1">
-        <v>6000</v>
+        <v>645000</v>
       </c>
       <c r="L80" s="1">
         <v>0</v>
@@ -4391,14 +4361,12 @@
       </c>
       <c r="N80" s="1"/>
       <c r="O80" s="1">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="P80" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q80" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q80" s="1"/>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A81" s="2">
@@ -4414,23 +4382,21 @@
         <v>18</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G81" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="G81" s="1"/>
       <c r="H81" s="1"/>
       <c r="I81" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J81" s="1">
-        <v>6</v>
+        <v>194.16667000000001</v>
       </c>
       <c r="K81" s="1">
-        <v>54000</v>
+        <v>2135833.2000000002</v>
       </c>
       <c r="L81" s="1">
         <v>0</v>
@@ -4440,14 +4406,12 @@
       </c>
       <c r="N81" s="1"/>
       <c r="O81" s="1">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="P81" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q81" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q81" s="1"/>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A82" s="2">
@@ -4463,23 +4427,21 @@
         <v>18</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G82" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="G82" s="1"/>
       <c r="H82" s="1"/>
       <c r="I82" s="1" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="J82" s="1">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="K82" s="1">
-        <v>18000</v>
+        <v>345000</v>
       </c>
       <c r="L82" s="1">
         <v>0</v>
@@ -4489,14 +4451,12 @@
       </c>
       <c r="N82" s="1"/>
       <c r="O82" s="1">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="P82" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q82" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q82" s="1"/>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A83" s="2">
@@ -4512,23 +4472,21 @@
         <v>18</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G83" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="G83" s="1"/>
       <c r="H83" s="1"/>
       <c r="I83" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J83" s="1">
-        <v>6</v>
+        <v>21.916665999999999</v>
       </c>
       <c r="K83" s="1">
-        <v>54000</v>
+        <v>197250</v>
       </c>
       <c r="L83" s="1">
         <v>0</v>
@@ -4538,14 +4496,12 @@
       </c>
       <c r="N83" s="1"/>
       <c r="O83" s="1">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="P83" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q83" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q83" s="1"/>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A84" s="2">
@@ -4561,23 +4517,21 @@
         <v>18</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G84" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="G84" s="1"/>
       <c r="H84" s="1"/>
       <c r="I84" s="1" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="J84" s="1">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="K84" s="1">
-        <v>12000</v>
+        <v>225000</v>
       </c>
       <c r="L84" s="1">
         <v>0</v>
@@ -4587,14 +4541,12 @@
       </c>
       <c r="N84" s="1"/>
       <c r="O84" s="1">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="P84" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q84" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q84" s="1"/>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A85" s="2">
@@ -4610,23 +4562,21 @@
         <v>18</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G85" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="G85" s="1"/>
       <c r="H85" s="1"/>
       <c r="I85" s="1" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="J85" s="1">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="K85" s="1">
-        <v>4500</v>
+        <v>375000</v>
       </c>
       <c r="L85" s="1">
         <v>0</v>
@@ -4636,14 +4586,12 @@
       </c>
       <c r="N85" s="1"/>
       <c r="O85" s="1">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="P85" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q85" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q85" s="1"/>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A86" s="2">
@@ -4659,23 +4607,21 @@
         <v>18</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G86" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="G86" s="1"/>
       <c r="H86" s="1"/>
       <c r="I86" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J86" s="1">
-        <v>2</v>
+        <v>92.375</v>
       </c>
       <c r="K86" s="1">
-        <v>18000</v>
+        <v>1062312.5</v>
       </c>
       <c r="L86" s="1">
         <v>0</v>
@@ -4685,14 +4631,12 @@
       </c>
       <c r="N86" s="1"/>
       <c r="O86" s="1">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P86" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q86" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q86" s="1"/>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A87" s="2">
@@ -4708,23 +4652,21 @@
         <v>18</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G87" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="G87" s="1"/>
       <c r="H87" s="1"/>
       <c r="I87" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J87" s="1">
-        <v>4.1666667999999997E-2</v>
+        <v>409</v>
       </c>
       <c r="K87" s="1">
-        <v>479.16665999999998</v>
+        <v>3681000</v>
       </c>
       <c r="L87" s="1">
         <v>0</v>
@@ -4734,14 +4676,12 @@
       </c>
       <c r="N87" s="1"/>
       <c r="O87" s="1">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="P87" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q87" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q87" s="1"/>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A88" s="2">
@@ -4763,27 +4703,27 @@
         <v>20</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H88" s="1"/>
       <c r="I88" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J88" s="1">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="K88" s="1">
-        <v>18000</v>
+        <v>297000</v>
       </c>
       <c r="L88" s="1">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="M88" s="1">
         <v>0</v>
       </c>
       <c r="N88" s="1"/>
       <c r="O88" s="1">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="P88" s="1" t="s">
         <v>23</v>
@@ -4812,17 +4752,17 @@
         <v>20</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J89" s="1">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K89" s="1">
-        <v>72000</v>
+        <v>27000</v>
       </c>
       <c r="L89" s="1">
         <v>0</v>
@@ -4832,7 +4772,7 @@
       </c>
       <c r="N89" s="1"/>
       <c r="O89" s="1">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="P89" s="1" t="s">
         <v>23</v>
@@ -4861,17 +4801,17 @@
         <v>20</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="H90" s="1"/>
       <c r="I90" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J90" s="1">
-        <v>0.54166669999999995</v>
+        <v>1</v>
       </c>
       <c r="K90" s="1">
-        <v>6229.1665000000003</v>
+        <v>6000</v>
       </c>
       <c r="L90" s="1">
         <v>0</v>
@@ -4881,7 +4821,7 @@
       </c>
       <c r="N90" s="1"/>
       <c r="O90" s="1">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="P90" s="1" t="s">
         <v>23</v>
@@ -4910,17 +4850,17 @@
         <v>20</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H91" s="1"/>
       <c r="I91" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J91" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K91" s="1">
-        <v>22000</v>
+        <v>54000</v>
       </c>
       <c r="L91" s="1">
         <v>0</v>
@@ -4930,7 +4870,7 @@
       </c>
       <c r="N91" s="1"/>
       <c r="O91" s="1">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="P91" s="1" t="s">
         <v>23</v>
@@ -4959,17 +4899,17 @@
         <v>20</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J92" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K92" s="1">
-        <v>54000</v>
+        <v>18000</v>
       </c>
       <c r="L92" s="1">
         <v>0</v>
@@ -4979,7 +4919,7 @@
       </c>
       <c r="N92" s="1"/>
       <c r="O92" s="1">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="P92" s="1" t="s">
         <v>23</v>
@@ -5008,17 +4948,17 @@
         <v>20</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H93" s="1"/>
       <c r="I93" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J93" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K93" s="1">
-        <v>23000</v>
+        <v>54000</v>
       </c>
       <c r="L93" s="1">
         <v>0</v>
@@ -5028,7 +4968,7 @@
       </c>
       <c r="N93" s="1"/>
       <c r="O93" s="1">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="P93" s="1" t="s">
         <v>23</v>
@@ -5057,17 +4997,17 @@
         <v>20</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J94" s="1">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="K94" s="1">
-        <v>5500</v>
+        <v>12000</v>
       </c>
       <c r="L94" s="1">
         <v>0</v>
@@ -5077,7 +5017,7 @@
       </c>
       <c r="N94" s="1"/>
       <c r="O94" s="1">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="P94" s="1" t="s">
         <v>23</v>
@@ -5106,17 +5046,17 @@
         <v>20</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J95" s="1">
         <v>1</v>
       </c>
       <c r="K95" s="1">
-        <v>6000</v>
+        <v>4500</v>
       </c>
       <c r="L95" s="1">
         <v>0</v>
@@ -5126,7 +5066,7 @@
       </c>
       <c r="N95" s="1"/>
       <c r="O95" s="1">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="P95" s="1" t="s">
         <v>23</v>
@@ -5155,17 +5095,17 @@
         <v>20</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H96" s="1"/>
       <c r="I96" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J96" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K96" s="1">
-        <v>36000</v>
+        <v>18000</v>
       </c>
       <c r="L96" s="1">
         <v>0</v>
@@ -5175,7 +5115,7 @@
       </c>
       <c r="N96" s="1"/>
       <c r="O96" s="1">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="P96" s="1" t="s">
         <v>23</v>
@@ -5204,17 +5144,17 @@
         <v>20</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H97" s="1"/>
       <c r="I97" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J97" s="1">
-        <v>1</v>
+        <v>4.1666667999999997E-2</v>
       </c>
       <c r="K97" s="1">
-        <v>6000</v>
+        <v>479.16665999999998</v>
       </c>
       <c r="L97" s="1">
         <v>0</v>
@@ -5224,7 +5164,7 @@
       </c>
       <c r="N97" s="1"/>
       <c r="O97" s="1">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="P97" s="1" t="s">
         <v>23</v>
@@ -5253,17 +5193,17 @@
         <v>20</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H98" s="1"/>
       <c r="I98" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J98" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K98" s="1">
-        <v>45000</v>
+        <v>18000</v>
       </c>
       <c r="L98" s="1">
         <v>0</v>
@@ -5273,7 +5213,7 @@
       </c>
       <c r="N98" s="1"/>
       <c r="O98" s="1">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="P98" s="1" t="s">
         <v>23</v>
@@ -5302,17 +5242,17 @@
         <v>20</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="H99" s="1"/>
       <c r="I99" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J99" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K99" s="1">
-        <v>11000</v>
+        <v>72000</v>
       </c>
       <c r="L99" s="1">
         <v>0</v>
@@ -5322,7 +5262,7 @@
       </c>
       <c r="N99" s="1"/>
       <c r="O99" s="1">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="P99" s="1" t="s">
         <v>23</v>
@@ -5351,17 +5291,17 @@
         <v>20</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="H100" s="1"/>
       <c r="I100" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="J100" s="1">
-        <v>1</v>
+        <v>0.54166669999999995</v>
       </c>
       <c r="K100" s="1">
-        <v>4500</v>
+        <v>6229.1665000000003</v>
       </c>
       <c r="L100" s="1">
         <v>0</v>
@@ -5371,7 +5311,7 @@
       </c>
       <c r="N100" s="1"/>
       <c r="O100" s="1">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="P100" s="1" t="s">
         <v>23</v>
@@ -5400,17 +5340,17 @@
         <v>20</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="H101" s="1"/>
       <c r="I101" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J101" s="1">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="K101" s="1">
-        <v>171000</v>
+        <v>22000</v>
       </c>
       <c r="L101" s="1">
         <v>0</v>
@@ -5420,7 +5360,7 @@
       </c>
       <c r="N101" s="1"/>
       <c r="O101" s="1">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="P101" s="1" t="s">
         <v>23</v>
@@ -5449,17 +5389,17 @@
         <v>20</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="H102" s="1"/>
       <c r="I102" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J102" s="1">
-        <v>1.0833333999999999</v>
+        <v>6</v>
       </c>
       <c r="K102" s="1">
-        <v>11916.666999999999</v>
+        <v>54000</v>
       </c>
       <c r="L102" s="1">
         <v>0</v>
@@ -5469,7 +5409,7 @@
       </c>
       <c r="N102" s="1"/>
       <c r="O102" s="1">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="P102" s="1" t="s">
         <v>23</v>
@@ -5498,17 +5438,17 @@
         <v>20</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="H103" s="1"/>
       <c r="I103" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J103" s="1">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="K103" s="1">
-        <v>135000</v>
+        <v>23000</v>
       </c>
       <c r="L103" s="1">
         <v>0</v>
@@ -5518,7 +5458,7 @@
       </c>
       <c r="N103" s="1"/>
       <c r="O103" s="1">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="P103" s="1" t="s">
         <v>23</v>
@@ -5547,17 +5487,17 @@
         <v>20</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="H104" s="1"/>
       <c r="I104" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J104" s="1">
-        <v>1.0833333999999999</v>
+        <v>0.5</v>
       </c>
       <c r="K104" s="1">
-        <v>12458.333000000001</v>
+        <v>5500</v>
       </c>
       <c r="L104" s="1">
         <v>0</v>
@@ -5567,7 +5507,7 @@
       </c>
       <c r="N104" s="1"/>
       <c r="O104" s="1">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="P104" s="1" t="s">
         <v>23</v>
@@ -5596,19 +5536,17 @@
         <v>20</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H105" s="1" t="s">
-        <v>42</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="H105" s="1"/>
       <c r="I105" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J105" s="1">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="K105" s="1">
-        <v>450000</v>
+        <v>6000</v>
       </c>
       <c r="L105" s="1">
         <v>0</v>
@@ -5618,7 +5556,7 @@
       </c>
       <c r="N105" s="1"/>
       <c r="O105" s="1">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="P105" s="1" t="s">
         <v>23</v>
@@ -5647,19 +5585,17 @@
         <v>20</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H106" s="1" t="s">
-        <v>42</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="H106" s="1"/>
       <c r="I106" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J106" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K106" s="1">
-        <v>6000</v>
+        <v>36000</v>
       </c>
       <c r="L106" s="1">
         <v>0</v>
@@ -5669,7 +5605,7 @@
       </c>
       <c r="N106" s="1"/>
       <c r="O106" s="1">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="P106" s="1" t="s">
         <v>23</v>
@@ -5680,7 +5616,7 @@
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A107" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B107" s="1">
         <v>0</v>
@@ -5698,27 +5634,27 @@
         <v>20</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="H107" s="1"/>
       <c r="I107" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J107" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K107" s="1">
-        <v>27000</v>
+        <v>6000</v>
       </c>
       <c r="L107" s="1">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="M107" s="1">
         <v>0</v>
       </c>
       <c r="N107" s="1"/>
       <c r="O107" s="1">
-        <v>65</v>
+        <v>121</v>
       </c>
       <c r="P107" s="1" t="s">
         <v>23</v>
@@ -5729,7 +5665,7 @@
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A108" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B108" s="1">
         <v>0</v>
@@ -5747,17 +5683,17 @@
         <v>20</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H108" s="1"/>
       <c r="I108" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J108" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K108" s="1">
-        <v>12000</v>
+        <v>45000</v>
       </c>
       <c r="L108" s="1">
         <v>0</v>
@@ -5767,7 +5703,7 @@
       </c>
       <c r="N108" s="1"/>
       <c r="O108" s="1">
-        <v>66</v>
+        <v>122</v>
       </c>
       <c r="P108" s="1" t="s">
         <v>23</v>
@@ -5778,7 +5714,7 @@
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A109" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B109" s="1">
         <v>0</v>
@@ -5796,17 +5732,17 @@
         <v>20</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="H109" s="1"/>
       <c r="I109" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J109" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K109" s="1">
-        <v>18000</v>
+        <v>11000</v>
       </c>
       <c r="L109" s="1">
         <v>0</v>
@@ -5816,7 +5752,7 @@
       </c>
       <c r="N109" s="1"/>
       <c r="O109" s="1">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="P109" s="1" t="s">
         <v>23</v>
@@ -5827,7 +5763,7 @@
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A110" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B110" s="1">
         <v>0</v>
@@ -5845,17 +5781,17 @@
         <v>20</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="H110" s="1"/>
       <c r="I110" s="1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="J110" s="1">
-        <v>1.625</v>
+        <v>1</v>
       </c>
       <c r="K110" s="1">
-        <v>18687.5</v>
+        <v>4500</v>
       </c>
       <c r="L110" s="1">
         <v>0</v>
@@ -5865,7 +5801,7 @@
       </c>
       <c r="N110" s="1"/>
       <c r="O110" s="1">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="P110" s="1" t="s">
         <v>23</v>
@@ -5876,7 +5812,7 @@
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A111" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B111" s="1">
         <v>0</v>
@@ -5894,17 +5830,17 @@
         <v>20</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="H111" s="1"/>
       <c r="I111" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J111" s="1">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K111" s="1">
-        <v>12000</v>
+        <v>171000</v>
       </c>
       <c r="L111" s="1">
         <v>0</v>
@@ -5914,7 +5850,7 @@
       </c>
       <c r="N111" s="1"/>
       <c r="O111" s="1">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="P111" s="1" t="s">
         <v>23</v>
@@ -5925,7 +5861,7 @@
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A112" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B112" s="1">
         <v>0</v>
@@ -5943,17 +5879,17 @@
         <v>20</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H112" s="1"/>
       <c r="I112" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J112" s="1">
-        <v>1</v>
+        <v>1.0833333999999999</v>
       </c>
       <c r="K112" s="1">
-        <v>6000</v>
+        <v>11916.666999999999</v>
       </c>
       <c r="L112" s="1">
         <v>0</v>
@@ -5963,7 +5899,7 @@
       </c>
       <c r="N112" s="1"/>
       <c r="O112" s="1">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="P112" s="1" t="s">
         <v>23</v>
@@ -5974,7 +5910,7 @@
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A113" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B113" s="1">
         <v>0</v>
@@ -5992,17 +5928,17 @@
         <v>20</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H113" s="1"/>
       <c r="I113" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J113" s="1">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K113" s="1">
-        <v>9000</v>
+        <v>135000</v>
       </c>
       <c r="L113" s="1">
         <v>0</v>
@@ -6012,7 +5948,7 @@
       </c>
       <c r="N113" s="1"/>
       <c r="O113" s="1">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="P113" s="1" t="s">
         <v>23</v>
@@ -6023,7 +5959,7 @@
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A114" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B114" s="1">
         <v>0</v>
@@ -6041,17 +5977,17 @@
         <v>20</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H114" s="1"/>
       <c r="I114" s="1" t="s">
         <v>22</v>
       </c>
       <c r="J114" s="1">
-        <v>4.1666667999999997E-2</v>
+        <v>1.0833333999999999</v>
       </c>
       <c r="K114" s="1">
-        <v>479.16665999999998</v>
+        <v>12458.333000000001</v>
       </c>
       <c r="L114" s="1">
         <v>0</v>
@@ -6061,7 +5997,7 @@
       </c>
       <c r="N114" s="1"/>
       <c r="O114" s="1">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="P114" s="1" t="s">
         <v>23</v>
@@ -6072,7 +6008,7 @@
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A115" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B115" s="1">
         <v>0</v>
@@ -6090,17 +6026,19 @@
         <v>20</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H115" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="I115" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J115" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="K115" s="1">
-        <v>9000</v>
+        <v>450000</v>
       </c>
       <c r="L115" s="1">
         <v>0</v>
@@ -6110,7 +6048,7 @@
       </c>
       <c r="N115" s="1"/>
       <c r="O115" s="1">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="P115" s="1" t="s">
         <v>23</v>
@@ -6121,7 +6059,7 @@
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A116" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B116" s="1">
         <v>0</v>
@@ -6139,17 +6077,19 @@
         <v>20</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H116" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="I116" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J116" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K116" s="1">
-        <v>18000</v>
+        <v>6000</v>
       </c>
       <c r="L116" s="1">
         <v>0</v>
@@ -6159,7 +6099,7 @@
       </c>
       <c r="N116" s="1"/>
       <c r="O116" s="1">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="P116" s="1" t="s">
         <v>23</v>
@@ -6188,27 +6128,27 @@
         <v>20</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H117" s="1"/>
       <c r="I117" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J117" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K117" s="1">
-        <v>9000</v>
+        <v>27000</v>
       </c>
       <c r="L117" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="M117" s="1">
         <v>0</v>
       </c>
       <c r="N117" s="1"/>
       <c r="O117" s="1">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="P117" s="1" t="s">
         <v>23</v>
@@ -6237,17 +6177,17 @@
         <v>20</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="H118" s="1"/>
       <c r="I118" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J118" s="1">
         <v>2</v>
       </c>
       <c r="K118" s="1">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="L118" s="1">
         <v>0</v>
@@ -6257,7 +6197,7 @@
       </c>
       <c r="N118" s="1"/>
       <c r="O118" s="1">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="P118" s="1" t="s">
         <v>23</v>
@@ -6286,17 +6226,17 @@
         <v>20</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H119" s="1"/>
       <c r="I119" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J119" s="1">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="K119" s="1">
-        <v>4500</v>
+        <v>18000</v>
       </c>
       <c r="L119" s="1">
         <v>0</v>
@@ -6306,7 +6246,7 @@
       </c>
       <c r="N119" s="1"/>
       <c r="O119" s="1">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="P119" s="1" t="s">
         <v>23</v>
@@ -6335,17 +6275,17 @@
         <v>20</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="H120" s="1"/>
       <c r="I120" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J120" s="1">
-        <v>0.5</v>
+        <v>1.625</v>
       </c>
       <c r="K120" s="1">
-        <v>4500</v>
+        <v>18687.5</v>
       </c>
       <c r="L120" s="1">
         <v>0</v>
@@ -6355,7 +6295,7 @@
       </c>
       <c r="N120" s="1"/>
       <c r="O120" s="1">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="P120" s="1" t="s">
         <v>23</v>
@@ -6384,17 +6324,17 @@
         <v>20</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="H121" s="1"/>
       <c r="I121" s="1" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="J121" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K121" s="1">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="L121" s="1">
         <v>0</v>
@@ -6404,7 +6344,7 @@
       </c>
       <c r="N121" s="1"/>
       <c r="O121" s="1">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="P121" s="1" t="s">
         <v>23</v>
@@ -6433,17 +6373,17 @@
         <v>20</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H122" s="1"/>
       <c r="I122" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J122" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K122" s="1">
-        <v>27000</v>
+        <v>6000</v>
       </c>
       <c r="L122" s="1">
         <v>0</v>
@@ -6453,7 +6393,7 @@
       </c>
       <c r="N122" s="1"/>
       <c r="O122" s="1">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="P122" s="1" t="s">
         <v>23</v>
@@ -6482,17 +6422,17 @@
         <v>20</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H123" s="1"/>
       <c r="I123" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J123" s="1">
         <v>1</v>
       </c>
       <c r="K123" s="1">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="L123" s="1">
         <v>0</v>
@@ -6502,7 +6442,7 @@
       </c>
       <c r="N123" s="1"/>
       <c r="O123" s="1">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="P123" s="1" t="s">
         <v>23</v>
@@ -6531,17 +6471,17 @@
         <v>20</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H124" s="1"/>
       <c r="I124" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J124" s="1">
-        <v>0.16666666999999999</v>
+        <v>4.1666667999999997E-2</v>
       </c>
       <c r="K124" s="1">
-        <v>1833.3334</v>
+        <v>479.16665999999998</v>
       </c>
       <c r="L124" s="1">
         <v>0</v>
@@ -6551,7 +6491,7 @@
       </c>
       <c r="N124" s="1"/>
       <c r="O124" s="1">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="P124" s="1" t="s">
         <v>23</v>
@@ -6580,7 +6520,7 @@
         <v>20</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H125" s="1"/>
       <c r="I125" s="1" t="s">
@@ -6600,7 +6540,7 @@
       </c>
       <c r="N125" s="1"/>
       <c r="O125" s="1">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="P125" s="1" t="s">
         <v>23</v>
@@ -6629,17 +6569,17 @@
         <v>20</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="H126" s="1"/>
       <c r="I126" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J126" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K126" s="1">
-        <v>36000</v>
+        <v>18000</v>
       </c>
       <c r="L126" s="1">
         <v>0</v>
@@ -6649,7 +6589,7 @@
       </c>
       <c r="N126" s="1"/>
       <c r="O126" s="1">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="P126" s="1" t="s">
         <v>23</v>
@@ -6678,17 +6618,17 @@
         <v>20</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H127" s="1"/>
       <c r="I127" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J127" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K127" s="1">
-        <v>18000</v>
+        <v>9000</v>
       </c>
       <c r="L127" s="1">
         <v>0</v>
@@ -6698,7 +6638,7 @@
       </c>
       <c r="N127" s="1"/>
       <c r="O127" s="1">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="P127" s="1" t="s">
         <v>23</v>
@@ -6727,17 +6667,17 @@
         <v>20</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H128" s="1"/>
       <c r="I128" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J128" s="1">
-        <v>1.0833333999999999</v>
+        <v>2</v>
       </c>
       <c r="K128" s="1">
-        <v>12458.333000000001</v>
+        <v>18000</v>
       </c>
       <c r="L128" s="1">
         <v>0</v>
@@ -6747,7 +6687,7 @@
       </c>
       <c r="N128" s="1"/>
       <c r="O128" s="1">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="P128" s="1" t="s">
         <v>23</v>
@@ -6776,11 +6716,11 @@
         <v>20</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H129" s="1"/>
       <c r="I129" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J129" s="1">
         <v>0.5</v>
@@ -6796,7 +6736,7 @@
       </c>
       <c r="N129" s="1"/>
       <c r="O129" s="1">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="P129" s="1" t="s">
         <v>23</v>
@@ -6825,17 +6765,17 @@
         <v>20</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H130" s="1"/>
       <c r="I130" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J130" s="1">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="K130" s="1">
-        <v>27000</v>
+        <v>4500</v>
       </c>
       <c r="L130" s="1">
         <v>0</v>
@@ -6845,7 +6785,7 @@
       </c>
       <c r="N130" s="1"/>
       <c r="O130" s="1">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="P130" s="1" t="s">
         <v>23</v>
@@ -6874,17 +6814,17 @@
         <v>20</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H131" s="1"/>
       <c r="I131" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="J131" s="1">
-        <v>1.0833333999999999</v>
+        <v>1</v>
       </c>
       <c r="K131" s="1">
-        <v>11916.666999999999</v>
+        <v>15000</v>
       </c>
       <c r="L131" s="1">
         <v>0</v>
@@ -6894,7 +6834,7 @@
       </c>
       <c r="N131" s="1"/>
       <c r="O131" s="1">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="P131" s="1" t="s">
         <v>23</v>
@@ -6923,17 +6863,17 @@
         <v>20</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H132" s="1"/>
       <c r="I132" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J132" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K132" s="1">
-        <v>24000</v>
+        <v>27000</v>
       </c>
       <c r="L132" s="1">
         <v>0</v>
@@ -6943,7 +6883,7 @@
       </c>
       <c r="N132" s="1"/>
       <c r="O132" s="1">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="P132" s="1" t="s">
         <v>23</v>
@@ -6972,17 +6912,17 @@
         <v>20</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H133" s="1"/>
       <c r="I133" s="1" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="J133" s="1">
         <v>1</v>
       </c>
       <c r="K133" s="1">
-        <v>15000</v>
+        <v>6000</v>
       </c>
       <c r="L133" s="1">
         <v>0</v>
@@ -6992,7 +6932,7 @@
       </c>
       <c r="N133" s="1"/>
       <c r="O133" s="1">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="P133" s="1" t="s">
         <v>23</v>
@@ -7003,7 +6943,7 @@
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A134" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B134" s="1">
         <v>0</v>
@@ -7021,27 +6961,27 @@
         <v>20</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H134" s="1"/>
       <c r="I134" s="1" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="J134" s="1">
-        <v>2</v>
+        <v>0.16666666999999999</v>
       </c>
       <c r="K134" s="1">
-        <v>22000</v>
+        <v>1833.3334</v>
       </c>
       <c r="L134" s="1">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="M134" s="1">
         <v>0</v>
       </c>
       <c r="N134" s="1"/>
       <c r="O134" s="1">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="P134" s="1" t="s">
         <v>23</v>
@@ -7052,7 +6992,7 @@
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A135" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B135" s="1">
         <v>0</v>
@@ -7070,17 +7010,17 @@
         <v>20</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="H135" s="1"/>
       <c r="I135" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J135" s="1">
         <v>1</v>
       </c>
       <c r="K135" s="1">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="L135" s="1">
         <v>0</v>
@@ -7090,7 +7030,7 @@
       </c>
       <c r="N135" s="1"/>
       <c r="O135" s="1">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="P135" s="1" t="s">
         <v>23</v>
@@ -7101,7 +7041,7 @@
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A136" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B136" s="1">
         <v>0</v>
@@ -7119,17 +7059,17 @@
         <v>20</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="H136" s="1"/>
       <c r="I136" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="J136" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K136" s="1">
-        <v>4500</v>
+        <v>36000</v>
       </c>
       <c r="L136" s="1">
         <v>0</v>
@@ -7139,7 +7079,7 @@
       </c>
       <c r="N136" s="1"/>
       <c r="O136" s="1">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="P136" s="1" t="s">
         <v>23</v>
@@ -7150,7 +7090,7 @@
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A137" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B137" s="1">
         <v>0</v>
@@ -7168,17 +7108,17 @@
         <v>20</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="H137" s="1"/>
       <c r="I137" s="1" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="J137" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K137" s="1">
-        <v>22000</v>
+        <v>18000</v>
       </c>
       <c r="L137" s="1">
         <v>0</v>
@@ -7188,7 +7128,7 @@
       </c>
       <c r="N137" s="1"/>
       <c r="O137" s="1">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="P137" s="1" t="s">
         <v>23</v>
@@ -7199,7 +7139,7 @@
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A138" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B138" s="1">
         <v>0</v>
@@ -7217,17 +7157,17 @@
         <v>20</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="H138" s="1"/>
       <c r="I138" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J138" s="1">
-        <v>2</v>
+        <v>1.0833333999999999</v>
       </c>
       <c r="K138" s="1">
-        <v>12000</v>
+        <v>12458.333000000001</v>
       </c>
       <c r="L138" s="1">
         <v>0</v>
@@ -7237,7 +7177,7 @@
       </c>
       <c r="N138" s="1"/>
       <c r="O138" s="1">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="P138" s="1" t="s">
         <v>23</v>
@@ -7248,7 +7188,7 @@
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A139" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B139" s="1">
         <v>0</v>
@@ -7266,17 +7206,17 @@
         <v>20</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="H139" s="1"/>
       <c r="I139" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J139" s="1">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="K139" s="1">
-        <v>31500</v>
+        <v>4500</v>
       </c>
       <c r="L139" s="1">
         <v>0</v>
@@ -7286,7 +7226,7 @@
       </c>
       <c r="N139" s="1"/>
       <c r="O139" s="1">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="P139" s="1" t="s">
         <v>23</v>
@@ -7297,7 +7237,7 @@
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A140" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B140" s="1">
         <v>0</v>
@@ -7315,17 +7255,17 @@
         <v>20</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="H140" s="1"/>
       <c r="I140" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J140" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K140" s="1">
-        <v>9000</v>
+        <v>27000</v>
       </c>
       <c r="L140" s="1">
         <v>0</v>
@@ -7335,7 +7275,7 @@
       </c>
       <c r="N140" s="1"/>
       <c r="O140" s="1">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="P140" s="1" t="s">
         <v>23</v>
@@ -7346,7 +7286,7 @@
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A141" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B141" s="1">
         <v>0</v>
@@ -7364,17 +7304,17 @@
         <v>20</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="H141" s="1"/>
       <c r="I141" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J141" s="1">
-        <v>0.25</v>
+        <v>1.0833333999999999</v>
       </c>
       <c r="K141" s="1">
-        <v>2875</v>
+        <v>11916.666999999999</v>
       </c>
       <c r="L141" s="1">
         <v>0</v>
@@ -7384,7 +7324,7 @@
       </c>
       <c r="N141" s="1"/>
       <c r="O141" s="1">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="P141" s="1" t="s">
         <v>23</v>
@@ -7395,7 +7335,7 @@
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A142" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B142" s="1">
         <v>0</v>
@@ -7413,17 +7353,17 @@
         <v>20</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H142" s="1"/>
       <c r="I142" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J142" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K142" s="1">
-        <v>21000</v>
+        <v>24000</v>
       </c>
       <c r="L142" s="1">
         <v>0</v>
@@ -7433,7 +7373,7 @@
       </c>
       <c r="N142" s="1"/>
       <c r="O142" s="1">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="P142" s="1" t="s">
         <v>23</v>
@@ -7444,7 +7384,7 @@
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A143" s="2">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B143" s="1">
         <v>0</v>
@@ -7462,17 +7402,17 @@
         <v>20</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H143" s="1"/>
       <c r="I143" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="J143" s="1">
         <v>1</v>
       </c>
       <c r="K143" s="1">
-        <v>10500</v>
+        <v>15000</v>
       </c>
       <c r="L143" s="1">
         <v>0</v>
@@ -7482,7 +7422,7 @@
       </c>
       <c r="N143" s="1"/>
       <c r="O143" s="1">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="P143" s="1" t="s">
         <v>23</v>
@@ -7511,27 +7451,27 @@
         <v>20</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="H144" s="1"/>
       <c r="I144" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="J144" s="1">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="K144" s="1">
-        <v>3000</v>
+        <v>22000</v>
       </c>
       <c r="L144" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="M144" s="1">
         <v>0</v>
       </c>
       <c r="N144" s="1"/>
       <c r="O144" s="1">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="P144" s="1" t="s">
         <v>23</v>
@@ -7560,17 +7500,17 @@
         <v>20</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="H145" s="1"/>
       <c r="I145" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J145" s="1">
         <v>1</v>
       </c>
       <c r="K145" s="1">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="L145" s="1">
         <v>0</v>
@@ -7580,7 +7520,7 @@
       </c>
       <c r="N145" s="1"/>
       <c r="O145" s="1">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="P145" s="1" t="s">
         <v>23</v>
@@ -7609,17 +7549,17 @@
         <v>20</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="H146" s="1"/>
       <c r="I146" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J146" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K146" s="1">
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="L146" s="1">
         <v>0</v>
@@ -7629,7 +7569,7 @@
       </c>
       <c r="N146" s="1"/>
       <c r="O146" s="1">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="P146" s="1" t="s">
         <v>23</v>
@@ -7658,17 +7598,17 @@
         <v>20</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="H147" s="1"/>
       <c r="I147" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="J147" s="1">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="K147" s="1">
-        <v>3000</v>
+        <v>22000</v>
       </c>
       <c r="L147" s="1">
         <v>0</v>
@@ -7678,7 +7618,7 @@
       </c>
       <c r="N147" s="1"/>
       <c r="O147" s="1">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="P147" s="1" t="s">
         <v>23</v>
@@ -7707,17 +7647,17 @@
         <v>20</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H148" s="1"/>
       <c r="I148" s="1" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="J148" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K148" s="1">
-        <v>55000</v>
+        <v>12000</v>
       </c>
       <c r="L148" s="1">
         <v>0</v>
@@ -7727,7 +7667,7 @@
       </c>
       <c r="N148" s="1"/>
       <c r="O148" s="1">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="P148" s="1" t="s">
         <v>23</v>
@@ -7756,17 +7696,17 @@
         <v>20</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="H149" s="1"/>
       <c r="I149" s="1" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="J149" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K149" s="1">
-        <v>55000</v>
+        <v>31500</v>
       </c>
       <c r="L149" s="1">
         <v>0</v>
@@ -7776,7 +7716,7 @@
       </c>
       <c r="N149" s="1"/>
       <c r="O149" s="1">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="P149" s="1" t="s">
         <v>23</v>
@@ -7805,17 +7745,17 @@
         <v>20</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H150" s="1"/>
       <c r="I150" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J150" s="1">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="K150" s="1">
-        <v>2875</v>
+        <v>9000</v>
       </c>
       <c r="L150" s="1">
         <v>0</v>
@@ -7825,7 +7765,7 @@
       </c>
       <c r="N150" s="1"/>
       <c r="O150" s="1">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="P150" s="1" t="s">
         <v>23</v>
@@ -7854,7 +7794,7 @@
         <v>20</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H151" s="1"/>
       <c r="I151" s="1" t="s">
@@ -7874,7 +7814,7 @@
       </c>
       <c r="N151" s="1"/>
       <c r="O151" s="1">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="P151" s="1" t="s">
         <v>23</v>
@@ -7903,17 +7843,17 @@
         <v>20</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H152" s="1"/>
       <c r="I152" s="1" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="J152" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K152" s="1">
-        <v>11000</v>
+        <v>21000</v>
       </c>
       <c r="L152" s="1">
         <v>0</v>
@@ -7923,7 +7863,7 @@
       </c>
       <c r="N152" s="1"/>
       <c r="O152" s="1">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P152" s="1" t="s">
         <v>23</v>
@@ -7952,7 +7892,7 @@
         <v>20</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H153" s="1"/>
       <c r="I153" s="1" t="s">
@@ -7972,7 +7912,7 @@
       </c>
       <c r="N153" s="1"/>
       <c r="O153" s="1">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="P153" s="1" t="s">
         <v>23</v>
@@ -8001,17 +7941,17 @@
         <v>20</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H154" s="1"/>
       <c r="I154" s="1" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="J154" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K154" s="1">
-        <v>11000</v>
+        <v>3000</v>
       </c>
       <c r="L154" s="1">
         <v>0</v>
@@ -8021,7 +7961,7 @@
       </c>
       <c r="N154" s="1"/>
       <c r="O154" s="1">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="P154" s="1" t="s">
         <v>23</v>
@@ -8050,17 +7990,17 @@
         <v>20</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H155" s="1"/>
       <c r="I155" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="J155" s="1">
         <v>1</v>
       </c>
       <c r="K155" s="1">
-        <v>4500</v>
+        <v>9000</v>
       </c>
       <c r="L155" s="1">
         <v>0</v>
@@ -8070,7 +8010,7 @@
       </c>
       <c r="N155" s="1"/>
       <c r="O155" s="1">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="P155" s="1" t="s">
         <v>23</v>
@@ -8099,17 +8039,17 @@
         <v>20</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H156" s="1"/>
       <c r="I156" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J156" s="1">
-        <v>0.45833333999999998</v>
+        <v>0.5</v>
       </c>
       <c r="K156" s="1">
-        <v>5270.8334999999997</v>
+        <v>3000</v>
       </c>
       <c r="L156" s="1">
         <v>0</v>
@@ -8119,7 +8059,7 @@
       </c>
       <c r="N156" s="1"/>
       <c r="O156" s="1">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="P156" s="1" t="s">
         <v>23</v>
@@ -8130,7 +8070,7 @@
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A157" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B157" s="1">
         <v>0</v>
@@ -8142,21 +8082,23 @@
         <v>18</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G157" s="1"/>
+      <c r="G157" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="H157" s="1"/>
       <c r="I157" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J157" s="1">
-        <v>600</v>
+        <v>0.5</v>
       </c>
       <c r="K157" s="1">
-        <v>6300000</v>
+        <v>3000</v>
       </c>
       <c r="L157" s="1">
         <v>0</v>
@@ -8166,16 +8108,18 @@
       </c>
       <c r="N157" s="1"/>
       <c r="O157" s="1">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="P157" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q157" s="1"/>
+      <c r="Q157" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A158" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B158" s="1">
         <v>0</v>
@@ -8187,21 +8131,23 @@
         <v>18</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G158" s="1"/>
+      <c r="G158" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="H158" s="1"/>
       <c r="I158" s="1" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="J158" s="1">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="K158" s="1">
-        <v>2200000</v>
+        <v>55000</v>
       </c>
       <c r="L158" s="1">
         <v>0</v>
@@ -8211,16 +8157,18 @@
       </c>
       <c r="N158" s="1"/>
       <c r="O158" s="1">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="P158" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q158" s="1"/>
+      <c r="Q158" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A159" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B159" s="1">
         <v>0</v>
@@ -8232,21 +8180,23 @@
         <v>18</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G159" s="1"/>
+      <c r="G159" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="H159" s="1"/>
       <c r="I159" s="1" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="J159" s="1">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="K159" s="1">
-        <v>450000</v>
+        <v>55000</v>
       </c>
       <c r="L159" s="1">
         <v>0</v>
@@ -8256,16 +8206,18 @@
       </c>
       <c r="N159" s="1"/>
       <c r="O159" s="1">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="P159" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q159" s="1"/>
+      <c r="Q159" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A160" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B160" s="1">
         <v>0</v>
@@ -8277,21 +8229,23 @@
         <v>18</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G160" s="1"/>
+      <c r="G160" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="H160" s="1"/>
       <c r="I160" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J160" s="1">
-        <v>100</v>
+        <v>0.25</v>
       </c>
       <c r="K160" s="1">
-        <v>1100000</v>
+        <v>2875</v>
       </c>
       <c r="L160" s="1">
         <v>0</v>
@@ -8301,16 +8255,18 @@
       </c>
       <c r="N160" s="1"/>
       <c r="O160" s="1">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="P160" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q160" s="1"/>
+      <c r="Q160" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A161" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B161" s="1">
         <v>0</v>
@@ -8322,21 +8278,23 @@
         <v>18</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G161" s="1"/>
+      <c r="G161" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="H161" s="1"/>
       <c r="I161" s="1" t="s">
         <v>22</v>
       </c>
       <c r="J161" s="1">
-        <v>100</v>
+        <v>0.25</v>
       </c>
       <c r="K161" s="1">
-        <v>1150000</v>
+        <v>2875</v>
       </c>
       <c r="L161" s="1">
         <v>0</v>
@@ -8346,16 +8304,18 @@
       </c>
       <c r="N161" s="1"/>
       <c r="O161" s="1">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="P161" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q161" s="1"/>
+      <c r="Q161" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A162" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B162" s="1">
         <v>0</v>
@@ -8367,21 +8327,23 @@
         <v>18</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G162" s="1"/>
+      <c r="G162" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="H162" s="1"/>
       <c r="I162" s="1" t="s">
         <v>47</v>
       </c>
       <c r="J162" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K162" s="1">
-        <v>1100000</v>
+        <v>11000</v>
       </c>
       <c r="L162" s="1">
         <v>0</v>
@@ -8391,16 +8353,18 @@
       </c>
       <c r="N162" s="1"/>
       <c r="O162" s="1">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="P162" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q162" s="1"/>
+      <c r="Q162" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A163" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B163" s="1">
         <v>0</v>
@@ -8412,21 +8376,23 @@
         <v>18</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G163" s="1"/>
+      <c r="G163" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="H163" s="1"/>
       <c r="I163" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J163" s="1">
-        <v>140</v>
+        <v>1</v>
       </c>
       <c r="K163" s="1">
-        <v>840000</v>
+        <v>10500</v>
       </c>
       <c r="L163" s="1">
         <v>0</v>
@@ -8436,16 +8402,18 @@
       </c>
       <c r="N163" s="1"/>
       <c r="O163" s="1">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="P163" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q163" s="1"/>
+      <c r="Q163" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A164" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B164" s="1">
         <v>0</v>
@@ -8457,21 +8425,23 @@
         <v>18</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G164" s="1"/>
+      <c r="G164" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="H164" s="1"/>
       <c r="I164" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J164" s="1">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K164" s="1">
-        <v>375000</v>
+        <v>11000</v>
       </c>
       <c r="L164" s="1">
         <v>0</v>
@@ -8481,16 +8451,18 @@
       </c>
       <c r="N164" s="1"/>
       <c r="O164" s="1">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="P164" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q164" s="1"/>
+      <c r="Q164" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A165" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B165" s="1">
         <v>0</v>
@@ -8502,21 +8474,23 @@
         <v>18</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G165" s="1"/>
+      <c r="G165" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="H165" s="1"/>
       <c r="I165" s="1" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="J165" s="1">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K165" s="1">
-        <v>375000</v>
+        <v>4500</v>
       </c>
       <c r="L165" s="1">
         <v>0</v>
@@ -8526,16 +8500,18 @@
       </c>
       <c r="N165" s="1"/>
       <c r="O165" s="1">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="P165" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q165" s="1"/>
+      <c r="Q165" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A166" s="2">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B166" s="1">
         <v>0</v>
@@ -8547,21 +8523,23 @@
         <v>18</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G166" s="1"/>
+      <c r="G166" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="H166" s="1"/>
       <c r="I166" s="1" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="J166" s="1">
-        <v>25</v>
+        <v>0.45833333999999998</v>
       </c>
       <c r="K166" s="1">
-        <v>225000</v>
+        <v>5270.8334999999997</v>
       </c>
       <c r="L166" s="1">
         <v>0</v>
@@ -8571,12 +8549,14 @@
       </c>
       <c r="N166" s="1"/>
       <c r="O166" s="1">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="P166" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q166" s="1"/>
+      <c r="Q166" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A167" s="2">
@@ -8600,13 +8580,13 @@
       <c r="G167" s="1"/>
       <c r="H167" s="1"/>
       <c r="I167" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J167" s="1">
-        <v>25</v>
+        <v>600</v>
       </c>
       <c r="K167" s="1">
-        <v>225000</v>
+        <v>6300000</v>
       </c>
       <c r="L167" s="1">
         <v>0</v>
@@ -8616,7 +8596,7 @@
       </c>
       <c r="N167" s="1"/>
       <c r="O167" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="P167" s="1" t="s">
         <v>23</v>
@@ -8637,40 +8617,36 @@
         <v>18</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G168" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="G168" s="1"/>
       <c r="H168" s="1"/>
       <c r="I168" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J168" s="1">
-        <v>0.58333330000000005</v>
+        <v>200</v>
       </c>
       <c r="K168" s="1">
-        <v>5250</v>
+        <v>2200000</v>
       </c>
       <c r="L168" s="1">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="M168" s="1">
         <v>0</v>
       </c>
       <c r="N168" s="1"/>
       <c r="O168" s="1">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="P168" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q168" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q168" s="1"/>
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A169" s="2">
@@ -8686,23 +8662,21 @@
         <v>18</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G169" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="G169" s="1"/>
       <c r="H169" s="1"/>
       <c r="I169" s="1" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="J169" s="1">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="K169" s="1">
-        <v>66000</v>
+        <v>450000</v>
       </c>
       <c r="L169" s="1">
         <v>0</v>
@@ -8712,14 +8686,12 @@
       </c>
       <c r="N169" s="1"/>
       <c r="O169" s="1">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="P169" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q169" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q169" s="1"/>
     </row>
     <row r="170" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A170" s="2">
@@ -8735,23 +8707,21 @@
         <v>18</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G170" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="G170" s="1"/>
       <c r="H170" s="1"/>
       <c r="I170" s="1" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="J170" s="1">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="K170" s="1">
-        <v>66000</v>
+        <v>1100000</v>
       </c>
       <c r="L170" s="1">
         <v>0</v>
@@ -8761,14 +8731,12 @@
       </c>
       <c r="N170" s="1"/>
       <c r="O170" s="1">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P170" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q170" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q170" s="1"/>
     </row>
     <row r="171" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A171" s="2">
@@ -8784,23 +8752,21 @@
         <v>18</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G171" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="G171" s="1"/>
       <c r="H171" s="1"/>
       <c r="I171" s="1" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="J171" s="1">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="K171" s="1">
-        <v>66000</v>
+        <v>1150000</v>
       </c>
       <c r="L171" s="1">
         <v>0</v>
@@ -8810,14 +8776,12 @@
       </c>
       <c r="N171" s="1"/>
       <c r="O171" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="P171" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q171" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q171" s="1"/>
     </row>
     <row r="172" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A172" s="2">
@@ -8833,23 +8797,21 @@
         <v>18</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G172" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="G172" s="1"/>
       <c r="H172" s="1"/>
       <c r="I172" s="1" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="J172" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="K172" s="1">
-        <v>10500</v>
+        <v>1100000</v>
       </c>
       <c r="L172" s="1">
         <v>0</v>
@@ -8859,14 +8821,12 @@
       </c>
       <c r="N172" s="1"/>
       <c r="O172" s="1">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="P172" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q172" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q172" s="1"/>
     </row>
     <row r="173" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A173" s="2">
@@ -8882,23 +8842,21 @@
         <v>18</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G173" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="G173" s="1"/>
       <c r="H173" s="1"/>
       <c r="I173" s="1" t="s">
         <v>31</v>
       </c>
       <c r="J173" s="1">
-        <v>2</v>
+        <v>140</v>
       </c>
       <c r="K173" s="1">
-        <v>12000</v>
+        <v>840000</v>
       </c>
       <c r="L173" s="1">
         <v>0</v>
@@ -8908,14 +8866,12 @@
       </c>
       <c r="N173" s="1"/>
       <c r="O173" s="1">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="P173" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q173" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q173" s="1"/>
     </row>
     <row r="174" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A174" s="2">
@@ -8931,23 +8887,21 @@
         <v>18</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G174" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="G174" s="1"/>
       <c r="H174" s="1"/>
       <c r="I174" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J174" s="1">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="K174" s="1">
-        <v>77000</v>
+        <v>375000</v>
       </c>
       <c r="L174" s="1">
         <v>0</v>
@@ -8957,14 +8911,12 @@
       </c>
       <c r="N174" s="1"/>
       <c r="O174" s="1">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="P174" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q174" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q174" s="1"/>
     </row>
     <row r="175" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A175" s="2">
@@ -8980,23 +8932,21 @@
         <v>18</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G175" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="G175" s="1"/>
       <c r="H175" s="1"/>
       <c r="I175" s="1" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="J175" s="1">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="K175" s="1">
-        <v>12000</v>
+        <v>375000</v>
       </c>
       <c r="L175" s="1">
         <v>0</v>
@@ -9006,14 +8956,12 @@
       </c>
       <c r="N175" s="1"/>
       <c r="O175" s="1">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="P175" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q175" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q175" s="1"/>
     </row>
     <row r="176" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A176" s="2">
@@ -9029,23 +8977,21 @@
         <v>18</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G176" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="G176" s="1"/>
       <c r="H176" s="1"/>
       <c r="I176" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J176" s="1">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="K176" s="1">
-        <v>11000</v>
+        <v>225000</v>
       </c>
       <c r="L176" s="1">
         <v>0</v>
@@ -9055,14 +9001,12 @@
       </c>
       <c r="N176" s="1"/>
       <c r="O176" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="P176" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q176" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q176" s="1"/>
     </row>
     <row r="177" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A177" s="2">
@@ -9078,23 +9022,21 @@
         <v>18</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G177" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="G177" s="1"/>
       <c r="H177" s="1"/>
       <c r="I177" s="1" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="J177" s="1">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="K177" s="1">
-        <v>22000</v>
+        <v>225000</v>
       </c>
       <c r="L177" s="1">
         <v>0</v>
@@ -9104,14 +9046,12 @@
       </c>
       <c r="N177" s="1"/>
       <c r="O177" s="1">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="P177" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q177" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q177" s="1"/>
     </row>
     <row r="178" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A178" s="2">
@@ -9133,27 +9073,27 @@
         <v>20</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H178" s="1"/>
       <c r="I178" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J178" s="1">
-        <v>1</v>
+        <v>0.58333330000000005</v>
       </c>
       <c r="K178" s="1">
-        <v>6000</v>
+        <v>5250</v>
       </c>
       <c r="L178" s="1">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="M178" s="1">
         <v>0</v>
       </c>
       <c r="N178" s="1"/>
       <c r="O178" s="1">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="P178" s="1" t="s">
         <v>23</v>
@@ -9182,17 +9122,17 @@
         <v>20</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H179" s="1"/>
       <c r="I179" s="1" t="s">
         <v>47</v>
       </c>
       <c r="J179" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K179" s="1">
-        <v>110000</v>
+        <v>66000</v>
       </c>
       <c r="L179" s="1">
         <v>0</v>
@@ -9202,7 +9142,7 @@
       </c>
       <c r="N179" s="1"/>
       <c r="O179" s="1">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="P179" s="1" t="s">
         <v>23</v>
@@ -9231,17 +9171,17 @@
         <v>20</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H180" s="1"/>
       <c r="I180" s="1" t="s">
         <v>47</v>
       </c>
       <c r="J180" s="1">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K180" s="1">
-        <v>121000</v>
+        <v>66000</v>
       </c>
       <c r="L180" s="1">
         <v>0</v>
@@ -9251,7 +9191,7 @@
       </c>
       <c r="N180" s="1"/>
       <c r="O180" s="1">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="P180" s="1" t="s">
         <v>23</v>
@@ -9280,17 +9220,17 @@
         <v>20</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H181" s="1"/>
       <c r="I181" s="1" t="s">
         <v>47</v>
       </c>
       <c r="J181" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K181" s="1">
-        <v>55000</v>
+        <v>66000</v>
       </c>
       <c r="L181" s="1">
         <v>0</v>
@@ -9300,7 +9240,7 @@
       </c>
       <c r="N181" s="1"/>
       <c r="O181" s="1">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="P181" s="1" t="s">
         <v>23</v>
@@ -9329,17 +9269,17 @@
         <v>20</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="H182" s="1"/>
       <c r="I182" s="1" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="J182" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K182" s="1">
-        <v>55000</v>
+        <v>10500</v>
       </c>
       <c r="L182" s="1">
         <v>0</v>
@@ -9349,7 +9289,7 @@
       </c>
       <c r="N182" s="1"/>
       <c r="O182" s="1">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="P182" s="1" t="s">
         <v>23</v>
@@ -9378,17 +9318,17 @@
         <v>20</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="H183" s="1"/>
       <c r="I183" s="1" t="s">
         <v>31</v>
       </c>
       <c r="J183" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K183" s="1">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="L183" s="1">
         <v>0</v>
@@ -9398,7 +9338,7 @@
       </c>
       <c r="N183" s="1"/>
       <c r="O183" s="1">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="P183" s="1" t="s">
         <v>23</v>
@@ -9427,17 +9367,17 @@
         <v>20</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H184" s="1"/>
       <c r="I184" s="1" t="s">
         <v>47</v>
       </c>
       <c r="J184" s="1">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K184" s="1">
-        <v>165000</v>
+        <v>77000</v>
       </c>
       <c r="L184" s="1">
         <v>0</v>
@@ -9447,7 +9387,7 @@
       </c>
       <c r="N184" s="1"/>
       <c r="O184" s="1">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="P184" s="1" t="s">
         <v>23</v>
@@ -9476,17 +9416,17 @@
         <v>20</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H185" s="1"/>
       <c r="I185" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J185" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K185" s="1">
-        <v>4500</v>
+        <v>12000</v>
       </c>
       <c r="L185" s="1">
         <v>0</v>
@@ -9496,7 +9436,7 @@
       </c>
       <c r="N185" s="1"/>
       <c r="O185" s="1">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="P185" s="1" t="s">
         <v>23</v>
@@ -9525,17 +9465,17 @@
         <v>20</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H186" s="1"/>
       <c r="I186" s="1" t="s">
         <v>47</v>
       </c>
       <c r="J186" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K186" s="1">
-        <v>110000</v>
+        <v>11000</v>
       </c>
       <c r="L186" s="1">
         <v>0</v>
@@ -9545,7 +9485,7 @@
       </c>
       <c r="N186" s="1"/>
       <c r="O186" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P186" s="1" t="s">
         <v>23</v>
@@ -9568,21 +9508,23 @@
         <v>18</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G187" s="1"/>
+      <c r="G187" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="H187" s="1"/>
       <c r="I187" s="1" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="J187" s="1">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="K187" s="1">
-        <v>445500</v>
+        <v>22000</v>
       </c>
       <c r="L187" s="1">
         <v>0</v>
@@ -9592,12 +9534,14 @@
       </c>
       <c r="N187" s="1"/>
       <c r="O187" s="1">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="P187" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q187" s="1"/>
+      <c r="Q187" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="188" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A188" s="2">
@@ -9613,21 +9557,23 @@
         <v>18</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G188" s="1"/>
+      <c r="G188" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="H188" s="1"/>
       <c r="I188" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J188" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K188" s="1">
-        <v>1100000</v>
+        <v>6000</v>
       </c>
       <c r="L188" s="1">
         <v>0</v>
@@ -9637,12 +9583,14 @@
       </c>
       <c r="N188" s="1"/>
       <c r="O188" s="1">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="P188" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q188" s="1"/>
+      <c r="Q188" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="189" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A189" s="2">
@@ -9658,21 +9606,23 @@
         <v>18</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G189" s="1"/>
+      <c r="G189" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="H189" s="1"/>
       <c r="I189" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="J189" s="1">
-        <v>134</v>
+        <v>10</v>
       </c>
       <c r="K189" s="1">
-        <v>804000</v>
+        <v>110000</v>
       </c>
       <c r="L189" s="1">
         <v>0</v>
@@ -9682,12 +9632,14 @@
       </c>
       <c r="N189" s="1"/>
       <c r="O189" s="1">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="P189" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q189" s="1"/>
+      <c r="Q189" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="190" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A190" s="2">
@@ -9703,21 +9655,23 @@
         <v>18</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G190" s="1"/>
+      <c r="G190" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="H190" s="1"/>
       <c r="I190" s="1" t="s">
         <v>47</v>
       </c>
       <c r="J190" s="1">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K190" s="1">
-        <v>176000</v>
+        <v>121000</v>
       </c>
       <c r="L190" s="1">
         <v>0</v>
@@ -9727,12 +9681,14 @@
       </c>
       <c r="N190" s="1"/>
       <c r="O190" s="1">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="P190" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q190" s="1"/>
+      <c r="Q190" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="191" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A191" s="2">
@@ -9748,21 +9704,23 @@
         <v>18</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G191" s="1"/>
+      <c r="G191" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="H191" s="1"/>
       <c r="I191" s="1" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="J191" s="1">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="K191" s="1">
-        <v>2200000</v>
+        <v>55000</v>
       </c>
       <c r="L191" s="1">
         <v>0</v>
@@ -9772,12 +9730,14 @@
       </c>
       <c r="N191" s="1"/>
       <c r="O191" s="1">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="P191" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q191" s="1"/>
+      <c r="Q191" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="192" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A192" s="2">
@@ -9793,21 +9753,23 @@
         <v>18</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G192" s="1"/>
+      <c r="G192" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="H192" s="1"/>
       <c r="I192" s="1" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="J192" s="1">
-        <v>24.416665999999999</v>
+        <v>5</v>
       </c>
       <c r="K192" s="1">
-        <v>219750</v>
+        <v>55000</v>
       </c>
       <c r="L192" s="1">
         <v>0</v>
@@ -9817,12 +9779,14 @@
       </c>
       <c r="N192" s="1"/>
       <c r="O192" s="1">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="P192" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q192" s="1"/>
+      <c r="Q192" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="193" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A193" s="2">
@@ -9838,21 +9802,23 @@
         <v>18</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G193" s="1"/>
+      <c r="G193" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="H193" s="1"/>
       <c r="I193" s="1" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="J193" s="1">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K193" s="1">
-        <v>375000</v>
+        <v>6000</v>
       </c>
       <c r="L193" s="1">
         <v>0</v>
@@ -9862,12 +9828,14 @@
       </c>
       <c r="N193" s="1"/>
       <c r="O193" s="1">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="P193" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q193" s="1"/>
+      <c r="Q193" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="194" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A194" s="2">
@@ -9883,21 +9851,23 @@
         <v>18</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G194" s="1"/>
+      <c r="G194" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="H194" s="1"/>
       <c r="I194" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J194" s="1">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K194" s="1">
-        <v>225000</v>
+        <v>165000</v>
       </c>
       <c r="L194" s="1">
         <v>0</v>
@@ -9907,12 +9877,14 @@
       </c>
       <c r="N194" s="1"/>
       <c r="O194" s="1">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P194" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q194" s="1"/>
+      <c r="Q194" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="195" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A195" s="2">
@@ -9928,21 +9900,23 @@
         <v>18</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G195" s="1"/>
+      <c r="G195" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="H195" s="1"/>
       <c r="I195" s="1" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="J195" s="1">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K195" s="1">
-        <v>375000</v>
+        <v>4500</v>
       </c>
       <c r="L195" s="1">
         <v>0</v>
@@ -9952,12 +9926,14 @@
       </c>
       <c r="N195" s="1"/>
       <c r="O195" s="1">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="P195" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q195" s="1"/>
+      <c r="Q195" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="196" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A196" s="2">
@@ -9973,21 +9949,23 @@
         <v>18</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G196" s="1"/>
+      <c r="G196" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="H196" s="1"/>
       <c r="I196" s="1" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="J196" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K196" s="1">
-        <v>1150000</v>
+        <v>110000</v>
       </c>
       <c r="L196" s="1">
         <v>0</v>
@@ -9997,12 +9975,14 @@
       </c>
       <c r="N196" s="1"/>
       <c r="O196" s="1">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="P196" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q196" s="1"/>
+      <c r="Q196" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="197" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A197" s="2">
@@ -10026,13 +10006,13 @@
       <c r="G197" s="1"/>
       <c r="H197" s="1"/>
       <c r="I197" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="J197" s="1">
-        <v>599</v>
+        <v>99</v>
       </c>
       <c r="K197" s="1">
-        <v>6289500</v>
+        <v>445500</v>
       </c>
       <c r="L197" s="1">
         <v>0</v>
@@ -10042,12 +10022,462 @@
       </c>
       <c r="N197" s="1"/>
       <c r="O197" s="1">
+        <v>31</v>
+      </c>
+      <c r="P197" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q197" s="1"/>
+    </row>
+    <row r="198" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A198" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B198" s="1">
+        <v>0</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G198" s="1"/>
+      <c r="H198" s="1"/>
+      <c r="I198" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J198" s="1">
+        <v>100</v>
+      </c>
+      <c r="K198" s="1">
+        <v>1100000</v>
+      </c>
+      <c r="L198" s="1">
+        <v>0</v>
+      </c>
+      <c r="M198" s="1">
+        <v>0</v>
+      </c>
+      <c r="N198" s="1"/>
+      <c r="O198" s="1">
+        <v>32</v>
+      </c>
+      <c r="P198" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q198" s="1"/>
+    </row>
+    <row r="199" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A199" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B199" s="1">
+        <v>0</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F199" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G199" s="1"/>
+      <c r="H199" s="1"/>
+      <c r="I199" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J199" s="1">
+        <v>134</v>
+      </c>
+      <c r="K199" s="1">
+        <v>804000</v>
+      </c>
+      <c r="L199" s="1">
+        <v>0</v>
+      </c>
+      <c r="M199" s="1">
+        <v>0</v>
+      </c>
+      <c r="N199" s="1"/>
+      <c r="O199" s="1">
+        <v>33</v>
+      </c>
+      <c r="P199" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q199" s="1"/>
+    </row>
+    <row r="200" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A200" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B200" s="1">
+        <v>0</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G200" s="1"/>
+      <c r="H200" s="1"/>
+      <c r="I200" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J200" s="1">
+        <v>16</v>
+      </c>
+      <c r="K200" s="1">
+        <v>176000</v>
+      </c>
+      <c r="L200" s="1">
+        <v>0</v>
+      </c>
+      <c r="M200" s="1">
+        <v>0</v>
+      </c>
+      <c r="N200" s="1"/>
+      <c r="O200" s="1">
+        <v>34</v>
+      </c>
+      <c r="P200" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q200" s="1"/>
+    </row>
+    <row r="201" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A201" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B201" s="1">
+        <v>0</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G201" s="1"/>
+      <c r="H201" s="1"/>
+      <c r="I201" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J201" s="1">
+        <v>200</v>
+      </c>
+      <c r="K201" s="1">
+        <v>2200000</v>
+      </c>
+      <c r="L201" s="1">
+        <v>0</v>
+      </c>
+      <c r="M201" s="1">
+        <v>0</v>
+      </c>
+      <c r="N201" s="1"/>
+      <c r="O201" s="1">
+        <v>35</v>
+      </c>
+      <c r="P201" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q201" s="1"/>
+    </row>
+    <row r="202" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A202" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B202" s="1">
+        <v>0</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G202" s="1"/>
+      <c r="H202" s="1"/>
+      <c r="I202" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J202" s="1">
+        <v>24.416665999999999</v>
+      </c>
+      <c r="K202" s="1">
+        <v>219750</v>
+      </c>
+      <c r="L202" s="1">
+        <v>0</v>
+      </c>
+      <c r="M202" s="1">
+        <v>0</v>
+      </c>
+      <c r="N202" s="1"/>
+      <c r="O202" s="1">
+        <v>36</v>
+      </c>
+      <c r="P202" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q202" s="1"/>
+    </row>
+    <row r="203" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A203" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B203" s="1">
+        <v>0</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G203" s="1"/>
+      <c r="H203" s="1"/>
+      <c r="I203" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J203" s="1">
+        <v>25</v>
+      </c>
+      <c r="K203" s="1">
+        <v>375000</v>
+      </c>
+      <c r="L203" s="1">
+        <v>0</v>
+      </c>
+      <c r="M203" s="1">
+        <v>0</v>
+      </c>
+      <c r="N203" s="1"/>
+      <c r="O203" s="1">
+        <v>37</v>
+      </c>
+      <c r="P203" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q203" s="1"/>
+    </row>
+    <row r="204" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A204" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B204" s="1">
+        <v>0</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G204" s="1"/>
+      <c r="H204" s="1"/>
+      <c r="I204" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J204" s="1">
+        <v>25</v>
+      </c>
+      <c r="K204" s="1">
+        <v>225000</v>
+      </c>
+      <c r="L204" s="1">
+        <v>0</v>
+      </c>
+      <c r="M204" s="1">
+        <v>0</v>
+      </c>
+      <c r="N204" s="1"/>
+      <c r="O204" s="1">
+        <v>38</v>
+      </c>
+      <c r="P204" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q204" s="1"/>
+    </row>
+    <row r="205" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A205" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B205" s="1">
+        <v>0</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G205" s="1"/>
+      <c r="H205" s="1"/>
+      <c r="I205" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J205" s="1">
+        <v>25</v>
+      </c>
+      <c r="K205" s="1">
+        <v>375000</v>
+      </c>
+      <c r="L205" s="1">
+        <v>0</v>
+      </c>
+      <c r="M205" s="1">
+        <v>0</v>
+      </c>
+      <c r="N205" s="1"/>
+      <c r="O205" s="1">
+        <v>39</v>
+      </c>
+      <c r="P205" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q205" s="1"/>
+    </row>
+    <row r="206" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A206" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B206" s="1">
+        <v>0</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F206" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G206" s="1"/>
+      <c r="H206" s="1"/>
+      <c r="I206" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J206" s="1">
+        <v>100</v>
+      </c>
+      <c r="K206" s="1">
+        <v>1150000</v>
+      </c>
+      <c r="L206" s="1">
+        <v>0</v>
+      </c>
+      <c r="M206" s="1">
+        <v>0</v>
+      </c>
+      <c r="N206" s="1"/>
+      <c r="O206" s="1">
+        <v>40</v>
+      </c>
+      <c r="P206" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q206" s="1"/>
+    </row>
+    <row r="207" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A207" s="2">
+        <v>46221</v>
+      </c>
+      <c r="B207" s="1">
+        <v>0</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G207" s="1"/>
+      <c r="H207" s="1"/>
+      <c r="I207" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J207" s="1">
+        <v>599</v>
+      </c>
+      <c r="K207" s="1">
+        <v>6289500</v>
+      </c>
+      <c r="L207" s="1">
+        <v>0</v>
+      </c>
+      <c r="M207" s="1">
+        <v>0</v>
+      </c>
+      <c r="N207" s="1"/>
+      <c r="O207" s="1">
         <v>41</v>
       </c>
-      <c r="P197" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q197" s="1"/>
+      <c r="P207" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q207" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B17AE2-89B6-455D-BF3E-166A0F3AF154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D1B0AE-C2C2-472A-900A-149352411681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1564" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="48">
   <si>
     <t>Date</t>
   </si>
@@ -143,9 +143,6 @@
   </si>
   <si>
     <t>Nogueye THIAME (T2)</t>
-  </si>
-  <si>
-    <t>Autre</t>
   </si>
   <si>
     <t>Seynabou sow RZ</t>
@@ -1972,9 +1969,6 @@
       <c r="G29" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H29" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="I29" s="1" t="s">
         <v>25</v>
       </c>
@@ -2013,7 +2007,7 @@
         <v>18</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>20</v>
@@ -2056,7 +2050,7 @@
         <v>18</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>20</v>
@@ -2099,7 +2093,7 @@
         <v>18</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>20</v>
@@ -2142,7 +2136,7 @@
         <v>18</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>20</v>
@@ -2185,7 +2179,7 @@
         <v>18</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>20</v>
@@ -2228,7 +2222,7 @@
         <v>18</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>20</v>
@@ -2236,7 +2230,7 @@
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J35" s="1">
         <v>23</v>
@@ -2271,7 +2265,7 @@
         <v>18</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>20</v>
@@ -2279,7 +2273,7 @@
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J36" s="1">
         <v>25</v>
@@ -2314,7 +2308,7 @@
         <v>18</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>20</v>
@@ -2322,7 +2316,7 @@
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J37" s="1">
         <v>25</v>
@@ -2357,7 +2351,7 @@
         <v>18</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>20</v>
@@ -2400,7 +2394,7 @@
         <v>18</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>20</v>
@@ -3815,7 +3809,7 @@
         <v>18</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>20</v>
@@ -3858,7 +3852,7 @@
         <v>18</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>20</v>
@@ -3901,7 +3895,7 @@
         <v>18</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>20</v>
@@ -3944,7 +3938,7 @@
         <v>18</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>20</v>
@@ -3987,7 +3981,7 @@
         <v>18</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>20</v>
@@ -4030,7 +4024,7 @@
         <v>18</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>20</v>
@@ -4038,7 +4032,7 @@
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
       <c r="I73" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J73" s="1">
         <v>23</v>
@@ -4073,7 +4067,7 @@
         <v>18</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>20</v>
@@ -4081,7 +4075,7 @@
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
       <c r="I74" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J74" s="1">
         <v>25</v>
@@ -4116,7 +4110,7 @@
         <v>18</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>20</v>
@@ -4124,7 +4118,7 @@
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J75" s="1">
         <v>25</v>
@@ -4159,7 +4153,7 @@
         <v>18</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>20</v>
@@ -4202,7 +4196,7 @@
         <v>18</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>20</v>
@@ -4247,7 +4241,7 @@
         <v>18</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>20</v>
@@ -4292,7 +4286,7 @@
         <v>18</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>20</v>
@@ -4337,7 +4331,7 @@
         <v>18</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>20</v>
@@ -4382,7 +4376,7 @@
         <v>18</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>20</v>
@@ -4427,7 +4421,7 @@
         <v>18</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>20</v>
@@ -4435,7 +4429,7 @@
       <c r="G82" s="1"/>
       <c r="H82" s="1"/>
       <c r="I82" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J82" s="1">
         <v>23</v>
@@ -4472,7 +4466,7 @@
         <v>18</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>20</v>
@@ -4517,7 +4511,7 @@
         <v>18</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>20</v>
@@ -4525,7 +4519,7 @@
       <c r="G84" s="1"/>
       <c r="H84" s="1"/>
       <c r="I84" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J84" s="1">
         <v>25</v>
@@ -4562,7 +4556,7 @@
         <v>18</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>20</v>
@@ -4570,7 +4564,7 @@
       <c r="G85" s="1"/>
       <c r="H85" s="1"/>
       <c r="I85" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J85" s="1">
         <v>25</v>
@@ -4607,7 +4601,7 @@
         <v>18</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>20</v>
@@ -4652,7 +4646,7 @@
         <v>18</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>20</v>
@@ -6028,9 +6022,6 @@
       <c r="G115" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H115" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="I115" s="1" t="s">
         <v>25</v>
       </c>
@@ -6079,9 +6070,6 @@
       <c r="G116" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H116" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="I116" s="1" t="s">
         <v>31</v>
       </c>
@@ -6818,7 +6806,7 @@
       </c>
       <c r="H131" s="1"/>
       <c r="I131" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J131" s="1">
         <v>1</v>
@@ -7406,7 +7394,7 @@
       </c>
       <c r="H143" s="1"/>
       <c r="I143" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J143" s="1">
         <v>1</v>
@@ -7455,7 +7443,7 @@
       </c>
       <c r="H144" s="1"/>
       <c r="I144" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J144" s="1">
         <v>2</v>
@@ -7602,7 +7590,7 @@
       </c>
       <c r="H147" s="1"/>
       <c r="I147" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J147" s="1">
         <v>2</v>
@@ -8141,7 +8129,7 @@
       </c>
       <c r="H158" s="1"/>
       <c r="I158" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J158" s="1">
         <v>5</v>
@@ -8190,7 +8178,7 @@
       </c>
       <c r="H159" s="1"/>
       <c r="I159" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J159" s="1">
         <v>5</v>
@@ -8337,7 +8325,7 @@
       </c>
       <c r="H162" s="1"/>
       <c r="I162" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J162" s="1">
         <v>1</v>
@@ -8435,7 +8423,7 @@
       </c>
       <c r="H164" s="1"/>
       <c r="I164" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J164" s="1">
         <v>1</v>
@@ -8572,7 +8560,7 @@
         <v>18</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>20</v>
@@ -8617,7 +8605,7 @@
         <v>18</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>20</v>
@@ -8662,7 +8650,7 @@
         <v>18</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>20</v>
@@ -8707,7 +8695,7 @@
         <v>18</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>20</v>
@@ -8752,7 +8740,7 @@
         <v>18</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>20</v>
@@ -8797,7 +8785,7 @@
         <v>18</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>20</v>
@@ -8805,7 +8793,7 @@
       <c r="G172" s="1"/>
       <c r="H172" s="1"/>
       <c r="I172" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J172" s="1">
         <v>100</v>
@@ -8842,7 +8830,7 @@
         <v>18</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>20</v>
@@ -8887,7 +8875,7 @@
         <v>18</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>20</v>
@@ -8895,7 +8883,7 @@
       <c r="G174" s="1"/>
       <c r="H174" s="1"/>
       <c r="I174" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J174" s="1">
         <v>25</v>
@@ -8932,7 +8920,7 @@
         <v>18</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>20</v>
@@ -8940,7 +8928,7 @@
       <c r="G175" s="1"/>
       <c r="H175" s="1"/>
       <c r="I175" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J175" s="1">
         <v>25</v>
@@ -8977,7 +8965,7 @@
         <v>18</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>20</v>
@@ -8985,7 +8973,7 @@
       <c r="G176" s="1"/>
       <c r="H176" s="1"/>
       <c r="I176" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J176" s="1">
         <v>25</v>
@@ -9022,7 +9010,7 @@
         <v>18</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>20</v>
@@ -9126,7 +9114,7 @@
       </c>
       <c r="H179" s="1"/>
       <c r="I179" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J179" s="1">
         <v>6</v>
@@ -9175,7 +9163,7 @@
       </c>
       <c r="H180" s="1"/>
       <c r="I180" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J180" s="1">
         <v>6</v>
@@ -9224,7 +9212,7 @@
       </c>
       <c r="H181" s="1"/>
       <c r="I181" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J181" s="1">
         <v>6</v>
@@ -9371,7 +9359,7 @@
       </c>
       <c r="H184" s="1"/>
       <c r="I184" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J184" s="1">
         <v>7</v>
@@ -9469,7 +9457,7 @@
       </c>
       <c r="H186" s="1"/>
       <c r="I186" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J186" s="1">
         <v>1</v>
@@ -9518,7 +9506,7 @@
       </c>
       <c r="H187" s="1"/>
       <c r="I187" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J187" s="1">
         <v>2</v>
@@ -9616,7 +9604,7 @@
       </c>
       <c r="H189" s="1"/>
       <c r="I189" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J189" s="1">
         <v>10</v>
@@ -9665,7 +9653,7 @@
       </c>
       <c r="H190" s="1"/>
       <c r="I190" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J190" s="1">
         <v>11</v>
@@ -9714,7 +9702,7 @@
       </c>
       <c r="H191" s="1"/>
       <c r="I191" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J191" s="1">
         <v>5</v>
@@ -9763,7 +9751,7 @@
       </c>
       <c r="H192" s="1"/>
       <c r="I192" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J192" s="1">
         <v>5</v>
@@ -9861,7 +9849,7 @@
       </c>
       <c r="H194" s="1"/>
       <c r="I194" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J194" s="1">
         <v>15</v>
@@ -9959,7 +9947,7 @@
       </c>
       <c r="H196" s="1"/>
       <c r="I196" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J196" s="1">
         <v>10</v>
@@ -9998,7 +9986,7 @@
         <v>18</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>20</v>
@@ -10043,7 +10031,7 @@
         <v>18</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>20</v>
@@ -10088,7 +10076,7 @@
         <v>18</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>20</v>
@@ -10133,7 +10121,7 @@
         <v>18</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>20</v>
@@ -10141,7 +10129,7 @@
       <c r="G200" s="1"/>
       <c r="H200" s="1"/>
       <c r="I200" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J200" s="1">
         <v>16</v>
@@ -10178,7 +10166,7 @@
         <v>18</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>20</v>
@@ -10223,7 +10211,7 @@
         <v>18</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>20</v>
@@ -10268,7 +10256,7 @@
         <v>18</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>20</v>
@@ -10276,7 +10264,7 @@
       <c r="G203" s="1"/>
       <c r="H203" s="1"/>
       <c r="I203" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J203" s="1">
         <v>25</v>
@@ -10313,7 +10301,7 @@
         <v>18</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>20</v>
@@ -10321,7 +10309,7 @@
       <c r="G204" s="1"/>
       <c r="H204" s="1"/>
       <c r="I204" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J204" s="1">
         <v>25</v>
@@ -10358,7 +10346,7 @@
         <v>18</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>20</v>
@@ -10366,7 +10354,7 @@
       <c r="G205" s="1"/>
       <c r="H205" s="1"/>
       <c r="I205" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J205" s="1">
         <v>25</v>
@@ -10403,7 +10391,7 @@
         <v>18</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>20</v>
@@ -10448,7 +10436,7 @@
         <v>18</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>20</v>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4F2A645-6CC9-4F20-9056-BE008CDB5822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C671998-B105-4B76-97C6-A88CF1CB72B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2372" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2368" uniqueCount="51">
   <si>
     <t>Date</t>
   </si>
@@ -2221,9 +2221,6 @@
         <v>20</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H34" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I34" s="1" t="s">
@@ -2272,9 +2269,6 @@
         <v>20</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H35" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I35" s="1" t="s">
@@ -2323,9 +2317,6 @@
         <v>20</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H36" s="1" t="s">
         <v>43</v>
       </c>
       <c r="I36" s="1" t="s">
@@ -2374,9 +2365,6 @@
         <v>20</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H37" s="1" t="s">
         <v>43</v>
       </c>
       <c r="I37" s="1" t="s">

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C671998-B105-4B76-97C6-A88CF1CB72B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC176F3-F0A4-4F88-9216-65C984B3E082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2368" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2365" uniqueCount="50">
   <si>
     <t>Date</t>
   </si>
@@ -143,9 +143,6 @@
   </si>
   <si>
     <t>Chocolat 3-en-1 30x120 pcs</t>
-  </si>
-  <si>
-    <t>Autre</t>
   </si>
   <si>
     <t>Seynabou Sow RZ</t>
@@ -2221,7 +2218,7 @@
         <v>20</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>22</v>
@@ -2269,7 +2266,7 @@
         <v>20</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>24</v>
@@ -2317,7 +2314,7 @@
         <v>20</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>22</v>
@@ -2365,7 +2362,7 @@
         <v>20</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>28</v>
@@ -2417,7 +2414,7 @@
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J38" s="1">
         <v>8.3333335999999994E-2</v>
@@ -4328,7 +4325,7 @@
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J77" s="1">
         <v>1.8333333999999999</v>
@@ -5063,7 +5060,7 @@
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J92" s="1">
         <v>0.16666666999999999</v>
@@ -5198,7 +5195,7 @@
         <v>18</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>20</v>
@@ -5241,7 +5238,7 @@
         <v>18</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>20</v>
@@ -5284,7 +5281,7 @@
         <v>18</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>20</v>
@@ -5327,7 +5324,7 @@
         <v>18</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>20</v>
@@ -5370,7 +5367,7 @@
         <v>18</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>20</v>
@@ -5378,7 +5375,7 @@
       <c r="G99" s="1"/>
       <c r="H99" s="1"/>
       <c r="I99" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J99" s="1">
         <v>16.666665999999999</v>
@@ -5413,7 +5410,7 @@
         <v>18</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>20</v>
@@ -5456,7 +5453,7 @@
         <v>18</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>20</v>
@@ -5464,7 +5461,7 @@
       <c r="G101" s="1"/>
       <c r="H101" s="1"/>
       <c r="I101" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J101" s="1">
         <v>25</v>
@@ -5499,7 +5496,7 @@
         <v>18</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>20</v>
@@ -5507,7 +5504,7 @@
       <c r="G102" s="1"/>
       <c r="H102" s="1"/>
       <c r="I102" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J102" s="1">
         <v>25</v>
@@ -5542,7 +5539,7 @@
         <v>18</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>20</v>
@@ -5585,7 +5582,7 @@
         <v>18</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>20</v>
@@ -5836,7 +5833,7 @@
       </c>
       <c r="H109" s="1"/>
       <c r="I109" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J109" s="1">
         <v>1.0833333999999999</v>
@@ -6130,7 +6127,7 @@
       </c>
       <c r="H115" s="1"/>
       <c r="I115" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J115" s="1">
         <v>8.3333335999999994E-2</v>
@@ -6179,7 +6176,7 @@
       </c>
       <c r="H116" s="1"/>
       <c r="I116" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J116" s="1">
         <v>8.3333335999999994E-2</v>
@@ -6959,10 +6956,7 @@
         <v>20</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H132" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>22</v>
@@ -7002,7 +6996,7 @@
         <v>18</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>20</v>
@@ -7045,7 +7039,7 @@
         <v>18</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>20</v>
@@ -7088,7 +7082,7 @@
         <v>18</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>20</v>
@@ -7131,7 +7125,7 @@
         <v>18</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>20</v>
@@ -7174,7 +7168,7 @@
         <v>18</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>20</v>
@@ -7182,7 +7176,7 @@
       <c r="G137" s="1"/>
       <c r="H137" s="1"/>
       <c r="I137" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J137" s="1">
         <v>18.666665999999999</v>
@@ -7217,7 +7211,7 @@
         <v>18</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>20</v>
@@ -7260,7 +7254,7 @@
         <v>18</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>20</v>
@@ -7268,7 +7262,7 @@
       <c r="G139" s="1"/>
       <c r="H139" s="1"/>
       <c r="I139" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J139" s="1">
         <v>25</v>
@@ -7303,7 +7297,7 @@
         <v>18</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>20</v>
@@ -7311,7 +7305,7 @@
       <c r="G140" s="1"/>
       <c r="H140" s="1"/>
       <c r="I140" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J140" s="1">
         <v>25</v>
@@ -7346,7 +7340,7 @@
         <v>18</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>20</v>
@@ -7389,7 +7383,7 @@
         <v>18</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>20</v>
@@ -8571,7 +8565,7 @@
       </c>
       <c r="H166" s="1"/>
       <c r="I166" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J166" s="1">
         <v>2</v>
@@ -8804,7 +8798,7 @@
         <v>18</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>20</v>
@@ -8847,7 +8841,7 @@
         <v>18</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>20</v>
@@ -8890,7 +8884,7 @@
         <v>18</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>20</v>
@@ -8933,7 +8927,7 @@
         <v>18</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>20</v>
@@ -8941,7 +8935,7 @@
       <c r="G174" s="1"/>
       <c r="H174" s="1"/>
       <c r="I174" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J174" s="1">
         <v>19.916665999999999</v>
@@ -8976,7 +8970,7 @@
         <v>18</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>20</v>
@@ -9019,7 +9013,7 @@
         <v>18</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>20</v>
@@ -9062,7 +9056,7 @@
         <v>18</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>20</v>
@@ -9070,7 +9064,7 @@
       <c r="G177" s="1"/>
       <c r="H177" s="1"/>
       <c r="I177" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J177" s="1">
         <v>25</v>
@@ -9105,7 +9099,7 @@
         <v>18</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>20</v>
@@ -9113,7 +9107,7 @@
       <c r="G178" s="1"/>
       <c r="H178" s="1"/>
       <c r="I178" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J178" s="1">
         <v>25</v>
@@ -9148,7 +9142,7 @@
         <v>18</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>20</v>
@@ -9191,7 +9185,7 @@
         <v>18</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>20</v>
@@ -9236,7 +9230,7 @@
         <v>18</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>20</v>
@@ -9281,7 +9275,7 @@
         <v>18</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>20</v>
@@ -9326,7 +9320,7 @@
         <v>18</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>20</v>
@@ -9371,7 +9365,7 @@
         <v>18</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>20</v>
@@ -9416,7 +9410,7 @@
         <v>18</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>20</v>
@@ -9461,7 +9455,7 @@
         <v>18</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>20</v>
@@ -9469,7 +9463,7 @@
       <c r="G186" s="1"/>
       <c r="H186" s="1"/>
       <c r="I186" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J186" s="1">
         <v>21.916665999999999</v>
@@ -9506,7 +9500,7 @@
         <v>18</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>20</v>
@@ -9514,7 +9508,7 @@
       <c r="G187" s="1"/>
       <c r="H187" s="1"/>
       <c r="I187" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J187" s="1">
         <v>25</v>
@@ -9551,7 +9545,7 @@
         <v>18</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>20</v>
@@ -9559,7 +9553,7 @@
       <c r="G188" s="1"/>
       <c r="H188" s="1"/>
       <c r="I188" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J188" s="1">
         <v>25</v>
@@ -9596,7 +9590,7 @@
         <v>18</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>20</v>
@@ -9641,7 +9635,7 @@
         <v>18</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>20</v>
@@ -11015,10 +11009,7 @@
         <v>20</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H218" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>22</v>
@@ -11066,10 +11057,7 @@
         <v>20</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H219" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>28</v>
@@ -12199,7 +12187,7 @@
       </c>
       <c r="H242" s="1"/>
       <c r="I242" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J242" s="1">
         <v>0.5</v>
@@ -12444,7 +12432,7 @@
       </c>
       <c r="H247" s="1"/>
       <c r="I247" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J247" s="1">
         <v>2</v>
@@ -12591,7 +12579,7 @@
       </c>
       <c r="H250" s="1"/>
       <c r="I250" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J250" s="1">
         <v>2</v>
@@ -12738,7 +12726,7 @@
       </c>
       <c r="H253" s="1"/>
       <c r="I253" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J253" s="1">
         <v>1</v>
@@ -12983,7 +12971,7 @@
       </c>
       <c r="H258" s="1"/>
       <c r="I258" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J258" s="1">
         <v>1</v>
@@ -13130,7 +13118,7 @@
       </c>
       <c r="H261" s="1"/>
       <c r="I261" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J261" s="1">
         <v>5</v>
@@ -13179,7 +13167,7 @@
       </c>
       <c r="H262" s="1"/>
       <c r="I262" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J262" s="1">
         <v>5</v>
@@ -13326,7 +13314,7 @@
       </c>
       <c r="H265" s="1"/>
       <c r="I265" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J265" s="1">
         <v>1</v>
@@ -13424,7 +13412,7 @@
       </c>
       <c r="H267" s="1"/>
       <c r="I267" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J267" s="1">
         <v>1</v>
@@ -13561,7 +13549,7 @@
         <v>18</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>20</v>
@@ -13606,7 +13594,7 @@
         <v>18</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>20</v>
@@ -13651,7 +13639,7 @@
         <v>18</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>20</v>
@@ -13696,7 +13684,7 @@
         <v>18</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>20</v>
@@ -13741,7 +13729,7 @@
         <v>18</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>20</v>
@@ -13786,7 +13774,7 @@
         <v>18</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>20</v>
@@ -13794,7 +13782,7 @@
       <c r="G275" s="1"/>
       <c r="H275" s="1"/>
       <c r="I275" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J275" s="1">
         <v>100</v>
@@ -13831,7 +13819,7 @@
         <v>18</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>20</v>
@@ -13876,7 +13864,7 @@
         <v>18</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>20</v>
@@ -13921,7 +13909,7 @@
         <v>18</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>20</v>
@@ -13929,7 +13917,7 @@
       <c r="G278" s="1"/>
       <c r="H278" s="1"/>
       <c r="I278" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J278" s="1">
         <v>25</v>
@@ -13966,7 +13954,7 @@
         <v>18</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>20</v>
@@ -13974,7 +13962,7 @@
       <c r="G279" s="1"/>
       <c r="H279" s="1"/>
       <c r="I279" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J279" s="1">
         <v>25</v>
@@ -14011,7 +13999,7 @@
         <v>18</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>20</v>
@@ -14019,7 +14007,7 @@
       <c r="G280" s="1"/>
       <c r="H280" s="1"/>
       <c r="I280" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J280" s="1">
         <v>25</v>
@@ -14066,7 +14054,7 @@
       </c>
       <c r="H281" s="1"/>
       <c r="I281" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J281" s="1">
         <v>0.58333330000000005</v>
@@ -14115,7 +14103,7 @@
       </c>
       <c r="H282" s="1"/>
       <c r="I282" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J282" s="1">
         <v>6</v>
@@ -14164,7 +14152,7 @@
       </c>
       <c r="H283" s="1"/>
       <c r="I283" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J283" s="1">
         <v>6</v>
@@ -14213,7 +14201,7 @@
       </c>
       <c r="H284" s="1"/>
       <c r="I284" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J284" s="1">
         <v>6</v>
@@ -14360,7 +14348,7 @@
       </c>
       <c r="H287" s="1"/>
       <c r="I287" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J287" s="1">
         <v>7</v>
@@ -14458,7 +14446,7 @@
       </c>
       <c r="H289" s="1"/>
       <c r="I289" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J289" s="1">
         <v>1</v>
@@ -14507,7 +14495,7 @@
       </c>
       <c r="H290" s="1"/>
       <c r="I290" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J290" s="1">
         <v>2</v>
@@ -14605,7 +14593,7 @@
       </c>
       <c r="H292" s="1"/>
       <c r="I292" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J292" s="1">
         <v>10</v>
@@ -14654,7 +14642,7 @@
       </c>
       <c r="H293" s="1"/>
       <c r="I293" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J293" s="1">
         <v>11</v>
@@ -14703,7 +14691,7 @@
       </c>
       <c r="H294" s="1"/>
       <c r="I294" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J294" s="1">
         <v>5</v>
@@ -14752,7 +14740,7 @@
       </c>
       <c r="H295" s="1"/>
       <c r="I295" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J295" s="1">
         <v>5</v>
@@ -14850,7 +14838,7 @@
       </c>
       <c r="H297" s="1"/>
       <c r="I297" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J297" s="1">
         <v>15</v>
@@ -14948,7 +14936,7 @@
       </c>
       <c r="H299" s="1"/>
       <c r="I299" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J299" s="1">
         <v>10</v>
@@ -14987,7 +14975,7 @@
         <v>18</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>20</v>
@@ -15032,7 +15020,7 @@
         <v>18</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>20</v>
@@ -15077,7 +15065,7 @@
         <v>18</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>20</v>
@@ -15122,7 +15110,7 @@
         <v>18</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>20</v>
@@ -15130,7 +15118,7 @@
       <c r="G303" s="1"/>
       <c r="H303" s="1"/>
       <c r="I303" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J303" s="1">
         <v>16</v>
@@ -15167,7 +15155,7 @@
         <v>18</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>20</v>
@@ -15212,7 +15200,7 @@
         <v>18</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>20</v>
@@ -15220,7 +15208,7 @@
       <c r="G305" s="1"/>
       <c r="H305" s="1"/>
       <c r="I305" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J305" s="1">
         <v>24.416665999999999</v>
@@ -15257,7 +15245,7 @@
         <v>18</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>20</v>
@@ -15302,7 +15290,7 @@
         <v>18</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>20</v>
@@ -15310,7 +15298,7 @@
       <c r="G307" s="1"/>
       <c r="H307" s="1"/>
       <c r="I307" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J307" s="1">
         <v>25</v>
@@ -15347,7 +15335,7 @@
         <v>18</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>20</v>
@@ -15355,7 +15343,7 @@
       <c r="G308" s="1"/>
       <c r="H308" s="1"/>
       <c r="I308" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J308" s="1">
         <v>25</v>
@@ -15392,7 +15380,7 @@
         <v>18</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>20</v>
@@ -15437,7 +15425,7 @@
         <v>18</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>20</v>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC176F3-F0A4-4F88-9216-65C984B3E082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4264A3EE-87C6-4A32-BEC3-8741F1C734C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2365" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2368" uniqueCount="51">
   <si>
     <t>Date</t>
   </si>
@@ -170,6 +170,9 @@
   </si>
   <si>
     <t>Stock Lundi</t>
+  </si>
+  <si>
+    <t>Autre</t>
   </si>
 </sst>
 </file>
@@ -6956,6 +6959,9 @@
         <v>20</v>
       </c>
       <c r="G132" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H132" s="1" t="s">
         <v>47</v>
       </c>
       <c r="I132" s="1" t="s">
@@ -11009,6 +11015,9 @@
         <v>20</v>
       </c>
       <c r="G218" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H218" s="1" t="s">
         <v>47</v>
       </c>
       <c r="I218" s="1" t="s">
@@ -11057,6 +11066,9 @@
         <v>20</v>
       </c>
       <c r="G219" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H219" s="1" t="s">
         <v>47</v>
       </c>
       <c r="I219" s="1" t="s">

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E6CA2C-1D36-4B6B-A916-B57DBCA0619E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B63D0C6-E19A-4899-967F-A7D275651E1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2721" uniqueCount="51">
   <si>
     <t>Date</t>
   </si>
@@ -160,10 +160,10 @@
     <t>Kamlac Junior BLE cereal 230g x 12 sachet</t>
   </si>
   <si>
-    <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
+    <t>Kamlac Junior mais cereal 50g x 10 x 8 sachet</t>
   </si>
   <si>
-    <t>Kamlac Junior mais cereal 50g x 10 x 8 sachet</t>
+    <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
   </si>
   <si>
     <t>Seynabou Sow RZ</t>
@@ -1780,6 +1780,9 @@
         <v>20</v>
       </c>
       <c r="G25" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>41</v>
       </c>
       <c r="I25" s="1" t="s">
@@ -1828,6 +1831,9 @@
         <v>20</v>
       </c>
       <c r="G26" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>41</v>
       </c>
       <c r="I26" s="1" t="s">
@@ -1876,6 +1882,9 @@
         <v>20</v>
       </c>
       <c r="G27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H27" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I27" s="1" t="s">
@@ -1924,6 +1933,9 @@
         <v>20</v>
       </c>
       <c r="G28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H28" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I28" s="1" t="s">
@@ -1972,6 +1984,9 @@
         <v>20</v>
       </c>
       <c r="G29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I29" s="1" t="s">
@@ -2004,7 +2019,9 @@
       <c r="A30" s="2">
         <v>46230</v>
       </c>
-      <c r="B30" s="1"/>
+      <c r="B30" s="1">
+        <v>0</v>
+      </c>
       <c r="C30" s="1" t="s">
         <v>17</v>
       </c>
@@ -2020,13 +2037,13 @@
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="J30" s="1">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="K30" s="1">
-        <v>396000</v>
+        <v>117000</v>
       </c>
       <c r="L30" s="1">
         <v>0</v>
@@ -2047,7 +2064,9 @@
       <c r="A31" s="2">
         <v>46230</v>
       </c>
-      <c r="B31" s="1"/>
+      <c r="B31" s="1">
+        <v>0</v>
+      </c>
       <c r="C31" s="1" t="s">
         <v>17</v>
       </c>
@@ -2063,13 +2082,13 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="J31" s="1">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="K31" s="1">
-        <v>1078000</v>
+        <v>391500</v>
       </c>
       <c r="L31" s="1">
         <v>0</v>
@@ -2090,7 +2109,9 @@
       <c r="A32" s="2">
         <v>46230</v>
       </c>
-      <c r="B32" s="1"/>
+      <c r="B32" s="1">
+        <v>0</v>
+      </c>
       <c r="C32" s="1" t="s">
         <v>17</v>
       </c>
@@ -2106,13 +2127,13 @@
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="J32" s="1">
-        <v>76.7</v>
+        <v>98</v>
       </c>
       <c r="K32" s="1">
-        <v>460200</v>
+        <v>1078000</v>
       </c>
       <c r="L32" s="1">
         <v>0</v>
@@ -2133,7 +2154,9 @@
       <c r="A33" s="2">
         <v>46230</v>
       </c>
-      <c r="B33" s="1"/>
+      <c r="B33" s="1">
+        <v>0</v>
+      </c>
       <c r="C33" s="1" t="s">
         <v>17</v>
       </c>
@@ -2149,13 +2172,13 @@
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J33" s="1">
-        <v>184.75</v>
+        <v>65</v>
       </c>
       <c r="K33" s="1">
-        <v>2032250</v>
+        <v>747500</v>
       </c>
       <c r="L33" s="1">
         <v>0</v>
@@ -2176,7 +2199,9 @@
       <c r="A34" s="2">
         <v>46230</v>
       </c>
-      <c r="B34" s="1"/>
+      <c r="B34" s="1">
+        <v>0</v>
+      </c>
       <c r="C34" s="1" t="s">
         <v>17</v>
       </c>
@@ -2192,13 +2217,13 @@
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="J34" s="1">
-        <v>16.583334000000001</v>
+        <v>77</v>
       </c>
       <c r="K34" s="1">
-        <v>149250</v>
+        <v>462000</v>
       </c>
       <c r="L34" s="1">
         <v>0</v>
@@ -2219,7 +2244,9 @@
       <c r="A35" s="2">
         <v>46230</v>
       </c>
-      <c r="B35" s="1"/>
+      <c r="B35" s="1">
+        <v>0</v>
+      </c>
       <c r="C35" s="1" t="s">
         <v>17</v>
       </c>
@@ -2238,10 +2265,10 @@
         <v>26</v>
       </c>
       <c r="J35" s="1">
-        <v>17.625</v>
+        <v>17.25</v>
       </c>
       <c r="K35" s="1">
-        <v>264375</v>
+        <v>258750</v>
       </c>
       <c r="L35" s="1">
         <v>0</v>
@@ -2262,7 +2289,9 @@
       <c r="A36" s="2">
         <v>46230</v>
       </c>
-      <c r="B36" s="1"/>
+      <c r="B36" s="1">
+        <v>0</v>
+      </c>
       <c r="C36" s="1" t="s">
         <v>17</v>
       </c>
@@ -2278,13 +2307,13 @@
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J36" s="1">
-        <v>25</v>
+        <v>16.416665999999999</v>
       </c>
       <c r="K36" s="1">
-        <v>225000</v>
+        <v>147750</v>
       </c>
       <c r="L36" s="1">
         <v>0</v>
@@ -2305,7 +2334,9 @@
       <c r="A37" s="2">
         <v>46230</v>
       </c>
-      <c r="B37" s="1"/>
+      <c r="B37" s="1">
+        <v>0</v>
+      </c>
       <c r="C37" s="1" t="s">
         <v>17</v>
       </c>
@@ -2321,13 +2352,13 @@
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J37" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K37" s="1">
-        <v>375000</v>
+        <v>360000</v>
       </c>
       <c r="L37" s="1">
         <v>0</v>
@@ -2348,7 +2379,9 @@
       <c r="A38" s="2">
         <v>46230</v>
       </c>
-      <c r="B38" s="1"/>
+      <c r="B38" s="1">
+        <v>0</v>
+      </c>
       <c r="C38" s="1" t="s">
         <v>17</v>
       </c>
@@ -2364,13 +2397,13 @@
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="J38" s="1">
-        <v>65.5</v>
+        <v>25</v>
       </c>
       <c r="K38" s="1">
-        <v>753250</v>
+        <v>225000</v>
       </c>
       <c r="L38" s="1">
         <v>0</v>
@@ -2391,7 +2424,9 @@
       <c r="A39" s="2">
         <v>46230</v>
       </c>
-      <c r="B39" s="1"/>
+      <c r="B39" s="1">
+        <v>0</v>
+      </c>
       <c r="C39" s="1" t="s">
         <v>17</v>
       </c>
@@ -2407,13 +2442,13 @@
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J39" s="1">
-        <v>12</v>
+        <v>180</v>
       </c>
       <c r="K39" s="1">
-        <v>108000</v>
+        <v>1980000</v>
       </c>
       <c r="L39" s="1">
         <v>0</v>
@@ -4480,7 +4515,7 @@
       <c r="G82" s="1"/>
       <c r="H82" s="1"/>
       <c r="I82" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J82" s="1">
         <v>25</v>
@@ -4523,7 +4558,7 @@
       <c r="G83" s="1"/>
       <c r="H83" s="1"/>
       <c r="I83" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J83" s="1">
         <v>25</v>
@@ -7703,7 +7738,7 @@
       <c r="G149" s="1"/>
       <c r="H149" s="1"/>
       <c r="I149" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J149" s="1">
         <v>25</v>
@@ -7746,7 +7781,7 @@
       <c r="G150" s="1"/>
       <c r="H150" s="1"/>
       <c r="I150" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J150" s="1">
         <v>25</v>
@@ -9507,7 +9542,7 @@
       <c r="G187" s="1"/>
       <c r="H187" s="1"/>
       <c r="I187" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J187" s="1">
         <v>25</v>
@@ -9550,7 +9585,7 @@
       <c r="G188" s="1"/>
       <c r="H188" s="1"/>
       <c r="I188" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J188" s="1">
         <v>25</v>
@@ -11309,7 +11344,7 @@
       <c r="G225" s="1"/>
       <c r="H225" s="1"/>
       <c r="I225" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J225" s="1">
         <v>25</v>
@@ -11352,7 +11387,7 @@
       <c r="G226" s="1"/>
       <c r="H226" s="1"/>
       <c r="I226" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J226" s="1">
         <v>25</v>
@@ -11753,7 +11788,7 @@
       <c r="G235" s="1"/>
       <c r="H235" s="1"/>
       <c r="I235" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J235" s="1">
         <v>25</v>
@@ -11798,7 +11833,7 @@
       <c r="G236" s="1"/>
       <c r="H236" s="1"/>
       <c r="I236" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J236" s="1">
         <v>25</v>
@@ -16168,7 +16203,7 @@
       <c r="G326" s="1"/>
       <c r="H326" s="1"/>
       <c r="I326" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J326" s="1">
         <v>25</v>
@@ -16213,7 +16248,7 @@
       <c r="G327" s="1"/>
       <c r="H327" s="1"/>
       <c r="I327" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J327" s="1">
         <v>25</v>
@@ -17549,7 +17584,7 @@
       <c r="G355" s="1"/>
       <c r="H355" s="1"/>
       <c r="I355" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J355" s="1">
         <v>25</v>
@@ -17594,7 +17629,7 @@
       <c r="G356" s="1"/>
       <c r="H356" s="1"/>
       <c r="I356" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J356" s="1">
         <v>25</v>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{722FBA7C-26DB-40DC-9F48-6EB2E144D6FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09C33C4-AB8A-44D2-B858-0F372937FC75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09C33C4-AB8A-44D2-B858-0F372937FC75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC218B7E-6B45-4E17-B505-55226A38AC85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -666,7 +666,7 @@
         <v>18000</v>
       </c>
       <c r="L2" s="1">
-        <v>4500</v>
+        <v>10000</v>
       </c>
       <c r="M2" s="1">
         <v>0</v>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC218B7E-6B45-4E17-B505-55226A38AC85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C62AE9-E555-47A5-9239-688746F88DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2018,10 +2018,10 @@
         <v>24</v>
       </c>
       <c r="J30" s="1">
-        <v>70</v>
+        <v>69.7</v>
       </c>
       <c r="K30" s="1">
-        <v>420000</v>
+        <v>418200</v>
       </c>
       <c r="L30" s="1">
         <v>0</v>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C62AE9-E555-47A5-9239-688746F88DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F0592B-2DAF-4586-B394-8563D4781892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -712,7 +712,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="1">
-        <v>12000</v>
+        <v>10500</v>
       </c>
       <c r="L3" s="1">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>2</v>
       </c>
       <c r="K4" s="1">
-        <v>12000</v>
+        <v>10500</v>
       </c>
       <c r="L4" s="1">
         <v>0</v>
@@ -1398,7 +1398,7 @@
         <v>3</v>
       </c>
       <c r="K17" s="1">
-        <v>18000</v>
+        <v>15750</v>
       </c>
       <c r="L17" s="1">
         <v>0</v>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B73777F8-7FC5-4A3D-97F8-A96B1253A086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F856A35-E982-46E5-8512-87313FA2CCBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3111" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3113" uniqueCount="51">
   <si>
     <t>Date</t>
   </si>
@@ -1437,6 +1437,9 @@
         <v>20</v>
       </c>
       <c r="G18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>38</v>
       </c>
       <c r="I18" s="1" t="s">
@@ -1485,6 +1488,9 @@
         <v>20</v>
       </c>
       <c r="G19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>39</v>
       </c>
       <c r="I19" s="1" t="s">
@@ -1517,7 +1523,9 @@
       <c r="A20" s="2">
         <v>46232</v>
       </c>
-      <c r="B20" s="1"/>
+      <c r="B20" s="1">
+        <v>0</v>
+      </c>
       <c r="C20" s="1" t="s">
         <v>17</v>
       </c>
@@ -1536,10 +1544,10 @@
         <v>33</v>
       </c>
       <c r="J20" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K20" s="1">
-        <v>275000</v>
+        <v>264000</v>
       </c>
       <c r="L20" s="1">
         <v>0</v>
@@ -1560,7 +1568,9 @@
       <c r="A21" s="2">
         <v>46232</v>
       </c>
-      <c r="B21" s="1"/>
+      <c r="B21" s="1">
+        <v>0</v>
+      </c>
       <c r="C21" s="1" t="s">
         <v>17</v>
       </c>
@@ -1582,7 +1592,7 @@
         <v>1000</v>
       </c>
       <c r="K21" s="1">
-        <v>9000000</v>
+        <v>8500000</v>
       </c>
       <c r="L21" s="1">
         <v>0</v>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7096B4ED-C875-473D-B557-9A28CCAE3193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E228E7C-E3A3-4A7C-A4B1-0430A8036E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -661,7 +661,7 @@
         <v>646</v>
       </c>
       <c r="K2" s="1">
-        <v>5814000</v>
+        <v>5491000</v>
       </c>
       <c r="L2" s="1">
         <v>0</v>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -2317,7 +2317,7 @@
         <v>35.0</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>358750.0</v>
+        <v>393750.0</v>
       </c>
       <c r="L38" s="1" t="n">
         <v>0.0</v>
@@ -4460,7 +4460,7 @@
         <v>1.0</v>
       </c>
       <c r="K77" s="1" t="n">
-        <v>10250.0</v>
+        <v>11250.0</v>
       </c>
       <c r="L77" s="1" t="n">
         <v>0.0</v>
@@ -4915,7 +4915,7 @@
         <v>1.0</v>
       </c>
       <c r="K84" s="1" t="n">
-        <v>10250.0</v>
+        <v>11250.0</v>
       </c>
       <c r="L84" s="1" t="n">
         <v>0.0</v>
@@ -5870,7 +5870,7 @@
         <v>35.0</v>
       </c>
       <c r="K99" s="1" t="n">
-        <v>358750.0</v>
+        <v>393750.0</v>
       </c>
       <c r="L99" s="1" t="n">
         <v>0.0</v>
@@ -6241,7 +6241,7 @@
         <v>20.0</v>
       </c>
       <c r="K106" s="1" t="n">
-        <v>210000.0</v>
+        <v>180000.0</v>
       </c>
       <c r="L106" s="1" t="n">
         <v>0.0</v>
@@ -7068,7 +7068,7 @@
         <v>3.0</v>
       </c>
       <c r="K121" s="1" t="n">
-        <v>30750.0</v>
+        <v>33750.0</v>
       </c>
       <c r="L121" s="1" t="n">
         <v>0.0</v>
@@ -7198,7 +7198,7 @@
         <v>1.0</v>
       </c>
       <c r="K123" s="1" t="n">
-        <v>10250.0</v>
+        <v>11250.0</v>
       </c>
       <c r="L123" s="1" t="n">
         <v>0.0</v>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -73,7 +73,6 @@
     <col min="5" max="5" width="16.5234375" customWidth="true"/>
     <col min="6" max="6" width="13.828125" customWidth="true"/>
     <col min="7" max="7" width="20.43359375" customWidth="true"/>
-    <col min="8" max="8" width="8.69921875" customWidth="true"/>
     <col min="9" max="9" width="41.47265625" customWidth="true"/>
     <col min="10" max="10" width="12.73828125" customWidth="true"/>
     <col min="11" max="11" width="11.515625" customWidth="true"/>
@@ -4374,14 +4373,10 @@
       </c>
       <c r="G76" s="1" t="inlineStr">
         <is>
-          <t>Autre</t>
-        </is>
-      </c>
-      <c r="H76" s="1" t="inlineStr">
-        <is>
           <t>Nogaye</t>
         </is>
       </c>
+      <c r="H76" s="1"/>
       <c r="I76" s="1" t="inlineStr">
         <is>
           <t>Café pot Refraish 200g</t>
@@ -4443,14 +4438,10 @@
       </c>
       <c r="G77" s="1" t="inlineStr">
         <is>
-          <t>Autre</t>
-        </is>
-      </c>
-      <c r="H77" s="1" t="inlineStr">
-        <is>
           <t>Nogaye</t>
         </is>
       </c>
+      <c r="H77" s="1"/>
       <c r="I77" s="1" t="inlineStr">
         <is>
           <t>Café pot Refraish 50g</t>

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E409C362-0D77-42AD-AFDA-AAA931145716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C1CE70-A062-4888-9534-C439AED10E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -796,7 +796,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:Q663"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -871,7 +870,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>46248</v>
       </c>
@@ -914,7 +913,7 @@
       </c>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>46248</v>
       </c>
@@ -965,7 +964,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>46248</v>
       </c>
@@ -1016,7 +1015,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>46248</v>
       </c>
@@ -1067,7 +1066,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>46248</v>
       </c>
@@ -1118,7 +1117,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>46248</v>
       </c>
@@ -1169,7 +1168,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
         <v>46248</v>
       </c>
@@ -1220,7 +1219,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
         <v>46248</v>
       </c>
@@ -1271,7 +1270,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
         <v>46248</v>
       </c>
@@ -1322,7 +1321,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A11" s="2">
         <v>46248</v>
       </c>
@@ -1373,7 +1372,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A12" s="2">
         <v>46248</v>
       </c>
@@ -1424,7 +1423,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A13" s="2">
         <v>46248</v>
       </c>
@@ -1475,7 +1474,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A14" s="2">
         <v>46248</v>
       </c>
@@ -1526,7 +1525,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A15" s="2">
         <v>46247</v>
       </c>
@@ -1577,7 +1576,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A16" s="2">
         <v>46248</v>
       </c>
@@ -1626,7 +1625,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A17" s="2">
         <v>46248</v>
       </c>
@@ -1675,7 +1674,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A18" s="2">
         <v>46248</v>
       </c>
@@ -1724,7 +1723,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A19" s="2">
         <v>46248</v>
       </c>
@@ -1773,7 +1772,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A20" s="2">
         <v>46248</v>
       </c>
@@ -1822,7 +1821,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A21" s="2">
         <v>46248</v>
       </c>
@@ -1871,7 +1870,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A22" s="2">
         <v>46248</v>
       </c>
@@ -1920,7 +1919,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A23" s="2">
         <v>46248</v>
       </c>
@@ -1969,7 +1968,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A24" s="2">
         <v>46248</v>
       </c>
@@ -2018,7 +2017,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A25" s="2">
         <v>46248</v>
       </c>
@@ -2067,7 +2066,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A26" s="2">
         <v>46248</v>
       </c>
@@ -2116,7 +2115,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A27" s="2">
         <v>46248</v>
       </c>
@@ -2165,7 +2164,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A28" s="2">
         <v>46248</v>
       </c>
@@ -2214,7 +2213,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A29" s="2">
         <v>46248</v>
       </c>
@@ -2263,7 +2262,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A30" s="2">
         <v>46248</v>
       </c>
@@ -2312,7 +2311,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A31" s="2">
         <v>46248</v>
       </c>
@@ -2361,7 +2360,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A32" s="2">
         <v>46248</v>
       </c>
@@ -2410,7 +2409,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A33" s="2">
         <v>46248</v>
       </c>
@@ -2459,7 +2458,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A34" s="2">
         <v>46248</v>
       </c>
@@ -2508,7 +2507,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A35" s="2">
         <v>46248</v>
       </c>
@@ -2557,7 +2556,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A36" s="2">
         <v>46248</v>
       </c>
@@ -2606,7 +2605,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A37" s="2">
         <v>46248</v>
       </c>
@@ -2655,7 +2654,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A38" s="2">
         <v>46248</v>
       </c>
@@ -2704,7 +2703,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A39" s="2">
         <v>46248</v>
       </c>
@@ -2753,7 +2752,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A40" s="2">
         <v>46248</v>
       </c>
@@ -2802,7 +2801,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A41" s="2">
         <v>46248</v>
       </c>
@@ -2851,7 +2850,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A42" s="2">
         <v>46248</v>
       </c>
@@ -2900,7 +2899,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A43" s="2">
         <v>46248</v>
       </c>
@@ -2949,7 +2948,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A44" s="2">
         <v>46248</v>
       </c>
@@ -2998,7 +2997,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A45" s="2">
         <v>46248</v>
       </c>
@@ -3041,7 +3040,7 @@
       </c>
       <c r="Q45" s="1"/>
     </row>
-    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A46" s="2">
         <v>46248</v>
       </c>
@@ -3084,7 +3083,7 @@
       </c>
       <c r="Q46" s="1"/>
     </row>
-    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A47" s="2">
         <v>46248</v>
       </c>
@@ -3127,7 +3126,7 @@
       </c>
       <c r="Q47" s="1"/>
     </row>
-    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A48" s="2">
         <v>46248</v>
       </c>
@@ -3170,7 +3169,7 @@
       </c>
       <c r="Q48" s="1"/>
     </row>
-    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A49" s="2">
         <v>46248</v>
       </c>
@@ -3213,7 +3212,7 @@
       </c>
       <c r="Q49" s="1"/>
     </row>
-    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A50" s="2">
         <v>46248</v>
       </c>
@@ -3256,7 +3255,7 @@
       </c>
       <c r="Q50" s="1"/>
     </row>
-    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A51" s="2">
         <v>46248</v>
       </c>
@@ -3299,7 +3298,7 @@
       </c>
       <c r="Q51" s="1"/>
     </row>
-    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A52" s="2">
         <v>46248</v>
       </c>
@@ -3342,7 +3341,7 @@
       </c>
       <c r="Q52" s="1"/>
     </row>
-    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A53" s="2">
         <v>46248</v>
       </c>
@@ -3385,7 +3384,7 @@
       </c>
       <c r="Q53" s="1"/>
     </row>
-    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A54" s="2">
         <v>46248</v>
       </c>
@@ -3428,7 +3427,7 @@
       </c>
       <c r="Q54" s="1"/>
     </row>
-    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A55" s="2">
         <v>46248</v>
       </c>
@@ -3471,7 +3470,7 @@
       </c>
       <c r="Q55" s="1"/>
     </row>
-    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A56" s="2">
         <v>46248</v>
       </c>
@@ -3514,7 +3513,7 @@
       </c>
       <c r="Q56" s="1"/>
     </row>
-    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A57" s="2">
         <v>46248</v>
       </c>
@@ -3557,7 +3556,7 @@
       </c>
       <c r="Q57" s="1"/>
     </row>
-    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A58" s="2">
         <v>46248</v>
       </c>
@@ -3600,7 +3599,7 @@
       </c>
       <c r="Q58" s="1"/>
     </row>
-    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A59" s="2">
         <v>46248</v>
       </c>
@@ -3643,7 +3642,7 @@
       </c>
       <c r="Q59" s="1"/>
     </row>
-    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A60" s="2">
         <v>46248</v>
       </c>
@@ -3686,7 +3685,7 @@
       </c>
       <c r="Q60" s="1"/>
     </row>
-    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A61" s="2">
         <v>46248</v>
       </c>
@@ -3729,7 +3728,7 @@
       </c>
       <c r="Q61" s="1"/>
     </row>
-    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A62" s="2">
         <v>46248</v>
       </c>
@@ -3772,7 +3771,7 @@
       </c>
       <c r="Q62" s="1"/>
     </row>
-    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A63" s="2">
         <v>46248</v>
       </c>
@@ -3815,7 +3814,7 @@
       </c>
       <c r="Q63" s="1"/>
     </row>
-    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A64" s="2">
         <v>46248</v>
       </c>
@@ -3858,7 +3857,7 @@
       </c>
       <c r="Q64" s="1"/>
     </row>
-    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A65" s="2">
         <v>46248</v>
       </c>
@@ -3901,7 +3900,7 @@
       </c>
       <c r="Q65" s="1"/>
     </row>
-    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A66" s="2">
         <v>46248</v>
       </c>
@@ -3944,7 +3943,7 @@
       </c>
       <c r="Q66" s="1"/>
     </row>
-    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A67" s="2">
         <v>46248</v>
       </c>
@@ -3987,7 +3986,7 @@
       </c>
       <c r="Q67" s="1"/>
     </row>
-    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A68" s="2">
         <v>46248</v>
       </c>
@@ -4030,7 +4029,7 @@
       </c>
       <c r="Q68" s="1"/>
     </row>
-    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A69" s="2">
         <v>46248</v>
       </c>
@@ -4073,7 +4072,7 @@
       </c>
       <c r="Q69" s="1"/>
     </row>
-    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A70" s="2">
         <v>46248</v>
       </c>
@@ -4122,7 +4121,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A71" s="2">
         <v>46248</v>
       </c>
@@ -4171,7 +4170,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A72" s="2">
         <v>46248</v>
       </c>
@@ -4220,7 +4219,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A73" s="2">
         <v>46248</v>
       </c>
@@ -4269,7 +4268,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A74" s="2">
         <v>46248</v>
       </c>
@@ -4318,7 +4317,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A75" s="2">
         <v>46248</v>
       </c>
@@ -4367,7 +4366,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A76" s="2">
         <v>46248</v>
       </c>
@@ -4416,7 +4415,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A77" s="2">
         <v>46248</v>
       </c>
@@ -4465,7 +4464,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A78" s="2">
         <v>46248</v>
       </c>
@@ -4514,7 +4513,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A79" s="2">
         <v>46248</v>
       </c>
@@ -4563,7 +4562,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A80" s="2">
         <v>46248</v>
       </c>
@@ -4612,7 +4611,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A81" s="2">
         <v>46248</v>
       </c>
@@ -4661,7 +4660,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A82" s="2">
         <v>46248</v>
       </c>
@@ -4710,7 +4709,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A83" s="2">
         <v>46248</v>
       </c>
@@ -4759,7 +4758,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A84" s="2">
         <v>46248</v>
       </c>
@@ -4808,7 +4807,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A85" s="2">
         <v>46248</v>
       </c>
@@ -4857,7 +4856,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A86" s="2">
         <v>46248</v>
       </c>
@@ -4906,7 +4905,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A87" s="2">
         <v>46248</v>
       </c>
@@ -4955,7 +4954,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A88" s="2">
         <v>46248</v>
       </c>
@@ -5004,7 +5003,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A89" s="2">
         <v>46248</v>
       </c>
@@ -5053,7 +5052,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A90" s="2">
         <v>46248</v>
       </c>
@@ -5102,7 +5101,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A91" s="2">
         <v>46248</v>
       </c>
@@ -5151,7 +5150,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A92" s="2">
         <v>46248</v>
       </c>
@@ -5200,7 +5199,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A93" s="2">
         <v>46248</v>
       </c>
@@ -5249,7 +5248,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A94" s="2">
         <v>46248</v>
       </c>
@@ -5298,7 +5297,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A95" s="2">
         <v>46248</v>
       </c>
@@ -5347,7 +5346,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A96" s="2">
         <v>46248</v>
       </c>
@@ -5396,7 +5395,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A97" s="2">
         <v>46248</v>
       </c>
@@ -5445,7 +5444,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A98" s="2">
         <v>46248</v>
       </c>
@@ -5494,7 +5493,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A99" s="2">
         <v>46248</v>
       </c>
@@ -5543,7 +5542,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A100" s="2">
         <v>46248</v>
       </c>
@@ -5592,7 +5591,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A101" s="2">
         <v>46248</v>
       </c>
@@ -5641,7 +5640,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A102" s="2">
         <v>46248</v>
       </c>
@@ -5690,7 +5689,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A103" s="2">
         <v>46248</v>
       </c>
@@ -5739,7 +5738,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A104" s="2">
         <v>46248</v>
       </c>
@@ -5788,7 +5787,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A105" s="2">
         <v>46248</v>
       </c>
@@ -5837,7 +5836,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A106" s="2">
         <v>46248</v>
       </c>
@@ -5886,7 +5885,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A107" s="2">
         <v>46248</v>
       </c>
@@ -5935,7 +5934,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A108" s="2">
         <v>46248</v>
       </c>
@@ -5984,7 +5983,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A109" s="2">
         <v>46248</v>
       </c>
@@ -6033,7 +6032,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A110" s="2">
         <v>46248</v>
       </c>
@@ -6082,7 +6081,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A111" s="2">
         <v>46248</v>
       </c>
@@ -6131,7 +6130,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A112" s="2">
         <v>46248</v>
       </c>
@@ -6180,7 +6179,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A113" s="2">
         <v>46248</v>
       </c>
@@ -6229,7 +6228,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A114" s="2">
         <v>46248</v>
       </c>
@@ -6278,7 +6277,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A115" s="2">
         <v>46248</v>
       </c>
@@ -6327,7 +6326,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="116" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A116" s="2">
         <v>46248</v>
       </c>
@@ -6376,7 +6375,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A117" s="2">
         <v>46248</v>
       </c>
@@ -6425,7 +6424,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A118" s="2">
         <v>46248</v>
       </c>
@@ -6474,7 +6473,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A119" s="2">
         <v>46248</v>
       </c>
@@ -6523,7 +6522,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A120" s="2">
         <v>46248</v>
       </c>
@@ -6566,7 +6565,7 @@
       </c>
       <c r="Q120" s="1"/>
     </row>
-    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A121" s="2">
         <v>46248</v>
       </c>
@@ -6609,7 +6608,7 @@
       </c>
       <c r="Q121" s="1"/>
     </row>
-    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A122" s="2">
         <v>46248</v>
       </c>
@@ -6652,7 +6651,7 @@
       </c>
       <c r="Q122" s="1"/>
     </row>
-    <row r="123" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A123" s="2">
         <v>46248</v>
       </c>
@@ -6695,7 +6694,7 @@
       </c>
       <c r="Q123" s="1"/>
     </row>
-    <row r="124" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A124" s="2">
         <v>46248</v>
       </c>
@@ -6738,7 +6737,7 @@
       </c>
       <c r="Q124" s="1"/>
     </row>
-    <row r="125" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A125" s="2">
         <v>46248</v>
       </c>
@@ -6781,7 +6780,7 @@
       </c>
       <c r="Q125" s="1"/>
     </row>
-    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A126" s="2">
         <v>46248</v>
       </c>
@@ -6824,7 +6823,7 @@
       </c>
       <c r="Q126" s="1"/>
     </row>
-    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A127" s="2">
         <v>46248</v>
       </c>
@@ -6867,7 +6866,7 @@
       </c>
       <c r="Q127" s="1"/>
     </row>
-    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A128" s="2">
         <v>46248</v>
       </c>
@@ -6910,7 +6909,7 @@
       </c>
       <c r="Q128" s="1"/>
     </row>
-    <row r="129" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A129" s="2">
         <v>46248</v>
       </c>
@@ -6953,7 +6952,7 @@
       </c>
       <c r="Q129" s="1"/>
     </row>
-    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A130" s="2">
         <v>46248</v>
       </c>
@@ -6996,7 +6995,7 @@
       </c>
       <c r="Q130" s="1"/>
     </row>
-    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A131" s="2">
         <v>46248</v>
       </c>
@@ -7039,7 +7038,7 @@
       </c>
       <c r="Q131" s="1"/>
     </row>
-    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A132" s="2">
         <v>46248</v>
       </c>
@@ -7082,7 +7081,7 @@
       </c>
       <c r="Q132" s="1"/>
     </row>
-    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A133" s="2">
         <v>46248</v>
       </c>
@@ -7125,7 +7124,7 @@
       </c>
       <c r="Q133" s="1"/>
     </row>
-    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A134" s="2">
         <v>46248</v>
       </c>
@@ -7168,7 +7167,7 @@
       </c>
       <c r="Q134" s="1"/>
     </row>
-    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A135" s="2">
         <v>46248</v>
       </c>
@@ -7211,7 +7210,7 @@
       </c>
       <c r="Q135" s="1"/>
     </row>
-    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A136" s="2">
         <v>46248</v>
       </c>
@@ -7254,7 +7253,7 @@
       </c>
       <c r="Q136" s="1"/>
     </row>
-    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A137" s="2">
         <v>46248</v>
       </c>
@@ -7297,7 +7296,7 @@
       </c>
       <c r="Q137" s="1"/>
     </row>
-    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A138" s="2">
         <v>46248</v>
       </c>
@@ -7340,7 +7339,7 @@
       </c>
       <c r="Q138" s="1"/>
     </row>
-    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A139" s="2">
         <v>46248</v>
       </c>
@@ -7383,7 +7382,7 @@
       </c>
       <c r="Q139" s="1"/>
     </row>
-    <row r="140" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A140" s="2">
         <v>46247</v>
       </c>
@@ -7432,7 +7431,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A141" s="2">
         <v>46247</v>
       </c>
@@ -7481,7 +7480,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="142" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A142" s="2">
         <v>46247</v>
       </c>
@@ -7530,7 +7529,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A143" s="2">
         <v>46247</v>
       </c>
@@ -7579,7 +7578,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A144" s="2">
         <v>46247</v>
       </c>
@@ -7628,7 +7627,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A145" s="2">
         <v>46247</v>
       </c>
@@ -7677,7 +7676,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A146" s="2">
         <v>46247</v>
       </c>
@@ -7726,7 +7725,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A147" s="2">
         <v>46247</v>
       </c>
@@ -7775,7 +7774,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A148" s="2">
         <v>46247</v>
       </c>
@@ -7824,7 +7823,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="149" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A149" s="2">
         <v>46247</v>
       </c>
@@ -7873,7 +7872,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A150" s="2">
         <v>46247</v>
       </c>
@@ -7922,7 +7921,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A151" s="2">
         <v>46247</v>
       </c>
@@ -8069,7 +8068,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="154" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A154" s="2">
         <v>46247</v>
       </c>
@@ -8118,7 +8117,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A155" s="2">
         <v>46247</v>
       </c>
@@ -8167,7 +8166,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="156" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A156" s="2">
         <v>46247</v>
       </c>
@@ -8216,7 +8215,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="157" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A157" s="2">
         <v>46247</v>
       </c>
@@ -8265,7 +8264,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="158" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A158" s="2">
         <v>46247</v>
       </c>
@@ -8314,7 +8313,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="159" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A159" s="2">
         <v>46247</v>
       </c>
@@ -8363,7 +8362,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="160" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A160" s="2">
         <v>46247</v>
       </c>
@@ -8412,7 +8411,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="161" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A161" s="2">
         <v>46247</v>
       </c>
@@ -8461,7 +8460,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="162" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A162" s="2">
         <v>46247</v>
       </c>
@@ -8504,7 +8503,7 @@
       </c>
       <c r="Q162" s="1"/>
     </row>
-    <row r="163" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A163" s="2">
         <v>46247</v>
       </c>
@@ -8547,7 +8546,7 @@
       </c>
       <c r="Q163" s="1"/>
     </row>
-    <row r="164" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A164" s="2">
         <v>46247</v>
       </c>
@@ -8590,7 +8589,7 @@
       </c>
       <c r="Q164" s="1"/>
     </row>
-    <row r="165" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A165" s="2">
         <v>46247</v>
       </c>
@@ -8633,7 +8632,7 @@
       </c>
       <c r="Q165" s="1"/>
     </row>
-    <row r="166" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A166" s="2">
         <v>46247</v>
       </c>
@@ -8676,7 +8675,7 @@
       </c>
       <c r="Q166" s="1"/>
     </row>
-    <row r="167" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A167" s="2">
         <v>46247</v>
       </c>
@@ -8719,7 +8718,7 @@
       </c>
       <c r="Q167" s="1"/>
     </row>
-    <row r="168" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A168" s="2">
         <v>46247</v>
       </c>
@@ -8762,7 +8761,7 @@
       </c>
       <c r="Q168" s="1"/>
     </row>
-    <row r="169" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A169" s="2">
         <v>46247</v>
       </c>
@@ -8805,7 +8804,7 @@
       </c>
       <c r="Q169" s="1"/>
     </row>
-    <row r="170" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A170" s="2">
         <v>46247</v>
       </c>
@@ -8848,7 +8847,7 @@
       </c>
       <c r="Q170" s="1"/>
     </row>
-    <row r="171" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A171" s="2">
         <v>46247</v>
       </c>
@@ -8891,7 +8890,7 @@
       </c>
       <c r="Q171" s="1"/>
     </row>
-    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A172" s="2">
         <v>46247</v>
       </c>
@@ -8934,7 +8933,7 @@
       </c>
       <c r="Q172" s="1"/>
     </row>
-    <row r="173" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A173" s="2">
         <v>46247</v>
       </c>
@@ -8977,7 +8976,7 @@
       </c>
       <c r="Q173" s="1"/>
     </row>
-    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A174" s="2">
         <v>46247</v>
       </c>
@@ -9020,7 +9019,7 @@
       </c>
       <c r="Q174" s="1"/>
     </row>
-    <row r="175" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A175" s="2">
         <v>46247</v>
       </c>
@@ -9063,7 +9062,7 @@
       </c>
       <c r="Q175" s="1"/>
     </row>
-    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A176" s="2">
         <v>46247</v>
       </c>
@@ -9106,7 +9105,7 @@
       </c>
       <c r="Q176" s="1"/>
     </row>
-    <row r="177" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A177" s="2">
         <v>46247</v>
       </c>
@@ -9149,7 +9148,7 @@
       </c>
       <c r="Q177" s="1"/>
     </row>
-    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A178" s="2">
         <v>46247</v>
       </c>
@@ -9192,7 +9191,7 @@
       </c>
       <c r="Q178" s="1"/>
     </row>
-    <row r="179" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A179" s="2">
         <v>46247</v>
       </c>
@@ -9235,7 +9234,7 @@
       </c>
       <c r="Q179" s="1"/>
     </row>
-    <row r="180" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A180" s="2">
         <v>46247</v>
       </c>
@@ -9278,7 +9277,7 @@
       </c>
       <c r="Q180" s="1"/>
     </row>
-    <row r="181" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A181" s="2">
         <v>46247</v>
       </c>
@@ -9321,7 +9320,7 @@
       </c>
       <c r="Q181" s="1"/>
     </row>
-    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A182" s="2">
         <v>46247</v>
       </c>
@@ -9364,7 +9363,7 @@
       </c>
       <c r="Q182" s="1"/>
     </row>
-    <row r="183" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A183" s="2">
         <v>46247</v>
       </c>
@@ -9407,7 +9406,7 @@
       </c>
       <c r="Q183" s="1"/>
     </row>
-    <row r="184" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A184" s="2">
         <v>46247</v>
       </c>
@@ -9450,7 +9449,7 @@
       </c>
       <c r="Q184" s="1"/>
     </row>
-    <row r="185" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A185" s="2">
         <v>46247</v>
       </c>
@@ -9493,7 +9492,7 @@
       </c>
       <c r="Q185" s="1"/>
     </row>
-    <row r="186" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A186" s="2">
         <v>46247</v>
       </c>
@@ -9536,7 +9535,7 @@
       </c>
       <c r="Q186" s="1"/>
     </row>
-    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A187" s="2">
         <v>46247</v>
       </c>
@@ -9579,7 +9578,7 @@
       </c>
       <c r="Q187" s="1"/>
     </row>
-    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A188" s="2">
         <v>46247</v>
       </c>
@@ -9622,7 +9621,7 @@
       </c>
       <c r="Q188" s="1"/>
     </row>
-    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A189" s="2">
         <v>46247</v>
       </c>
@@ -9655,7 +9654,7 @@
         <v>31111.111000000001</v>
       </c>
       <c r="L189" s="1">
-        <v>2000</v>
+        <v>55000</v>
       </c>
       <c r="M189" s="1">
         <v>0</v>
@@ -9671,7 +9670,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A190" s="2">
         <v>46247</v>
       </c>
@@ -9720,7 +9719,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A191" s="2">
         <v>46247</v>
       </c>
@@ -9769,7 +9768,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A192" s="2">
         <v>46247</v>
       </c>
@@ -9818,7 +9817,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A193" s="2">
         <v>46247</v>
       </c>
@@ -9867,7 +9866,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A194" s="2">
         <v>46247</v>
       </c>
@@ -9916,7 +9915,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A195" s="2">
         <v>46247</v>
       </c>
@@ -9965,7 +9964,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A196" s="2">
         <v>46247</v>
       </c>
@@ -10014,7 +10013,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A197" s="2">
         <v>46247</v>
       </c>
@@ -10063,7 +10062,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A198" s="2">
         <v>46247</v>
       </c>
@@ -10112,7 +10111,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="199" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A199" s="2">
         <v>46247</v>
       </c>
@@ -10161,7 +10160,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="200" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A200" s="2">
         <v>46247</v>
       </c>
@@ -10210,7 +10209,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="201" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A201" s="2">
         <v>46247</v>
       </c>
@@ -10259,7 +10258,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="202" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A202" s="2">
         <v>46247</v>
       </c>
@@ -10308,7 +10307,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="203" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A203" s="2">
         <v>46247</v>
       </c>
@@ -10357,7 +10356,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="204" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A204" s="2">
         <v>46247</v>
       </c>
@@ -10406,7 +10405,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="205" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A205" s="2">
         <v>46247</v>
       </c>
@@ -10455,7 +10454,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="206" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A206" s="2">
         <v>46247</v>
       </c>
@@ -10504,7 +10503,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="207" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A207" s="2">
         <v>46247</v>
       </c>
@@ -10553,7 +10552,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="208" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A208" s="2">
         <v>46247</v>
       </c>
@@ -10602,7 +10601,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="209" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A209" s="2">
         <v>46247</v>
       </c>
@@ -10651,7 +10650,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="210" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A210" s="2">
         <v>46247</v>
       </c>
@@ -10700,7 +10699,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="211" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A211" s="2">
         <v>46247</v>
       </c>
@@ -10749,7 +10748,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="212" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A212" s="2">
         <v>46247</v>
       </c>
@@ -10798,7 +10797,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="213" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A213" s="2">
         <v>46247</v>
       </c>
@@ -10847,7 +10846,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="214" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A214" s="2">
         <v>46247</v>
       </c>
@@ -10896,7 +10895,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="215" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A215" s="2">
         <v>46247</v>
       </c>
@@ -10945,7 +10944,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="216" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A216" s="2">
         <v>46247</v>
       </c>
@@ -10994,7 +10993,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="217" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A217" s="2">
         <v>46247</v>
       </c>
@@ -11043,7 +11042,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="218" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A218" s="2">
         <v>46247</v>
       </c>
@@ -11092,7 +11091,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="219" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A219" s="2">
         <v>46247</v>
       </c>
@@ -11141,7 +11140,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="220" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A220" s="2">
         <v>46247</v>
       </c>
@@ -11190,7 +11189,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="221" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A221" s="2">
         <v>46247</v>
       </c>
@@ -11239,7 +11238,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="222" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A222" s="2">
         <v>46247</v>
       </c>
@@ -11288,7 +11287,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="223" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A223" s="2">
         <v>46247</v>
       </c>
@@ -11337,7 +11336,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="224" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A224" s="2">
         <v>46247</v>
       </c>
@@ -11386,7 +11385,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="225" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A225" s="2">
         <v>46247</v>
       </c>
@@ -11435,7 +11434,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="226" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A226" s="2">
         <v>46247</v>
       </c>
@@ -11484,7 +11483,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="227" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A227" s="2">
         <v>46247</v>
       </c>
@@ -11533,7 +11532,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="228" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A228" s="2">
         <v>46247</v>
       </c>
@@ -11582,7 +11581,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="229" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A229" s="2">
         <v>46247</v>
       </c>
@@ -11631,7 +11630,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="230" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A230" s="2">
         <v>46247</v>
       </c>
@@ -11680,7 +11679,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="231" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A231" s="2">
         <v>46247</v>
       </c>
@@ -11729,7 +11728,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="232" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A232" s="2">
         <v>46247</v>
       </c>
@@ -11778,7 +11777,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="233" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A233" s="2">
         <v>46247</v>
       </c>
@@ -11821,7 +11820,7 @@
       </c>
       <c r="Q233" s="1"/>
     </row>
-    <row r="234" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A234" s="2">
         <v>46247</v>
       </c>
@@ -11864,7 +11863,7 @@
       </c>
       <c r="Q234" s="1"/>
     </row>
-    <row r="235" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A235" s="2">
         <v>46247</v>
       </c>
@@ -11907,7 +11906,7 @@
       </c>
       <c r="Q235" s="1"/>
     </row>
-    <row r="236" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A236" s="2">
         <v>46247</v>
       </c>
@@ -11950,7 +11949,7 @@
       </c>
       <c r="Q236" s="1"/>
     </row>
-    <row r="237" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A237" s="2">
         <v>46247</v>
       </c>
@@ -11993,7 +11992,7 @@
       </c>
       <c r="Q237" s="1"/>
     </row>
-    <row r="238" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A238" s="2">
         <v>46247</v>
       </c>
@@ -12036,7 +12035,7 @@
       </c>
       <c r="Q238" s="1"/>
     </row>
-    <row r="239" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A239" s="2">
         <v>46247</v>
       </c>
@@ -12079,7 +12078,7 @@
       </c>
       <c r="Q239" s="1"/>
     </row>
-    <row r="240" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A240" s="2">
         <v>46247</v>
       </c>
@@ -12122,7 +12121,7 @@
       </c>
       <c r="Q240" s="1"/>
     </row>
-    <row r="241" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A241" s="2">
         <v>46247</v>
       </c>
@@ -12165,7 +12164,7 @@
       </c>
       <c r="Q241" s="1"/>
     </row>
-    <row r="242" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A242" s="2">
         <v>46247</v>
       </c>
@@ -12208,7 +12207,7 @@
       </c>
       <c r="Q242" s="1"/>
     </row>
-    <row r="243" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A243" s="2">
         <v>46247</v>
       </c>
@@ -12251,7 +12250,7 @@
       </c>
       <c r="Q243" s="1"/>
     </row>
-    <row r="244" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A244" s="2">
         <v>46247</v>
       </c>
@@ -12294,7 +12293,7 @@
       </c>
       <c r="Q244" s="1"/>
     </row>
-    <row r="245" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A245" s="2">
         <v>46247</v>
       </c>
@@ -12337,7 +12336,7 @@
       </c>
       <c r="Q245" s="1"/>
     </row>
-    <row r="246" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A246" s="2">
         <v>46247</v>
       </c>
@@ -12380,7 +12379,7 @@
       </c>
       <c r="Q246" s="1"/>
     </row>
-    <row r="247" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A247" s="2">
         <v>46247</v>
       </c>
@@ -12423,7 +12422,7 @@
       </c>
       <c r="Q247" s="1"/>
     </row>
-    <row r="248" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A248" s="2">
         <v>46247</v>
       </c>
@@ -12466,7 +12465,7 @@
       </c>
       <c r="Q248" s="1"/>
     </row>
-    <row r="249" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A249" s="2">
         <v>46247</v>
       </c>
@@ -12509,7 +12508,7 @@
       </c>
       <c r="Q249" s="1"/>
     </row>
-    <row r="250" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A250" s="2">
         <v>46247</v>
       </c>
@@ -12552,7 +12551,7 @@
       </c>
       <c r="Q250" s="1"/>
     </row>
-    <row r="251" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A251" s="2">
         <v>46247</v>
       </c>
@@ -12595,7 +12594,7 @@
       </c>
       <c r="Q251" s="1"/>
     </row>
-    <row r="252" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A252" s="2">
         <v>46247</v>
       </c>
@@ -12638,7 +12637,7 @@
       </c>
       <c r="Q252" s="1"/>
     </row>
-    <row r="253" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A253" s="2">
         <v>46246</v>
       </c>
@@ -12687,7 +12686,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="254" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A254" s="2">
         <v>46246</v>
       </c>
@@ -12736,7 +12735,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="255" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A255" s="2">
         <v>46246</v>
       </c>
@@ -12785,7 +12784,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="256" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A256" s="2">
         <v>46246</v>
       </c>
@@ -12834,7 +12833,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="257" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A257" s="2">
         <v>46246</v>
       </c>
@@ -12883,7 +12882,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="258" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A258" s="2">
         <v>46246</v>
       </c>
@@ -12932,7 +12931,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="259" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A259" s="2">
         <v>46246</v>
       </c>
@@ -12981,7 +12980,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="260" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A260" s="2">
         <v>46246</v>
       </c>
@@ -13030,7 +13029,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="261" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A261" s="2">
         <v>46246</v>
       </c>
@@ -13079,7 +13078,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="262" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A262" s="2">
         <v>46246</v>
       </c>
@@ -13128,7 +13127,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="263" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A263" s="2">
         <v>46246</v>
       </c>
@@ -13177,7 +13176,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="264" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A264" s="2">
         <v>46246</v>
       </c>
@@ -13226,7 +13225,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="265" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A265" s="2">
         <v>46246</v>
       </c>
@@ -13275,7 +13274,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="266" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A266" s="2">
         <v>46246</v>
       </c>
@@ -13324,7 +13323,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="267" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A267" s="2">
         <v>46246</v>
       </c>
@@ -13373,7 +13372,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="268" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A268" s="2">
         <v>46246</v>
       </c>
@@ -13422,7 +13421,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="269" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A269" s="2">
         <v>46246</v>
       </c>
@@ -13471,7 +13470,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="270" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A270" s="2">
         <v>46246</v>
       </c>
@@ -13520,7 +13519,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="271" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A271" s="2">
         <v>46246</v>
       </c>
@@ -13569,7 +13568,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="272" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A272" s="2">
         <v>46246</v>
       </c>
@@ -13618,7 +13617,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="273" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A273" s="2">
         <v>46246</v>
       </c>
@@ -13667,7 +13666,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="274" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A274" s="2">
         <v>46246</v>
       </c>
@@ -13716,7 +13715,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="275" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A275" s="2">
         <v>46246</v>
       </c>
@@ -13765,7 +13764,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="276" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A276" s="2">
         <v>46246</v>
       </c>
@@ -13814,7 +13813,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="277" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A277" s="2">
         <v>46246</v>
       </c>
@@ -13863,7 +13862,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="278" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A278" s="2">
         <v>46246</v>
       </c>
@@ -13912,7 +13911,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="279" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A279" s="2">
         <v>46246</v>
       </c>
@@ -13961,7 +13960,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="280" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A280" s="2">
         <v>46246</v>
       </c>
@@ -14157,7 +14156,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="284" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A284" s="2">
         <v>46246</v>
       </c>
@@ -14200,7 +14199,7 @@
       </c>
       <c r="Q284" s="1"/>
     </row>
-    <row r="285" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A285" s="2">
         <v>46246</v>
       </c>
@@ -14243,7 +14242,7 @@
       </c>
       <c r="Q285" s="1"/>
     </row>
-    <row r="286" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A286" s="2">
         <v>46246</v>
       </c>
@@ -14286,7 +14285,7 @@
       </c>
       <c r="Q286" s="1"/>
     </row>
-    <row r="287" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A287" s="2">
         <v>46246</v>
       </c>
@@ -14329,7 +14328,7 @@
       </c>
       <c r="Q287" s="1"/>
     </row>
-    <row r="288" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A288" s="2">
         <v>46246</v>
       </c>
@@ -14372,7 +14371,7 @@
       </c>
       <c r="Q288" s="1"/>
     </row>
-    <row r="289" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A289" s="2">
         <v>46246</v>
       </c>
@@ -14415,7 +14414,7 @@
       </c>
       <c r="Q289" s="1"/>
     </row>
-    <row r="290" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A290" s="2">
         <v>46246</v>
       </c>
@@ -14458,7 +14457,7 @@
       </c>
       <c r="Q290" s="1"/>
     </row>
-    <row r="291" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A291" s="2">
         <v>46246</v>
       </c>
@@ -14501,7 +14500,7 @@
       </c>
       <c r="Q291" s="1"/>
     </row>
-    <row r="292" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A292" s="2">
         <v>46246</v>
       </c>
@@ -14544,7 +14543,7 @@
       </c>
       <c r="Q292" s="1"/>
     </row>
-    <row r="293" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A293" s="2">
         <v>46246</v>
       </c>
@@ -14587,7 +14586,7 @@
       </c>
       <c r="Q293" s="1"/>
     </row>
-    <row r="294" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A294" s="2">
         <v>46246</v>
       </c>
@@ -14630,7 +14629,7 @@
       </c>
       <c r="Q294" s="1"/>
     </row>
-    <row r="295" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A295" s="2">
         <v>46246</v>
       </c>
@@ -14673,7 +14672,7 @@
       </c>
       <c r="Q295" s="1"/>
     </row>
-    <row r="296" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A296" s="2">
         <v>46246</v>
       </c>
@@ -14716,7 +14715,7 @@
       </c>
       <c r="Q296" s="1"/>
     </row>
-    <row r="297" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A297" s="2">
         <v>46246</v>
       </c>
@@ -14759,7 +14758,7 @@
       </c>
       <c r="Q297" s="1"/>
     </row>
-    <row r="298" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A298" s="2">
         <v>46246</v>
       </c>
@@ -14802,7 +14801,7 @@
       </c>
       <c r="Q298" s="1"/>
     </row>
-    <row r="299" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A299" s="2">
         <v>46246</v>
       </c>
@@ -14845,7 +14844,7 @@
       </c>
       <c r="Q299" s="1"/>
     </row>
-    <row r="300" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A300" s="2">
         <v>46246</v>
       </c>
@@ -14888,7 +14887,7 @@
       </c>
       <c r="Q300" s="1"/>
     </row>
-    <row r="301" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A301" s="2">
         <v>46246</v>
       </c>
@@ -14931,7 +14930,7 @@
       </c>
       <c r="Q301" s="1"/>
     </row>
-    <row r="302" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A302" s="2">
         <v>46246</v>
       </c>
@@ -14974,7 +14973,7 @@
       </c>
       <c r="Q302" s="1"/>
     </row>
-    <row r="303" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A303" s="2">
         <v>46246</v>
       </c>
@@ -15017,7 +15016,7 @@
       </c>
       <c r="Q303" s="1"/>
     </row>
-    <row r="304" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A304" s="2">
         <v>46246</v>
       </c>
@@ -15060,7 +15059,7 @@
       </c>
       <c r="Q304" s="1"/>
     </row>
-    <row r="305" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A305" s="2">
         <v>46246</v>
       </c>
@@ -15103,7 +15102,7 @@
       </c>
       <c r="Q305" s="1"/>
     </row>
-    <row r="306" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A306" s="2">
         <v>46246</v>
       </c>
@@ -15146,7 +15145,7 @@
       </c>
       <c r="Q306" s="1"/>
     </row>
-    <row r="307" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A307" s="2">
         <v>46246</v>
       </c>
@@ -15189,7 +15188,7 @@
       </c>
       <c r="Q307" s="1"/>
     </row>
-    <row r="308" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A308" s="2">
         <v>46246</v>
       </c>
@@ -15232,7 +15231,7 @@
       </c>
       <c r="Q308" s="1"/>
     </row>
-    <row r="309" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A309" s="2">
         <v>46246</v>
       </c>
@@ -15275,7 +15274,7 @@
       </c>
       <c r="Q309" s="1"/>
     </row>
-    <row r="310" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A310" s="2">
         <v>46246</v>
       </c>
@@ -15318,7 +15317,7 @@
       </c>
       <c r="Q310" s="1"/>
     </row>
-    <row r="311" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A311" s="2">
         <v>46246</v>
       </c>
@@ -15367,7 +15366,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="312" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A312" s="2">
         <v>46246</v>
       </c>
@@ -15416,7 +15415,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="313" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A313" s="2">
         <v>46246</v>
       </c>
@@ -15465,7 +15464,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="314" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A314" s="2">
         <v>46246</v>
       </c>
@@ -15514,7 +15513,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="315" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A315" s="2">
         <v>46246</v>
       </c>
@@ -15563,7 +15562,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="316" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A316" s="2">
         <v>46246</v>
       </c>
@@ -15612,7 +15611,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="317" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A317" s="2">
         <v>46246</v>
       </c>
@@ -15661,7 +15660,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="318" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A318" s="2">
         <v>46246</v>
       </c>
@@ -15710,7 +15709,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="319" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A319" s="2">
         <v>46246</v>
       </c>
@@ -15759,7 +15758,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="320" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A320" s="2">
         <v>46246</v>
       </c>
@@ -15808,7 +15807,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="321" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A321" s="2">
         <v>46246</v>
       </c>
@@ -15857,7 +15856,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="322" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A322" s="2">
         <v>46246</v>
       </c>
@@ -15906,7 +15905,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="323" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A323" s="2">
         <v>46246</v>
       </c>
@@ -15955,7 +15954,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="324" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A324" s="2">
         <v>46246</v>
       </c>
@@ -16004,7 +16003,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="325" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A325" s="2">
         <v>46246</v>
       </c>
@@ -16053,7 +16052,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="326" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A326" s="2">
         <v>46246</v>
       </c>
@@ -16102,7 +16101,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="327" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A327" s="2">
         <v>46246</v>
       </c>
@@ -16151,7 +16150,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="328" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A328" s="2">
         <v>46246</v>
       </c>
@@ -16200,7 +16199,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="329" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A329" s="2">
         <v>46246</v>
       </c>
@@ -16249,7 +16248,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="330" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A330" s="2">
         <v>46246</v>
       </c>
@@ -16298,7 +16297,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="331" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A331" s="2">
         <v>46246</v>
       </c>
@@ -16347,7 +16346,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="332" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A332" s="2">
         <v>46246</v>
       </c>
@@ -16396,7 +16395,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="333" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A333" s="2">
         <v>46246</v>
       </c>
@@ -16445,7 +16444,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="334" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A334" s="2">
         <v>46246</v>
       </c>
@@ -16494,7 +16493,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="335" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A335" s="2">
         <v>46246</v>
       </c>
@@ -16543,7 +16542,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="336" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A336" s="2">
         <v>46246</v>
       </c>
@@ -16592,7 +16591,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="337" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A337" s="2">
         <v>46246</v>
       </c>
@@ -16641,7 +16640,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="338" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A338" s="2">
         <v>46246</v>
       </c>
@@ -16690,7 +16689,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="339" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A339" s="2">
         <v>46246</v>
       </c>
@@ -16739,7 +16738,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="340" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A340" s="2">
         <v>46246</v>
       </c>
@@ -16788,7 +16787,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="341" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A341" s="2">
         <v>46246</v>
       </c>
@@ -16837,7 +16836,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="342" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A342" s="2">
         <v>46246</v>
       </c>
@@ -16886,7 +16885,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="343" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A343" s="2">
         <v>46246</v>
       </c>
@@ -16935,7 +16934,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="344" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A344" s="2">
         <v>46246</v>
       </c>
@@ -16984,7 +16983,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="345" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A345" s="2">
         <v>46246</v>
       </c>
@@ -17033,7 +17032,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="346" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A346" s="2">
         <v>46246</v>
       </c>
@@ -17082,7 +17081,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="347" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A347" s="2">
         <v>46246</v>
       </c>
@@ -17131,7 +17130,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="348" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A348" s="2">
         <v>46246</v>
       </c>
@@ -17180,7 +17179,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="349" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A349" s="2">
         <v>46246</v>
       </c>
@@ -17229,7 +17228,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="350" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A350" s="2">
         <v>46246</v>
       </c>
@@ -17278,7 +17277,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="351" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A351" s="2">
         <v>46246</v>
       </c>
@@ -17327,7 +17326,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="352" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A352" s="2">
         <v>46246</v>
       </c>
@@ -17376,7 +17375,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="353" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A353" s="2">
         <v>46246</v>
       </c>
@@ -17425,7 +17424,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="354" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A354" s="2">
         <v>46246</v>
       </c>
@@ -17474,7 +17473,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="355" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A355" s="2">
         <v>46246</v>
       </c>
@@ -17523,7 +17522,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="356" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A356" s="2">
         <v>46246</v>
       </c>
@@ -17572,7 +17571,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="357" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A357" s="2">
         <v>46246</v>
       </c>
@@ -17621,7 +17620,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="358" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A358" s="2">
         <v>46246</v>
       </c>
@@ -17670,7 +17669,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="359" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A359" s="2">
         <v>46246</v>
       </c>
@@ -17719,7 +17718,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="360" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A360" s="2">
         <v>46246</v>
       </c>
@@ -17768,7 +17767,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="361" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A361" s="2">
         <v>46246</v>
       </c>
@@ -17817,7 +17816,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="362" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A362" s="2">
         <v>46246</v>
       </c>
@@ -17866,7 +17865,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="363" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A363" s="2">
         <v>46246</v>
       </c>
@@ -17915,7 +17914,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="364" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A364" s="2">
         <v>46246</v>
       </c>
@@ -17958,7 +17957,7 @@
       </c>
       <c r="Q364" s="1"/>
     </row>
-    <row r="365" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A365" s="2">
         <v>46246</v>
       </c>
@@ -18001,7 +18000,7 @@
       </c>
       <c r="Q365" s="1"/>
     </row>
-    <row r="366" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A366" s="2">
         <v>46246</v>
       </c>
@@ -18044,7 +18043,7 @@
       </c>
       <c r="Q366" s="1"/>
     </row>
-    <row r="367" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A367" s="2">
         <v>46246</v>
       </c>
@@ -18087,7 +18086,7 @@
       </c>
       <c r="Q367" s="1"/>
     </row>
-    <row r="368" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A368" s="2">
         <v>46246</v>
       </c>
@@ -18130,7 +18129,7 @@
       </c>
       <c r="Q368" s="1"/>
     </row>
-    <row r="369" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A369" s="2">
         <v>46246</v>
       </c>
@@ -18173,7 +18172,7 @@
       </c>
       <c r="Q369" s="1"/>
     </row>
-    <row r="370" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A370" s="2">
         <v>46246</v>
       </c>
@@ -18216,7 +18215,7 @@
       </c>
       <c r="Q370" s="1"/>
     </row>
-    <row r="371" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A371" s="2">
         <v>46246</v>
       </c>
@@ -18259,7 +18258,7 @@
       </c>
       <c r="Q371" s="1"/>
     </row>
-    <row r="372" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A372" s="2">
         <v>46246</v>
       </c>
@@ -18302,7 +18301,7 @@
       </c>
       <c r="Q372" s="1"/>
     </row>
-    <row r="373" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A373" s="2">
         <v>46246</v>
       </c>
@@ -18345,7 +18344,7 @@
       </c>
       <c r="Q373" s="1"/>
     </row>
-    <row r="374" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A374" s="2">
         <v>46246</v>
       </c>
@@ -18388,7 +18387,7 @@
       </c>
       <c r="Q374" s="1"/>
     </row>
-    <row r="375" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A375" s="2">
         <v>46246</v>
       </c>
@@ -18431,7 +18430,7 @@
       </c>
       <c r="Q375" s="1"/>
     </row>
-    <row r="376" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A376" s="2">
         <v>46246</v>
       </c>
@@ -18474,7 +18473,7 @@
       </c>
       <c r="Q376" s="1"/>
     </row>
-    <row r="377" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A377" s="2">
         <v>46246</v>
       </c>
@@ -18517,7 +18516,7 @@
       </c>
       <c r="Q377" s="1"/>
     </row>
-    <row r="378" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A378" s="2">
         <v>46246</v>
       </c>
@@ -18560,7 +18559,7 @@
       </c>
       <c r="Q378" s="1"/>
     </row>
-    <row r="379" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A379" s="2">
         <v>46246</v>
       </c>
@@ -18603,7 +18602,7 @@
       </c>
       <c r="Q379" s="1"/>
     </row>
-    <row r="380" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A380" s="2">
         <v>46246</v>
       </c>
@@ -18646,7 +18645,7 @@
       </c>
       <c r="Q380" s="1"/>
     </row>
-    <row r="381" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A381" s="2">
         <v>46246</v>
       </c>
@@ -18689,7 +18688,7 @@
       </c>
       <c r="Q381" s="1"/>
     </row>
-    <row r="382" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A382" s="2">
         <v>46246</v>
       </c>
@@ -18732,7 +18731,7 @@
       </c>
       <c r="Q382" s="1"/>
     </row>
-    <row r="383" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A383" s="2">
         <v>46246</v>
       </c>
@@ -18775,7 +18774,7 @@
       </c>
       <c r="Q383" s="1"/>
     </row>
-    <row r="384" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A384" s="2">
         <v>46245</v>
       </c>
@@ -18824,7 +18823,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="385" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A385" s="2">
         <v>46245</v>
       </c>
@@ -18873,7 +18872,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="386" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A386" s="2">
         <v>46245</v>
       </c>
@@ -18922,7 +18921,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="387" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="387" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A387" s="2">
         <v>46245</v>
       </c>
@@ -18971,7 +18970,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="388" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A388" s="2">
         <v>46245</v>
       </c>
@@ -19020,7 +19019,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="389" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="389" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A389" s="2">
         <v>46245</v>
       </c>
@@ -19069,7 +19068,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="390" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="390" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A390" s="2">
         <v>46245</v>
       </c>
@@ -19118,7 +19117,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="391" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A391" s="2">
         <v>46245</v>
       </c>
@@ -19167,7 +19166,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="392" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A392" s="2">
         <v>46245</v>
       </c>
@@ -19216,7 +19215,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="393" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A393" s="2">
         <v>46245</v>
       </c>
@@ -19265,7 +19264,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="394" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A394" s="2">
         <v>46245</v>
       </c>
@@ -19314,7 +19313,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="395" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A395" s="2">
         <v>46245</v>
       </c>
@@ -19363,7 +19362,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="396" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A396" s="2">
         <v>46245</v>
       </c>
@@ -19412,7 +19411,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="397" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A397" s="2">
         <v>46245</v>
       </c>
@@ -19461,7 +19460,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="398" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A398" s="2">
         <v>46245</v>
       </c>
@@ -19510,7 +19509,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="399" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A399" s="2">
         <v>46245</v>
       </c>
@@ -19559,7 +19558,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="400" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A400" s="2">
         <v>46245</v>
       </c>
@@ -19602,7 +19601,7 @@
       </c>
       <c r="Q400" s="1"/>
     </row>
-    <row r="401" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A401" s="2">
         <v>46245</v>
       </c>
@@ -19645,7 +19644,7 @@
       </c>
       <c r="Q401" s="1"/>
     </row>
-    <row r="402" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A402" s="2">
         <v>46245</v>
       </c>
@@ -19688,7 +19687,7 @@
       </c>
       <c r="Q402" s="1"/>
     </row>
-    <row r="403" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A403" s="2">
         <v>46245</v>
       </c>
@@ -19731,7 +19730,7 @@
       </c>
       <c r="Q403" s="1"/>
     </row>
-    <row r="404" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A404" s="2">
         <v>46245</v>
       </c>
@@ -19774,7 +19773,7 @@
       </c>
       <c r="Q404" s="1"/>
     </row>
-    <row r="405" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A405" s="2">
         <v>46245</v>
       </c>
@@ -19817,7 +19816,7 @@
       </c>
       <c r="Q405" s="1"/>
     </row>
-    <row r="406" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A406" s="2">
         <v>46245</v>
       </c>
@@ -19860,7 +19859,7 @@
       </c>
       <c r="Q406" s="1"/>
     </row>
-    <row r="407" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A407" s="2">
         <v>46245</v>
       </c>
@@ -19903,7 +19902,7 @@
       </c>
       <c r="Q407" s="1"/>
     </row>
-    <row r="408" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A408" s="2">
         <v>46245</v>
       </c>
@@ -19946,7 +19945,7 @@
       </c>
       <c r="Q408" s="1"/>
     </row>
-    <row r="409" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A409" s="2">
         <v>46245</v>
       </c>
@@ -19989,7 +19988,7 @@
       </c>
       <c r="Q409" s="1"/>
     </row>
-    <row r="410" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A410" s="2">
         <v>46245</v>
       </c>
@@ -20032,7 +20031,7 @@
       </c>
       <c r="Q410" s="1"/>
     </row>
-    <row r="411" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A411" s="2">
         <v>46245</v>
       </c>
@@ -20075,7 +20074,7 @@
       </c>
       <c r="Q411" s="1"/>
     </row>
-    <row r="412" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A412" s="2">
         <v>46245</v>
       </c>
@@ -20118,7 +20117,7 @@
       </c>
       <c r="Q412" s="1"/>
     </row>
-    <row r="413" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="413" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A413" s="2">
         <v>46245</v>
       </c>
@@ -20161,7 +20160,7 @@
       </c>
       <c r="Q413" s="1"/>
     </row>
-    <row r="414" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A414" s="2">
         <v>46245</v>
       </c>
@@ -20204,7 +20203,7 @@
       </c>
       <c r="Q414" s="1"/>
     </row>
-    <row r="415" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="415" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A415" s="2">
         <v>46245</v>
       </c>
@@ -20247,7 +20246,7 @@
       </c>
       <c r="Q415" s="1"/>
     </row>
-    <row r="416" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A416" s="2">
         <v>46245</v>
       </c>
@@ -20290,7 +20289,7 @@
       </c>
       <c r="Q416" s="1"/>
     </row>
-    <row r="417" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A417" s="2">
         <v>46245</v>
       </c>
@@ -20333,7 +20332,7 @@
       </c>
       <c r="Q417" s="1"/>
     </row>
-    <row r="418" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="418" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A418" s="2">
         <v>46245</v>
       </c>
@@ -20376,7 +20375,7 @@
       </c>
       <c r="Q418" s="1"/>
     </row>
-    <row r="419" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A419" s="2">
         <v>46245</v>
       </c>
@@ -20419,7 +20418,7 @@
       </c>
       <c r="Q419" s="1"/>
     </row>
-    <row r="420" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A420" s="2">
         <v>46245</v>
       </c>
@@ -20462,7 +20461,7 @@
       </c>
       <c r="Q420" s="1"/>
     </row>
-    <row r="421" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A421" s="2">
         <v>46245</v>
       </c>
@@ -20505,7 +20504,7 @@
       </c>
       <c r="Q421" s="1"/>
     </row>
-    <row r="422" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A422" s="2">
         <v>46245</v>
       </c>
@@ -20548,7 +20547,7 @@
       </c>
       <c r="Q422" s="1"/>
     </row>
-    <row r="423" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A423" s="2">
         <v>46245</v>
       </c>
@@ -20591,7 +20590,7 @@
       </c>
       <c r="Q423" s="1"/>
     </row>
-    <row r="424" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A424" s="2">
         <v>46245</v>
       </c>
@@ -20634,7 +20633,7 @@
       </c>
       <c r="Q424" s="1"/>
     </row>
-    <row r="425" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A425" s="2">
         <v>46245</v>
       </c>
@@ -20677,7 +20676,7 @@
       </c>
       <c r="Q425" s="1"/>
     </row>
-    <row r="426" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A426" s="2">
         <v>46245</v>
       </c>
@@ -20726,7 +20725,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="427" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A427" s="2">
         <v>46245</v>
       </c>
@@ -20775,7 +20774,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="428" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A428" s="2">
         <v>46245</v>
       </c>
@@ -20824,7 +20823,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="429" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="429" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A429" s="2">
         <v>46245</v>
       </c>
@@ -20873,7 +20872,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="430" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A430" s="2">
         <v>46245</v>
       </c>
@@ -20922,7 +20921,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="431" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A431" s="2">
         <v>46245</v>
       </c>
@@ -20971,7 +20970,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="432" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A432" s="2">
         <v>46245</v>
       </c>
@@ -21020,7 +21019,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="433" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A433" s="2">
         <v>46245</v>
       </c>
@@ -21069,7 +21068,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="434" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A434" s="2">
         <v>46245</v>
       </c>
@@ -21118,7 +21117,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="435" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A435" s="2">
         <v>46245</v>
       </c>
@@ -21167,7 +21166,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="436" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A436" s="2">
         <v>46245</v>
       </c>
@@ -21216,7 +21215,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="437" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="437" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A437" s="2">
         <v>46245</v>
       </c>
@@ -21265,7 +21264,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="438" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A438" s="2">
         <v>46245</v>
       </c>
@@ -21314,7 +21313,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="439" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A439" s="2">
         <v>46245</v>
       </c>
@@ -21363,7 +21362,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="440" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A440" s="2">
         <v>46245</v>
       </c>
@@ -21412,7 +21411,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="441" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A441" s="2">
         <v>46245</v>
       </c>
@@ -21461,7 +21460,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="442" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A442" s="2">
         <v>46245</v>
       </c>
@@ -21510,7 +21509,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="443" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="443" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A443" s="2">
         <v>46245</v>
       </c>
@@ -21559,7 +21558,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="444" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="444" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A444" s="2">
         <v>46245</v>
       </c>
@@ -21608,7 +21607,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="445" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A445" s="2">
         <v>46245</v>
       </c>
@@ -21657,7 +21656,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="446" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A446" s="2">
         <v>46245</v>
       </c>
@@ -21706,7 +21705,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="447" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A447" s="2">
         <v>46245</v>
       </c>
@@ -21755,7 +21754,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="448" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="448" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A448" s="2">
         <v>46245</v>
       </c>
@@ -21804,7 +21803,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="449" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A449" s="2">
         <v>46245</v>
       </c>
@@ -21853,7 +21852,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="450" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A450" s="2">
         <v>46245</v>
       </c>
@@ -21902,7 +21901,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="451" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A451" s="2">
         <v>46245</v>
       </c>
@@ -21951,7 +21950,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="452" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A452" s="2">
         <v>46245</v>
       </c>
@@ -22000,7 +21999,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="453" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A453" s="2">
         <v>46245</v>
       </c>
@@ -22049,7 +22048,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="454" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A454" s="2">
         <v>46245</v>
       </c>
@@ -22098,7 +22097,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="455" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A455" s="2">
         <v>46245</v>
       </c>
@@ -22147,7 +22146,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="456" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A456" s="2">
         <v>46245</v>
       </c>
@@ -22196,7 +22195,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="457" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A457" s="2">
         <v>46245</v>
       </c>
@@ -22245,7 +22244,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="458" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="458" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A458" s="2">
         <v>46245</v>
       </c>
@@ -22294,7 +22293,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="459" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="459" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A459" s="2">
         <v>46245</v>
       </c>
@@ -22343,7 +22342,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="460" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="460" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A460" s="2">
         <v>46245</v>
       </c>
@@ -22392,7 +22391,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="461" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="461" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A461" s="2">
         <v>46245</v>
       </c>
@@ -22441,7 +22440,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="462" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="462" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A462" s="2">
         <v>46245</v>
       </c>
@@ -22490,7 +22489,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="463" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="463" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A463" s="2">
         <v>46245</v>
       </c>
@@ -22539,7 +22538,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="464" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="464" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A464" s="2">
         <v>46245</v>
       </c>
@@ -22588,7 +22587,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="465" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="465" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A465" s="2">
         <v>46245</v>
       </c>
@@ -22637,7 +22636,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="466" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="466" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A466" s="2">
         <v>46245</v>
       </c>
@@ -22686,7 +22685,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="467" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="467" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A467" s="2">
         <v>46245</v>
       </c>
@@ -22735,7 +22734,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="468" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="468" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A468" s="2">
         <v>46245</v>
       </c>
@@ -22784,7 +22783,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="469" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="469" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A469" s="2">
         <v>46245</v>
       </c>
@@ -22833,7 +22832,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="470" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A470" s="2">
         <v>46245</v>
       </c>
@@ -22882,7 +22881,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="471" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="471" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A471" s="2">
         <v>46245</v>
       </c>
@@ -22931,7 +22930,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="472" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="472" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A472" s="2">
         <v>46245</v>
       </c>
@@ -22980,7 +22979,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="473" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A473" s="2">
         <v>46245</v>
       </c>
@@ -23029,7 +23028,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="474" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="474" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A474" s="2">
         <v>46245</v>
       </c>
@@ -23078,7 +23077,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="475" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="475" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A475" s="2">
         <v>46245</v>
       </c>
@@ -23127,7 +23126,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="476" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="476" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A476" s="2">
         <v>46245</v>
       </c>
@@ -23176,7 +23175,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="477" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="477" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A477" s="2">
         <v>46245</v>
       </c>
@@ -23225,7 +23224,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="478" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="478" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A478" s="2">
         <v>46245</v>
       </c>
@@ -23274,7 +23273,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="479" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="479" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A479" s="2">
         <v>46245</v>
       </c>
@@ -23323,7 +23322,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="480" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="480" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A480" s="2">
         <v>46245</v>
       </c>
@@ -23372,7 +23371,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="481" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="481" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A481" s="2">
         <v>46245</v>
       </c>
@@ -23421,7 +23420,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="482" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="482" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A482" s="2">
         <v>46245</v>
       </c>
@@ -23470,7 +23469,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="483" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="483" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A483" s="2">
         <v>46245</v>
       </c>
@@ -23519,7 +23518,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="484" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="484" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A484" s="2">
         <v>46245</v>
       </c>
@@ -23562,7 +23561,7 @@
       </c>
       <c r="Q484" s="1"/>
     </row>
-    <row r="485" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="485" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A485" s="2">
         <v>46245</v>
       </c>
@@ -23605,7 +23604,7 @@
       </c>
       <c r="Q485" s="1"/>
     </row>
-    <row r="486" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="486" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A486" s="2">
         <v>46245</v>
       </c>
@@ -23648,7 +23647,7 @@
       </c>
       <c r="Q486" s="1"/>
     </row>
-    <row r="487" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="487" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A487" s="2">
         <v>46245</v>
       </c>
@@ -23691,7 +23690,7 @@
       </c>
       <c r="Q487" s="1"/>
     </row>
-    <row r="488" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="488" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A488" s="2">
         <v>46245</v>
       </c>
@@ -23734,7 +23733,7 @@
       </c>
       <c r="Q488" s="1"/>
     </row>
-    <row r="489" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="489" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A489" s="2">
         <v>46245</v>
       </c>
@@ -23777,7 +23776,7 @@
       </c>
       <c r="Q489" s="1"/>
     </row>
-    <row r="490" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="490" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A490" s="2">
         <v>46245</v>
       </c>
@@ -23820,7 +23819,7 @@
       </c>
       <c r="Q490" s="1"/>
     </row>
-    <row r="491" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="491" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A491" s="2">
         <v>46245</v>
       </c>
@@ -23863,7 +23862,7 @@
       </c>
       <c r="Q491" s="1"/>
     </row>
-    <row r="492" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="492" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A492" s="2">
         <v>46245</v>
       </c>
@@ -23906,7 +23905,7 @@
       </c>
       <c r="Q492" s="1"/>
     </row>
-    <row r="493" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="493" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A493" s="2">
         <v>46245</v>
       </c>
@@ -23949,7 +23948,7 @@
       </c>
       <c r="Q493" s="1"/>
     </row>
-    <row r="494" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="494" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A494" s="2">
         <v>46245</v>
       </c>
@@ -23992,7 +23991,7 @@
       </c>
       <c r="Q494" s="1"/>
     </row>
-    <row r="495" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="495" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A495" s="2">
         <v>46245</v>
       </c>
@@ -24035,7 +24034,7 @@
       </c>
       <c r="Q495" s="1"/>
     </row>
-    <row r="496" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="496" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A496" s="2">
         <v>46245</v>
       </c>
@@ -24078,7 +24077,7 @@
       </c>
       <c r="Q496" s="1"/>
     </row>
-    <row r="497" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="497" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A497" s="2">
         <v>46245</v>
       </c>
@@ -24121,7 +24120,7 @@
       </c>
       <c r="Q497" s="1"/>
     </row>
-    <row r="498" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="498" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A498" s="2">
         <v>46245</v>
       </c>
@@ -24164,7 +24163,7 @@
       </c>
       <c r="Q498" s="1"/>
     </row>
-    <row r="499" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="499" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A499" s="2">
         <v>46245</v>
       </c>
@@ -24207,7 +24206,7 @@
       </c>
       <c r="Q499" s="1"/>
     </row>
-    <row r="500" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="500" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A500" s="2">
         <v>46245</v>
       </c>
@@ -24250,7 +24249,7 @@
       </c>
       <c r="Q500" s="1"/>
     </row>
-    <row r="501" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="501" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A501" s="2">
         <v>46245</v>
       </c>
@@ -24293,7 +24292,7 @@
       </c>
       <c r="Q501" s="1"/>
     </row>
-    <row r="502" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="502" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A502" s="2">
         <v>46245</v>
       </c>
@@ -24336,7 +24335,7 @@
       </c>
       <c r="Q502" s="1"/>
     </row>
-    <row r="503" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="503" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A503" s="2">
         <v>46244</v>
       </c>
@@ -24379,7 +24378,7 @@
       </c>
       <c r="Q503" s="1"/>
     </row>
-    <row r="504" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="504" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A504" s="2">
         <v>46244</v>
       </c>
@@ -24422,7 +24421,7 @@
       </c>
       <c r="Q504" s="1"/>
     </row>
-    <row r="505" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="505" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A505" s="2">
         <v>46244</v>
       </c>
@@ -24465,7 +24464,7 @@
       </c>
       <c r="Q505" s="1"/>
     </row>
-    <row r="506" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="506" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A506" s="2">
         <v>46244</v>
       </c>
@@ -24508,7 +24507,7 @@
       </c>
       <c r="Q506" s="1"/>
     </row>
-    <row r="507" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="507" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A507" s="2">
         <v>46244</v>
       </c>
@@ -24551,7 +24550,7 @@
       </c>
       <c r="Q507" s="1"/>
     </row>
-    <row r="508" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="508" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A508" s="2">
         <v>46244</v>
       </c>
@@ -24600,7 +24599,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="509" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="509" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A509" s="2">
         <v>46244</v>
       </c>
@@ -24649,7 +24648,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="510" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="510" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A510" s="2">
         <v>46244</v>
       </c>
@@ -24698,7 +24697,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="511" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="511" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A511" s="2">
         <v>46244</v>
       </c>
@@ -24747,7 +24746,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="512" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="512" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A512" s="2">
         <v>46244</v>
       </c>
@@ -24796,7 +24795,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="513" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="513" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A513" s="2">
         <v>46244</v>
       </c>
@@ -24845,7 +24844,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="514" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="514" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A514" s="2">
         <v>46244</v>
       </c>
@@ -24894,7 +24893,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="515" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="515" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A515" s="2">
         <v>46244</v>
       </c>
@@ -24943,7 +24942,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="516" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="516" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A516" s="2">
         <v>46244</v>
       </c>
@@ -24992,7 +24991,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="517" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="517" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A517" s="2">
         <v>46244</v>
       </c>
@@ -25041,7 +25040,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="518" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="518" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A518" s="2">
         <v>46244</v>
       </c>
@@ -25090,7 +25089,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="519" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="519" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A519" s="2">
         <v>46244</v>
       </c>
@@ -25139,7 +25138,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="520" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="520" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A520" s="2">
         <v>46244</v>
       </c>
@@ -25188,7 +25187,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="521" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="521" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A521" s="2">
         <v>46244</v>
       </c>
@@ -25237,7 +25236,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="522" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="522" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A522" s="2">
         <v>46244</v>
       </c>
@@ -25286,7 +25285,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="523" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="523" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A523" s="2">
         <v>46244</v>
       </c>
@@ -25335,7 +25334,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="524" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="524" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A524" s="2">
         <v>46244</v>
       </c>
@@ -25384,7 +25383,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="525" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="525" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A525" s="2">
         <v>46244</v>
       </c>
@@ -25427,7 +25426,7 @@
       </c>
       <c r="Q525" s="1"/>
     </row>
-    <row r="526" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="526" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A526" s="2">
         <v>46244</v>
       </c>
@@ -25470,7 +25469,7 @@
       </c>
       <c r="Q526" s="1"/>
     </row>
-    <row r="527" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="527" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A527" s="2">
         <v>46244</v>
       </c>
@@ -25513,7 +25512,7 @@
       </c>
       <c r="Q527" s="1"/>
     </row>
-    <row r="528" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="528" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A528" s="2">
         <v>46244</v>
       </c>
@@ -25556,7 +25555,7 @@
       </c>
       <c r="Q528" s="1"/>
     </row>
-    <row r="529" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="529" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A529" s="2">
         <v>46244</v>
       </c>
@@ -25599,7 +25598,7 @@
       </c>
       <c r="Q529" s="1"/>
     </row>
-    <row r="530" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="530" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A530" s="2">
         <v>46244</v>
       </c>
@@ -25642,7 +25641,7 @@
       </c>
       <c r="Q530" s="1"/>
     </row>
-    <row r="531" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="531" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A531" s="2">
         <v>46244</v>
       </c>
@@ -25685,7 +25684,7 @@
       </c>
       <c r="Q531" s="1"/>
     </row>
-    <row r="532" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="532" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A532" s="2">
         <v>46244</v>
       </c>
@@ -25728,7 +25727,7 @@
       </c>
       <c r="Q532" s="1"/>
     </row>
-    <row r="533" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="533" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A533" s="2">
         <v>46244</v>
       </c>
@@ -25771,7 +25770,7 @@
       </c>
       <c r="Q533" s="1"/>
     </row>
-    <row r="534" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="534" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A534" s="2">
         <v>46244</v>
       </c>
@@ -25814,7 +25813,7 @@
       </c>
       <c r="Q534" s="1"/>
     </row>
-    <row r="535" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="535" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A535" s="2">
         <v>46244</v>
       </c>
@@ -25857,7 +25856,7 @@
       </c>
       <c r="Q535" s="1"/>
     </row>
-    <row r="536" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="536" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A536" s="2">
         <v>46244</v>
       </c>
@@ -25900,7 +25899,7 @@
       </c>
       <c r="Q536" s="1"/>
     </row>
-    <row r="537" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="537" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A537" s="2">
         <v>46244</v>
       </c>
@@ -25943,7 +25942,7 @@
       </c>
       <c r="Q537" s="1"/>
     </row>
-    <row r="538" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="538" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A538" s="2">
         <v>46244</v>
       </c>
@@ -25986,7 +25985,7 @@
       </c>
       <c r="Q538" s="1"/>
     </row>
-    <row r="539" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="539" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A539" s="2">
         <v>46244</v>
       </c>
@@ -26029,7 +26028,7 @@
       </c>
       <c r="Q539" s="1"/>
     </row>
-    <row r="540" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="540" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A540" s="2">
         <v>46244</v>
       </c>
@@ -26072,7 +26071,7 @@
       </c>
       <c r="Q540" s="1"/>
     </row>
-    <row r="541" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="541" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A541" s="2">
         <v>46244</v>
       </c>
@@ -26115,7 +26114,7 @@
       </c>
       <c r="Q541" s="1"/>
     </row>
-    <row r="542" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="542" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A542" s="2">
         <v>46244</v>
       </c>
@@ -26158,7 +26157,7 @@
       </c>
       <c r="Q542" s="1"/>
     </row>
-    <row r="543" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="543" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A543" s="2">
         <v>46244</v>
       </c>
@@ -26201,7 +26200,7 @@
       </c>
       <c r="Q543" s="1"/>
     </row>
-    <row r="544" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="544" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A544" s="2">
         <v>46244</v>
       </c>
@@ -26244,7 +26243,7 @@
       </c>
       <c r="Q544" s="1"/>
     </row>
-    <row r="545" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="545" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A545" s="2">
         <v>46244</v>
       </c>
@@ -26287,7 +26286,7 @@
       </c>
       <c r="Q545" s="1"/>
     </row>
-    <row r="546" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="546" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A546" s="2">
         <v>46244</v>
       </c>
@@ -26330,7 +26329,7 @@
       </c>
       <c r="Q546" s="1"/>
     </row>
-    <row r="547" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="547" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A547" s="2">
         <v>46244</v>
       </c>
@@ -26373,7 +26372,7 @@
       </c>
       <c r="Q547" s="1"/>
     </row>
-    <row r="548" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="548" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A548" s="2">
         <v>46244</v>
       </c>
@@ -26416,7 +26415,7 @@
       </c>
       <c r="Q548" s="1"/>
     </row>
-    <row r="549" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="549" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A549" s="2">
         <v>46244</v>
       </c>
@@ -26459,7 +26458,7 @@
       </c>
       <c r="Q549" s="1"/>
     </row>
-    <row r="550" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="550" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A550" s="2">
         <v>46244</v>
       </c>
@@ -26502,7 +26501,7 @@
       </c>
       <c r="Q550" s="1"/>
     </row>
-    <row r="551" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="551" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A551" s="2">
         <v>46244</v>
       </c>
@@ -26545,7 +26544,7 @@
       </c>
       <c r="Q551" s="1"/>
     </row>
-    <row r="552" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="552" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A552" s="2">
         <v>46244</v>
       </c>
@@ -26588,7 +26587,7 @@
       </c>
       <c r="Q552" s="1"/>
     </row>
-    <row r="553" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="553" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A553" s="2">
         <v>46244</v>
       </c>
@@ -26631,7 +26630,7 @@
       </c>
       <c r="Q553" s="1"/>
     </row>
-    <row r="554" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="554" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A554" s="2">
         <v>46244</v>
       </c>
@@ -26674,7 +26673,7 @@
       </c>
       <c r="Q554" s="1"/>
     </row>
-    <row r="555" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="555" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A555" s="2">
         <v>46244</v>
       </c>
@@ -26717,7 +26716,7 @@
       </c>
       <c r="Q555" s="1"/>
     </row>
-    <row r="556" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="556" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A556" s="2">
         <v>46244</v>
       </c>
@@ -26760,7 +26759,7 @@
       </c>
       <c r="Q556" s="1"/>
     </row>
-    <row r="557" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="557" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A557" s="2">
         <v>46244</v>
       </c>
@@ -26803,7 +26802,7 @@
       </c>
       <c r="Q557" s="1"/>
     </row>
-    <row r="558" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="558" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A558" s="2">
         <v>46244</v>
       </c>
@@ -26846,7 +26845,7 @@
       </c>
       <c r="Q558" s="1"/>
     </row>
-    <row r="559" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="559" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A559" s="2">
         <v>46244</v>
       </c>
@@ -26889,7 +26888,7 @@
       </c>
       <c r="Q559" s="1"/>
     </row>
-    <row r="560" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="560" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A560" s="2">
         <v>46244</v>
       </c>
@@ -26932,7 +26931,7 @@
       </c>
       <c r="Q560" s="1"/>
     </row>
-    <row r="561" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="561" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A561" s="2">
         <v>46244</v>
       </c>
@@ -26975,7 +26974,7 @@
       </c>
       <c r="Q561" s="1"/>
     </row>
-    <row r="562" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="562" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A562" s="2">
         <v>46244</v>
       </c>
@@ -27018,7 +27017,7 @@
       </c>
       <c r="Q562" s="1"/>
     </row>
-    <row r="563" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="563" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A563" s="2">
         <v>46244</v>
       </c>
@@ -27061,7 +27060,7 @@
       </c>
       <c r="Q563" s="1"/>
     </row>
-    <row r="564" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="564" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A564" s="2">
         <v>46244</v>
       </c>
@@ -27104,7 +27103,7 @@
       </c>
       <c r="Q564" s="1"/>
     </row>
-    <row r="565" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="565" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A565" s="2">
         <v>46244</v>
       </c>
@@ -27147,7 +27146,7 @@
       </c>
       <c r="Q565" s="1"/>
     </row>
-    <row r="566" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="566" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A566" s="2">
         <v>46244</v>
       </c>
@@ -27190,7 +27189,7 @@
       </c>
       <c r="Q566" s="1"/>
     </row>
-    <row r="567" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="567" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A567" s="2">
         <v>46244</v>
       </c>
@@ -27233,7 +27232,7 @@
       </c>
       <c r="Q567" s="1"/>
     </row>
-    <row r="568" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="568" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A568" s="2">
         <v>46244</v>
       </c>
@@ -27276,7 +27275,7 @@
       </c>
       <c r="Q568" s="1"/>
     </row>
-    <row r="569" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="569" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A569" s="2">
         <v>46244</v>
       </c>
@@ -27319,7 +27318,7 @@
       </c>
       <c r="Q569" s="1"/>
     </row>
-    <row r="570" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="570" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A570" s="2">
         <v>46244</v>
       </c>
@@ -27362,7 +27361,7 @@
       </c>
       <c r="Q570" s="1"/>
     </row>
-    <row r="571" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="571" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A571" s="2">
         <v>46244</v>
       </c>
@@ -27405,7 +27404,7 @@
       </c>
       <c r="Q571" s="1"/>
     </row>
-    <row r="572" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="572" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A572" s="2">
         <v>46244</v>
       </c>
@@ -27448,7 +27447,7 @@
       </c>
       <c r="Q572" s="1"/>
     </row>
-    <row r="573" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="573" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A573" s="2">
         <v>46244</v>
       </c>
@@ -27497,7 +27496,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="574" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="574" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A574" s="2">
         <v>46244</v>
       </c>
@@ -27546,7 +27545,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="575" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="575" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A575" s="2">
         <v>46244</v>
       </c>
@@ -27595,7 +27594,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="576" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="576" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A576" s="2">
         <v>46244</v>
       </c>
@@ -27644,7 +27643,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="577" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="577" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A577" s="2">
         <v>46244</v>
       </c>
@@ -27693,7 +27692,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="578" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="578" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A578" s="2">
         <v>46244</v>
       </c>
@@ -27742,7 +27741,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="579" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="579" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A579" s="2">
         <v>46244</v>
       </c>
@@ -27791,7 +27790,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="580" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="580" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A580" s="2">
         <v>46244</v>
       </c>
@@ -27840,7 +27839,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="581" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="581" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A581" s="2">
         <v>46244</v>
       </c>
@@ -27889,7 +27888,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="582" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="582" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A582" s="2">
         <v>46244</v>
       </c>
@@ -27938,7 +27937,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="583" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="583" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A583" s="2">
         <v>46244</v>
       </c>
@@ -27987,7 +27986,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="584" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="584" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A584" s="2">
         <v>46244</v>
       </c>
@@ -28036,7 +28035,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="585" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="585" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A585" s="2">
         <v>46244</v>
       </c>
@@ -28085,7 +28084,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="586" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="586" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A586" s="2">
         <v>46244</v>
       </c>
@@ -28134,7 +28133,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="587" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="587" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A587" s="2">
         <v>46244</v>
       </c>
@@ -28183,7 +28182,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="588" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="588" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A588" s="2">
         <v>46244</v>
       </c>
@@ -28232,7 +28231,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="589" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="589" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A589" s="2">
         <v>46244</v>
       </c>
@@ -28281,7 +28280,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="590" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="590" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A590" s="2">
         <v>46244</v>
       </c>
@@ -28330,7 +28329,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="591" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="591" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A591" s="2">
         <v>46244</v>
       </c>
@@ -28379,7 +28378,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="592" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="592" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A592" s="2">
         <v>46244</v>
       </c>
@@ -28428,7 +28427,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="593" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="593" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A593" s="2">
         <v>46244</v>
       </c>
@@ -28477,7 +28476,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="594" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="594" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A594" s="2">
         <v>46244</v>
       </c>
@@ -28526,7 +28525,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="595" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="595" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A595" s="2">
         <v>46244</v>
       </c>
@@ -28575,7 +28574,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="596" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="596" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A596" s="2">
         <v>46244</v>
       </c>
@@ -28624,7 +28623,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="597" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="597" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A597" s="2">
         <v>46244</v>
       </c>
@@ -28673,7 +28672,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="598" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="598" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A598" s="2">
         <v>46244</v>
       </c>
@@ -28722,7 +28721,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="599" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="599" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A599" s="2">
         <v>46244</v>
       </c>
@@ -28765,7 +28764,7 @@
       </c>
       <c r="Q599" s="1"/>
     </row>
-    <row r="600" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="600" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A600" s="2">
         <v>46244</v>
       </c>
@@ -28808,7 +28807,7 @@
       </c>
       <c r="Q600" s="1"/>
     </row>
-    <row r="601" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="601" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A601" s="2">
         <v>46244</v>
       </c>
@@ -28851,7 +28850,7 @@
       </c>
       <c r="Q601" s="1"/>
     </row>
-    <row r="602" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="602" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A602" s="2">
         <v>46244</v>
       </c>
@@ -28894,7 +28893,7 @@
       </c>
       <c r="Q602" s="1"/>
     </row>
-    <row r="603" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="603" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A603" s="2">
         <v>46244</v>
       </c>
@@ -28937,7 +28936,7 @@
       </c>
       <c r="Q603" s="1"/>
     </row>
-    <row r="604" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="604" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A604" s="2">
         <v>46244</v>
       </c>
@@ -28980,7 +28979,7 @@
       </c>
       <c r="Q604" s="1"/>
     </row>
-    <row r="605" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="605" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A605" s="2">
         <v>46244</v>
       </c>
@@ -29023,7 +29022,7 @@
       </c>
       <c r="Q605" s="1"/>
     </row>
-    <row r="606" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="606" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A606" s="2">
         <v>46244</v>
       </c>
@@ -29066,7 +29065,7 @@
       </c>
       <c r="Q606" s="1"/>
     </row>
-    <row r="607" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="607" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A607" s="2">
         <v>46244</v>
       </c>
@@ -29109,7 +29108,7 @@
       </c>
       <c r="Q607" s="1"/>
     </row>
-    <row r="608" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="608" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A608" s="2">
         <v>46244</v>
       </c>
@@ -29152,7 +29151,7 @@
       </c>
       <c r="Q608" s="1"/>
     </row>
-    <row r="609" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="609" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A609" s="2">
         <v>46244</v>
       </c>
@@ -29195,7 +29194,7 @@
       </c>
       <c r="Q609" s="1"/>
     </row>
-    <row r="610" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="610" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A610" s="2">
         <v>46244</v>
       </c>
@@ -29238,7 +29237,7 @@
       </c>
       <c r="Q610" s="1"/>
     </row>
-    <row r="611" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="611" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A611" s="2">
         <v>46244</v>
       </c>
@@ -29281,7 +29280,7 @@
       </c>
       <c r="Q611" s="1"/>
     </row>
-    <row r="612" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="612" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A612" s="2">
         <v>46244</v>
       </c>
@@ -29324,7 +29323,7 @@
       </c>
       <c r="Q612" s="1"/>
     </row>
-    <row r="613" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="613" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A613" s="2">
         <v>46244</v>
       </c>
@@ -29367,7 +29366,7 @@
       </c>
       <c r="Q613" s="1"/>
     </row>
-    <row r="614" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="614" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A614" s="2">
         <v>46244</v>
       </c>
@@ -29410,7 +29409,7 @@
       </c>
       <c r="Q614" s="1"/>
     </row>
-    <row r="615" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="615" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A615" s="2">
         <v>46244</v>
       </c>
@@ -29453,7 +29452,7 @@
       </c>
       <c r="Q615" s="1"/>
     </row>
-    <row r="616" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="616" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A616" s="2">
         <v>46244</v>
       </c>
@@ -29496,7 +29495,7 @@
       </c>
       <c r="Q616" s="1"/>
     </row>
-    <row r="617" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="617" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A617" s="2">
         <v>46244</v>
       </c>
@@ -29539,7 +29538,7 @@
       </c>
       <c r="Q617" s="1"/>
     </row>
-    <row r="618" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="618" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A618" s="2">
         <v>46244</v>
       </c>
@@ -29582,7 +29581,7 @@
       </c>
       <c r="Q618" s="1"/>
     </row>
-    <row r="619" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="619" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A619" s="2">
         <v>46244</v>
       </c>
@@ -29625,7 +29624,7 @@
       </c>
       <c r="Q619" s="1"/>
     </row>
-    <row r="620" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="620" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A620" s="2">
         <v>46244</v>
       </c>
@@ -29674,7 +29673,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="621" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="621" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A621" s="2">
         <v>46244</v>
       </c>
@@ -29723,7 +29722,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="622" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="622" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A622" s="2">
         <v>46244</v>
       </c>
@@ -29772,7 +29771,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="623" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="623" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A623" s="2">
         <v>46244</v>
       </c>
@@ -29821,7 +29820,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="624" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="624" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A624" s="2">
         <v>46244</v>
       </c>
@@ -29870,7 +29869,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="625" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="625" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A625" s="2">
         <v>46244</v>
       </c>
@@ -29919,7 +29918,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="626" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="626" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A626" s="2">
         <v>46244</v>
       </c>
@@ -29968,7 +29967,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="627" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="627" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A627" s="2">
         <v>46244</v>
       </c>
@@ -30017,7 +30016,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="628" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="628" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A628" s="2">
         <v>46244</v>
       </c>
@@ -30066,7 +30065,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="629" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="629" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A629" s="2">
         <v>46244</v>
       </c>
@@ -30115,7 +30114,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="630" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="630" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A630" s="2">
         <v>46244</v>
       </c>
@@ -30164,7 +30163,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="631" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="631" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A631" s="2">
         <v>46244</v>
       </c>
@@ -30213,7 +30212,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="632" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="632" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A632" s="2">
         <v>46244</v>
       </c>
@@ -30262,7 +30261,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="633" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="633" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A633" s="2">
         <v>46244</v>
       </c>
@@ -30311,7 +30310,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="634" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="634" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A634" s="2">
         <v>46244</v>
       </c>
@@ -30360,7 +30359,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="635" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="635" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A635" s="2">
         <v>46244</v>
       </c>
@@ -30409,7 +30408,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="636" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="636" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A636" s="2">
         <v>46244</v>
       </c>
@@ -30458,7 +30457,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="637" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="637" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A637" s="2">
         <v>46244</v>
       </c>
@@ -30507,7 +30506,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="638" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="638" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A638" s="2">
         <v>46244</v>
       </c>
@@ -30556,7 +30555,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="639" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="639" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A639" s="2">
         <v>46244</v>
       </c>
@@ -30605,7 +30604,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="640" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="640" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A640" s="2">
         <v>46244</v>
       </c>
@@ -30654,7 +30653,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="641" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="641" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A641" s="2">
         <v>46244</v>
       </c>
@@ -30703,7 +30702,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="642" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="642" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A642" s="2">
         <v>46244</v>
       </c>
@@ -30752,7 +30751,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="643" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="643" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A643" s="2">
         <v>46244</v>
       </c>
@@ -30795,7 +30794,7 @@
       </c>
       <c r="Q643" s="1"/>
     </row>
-    <row r="644" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="644" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A644" s="2">
         <v>46244</v>
       </c>
@@ -30838,7 +30837,7 @@
       </c>
       <c r="Q644" s="1"/>
     </row>
-    <row r="645" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="645" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A645" s="2">
         <v>46244</v>
       </c>
@@ -30881,7 +30880,7 @@
       </c>
       <c r="Q645" s="1"/>
     </row>
-    <row r="646" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="646" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A646" s="2">
         <v>46244</v>
       </c>
@@ -30924,7 +30923,7 @@
       </c>
       <c r="Q646" s="1"/>
     </row>
-    <row r="647" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="647" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A647" s="2">
         <v>46244</v>
       </c>
@@ -30967,7 +30966,7 @@
       </c>
       <c r="Q647" s="1"/>
     </row>
-    <row r="648" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="648" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A648" s="2">
         <v>46244</v>
       </c>
@@ -31010,7 +31009,7 @@
       </c>
       <c r="Q648" s="1"/>
     </row>
-    <row r="649" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="649" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A649" s="2">
         <v>46244</v>
       </c>
@@ -31053,7 +31052,7 @@
       </c>
       <c r="Q649" s="1"/>
     </row>
-    <row r="650" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="650" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A650" s="2">
         <v>46244</v>
       </c>
@@ -31096,7 +31095,7 @@
       </c>
       <c r="Q650" s="1"/>
     </row>
-    <row r="651" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="651" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A651" s="2">
         <v>46244</v>
       </c>
@@ -31139,7 +31138,7 @@
       </c>
       <c r="Q651" s="1"/>
     </row>
-    <row r="652" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="652" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A652" s="2">
         <v>46244</v>
       </c>
@@ -31182,7 +31181,7 @@
       </c>
       <c r="Q652" s="1"/>
     </row>
-    <row r="653" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="653" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A653" s="2">
         <v>46244</v>
       </c>
@@ -31225,7 +31224,7 @@
       </c>
       <c r="Q653" s="1"/>
     </row>
-    <row r="654" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="654" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A654" s="2">
         <v>46244</v>
       </c>
@@ -31268,7 +31267,7 @@
       </c>
       <c r="Q654" s="1"/>
     </row>
-    <row r="655" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="655" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A655" s="2">
         <v>46244</v>
       </c>
@@ -31311,7 +31310,7 @@
       </c>
       <c r="Q655" s="1"/>
     </row>
-    <row r="656" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="656" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A656" s="2">
         <v>46244</v>
       </c>
@@ -31354,7 +31353,7 @@
       </c>
       <c r="Q656" s="1"/>
     </row>
-    <row r="657" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="657" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A657" s="2">
         <v>46244</v>
       </c>
@@ -31397,7 +31396,7 @@
       </c>
       <c r="Q657" s="1"/>
     </row>
-    <row r="658" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="658" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A658" s="2">
         <v>46244</v>
       </c>
@@ -31440,7 +31439,7 @@
       </c>
       <c r="Q658" s="1"/>
     </row>
-    <row r="659" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="659" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A659" s="2">
         <v>46244</v>
       </c>
@@ -31483,7 +31482,7 @@
       </c>
       <c r="Q659" s="1"/>
     </row>
-    <row r="660" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="660" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A660" s="2">
         <v>46244</v>
       </c>
@@ -31526,7 +31525,7 @@
       </c>
       <c r="Q660" s="1"/>
     </row>
-    <row r="661" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="661" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A661" s="2">
         <v>46244</v>
       </c>
@@ -31569,7 +31568,7 @@
       </c>
       <c r="Q661" s="1"/>
     </row>
-    <row r="662" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="662" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A662" s="2">
         <v>46244</v>
       </c>
@@ -31612,7 +31611,7 @@
       </c>
       <c r="Q662" s="1"/>
     </row>
-    <row r="663" spans="1:17" hidden="1" x14ac:dyDescent="0.45">
+    <row r="663" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A663" s="2">
         <v>46244</v>
       </c>
@@ -31656,18 +31655,7 @@
       <c r="Q663" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q663" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="TATA 3"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="7">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:Q663" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -52678,39 +52678,47 @@
     </row>
     <row r="871">
       <c r="A871" s="2" t="n">
-        <v>46250.0</v>
+        <v>46248.0</v>
       </c>
       <c r="B871" s="1" t="n">
         <v>0.0</v>
       </c>
       <c r="C871" s="1" t="inlineStr">
         <is>
-          <t>TATA 2</t>
+          <t>TATA 3</t>
         </is>
       </c>
       <c r="D871" s="1" t="inlineStr">
         <is>
-          <t>ALIOUNE BADARA (MANSOUR) SANE</t>
+          <t>IBRAHIMA COLY</t>
         </is>
       </c>
       <c r="E871" s="1" t="inlineStr">
         <is>
-          <t>Stock Lundi</t>
-        </is>
-      </c>
-      <c r="F871" s="1"/>
-      <c r="G871" s="1"/>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F871" s="1" t="inlineStr">
+        <is>
+          <t>PIKINE</t>
+        </is>
+      </c>
+      <c r="G871" s="1" t="inlineStr">
+        <is>
+          <t>Mariama DIEDHIOU</t>
+        </is>
+      </c>
       <c r="H871" s="1"/>
       <c r="I871" s="1" t="inlineStr">
         <is>
-          <t>Café pot Refraish 200g</t>
+          <t>Jus Lido</t>
         </is>
       </c>
       <c r="J871" s="1" t="n">
-        <v>6.0</v>
+        <v>0.16666667</v>
       </c>
       <c r="K871" s="1" t="n">
-        <v>117000.0</v>
+        <v>1833.3334</v>
       </c>
       <c r="L871" s="1" t="n">
         <v>0.0</v>
@@ -52720,30 +52728,34 @@
       </c>
       <c r="N871" s="1"/>
       <c r="O871" s="1" t="n">
-        <v>649.0</v>
+        <v>525.0</v>
       </c>
       <c r="P871" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q871" s="1"/>
+      <c r="Q871" s="1" t="inlineStr">
+        <is>
+          <t>JUS</t>
+        </is>
+      </c>
     </row>
     <row r="872">
       <c r="A872" s="2" t="n">
-        <v>46250.0</v>
+        <v>46248.0</v>
       </c>
       <c r="B872" s="1" t="n">
         <v>0.0</v>
       </c>
       <c r="C872" s="1" t="inlineStr">
         <is>
-          <t>TATA 2</t>
+          <t>TATA 3</t>
         </is>
       </c>
       <c r="D872" s="1" t="inlineStr">
         <is>
-          <t>ALIOUNE BADARA (MANSOUR) SANE</t>
+          <t>IBRAHIMA COLY</t>
         </is>
       </c>
       <c r="E872" s="1" t="inlineStr">
@@ -52758,20 +52770,20 @@
       </c>
       <c r="G872" s="1" t="inlineStr">
         <is>
-          <t>Coura DIONE</t>
+          <t>Mamy DIAW</t>
         </is>
       </c>
       <c r="H872" s="1"/>
       <c r="I872" s="1" t="inlineStr">
         <is>
-          <t>Café pot Refraish 200g</t>
+          <t>Jus Lido</t>
         </is>
       </c>
       <c r="J872" s="1" t="n">
-        <v>0.5</v>
+        <v>0.41666666</v>
       </c>
       <c r="K872" s="1" t="n">
-        <v>9750.0</v>
+        <v>4583.3335</v>
       </c>
       <c r="L872" s="1" t="n">
         <v>0.0</v>
@@ -52779,13 +52791,9 @@
       <c r="M872" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="N872" s="1" t="inlineStr">
-        <is>
-          <t>Nd</t>
-        </is>
-      </c>
+      <c r="N872" s="1"/>
       <c r="O872" s="1" t="n">
-        <v>650.0</v>
+        <v>526.0</v>
       </c>
       <c r="P872" s="1" t="inlineStr">
         <is>
@@ -52794,25 +52802,25 @@
       </c>
       <c r="Q872" s="1" t="inlineStr">
         <is>
-          <t>REFRAISH</t>
+          <t>JUS</t>
         </is>
       </c>
     </row>
     <row r="873">
       <c r="A873" s="2" t="n">
-        <v>46250.0</v>
+        <v>46248.0</v>
       </c>
       <c r="B873" s="1" t="n">
         <v>0.0</v>
       </c>
       <c r="C873" s="1" t="inlineStr">
         <is>
-          <t>TATA 2</t>
+          <t>TATA 3</t>
         </is>
       </c>
       <c r="D873" s="1" t="inlineStr">
         <is>
-          <t>ALIOUNE BADARA (MANSOUR) SANE</t>
+          <t>IBRAHIMA COLY</t>
         </is>
       </c>
       <c r="E873" s="1" t="inlineStr">
@@ -52827,20 +52835,20 @@
       </c>
       <c r="G873" s="1" t="inlineStr">
         <is>
-          <t>Coura DIONE</t>
+          <t>Jackline DIEDHIOU</t>
         </is>
       </c>
       <c r="H873" s="1"/>
       <c r="I873" s="1" t="inlineStr">
         <is>
-          <t>Café Refraish 100g</t>
+          <t>Jus Lido</t>
         </is>
       </c>
       <c r="J873" s="1" t="n">
-        <v>0.041666668</v>
+        <v>0.083333336</v>
       </c>
       <c r="K873" s="1" t="n">
-        <v>791.6667</v>
+        <v>916.6667</v>
       </c>
       <c r="L873" s="1" t="n">
         <v>0.0</v>
@@ -52848,13 +52856,9 @@
       <c r="M873" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="N873" s="1" t="inlineStr">
-        <is>
-          <t>Nd</t>
-        </is>
-      </c>
+      <c r="N873" s="1"/>
       <c r="O873" s="1" t="n">
-        <v>651.0</v>
+        <v>527.0</v>
       </c>
       <c r="P873" s="1" t="inlineStr">
         <is>
@@ -52863,25 +52867,25 @@
       </c>
       <c r="Q873" s="1" t="inlineStr">
         <is>
-          <t>REFRAISH</t>
+          <t>JUS</t>
         </is>
       </c>
     </row>
     <row r="874">
       <c r="A874" s="2" t="n">
-        <v>46250.0</v>
+        <v>46248.0</v>
       </c>
       <c r="B874" s="1" t="n">
         <v>0.0</v>
       </c>
       <c r="C874" s="1" t="inlineStr">
         <is>
-          <t>TATA 2</t>
+          <t>TATA 3</t>
         </is>
       </c>
       <c r="D874" s="1" t="inlineStr">
         <is>
-          <t>ALIOUNE BADARA (MANSOUR) SANE</t>
+          <t>IBRAHIMA COLY</t>
         </is>
       </c>
       <c r="E874" s="1" t="inlineStr">
@@ -52896,20 +52900,20 @@
       </c>
       <c r="G874" s="1" t="inlineStr">
         <is>
-          <t>Coura DIONE</t>
+          <t>Khady DEME</t>
         </is>
       </c>
       <c r="H874" s="1"/>
       <c r="I874" s="1" t="inlineStr">
         <is>
-          <t>Café stick Refraish 1,5gx09boites</t>
+          <t>Jus Lido</t>
         </is>
       </c>
       <c r="J874" s="1" t="n">
-        <v>1.0</v>
+        <v>0.16666667</v>
       </c>
       <c r="K874" s="1" t="n">
-        <v>26000.0</v>
+        <v>1833.3334</v>
       </c>
       <c r="L874" s="1" t="n">
         <v>0.0</v>
@@ -52917,13 +52921,9 @@
       <c r="M874" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="N874" s="1" t="inlineStr">
-        <is>
-          <t>Nd</t>
-        </is>
-      </c>
+      <c r="N874" s="1"/>
       <c r="O874" s="1" t="n">
-        <v>652.0</v>
+        <v>528.0</v>
       </c>
       <c r="P874" s="1" t="inlineStr">
         <is>
@@ -52932,25 +52932,25 @@
       </c>
       <c r="Q874" s="1" t="inlineStr">
         <is>
-          <t>REFRAISH</t>
+          <t>JUS</t>
         </is>
       </c>
     </row>
     <row r="875">
       <c r="A875" s="2" t="n">
-        <v>46250.0</v>
+        <v>46248.0</v>
       </c>
       <c r="B875" s="1" t="n">
         <v>0.0</v>
       </c>
       <c r="C875" s="1" t="inlineStr">
         <is>
-          <t>TATA 2</t>
+          <t>TATA 3</t>
         </is>
       </c>
       <c r="D875" s="1" t="inlineStr">
         <is>
-          <t>ALIOUNE BADARA (MANSOUR) SANE</t>
+          <t>IBRAHIMA COLY</t>
         </is>
       </c>
       <c r="E875" s="1" t="inlineStr">
@@ -52965,20 +52965,20 @@
       </c>
       <c r="G875" s="1" t="inlineStr">
         <is>
-          <t>Adama</t>
+          <t>Oumy DIOP</t>
         </is>
       </c>
       <c r="H875" s="1"/>
       <c r="I875" s="1" t="inlineStr">
         <is>
-          <t>Café Altimo pot 100g x 24 pcs</t>
+          <t>Jus Lido</t>
         </is>
       </c>
       <c r="J875" s="1" t="n">
-        <v>0.041666668</v>
+        <v>0.33333334</v>
       </c>
       <c r="K875" s="1" t="n">
-        <v>1395.8334</v>
+        <v>3666.6667</v>
       </c>
       <c r="L875" s="1" t="n">
         <v>0.0</v>
@@ -52986,13 +52986,9 @@
       <c r="M875" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="N875" s="1" t="inlineStr">
-        <is>
-          <t>Nd</t>
-        </is>
-      </c>
+      <c r="N875" s="1"/>
       <c r="O875" s="1" t="n">
-        <v>653.0</v>
+        <v>529.0</v>
       </c>
       <c r="P875" s="1" t="inlineStr">
         <is>
@@ -53001,25 +52997,25 @@
       </c>
       <c r="Q875" s="1" t="inlineStr">
         <is>
-          <t>ALTIMO</t>
+          <t>JUS</t>
         </is>
       </c>
     </row>
     <row r="876">
       <c r="A876" s="2" t="n">
-        <v>46250.0</v>
+        <v>46248.0</v>
       </c>
       <c r="B876" s="1" t="n">
         <v>0.0</v>
       </c>
       <c r="C876" s="1" t="inlineStr">
         <is>
-          <t>TATA 2</t>
+          <t>TATA 3</t>
         </is>
       </c>
       <c r="D876" s="1" t="inlineStr">
         <is>
-          <t>ALIOUNE BADARA (MANSOUR) SANE</t>
+          <t>IBRAHIMA COLY</t>
         </is>
       </c>
       <c r="E876" s="1" t="inlineStr">
@@ -53034,20 +53030,20 @@
       </c>
       <c r="G876" s="1" t="inlineStr">
         <is>
-          <t>Adama</t>
+          <t>Thida DIA</t>
         </is>
       </c>
       <c r="H876" s="1"/>
       <c r="I876" s="1" t="inlineStr">
         <is>
-          <t>Café Altimo pot 200g x 12 pcs</t>
+          <t>Jus Lido</t>
         </is>
       </c>
       <c r="J876" s="1" t="n">
-        <v>0.6666667</v>
+        <v>0.25</v>
       </c>
       <c r="K876" s="1" t="n">
-        <v>22333.334</v>
+        <v>2750.0</v>
       </c>
       <c r="L876" s="1" t="n">
         <v>0.0</v>
@@ -53055,13 +53051,9 @@
       <c r="M876" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="N876" s="1" t="inlineStr">
-        <is>
-          <t>Nd</t>
-        </is>
-      </c>
+      <c r="N876" s="1"/>
       <c r="O876" s="1" t="n">
-        <v>654.0</v>
+        <v>530.0</v>
       </c>
       <c r="P876" s="1" t="inlineStr">
         <is>
@@ -53070,25 +53062,25 @@
       </c>
       <c r="Q876" s="1" t="inlineStr">
         <is>
-          <t>ALTIMO</t>
+          <t>JUS</t>
         </is>
       </c>
     </row>
     <row r="877">
       <c r="A877" s="2" t="n">
-        <v>46250.0</v>
+        <v>46248.0</v>
       </c>
       <c r="B877" s="1" t="n">
         <v>0.0</v>
       </c>
       <c r="C877" s="1" t="inlineStr">
         <is>
-          <t>TATA 2</t>
+          <t>TATA 3</t>
         </is>
       </c>
       <c r="D877" s="1" t="inlineStr">
         <is>
-          <t>ALIOUNE BADARA (MANSOUR) SANE</t>
+          <t>IBRAHIMA COLY</t>
         </is>
       </c>
       <c r="E877" s="1" t="inlineStr">
@@ -53103,20 +53095,20 @@
       </c>
       <c r="G877" s="1" t="inlineStr">
         <is>
-          <t>Nogueye THIAME</t>
+          <t>Mame Fatou</t>
         </is>
       </c>
       <c r="H877" s="1"/>
       <c r="I877" s="1" t="inlineStr">
         <is>
-          <t>Chocolat transparent 200gx24pcs</t>
+          <t>Jus Lido</t>
         </is>
       </c>
       <c r="J877" s="1" t="n">
-        <v>1.0</v>
+        <v>0.25</v>
       </c>
       <c r="K877" s="1" t="n">
-        <v>12500.0</v>
+        <v>2750.0</v>
       </c>
       <c r="L877" s="1" t="n">
         <v>0.0</v>
@@ -53124,13 +53116,9 @@
       <c r="M877" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="N877" s="1" t="inlineStr">
-        <is>
-          <t>Nd</t>
-        </is>
-      </c>
+      <c r="N877" s="1"/>
       <c r="O877" s="1" t="n">
-        <v>655.0</v>
+        <v>531.0</v>
       </c>
       <c r="P877" s="1" t="inlineStr">
         <is>
@@ -53139,25 +53127,25 @@
       </c>
       <c r="Q877" s="1" t="inlineStr">
         <is>
-          <t>CHOC TRANS</t>
+          <t>JUS</t>
         </is>
       </c>
     </row>
     <row r="878">
       <c r="A878" s="2" t="n">
-        <v>46250.0</v>
+        <v>46248.0</v>
       </c>
       <c r="B878" s="1" t="n">
         <v>0.0</v>
       </c>
       <c r="C878" s="1" t="inlineStr">
         <is>
-          <t>TATA 2</t>
+          <t>TATA 3</t>
         </is>
       </c>
       <c r="D878" s="1" t="inlineStr">
         <is>
-          <t>ALIOUNE BADARA (MANSOUR) SANE</t>
+          <t>IBRAHIMA COLY</t>
         </is>
       </c>
       <c r="E878" s="1" t="inlineStr">
@@ -53172,20 +53160,20 @@
       </c>
       <c r="G878" s="1" t="inlineStr">
         <is>
-          <t>Nogueye THIAME</t>
+          <t>Kadia GUEYE</t>
         </is>
       </c>
       <c r="H878" s="1"/>
       <c r="I878" s="1" t="inlineStr">
         <is>
-          <t>Chocolat transparent 400gx12pcs</t>
+          <t>Jus Lido</t>
         </is>
       </c>
       <c r="J878" s="1" t="n">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
       <c r="K878" s="1" t="n">
-        <v>12500.0</v>
+        <v>5500.0</v>
       </c>
       <c r="L878" s="1" t="n">
         <v>0.0</v>
@@ -53193,13 +53181,9 @@
       <c r="M878" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="N878" s="1" t="inlineStr">
-        <is>
-          <t>Nd</t>
-        </is>
-      </c>
+      <c r="N878" s="1"/>
       <c r="O878" s="1" t="n">
-        <v>656.0</v>
+        <v>532.0</v>
       </c>
       <c r="P878" s="1" t="inlineStr">
         <is>
@@ -53208,25 +53192,25 @@
       </c>
       <c r="Q878" s="1" t="inlineStr">
         <is>
-          <t>CHOC TRANS</t>
+          <t>JUS</t>
         </is>
       </c>
     </row>
     <row r="879">
       <c r="A879" s="2" t="n">
-        <v>46250.0</v>
+        <v>46248.0</v>
       </c>
       <c r="B879" s="1" t="n">
         <v>0.0</v>
       </c>
       <c r="C879" s="1" t="inlineStr">
         <is>
-          <t>TATA 2</t>
+          <t>TATA 3</t>
         </is>
       </c>
       <c r="D879" s="1" t="inlineStr">
         <is>
-          <t>ALIOUNE BADARA (MANSOUR) SANE</t>
+          <t>IBRAHIMA COLY</t>
         </is>
       </c>
       <c r="E879" s="1" t="inlineStr">
@@ -53241,20 +53225,20 @@
       </c>
       <c r="G879" s="1" t="inlineStr">
         <is>
-          <t>Nogueye THIAME</t>
+          <t>Rokhaya SANE</t>
         </is>
       </c>
       <c r="H879" s="1"/>
       <c r="I879" s="1" t="inlineStr">
         <is>
-          <t>Chocolat 3-en-1 30x120 pcs</t>
+          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
         </is>
       </c>
       <c r="J879" s="1" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="K879" s="1" t="n">
-        <v>2200.0</v>
+        <v>4500.0</v>
       </c>
       <c r="L879" s="1" t="n">
         <v>0.0</v>
@@ -53262,13 +53246,9 @@
       <c r="M879" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="N879" s="1" t="inlineStr">
-        <is>
-          <t>Nd</t>
-        </is>
-      </c>
+      <c r="N879" s="1"/>
       <c r="O879" s="1" t="n">
-        <v>657.0</v>
+        <v>579.0</v>
       </c>
       <c r="P879" s="1" t="inlineStr">
         <is>
@@ -53277,25 +53257,25 @@
       </c>
       <c r="Q879" s="1" t="inlineStr">
         <is>
-          <t>CHOC TRANS</t>
+          <t>CEREAL</t>
         </is>
       </c>
     </row>
     <row r="880">
       <c r="A880" s="2" t="n">
-        <v>46250.0</v>
+        <v>46248.0</v>
       </c>
       <c r="B880" s="1" t="n">
         <v>0.0</v>
       </c>
       <c r="C880" s="1" t="inlineStr">
         <is>
-          <t>TATA 2</t>
+          <t>TATA 3</t>
         </is>
       </c>
       <c r="D880" s="1" t="inlineStr">
         <is>
-          <t>ALIOUNE BADARA (MANSOUR) SANE</t>
+          <t>IBRAHIMA COLY</t>
         </is>
       </c>
       <c r="E880" s="1" t="inlineStr">
@@ -53310,20 +53290,20 @@
       </c>
       <c r="G880" s="1" t="inlineStr">
         <is>
-          <t>Baye Cheikh</t>
+          <t>Rokhaya SANE</t>
         </is>
       </c>
       <c r="H880" s="1"/>
       <c r="I880" s="1" t="inlineStr">
         <is>
-          <t>Kamlac évaporé 48x160g</t>
+          <t>Kamlac Junior BLE cereal 230g x 12 sachet</t>
         </is>
       </c>
       <c r="J880" s="1" t="n">
-        <v>1.0</v>
+        <v>1.25</v>
       </c>
       <c r="K880" s="1" t="n">
-        <v>9000.0</v>
+        <v>11250.0</v>
       </c>
       <c r="L880" s="1" t="n">
         <v>0.0</v>
@@ -53331,13 +53311,9 @@
       <c r="M880" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="N880" s="1" t="inlineStr">
-        <is>
-          <t>Nd</t>
-        </is>
-      </c>
+      <c r="N880" s="1"/>
       <c r="O880" s="1" t="n">
-        <v>658.0</v>
+        <v>580.0</v>
       </c>
       <c r="P880" s="1" t="inlineStr">
         <is>
@@ -53346,25 +53322,25 @@
       </c>
       <c r="Q880" s="1" t="inlineStr">
         <is>
-          <t>LAIT</t>
+          <t>CEREAL</t>
         </is>
       </c>
     </row>
     <row r="881">
       <c r="A881" s="2" t="n">
-        <v>46250.0</v>
+        <v>46248.0</v>
       </c>
       <c r="B881" s="1" t="n">
         <v>0.0</v>
       </c>
       <c r="C881" s="1" t="inlineStr">
         <is>
-          <t>TATA 2</t>
+          <t>TATA 3</t>
         </is>
       </c>
       <c r="D881" s="1" t="inlineStr">
         <is>
-          <t>ALIOUNE BADARA (MANSOUR) SANE</t>
+          <t>IBRAHIMA COLY</t>
         </is>
       </c>
       <c r="E881" s="1" t="inlineStr">
@@ -53379,20 +53355,20 @@
       </c>
       <c r="G881" s="1" t="inlineStr">
         <is>
-          <t>Baye Cheikh</t>
+          <t>Rokhaya SANE</t>
         </is>
       </c>
       <c r="H881" s="1"/>
       <c r="I881" s="1" t="inlineStr">
         <is>
-          <t>KamLac Lait concentré sucré 24x1kg</t>
+          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
         </is>
       </c>
       <c r="J881" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="K881" s="1" t="n">
-        <v>13250.0</v>
+        <v>4500.0</v>
       </c>
       <c r="L881" s="1" t="n">
         <v>0.0</v>
@@ -53400,13 +53376,9 @@
       <c r="M881" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="N881" s="1" t="inlineStr">
-        <is>
-          <t>Nd</t>
-        </is>
-      </c>
+      <c r="N881" s="1"/>
       <c r="O881" s="1" t="n">
-        <v>659.0</v>
+        <v>581.0</v>
       </c>
       <c r="P881" s="1" t="inlineStr">
         <is>
@@ -53415,25 +53387,25 @@
       </c>
       <c r="Q881" s="1" t="inlineStr">
         <is>
-          <t>LAIT</t>
+          <t>CEREAL</t>
         </is>
       </c>
     </row>
     <row r="882">
       <c r="A882" s="2" t="n">
-        <v>46250.0</v>
+        <v>46248.0</v>
       </c>
       <c r="B882" s="1" t="n">
         <v>0.0</v>
       </c>
       <c r="C882" s="1" t="inlineStr">
         <is>
-          <t>TATA 2</t>
+          <t>TATA 3</t>
         </is>
       </c>
       <c r="D882" s="1" t="inlineStr">
         <is>
-          <t>ALIOUNE BADARA (MANSOUR) SANE</t>
+          <t>IBRAHIMA COLY</t>
         </is>
       </c>
       <c r="E882" s="1" t="inlineStr">
@@ -53448,20 +53420,20 @@
       </c>
       <c r="G882" s="1" t="inlineStr">
         <is>
-          <t>Baye Cheikh</t>
+          <t>Ndeye Fatou GUEYE</t>
         </is>
       </c>
       <c r="H882" s="1"/>
       <c r="I882" s="1" t="inlineStr">
         <is>
-          <t>Lait Janus 18gx10</t>
+          <t>Kamlac Junior mais cereal 50g x 10 x 8 sachet</t>
         </is>
       </c>
       <c r="J882" s="1" t="n">
-        <v>0.2</v>
+        <v>0.375</v>
       </c>
       <c r="K882" s="1" t="n">
-        <v>1200.0</v>
+        <v>5625.0</v>
       </c>
       <c r="L882" s="1" t="n">
         <v>0.0</v>
@@ -53469,13 +53441,9 @@
       <c r="M882" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="N882" s="1" t="inlineStr">
-        <is>
-          <t>Nd</t>
-        </is>
-      </c>
+      <c r="N882" s="1"/>
       <c r="O882" s="1" t="n">
-        <v>660.0</v>
+        <v>582.0</v>
       </c>
       <c r="P882" s="1" t="inlineStr">
         <is>
@@ -53484,25 +53452,25 @@
       </c>
       <c r="Q882" s="1" t="inlineStr">
         <is>
-          <t>LAIT</t>
+          <t>CEREAL</t>
         </is>
       </c>
     </row>
     <row r="883">
       <c r="A883" s="2" t="n">
-        <v>46250.0</v>
+        <v>46248.0</v>
       </c>
       <c r="B883" s="1" t="n">
         <v>0.0</v>
       </c>
       <c r="C883" s="1" t="inlineStr">
         <is>
-          <t>TATA 2</t>
+          <t>TATA 3</t>
         </is>
       </c>
       <c r="D883" s="1" t="inlineStr">
         <is>
-          <t>ALIOUNE BADARA (MANSOUR) SANE</t>
+          <t>IBRAHIMA COLY</t>
         </is>
       </c>
       <c r="E883" s="1" t="inlineStr">
@@ -53517,20 +53485,20 @@
       </c>
       <c r="G883" s="1" t="inlineStr">
         <is>
-          <t>Baye Cheikh</t>
+          <t>Ndeye Fatou GUEYE</t>
         </is>
       </c>
       <c r="H883" s="1"/>
       <c r="I883" s="1" t="inlineStr">
         <is>
-          <t>Cafe au Lait 3-en-1</t>
+          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
         </is>
       </c>
       <c r="J883" s="1" t="n">
-        <v>0.2</v>
+        <v>0.6666667</v>
       </c>
       <c r="K883" s="1" t="n">
-        <v>900.0</v>
+        <v>6000.0</v>
       </c>
       <c r="L883" s="1" t="n">
         <v>0.0</v>
@@ -53538,13 +53506,9 @@
       <c r="M883" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="N883" s="1" t="inlineStr">
-        <is>
-          <t>Nd</t>
-        </is>
-      </c>
+      <c r="N883" s="1"/>
       <c r="O883" s="1" t="n">
-        <v>661.0</v>
+        <v>583.0</v>
       </c>
       <c r="P883" s="1" t="inlineStr">
         <is>
@@ -53553,25 +53517,25 @@
       </c>
       <c r="Q883" s="1" t="inlineStr">
         <is>
-          <t>LAIT</t>
+          <t>CEREAL</t>
         </is>
       </c>
     </row>
     <row r="884">
       <c r="A884" s="2" t="n">
-        <v>46250.0</v>
+        <v>46248.0</v>
       </c>
       <c r="B884" s="1" t="n">
         <v>0.0</v>
       </c>
       <c r="C884" s="1" t="inlineStr">
         <is>
-          <t>TATA 2</t>
+          <t>TATA 3</t>
         </is>
       </c>
       <c r="D884" s="1" t="inlineStr">
         <is>
-          <t>ALIOUNE BADARA (MANSOUR) SANE</t>
+          <t>IBRAHIMA COLY</t>
         </is>
       </c>
       <c r="E884" s="1" t="inlineStr">
@@ -53586,20 +53550,20 @@
       </c>
       <c r="G884" s="1" t="inlineStr">
         <is>
-          <t>Saly THIOUNE</t>
+          <t>Ndeye Fatou GUEYE</t>
         </is>
       </c>
       <c r="H884" s="1"/>
       <c r="I884" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Thé 7g</t>
+          <t>Kamlac Junior BLE cereal 230g x 12 sachet</t>
         </is>
       </c>
       <c r="J884" s="1" t="n">
-        <v>3.5833333</v>
+        <v>1.0</v>
       </c>
       <c r="K884" s="1" t="n">
-        <v>41208.332</v>
+        <v>9000.0</v>
       </c>
       <c r="L884" s="1" t="n">
         <v>0.0</v>
@@ -53607,13 +53571,9 @@
       <c r="M884" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="N884" s="1" t="inlineStr">
-        <is>
-          <t>Nd</t>
-        </is>
-      </c>
+      <c r="N884" s="1"/>
       <c r="O884" s="1" t="n">
-        <v>662.0</v>
+        <v>584.0</v>
       </c>
       <c r="P884" s="1" t="inlineStr">
         <is>
@@ -53622,7 +53582,7 @@
       </c>
       <c r="Q884" s="1" t="inlineStr">
         <is>
-          <t>THE</t>
+          <t>CEREAL</t>
         </is>
       </c>
     </row>
@@ -53655,20 +53615,20 @@
       </c>
       <c r="G885" s="1" t="inlineStr">
         <is>
-          <t>Mariama DIEDHIOU</t>
+          <t>Oumou DIALLO</t>
         </is>
       </c>
       <c r="H885" s="1"/>
       <c r="I885" s="1" t="inlineStr">
         <is>
-          <t>Jus Lido</t>
+          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
         </is>
       </c>
       <c r="J885" s="1" t="n">
-        <v>0.16666667</v>
+        <v>0.5</v>
       </c>
       <c r="K885" s="1" t="n">
-        <v>1833.3334</v>
+        <v>4500.0</v>
       </c>
       <c r="L885" s="1" t="n">
         <v>0.0</v>
@@ -53678,7 +53638,7 @@
       </c>
       <c r="N885" s="1"/>
       <c r="O885" s="1" t="n">
-        <v>525.0</v>
+        <v>585.0</v>
       </c>
       <c r="P885" s="1" t="inlineStr">
         <is>
@@ -53687,7 +53647,7 @@
       </c>
       <c r="Q885" s="1" t="inlineStr">
         <is>
-          <t>JUS</t>
+          <t>CEREAL</t>
         </is>
       </c>
     </row>
@@ -53720,20 +53680,20 @@
       </c>
       <c r="G886" s="1" t="inlineStr">
         <is>
-          <t>Mamy DIAW</t>
+          <t>Oumou DIALLO</t>
         </is>
       </c>
       <c r="H886" s="1"/>
       <c r="I886" s="1" t="inlineStr">
         <is>
-          <t>Jus Lido</t>
+          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
         </is>
       </c>
       <c r="J886" s="1" t="n">
-        <v>0.41666666</v>
+        <v>1.0</v>
       </c>
       <c r="K886" s="1" t="n">
-        <v>4583.3335</v>
+        <v>9000.0</v>
       </c>
       <c r="L886" s="1" t="n">
         <v>0.0</v>
@@ -53743,7 +53703,7 @@
       </c>
       <c r="N886" s="1"/>
       <c r="O886" s="1" t="n">
-        <v>526.0</v>
+        <v>586.0</v>
       </c>
       <c r="P886" s="1" t="inlineStr">
         <is>
@@ -53752,7 +53712,7 @@
       </c>
       <c r="Q886" s="1" t="inlineStr">
         <is>
-          <t>JUS</t>
+          <t>CEREAL</t>
         </is>
       </c>
     </row>
@@ -53785,20 +53745,20 @@
       </c>
       <c r="G887" s="1" t="inlineStr">
         <is>
-          <t>Jackline DIEDHIOU</t>
+          <t>Safietou SENE</t>
         </is>
       </c>
       <c r="H887" s="1"/>
       <c r="I887" s="1" t="inlineStr">
         <is>
-          <t>Jus Lido</t>
+          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
         </is>
       </c>
       <c r="J887" s="1" t="n">
-        <v>0.083333336</v>
+        <v>1.0</v>
       </c>
       <c r="K887" s="1" t="n">
-        <v>916.6667</v>
+        <v>9000.0</v>
       </c>
       <c r="L887" s="1" t="n">
         <v>0.0</v>
@@ -53808,7 +53768,7 @@
       </c>
       <c r="N887" s="1"/>
       <c r="O887" s="1" t="n">
-        <v>527.0</v>
+        <v>587.0</v>
       </c>
       <c r="P887" s="1" t="inlineStr">
         <is>
@@ -53817,7 +53777,7 @@
       </c>
       <c r="Q887" s="1" t="inlineStr">
         <is>
-          <t>JUS</t>
+          <t>CEREAL</t>
         </is>
       </c>
     </row>
@@ -53850,20 +53810,20 @@
       </c>
       <c r="G888" s="1" t="inlineStr">
         <is>
-          <t>Khady DEME</t>
+          <t>Anta DIOP</t>
         </is>
       </c>
       <c r="H888" s="1"/>
       <c r="I888" s="1" t="inlineStr">
         <is>
-          <t>Jus Lido</t>
+          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
         </is>
       </c>
       <c r="J888" s="1" t="n">
-        <v>0.16666667</v>
+        <v>1.0</v>
       </c>
       <c r="K888" s="1" t="n">
-        <v>1833.3334</v>
+        <v>9000.0</v>
       </c>
       <c r="L888" s="1" t="n">
         <v>0.0</v>
@@ -53873,7 +53833,7 @@
       </c>
       <c r="N888" s="1"/>
       <c r="O888" s="1" t="n">
-        <v>528.0</v>
+        <v>588.0</v>
       </c>
       <c r="P888" s="1" t="inlineStr">
         <is>
@@ -53882,7 +53842,7 @@
       </c>
       <c r="Q888" s="1" t="inlineStr">
         <is>
-          <t>JUS</t>
+          <t>CEREAL</t>
         </is>
       </c>
     </row>
@@ -53915,20 +53875,20 @@
       </c>
       <c r="G889" s="1" t="inlineStr">
         <is>
-          <t>Oumy DIOP</t>
+          <t>Anta DIOP</t>
         </is>
       </c>
       <c r="H889" s="1"/>
       <c r="I889" s="1" t="inlineStr">
         <is>
-          <t>Jus Lido</t>
+          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
         </is>
       </c>
       <c r="J889" s="1" t="n">
-        <v>0.33333334</v>
+        <v>0.6666667</v>
       </c>
       <c r="K889" s="1" t="n">
-        <v>3666.6667</v>
+        <v>6000.0</v>
       </c>
       <c r="L889" s="1" t="n">
         <v>0.0</v>
@@ -53938,7 +53898,7 @@
       </c>
       <c r="N889" s="1"/>
       <c r="O889" s="1" t="n">
-        <v>529.0</v>
+        <v>589.0</v>
       </c>
       <c r="P889" s="1" t="inlineStr">
         <is>
@@ -53947,7 +53907,7 @@
       </c>
       <c r="Q889" s="1" t="inlineStr">
         <is>
-          <t>JUS</t>
+          <t>CEREAL</t>
         </is>
       </c>
     </row>
@@ -53980,20 +53940,20 @@
       </c>
       <c r="G890" s="1" t="inlineStr">
         <is>
-          <t>Thida DIA</t>
+          <t>Sira Soumare</t>
         </is>
       </c>
       <c r="H890" s="1"/>
       <c r="I890" s="1" t="inlineStr">
         <is>
-          <t>Jus Lido</t>
+          <t>Kamlac Junior mais cereal 50g x 10 x 8 sachet</t>
         </is>
       </c>
       <c r="J890" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="K890" s="1" t="n">
-        <v>2750.0</v>
+        <v>3750.0</v>
       </c>
       <c r="L890" s="1" t="n">
         <v>0.0</v>
@@ -54003,7 +53963,7 @@
       </c>
       <c r="N890" s="1"/>
       <c r="O890" s="1" t="n">
-        <v>530.0</v>
+        <v>590.0</v>
       </c>
       <c r="P890" s="1" t="inlineStr">
         <is>
@@ -54012,7 +53972,7 @@
       </c>
       <c r="Q890" s="1" t="inlineStr">
         <is>
-          <t>JUS</t>
+          <t>CEREAL</t>
         </is>
       </c>
     </row>
@@ -54045,20 +54005,20 @@
       </c>
       <c r="G891" s="1" t="inlineStr">
         <is>
-          <t>Mame Fatou</t>
+          <t>Sira Soumare</t>
         </is>
       </c>
       <c r="H891" s="1"/>
       <c r="I891" s="1" t="inlineStr">
         <is>
-          <t>Jus Lido</t>
+          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
         </is>
       </c>
       <c r="J891" s="1" t="n">
-        <v>0.25</v>
+        <v>0.8333333</v>
       </c>
       <c r="K891" s="1" t="n">
-        <v>2750.0</v>
+        <v>7500.0</v>
       </c>
       <c r="L891" s="1" t="n">
         <v>0.0</v>
@@ -54068,7 +54028,7 @@
       </c>
       <c r="N891" s="1"/>
       <c r="O891" s="1" t="n">
-        <v>531.0</v>
+        <v>591.0</v>
       </c>
       <c r="P891" s="1" t="inlineStr">
         <is>
@@ -54077,7 +54037,7 @@
       </c>
       <c r="Q891" s="1" t="inlineStr">
         <is>
-          <t>JUS</t>
+          <t>CEREAL</t>
         </is>
       </c>
     </row>
@@ -54110,20 +54070,20 @@
       </c>
       <c r="G892" s="1" t="inlineStr">
         <is>
-          <t>Kadia GUEYE</t>
+          <t>Rokhaya DIENG</t>
         </is>
       </c>
       <c r="H892" s="1"/>
       <c r="I892" s="1" t="inlineStr">
         <is>
-          <t>Jus Lido</t>
+          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
         </is>
       </c>
       <c r="J892" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="K892" s="1" t="n">
-        <v>5500.0</v>
+        <v>4500.0</v>
       </c>
       <c r="L892" s="1" t="n">
         <v>0.0</v>
@@ -54133,7 +54093,7 @@
       </c>
       <c r="N892" s="1"/>
       <c r="O892" s="1" t="n">
-        <v>532.0</v>
+        <v>592.0</v>
       </c>
       <c r="P892" s="1" t="inlineStr">
         <is>
@@ -54142,7 +54102,7 @@
       </c>
       <c r="Q892" s="1" t="inlineStr">
         <is>
-          <t>JUS</t>
+          <t>CEREAL</t>
         </is>
       </c>
     </row>
@@ -54175,7 +54135,7 @@
       </c>
       <c r="G893" s="1" t="inlineStr">
         <is>
-          <t>Rokhaya SANE</t>
+          <t>Rokhaya DIENG</t>
         </is>
       </c>
       <c r="H893" s="1"/>
@@ -54185,10 +54145,10 @@
         </is>
       </c>
       <c r="J893" s="1" t="n">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="K893" s="1" t="n">
-        <v>4500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="L893" s="1" t="n">
         <v>0.0</v>
@@ -54198,7 +54158,7 @@
       </c>
       <c r="N893" s="1"/>
       <c r="O893" s="1" t="n">
-        <v>579.0</v>
+        <v>593.0</v>
       </c>
       <c r="P893" s="1" t="inlineStr">
         <is>
@@ -54240,20 +54200,20 @@
       </c>
       <c r="G894" s="1" t="inlineStr">
         <is>
-          <t>Rokhaya SANE</t>
+          <t>Marie BIAYE</t>
         </is>
       </c>
       <c r="H894" s="1"/>
       <c r="I894" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior BLE cereal 230g x 12 sachet</t>
+          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
         </is>
       </c>
       <c r="J894" s="1" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="K894" s="1" t="n">
-        <v>11250.0</v>
+        <v>4500.0</v>
       </c>
       <c r="L894" s="1" t="n">
         <v>0.0</v>
@@ -54263,7 +54223,7 @@
       </c>
       <c r="N894" s="1"/>
       <c r="O894" s="1" t="n">
-        <v>580.0</v>
+        <v>594.0</v>
       </c>
       <c r="P894" s="1" t="inlineStr">
         <is>
@@ -54305,7 +54265,7 @@
       </c>
       <c r="G895" s="1" t="inlineStr">
         <is>
-          <t>Rokhaya SANE</t>
+          <t>Marie BIAYE</t>
         </is>
       </c>
       <c r="H895" s="1"/>
@@ -54315,10 +54275,10 @@
         </is>
       </c>
       <c r="J895" s="1" t="n">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="K895" s="1" t="n">
-        <v>4500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="L895" s="1" t="n">
         <v>0.0</v>
@@ -54328,7 +54288,7 @@
       </c>
       <c r="N895" s="1"/>
       <c r="O895" s="1" t="n">
-        <v>581.0</v>
+        <v>595.0</v>
       </c>
       <c r="P895" s="1" t="inlineStr">
         <is>
@@ -54370,20 +54330,20 @@
       </c>
       <c r="G896" s="1" t="inlineStr">
         <is>
-          <t>Ndeye Fatou GUEYE</t>
+          <t>Kine GUEYE</t>
         </is>
       </c>
       <c r="H896" s="1"/>
       <c r="I896" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior mais cereal 50g x 10 x 8 sachet</t>
+          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
         </is>
       </c>
       <c r="J896" s="1" t="n">
-        <v>0.375</v>
+        <v>0.41666666</v>
       </c>
       <c r="K896" s="1" t="n">
-        <v>5625.0</v>
+        <v>3750.0</v>
       </c>
       <c r="L896" s="1" t="n">
         <v>0.0</v>
@@ -54393,7 +54353,7 @@
       </c>
       <c r="N896" s="1"/>
       <c r="O896" s="1" t="n">
-        <v>582.0</v>
+        <v>596.0</v>
       </c>
       <c r="P896" s="1" t="inlineStr">
         <is>
@@ -54435,20 +54395,20 @@
       </c>
       <c r="G897" s="1" t="inlineStr">
         <is>
-          <t>Ndeye Fatou GUEYE</t>
+          <t>Khady TALL</t>
         </is>
       </c>
       <c r="H897" s="1"/>
       <c r="I897" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
+          <t>Kamlac Junior mais cereal 50g x 10 x 8 sachet</t>
         </is>
       </c>
       <c r="J897" s="1" t="n">
-        <v>0.6666667</v>
+        <v>0.125</v>
       </c>
       <c r="K897" s="1" t="n">
-        <v>6000.0</v>
+        <v>1875.0</v>
       </c>
       <c r="L897" s="1" t="n">
         <v>0.0</v>
@@ -54458,7 +54418,7 @@
       </c>
       <c r="N897" s="1"/>
       <c r="O897" s="1" t="n">
-        <v>583.0</v>
+        <v>597.0</v>
       </c>
       <c r="P897" s="1" t="inlineStr">
         <is>
@@ -54500,13 +54460,13 @@
       </c>
       <c r="G898" s="1" t="inlineStr">
         <is>
-          <t>Ndeye Fatou GUEYE</t>
+          <t>Khady TALL</t>
         </is>
       </c>
       <c r="H898" s="1"/>
       <c r="I898" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior BLE cereal 230g x 12 sachet</t>
+          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
         </is>
       </c>
       <c r="J898" s="1" t="n">
@@ -54523,7 +54483,7 @@
       </c>
       <c r="N898" s="1"/>
       <c r="O898" s="1" t="n">
-        <v>584.0</v>
+        <v>598.0</v>
       </c>
       <c r="P898" s="1" t="inlineStr">
         <is>
@@ -54565,20 +54525,20 @@
       </c>
       <c r="G899" s="1" t="inlineStr">
         <is>
-          <t>Oumou DIALLO</t>
+          <t>Khady TALL</t>
         </is>
       </c>
       <c r="H899" s="1"/>
       <c r="I899" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
+          <t>Kamlac Junior BLE cereal 50g x 10 x 8 sachet</t>
         </is>
       </c>
       <c r="J899" s="1" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="K899" s="1" t="n">
-        <v>4500.0</v>
+        <v>3750.0</v>
       </c>
       <c r="L899" s="1" t="n">
         <v>0.0</v>
@@ -54588,7 +54548,7 @@
       </c>
       <c r="N899" s="1"/>
       <c r="O899" s="1" t="n">
-        <v>585.0</v>
+        <v>599.0</v>
       </c>
       <c r="P899" s="1" t="inlineStr">
         <is>
@@ -54620,30 +54580,22 @@
       </c>
       <c r="E900" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
-        </is>
-      </c>
-      <c r="F900" s="1" t="inlineStr">
-        <is>
-          <t>PIKINE</t>
-        </is>
-      </c>
-      <c r="G900" s="1" t="inlineStr">
-        <is>
-          <t>Oumou DIALLO</t>
-        </is>
-      </c>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F900" s="1"/>
+      <c r="G900" s="1"/>
       <c r="H900" s="1"/>
       <c r="I900" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
+          <t>Kamlac Junior BLE cereal 230g x 12 sachet</t>
         </is>
       </c>
       <c r="J900" s="1" t="n">
-        <v>1.0</v>
+        <v>11.5</v>
       </c>
       <c r="K900" s="1" t="n">
-        <v>9000.0</v>
+        <v>103500.0</v>
       </c>
       <c r="L900" s="1" t="n">
         <v>0.0</v>
@@ -54653,18 +54605,14 @@
       </c>
       <c r="N900" s="1"/>
       <c r="O900" s="1" t="n">
-        <v>586.0</v>
+        <v>600.0</v>
       </c>
       <c r="P900" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q900" s="1" t="inlineStr">
-        <is>
-          <t>CEREAL</t>
-        </is>
-      </c>
+      <c r="Q900" s="1"/>
     </row>
     <row r="901">
       <c r="A901" s="2" t="n">
@@ -54685,30 +54633,22 @@
       </c>
       <c r="E901" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
-        </is>
-      </c>
-      <c r="F901" s="1" t="inlineStr">
-        <is>
-          <t>PIKINE</t>
-        </is>
-      </c>
-      <c r="G901" s="1" t="inlineStr">
-        <is>
-          <t>Safietou SENE</t>
-        </is>
-      </c>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F901" s="1"/>
+      <c r="G901" s="1"/>
       <c r="H901" s="1"/>
       <c r="I901" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
+          <t>Kamlac Junior BLE cereal 50g x 10 x 8 sachet</t>
         </is>
       </c>
       <c r="J901" s="1" t="n">
-        <v>1.0</v>
+        <v>2.375</v>
       </c>
       <c r="K901" s="1" t="n">
-        <v>9000.0</v>
+        <v>35625.0</v>
       </c>
       <c r="L901" s="1" t="n">
         <v>0.0</v>
@@ -54718,18 +54658,14 @@
       </c>
       <c r="N901" s="1"/>
       <c r="O901" s="1" t="n">
-        <v>587.0</v>
+        <v>601.0</v>
       </c>
       <c r="P901" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q901" s="1" t="inlineStr">
-        <is>
-          <t>CEREAL</t>
-        </is>
-      </c>
+      <c r="Q901" s="1"/>
     </row>
     <row r="902">
       <c r="A902" s="2" t="n">
@@ -54750,19 +54686,11 @@
       </c>
       <c r="E902" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
-        </is>
-      </c>
-      <c r="F902" s="1" t="inlineStr">
-        <is>
-          <t>PIKINE</t>
-        </is>
-      </c>
-      <c r="G902" s="1" t="inlineStr">
-        <is>
-          <t>Anta DIOP</t>
-        </is>
-      </c>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F902" s="1"/>
+      <c r="G902" s="1"/>
       <c r="H902" s="1"/>
       <c r="I902" s="1" t="inlineStr">
         <is>
@@ -54770,10 +54698,10 @@
         </is>
       </c>
       <c r="J902" s="1" t="n">
-        <v>1.0</v>
+        <v>1.0833334</v>
       </c>
       <c r="K902" s="1" t="n">
-        <v>9000.0</v>
+        <v>9750.0</v>
       </c>
       <c r="L902" s="1" t="n">
         <v>0.0</v>
@@ -54783,18 +54711,14 @@
       </c>
       <c r="N902" s="1"/>
       <c r="O902" s="1" t="n">
-        <v>588.0</v>
+        <v>602.0</v>
       </c>
       <c r="P902" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q902" s="1" t="inlineStr">
-        <is>
-          <t>CEREAL</t>
-        </is>
-      </c>
+      <c r="Q902" s="1"/>
     </row>
     <row r="903">
       <c r="A903" s="2" t="n">
@@ -54815,30 +54739,22 @@
       </c>
       <c r="E903" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
-        </is>
-      </c>
-      <c r="F903" s="1" t="inlineStr">
-        <is>
-          <t>PIKINE</t>
-        </is>
-      </c>
-      <c r="G903" s="1" t="inlineStr">
-        <is>
-          <t>Anta DIOP</t>
-        </is>
-      </c>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F903" s="1"/>
+      <c r="G903" s="1"/>
       <c r="H903" s="1"/>
       <c r="I903" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
+          <t>Kamlac Junior mais cereal 50g x 10 x 8 sachet</t>
         </is>
       </c>
       <c r="J903" s="1" t="n">
-        <v>0.6666667</v>
+        <v>5.75</v>
       </c>
       <c r="K903" s="1" t="n">
-        <v>6000.0</v>
+        <v>86250.0</v>
       </c>
       <c r="L903" s="1" t="n">
         <v>0.0</v>
@@ -54848,18 +54764,14 @@
       </c>
       <c r="N903" s="1"/>
       <c r="O903" s="1" t="n">
-        <v>589.0</v>
+        <v>603.0</v>
       </c>
       <c r="P903" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q903" s="1" t="inlineStr">
-        <is>
-          <t>CEREAL</t>
-        </is>
-      </c>
+      <c r="Q903" s="1"/>
     </row>
     <row r="904">
       <c r="A904" s="2" t="n">
@@ -54880,30 +54792,22 @@
       </c>
       <c r="E904" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
-        </is>
-      </c>
-      <c r="F904" s="1" t="inlineStr">
-        <is>
-          <t>PIKINE</t>
-        </is>
-      </c>
-      <c r="G904" s="1" t="inlineStr">
-        <is>
-          <t>Sira Soumare</t>
-        </is>
-      </c>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F904" s="1"/>
+      <c r="G904" s="1"/>
       <c r="H904" s="1"/>
       <c r="I904" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior mais cereal 50g x 10 x 8 sachet</t>
+          <t>Jus Lido</t>
         </is>
       </c>
       <c r="J904" s="1" t="n">
-        <v>0.25</v>
+        <v>56.416668</v>
       </c>
       <c r="K904" s="1" t="n">
-        <v>3750.0</v>
+        <v>620583.3</v>
       </c>
       <c r="L904" s="1" t="n">
         <v>0.0</v>
@@ -54913,18 +54817,14 @@
       </c>
       <c r="N904" s="1"/>
       <c r="O904" s="1" t="n">
-        <v>590.0</v>
+        <v>604.0</v>
       </c>
       <c r="P904" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q904" s="1" t="inlineStr">
-        <is>
-          <t>CEREAL</t>
-        </is>
-      </c>
+      <c r="Q904" s="1"/>
     </row>
     <row r="905">
       <c r="A905" s="2" t="n">
@@ -54935,40 +54835,32 @@
       </c>
       <c r="C905" s="1" t="inlineStr">
         <is>
-          <t>TATA 3</t>
+          <t>TATA 1</t>
         </is>
       </c>
       <c r="D905" s="1" t="inlineStr">
         <is>
-          <t>IBRAHIMA COLY</t>
+          <t>DJIBRIL DIOP</t>
         </is>
       </c>
       <c r="E905" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
-        </is>
-      </c>
-      <c r="F905" s="1" t="inlineStr">
-        <is>
-          <t>PIKINE</t>
-        </is>
-      </c>
-      <c r="G905" s="1" t="inlineStr">
-        <is>
-          <t>Sira Soumare</t>
-        </is>
-      </c>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F905" s="1"/>
+      <c r="G905" s="1"/>
       <c r="H905" s="1"/>
       <c r="I905" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
+          <t>Lait Janus 18gx10</t>
         </is>
       </c>
       <c r="J905" s="1" t="n">
-        <v>0.8333333</v>
+        <v>0.3</v>
       </c>
       <c r="K905" s="1" t="n">
-        <v>7500.0</v>
+        <v>1800.0</v>
       </c>
       <c r="L905" s="1" t="n">
         <v>0.0</v>
@@ -54978,18 +54870,14 @@
       </c>
       <c r="N905" s="1"/>
       <c r="O905" s="1" t="n">
-        <v>591.0</v>
+        <v>533.0</v>
       </c>
       <c r="P905" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q905" s="1" t="inlineStr">
-        <is>
-          <t>CEREAL</t>
-        </is>
-      </c>
+      <c r="Q905" s="1"/>
     </row>
     <row r="906">
       <c r="A906" s="2" t="n">
@@ -55000,40 +54888,32 @@
       </c>
       <c r="C906" s="1" t="inlineStr">
         <is>
-          <t>TATA 3</t>
+          <t>TATA 1</t>
         </is>
       </c>
       <c r="D906" s="1" t="inlineStr">
         <is>
-          <t>IBRAHIMA COLY</t>
+          <t>DJIBRIL DIOP</t>
         </is>
       </c>
       <c r="E906" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
-        </is>
-      </c>
-      <c r="F906" s="1" t="inlineStr">
-        <is>
-          <t>PIKINE</t>
-        </is>
-      </c>
-      <c r="G906" s="1" t="inlineStr">
-        <is>
-          <t>Rokhaya DIENG</t>
-        </is>
-      </c>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F906" s="1"/>
+      <c r="G906" s="1"/>
       <c r="H906" s="1"/>
       <c r="I906" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
+          <t>Lait Janus 20gx10</t>
         </is>
       </c>
       <c r="J906" s="1" t="n">
-        <v>0.5</v>
+        <v>5.0</v>
       </c>
       <c r="K906" s="1" t="n">
-        <v>4500.0</v>
+        <v>30000.0</v>
       </c>
       <c r="L906" s="1" t="n">
         <v>0.0</v>
@@ -55043,18 +54923,14 @@
       </c>
       <c r="N906" s="1"/>
       <c r="O906" s="1" t="n">
-        <v>592.0</v>
+        <v>534.0</v>
       </c>
       <c r="P906" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q906" s="1" t="inlineStr">
-        <is>
-          <t>CEREAL</t>
-        </is>
-      </c>
+      <c r="Q906" s="1"/>
     </row>
     <row r="907">
       <c r="A907" s="2" t="n">
@@ -55065,40 +54941,32 @@
       </c>
       <c r="C907" s="1" t="inlineStr">
         <is>
-          <t>TATA 3</t>
+          <t>TATA 1</t>
         </is>
       </c>
       <c r="D907" s="1" t="inlineStr">
         <is>
-          <t>IBRAHIMA COLY</t>
+          <t>DJIBRIL DIOP</t>
         </is>
       </c>
       <c r="E907" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
-        </is>
-      </c>
-      <c r="F907" s="1" t="inlineStr">
-        <is>
-          <t>PIKINE</t>
-        </is>
-      </c>
-      <c r="G907" s="1" t="inlineStr">
-        <is>
-          <t>Rokhaya DIENG</t>
-        </is>
-      </c>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F907" s="1"/>
+      <c r="G907" s="1"/>
       <c r="H907" s="1"/>
       <c r="I907" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
+          <t>Lait Janus 400gx10</t>
         </is>
       </c>
       <c r="J907" s="1" t="n">
-        <v>1.0</v>
+        <v>0.6</v>
       </c>
       <c r="K907" s="1" t="n">
-        <v>9000.0</v>
+        <v>7200.0</v>
       </c>
       <c r="L907" s="1" t="n">
         <v>0.0</v>
@@ -55108,18 +54976,14 @@
       </c>
       <c r="N907" s="1"/>
       <c r="O907" s="1" t="n">
-        <v>593.0</v>
+        <v>535.0</v>
       </c>
       <c r="P907" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q907" s="1" t="inlineStr">
-        <is>
-          <t>CEREAL</t>
-        </is>
-      </c>
+      <c r="Q907" s="1"/>
     </row>
     <row r="908">
       <c r="A908" s="2" t="n">
@@ -55130,40 +54994,32 @@
       </c>
       <c r="C908" s="1" t="inlineStr">
         <is>
-          <t>TATA 3</t>
+          <t>TATA 1</t>
         </is>
       </c>
       <c r="D908" s="1" t="inlineStr">
         <is>
-          <t>IBRAHIMA COLY</t>
+          <t>DJIBRIL DIOP</t>
         </is>
       </c>
       <c r="E908" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
-        </is>
-      </c>
-      <c r="F908" s="1" t="inlineStr">
-        <is>
-          <t>PIKINE</t>
-        </is>
-      </c>
-      <c r="G908" s="1" t="inlineStr">
-        <is>
-          <t>Marie BIAYE</t>
-        </is>
-      </c>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F908" s="1"/>
+      <c r="G908" s="1"/>
       <c r="H908" s="1"/>
       <c r="I908" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
+          <t>Café Altimo pot 50g x 24 pcs</t>
         </is>
       </c>
       <c r="J908" s="1" t="n">
-        <v>0.5</v>
+        <v>16.958334</v>
       </c>
       <c r="K908" s="1" t="n">
-        <v>4500.0</v>
+        <v>296770.84</v>
       </c>
       <c r="L908" s="1" t="n">
         <v>0.0</v>
@@ -55173,18 +55029,14 @@
       </c>
       <c r="N908" s="1"/>
       <c r="O908" s="1" t="n">
-        <v>594.0</v>
+        <v>536.0</v>
       </c>
       <c r="P908" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q908" s="1" t="inlineStr">
-        <is>
-          <t>CEREAL</t>
-        </is>
-      </c>
+      <c r="Q908" s="1"/>
     </row>
     <row r="909">
       <c r="A909" s="2" t="n">
@@ -55195,40 +55047,32 @@
       </c>
       <c r="C909" s="1" t="inlineStr">
         <is>
-          <t>TATA 3</t>
+          <t>TATA 1</t>
         </is>
       </c>
       <c r="D909" s="1" t="inlineStr">
         <is>
-          <t>IBRAHIMA COLY</t>
+          <t>DJIBRIL DIOP</t>
         </is>
       </c>
       <c r="E909" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
-        </is>
-      </c>
-      <c r="F909" s="1" t="inlineStr">
-        <is>
-          <t>PIKINE</t>
-        </is>
-      </c>
-      <c r="G909" s="1" t="inlineStr">
-        <is>
-          <t>Marie BIAYE</t>
-        </is>
-      </c>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F909" s="1"/>
+      <c r="G909" s="1"/>
       <c r="H909" s="1"/>
       <c r="I909" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
+          <t>Café Altimo pot 100g x 24 pcs</t>
         </is>
       </c>
       <c r="J909" s="1" t="n">
-        <v>1.0</v>
+        <v>18.416666</v>
       </c>
       <c r="K909" s="1" t="n">
-        <v>9000.0</v>
+        <v>616958.3</v>
       </c>
       <c r="L909" s="1" t="n">
         <v>0.0</v>
@@ -55238,18 +55082,14 @@
       </c>
       <c r="N909" s="1"/>
       <c r="O909" s="1" t="n">
-        <v>595.0</v>
+        <v>537.0</v>
       </c>
       <c r="P909" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q909" s="1" t="inlineStr">
-        <is>
-          <t>CEREAL</t>
-        </is>
-      </c>
+      <c r="Q909" s="1"/>
     </row>
     <row r="910">
       <c r="A910" s="2" t="n">
@@ -55260,40 +55100,32 @@
       </c>
       <c r="C910" s="1" t="inlineStr">
         <is>
-          <t>TATA 3</t>
+          <t>TATA 1</t>
         </is>
       </c>
       <c r="D910" s="1" t="inlineStr">
         <is>
-          <t>IBRAHIMA COLY</t>
+          <t>DJIBRIL DIOP</t>
         </is>
       </c>
       <c r="E910" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
-        </is>
-      </c>
-      <c r="F910" s="1" t="inlineStr">
-        <is>
-          <t>PIKINE</t>
-        </is>
-      </c>
-      <c r="G910" s="1" t="inlineStr">
-        <is>
-          <t>Kine GUEYE</t>
-        </is>
-      </c>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F910" s="1"/>
+      <c r="G910" s="1"/>
       <c r="H910" s="1"/>
       <c r="I910" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
+          <t>Café Altimo pot 200g x 12 pcs</t>
         </is>
       </c>
       <c r="J910" s="1" t="n">
-        <v>0.41666666</v>
+        <v>12.5</v>
       </c>
       <c r="K910" s="1" t="n">
-        <v>3750.0</v>
+        <v>418750.0</v>
       </c>
       <c r="L910" s="1" t="n">
         <v>0.0</v>
@@ -55303,18 +55135,14 @@
       </c>
       <c r="N910" s="1"/>
       <c r="O910" s="1" t="n">
-        <v>596.0</v>
+        <v>538.0</v>
       </c>
       <c r="P910" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q910" s="1" t="inlineStr">
-        <is>
-          <t>CEREAL</t>
-        </is>
-      </c>
+      <c r="Q910" s="1"/>
     </row>
     <row r="911">
       <c r="A911" s="2" t="n">
@@ -55325,40 +55153,32 @@
       </c>
       <c r="C911" s="1" t="inlineStr">
         <is>
-          <t>TATA 3</t>
+          <t>TATA 1</t>
         </is>
       </c>
       <c r="D911" s="1" t="inlineStr">
         <is>
-          <t>IBRAHIMA COLY</t>
+          <t>DJIBRIL DIOP</t>
         </is>
       </c>
       <c r="E911" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
-        </is>
-      </c>
-      <c r="F911" s="1" t="inlineStr">
-        <is>
-          <t>PIKINE</t>
-        </is>
-      </c>
-      <c r="G911" s="1" t="inlineStr">
-        <is>
-          <t>Khady TALL</t>
-        </is>
-      </c>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F911" s="1"/>
+      <c r="G911" s="1"/>
       <c r="H911" s="1"/>
       <c r="I911" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior mais cereal 50g x 10 x 8 sachet</t>
+          <t>Café pot Refraish 50g</t>
         </is>
       </c>
       <c r="J911" s="1" t="n">
-        <v>0.125</v>
+        <v>15.5</v>
       </c>
       <c r="K911" s="1" t="n">
-        <v>1875.0</v>
+        <v>174375.0</v>
       </c>
       <c r="L911" s="1" t="n">
         <v>0.0</v>
@@ -55368,18 +55188,14 @@
       </c>
       <c r="N911" s="1"/>
       <c r="O911" s="1" t="n">
-        <v>597.0</v>
+        <v>539.0</v>
       </c>
       <c r="P911" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q911" s="1" t="inlineStr">
-        <is>
-          <t>CEREAL</t>
-        </is>
-      </c>
+      <c r="Q911" s="1"/>
     </row>
     <row r="912">
       <c r="A912" s="2" t="n">
@@ -55390,40 +55206,32 @@
       </c>
       <c r="C912" s="1" t="inlineStr">
         <is>
-          <t>TATA 3</t>
+          <t>TATA 1</t>
         </is>
       </c>
       <c r="D912" s="1" t="inlineStr">
         <is>
-          <t>IBRAHIMA COLY</t>
+          <t>DJIBRIL DIOP</t>
         </is>
       </c>
       <c r="E912" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
-        </is>
-      </c>
-      <c r="F912" s="1" t="inlineStr">
-        <is>
-          <t>PIKINE</t>
-        </is>
-      </c>
-      <c r="G912" s="1" t="inlineStr">
-        <is>
-          <t>Khady TALL</t>
-        </is>
-      </c>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F912" s="1"/>
+      <c r="G912" s="1"/>
       <c r="H912" s="1"/>
       <c r="I912" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
+          <t>Café Refraish 100g</t>
         </is>
       </c>
       <c r="J912" s="1" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="K912" s="1" t="n">
-        <v>9000.0</v>
+        <v>171000.0</v>
       </c>
       <c r="L912" s="1" t="n">
         <v>0.0</v>
@@ -55433,18 +55241,14 @@
       </c>
       <c r="N912" s="1"/>
       <c r="O912" s="1" t="n">
-        <v>598.0</v>
+        <v>540.0</v>
       </c>
       <c r="P912" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q912" s="1" t="inlineStr">
-        <is>
-          <t>CEREAL</t>
-        </is>
-      </c>
+      <c r="Q912" s="1"/>
     </row>
     <row r="913">
       <c r="A913" s="2" t="n">
@@ -55455,40 +55259,32 @@
       </c>
       <c r="C913" s="1" t="inlineStr">
         <is>
-          <t>TATA 3</t>
+          <t>TATA 1</t>
         </is>
       </c>
       <c r="D913" s="1" t="inlineStr">
         <is>
-          <t>IBRAHIMA COLY</t>
+          <t>DJIBRIL DIOP</t>
         </is>
       </c>
       <c r="E913" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
-        </is>
-      </c>
-      <c r="F913" s="1" t="inlineStr">
-        <is>
-          <t>PIKINE</t>
-        </is>
-      </c>
-      <c r="G913" s="1" t="inlineStr">
-        <is>
-          <t>Khady TALL</t>
-        </is>
-      </c>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F913" s="1"/>
+      <c r="G913" s="1"/>
       <c r="H913" s="1"/>
       <c r="I913" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior BLE cereal 50g x 10 x 8 sachet</t>
+          <t>Café pot Refraish 200g</t>
         </is>
       </c>
       <c r="J913" s="1" t="n">
-        <v>0.25</v>
+        <v>18.5</v>
       </c>
       <c r="K913" s="1" t="n">
-        <v>3750.0</v>
+        <v>360750.0</v>
       </c>
       <c r="L913" s="1" t="n">
         <v>0.0</v>
@@ -55498,18 +55294,14 @@
       </c>
       <c r="N913" s="1"/>
       <c r="O913" s="1" t="n">
-        <v>599.0</v>
+        <v>541.0</v>
       </c>
       <c r="P913" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q913" s="1" t="inlineStr">
-        <is>
-          <t>CEREAL</t>
-        </is>
-      </c>
+      <c r="Q913" s="1"/>
     </row>
     <row r="914">
       <c r="A914" s="2" t="n">
@@ -55520,12 +55312,12 @@
       </c>
       <c r="C914" s="1" t="inlineStr">
         <is>
-          <t>TATA 3</t>
+          <t>TATA 1</t>
         </is>
       </c>
       <c r="D914" s="1" t="inlineStr">
         <is>
-          <t>IBRAHIMA COLY</t>
+          <t>DJIBRIL DIOP</t>
         </is>
       </c>
       <c r="E914" s="1" t="inlineStr">
@@ -55538,14 +55330,14 @@
       <c r="H914" s="1"/>
       <c r="I914" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior BLE cereal 230g x 12 sachet</t>
+          <t>Café stick Refraish 1,5gx09boites</t>
         </is>
       </c>
       <c r="J914" s="1" t="n">
-        <v>11.5</v>
+        <v>5.6666665</v>
       </c>
       <c r="K914" s="1" t="n">
-        <v>103500.0</v>
+        <v>147333.33</v>
       </c>
       <c r="L914" s="1" t="n">
         <v>0.0</v>
@@ -55555,7 +55347,7 @@
       </c>
       <c r="N914" s="1"/>
       <c r="O914" s="1" t="n">
-        <v>600.0</v>
+        <v>542.0</v>
       </c>
       <c r="P914" s="1" t="inlineStr">
         <is>
@@ -55573,12 +55365,12 @@
       </c>
       <c r="C915" s="1" t="inlineStr">
         <is>
-          <t>TATA 3</t>
+          <t>TATA 1</t>
         </is>
       </c>
       <c r="D915" s="1" t="inlineStr">
         <is>
-          <t>IBRAHIMA COLY</t>
+          <t>DJIBRIL DIOP</t>
         </is>
       </c>
       <c r="E915" s="1" t="inlineStr">
@@ -55591,14 +55383,14 @@
       <c r="H915" s="1"/>
       <c r="I915" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior BLE cereal 50g x 10 x 8 sachet</t>
+          <t>Kamlac évaporé 48x160g</t>
         </is>
       </c>
       <c r="J915" s="1" t="n">
-        <v>2.375</v>
+        <v>6.5</v>
       </c>
       <c r="K915" s="1" t="n">
-        <v>35625.0</v>
+        <v>58500.0</v>
       </c>
       <c r="L915" s="1" t="n">
         <v>0.0</v>
@@ -55608,7 +55400,7 @@
       </c>
       <c r="N915" s="1"/>
       <c r="O915" s="1" t="n">
-        <v>601.0</v>
+        <v>543.0</v>
       </c>
       <c r="P915" s="1" t="inlineStr">
         <is>
@@ -55626,12 +55418,12 @@
       </c>
       <c r="C916" s="1" t="inlineStr">
         <is>
-          <t>TATA 3</t>
+          <t>TATA 1</t>
         </is>
       </c>
       <c r="D916" s="1" t="inlineStr">
         <is>
-          <t>IBRAHIMA COLY</t>
+          <t>DJIBRIL DIOP</t>
         </is>
       </c>
       <c r="E916" s="1" t="inlineStr">
@@ -55644,14 +55436,14 @@
       <c r="H916" s="1"/>
       <c r="I916" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior mais cereal 230g x 12 sachet</t>
+          <t>Cafe au Lait 3-en-1</t>
         </is>
       </c>
       <c r="J916" s="1" t="n">
-        <v>1.0833334</v>
+        <v>12.4</v>
       </c>
       <c r="K916" s="1" t="n">
-        <v>9750.0</v>
+        <v>55800.0</v>
       </c>
       <c r="L916" s="1" t="n">
         <v>0.0</v>
@@ -55661,7 +55453,7 @@
       </c>
       <c r="N916" s="1"/>
       <c r="O916" s="1" t="n">
-        <v>602.0</v>
+        <v>544.0</v>
       </c>
       <c r="P916" s="1" t="inlineStr">
         <is>
@@ -55679,12 +55471,12 @@
       </c>
       <c r="C917" s="1" t="inlineStr">
         <is>
-          <t>TATA 3</t>
+          <t>TATA 1</t>
         </is>
       </c>
       <c r="D917" s="1" t="inlineStr">
         <is>
-          <t>IBRAHIMA COLY</t>
+          <t>DJIBRIL DIOP</t>
         </is>
       </c>
       <c r="E917" s="1" t="inlineStr">
@@ -55697,14 +55489,14 @@
       <c r="H917" s="1"/>
       <c r="I917" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Junior mais cereal 50g x 10 x 8 sachet</t>
+          <t>Chocolat 3-en-1 30x120 pcs</t>
         </is>
       </c>
       <c r="J917" s="1" t="n">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="K917" s="1" t="n">
-        <v>86250.0</v>
+        <v>46200.0</v>
       </c>
       <c r="L917" s="1" t="n">
         <v>0.0</v>
@@ -55714,7 +55506,7 @@
       </c>
       <c r="N917" s="1"/>
       <c r="O917" s="1" t="n">
-        <v>603.0</v>
+        <v>545.0</v>
       </c>
       <c r="P917" s="1" t="inlineStr">
         <is>
@@ -55732,12 +55524,12 @@
       </c>
       <c r="C918" s="1" t="inlineStr">
         <is>
-          <t>TATA 3</t>
+          <t>TATA 1</t>
         </is>
       </c>
       <c r="D918" s="1" t="inlineStr">
         <is>
-          <t>IBRAHIMA COLY</t>
+          <t>DJIBRIL DIOP</t>
         </is>
       </c>
       <c r="E918" s="1" t="inlineStr">
@@ -55750,14 +55542,14 @@
       <c r="H918" s="1"/>
       <c r="I918" s="1" t="inlineStr">
         <is>
-          <t>Jus Lido</t>
+          <t>KamLac Lait concentré sucré 24x1kg</t>
         </is>
       </c>
       <c r="J918" s="1" t="n">
-        <v>56.416668</v>
+        <v>1.5</v>
       </c>
       <c r="K918" s="1" t="n">
-        <v>620583.3</v>
+        <v>39750.0</v>
       </c>
       <c r="L918" s="1" t="n">
         <v>0.0</v>
@@ -55767,7 +55559,7 @@
       </c>
       <c r="N918" s="1"/>
       <c r="O918" s="1" t="n">
-        <v>604.0</v>
+        <v>546.0</v>
       </c>
       <c r="P918" s="1" t="inlineStr">
         <is>
@@ -55803,14 +55595,14 @@
       <c r="H919" s="1"/>
       <c r="I919" s="1" t="inlineStr">
         <is>
-          <t>Lait Janus 18gx10</t>
+          <t>Kamlac Thé 7g</t>
         </is>
       </c>
       <c r="J919" s="1" t="n">
-        <v>0.3</v>
+        <v>14.0</v>
       </c>
       <c r="K919" s="1" t="n">
-        <v>1800.0</v>
+        <v>161000.0</v>
       </c>
       <c r="L919" s="1" t="n">
         <v>0.0</v>
@@ -55820,7 +55612,7 @@
       </c>
       <c r="N919" s="1"/>
       <c r="O919" s="1" t="n">
-        <v>533.0</v>
+        <v>547.0</v>
       </c>
       <c r="P919" s="1" t="inlineStr">
         <is>
@@ -55856,14 +55648,14 @@
       <c r="H920" s="1"/>
       <c r="I920" s="1" t="inlineStr">
         <is>
-          <t>Lait Janus 20gx10</t>
+          <t>Chocolat Orange 400g x12 pcs</t>
         </is>
       </c>
       <c r="J920" s="1" t="n">
-        <v>5.0</v>
+        <v>2.8333333</v>
       </c>
       <c r="K920" s="1" t="n">
-        <v>30000.0</v>
+        <v>51000.0</v>
       </c>
       <c r="L920" s="1" t="n">
         <v>0.0</v>
@@ -55873,7 +55665,7 @@
       </c>
       <c r="N920" s="1"/>
       <c r="O920" s="1" t="n">
-        <v>534.0</v>
+        <v>548.0</v>
       </c>
       <c r="P920" s="1" t="inlineStr">
         <is>
@@ -55909,14 +55701,14 @@
       <c r="H921" s="1"/>
       <c r="I921" s="1" t="inlineStr">
         <is>
-          <t>Lait Janus 400gx10</t>
+          <t>Chocolat transparent 400gx12pcs</t>
         </is>
       </c>
       <c r="J921" s="1" t="n">
-        <v>0.6</v>
+        <v>11.666667</v>
       </c>
       <c r="K921" s="1" t="n">
-        <v>7200.0</v>
+        <v>145833.33</v>
       </c>
       <c r="L921" s="1" t="n">
         <v>0.0</v>
@@ -55926,7 +55718,7 @@
       </c>
       <c r="N921" s="1"/>
       <c r="O921" s="1" t="n">
-        <v>535.0</v>
+        <v>549.0</v>
       </c>
       <c r="P921" s="1" t="inlineStr">
         <is>
@@ -55962,14 +55754,14 @@
       <c r="H922" s="1"/>
       <c r="I922" s="1" t="inlineStr">
         <is>
-          <t>Café Altimo pot 50g x 24 pcs</t>
+          <t>Chocolat jaune 200g x 24 pcs</t>
         </is>
       </c>
       <c r="J922" s="1" t="n">
-        <v>16.958334</v>
+        <v>16.0</v>
       </c>
       <c r="K922" s="1" t="n">
-        <v>296770.84</v>
+        <v>248000.0</v>
       </c>
       <c r="L922" s="1" t="n">
         <v>0.0</v>
@@ -55979,7 +55771,7 @@
       </c>
       <c r="N922" s="1"/>
       <c r="O922" s="1" t="n">
-        <v>536.0</v>
+        <v>550.0</v>
       </c>
       <c r="P922" s="1" t="inlineStr">
         <is>
@@ -56015,14 +55807,14 @@
       <c r="H923" s="1"/>
       <c r="I923" s="1" t="inlineStr">
         <is>
-          <t>Café Altimo pot 100g x 24 pcs</t>
+          <t>Chocolat jaune 400g x 12 pcs</t>
         </is>
       </c>
       <c r="J923" s="1" t="n">
-        <v>18.416666</v>
+        <v>10.166667</v>
       </c>
       <c r="K923" s="1" t="n">
-        <v>616958.3</v>
+        <v>157583.33</v>
       </c>
       <c r="L923" s="1" t="n">
         <v>0.0</v>
@@ -56032,7 +55824,7 @@
       </c>
       <c r="N923" s="1"/>
       <c r="O923" s="1" t="n">
-        <v>537.0</v>
+        <v>551.0</v>
       </c>
       <c r="P923" s="1" t="inlineStr">
         <is>
@@ -56068,14 +55860,14 @@
       <c r="H924" s="1"/>
       <c r="I924" s="1" t="inlineStr">
         <is>
-          <t>Café Altimo pot 200g x 12 pcs</t>
+          <t>Chocolat Orange 10 g x 60 pcs x 6 boites</t>
         </is>
       </c>
       <c r="J924" s="1" t="n">
-        <v>12.5</v>
+        <v>4.3333335</v>
       </c>
       <c r="K924" s="1" t="n">
-        <v>418750.0</v>
+        <v>52000.0</v>
       </c>
       <c r="L924" s="1" t="n">
         <v>0.0</v>
@@ -56085,7 +55877,7 @@
       </c>
       <c r="N924" s="1"/>
       <c r="O924" s="1" t="n">
-        <v>538.0</v>
+        <v>552.0</v>
       </c>
       <c r="P924" s="1" t="inlineStr">
         <is>
@@ -56113,39 +55905,55 @@
       </c>
       <c r="E925" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
-        </is>
-      </c>
-      <c r="F925" s="1"/>
-      <c r="G925" s="1"/>
-      <c r="H925" s="1"/>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F925" s="1" t="inlineStr">
+        <is>
+          <t>YEUMBEUL</t>
+        </is>
+      </c>
+      <c r="G925" s="1" t="inlineStr">
+        <is>
+          <t>Autre</t>
+        </is>
+      </c>
+      <c r="H925" s="1" t="inlineStr">
+        <is>
+          <t>Nogaye ndiaye</t>
+        </is>
+      </c>
       <c r="I925" s="1" t="inlineStr">
         <is>
           <t>Café pot Refraish 50g</t>
         </is>
       </c>
       <c r="J925" s="1" t="n">
-        <v>15.5</v>
+        <v>2.0</v>
       </c>
       <c r="K925" s="1" t="n">
-        <v>174375.0</v>
+        <v>22500.0</v>
       </c>
       <c r="L925" s="1" t="n">
-        <v>0.0</v>
+        <v>56000.0</v>
       </c>
       <c r="M925" s="1" t="n">
-        <v>0.0</v>
+        <v>15000.0</v>
       </c>
       <c r="N925" s="1"/>
       <c r="O925" s="1" t="n">
-        <v>539.0</v>
+        <v>553.0</v>
       </c>
       <c r="P925" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q925" s="1"/>
+      <c r="Q925" s="1" t="inlineStr">
+        <is>
+          <t>REFRAISH</t>
+        </is>
+      </c>
     </row>
     <row r="926">
       <c r="A926" s="2" t="n">
@@ -56166,22 +55974,34 @@
       </c>
       <c r="E926" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
-        </is>
-      </c>
-      <c r="F926" s="1"/>
-      <c r="G926" s="1"/>
-      <c r="H926" s="1"/>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F926" s="1" t="inlineStr">
+        <is>
+          <t>YEUMBEUL</t>
+        </is>
+      </c>
+      <c r="G926" s="1" t="inlineStr">
+        <is>
+          <t>Autre</t>
+        </is>
+      </c>
+      <c r="H926" s="1" t="inlineStr">
+        <is>
+          <t>Nogaye ndiaye</t>
+        </is>
+      </c>
       <c r="I926" s="1" t="inlineStr">
         <is>
-          <t>Café Refraish 100g</t>
+          <t>Café stick Refraish 1,5gx09boites</t>
         </is>
       </c>
       <c r="J926" s="1" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
       <c r="K926" s="1" t="n">
-        <v>171000.0</v>
+        <v>52000.0</v>
       </c>
       <c r="L926" s="1" t="n">
         <v>0.0</v>
@@ -56191,14 +56011,18 @@
       </c>
       <c r="N926" s="1"/>
       <c r="O926" s="1" t="n">
-        <v>540.0</v>
+        <v>554.0</v>
       </c>
       <c r="P926" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q926" s="1"/>
+      <c r="Q926" s="1" t="inlineStr">
+        <is>
+          <t>REFRAISH</t>
+        </is>
+      </c>
     </row>
     <row r="927">
       <c r="A927" s="2" t="n">
@@ -56219,22 +56043,34 @@
       </c>
       <c r="E927" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
-        </is>
-      </c>
-      <c r="F927" s="1"/>
-      <c r="G927" s="1"/>
-      <c r="H927" s="1"/>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F927" s="1" t="inlineStr">
+        <is>
+          <t>YEUMBEUL</t>
+        </is>
+      </c>
+      <c r="G927" s="1" t="inlineStr">
+        <is>
+          <t>Autre</t>
+        </is>
+      </c>
+      <c r="H927" s="1" t="inlineStr">
+        <is>
+          <t>Nogaye ndiaye</t>
+        </is>
+      </c>
       <c r="I927" s="1" t="inlineStr">
         <is>
           <t>Café pot Refraish 200g</t>
         </is>
       </c>
       <c r="J927" s="1" t="n">
-        <v>18.5</v>
+        <v>0.5</v>
       </c>
       <c r="K927" s="1" t="n">
-        <v>360750.0</v>
+        <v>9750.0</v>
       </c>
       <c r="L927" s="1" t="n">
         <v>0.0</v>
@@ -56244,14 +56080,18 @@
       </c>
       <c r="N927" s="1"/>
       <c r="O927" s="1" t="n">
-        <v>541.0</v>
+        <v>555.0</v>
       </c>
       <c r="P927" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q927" s="1"/>
+      <c r="Q927" s="1" t="inlineStr">
+        <is>
+          <t>REFRAISH</t>
+        </is>
+      </c>
     </row>
     <row r="928">
       <c r="A928" s="2" t="n">
@@ -56272,11 +56112,19 @@
       </c>
       <c r="E928" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
-        </is>
-      </c>
-      <c r="F928" s="1"/>
-      <c r="G928" s="1"/>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F928" s="1" t="inlineStr">
+        <is>
+          <t>YEUMBEUL</t>
+        </is>
+      </c>
+      <c r="G928" s="1" t="inlineStr">
+        <is>
+          <t>Mariama SADIO</t>
+        </is>
+      </c>
       <c r="H928" s="1"/>
       <c r="I928" s="1" t="inlineStr">
         <is>
@@ -56284,10 +56132,10 @@
         </is>
       </c>
       <c r="J928" s="1" t="n">
-        <v>5.6666665</v>
+        <v>1.6666666</v>
       </c>
       <c r="K928" s="1" t="n">
-        <v>147333.33</v>
+        <v>43333.332</v>
       </c>
       <c r="L928" s="1" t="n">
         <v>0.0</v>
@@ -56297,14 +56145,18 @@
       </c>
       <c r="N928" s="1"/>
       <c r="O928" s="1" t="n">
-        <v>542.0</v>
+        <v>556.0</v>
       </c>
       <c r="P928" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q928" s="1"/>
+      <c r="Q928" s="1" t="inlineStr">
+        <is>
+          <t>REFRAISH</t>
+        </is>
+      </c>
     </row>
     <row r="929">
       <c r="A929" s="2" t="n">
@@ -56325,22 +56177,30 @@
       </c>
       <c r="E929" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
-        </is>
-      </c>
-      <c r="F929" s="1"/>
-      <c r="G929" s="1"/>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F929" s="1" t="inlineStr">
+        <is>
+          <t>YEUMBEUL</t>
+        </is>
+      </c>
+      <c r="G929" s="1" t="inlineStr">
+        <is>
+          <t>Mariama SADIO</t>
+        </is>
+      </c>
       <c r="H929" s="1"/>
       <c r="I929" s="1" t="inlineStr">
         <is>
-          <t>Kamlac évaporé 48x160g</t>
+          <t>Café pot Refraish 200g</t>
         </is>
       </c>
       <c r="J929" s="1" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="K929" s="1" t="n">
-        <v>58500.0</v>
+        <v>48750.0</v>
       </c>
       <c r="L929" s="1" t="n">
         <v>0.0</v>
@@ -56350,14 +56210,18 @@
       </c>
       <c r="N929" s="1"/>
       <c r="O929" s="1" t="n">
-        <v>543.0</v>
+        <v>557.0</v>
       </c>
       <c r="P929" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q929" s="1"/>
+      <c r="Q929" s="1" t="inlineStr">
+        <is>
+          <t>REFRAISH</t>
+        </is>
+      </c>
     </row>
     <row r="930">
       <c r="A930" s="2" t="n">
@@ -56378,22 +56242,30 @@
       </c>
       <c r="E930" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
-        </is>
-      </c>
-      <c r="F930" s="1"/>
-      <c r="G930" s="1"/>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F930" s="1" t="inlineStr">
+        <is>
+          <t>YEUMBEUL</t>
+        </is>
+      </c>
+      <c r="G930" s="1" t="inlineStr">
+        <is>
+          <t>Mariama SADIO</t>
+        </is>
+      </c>
       <c r="H930" s="1"/>
       <c r="I930" s="1" t="inlineStr">
         <is>
-          <t>Cafe au Lait 3-en-1</t>
+          <t>Café pot Refraish 50g</t>
         </is>
       </c>
       <c r="J930" s="1" t="n">
-        <v>12.4</v>
+        <v>3.0</v>
       </c>
       <c r="K930" s="1" t="n">
-        <v>55800.0</v>
+        <v>33750.0</v>
       </c>
       <c r="L930" s="1" t="n">
         <v>0.0</v>
@@ -56403,14 +56275,18 @@
       </c>
       <c r="N930" s="1"/>
       <c r="O930" s="1" t="n">
-        <v>544.0</v>
+        <v>558.0</v>
       </c>
       <c r="P930" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q930" s="1"/>
+      <c r="Q930" s="1" t="inlineStr">
+        <is>
+          <t>REFRAISH</t>
+        </is>
+      </c>
     </row>
     <row r="931">
       <c r="A931" s="2" t="n">
@@ -56431,22 +56307,30 @@
       </c>
       <c r="E931" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
-        </is>
-      </c>
-      <c r="F931" s="1"/>
-      <c r="G931" s="1"/>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F931" s="1" t="inlineStr">
+        <is>
+          <t>YEUMBEUL</t>
+        </is>
+      </c>
+      <c r="G931" s="1" t="inlineStr">
+        <is>
+          <t>Anta CISSE</t>
+        </is>
+      </c>
       <c r="H931" s="1"/>
       <c r="I931" s="1" t="inlineStr">
         <is>
-          <t>Chocolat 3-en-1 30x120 pcs</t>
+          <t>Café pot Refraish 200g</t>
         </is>
       </c>
       <c r="J931" s="1" t="n">
-        <v>4.2</v>
+        <v>1.0</v>
       </c>
       <c r="K931" s="1" t="n">
-        <v>46200.0</v>
+        <v>19500.0</v>
       </c>
       <c r="L931" s="1" t="n">
         <v>0.0</v>
@@ -56456,14 +56340,18 @@
       </c>
       <c r="N931" s="1"/>
       <c r="O931" s="1" t="n">
-        <v>545.0</v>
+        <v>559.0</v>
       </c>
       <c r="P931" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q931" s="1"/>
+      <c r="Q931" s="1" t="inlineStr">
+        <is>
+          <t>REFRAISH</t>
+        </is>
+      </c>
     </row>
     <row r="932">
       <c r="A932" s="2" t="n">
@@ -56484,22 +56372,30 @@
       </c>
       <c r="E932" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
-        </is>
-      </c>
-      <c r="F932" s="1"/>
-      <c r="G932" s="1"/>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F932" s="1" t="inlineStr">
+        <is>
+          <t>YEUMBEUL</t>
+        </is>
+      </c>
+      <c r="G932" s="1" t="inlineStr">
+        <is>
+          <t>Anta CISSE</t>
+        </is>
+      </c>
       <c r="H932" s="1"/>
       <c r="I932" s="1" t="inlineStr">
         <is>
-          <t>KamLac Lait concentré sucré 24x1kg</t>
+          <t>Café pot Refraish 50g</t>
         </is>
       </c>
       <c r="J932" s="1" t="n">
-        <v>1.5</v>
+        <v>1.0</v>
       </c>
       <c r="K932" s="1" t="n">
-        <v>39750.0</v>
+        <v>11250.0</v>
       </c>
       <c r="L932" s="1" t="n">
         <v>0.0</v>
@@ -56509,14 +56405,18 @@
       </c>
       <c r="N932" s="1"/>
       <c r="O932" s="1" t="n">
-        <v>546.0</v>
+        <v>560.0</v>
       </c>
       <c r="P932" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q932" s="1"/>
+      <c r="Q932" s="1" t="inlineStr">
+        <is>
+          <t>REFRAISH</t>
+        </is>
+      </c>
     </row>
     <row r="933">
       <c r="A933" s="2" t="n">
@@ -56537,22 +56437,30 @@
       </c>
       <c r="E933" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
-        </is>
-      </c>
-      <c r="F933" s="1"/>
-      <c r="G933" s="1"/>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F933" s="1" t="inlineStr">
+        <is>
+          <t>YEUMBEUL</t>
+        </is>
+      </c>
+      <c r="G933" s="1" t="inlineStr">
+        <is>
+          <t>Anta CISSE</t>
+        </is>
+      </c>
       <c r="H933" s="1"/>
       <c r="I933" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Thé 7g</t>
+          <t>Café stick Refraish 1,5gx09boites</t>
         </is>
       </c>
       <c r="J933" s="1" t="n">
-        <v>14.0</v>
+        <v>6.4444447</v>
       </c>
       <c r="K933" s="1" t="n">
-        <v>161000.0</v>
+        <v>167555.56</v>
       </c>
       <c r="L933" s="1" t="n">
         <v>0.0</v>
@@ -56562,14 +56470,18 @@
       </c>
       <c r="N933" s="1"/>
       <c r="O933" s="1" t="n">
-        <v>547.0</v>
+        <v>561.0</v>
       </c>
       <c r="P933" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q933" s="1"/>
+      <c r="Q933" s="1" t="inlineStr">
+        <is>
+          <t>REFRAISH</t>
+        </is>
+      </c>
     </row>
     <row r="934">
       <c r="A934" s="2" t="n">
@@ -56590,22 +56502,30 @@
       </c>
       <c r="E934" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
-        </is>
-      </c>
-      <c r="F934" s="1"/>
-      <c r="G934" s="1"/>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F934" s="1" t="inlineStr">
+        <is>
+          <t>YEUMBEUL</t>
+        </is>
+      </c>
+      <c r="G934" s="1" t="inlineStr">
+        <is>
+          <t>Saly SEYDI</t>
+        </is>
+      </c>
       <c r="H934" s="1"/>
       <c r="I934" s="1" t="inlineStr">
         <is>
-          <t>Chocolat Orange 400g x12 pcs</t>
+          <t>Chocolat jaune 400g x 12 pcs</t>
         </is>
       </c>
       <c r="J934" s="1" t="n">
-        <v>2.8333333</v>
+        <v>0.16666667</v>
       </c>
       <c r="K934" s="1" t="n">
-        <v>51000.0</v>
+        <v>2583.3333</v>
       </c>
       <c r="L934" s="1" t="n">
         <v>0.0</v>
@@ -56615,14 +56535,18 @@
       </c>
       <c r="N934" s="1"/>
       <c r="O934" s="1" t="n">
-        <v>548.0</v>
+        <v>562.0</v>
       </c>
       <c r="P934" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q934" s="1"/>
+      <c r="Q934" s="1" t="inlineStr">
+        <is>
+          <t>CHOC TRANS</t>
+        </is>
+      </c>
     </row>
     <row r="935">
       <c r="A935" s="2" t="n">
@@ -56643,11 +56567,19 @@
       </c>
       <c r="E935" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
-        </is>
-      </c>
-      <c r="F935" s="1"/>
-      <c r="G935" s="1"/>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F935" s="1" t="inlineStr">
+        <is>
+          <t>YEUMBEUL</t>
+        </is>
+      </c>
+      <c r="G935" s="1" t="inlineStr">
+        <is>
+          <t>Dior</t>
+        </is>
+      </c>
       <c r="H935" s="1"/>
       <c r="I935" s="1" t="inlineStr">
         <is>
@@ -56655,10 +56587,10 @@
         </is>
       </c>
       <c r="J935" s="1" t="n">
-        <v>11.666667</v>
+        <v>0.25</v>
       </c>
       <c r="K935" s="1" t="n">
-        <v>145833.33</v>
+        <v>3125.0</v>
       </c>
       <c r="L935" s="1" t="n">
         <v>0.0</v>
@@ -56668,14 +56600,18 @@
       </c>
       <c r="N935" s="1"/>
       <c r="O935" s="1" t="n">
-        <v>549.0</v>
+        <v>563.0</v>
       </c>
       <c r="P935" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q935" s="1"/>
+      <c r="Q935" s="1" t="inlineStr">
+        <is>
+          <t>CHOC TRANS</t>
+        </is>
+      </c>
     </row>
     <row r="936">
       <c r="A936" s="2" t="n">
@@ -56696,22 +56632,30 @@
       </c>
       <c r="E936" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
-        </is>
-      </c>
-      <c r="F936" s="1"/>
-      <c r="G936" s="1"/>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F936" s="1" t="inlineStr">
+        <is>
+          <t>YEUMBEUL</t>
+        </is>
+      </c>
+      <c r="G936" s="1" t="inlineStr">
+        <is>
+          <t>Dior</t>
+        </is>
+      </c>
       <c r="H936" s="1"/>
       <c r="I936" s="1" t="inlineStr">
         <is>
-          <t>Chocolat jaune 200g x 24 pcs</t>
+          <t>Chocolat jaune 400g x 12 pcs</t>
         </is>
       </c>
       <c r="J936" s="1" t="n">
-        <v>16.0</v>
+        <v>0.25</v>
       </c>
       <c r="K936" s="1" t="n">
-        <v>248000.0</v>
+        <v>3875.0</v>
       </c>
       <c r="L936" s="1" t="n">
         <v>0.0</v>
@@ -56721,14 +56665,18 @@
       </c>
       <c r="N936" s="1"/>
       <c r="O936" s="1" t="n">
-        <v>550.0</v>
+        <v>564.0</v>
       </c>
       <c r="P936" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q936" s="1"/>
+      <c r="Q936" s="1" t="inlineStr">
+        <is>
+          <t>CHOC TRANS</t>
+        </is>
+      </c>
     </row>
     <row r="937">
       <c r="A937" s="2" t="n">
@@ -56749,22 +56697,30 @@
       </c>
       <c r="E937" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
-        </is>
-      </c>
-      <c r="F937" s="1"/>
-      <c r="G937" s="1"/>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F937" s="1" t="inlineStr">
+        <is>
+          <t>YEUMBEUL</t>
+        </is>
+      </c>
+      <c r="G937" s="1" t="inlineStr">
+        <is>
+          <t>Mariama BA</t>
+        </is>
+      </c>
       <c r="H937" s="1"/>
       <c r="I937" s="1" t="inlineStr">
         <is>
-          <t>Chocolat jaune 400g x 12 pcs</t>
+          <t>Café Altimo pot 100g x 24 pcs</t>
         </is>
       </c>
       <c r="J937" s="1" t="n">
-        <v>10.166667</v>
+        <v>0.5</v>
       </c>
       <c r="K937" s="1" t="n">
-        <v>157583.33</v>
+        <v>16750.0</v>
       </c>
       <c r="L937" s="1" t="n">
         <v>0.0</v>
@@ -56774,14 +56730,18 @@
       </c>
       <c r="N937" s="1"/>
       <c r="O937" s="1" t="n">
-        <v>551.0</v>
+        <v>565.0</v>
       </c>
       <c r="P937" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q937" s="1"/>
+      <c r="Q937" s="1" t="inlineStr">
+        <is>
+          <t>ALTIMO</t>
+        </is>
+      </c>
     </row>
     <row r="938">
       <c r="A938" s="2" t="n">
@@ -56802,22 +56762,30 @@
       </c>
       <c r="E938" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
-        </is>
-      </c>
-      <c r="F938" s="1"/>
-      <c r="G938" s="1"/>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F938" s="1" t="inlineStr">
+        <is>
+          <t>YEUMBEUL</t>
+        </is>
+      </c>
+      <c r="G938" s="1" t="inlineStr">
+        <is>
+          <t>Fatou THIOMBENE</t>
+        </is>
+      </c>
       <c r="H938" s="1"/>
       <c r="I938" s="1" t="inlineStr">
         <is>
-          <t>Chocolat Orange 10 g x 60 pcs x 6 boites</t>
+          <t>Café Altimo pot 50g x 24 pcs</t>
         </is>
       </c>
       <c r="J938" s="1" t="n">
-        <v>4.3333335</v>
+        <v>0.041666668</v>
       </c>
       <c r="K938" s="1" t="n">
-        <v>52000.0</v>
+        <v>729.1667</v>
       </c>
       <c r="L938" s="1" t="n">
         <v>0.0</v>
@@ -56827,14 +56795,18 @@
       </c>
       <c r="N938" s="1"/>
       <c r="O938" s="1" t="n">
-        <v>552.0</v>
+        <v>566.0</v>
       </c>
       <c r="P938" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q938" s="1"/>
+      <c r="Q938" s="1" t="inlineStr">
+        <is>
+          <t>ALTIMO</t>
+        </is>
+      </c>
     </row>
     <row r="939">
       <c r="A939" s="2" t="n">
@@ -56865,34 +56837,30 @@
       </c>
       <c r="G939" s="1" t="inlineStr">
         <is>
-          <t>Autre</t>
-        </is>
-      </c>
-      <c r="H939" s="1" t="inlineStr">
-        <is>
-          <t>Nogaye ndiaye</t>
-        </is>
-      </c>
+          <t>Ndeye DIONE</t>
+        </is>
+      </c>
+      <c r="H939" s="1"/>
       <c r="I939" s="1" t="inlineStr">
         <is>
-          <t>Café pot Refraish 50g</t>
+          <t>Café stick Altimo 1,5gx09boites</t>
         </is>
       </c>
       <c r="J939" s="1" t="n">
-        <v>2.0</v>
+        <v>0.5555556</v>
       </c>
       <c r="K939" s="1" t="n">
-        <v>22500.0</v>
+        <v>15555.556</v>
       </c>
       <c r="L939" s="1" t="n">
-        <v>56000.0</v>
+        <v>0.0</v>
       </c>
       <c r="M939" s="1" t="n">
-        <v>15000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N939" s="1"/>
       <c r="O939" s="1" t="n">
-        <v>553.0</v>
+        <v>567.0</v>
       </c>
       <c r="P939" s="1" t="inlineStr">
         <is>
@@ -56901,7 +56869,7 @@
       </c>
       <c r="Q939" s="1" t="inlineStr">
         <is>
-          <t>REFRAISH</t>
+          <t>ALTIMO</t>
         </is>
       </c>
     </row>
@@ -56934,24 +56902,20 @@
       </c>
       <c r="G940" s="1" t="inlineStr">
         <is>
-          <t>Autre</t>
-        </is>
-      </c>
-      <c r="H940" s="1" t="inlineStr">
-        <is>
-          <t>Nogaye ndiaye</t>
-        </is>
-      </c>
+          <t>Khady SANE</t>
+        </is>
+      </c>
+      <c r="H940" s="1"/>
       <c r="I940" s="1" t="inlineStr">
         <is>
-          <t>Café stick Refraish 1,5gx09boites</t>
+          <t>Café Altimo pot 100g x 24 pcs</t>
         </is>
       </c>
       <c r="J940" s="1" t="n">
-        <v>2.0</v>
+        <v>0.5</v>
       </c>
       <c r="K940" s="1" t="n">
-        <v>52000.0</v>
+        <v>16750.0</v>
       </c>
       <c r="L940" s="1" t="n">
         <v>0.0</v>
@@ -56961,7 +56925,7 @@
       </c>
       <c r="N940" s="1"/>
       <c r="O940" s="1" t="n">
-        <v>554.0</v>
+        <v>568.0</v>
       </c>
       <c r="P940" s="1" t="inlineStr">
         <is>
@@ -56970,7 +56934,7 @@
       </c>
       <c r="Q940" s="1" t="inlineStr">
         <is>
-          <t>REFRAISH</t>
+          <t>ALTIMO</t>
         </is>
       </c>
     </row>
@@ -57003,24 +56967,20 @@
       </c>
       <c r="G941" s="1" t="inlineStr">
         <is>
-          <t>Autre</t>
-        </is>
-      </c>
-      <c r="H941" s="1" t="inlineStr">
-        <is>
-          <t>Nogaye ndiaye</t>
-        </is>
-      </c>
+          <t>Adama DABO</t>
+        </is>
+      </c>
+      <c r="H941" s="1"/>
       <c r="I941" s="1" t="inlineStr">
         <is>
-          <t>Café pot Refraish 200g</t>
+          <t>Kamlac évaporé 48x160g</t>
         </is>
       </c>
       <c r="J941" s="1" t="n">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="K941" s="1" t="n">
-        <v>9750.0</v>
+        <v>9000.0</v>
       </c>
       <c r="L941" s="1" t="n">
         <v>0.0</v>
@@ -57030,7 +56990,7 @@
       </c>
       <c r="N941" s="1"/>
       <c r="O941" s="1" t="n">
-        <v>555.0</v>
+        <v>569.0</v>
       </c>
       <c r="P941" s="1" t="inlineStr">
         <is>
@@ -57039,7 +56999,7 @@
       </c>
       <c r="Q941" s="1" t="inlineStr">
         <is>
-          <t>REFRAISH</t>
+          <t>LAIT</t>
         </is>
       </c>
     </row>
@@ -57072,20 +57032,20 @@
       </c>
       <c r="G942" s="1" t="inlineStr">
         <is>
-          <t>Mariama SADIO</t>
+          <t>Adama DABO</t>
         </is>
       </c>
       <c r="H942" s="1"/>
       <c r="I942" s="1" t="inlineStr">
         <is>
-          <t>Café stick Refraish 1,5gx09boites</t>
+          <t>Lait Janus 18gx10</t>
         </is>
       </c>
       <c r="J942" s="1" t="n">
-        <v>1.6666666</v>
+        <v>1.2</v>
       </c>
       <c r="K942" s="1" t="n">
-        <v>43333.332</v>
+        <v>7200.0</v>
       </c>
       <c r="L942" s="1" t="n">
         <v>0.0</v>
@@ -57095,7 +57055,7 @@
       </c>
       <c r="N942" s="1"/>
       <c r="O942" s="1" t="n">
-        <v>556.0</v>
+        <v>570.0</v>
       </c>
       <c r="P942" s="1" t="inlineStr">
         <is>
@@ -57104,7 +57064,7 @@
       </c>
       <c r="Q942" s="1" t="inlineStr">
         <is>
-          <t>REFRAISH</t>
+          <t>LAIT</t>
         </is>
       </c>
     </row>
@@ -57137,20 +57097,20 @@
       </c>
       <c r="G943" s="1" t="inlineStr">
         <is>
-          <t>Mariama SADIO</t>
+          <t>Thierno SOW</t>
         </is>
       </c>
       <c r="H943" s="1"/>
       <c r="I943" s="1" t="inlineStr">
         <is>
-          <t>Café pot Refraish 200g</t>
+          <t>Kamlac évaporé 48x160g</t>
         </is>
       </c>
       <c r="J943" s="1" t="n">
-        <v>2.5</v>
+        <v>1.0</v>
       </c>
       <c r="K943" s="1" t="n">
-        <v>48750.0</v>
+        <v>9000.0</v>
       </c>
       <c r="L943" s="1" t="n">
         <v>0.0</v>
@@ -57160,7 +57120,7 @@
       </c>
       <c r="N943" s="1"/>
       <c r="O943" s="1" t="n">
-        <v>557.0</v>
+        <v>571.0</v>
       </c>
       <c r="P943" s="1" t="inlineStr">
         <is>
@@ -57169,7 +57129,7 @@
       </c>
       <c r="Q943" s="1" t="inlineStr">
         <is>
-          <t>REFRAISH</t>
+          <t>LAIT</t>
         </is>
       </c>
     </row>
@@ -57202,20 +57162,20 @@
       </c>
       <c r="G944" s="1" t="inlineStr">
         <is>
-          <t>Mariama SADIO</t>
+          <t>Mariama KANE</t>
         </is>
       </c>
       <c r="H944" s="1"/>
       <c r="I944" s="1" t="inlineStr">
         <is>
-          <t>Café pot Refraish 50g</t>
+          <t>Chocolat Orange 10 g x 60 pcs x 6 boites</t>
         </is>
       </c>
       <c r="J944" s="1" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="K944" s="1" t="n">
-        <v>33750.0</v>
+        <v>12000.0</v>
       </c>
       <c r="L944" s="1" t="n">
         <v>0.0</v>
@@ -57225,7 +57185,7 @@
       </c>
       <c r="N944" s="1"/>
       <c r="O944" s="1" t="n">
-        <v>558.0</v>
+        <v>572.0</v>
       </c>
       <c r="P944" s="1" t="inlineStr">
         <is>
@@ -57234,7 +57194,7 @@
       </c>
       <c r="Q944" s="1" t="inlineStr">
         <is>
-          <t>REFRAISH</t>
+          <t>CHOC ORANGE</t>
         </is>
       </c>
     </row>
@@ -57267,20 +57227,20 @@
       </c>
       <c r="G945" s="1" t="inlineStr">
         <is>
-          <t>Anta CISSE</t>
+          <t>Mariama KANE</t>
         </is>
       </c>
       <c r="H945" s="1"/>
       <c r="I945" s="1" t="inlineStr">
         <is>
-          <t>Café pot Refraish 200g</t>
+          <t>Chocolat Jaune 10gx60pcsx6 boites</t>
         </is>
       </c>
       <c r="J945" s="1" t="n">
-        <v>1.0</v>
+        <v>0.16666667</v>
       </c>
       <c r="K945" s="1" t="n">
-        <v>19500.0</v>
+        <v>1666.6666</v>
       </c>
       <c r="L945" s="1" t="n">
         <v>0.0</v>
@@ -57290,7 +57250,7 @@
       </c>
       <c r="N945" s="1"/>
       <c r="O945" s="1" t="n">
-        <v>559.0</v>
+        <v>573.0</v>
       </c>
       <c r="P945" s="1" t="inlineStr">
         <is>
@@ -57299,7 +57259,7 @@
       </c>
       <c r="Q945" s="1" t="inlineStr">
         <is>
-          <t>REFRAISH</t>
+          <t>CHOC ORANGE</t>
         </is>
       </c>
     </row>
@@ -57332,20 +57292,20 @@
       </c>
       <c r="G946" s="1" t="inlineStr">
         <is>
-          <t>Anta CISSE</t>
+          <t>Sada BALDE</t>
         </is>
       </c>
       <c r="H946" s="1"/>
       <c r="I946" s="1" t="inlineStr">
         <is>
-          <t>Café pot Refraish 50g</t>
+          <t>Chocolat Orange 10 g x 60 pcs x 6 boites</t>
         </is>
       </c>
       <c r="J946" s="1" t="n">
-        <v>1.0</v>
+        <v>0.33333334</v>
       </c>
       <c r="K946" s="1" t="n">
-        <v>11250.0</v>
+        <v>4000.0</v>
       </c>
       <c r="L946" s="1" t="n">
         <v>0.0</v>
@@ -57355,7 +57315,7 @@
       </c>
       <c r="N946" s="1"/>
       <c r="O946" s="1" t="n">
-        <v>560.0</v>
+        <v>574.0</v>
       </c>
       <c r="P946" s="1" t="inlineStr">
         <is>
@@ -57364,7 +57324,7 @@
       </c>
       <c r="Q946" s="1" t="inlineStr">
         <is>
-          <t>REFRAISH</t>
+          <t>CHOC ORANGE</t>
         </is>
       </c>
     </row>
@@ -57397,20 +57357,20 @@
       </c>
       <c r="G947" s="1" t="inlineStr">
         <is>
-          <t>Anta CISSE</t>
+          <t>Sada BALDE</t>
         </is>
       </c>
       <c r="H947" s="1"/>
       <c r="I947" s="1" t="inlineStr">
         <is>
-          <t>Café stick Refraish 1,5gx09boites</t>
+          <t>Chocolat Jaune 10gx60pcsx6 boites</t>
         </is>
       </c>
       <c r="J947" s="1" t="n">
-        <v>6.4444447</v>
+        <v>0.16666667</v>
       </c>
       <c r="K947" s="1" t="n">
-        <v>167555.56</v>
+        <v>1666.6666</v>
       </c>
       <c r="L947" s="1" t="n">
         <v>0.0</v>
@@ -57420,7 +57380,7 @@
       </c>
       <c r="N947" s="1"/>
       <c r="O947" s="1" t="n">
-        <v>561.0</v>
+        <v>575.0</v>
       </c>
       <c r="P947" s="1" t="inlineStr">
         <is>
@@ -57429,7 +57389,7 @@
       </c>
       <c r="Q947" s="1" t="inlineStr">
         <is>
-          <t>REFRAISH</t>
+          <t>CHOC ORANGE</t>
         </is>
       </c>
     </row>
@@ -57462,20 +57422,20 @@
       </c>
       <c r="G948" s="1" t="inlineStr">
         <is>
-          <t>Saly SEYDI</t>
+          <t>Sada BALDE</t>
         </is>
       </c>
       <c r="H948" s="1"/>
       <c r="I948" s="1" t="inlineStr">
         <is>
-          <t>Chocolat jaune 400g x 12 pcs</t>
+          <t>Chocolat jaune 200g x 24 pcs</t>
         </is>
       </c>
       <c r="J948" s="1" t="n">
-        <v>0.16666667</v>
+        <v>0.5</v>
       </c>
       <c r="K948" s="1" t="n">
-        <v>2583.3333</v>
+        <v>7750.0</v>
       </c>
       <c r="L948" s="1" t="n">
         <v>0.0</v>
@@ -57485,7 +57445,7 @@
       </c>
       <c r="N948" s="1"/>
       <c r="O948" s="1" t="n">
-        <v>562.0</v>
+        <v>576.0</v>
       </c>
       <c r="P948" s="1" t="inlineStr">
         <is>
@@ -57494,7 +57454,7 @@
       </c>
       <c r="Q948" s="1" t="inlineStr">
         <is>
-          <t>CHOC TRANS</t>
+          <t>CHOC ORANGE</t>
         </is>
       </c>
     </row>
@@ -57527,20 +57487,20 @@
       </c>
       <c r="G949" s="1" t="inlineStr">
         <is>
-          <t>Dior</t>
+          <t>Aida SENE</t>
         </is>
       </c>
       <c r="H949" s="1"/>
       <c r="I949" s="1" t="inlineStr">
         <is>
-          <t>Chocolat transparent 400gx12pcs</t>
+          <t>Kamlac Thé 7g</t>
         </is>
       </c>
       <c r="J949" s="1" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="K949" s="1" t="n">
-        <v>3125.0</v>
+        <v>5750.0</v>
       </c>
       <c r="L949" s="1" t="n">
         <v>0.0</v>
@@ -57550,7 +57510,7 @@
       </c>
       <c r="N949" s="1"/>
       <c r="O949" s="1" t="n">
-        <v>563.0</v>
+        <v>577.0</v>
       </c>
       <c r="P949" s="1" t="inlineStr">
         <is>
@@ -57559,7 +57519,7 @@
       </c>
       <c r="Q949" s="1" t="inlineStr">
         <is>
-          <t>CHOC TRANS</t>
+          <t>THE</t>
         </is>
       </c>
     </row>
@@ -57592,20 +57552,20 @@
       </c>
       <c r="G950" s="1" t="inlineStr">
         <is>
-          <t>Dior</t>
+          <t>Fama DIOUF</t>
         </is>
       </c>
       <c r="H950" s="1"/>
       <c r="I950" s="1" t="inlineStr">
         <is>
-          <t>Chocolat jaune 400g x 12 pcs</t>
+          <t>Kamlac Thé 7g</t>
         </is>
       </c>
       <c r="J950" s="1" t="n">
-        <v>0.25</v>
+        <v>0.9166667</v>
       </c>
       <c r="K950" s="1" t="n">
-        <v>3875.0</v>
+        <v>10541.667</v>
       </c>
       <c r="L950" s="1" t="n">
         <v>0.0</v>
@@ -57615,7 +57575,7 @@
       </c>
       <c r="N950" s="1"/>
       <c r="O950" s="1" t="n">
-        <v>564.0</v>
+        <v>578.0</v>
       </c>
       <c r="P950" s="1" t="inlineStr">
         <is>
@@ -57624,7 +57584,7 @@
       </c>
       <c r="Q950" s="1" t="inlineStr">
         <is>
-          <t>CHOC TRANS</t>
+          <t>THE</t>
         </is>
       </c>
     </row>
@@ -57637,12 +57597,12 @@
       </c>
       <c r="C951" s="1" t="inlineStr">
         <is>
-          <t>TATA 1</t>
+          <t>TATA 2</t>
         </is>
       </c>
       <c r="D951" s="1" t="inlineStr">
         <is>
-          <t>DJIBRIL DIOP</t>
+          <t>ALIOUNE BADARA (MANSOUR) SANE</t>
         </is>
       </c>
       <c r="E951" s="1" t="inlineStr">
@@ -57652,35 +57612,35 @@
       </c>
       <c r="F951" s="1" t="inlineStr">
         <is>
-          <t>YEUMBEUL</t>
+          <t>PIKINE</t>
         </is>
       </c>
       <c r="G951" s="1" t="inlineStr">
         <is>
-          <t>Mariama BA</t>
+          <t>Coura DIONE</t>
         </is>
       </c>
       <c r="H951" s="1"/>
       <c r="I951" s="1" t="inlineStr">
         <is>
-          <t>Café Altimo pot 100g x 24 pcs</t>
+          <t>Café pot Refraish 200g</t>
         </is>
       </c>
       <c r="J951" s="1" t="n">
-        <v>0.5</v>
+        <v>2.0</v>
       </c>
       <c r="K951" s="1" t="n">
-        <v>16750.0</v>
+        <v>39000.0</v>
       </c>
       <c r="L951" s="1" t="n">
-        <v>0.0</v>
+        <v>3000.0</v>
       </c>
       <c r="M951" s="1" t="n">
         <v>0.0</v>
       </c>
       <c r="N951" s="1"/>
       <c r="O951" s="1" t="n">
-        <v>565.0</v>
+        <v>605.0</v>
       </c>
       <c r="P951" s="1" t="inlineStr">
         <is>
@@ -57689,7 +57649,7 @@
       </c>
       <c r="Q951" s="1" t="inlineStr">
         <is>
-          <t>ALTIMO</t>
+          <t>REFRAISH</t>
         </is>
       </c>
     </row>
@@ -57702,12 +57662,12 @@
       </c>
       <c r="C952" s="1" t="inlineStr">
         <is>
-          <t>TATA 1</t>
+          <t>TATA 2</t>
         </is>
       </c>
       <c r="D952" s="1" t="inlineStr">
         <is>
-          <t>DJIBRIL DIOP</t>
+          <t>ALIOUNE BADARA (MANSOUR) SANE</t>
         </is>
       </c>
       <c r="E952" s="1" t="inlineStr">
@@ -57717,25 +57677,25 @@
       </c>
       <c r="F952" s="1" t="inlineStr">
         <is>
-          <t>YEUMBEUL</t>
+          <t>PIKINE</t>
         </is>
       </c>
       <c r="G952" s="1" t="inlineStr">
         <is>
-          <t>Fatou THIOMBENE</t>
+          <t>Daba DABO</t>
         </is>
       </c>
       <c r="H952" s="1"/>
       <c r="I952" s="1" t="inlineStr">
         <is>
-          <t>Café Altimo pot 50g x 24 pcs</t>
+          <t>Café pot Refraish 50g</t>
         </is>
       </c>
       <c r="J952" s="1" t="n">
-        <v>0.041666668</v>
+        <v>0.0</v>
       </c>
       <c r="K952" s="1" t="n">
-        <v>729.1667</v>
+        <v>0.0</v>
       </c>
       <c r="L952" s="1" t="n">
         <v>0.0</v>
@@ -57745,7 +57705,7 @@
       </c>
       <c r="N952" s="1"/>
       <c r="O952" s="1" t="n">
-        <v>566.0</v>
+        <v>606.0</v>
       </c>
       <c r="P952" s="1" t="inlineStr">
         <is>
@@ -57754,7 +57714,7 @@
       </c>
       <c r="Q952" s="1" t="inlineStr">
         <is>
-          <t>ALTIMO</t>
+          <t>REFRAISH</t>
         </is>
       </c>
     </row>
@@ -57767,12 +57727,12 @@
       </c>
       <c r="C953" s="1" t="inlineStr">
         <is>
-          <t>TATA 1</t>
+          <t>TATA 2</t>
         </is>
       </c>
       <c r="D953" s="1" t="inlineStr">
         <is>
-          <t>DJIBRIL DIOP</t>
+          <t>ALIOUNE BADARA (MANSOUR) SANE</t>
         </is>
       </c>
       <c r="E953" s="1" t="inlineStr">
@@ -57782,25 +57742,25 @@
       </c>
       <c r="F953" s="1" t="inlineStr">
         <is>
-          <t>YEUMBEUL</t>
+          <t>PIKINE</t>
         </is>
       </c>
       <c r="G953" s="1" t="inlineStr">
         <is>
-          <t>Ndeye DIONE</t>
+          <t>Daba DABO</t>
         </is>
       </c>
       <c r="H953" s="1"/>
       <c r="I953" s="1" t="inlineStr">
         <is>
-          <t>Café stick Altimo 1,5gx09boites</t>
+          <t>Café pot Refraish 200g</t>
         </is>
       </c>
       <c r="J953" s="1" t="n">
-        <v>0.5555556</v>
+        <v>1.5</v>
       </c>
       <c r="K953" s="1" t="n">
-        <v>15555.556</v>
+        <v>29250.0</v>
       </c>
       <c r="L953" s="1" t="n">
         <v>0.0</v>
@@ -57810,7 +57770,7 @@
       </c>
       <c r="N953" s="1"/>
       <c r="O953" s="1" t="n">
-        <v>567.0</v>
+        <v>607.0</v>
       </c>
       <c r="P953" s="1" t="inlineStr">
         <is>
@@ -57819,7 +57779,7 @@
       </c>
       <c r="Q953" s="1" t="inlineStr">
         <is>
-          <t>ALTIMO</t>
+          <t>REFRAISH</t>
         </is>
       </c>
     </row>
@@ -57832,12 +57792,12 @@
       </c>
       <c r="C954" s="1" t="inlineStr">
         <is>
-          <t>TATA 1</t>
+          <t>TATA 2</t>
         </is>
       </c>
       <c r="D954" s="1" t="inlineStr">
         <is>
-          <t>DJIBRIL DIOP</t>
+          <t>ALIOUNE BADARA (MANSOUR) SANE</t>
         </is>
       </c>
       <c r="E954" s="1" t="inlineStr">
@@ -57847,25 +57807,25 @@
       </c>
       <c r="F954" s="1" t="inlineStr">
         <is>
-          <t>YEUMBEUL</t>
+          <t>PIKINE</t>
         </is>
       </c>
       <c r="G954" s="1" t="inlineStr">
         <is>
-          <t>Khady SANE</t>
+          <t>Daba DABO</t>
         </is>
       </c>
       <c r="H954" s="1"/>
       <c r="I954" s="1" t="inlineStr">
         <is>
-          <t>Café Altimo pot 100g x 24 pcs</t>
+          <t>Café stick Refraish 1,5gx09boites</t>
         </is>
       </c>
       <c r="J954" s="1" t="n">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="K954" s="1" t="n">
-        <v>16750.0</v>
+        <v>26000.0</v>
       </c>
       <c r="L954" s="1" t="n">
         <v>0.0</v>
@@ -57875,7 +57835,7 @@
       </c>
       <c r="N954" s="1"/>
       <c r="O954" s="1" t="n">
-        <v>568.0</v>
+        <v>608.0</v>
       </c>
       <c r="P954" s="1" t="inlineStr">
         <is>
@@ -57884,7 +57844,7 @@
       </c>
       <c r="Q954" s="1" t="inlineStr">
         <is>
-          <t>ALTIMO</t>
+          <t>REFRAISH</t>
         </is>
       </c>
     </row>
@@ -57897,12 +57857,12 @@
       </c>
       <c r="C955" s="1" t="inlineStr">
         <is>
-          <t>TATA 1</t>
+          <t>TATA 2</t>
         </is>
       </c>
       <c r="D955" s="1" t="inlineStr">
         <is>
-          <t>DJIBRIL DIOP</t>
+          <t>ALIOUNE BADARA (MANSOUR) SANE</t>
         </is>
       </c>
       <c r="E955" s="1" t="inlineStr">
@@ -57912,25 +57872,25 @@
       </c>
       <c r="F955" s="1" t="inlineStr">
         <is>
-          <t>YEUMBEUL</t>
+          <t>PIKINE</t>
         </is>
       </c>
       <c r="G955" s="1" t="inlineStr">
         <is>
-          <t>Adama DABO</t>
+          <t>Ado DABO</t>
         </is>
       </c>
       <c r="H955" s="1"/>
       <c r="I955" s="1" t="inlineStr">
         <is>
-          <t>Kamlac évaporé 48x160g</t>
+          <t>Café stick Refraish 1,5gx09boites</t>
         </is>
       </c>
       <c r="J955" s="1" t="n">
-        <v>1.0</v>
+        <v>0.33333334</v>
       </c>
       <c r="K955" s="1" t="n">
-        <v>9000.0</v>
+        <v>8666.667</v>
       </c>
       <c r="L955" s="1" t="n">
         <v>0.0</v>
@@ -57940,7 +57900,7 @@
       </c>
       <c r="N955" s="1"/>
       <c r="O955" s="1" t="n">
-        <v>569.0</v>
+        <v>609.0</v>
       </c>
       <c r="P955" s="1" t="inlineStr">
         <is>
@@ -57949,7 +57909,7 @@
       </c>
       <c r="Q955" s="1" t="inlineStr">
         <is>
-          <t>LAIT</t>
+          <t>REFRAISH</t>
         </is>
       </c>
     </row>
@@ -57962,12 +57922,12 @@
       </c>
       <c r="C956" s="1" t="inlineStr">
         <is>
-          <t>TATA 1</t>
+          <t>TATA 2</t>
         </is>
       </c>
       <c r="D956" s="1" t="inlineStr">
         <is>
-          <t>DJIBRIL DIOP</t>
+          <t>ALIOUNE BADARA (MANSOUR) SANE</t>
         </is>
       </c>
       <c r="E956" s="1" t="inlineStr">
@@ -57977,25 +57937,25 @@
       </c>
       <c r="F956" s="1" t="inlineStr">
         <is>
-          <t>YEUMBEUL</t>
+          <t>PIKINE</t>
         </is>
       </c>
       <c r="G956" s="1" t="inlineStr">
         <is>
-          <t>Adama DABO</t>
+          <t>Ado DABO</t>
         </is>
       </c>
       <c r="H956" s="1"/>
       <c r="I956" s="1" t="inlineStr">
         <is>
-          <t>Lait Janus 18gx10</t>
+          <t>Café pot Refraish 50g</t>
         </is>
       </c>
       <c r="J956" s="1" t="n">
-        <v>1.2</v>
+        <v>0.0</v>
       </c>
       <c r="K956" s="1" t="n">
-        <v>7200.0</v>
+        <v>0.0</v>
       </c>
       <c r="L956" s="1" t="n">
         <v>0.0</v>
@@ -58005,7 +57965,7 @@
       </c>
       <c r="N956" s="1"/>
       <c r="O956" s="1" t="n">
-        <v>570.0</v>
+        <v>610.0</v>
       </c>
       <c r="P956" s="1" t="inlineStr">
         <is>
@@ -58014,7 +57974,7 @@
       </c>
       <c r="Q956" s="1" t="inlineStr">
         <is>
-          <t>LAIT</t>
+          <t>REFRAISH</t>
         </is>
       </c>
     </row>
@@ -58027,12 +57987,12 @@
       </c>
       <c r="C957" s="1" t="inlineStr">
         <is>
-          <t>TATA 1</t>
+          <t>TATA 2</t>
         </is>
       </c>
       <c r="D957" s="1" t="inlineStr">
         <is>
-          <t>DJIBRIL DIOP</t>
+          <t>ALIOUNE BADARA (MANSOUR) SANE</t>
         </is>
       </c>
       <c r="E957" s="1" t="inlineStr">
@@ -58042,25 +58002,25 @@
       </c>
       <c r="F957" s="1" t="inlineStr">
         <is>
-          <t>YEUMBEUL</t>
+          <t>PIKINE</t>
         </is>
       </c>
       <c r="G957" s="1" t="inlineStr">
         <is>
-          <t>Thierno SOW</t>
+          <t>Astou DIENG</t>
         </is>
       </c>
       <c r="H957" s="1"/>
       <c r="I957" s="1" t="inlineStr">
         <is>
-          <t>Kamlac évaporé 48x160g</t>
+          <t>Café stick Altimo 1,5gx09boites</t>
         </is>
       </c>
       <c r="J957" s="1" t="n">
         <v>1.0</v>
       </c>
       <c r="K957" s="1" t="n">
-        <v>9000.0</v>
+        <v>28000.0</v>
       </c>
       <c r="L957" s="1" t="n">
         <v>0.0</v>
@@ -58070,7 +58030,7 @@
       </c>
       <c r="N957" s="1"/>
       <c r="O957" s="1" t="n">
-        <v>571.0</v>
+        <v>611.0</v>
       </c>
       <c r="P957" s="1" t="inlineStr">
         <is>
@@ -58079,7 +58039,7 @@
       </c>
       <c r="Q957" s="1" t="inlineStr">
         <is>
-          <t>LAIT</t>
+          <t>ALTIMO</t>
         </is>
       </c>
     </row>
@@ -58092,12 +58052,12 @@
       </c>
       <c r="C958" s="1" t="inlineStr">
         <is>
-          <t>TATA 1</t>
+          <t>TATA 2</t>
         </is>
       </c>
       <c r="D958" s="1" t="inlineStr">
         <is>
-          <t>DJIBRIL DIOP</t>
+          <t>ALIOUNE BADARA (MANSOUR) SANE</t>
         </is>
       </c>
       <c r="E958" s="1" t="inlineStr">
@@ -58107,25 +58067,25 @@
       </c>
       <c r="F958" s="1" t="inlineStr">
         <is>
-          <t>YEUMBEUL</t>
+          <t>PIKINE</t>
         </is>
       </c>
       <c r="G958" s="1" t="inlineStr">
         <is>
-          <t>Mariama KANE</t>
+          <t>Awa COLY</t>
         </is>
       </c>
       <c r="H958" s="1"/>
       <c r="I958" s="1" t="inlineStr">
         <is>
-          <t>Chocolat Orange 10 g x 60 pcs x 6 boites</t>
+          <t>Café stick Altimo 1,5gx09boites</t>
         </is>
       </c>
       <c r="J958" s="1" t="n">
-        <v>1.0</v>
+        <v>0.22222222</v>
       </c>
       <c r="K958" s="1" t="n">
-        <v>12000.0</v>
+        <v>6222.222</v>
       </c>
       <c r="L958" s="1" t="n">
         <v>0.0</v>
@@ -58135,7 +58095,7 @@
       </c>
       <c r="N958" s="1"/>
       <c r="O958" s="1" t="n">
-        <v>572.0</v>
+        <v>612.0</v>
       </c>
       <c r="P958" s="1" t="inlineStr">
         <is>
@@ -58144,7 +58104,7 @@
       </c>
       <c r="Q958" s="1" t="inlineStr">
         <is>
-          <t>CHOC ORANGE</t>
+          <t>ALTIMO</t>
         </is>
       </c>
     </row>
@@ -58157,12 +58117,12 @@
       </c>
       <c r="C959" s="1" t="inlineStr">
         <is>
-          <t>TATA 1</t>
+          <t>TATA 2</t>
         </is>
       </c>
       <c r="D959" s="1" t="inlineStr">
         <is>
-          <t>DJIBRIL DIOP</t>
+          <t>ALIOUNE BADARA (MANSOUR) SANE</t>
         </is>
       </c>
       <c r="E959" s="1" t="inlineStr">
@@ -58172,25 +58132,25 @@
       </c>
       <c r="F959" s="1" t="inlineStr">
         <is>
-          <t>YEUMBEUL</t>
+          <t>PIKINE</t>
         </is>
       </c>
       <c r="G959" s="1" t="inlineStr">
         <is>
-          <t>Mariama KANE</t>
+          <t>Adama</t>
         </is>
       </c>
       <c r="H959" s="1"/>
       <c r="I959" s="1" t="inlineStr">
         <is>
-          <t>Chocolat Jaune 10gx60pcsx6 boites</t>
+          <t>Café stick Altimo 1,5gx09boites</t>
         </is>
       </c>
       <c r="J959" s="1" t="n">
-        <v>0.16666667</v>
+        <v>0.8888889</v>
       </c>
       <c r="K959" s="1" t="n">
-        <v>1666.6666</v>
+        <v>24888.889</v>
       </c>
       <c r="L959" s="1" t="n">
         <v>0.0</v>
@@ -58200,7 +58160,7 @@
       </c>
       <c r="N959" s="1"/>
       <c r="O959" s="1" t="n">
-        <v>573.0</v>
+        <v>613.0</v>
       </c>
       <c r="P959" s="1" t="inlineStr">
         <is>
@@ -58209,7 +58169,7 @@
       </c>
       <c r="Q959" s="1" t="inlineStr">
         <is>
-          <t>CHOC ORANGE</t>
+          <t>ALTIMO</t>
         </is>
       </c>
     </row>
@@ -58222,12 +58182,12 @@
       </c>
       <c r="C960" s="1" t="inlineStr">
         <is>
-          <t>TATA 1</t>
+          <t>TATA 2</t>
         </is>
       </c>
       <c r="D960" s="1" t="inlineStr">
         <is>
-          <t>DJIBRIL DIOP</t>
+          <t>ALIOUNE BADARA (MANSOUR) SANE</t>
         </is>
       </c>
       <c r="E960" s="1" t="inlineStr">
@@ -58237,25 +58197,25 @@
       </c>
       <c r="F960" s="1" t="inlineStr">
         <is>
-          <t>YEUMBEUL</t>
+          <t>PIKINE</t>
         </is>
       </c>
       <c r="G960" s="1" t="inlineStr">
         <is>
-          <t>Sada BALDE</t>
+          <t>Nogueye THIAME</t>
         </is>
       </c>
       <c r="H960" s="1"/>
       <c r="I960" s="1" t="inlineStr">
         <is>
-          <t>Chocolat Orange 10 g x 60 pcs x 6 boites</t>
+          <t>Chocolat transparent 400gx12pcs</t>
         </is>
       </c>
       <c r="J960" s="1" t="n">
         <v>0.33333334</v>
       </c>
       <c r="K960" s="1" t="n">
-        <v>4000.0</v>
+        <v>4166.6665</v>
       </c>
       <c r="L960" s="1" t="n">
         <v>0.0</v>
@@ -58265,7 +58225,7 @@
       </c>
       <c r="N960" s="1"/>
       <c r="O960" s="1" t="n">
-        <v>574.0</v>
+        <v>614.0</v>
       </c>
       <c r="P960" s="1" t="inlineStr">
         <is>
@@ -58274,7 +58234,7 @@
       </c>
       <c r="Q960" s="1" t="inlineStr">
         <is>
-          <t>CHOC ORANGE</t>
+          <t>CHOC TRANS</t>
         </is>
       </c>
     </row>
@@ -58287,12 +58247,12 @@
       </c>
       <c r="C961" s="1" t="inlineStr">
         <is>
-          <t>TATA 1</t>
+          <t>TATA 2</t>
         </is>
       </c>
       <c r="D961" s="1" t="inlineStr">
         <is>
-          <t>DJIBRIL DIOP</t>
+          <t>ALIOUNE BADARA (MANSOUR) SANE</t>
         </is>
       </c>
       <c r="E961" s="1" t="inlineStr">
@@ -58302,25 +58262,25 @@
       </c>
       <c r="F961" s="1" t="inlineStr">
         <is>
-          <t>YEUMBEUL</t>
+          <t>PIKINE</t>
         </is>
       </c>
       <c r="G961" s="1" t="inlineStr">
         <is>
-          <t>Sada BALDE</t>
+          <t>Amsatou GUEYE</t>
         </is>
       </c>
       <c r="H961" s="1"/>
       <c r="I961" s="1" t="inlineStr">
         <is>
-          <t>Chocolat Jaune 10gx60pcsx6 boites</t>
+          <t>Chocolat 3-en-1 30x120 pcs</t>
         </is>
       </c>
       <c r="J961" s="1" t="n">
-        <v>0.16666667</v>
+        <v>0.1</v>
       </c>
       <c r="K961" s="1" t="n">
-        <v>1666.6666</v>
+        <v>1100.0</v>
       </c>
       <c r="L961" s="1" t="n">
         <v>0.0</v>
@@ -58330,7 +58290,7 @@
       </c>
       <c r="N961" s="1"/>
       <c r="O961" s="1" t="n">
-        <v>575.0</v>
+        <v>615.0</v>
       </c>
       <c r="P961" s="1" t="inlineStr">
         <is>
@@ -58339,7 +58299,7 @@
       </c>
       <c r="Q961" s="1" t="inlineStr">
         <is>
-          <t>CHOC ORANGE</t>
+          <t>CHOC TRANS</t>
         </is>
       </c>
     </row>
@@ -58352,12 +58312,12 @@
       </c>
       <c r="C962" s="1" t="inlineStr">
         <is>
-          <t>TATA 1</t>
+          <t>TATA 2</t>
         </is>
       </c>
       <c r="D962" s="1" t="inlineStr">
         <is>
-          <t>DJIBRIL DIOP</t>
+          <t>ALIOUNE BADARA (MANSOUR) SANE</t>
         </is>
       </c>
       <c r="E962" s="1" t="inlineStr">
@@ -58367,25 +58327,25 @@
       </c>
       <c r="F962" s="1" t="inlineStr">
         <is>
-          <t>YEUMBEUL</t>
+          <t>PIKINE</t>
         </is>
       </c>
       <c r="G962" s="1" t="inlineStr">
         <is>
-          <t>Sada BALDE</t>
+          <t>Amsatou GUEYE</t>
         </is>
       </c>
       <c r="H962" s="1"/>
       <c r="I962" s="1" t="inlineStr">
         <is>
-          <t>Chocolat jaune 200g x 24 pcs</t>
+          <t>Chocolat transparent 400gx12pcs</t>
         </is>
       </c>
       <c r="J962" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="K962" s="1" t="n">
-        <v>7750.0</v>
+        <v>6250.0</v>
       </c>
       <c r="L962" s="1" t="n">
         <v>0.0</v>
@@ -58395,7 +58355,7 @@
       </c>
       <c r="N962" s="1"/>
       <c r="O962" s="1" t="n">
-        <v>576.0</v>
+        <v>616.0</v>
       </c>
       <c r="P962" s="1" t="inlineStr">
         <is>
@@ -58404,7 +58364,7 @@
       </c>
       <c r="Q962" s="1" t="inlineStr">
         <is>
-          <t>CHOC ORANGE</t>
+          <t>CHOC TRANS</t>
         </is>
       </c>
     </row>
@@ -58417,12 +58377,12 @@
       </c>
       <c r="C963" s="1" t="inlineStr">
         <is>
-          <t>TATA 1</t>
+          <t>TATA 2</t>
         </is>
       </c>
       <c r="D963" s="1" t="inlineStr">
         <is>
-          <t>DJIBRIL DIOP</t>
+          <t>ALIOUNE BADARA (MANSOUR) SANE</t>
         </is>
       </c>
       <c r="E963" s="1" t="inlineStr">
@@ -58432,25 +58392,25 @@
       </c>
       <c r="F963" s="1" t="inlineStr">
         <is>
-          <t>YEUMBEUL</t>
+          <t>PIKINE</t>
         </is>
       </c>
       <c r="G963" s="1" t="inlineStr">
         <is>
-          <t>Aida SENE</t>
+          <t>Amsatou GUEYE</t>
         </is>
       </c>
       <c r="H963" s="1"/>
       <c r="I963" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Thé 7g</t>
+          <t>Chocolat jaune 400g x 12 pcs</t>
         </is>
       </c>
       <c r="J963" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="K963" s="1" t="n">
-        <v>5750.0</v>
+        <v>7750.0</v>
       </c>
       <c r="L963" s="1" t="n">
         <v>0.0</v>
@@ -58460,7 +58420,7 @@
       </c>
       <c r="N963" s="1"/>
       <c r="O963" s="1" t="n">
-        <v>577.0</v>
+        <v>617.0</v>
       </c>
       <c r="P963" s="1" t="inlineStr">
         <is>
@@ -58469,7 +58429,7 @@
       </c>
       <c r="Q963" s="1" t="inlineStr">
         <is>
-          <t>THE</t>
+          <t>CHOC TRANS</t>
         </is>
       </c>
     </row>
@@ -58482,12 +58442,12 @@
       </c>
       <c r="C964" s="1" t="inlineStr">
         <is>
-          <t>TATA 1</t>
+          <t>TATA 2</t>
         </is>
       </c>
       <c r="D964" s="1" t="inlineStr">
         <is>
-          <t>DJIBRIL DIOP</t>
+          <t>ALIOUNE BADARA (MANSOUR) SANE</t>
         </is>
       </c>
       <c r="E964" s="1" t="inlineStr">
@@ -58497,25 +58457,25 @@
       </c>
       <c r="F964" s="1" t="inlineStr">
         <is>
-          <t>YEUMBEUL</t>
+          <t>PIKINE</t>
         </is>
       </c>
       <c r="G964" s="1" t="inlineStr">
         <is>
-          <t>Fama DIOUF</t>
+          <t>Oumou SALAM</t>
         </is>
       </c>
       <c r="H964" s="1"/>
       <c r="I964" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Thé 7g</t>
+          <t>Chocolat Jaune 10gx60pcsx6 boites</t>
         </is>
       </c>
       <c r="J964" s="1" t="n">
-        <v>0.9166667</v>
+        <v>0.5</v>
       </c>
       <c r="K964" s="1" t="n">
-        <v>10541.667</v>
+        <v>5000.0</v>
       </c>
       <c r="L964" s="1" t="n">
         <v>0.0</v>
@@ -58525,7 +58485,7 @@
       </c>
       <c r="N964" s="1"/>
       <c r="O964" s="1" t="n">
-        <v>578.0</v>
+        <v>618.0</v>
       </c>
       <c r="P964" s="1" t="inlineStr">
         <is>
@@ -58534,7 +58494,7 @@
       </c>
       <c r="Q964" s="1" t="inlineStr">
         <is>
-          <t>THE</t>
+          <t>CHOC ORANGE</t>
         </is>
       </c>
     </row>
@@ -58567,30 +58527,30 @@
       </c>
       <c r="G965" s="1" t="inlineStr">
         <is>
-          <t>Coura DIONE</t>
+          <t>Oumou SALAM</t>
         </is>
       </c>
       <c r="H965" s="1"/>
       <c r="I965" s="1" t="inlineStr">
         <is>
-          <t>Café pot Refraish 200g</t>
+          <t>Chocolat Orange 10 g x 60 pcs x 6 boites</t>
         </is>
       </c>
       <c r="J965" s="1" t="n">
-        <v>2.0</v>
+        <v>0.16666667</v>
       </c>
       <c r="K965" s="1" t="n">
-        <v>39000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="L965" s="1" t="n">
-        <v>3000.0</v>
+        <v>0.0</v>
       </c>
       <c r="M965" s="1" t="n">
         <v>0.0</v>
       </c>
       <c r="N965" s="1"/>
       <c r="O965" s="1" t="n">
-        <v>605.0</v>
+        <v>619.0</v>
       </c>
       <c r="P965" s="1" t="inlineStr">
         <is>
@@ -58599,7 +58559,7 @@
       </c>
       <c r="Q965" s="1" t="inlineStr">
         <is>
-          <t>REFRAISH</t>
+          <t>CHOC ORANGE</t>
         </is>
       </c>
     </row>
@@ -58632,20 +58592,20 @@
       </c>
       <c r="G966" s="1" t="inlineStr">
         <is>
-          <t>Daba DABO</t>
+          <t>Aissatou DIALLO</t>
         </is>
       </c>
       <c r="H966" s="1"/>
       <c r="I966" s="1" t="inlineStr">
         <is>
-          <t>Café pot Refraish 50g</t>
+          <t>Chocolat Jaune 10gx60pcsx6 boites</t>
         </is>
       </c>
       <c r="J966" s="1" t="n">
-        <v>0.0</v>
+        <v>1.3333334</v>
       </c>
       <c r="K966" s="1" t="n">
-        <v>0.0</v>
+        <v>13333.333</v>
       </c>
       <c r="L966" s="1" t="n">
         <v>0.0</v>
@@ -58655,7 +58615,7 @@
       </c>
       <c r="N966" s="1"/>
       <c r="O966" s="1" t="n">
-        <v>606.0</v>
+        <v>620.0</v>
       </c>
       <c r="P966" s="1" t="inlineStr">
         <is>
@@ -58664,7 +58624,7 @@
       </c>
       <c r="Q966" s="1" t="inlineStr">
         <is>
-          <t>REFRAISH</t>
+          <t>CHOC ORANGE</t>
         </is>
       </c>
     </row>
@@ -58697,20 +58657,20 @@
       </c>
       <c r="G967" s="1" t="inlineStr">
         <is>
-          <t>Daba DABO</t>
+          <t>Aissatou DIALLO</t>
         </is>
       </c>
       <c r="H967" s="1"/>
       <c r="I967" s="1" t="inlineStr">
         <is>
-          <t>Café pot Refraish 200g</t>
+          <t>Chocolat Orange 10 g x 60 pcs x 6 boites</t>
         </is>
       </c>
       <c r="J967" s="1" t="n">
-        <v>1.5</v>
+        <v>0.33333334</v>
       </c>
       <c r="K967" s="1" t="n">
-        <v>29250.0</v>
+        <v>4000.0</v>
       </c>
       <c r="L967" s="1" t="n">
         <v>0.0</v>
@@ -58720,7 +58680,7 @@
       </c>
       <c r="N967" s="1"/>
       <c r="O967" s="1" t="n">
-        <v>607.0</v>
+        <v>621.0</v>
       </c>
       <c r="P967" s="1" t="inlineStr">
         <is>
@@ -58729,7 +58689,7 @@
       </c>
       <c r="Q967" s="1" t="inlineStr">
         <is>
-          <t>REFRAISH</t>
+          <t>CHOC ORANGE</t>
         </is>
       </c>
     </row>
@@ -58762,20 +58722,20 @@
       </c>
       <c r="G968" s="1" t="inlineStr">
         <is>
-          <t>Daba DABO</t>
+          <t>Baye Cheikh</t>
         </is>
       </c>
       <c r="H968" s="1"/>
       <c r="I968" s="1" t="inlineStr">
         <is>
-          <t>Café stick Refraish 1,5gx09boites</t>
+          <t>Cafe au Lait 3-en-1</t>
         </is>
       </c>
       <c r="J968" s="1" t="n">
         <v>1.0</v>
       </c>
       <c r="K968" s="1" t="n">
-        <v>26000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="L968" s="1" t="n">
         <v>0.0</v>
@@ -58785,7 +58745,7 @@
       </c>
       <c r="N968" s="1"/>
       <c r="O968" s="1" t="n">
-        <v>608.0</v>
+        <v>622.0</v>
       </c>
       <c r="P968" s="1" t="inlineStr">
         <is>
@@ -58794,7 +58754,7 @@
       </c>
       <c r="Q968" s="1" t="inlineStr">
         <is>
-          <t>REFRAISH</t>
+          <t>LAIT</t>
         </is>
       </c>
     </row>
@@ -58827,20 +58787,20 @@
       </c>
       <c r="G969" s="1" t="inlineStr">
         <is>
-          <t>Ado DABO</t>
+          <t>Pape DABO</t>
         </is>
       </c>
       <c r="H969" s="1"/>
       <c r="I969" s="1" t="inlineStr">
         <is>
-          <t>Café stick Refraish 1,5gx09boites</t>
+          <t>Kamlac évaporé 48x160g</t>
         </is>
       </c>
       <c r="J969" s="1" t="n">
-        <v>0.33333334</v>
+        <v>1.0</v>
       </c>
       <c r="K969" s="1" t="n">
-        <v>8666.667</v>
+        <v>9000.0</v>
       </c>
       <c r="L969" s="1" t="n">
         <v>0.0</v>
@@ -58850,7 +58810,7 @@
       </c>
       <c r="N969" s="1"/>
       <c r="O969" s="1" t="n">
-        <v>609.0</v>
+        <v>623.0</v>
       </c>
       <c r="P969" s="1" t="inlineStr">
         <is>
@@ -58859,7 +58819,7 @@
       </c>
       <c r="Q969" s="1" t="inlineStr">
         <is>
-          <t>REFRAISH</t>
+          <t>LAIT</t>
         </is>
       </c>
     </row>
@@ -58892,20 +58852,20 @@
       </c>
       <c r="G970" s="1" t="inlineStr">
         <is>
-          <t>Ado DABO</t>
+          <t>Pape DABO</t>
         </is>
       </c>
       <c r="H970" s="1"/>
       <c r="I970" s="1" t="inlineStr">
         <is>
-          <t>Café pot Refraish 50g</t>
+          <t>Cafe au Lait 3-en-1</t>
         </is>
       </c>
       <c r="J970" s="1" t="n">
-        <v>0.0</v>
+        <v>0.2</v>
       </c>
       <c r="K970" s="1" t="n">
-        <v>0.0</v>
+        <v>900.0</v>
       </c>
       <c r="L970" s="1" t="n">
         <v>0.0</v>
@@ -58915,7 +58875,7 @@
       </c>
       <c r="N970" s="1"/>
       <c r="O970" s="1" t="n">
-        <v>610.0</v>
+        <v>624.0</v>
       </c>
       <c r="P970" s="1" t="inlineStr">
         <is>
@@ -58924,7 +58884,7 @@
       </c>
       <c r="Q970" s="1" t="inlineStr">
         <is>
-          <t>REFRAISH</t>
+          <t>LAIT</t>
         </is>
       </c>
     </row>
@@ -58957,20 +58917,20 @@
       </c>
       <c r="G971" s="1" t="inlineStr">
         <is>
-          <t>Astou DIENG</t>
+          <t>Papa SAMOURE</t>
         </is>
       </c>
       <c r="H971" s="1"/>
       <c r="I971" s="1" t="inlineStr">
         <is>
-          <t>Café stick Altimo 1,5gx09boites</t>
+          <t>Cafe au Lait 3-en-1</t>
         </is>
       </c>
       <c r="J971" s="1" t="n">
-        <v>1.0</v>
+        <v>0.8</v>
       </c>
       <c r="K971" s="1" t="n">
-        <v>28000.0</v>
+        <v>3600.0</v>
       </c>
       <c r="L971" s="1" t="n">
         <v>0.0</v>
@@ -58980,7 +58940,7 @@
       </c>
       <c r="N971" s="1"/>
       <c r="O971" s="1" t="n">
-        <v>611.0</v>
+        <v>625.0</v>
       </c>
       <c r="P971" s="1" t="inlineStr">
         <is>
@@ -58989,7 +58949,7 @@
       </c>
       <c r="Q971" s="1" t="inlineStr">
         <is>
-          <t>ALTIMO</t>
+          <t>LAIT</t>
         </is>
       </c>
     </row>
@@ -59022,20 +58982,20 @@
       </c>
       <c r="G972" s="1" t="inlineStr">
         <is>
-          <t>Awa COLY</t>
+          <t>Fallou SOLY</t>
         </is>
       </c>
       <c r="H972" s="1"/>
       <c r="I972" s="1" t="inlineStr">
         <is>
-          <t>Café stick Altimo 1,5gx09boites</t>
+          <t>Kamlac évaporé 48x160g</t>
         </is>
       </c>
       <c r="J972" s="1" t="n">
-        <v>0.22222222</v>
+        <v>0.5</v>
       </c>
       <c r="K972" s="1" t="n">
-        <v>6222.222</v>
+        <v>4500.0</v>
       </c>
       <c r="L972" s="1" t="n">
         <v>0.0</v>
@@ -59045,7 +59005,7 @@
       </c>
       <c r="N972" s="1"/>
       <c r="O972" s="1" t="n">
-        <v>612.0</v>
+        <v>626.0</v>
       </c>
       <c r="P972" s="1" t="inlineStr">
         <is>
@@ -59054,7 +59014,7 @@
       </c>
       <c r="Q972" s="1" t="inlineStr">
         <is>
-          <t>ALTIMO</t>
+          <t>LAIT</t>
         </is>
       </c>
     </row>
@@ -59087,20 +59047,20 @@
       </c>
       <c r="G973" s="1" t="inlineStr">
         <is>
-          <t>Adama</t>
+          <t>Fallou SOLY</t>
         </is>
       </c>
       <c r="H973" s="1"/>
       <c r="I973" s="1" t="inlineStr">
         <is>
-          <t>Café stick Altimo 1,5gx09boites</t>
+          <t>Cafe au Lait 3-en-1</t>
         </is>
       </c>
       <c r="J973" s="1" t="n">
-        <v>0.8888889</v>
+        <v>1.0</v>
       </c>
       <c r="K973" s="1" t="n">
-        <v>24888.889</v>
+        <v>4500.0</v>
       </c>
       <c r="L973" s="1" t="n">
         <v>0.0</v>
@@ -59110,7 +59070,7 @@
       </c>
       <c r="N973" s="1"/>
       <c r="O973" s="1" t="n">
-        <v>613.0</v>
+        <v>627.0</v>
       </c>
       <c r="P973" s="1" t="inlineStr">
         <is>
@@ -59119,7 +59079,7 @@
       </c>
       <c r="Q973" s="1" t="inlineStr">
         <is>
-          <t>ALTIMO</t>
+          <t>LAIT</t>
         </is>
       </c>
     </row>
@@ -59152,20 +59112,20 @@
       </c>
       <c r="G974" s="1" t="inlineStr">
         <is>
-          <t>Nogueye THIAME</t>
+          <t>Saly THIOUNE</t>
         </is>
       </c>
       <c r="H974" s="1"/>
       <c r="I974" s="1" t="inlineStr">
         <is>
-          <t>Chocolat transparent 400gx12pcs</t>
+          <t>Kamlac Thé 7g</t>
         </is>
       </c>
       <c r="J974" s="1" t="n">
-        <v>0.33333334</v>
+        <v>2.0</v>
       </c>
       <c r="K974" s="1" t="n">
-        <v>4166.6665</v>
+        <v>23000.0</v>
       </c>
       <c r="L974" s="1" t="n">
         <v>0.0</v>
@@ -59175,7 +59135,7 @@
       </c>
       <c r="N974" s="1"/>
       <c r="O974" s="1" t="n">
-        <v>614.0</v>
+        <v>628.0</v>
       </c>
       <c r="P974" s="1" t="inlineStr">
         <is>
@@ -59184,7 +59144,7 @@
       </c>
       <c r="Q974" s="1" t="inlineStr">
         <is>
-          <t>CHOC TRANS</t>
+          <t>THE</t>
         </is>
       </c>
     </row>
@@ -59207,30 +59167,22 @@
       </c>
       <c r="E975" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
-        </is>
-      </c>
-      <c r="F975" s="1" t="inlineStr">
-        <is>
-          <t>PIKINE</t>
-        </is>
-      </c>
-      <c r="G975" s="1" t="inlineStr">
-        <is>
-          <t>Amsatou GUEYE</t>
-        </is>
-      </c>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F975" s="1"/>
+      <c r="G975" s="1"/>
       <c r="H975" s="1"/>
       <c r="I975" s="1" t="inlineStr">
         <is>
-          <t>Chocolat 3-en-1 30x120 pcs</t>
+          <t>Café stick Refraish 1,5gx09boites</t>
         </is>
       </c>
       <c r="J975" s="1" t="n">
-        <v>0.1</v>
+        <v>7.5555553</v>
       </c>
       <c r="K975" s="1" t="n">
-        <v>1100.0</v>
+        <v>196444.44</v>
       </c>
       <c r="L975" s="1" t="n">
         <v>0.0</v>
@@ -59240,18 +59192,14 @@
       </c>
       <c r="N975" s="1"/>
       <c r="O975" s="1" t="n">
-        <v>615.0</v>
+        <v>629.0</v>
       </c>
       <c r="P975" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q975" s="1" t="inlineStr">
-        <is>
-          <t>CHOC TRANS</t>
-        </is>
-      </c>
+      <c r="Q975" s="1"/>
     </row>
     <row r="976">
       <c r="A976" s="2" t="n">
@@ -59272,30 +59220,22 @@
       </c>
       <c r="E976" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
-        </is>
-      </c>
-      <c r="F976" s="1" t="inlineStr">
-        <is>
-          <t>PIKINE</t>
-        </is>
-      </c>
-      <c r="G976" s="1" t="inlineStr">
-        <is>
-          <t>Amsatou GUEYE</t>
-        </is>
-      </c>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F976" s="1"/>
+      <c r="G976" s="1"/>
       <c r="H976" s="1"/>
       <c r="I976" s="1" t="inlineStr">
         <is>
-          <t>Chocolat transparent 400gx12pcs</t>
+          <t>Café pot Refraish 50g</t>
         </is>
       </c>
       <c r="J976" s="1" t="n">
-        <v>0.5</v>
+        <v>23.0</v>
       </c>
       <c r="K976" s="1" t="n">
-        <v>6250.0</v>
+        <v>258750.0</v>
       </c>
       <c r="L976" s="1" t="n">
         <v>0.0</v>
@@ -59305,18 +59245,14 @@
       </c>
       <c r="N976" s="1"/>
       <c r="O976" s="1" t="n">
-        <v>616.0</v>
+        <v>630.0</v>
       </c>
       <c r="P976" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q976" s="1" t="inlineStr">
-        <is>
-          <t>CHOC TRANS</t>
-        </is>
-      </c>
+      <c r="Q976" s="1"/>
     </row>
     <row r="977">
       <c r="A977" s="2" t="n">
@@ -59337,30 +59273,22 @@
       </c>
       <c r="E977" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
-        </is>
-      </c>
-      <c r="F977" s="1" t="inlineStr">
-        <is>
-          <t>PIKINE</t>
-        </is>
-      </c>
-      <c r="G977" s="1" t="inlineStr">
-        <is>
-          <t>Amsatou GUEYE</t>
-        </is>
-      </c>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F977" s="1"/>
+      <c r="G977" s="1"/>
       <c r="H977" s="1"/>
       <c r="I977" s="1" t="inlineStr">
         <is>
-          <t>Chocolat jaune 400g x 12 pcs</t>
+          <t>Café Refraish 100g</t>
         </is>
       </c>
       <c r="J977" s="1" t="n">
-        <v>0.5</v>
+        <v>7.1666665</v>
       </c>
       <c r="K977" s="1" t="n">
-        <v>7750.0</v>
+        <v>136166.67</v>
       </c>
       <c r="L977" s="1" t="n">
         <v>0.0</v>
@@ -59370,18 +59298,14 @@
       </c>
       <c r="N977" s="1"/>
       <c r="O977" s="1" t="n">
-        <v>617.0</v>
+        <v>631.0</v>
       </c>
       <c r="P977" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q977" s="1" t="inlineStr">
-        <is>
-          <t>CHOC TRANS</t>
-        </is>
-      </c>
+      <c r="Q977" s="1"/>
     </row>
     <row r="978">
       <c r="A978" s="2" t="n">
@@ -59402,30 +59326,22 @@
       </c>
       <c r="E978" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
-        </is>
-      </c>
-      <c r="F978" s="1" t="inlineStr">
-        <is>
-          <t>PIKINE</t>
-        </is>
-      </c>
-      <c r="G978" s="1" t="inlineStr">
-        <is>
-          <t>Oumou SALAM</t>
-        </is>
-      </c>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F978" s="1"/>
+      <c r="G978" s="1"/>
       <c r="H978" s="1"/>
       <c r="I978" s="1" t="inlineStr">
         <is>
-          <t>Chocolat Jaune 10gx60pcsx6 boites</t>
+          <t>Café pot Refraish 200g</t>
         </is>
       </c>
       <c r="J978" s="1" t="n">
-        <v>0.5</v>
+        <v>20.5</v>
       </c>
       <c r="K978" s="1" t="n">
-        <v>5000.0</v>
+        <v>399750.0</v>
       </c>
       <c r="L978" s="1" t="n">
         <v>0.0</v>
@@ -59435,18 +59351,14 @@
       </c>
       <c r="N978" s="1"/>
       <c r="O978" s="1" t="n">
-        <v>618.0</v>
+        <v>632.0</v>
       </c>
       <c r="P978" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q978" s="1" t="inlineStr">
-        <is>
-          <t>CHOC ORANGE</t>
-        </is>
-      </c>
+      <c r="Q978" s="1"/>
     </row>
     <row r="979">
       <c r="A979" s="2" t="n">
@@ -59467,30 +59379,22 @@
       </c>
       <c r="E979" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
-        </is>
-      </c>
-      <c r="F979" s="1" t="inlineStr">
-        <is>
-          <t>PIKINE</t>
-        </is>
-      </c>
-      <c r="G979" s="1" t="inlineStr">
-        <is>
-          <t>Oumou SALAM</t>
-        </is>
-      </c>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F979" s="1"/>
+      <c r="G979" s="1"/>
       <c r="H979" s="1"/>
       <c r="I979" s="1" t="inlineStr">
         <is>
-          <t>Chocolat Orange 10 g x 60 pcs x 6 boites</t>
+          <t>Café stick Altimo 1,5gx09boites</t>
         </is>
       </c>
       <c r="J979" s="1" t="n">
-        <v>0.16666667</v>
+        <v>13.111111</v>
       </c>
       <c r="K979" s="1" t="n">
-        <v>2000.0</v>
+        <v>367111.12</v>
       </c>
       <c r="L979" s="1" t="n">
         <v>0.0</v>
@@ -59500,18 +59404,14 @@
       </c>
       <c r="N979" s="1"/>
       <c r="O979" s="1" t="n">
-        <v>619.0</v>
+        <v>633.0</v>
       </c>
       <c r="P979" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q979" s="1" t="inlineStr">
-        <is>
-          <t>CHOC ORANGE</t>
-        </is>
-      </c>
+      <c r="Q979" s="1"/>
     </row>
     <row r="980">
       <c r="A980" s="2" t="n">
@@ -59532,30 +59432,22 @@
       </c>
       <c r="E980" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
-        </is>
-      </c>
-      <c r="F980" s="1" t="inlineStr">
-        <is>
-          <t>PIKINE</t>
-        </is>
-      </c>
-      <c r="G980" s="1" t="inlineStr">
-        <is>
-          <t>Aissatou DIALLO</t>
-        </is>
-      </c>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F980" s="1"/>
+      <c r="G980" s="1"/>
       <c r="H980" s="1"/>
       <c r="I980" s="1" t="inlineStr">
         <is>
-          <t>Chocolat Jaune 10gx60pcsx6 boites</t>
+          <t>Café Altimo pot 50g x 24 pcs</t>
         </is>
       </c>
       <c r="J980" s="1" t="n">
-        <v>1.3333334</v>
+        <v>8.791667</v>
       </c>
       <c r="K980" s="1" t="n">
-        <v>13333.333</v>
+        <v>153854.17</v>
       </c>
       <c r="L980" s="1" t="n">
         <v>0.0</v>
@@ -59565,18 +59457,14 @@
       </c>
       <c r="N980" s="1"/>
       <c r="O980" s="1" t="n">
-        <v>620.0</v>
+        <v>634.0</v>
       </c>
       <c r="P980" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q980" s="1" t="inlineStr">
-        <is>
-          <t>CHOC ORANGE</t>
-        </is>
-      </c>
+      <c r="Q980" s="1"/>
     </row>
     <row r="981">
       <c r="A981" s="2" t="n">
@@ -59597,30 +59485,22 @@
       </c>
       <c r="E981" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
-        </is>
-      </c>
-      <c r="F981" s="1" t="inlineStr">
-        <is>
-          <t>PIKINE</t>
-        </is>
-      </c>
-      <c r="G981" s="1" t="inlineStr">
-        <is>
-          <t>Aissatou DIALLO</t>
-        </is>
-      </c>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F981" s="1"/>
+      <c r="G981" s="1"/>
       <c r="H981" s="1"/>
       <c r="I981" s="1" t="inlineStr">
         <is>
-          <t>Chocolat Orange 10 g x 60 pcs x 6 boites</t>
+          <t>Café Altimo pot 100g x 24 pcs</t>
         </is>
       </c>
       <c r="J981" s="1" t="n">
-        <v>0.33333334</v>
+        <v>8.208333</v>
       </c>
       <c r="K981" s="1" t="n">
-        <v>4000.0</v>
+        <v>274979.16</v>
       </c>
       <c r="L981" s="1" t="n">
         <v>0.0</v>
@@ -59630,18 +59510,14 @@
       </c>
       <c r="N981" s="1"/>
       <c r="O981" s="1" t="n">
-        <v>621.0</v>
+        <v>635.0</v>
       </c>
       <c r="P981" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q981" s="1" t="inlineStr">
-        <is>
-          <t>CHOC ORANGE</t>
-        </is>
-      </c>
+      <c r="Q981" s="1"/>
     </row>
     <row r="982">
       <c r="A982" s="2" t="n">
@@ -59662,30 +59538,22 @@
       </c>
       <c r="E982" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
-        </is>
-      </c>
-      <c r="F982" s="1" t="inlineStr">
-        <is>
-          <t>PIKINE</t>
-        </is>
-      </c>
-      <c r="G982" s="1" t="inlineStr">
-        <is>
-          <t>Baye Cheikh</t>
-        </is>
-      </c>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F982" s="1"/>
+      <c r="G982" s="1"/>
       <c r="H982" s="1"/>
       <c r="I982" s="1" t="inlineStr">
         <is>
-          <t>Cafe au Lait 3-en-1</t>
+          <t>Café Altimo pot 200g x 12 pcs</t>
         </is>
       </c>
       <c r="J982" s="1" t="n">
-        <v>1.0</v>
+        <v>5.6666665</v>
       </c>
       <c r="K982" s="1" t="n">
-        <v>4500.0</v>
+        <v>189833.33</v>
       </c>
       <c r="L982" s="1" t="n">
         <v>0.0</v>
@@ -59695,18 +59563,14 @@
       </c>
       <c r="N982" s="1"/>
       <c r="O982" s="1" t="n">
-        <v>622.0</v>
+        <v>636.0</v>
       </c>
       <c r="P982" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q982" s="1" t="inlineStr">
-        <is>
-          <t>LAIT</t>
-        </is>
-      </c>
+      <c r="Q982" s="1"/>
     </row>
     <row r="983">
       <c r="A983" s="2" t="n">
@@ -59727,19 +59591,11 @@
       </c>
       <c r="E983" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
-        </is>
-      </c>
-      <c r="F983" s="1" t="inlineStr">
-        <is>
-          <t>PIKINE</t>
-        </is>
-      </c>
-      <c r="G983" s="1" t="inlineStr">
-        <is>
-          <t>Pape DABO</t>
-        </is>
-      </c>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F983" s="1"/>
+      <c r="G983" s="1"/>
       <c r="H983" s="1"/>
       <c r="I983" s="1" t="inlineStr">
         <is>
@@ -59747,10 +59603,10 @@
         </is>
       </c>
       <c r="J983" s="1" t="n">
-        <v>1.0</v>
+        <v>3.5</v>
       </c>
       <c r="K983" s="1" t="n">
-        <v>9000.0</v>
+        <v>31500.0</v>
       </c>
       <c r="L983" s="1" t="n">
         <v>0.0</v>
@@ -59760,18 +59616,14 @@
       </c>
       <c r="N983" s="1"/>
       <c r="O983" s="1" t="n">
-        <v>623.0</v>
+        <v>637.0</v>
       </c>
       <c r="P983" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q983" s="1" t="inlineStr">
-        <is>
-          <t>LAIT</t>
-        </is>
-      </c>
+      <c r="Q983" s="1"/>
     </row>
     <row r="984">
       <c r="A984" s="2" t="n">
@@ -59792,30 +59644,22 @@
       </c>
       <c r="E984" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
-        </is>
-      </c>
-      <c r="F984" s="1" t="inlineStr">
-        <is>
-          <t>PIKINE</t>
-        </is>
-      </c>
-      <c r="G984" s="1" t="inlineStr">
-        <is>
-          <t>Pape DABO</t>
-        </is>
-      </c>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F984" s="1"/>
+      <c r="G984" s="1"/>
       <c r="H984" s="1"/>
       <c r="I984" s="1" t="inlineStr">
         <is>
-          <t>Cafe au Lait 3-en-1</t>
+          <t>KamLac Lait concentré sucré 24x1kg</t>
         </is>
       </c>
       <c r="J984" s="1" t="n">
-        <v>0.2</v>
+        <v>1.5416666</v>
       </c>
       <c r="K984" s="1" t="n">
-        <v>900.0</v>
+        <v>40854.168</v>
       </c>
       <c r="L984" s="1" t="n">
         <v>0.0</v>
@@ -59825,18 +59669,14 @@
       </c>
       <c r="N984" s="1"/>
       <c r="O984" s="1" t="n">
-        <v>624.0</v>
+        <v>638.0</v>
       </c>
       <c r="P984" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q984" s="1" t="inlineStr">
-        <is>
-          <t>LAIT</t>
-        </is>
-      </c>
+      <c r="Q984" s="1"/>
     </row>
     <row r="985">
       <c r="A985" s="2" t="n">
@@ -59857,30 +59697,22 @@
       </c>
       <c r="E985" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
-        </is>
-      </c>
-      <c r="F985" s="1" t="inlineStr">
-        <is>
-          <t>PIKINE</t>
-        </is>
-      </c>
-      <c r="G985" s="1" t="inlineStr">
-        <is>
-          <t>Papa SAMOURE</t>
-        </is>
-      </c>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F985" s="1"/>
+      <c r="G985" s="1"/>
       <c r="H985" s="1"/>
       <c r="I985" s="1" t="inlineStr">
         <is>
-          <t>Cafe au Lait 3-en-1</t>
+          <t>Lait Janus 18gx10</t>
         </is>
       </c>
       <c r="J985" s="1" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="K985" s="1" t="n">
-        <v>3600.0</v>
+        <v>1200.0</v>
       </c>
       <c r="L985" s="1" t="n">
         <v>0.0</v>
@@ -59890,18 +59722,14 @@
       </c>
       <c r="N985" s="1"/>
       <c r="O985" s="1" t="n">
-        <v>625.0</v>
+        <v>639.0</v>
       </c>
       <c r="P985" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q985" s="1" t="inlineStr">
-        <is>
-          <t>LAIT</t>
-        </is>
-      </c>
+      <c r="Q985" s="1"/>
     </row>
     <row r="986">
       <c r="A986" s="2" t="n">
@@ -59922,30 +59750,22 @@
       </c>
       <c r="E986" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
-        </is>
-      </c>
-      <c r="F986" s="1" t="inlineStr">
-        <is>
-          <t>PIKINE</t>
-        </is>
-      </c>
-      <c r="G986" s="1" t="inlineStr">
-        <is>
-          <t>Fallou SOLY</t>
-        </is>
-      </c>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F986" s="1"/>
+      <c r="G986" s="1"/>
       <c r="H986" s="1"/>
       <c r="I986" s="1" t="inlineStr">
         <is>
-          <t>Kamlac évaporé 48x160g</t>
+          <t>Chocolat transparent 200gx24pcs</t>
         </is>
       </c>
       <c r="J986" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="K986" s="1" t="n">
-        <v>4500.0</v>
+        <v>6250.0</v>
       </c>
       <c r="L986" s="1" t="n">
         <v>0.0</v>
@@ -59955,18 +59775,14 @@
       </c>
       <c r="N986" s="1"/>
       <c r="O986" s="1" t="n">
-        <v>626.0</v>
+        <v>640.0</v>
       </c>
       <c r="P986" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q986" s="1" t="inlineStr">
-        <is>
-          <t>LAIT</t>
-        </is>
-      </c>
+      <c r="Q986" s="1"/>
     </row>
     <row r="987">
       <c r="A987" s="2" t="n">
@@ -59987,30 +59803,22 @@
       </c>
       <c r="E987" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
-        </is>
-      </c>
-      <c r="F987" s="1" t="inlineStr">
-        <is>
-          <t>PIKINE</t>
-        </is>
-      </c>
-      <c r="G987" s="1" t="inlineStr">
-        <is>
-          <t>Fallou SOLY</t>
-        </is>
-      </c>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F987" s="1"/>
+      <c r="G987" s="1"/>
       <c r="H987" s="1"/>
       <c r="I987" s="1" t="inlineStr">
         <is>
-          <t>Cafe au Lait 3-en-1</t>
+          <t>Chocolat 3-en-1 30x120 pcs</t>
         </is>
       </c>
       <c r="J987" s="1" t="n">
-        <v>1.0</v>
+        <v>8.9</v>
       </c>
       <c r="K987" s="1" t="n">
-        <v>4500.0</v>
+        <v>97900.0</v>
       </c>
       <c r="L987" s="1" t="n">
         <v>0.0</v>
@@ -60020,18 +59828,14 @@
       </c>
       <c r="N987" s="1"/>
       <c r="O987" s="1" t="n">
-        <v>627.0</v>
+        <v>641.0</v>
       </c>
       <c r="P987" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q987" s="1" t="inlineStr">
-        <is>
-          <t>LAIT</t>
-        </is>
-      </c>
+      <c r="Q987" s="1"/>
     </row>
     <row r="988">
       <c r="A988" s="2" t="n">
@@ -60052,30 +59856,22 @@
       </c>
       <c r="E988" s="1" t="inlineStr">
         <is>
-          <t>Vente</t>
-        </is>
-      </c>
-      <c r="F988" s="1" t="inlineStr">
-        <is>
-          <t>PIKINE</t>
-        </is>
-      </c>
-      <c r="G988" s="1" t="inlineStr">
-        <is>
-          <t>Saly THIOUNE</t>
-        </is>
-      </c>
+          <t>Stock Descente</t>
+        </is>
+      </c>
+      <c r="F988" s="1"/>
+      <c r="G988" s="1"/>
       <c r="H988" s="1"/>
       <c r="I988" s="1" t="inlineStr">
         <is>
-          <t>Kamlac Thé 7g</t>
+          <t>Chocolat transparent 400gx12pcs</t>
         </is>
       </c>
       <c r="J988" s="1" t="n">
-        <v>2.0</v>
+        <v>6.1666665</v>
       </c>
       <c r="K988" s="1" t="n">
-        <v>23000.0</v>
+        <v>77083.336</v>
       </c>
       <c r="L988" s="1" t="n">
         <v>0.0</v>
@@ -60085,18 +59881,14 @@
       </c>
       <c r="N988" s="1"/>
       <c r="O988" s="1" t="n">
-        <v>628.0</v>
+        <v>642.0</v>
       </c>
       <c r="P988" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q988" s="1" t="inlineStr">
-        <is>
-          <t>THE</t>
-        </is>
-      </c>
+      <c r="Q988" s="1"/>
     </row>
     <row r="989">
       <c r="A989" s="2" t="n">
@@ -60125,14 +59917,14 @@
       <c r="H989" s="1"/>
       <c r="I989" s="1" t="inlineStr">
         <is>
-          <t>Café stick Refraish 1,5gx09boites</t>
+          <t>Chocolat Jaune 10gx60pcsx6 boites</t>
         </is>
       </c>
       <c r="J989" s="1" t="n">
-        <v>7.5555553</v>
+        <v>8.0</v>
       </c>
       <c r="K989" s="1" t="n">
-        <v>196444.44</v>
+        <v>80000.0</v>
       </c>
       <c r="L989" s="1" t="n">
         <v>0.0</v>
@@ -60142,7 +59934,7 @@
       </c>
       <c r="N989" s="1"/>
       <c r="O989" s="1" t="n">
-        <v>629.0</v>
+        <v>643.0</v>
       </c>
       <c r="P989" s="1" t="inlineStr">
         <is>
@@ -60178,14 +59970,14 @@
       <c r="H990" s="1"/>
       <c r="I990" s="1" t="inlineStr">
         <is>
-          <t>Café pot Refraish 50g</t>
+          <t>Chocolat jaune 400g x 12 pcs</t>
         </is>
       </c>
       <c r="J990" s="1" t="n">
-        <v>23.0</v>
+        <v>7.9166665</v>
       </c>
       <c r="K990" s="1" t="n">
-        <v>258750.0</v>
+        <v>122708.336</v>
       </c>
       <c r="L990" s="1" t="n">
         <v>0.0</v>
@@ -60195,7 +59987,7 @@
       </c>
       <c r="N990" s="1"/>
       <c r="O990" s="1" t="n">
-        <v>630.0</v>
+        <v>644.0</v>
       </c>
       <c r="P990" s="1" t="inlineStr">
         <is>
@@ -60231,14 +60023,14 @@
       <c r="H991" s="1"/>
       <c r="I991" s="1" t="inlineStr">
         <is>
-          <t>Café Refraish 100g</t>
+          <t>Chocolat Orange 10 g x 60 pcs x 6 boites</t>
         </is>
       </c>
       <c r="J991" s="1" t="n">
-        <v>7.1666665</v>
+        <v>4.6666665</v>
       </c>
       <c r="K991" s="1" t="n">
-        <v>136166.67</v>
+        <v>56000.0</v>
       </c>
       <c r="L991" s="1" t="n">
         <v>0.0</v>
@@ -60248,7 +60040,7 @@
       </c>
       <c r="N991" s="1"/>
       <c r="O991" s="1" t="n">
-        <v>631.0</v>
+        <v>645.0</v>
       </c>
       <c r="P991" s="1" t="inlineStr">
         <is>
@@ -60284,14 +60076,14 @@
       <c r="H992" s="1"/>
       <c r="I992" s="1" t="inlineStr">
         <is>
-          <t>Café pot Refraish 200g</t>
+          <t>Chocolat Orange 400g x12 pcs</t>
         </is>
       </c>
       <c r="J992" s="1" t="n">
-        <v>20.5</v>
+        <v>1.5</v>
       </c>
       <c r="K992" s="1" t="n">
-        <v>399750.0</v>
+        <v>27000.0</v>
       </c>
       <c r="L992" s="1" t="n">
         <v>0.0</v>
@@ -60301,7 +60093,7 @@
       </c>
       <c r="N992" s="1"/>
       <c r="O992" s="1" t="n">
-        <v>632.0</v>
+        <v>646.0</v>
       </c>
       <c r="P992" s="1" t="inlineStr">
         <is>
@@ -60337,14 +60129,14 @@
       <c r="H993" s="1"/>
       <c r="I993" s="1" t="inlineStr">
         <is>
-          <t>Café stick Altimo 1,5gx09boites</t>
+          <t>Cafe au Lait 3-en-1</t>
         </is>
       </c>
       <c r="J993" s="1" t="n">
-        <v>13.111111</v>
+        <v>10.2</v>
       </c>
       <c r="K993" s="1" t="n">
-        <v>367111.12</v>
+        <v>45900.0</v>
       </c>
       <c r="L993" s="1" t="n">
         <v>0.0</v>
@@ -60354,7 +60146,7 @@
       </c>
       <c r="N993" s="1"/>
       <c r="O993" s="1" t="n">
-        <v>633.0</v>
+        <v>647.0</v>
       </c>
       <c r="P993" s="1" t="inlineStr">
         <is>
@@ -60390,14 +60182,14 @@
       <c r="H994" s="1"/>
       <c r="I994" s="1" t="inlineStr">
         <is>
-          <t>Café Altimo pot 50g x 24 pcs</t>
+          <t>Kamlac Thé 7g</t>
         </is>
       </c>
       <c r="J994" s="1" t="n">
-        <v>8.791667</v>
+        <v>8.875</v>
       </c>
       <c r="K994" s="1" t="n">
-        <v>153854.17</v>
+        <v>102062.5</v>
       </c>
       <c r="L994" s="1" t="n">
         <v>0.0</v>
@@ -60407,7 +60199,7 @@
       </c>
       <c r="N994" s="1"/>
       <c r="O994" s="1" t="n">
-        <v>634.0</v>
+        <v>648.0</v>
       </c>
       <c r="P994" s="1" t="inlineStr">
         <is>
@@ -60435,7 +60227,7 @@
       </c>
       <c r="E995" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
+          <t>Stock Lundi</t>
         </is>
       </c>
       <c r="F995" s="1"/>
@@ -60443,14 +60235,14 @@
       <c r="H995" s="1"/>
       <c r="I995" s="1" t="inlineStr">
         <is>
-          <t>Café Altimo pot 100g x 24 pcs</t>
+          <t>Café pot Refraish 200g</t>
         </is>
       </c>
       <c r="J995" s="1" t="n">
-        <v>8.208333</v>
+        <v>6.0</v>
       </c>
       <c r="K995" s="1" t="n">
-        <v>274979.16</v>
+        <v>117000.0</v>
       </c>
       <c r="L995" s="1" t="n">
         <v>0.0</v>
@@ -60460,7 +60252,7 @@
       </c>
       <c r="N995" s="1"/>
       <c r="O995" s="1" t="n">
-        <v>635.0</v>
+        <v>649.0</v>
       </c>
       <c r="P995" s="1" t="inlineStr">
         <is>
@@ -60488,22 +60280,30 @@
       </c>
       <c r="E996" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
-        </is>
-      </c>
-      <c r="F996" s="1"/>
-      <c r="G996" s="1"/>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F996" s="1" t="inlineStr">
+        <is>
+          <t>PIKINE</t>
+        </is>
+      </c>
+      <c r="G996" s="1" t="inlineStr">
+        <is>
+          <t>Coura DIONE</t>
+        </is>
+      </c>
       <c r="H996" s="1"/>
       <c r="I996" s="1" t="inlineStr">
         <is>
-          <t>Café Altimo pot 200g x 12 pcs</t>
+          <t>Café pot Refraish 200g</t>
         </is>
       </c>
       <c r="J996" s="1" t="n">
-        <v>5.6666665</v>
+        <v>0.5</v>
       </c>
       <c r="K996" s="1" t="n">
-        <v>189833.33</v>
+        <v>9750.0</v>
       </c>
       <c r="L996" s="1" t="n">
         <v>0.0</v>
@@ -60511,16 +60311,24 @@
       <c r="M996" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="N996" s="1"/>
+      <c r="N996" s="1" t="inlineStr">
+        <is>
+          <t>Nd</t>
+        </is>
+      </c>
       <c r="O996" s="1" t="n">
-        <v>636.0</v>
+        <v>650.0</v>
       </c>
       <c r="P996" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q996" s="1"/>
+      <c r="Q996" s="1" t="inlineStr">
+        <is>
+          <t>REFRAISH</t>
+        </is>
+      </c>
     </row>
     <row r="997">
       <c r="A997" s="2" t="n">
@@ -60541,22 +60349,30 @@
       </c>
       <c r="E997" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
-        </is>
-      </c>
-      <c r="F997" s="1"/>
-      <c r="G997" s="1"/>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F997" s="1" t="inlineStr">
+        <is>
+          <t>PIKINE</t>
+        </is>
+      </c>
+      <c r="G997" s="1" t="inlineStr">
+        <is>
+          <t>Coura DIONE</t>
+        </is>
+      </c>
       <c r="H997" s="1"/>
       <c r="I997" s="1" t="inlineStr">
         <is>
-          <t>Kamlac évaporé 48x160g</t>
+          <t>Café Refraish 100g</t>
         </is>
       </c>
       <c r="J997" s="1" t="n">
-        <v>3.5</v>
+        <v>0.041666668</v>
       </c>
       <c r="K997" s="1" t="n">
-        <v>31500.0</v>
+        <v>791.6667</v>
       </c>
       <c r="L997" s="1" t="n">
         <v>0.0</v>
@@ -60564,16 +60380,24 @@
       <c r="M997" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="N997" s="1"/>
+      <c r="N997" s="1" t="inlineStr">
+        <is>
+          <t>Nd</t>
+        </is>
+      </c>
       <c r="O997" s="1" t="n">
-        <v>637.0</v>
+        <v>651.0</v>
       </c>
       <c r="P997" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q997" s="1"/>
+      <c r="Q997" s="1" t="inlineStr">
+        <is>
+          <t>REFRAISH</t>
+        </is>
+      </c>
     </row>
     <row r="998">
       <c r="A998" s="2" t="n">
@@ -60594,22 +60418,30 @@
       </c>
       <c r="E998" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
-        </is>
-      </c>
-      <c r="F998" s="1"/>
-      <c r="G998" s="1"/>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F998" s="1" t="inlineStr">
+        <is>
+          <t>PIKINE</t>
+        </is>
+      </c>
+      <c r="G998" s="1" t="inlineStr">
+        <is>
+          <t>Coura DIONE</t>
+        </is>
+      </c>
       <c r="H998" s="1"/>
       <c r="I998" s="1" t="inlineStr">
         <is>
-          <t>KamLac Lait concentré sucré 24x1kg</t>
+          <t>Café stick Refraish 1,5gx09boites</t>
         </is>
       </c>
       <c r="J998" s="1" t="n">
-        <v>1.5416666</v>
+        <v>1.0</v>
       </c>
       <c r="K998" s="1" t="n">
-        <v>40854.168</v>
+        <v>26000.0</v>
       </c>
       <c r="L998" s="1" t="n">
         <v>0.0</v>
@@ -60617,16 +60449,24 @@
       <c r="M998" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="N998" s="1"/>
+      <c r="N998" s="1" t="inlineStr">
+        <is>
+          <t>Nd</t>
+        </is>
+      </c>
       <c r="O998" s="1" t="n">
-        <v>638.0</v>
+        <v>652.0</v>
       </c>
       <c r="P998" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q998" s="1"/>
+      <c r="Q998" s="1" t="inlineStr">
+        <is>
+          <t>REFRAISH</t>
+        </is>
+      </c>
     </row>
     <row r="999">
       <c r="A999" s="2" t="n">
@@ -60647,22 +60487,30 @@
       </c>
       <c r="E999" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
-        </is>
-      </c>
-      <c r="F999" s="1"/>
-      <c r="G999" s="1"/>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F999" s="1" t="inlineStr">
+        <is>
+          <t>PIKINE</t>
+        </is>
+      </c>
+      <c r="G999" s="1" t="inlineStr">
+        <is>
+          <t>Adama</t>
+        </is>
+      </c>
       <c r="H999" s="1"/>
       <c r="I999" s="1" t="inlineStr">
         <is>
-          <t>Lait Janus 18gx10</t>
+          <t>Café Altimo pot 100g x 24 pcs</t>
         </is>
       </c>
       <c r="J999" s="1" t="n">
-        <v>0.2</v>
+        <v>0.041666668</v>
       </c>
       <c r="K999" s="1" t="n">
-        <v>1200.0</v>
+        <v>1395.8334</v>
       </c>
       <c r="L999" s="1" t="n">
         <v>0.0</v>
@@ -60670,16 +60518,24 @@
       <c r="M999" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="N999" s="1"/>
+      <c r="N999" s="1" t="inlineStr">
+        <is>
+          <t>Nd</t>
+        </is>
+      </c>
       <c r="O999" s="1" t="n">
-        <v>639.0</v>
+        <v>653.0</v>
       </c>
       <c r="P999" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q999" s="1"/>
+      <c r="Q999" s="1" t="inlineStr">
+        <is>
+          <t>ALTIMO</t>
+        </is>
+      </c>
     </row>
     <row r="1000">
       <c r="A1000" s="2" t="n">
@@ -60700,22 +60556,30 @@
       </c>
       <c r="E1000" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
-        </is>
-      </c>
-      <c r="F1000" s="1"/>
-      <c r="G1000" s="1"/>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F1000" s="1" t="inlineStr">
+        <is>
+          <t>PIKINE</t>
+        </is>
+      </c>
+      <c r="G1000" s="1" t="inlineStr">
+        <is>
+          <t>Adama</t>
+        </is>
+      </c>
       <c r="H1000" s="1"/>
       <c r="I1000" s="1" t="inlineStr">
         <is>
-          <t>Chocolat transparent 200gx24pcs</t>
+          <t>Café Altimo pot 200g x 12 pcs</t>
         </is>
       </c>
       <c r="J1000" s="1" t="n">
-        <v>0.5</v>
+        <v>0.6666667</v>
       </c>
       <c r="K1000" s="1" t="n">
-        <v>6250.0</v>
+        <v>22333.334</v>
       </c>
       <c r="L1000" s="1" t="n">
         <v>0.0</v>
@@ -60723,16 +60587,24 @@
       <c r="M1000" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="N1000" s="1"/>
+      <c r="N1000" s="1" t="inlineStr">
+        <is>
+          <t>Nd</t>
+        </is>
+      </c>
       <c r="O1000" s="1" t="n">
-        <v>640.0</v>
+        <v>654.0</v>
       </c>
       <c r="P1000" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q1000" s="1"/>
+      <c r="Q1000" s="1" t="inlineStr">
+        <is>
+          <t>ALTIMO</t>
+        </is>
+      </c>
     </row>
     <row r="1001">
       <c r="A1001" s="2" t="n">
@@ -60753,22 +60625,30 @@
       </c>
       <c r="E1001" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
-        </is>
-      </c>
-      <c r="F1001" s="1"/>
-      <c r="G1001" s="1"/>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F1001" s="1" t="inlineStr">
+        <is>
+          <t>PIKINE</t>
+        </is>
+      </c>
+      <c r="G1001" s="1" t="inlineStr">
+        <is>
+          <t>Nogueye THIAME</t>
+        </is>
+      </c>
       <c r="H1001" s="1"/>
       <c r="I1001" s="1" t="inlineStr">
         <is>
-          <t>Chocolat 3-en-1 30x120 pcs</t>
+          <t>Chocolat transparent 200gx24pcs</t>
         </is>
       </c>
       <c r="J1001" s="1" t="n">
-        <v>8.9</v>
+        <v>1.0</v>
       </c>
       <c r="K1001" s="1" t="n">
-        <v>97900.0</v>
+        <v>12500.0</v>
       </c>
       <c r="L1001" s="1" t="n">
         <v>0.0</v>
@@ -60776,16 +60656,24 @@
       <c r="M1001" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="N1001" s="1"/>
+      <c r="N1001" s="1" t="inlineStr">
+        <is>
+          <t>Nd</t>
+        </is>
+      </c>
       <c r="O1001" s="1" t="n">
-        <v>641.0</v>
+        <v>655.0</v>
       </c>
       <c r="P1001" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q1001" s="1"/>
+      <c r="Q1001" s="1" t="inlineStr">
+        <is>
+          <t>CHOC TRANS</t>
+        </is>
+      </c>
     </row>
     <row r="1002">
       <c r="A1002" s="2" t="n">
@@ -60806,11 +60694,19 @@
       </c>
       <c r="E1002" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
-        </is>
-      </c>
-      <c r="F1002" s="1"/>
-      <c r="G1002" s="1"/>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F1002" s="1" t="inlineStr">
+        <is>
+          <t>PIKINE</t>
+        </is>
+      </c>
+      <c r="G1002" s="1" t="inlineStr">
+        <is>
+          <t>Nogueye THIAME</t>
+        </is>
+      </c>
       <c r="H1002" s="1"/>
       <c r="I1002" s="1" t="inlineStr">
         <is>
@@ -60818,10 +60714,10 @@
         </is>
       </c>
       <c r="J1002" s="1" t="n">
-        <v>6.1666665</v>
+        <v>1.0</v>
       </c>
       <c r="K1002" s="1" t="n">
-        <v>77083.336</v>
+        <v>12500.0</v>
       </c>
       <c r="L1002" s="1" t="n">
         <v>0.0</v>
@@ -60829,16 +60725,24 @@
       <c r="M1002" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="N1002" s="1"/>
+      <c r="N1002" s="1" t="inlineStr">
+        <is>
+          <t>Nd</t>
+        </is>
+      </c>
       <c r="O1002" s="1" t="n">
-        <v>642.0</v>
+        <v>656.0</v>
       </c>
       <c r="P1002" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q1002" s="1"/>
+      <c r="Q1002" s="1" t="inlineStr">
+        <is>
+          <t>CHOC TRANS</t>
+        </is>
+      </c>
     </row>
     <row r="1003">
       <c r="A1003" s="2" t="n">
@@ -60859,22 +60763,30 @@
       </c>
       <c r="E1003" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
-        </is>
-      </c>
-      <c r="F1003" s="1"/>
-      <c r="G1003" s="1"/>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F1003" s="1" t="inlineStr">
+        <is>
+          <t>PIKINE</t>
+        </is>
+      </c>
+      <c r="G1003" s="1" t="inlineStr">
+        <is>
+          <t>Nogueye THIAME</t>
+        </is>
+      </c>
       <c r="H1003" s="1"/>
       <c r="I1003" s="1" t="inlineStr">
         <is>
-          <t>Chocolat Jaune 10gx60pcsx6 boites</t>
+          <t>Chocolat 3-en-1 30x120 pcs</t>
         </is>
       </c>
       <c r="J1003" s="1" t="n">
-        <v>8.0</v>
+        <v>0.2</v>
       </c>
       <c r="K1003" s="1" t="n">
-        <v>80000.0</v>
+        <v>2200.0</v>
       </c>
       <c r="L1003" s="1" t="n">
         <v>0.0</v>
@@ -60882,16 +60794,24 @@
       <c r="M1003" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="N1003" s="1"/>
+      <c r="N1003" s="1" t="inlineStr">
+        <is>
+          <t>Nd</t>
+        </is>
+      </c>
       <c r="O1003" s="1" t="n">
-        <v>643.0</v>
+        <v>657.0</v>
       </c>
       <c r="P1003" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q1003" s="1"/>
+      <c r="Q1003" s="1" t="inlineStr">
+        <is>
+          <t>CHOC TRANS</t>
+        </is>
+      </c>
     </row>
     <row r="1004">
       <c r="A1004" s="2" t="n">
@@ -60912,22 +60832,30 @@
       </c>
       <c r="E1004" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
-        </is>
-      </c>
-      <c r="F1004" s="1"/>
-      <c r="G1004" s="1"/>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F1004" s="1" t="inlineStr">
+        <is>
+          <t>PIKINE</t>
+        </is>
+      </c>
+      <c r="G1004" s="1" t="inlineStr">
+        <is>
+          <t>Baye Cheikh</t>
+        </is>
+      </c>
       <c r="H1004" s="1"/>
       <c r="I1004" s="1" t="inlineStr">
         <is>
-          <t>Chocolat jaune 400g x 12 pcs</t>
+          <t>Kamlac évaporé 48x160g</t>
         </is>
       </c>
       <c r="J1004" s="1" t="n">
-        <v>7.9166665</v>
+        <v>1.0</v>
       </c>
       <c r="K1004" s="1" t="n">
-        <v>122708.336</v>
+        <v>9000.0</v>
       </c>
       <c r="L1004" s="1" t="n">
         <v>0.0</v>
@@ -60935,16 +60863,24 @@
       <c r="M1004" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="N1004" s="1"/>
+      <c r="N1004" s="1" t="inlineStr">
+        <is>
+          <t>Nd</t>
+        </is>
+      </c>
       <c r="O1004" s="1" t="n">
-        <v>644.0</v>
+        <v>658.0</v>
       </c>
       <c r="P1004" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q1004" s="1"/>
+      <c r="Q1004" s="1" t="inlineStr">
+        <is>
+          <t>LAIT</t>
+        </is>
+      </c>
     </row>
     <row r="1005">
       <c r="A1005" s="2" t="n">
@@ -60965,22 +60901,30 @@
       </c>
       <c r="E1005" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
-        </is>
-      </c>
-      <c r="F1005" s="1"/>
-      <c r="G1005" s="1"/>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F1005" s="1" t="inlineStr">
+        <is>
+          <t>PIKINE</t>
+        </is>
+      </c>
+      <c r="G1005" s="1" t="inlineStr">
+        <is>
+          <t>Baye Cheikh</t>
+        </is>
+      </c>
       <c r="H1005" s="1"/>
       <c r="I1005" s="1" t="inlineStr">
         <is>
-          <t>Chocolat Orange 10 g x 60 pcs x 6 boites</t>
+          <t>KamLac Lait concentré sucré 24x1kg</t>
         </is>
       </c>
       <c r="J1005" s="1" t="n">
-        <v>4.6666665</v>
+        <v>0.5</v>
       </c>
       <c r="K1005" s="1" t="n">
-        <v>56000.0</v>
+        <v>13250.0</v>
       </c>
       <c r="L1005" s="1" t="n">
         <v>0.0</v>
@@ -60988,16 +60932,24 @@
       <c r="M1005" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="N1005" s="1"/>
+      <c r="N1005" s="1" t="inlineStr">
+        <is>
+          <t>Nd</t>
+        </is>
+      </c>
       <c r="O1005" s="1" t="n">
-        <v>645.0</v>
+        <v>659.0</v>
       </c>
       <c r="P1005" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q1005" s="1"/>
+      <c r="Q1005" s="1" t="inlineStr">
+        <is>
+          <t>LAIT</t>
+        </is>
+      </c>
     </row>
     <row r="1006">
       <c r="A1006" s="2" t="n">
@@ -61018,22 +60970,30 @@
       </c>
       <c r="E1006" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
-        </is>
-      </c>
-      <c r="F1006" s="1"/>
-      <c r="G1006" s="1"/>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F1006" s="1" t="inlineStr">
+        <is>
+          <t>PIKINE</t>
+        </is>
+      </c>
+      <c r="G1006" s="1" t="inlineStr">
+        <is>
+          <t>Baye Cheikh</t>
+        </is>
+      </c>
       <c r="H1006" s="1"/>
       <c r="I1006" s="1" t="inlineStr">
         <is>
-          <t>Chocolat Orange 400g x12 pcs</t>
+          <t>Lait Janus 18gx10</t>
         </is>
       </c>
       <c r="J1006" s="1" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="K1006" s="1" t="n">
-        <v>27000.0</v>
+        <v>1200.0</v>
       </c>
       <c r="L1006" s="1" t="n">
         <v>0.0</v>
@@ -61041,16 +61001,24 @@
       <c r="M1006" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="N1006" s="1"/>
+      <c r="N1006" s="1" t="inlineStr">
+        <is>
+          <t>Nd</t>
+        </is>
+      </c>
       <c r="O1006" s="1" t="n">
-        <v>646.0</v>
+        <v>660.0</v>
       </c>
       <c r="P1006" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q1006" s="1"/>
+      <c r="Q1006" s="1" t="inlineStr">
+        <is>
+          <t>LAIT</t>
+        </is>
+      </c>
     </row>
     <row r="1007">
       <c r="A1007" s="2" t="n">
@@ -61071,11 +61039,19 @@
       </c>
       <c r="E1007" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
-        </is>
-      </c>
-      <c r="F1007" s="1"/>
-      <c r="G1007" s="1"/>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F1007" s="1" t="inlineStr">
+        <is>
+          <t>PIKINE</t>
+        </is>
+      </c>
+      <c r="G1007" s="1" t="inlineStr">
+        <is>
+          <t>Baye Cheikh</t>
+        </is>
+      </c>
       <c r="H1007" s="1"/>
       <c r="I1007" s="1" t="inlineStr">
         <is>
@@ -61083,10 +61059,10 @@
         </is>
       </c>
       <c r="J1007" s="1" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="K1007" s="1" t="n">
-        <v>45900.0</v>
+        <v>900.0</v>
       </c>
       <c r="L1007" s="1" t="n">
         <v>0.0</v>
@@ -61094,16 +61070,24 @@
       <c r="M1007" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="N1007" s="1"/>
+      <c r="N1007" s="1" t="inlineStr">
+        <is>
+          <t>Nd</t>
+        </is>
+      </c>
       <c r="O1007" s="1" t="n">
-        <v>647.0</v>
+        <v>661.0</v>
       </c>
       <c r="P1007" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q1007" s="1"/>
+      <c r="Q1007" s="1" t="inlineStr">
+        <is>
+          <t>LAIT</t>
+        </is>
+      </c>
     </row>
     <row r="1008">
       <c r="A1008" s="2" t="n">
@@ -61124,11 +61108,19 @@
       </c>
       <c r="E1008" s="1" t="inlineStr">
         <is>
-          <t>Stock Descente</t>
-        </is>
-      </c>
-      <c r="F1008" s="1"/>
-      <c r="G1008" s="1"/>
+          <t>Vente</t>
+        </is>
+      </c>
+      <c r="F1008" s="1" t="inlineStr">
+        <is>
+          <t>PIKINE</t>
+        </is>
+      </c>
+      <c r="G1008" s="1" t="inlineStr">
+        <is>
+          <t>Saly THIOUNE</t>
+        </is>
+      </c>
       <c r="H1008" s="1"/>
       <c r="I1008" s="1" t="inlineStr">
         <is>
@@ -61136,10 +61128,10 @@
         </is>
       </c>
       <c r="J1008" s="1" t="n">
-        <v>8.875</v>
+        <v>3.5833333</v>
       </c>
       <c r="K1008" s="1" t="n">
-        <v>102062.5</v>
+        <v>41208.332</v>
       </c>
       <c r="L1008" s="1" t="n">
         <v>0.0</v>
@@ -61147,16 +61139,24 @@
       <c r="M1008" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="N1008" s="1"/>
+      <c r="N1008" s="1" t="inlineStr">
+        <is>
+          <t>Nd</t>
+        </is>
+      </c>
       <c r="O1008" s="1" t="n">
-        <v>648.0</v>
+        <v>662.0</v>
       </c>
       <c r="P1008" s="1" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="Q1008" s="1"/>
+      <c r="Q1008" s="1" t="inlineStr">
+        <is>
+          <t>THE</t>
+        </is>
+      </c>
     </row>
     <row r="1009">
       <c r="A1009" s="2" t="n">

--- a/Donnees_Promoteurs.xlsx
+++ b/Donnees_Promoteurs.xlsx
@@ -15,7 +15,20 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
